--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -67,7 +67,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -97,6 +97,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE6CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0F7FA"/>
       </patternFill>
     </fill>
     <fill>
@@ -136,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -156,13 +161,16 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -180,6 +188,8 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -545,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -556,9 +566,11 @@
     <col width="55" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="42" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="42" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -604,15 +616,25 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Art. @legislacao</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Texto @legislacao (vigente)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Divergência face ao Regulamento</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Necessidade de Alteração</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Notas de Reunião</t>
         </is>
@@ -673,15 +695,27 @@
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
+          <t>n.ºs 1, 2 e 3 do art.º 5.º do DL n.º 82/2019, de 27 de junho</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>1 — A identificação dos animais de companhia, pela sua marcação e registo no SIAC, deve ser realizada até 120 dias após o seu nascimento.
+2 — Na impossibilidade de determinar a data de nascimento exata, para efeitos de contagem do prazo referido no número anterior, a identificação deve ser efetuada até à perda dos dentes incisivos de leite.
+3 — Sem prejuízo dos números anteriores, e relativamente aos cães, gatos e furões que sejam cedidos e ou comercializados a partir de um criador ou de um estabelecimento autorizado para a detenção de animais de companhia, nomeadamente os centros de hospedagem com ou sem fins lucrativos e os centros de recolha oficiais, deve ser assegurada a sua marcação e registo no SIAC antes de abandonarem a instalação de nascimento ou de alojamento, independentemente da sua idade.</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
           <t>O @regulamento fixa o prazo de identificação em 3 meses para nascimentos e 30 dias para entrada em estabelecimentos. O @codigo fixa entre 3 e 6 meses, sem distinguir o contexto de estabelecimento. O @rgbeac alinha com o @regulamento mas aplica-se apenas a cães, gatos e furões.</t>
         </is>
       </c>
-      <c r="J2" s="8" t="inlineStr">
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="K2" s="9" t="inlineStr"/>
+      <c r="M2" s="10" t="inlineStr"/>
     </row>
     <row r="3" ht="120" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -735,15 +769,27 @@
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
+          <t>n.ºs 1, 2 e 3 do art.º 7.º do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
+2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
+3 — São proibidas todas as violências contra animais, considerando-se como tais os atos consistentes em, sem necessidade, se infligir a morte, o sofrimento ou lesões a um animal.</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
           <t>O @regulamento especifica o limite de 5 animais por família de acolhimento e atribui responsabilidade ao operador (não à família). O @rgbeac e o @codigo centram a responsabilidade no detentor individual, sem distinguir o contexto de acolhimento temporário nem fixar limites numéricos.</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr"/>
+      <c r="M3" s="10" t="inlineStr"/>
     </row>
     <row r="4" ht="120" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -806,15 +852,35 @@
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
+          <t>n.º 1 do art.º 3.º-A do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>1 — A mera comunicação prévia a que se refere a alínea a) do n.º 1 do artigo anterior é dirigida à DGAV e deve conter os seguintes elementos, quando aplicáveis:
+a) O nome ou a denominação social do interessado;
+b) A localização do alojamento e a sua designação comercial;
+c) O número de identificação fiscal ou de pessoa coletiva do interessado;
+d) Municípios integrantes, no caso dos centros de recolha intermunicipais;
+e) Caracterização das atividades a exercer;
+f) Indicação do médico veterinário responsável pelo alojamento;
+g) O número de celas de quarentena para isolamento de animais por suspeita de raiva, no caso dos centros de recolha;
+h) A capacidade máxima de animais e respetivas espécies a alojar;
+i) O número de animais detidos, espécies e raças;
+j) Declaração de responsabilidade, subscrita pelo interessado, relativa ao cumprimento da legislação aplicável aos animais de companhia, nomeadamente em matéria de instalações, equipamentos, higiene, saúde e bem-estar dos animais.</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
           <t>O @regulamento exige notificação prévia das autoridades com dados detalhados (capacidade, raças, ninhadas estimadas). O @codigo regula condições de reprodução mas não prevê registo ou notificação de estabelecimentos criadores. O @rgbeac trata da esterilização de errantes, não da notificação de criadores — há uma lacuna normativa face ao @regulamento.</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr"/>
+      <c r="M4" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -827,7 +893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -835,80 +901,92 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>DIPLOMA</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr"/>
+      <c r="B1" s="11" t="inlineStr"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>@regulamento (texto EN)</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Cor de fundo: #D6E4F0</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>@regulamento (tradução PT)</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Cor de fundo: #EBF5FB</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>@rgbeac</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Cor de fundo: #D5E8D4</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>@codigo</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Cor de fundo: #FFE6CC</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>@legislacao (legislação vigente)</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>Cor de fundo: #E0F7FA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>Divergência</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Cor de fundo: #EAD7F7</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Notas de Reunião</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Cor de fundo: #F5F5F5</t>
         </is>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -881,6 +881,249 @@
         </is>
       </c>
       <c r="M4" s="10" t="inlineStr"/>
+    </row>
+    <row r="5" ht="120" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Princípios Gerais de Bem-Estar</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 5.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Operators shall apply the following general welfare principles with respect to dogs or cats bred or kept in their establishment:
+(a) dogs and cats are provided with water and feed of a quality and of a quantity that enables them to have appropriate nutrition and hydration;
+(b) dogs and cats are kept in an appropriate and regularly cleaned physical environment which is secure and comfortable, especially in terms of space, air quality, temperature, light, protection against adverse climatic conditions and ease of movement, preventing overcrowding;
+(c) dogs and cats are kept safe, clean and in good health by preventing diseases, injuries, and pain, due in particular to management, handling practices and breeding practices;
+(d) dogs and cats are kept in an environment that enables them to exhibit species-specific and social non-harmful behaviour, and to establish a positive relationship with human beings;
+(e) dogs and cats are kept in such a way as to optimise their mental state by preventing or reducing negative stimuli in duration and intensity, as well as by maximising opportunities for positive stimuli in duration and intensity, preventing the development of abnormal repetitive and other behaviours indicative of negative animal welfare, and taking into consideration the individual dog's or cat's needs in the different domains referred to in points (a) to (d).</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Os operadores devem aplicar os seguintes princípios gerais de bem-estar aos cães e gatos criados ou detidos nos seus estabelecimentos:
+(a) os cães e gatos são alimentados e abebeirados com água e ração de qualidade e quantidade adequadas a uma nutrição e hidratação apropriadas;
+(b) os cães e gatos são mantidos num ambiente físico adequado, regularmente limpo, seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, iluminação, proteção face a condições climáticas adversas e facilidade de movimentação, prevenindo a sobrelotação;
+(c) os cães e gatos são mantidos seguros, limpos e com boa saúde, prevenindo doenças, lesões e dor, nomeadamente através de práticas de maneio, manuseamento e reprodução adequadas;
+(d) os cães e gatos são mantidos num ambiente que lhes permite exibir comportamentos específicos da espécie e comportamentos sociais não nocivos, e estabelecer uma relação positiva com os seres humanos;
+(e) os cães e gatos são mantidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo estímulos negativos em duração e intensidade, maximizando oportunidades de estímulos positivos, prevenindo o desenvolvimento de comportamentos repetitivos anormais, tendo em conta as necessidades individuais do animal nos domínios referidos nas alíneas (a) a (d).</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>al. a) do n.º 1 do art.º 10.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1 — O detentor do animal de companhia deve:
+a) Assegurar o bem-estar do animal, de acordo com sua espécie, raça, idade e necessidades físicas e etológicas, proporcionando-lhe:
+— Atenção, supervisão, controlo, exercício físico e estímulo mental;
+— Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável;
+— Condições higiossanitárias que atendam, no mínimo, ao estabelecido no presente decreto-lei e na demais legislação aplicável;
+— Liberdade de movimento, sendo proibidos todos os sistemas de contenção permanentes;
+— Abrigo adequado, em termos de tamanho e qualidade, com vista a proteger de condições atmosféricas adversas, incluindo frio, chuva, sol ou calor excessivos, com cama seca, limpa e confortável;
+— Contato social adequado a cada espécie, de acordo com a sua idade e atividade.</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>n.ºs 1, 2 e 3 do art.º 5.º do Código do Animal (DL n.º 214/2013)</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal.
+2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
+3 — É proibida a violência contra animais, considerando-se como tal todos os atos que, sem necessidade, infligem a morte, o sofrimento, abuso ou lesões a um animal.</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>n.º 1 do art.º 7.º e n.º 1 do art.º 9.º do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 7.º, n.º 1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
+Artigo 9.º, n.º 1 — A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam.</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>O @regulamento enuncia explicitamente 5 domínios de bem-estar — nutrição, ambiente, saúde, comportamento e estado mental — como obrigação vinculativa dos operadores de estabelecimentos. A @legislacao (DL n.º 276/2001, art.ºs 7.º e 9.º) e o @codigo (art.º 5.º) consagram os mesmos parâmetros de bem-estar, mas sem formulação sistemática nos 5 domínios: o @codigo refere 'parâmetros de bem-estar animal' genericamente; o DL n.º 276/2001 desenvolve cada parâmetro em artigos separados (alojamento, alimentação, ambiente) mas sem os denominar domínios. O @rgbeac (art.º 10.º, n.º 1, al. a)) articula obrigações equivalentes ao nível do detentor mas de forma descritiva, não sistematizada nos 5 domínios. Nenhum diploma nacional adota formalmente a nomenclatura dos 5 domínios OMSA como o @regulamento.</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr"/>
+    </row>
+    <row r="6" ht="120" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Estratégias de Criação — Conformação e Consanguinidade</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 6.a do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Operators of breeding establishments shall ensure that their breeding strategies minimise the risk of producing dogs or cats with genotypes associated with detrimental effects on their health and welfare.
+Operators of breeding establishments shall not use for reproduction dogs or cats that have excessive conformational traits leading to a high risk of detrimental effects on the welfare of these dogs or cats, or of their offspring. Before selection for breeding of a dog or cat that may be concerned by an excessive conformational trait the operator shall consult a veterinarian or an independent qualified person under the responsibility of a veterinarian.
+The following shall be prohibited in the management of the reproduction of dogs and cats:
+(a) the breeding between parents and offspring, between siblings, between half-siblings or between grandparents and grandchildren, unless approved by the competent authority based on a specific need to preserve local breeds with a limited genetic pool;
+(b) the breeding to produce hybrids.</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
+Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem traços conformacionais excessivos que conduzam a um risco elevado de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por traço conformacional excessivo, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária.
+São proibidos na gestão da reprodução de cães e gatos:
+(a) o cruzamento entre progenitores e descendentes, entre irmãos, entre meios-irmãos ou entre avós e netos, exceto com aprovação da autoridade competente por razão de necessidade específica de preservação de raças locais com reserva genética limitada;
+(b) o cruzamento para produção de híbridos.</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>n.ºs 1 e 2 do art.º 34.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1 — As intervenções cirúrgicas com o objetivo da modificação da aparência ou com fins não curativos ou não destinados a impedir a reprodução dos animais são proibidas, nos termos do disposto na alínea i) do n.º 1 do artigo 12.º.
+2 — O detentor de animal sujeito a intervenção curativa que modifique a sua aparência deve possuir documento comprovativo da necessidade da mesma, passado pelo médico veterinário que a ela procedeu, sob a forma de atestado do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura, ou, no caso de animais importados, documento comprovativo da necessidade dessa intervenção, emitida pelo médico veterinário que a ela procedeu, legalizado pela autoridade competente do respetivo país.</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>n.º 2, als. a), b) e c) do art.º 8.º do Código do Animal (DL n.º 214/2013)</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>2 — A reprodução de animais obedece ao seguinte:
+a) Os animais só devem ser utilizados na reprodução depois de atingida a maturidade reprodutiva para a espécie e raça devendo, no caso dos cães e gatos, seguir os parâmetros referidos no anexo I ao presente diploma, do qual faz parte integrante, não sendo autorizado, no caso das fêmeas, o acasalamento em cios sucessivos;
+b) Deve ser respeitada a regra do porte semelhante dos progenitores, para prevenir a possibilidade de distócia;
+c) Devem ser excluídos da reprodução, os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia da anca nos cães e rim poliquístico nos gatos, ou alterações comportamentais.</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>art.º 17.º e n.º 1 do art.º 18.º do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 17.º — As intervenções cirúrgicas, nomeadamente as destinadas ao corte de caudas nos canídeos, têm de ser executadas por um médico veterinário.
+Artigo 18.º, n.º 1 — Os detentores de animais de companhia que os apresentem com quaisquer amputações que modifiquem a aparência dos animais ou com fins não curativos devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa amputação, nomeadamente discriminando que as mesmas foram feitas por razões médico-veterinárias ou no interesse particular do animal ou para impedir a reprodução.</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>O @regulamento proíbe traços conformacionais excessivos e impõe consulta veterinária prévia ao acasalamento de animais potencialmente afetados, além de proibir consanguinidade próxima (pais/filhos, irmãos, avós/netos) e produção de híbridos. Estas exigências são inteiramente novas no direito nacional: a @legislacao (DL n.º 276/2001, art.ºs 17.º e 18.º) limita-se a exigir intervenção veterinária em cirurgias e documentação para amputações, sem abordar conformação ou consanguinidade. O @codigo (art.º 8.º, n.º 2) exclui da reprodução animais com defeitos genéticos e malformações, e proíbe acasalamento em cios sucessivos, mas não prevê o conceito de traços conformacionais excessivos nem proíbe consanguinidade. O @rgbeac (art.º 34.º) proíbe apenas intervenções cirúrgicas de modificação da aparência, sem norma sobre estratégia genética. Lacuna normativa transversal a toda a legislação nacional quanto ao núcleo central do art.º 6.a do @regulamento.</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr"/>
+    </row>
+    <row r="7" ht="120" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Saúde e Monitorização Sanitária</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 13.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Operators shall ensure that:
+(a) dogs or cats under their responsibility are inspected by animal caretakers at least once a day and vulnerable dogs and cats, such as newborns, ill or injured dogs and cats, and peri-partum bitches and queens, are inspected more frequently;
+(b) dogs or cats with compromised welfare are, where necessary, transferred without undue delay to a separate area and, where needed, receive appropriate treatment;
+(c) where the recovery of a dog or a cat with compromised welfare is not achievable and the dog or cat experiences severe pain or suffering, a veterinarian is consulted without undue delay, to decide whether the dog or cat shall be euthanised to end its suffering, and, if that is the case, to perform the euthanasia using anesthesia and analgesia;
+(d) measures to prevent and control external and internal parasites, and vaccinations to prevent common diseases to which dogs or cats are likely to be exposed are implemented.
+Operators of breeding establishments shall additionally ensure that:
+(-a) bitches or queens are only bred if they have reached a minimum age and skeletal maturity in accordance with point 3 of Annex I, and they have no diagnosed disease, clinical sign of diseases or physical conditions which could negatively impact their pregnancy and welfare;
+(-b) litter-giving pregnancies of bitches or queens follows a maximum frequency in accordance with point 3 of Annex I;
+(-c) lactating queens are not mated or inseminated.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Os operadores devem assegurar que:
+(a) os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados, fêmeas em período peri-parto, são inspecionados com maior frequência;
+(b) os cães e gatos com bem-estar comprometido são transferidos, quando necessário, sem demora injustificada para área separada e, se necessário, recebem tratamento adequado;
+(c) quando a recuperação de um animal com bem-estar comprometido não seja alcançável e o animal experiencie dor ou sofrimento severo, um médico veterinário é consultado sem demora injustificada para decidir sobre a eutanásia, que, se realizada, é executada com anestesia e analgesia;
+(d) são implementadas medidas de prevenção e controlo de parasitas externos e internos, bem como vacinações para prevenção de doenças comuns.
+Os operadores de estabelecimentos de criação devem adicionalmente assegurar que:
+(-a) as cadelas ou gatas só são reproduzidas se tiverem atingido a idade mínima e maturidade esquelética nos termos do Anexo I, e não apresentem doença diagnosticada, sinais clínicos ou condições físicas que possam impactar negativamente a gestação e o bem-estar;
+(-b) a frequência de gestações com ninhadas respeita o máximo fixado no Anexo I;
+(-c) as gatas a lactar não são acasaladas nem inseminadas.</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>n.ºs 1, 2 e 3 do art.º 33.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1 — Os detentores dos animais de companhia devem assegurar-lhes os cuidados de saúde adequados, nomeadamente seguindo as orientações da DGAV em matéria de vacinação e tratamentos obrigatórios, bem como consultas regulares junto de médico veterinário.
+2 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
+3 — Os médicos veterinários e os centros de atendimento médico-veterinário (CAMV) devem manter um arquivo com os dados clínicos de cada animal, pelo período mínimo de cinco anos, que ficará à disposição das autoridades competentes.</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>art.º 6.º do Código do Animal (DL n.º 214/2013)</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>O detentor do animal deve assegurar ao animal ferido ou doente os cuidados médico-veterinários adequados, designadamente retirando o mesmo do alojamento sempre que este seja um local de venda.</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>n.ºs 1 e 3 do art.º 13.º e n.ºs 1 e 2 do art.º 16.º do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 13.º, n.º 1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
+Artigo 13.º, n.º 3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados aos que tiverem sinais que levem a suspeitar estarem doentes, lesionados ou com alterações comportamentais.
+Artigo 16.º, n.º 1 — Sem prejuízo de quaisquer medidas determinadas pela DGAV, deve existir um programa de profilaxia médica e sanitária devidamente elaborado e supervisionado pelo médico veterinário responsável e executado por profissionais competentes.
+Artigo 16.º, n.º 2 — No âmbito do número anterior, os animais devem ser sujeitos a exames médico-veterinários de rotina, vacinações e desparasitações sempre que aconselhável.</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>O @regulamento impõe inspeção diária por cuidadores, isolamento imediato de animais com bem-estar comprometido e condições específicas para reprodução em criadores (idade mínima da fêmea, frequência máxima de partos por ninhada, proibição de cobrição de gatas a lactar). A @legislacao (DL n.º 276/2001, art.ºs 13.º e 16.º) prevê inspeção diária e programa de profilaxia supervisionado por veterinário — alinhamento parcial com o @regulamento — mas não fixa condições sanitárias específicas para a reprodução em criadores. O @rgbeac (art.º 33.º) centra os cuidados de saúde no detentor em geral, sem distinguir obrigações reforçadas para operadores de criação. O @codigo (art.º 6.º) limita o dever de cuidados médico-veterinários ao animal ferido ou doente, sem obrigação de inspeção sistemática nem regras sanitárias de criação. A @legislacao vigente é a mais próxima do @regulamento neste eixo, mas apresenta lacuna relevante nas condições sanitárias específicas da reprodução.</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -141,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -171,6 +171,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -555,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -568,9 +571,12 @@
     <col width="55" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
-    <col width="42" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="38" customWidth="1" min="11" max="11"/>
+    <col width="38" customWidth="1" min="12" max="12"/>
+    <col width="38" customWidth="1" min="13" max="13"/>
+    <col width="38" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -626,15 +632,30 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Divergência face ao Regulamento</t>
+          <t>Div. vs @legislacao</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Div. vs @codigo</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Div. vs @rgbeac</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Sumário / Proposta</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Necessidade de Alteração</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Notas de Reunião</t>
         </is>
@@ -707,15 +728,30 @@
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>O @regulamento fixa o prazo de identificação em 3 meses para nascimentos e 30 dias para entrada em estabelecimentos. A @legislacao (DL n.º 82/2019, art.º 5.º) prevê um prazo geral de 120 dias após o nascimento, sem distinguir o contexto de estabelecimento — prazo superior ao fixado pelo @regulamento e que exigirá redução. O @codigo fixa entre 3 e 6 meses, igualmente sem distinção de contexto. O @rgbeac alinha com o @regulamento nos prazos, mas aplica-se apenas a cães, gatos e furões. Nenhum dos diplomas nacionais vigentes distingue o prazo de 30 dias aplicável a animais que entram em estabelecimentos, previsto no @regulamento.</t>
+          <t>O DL n.º 82/2019 (art.º 5.º) prevê prazo geral de 120 dias após o nascimento, sem distinguir o contexto de estabelecimento — prazo superior ao máximo de 3 meses do @regulamento, que exigirá redução. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
+          <t>O @codigo fixa prazo de identificação entre 3 e 6 meses, igualmente sem distinção entre nascimentos e entrada em estabelecimentos, ficando aquém da precisão exigida pelo @regulamento.</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac aproxima-se dos prazos do @regulamento mas aplica-se apenas a cães, gatos e furões. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
+        </is>
+      </c>
+      <c r="N2" s="11" t="inlineStr">
+        <is>
+          <t>Necessidade de alteração: (1) reduzir prazo máximo de identificação de nascimentos para 3 meses; (2) criar prazo diferenciado de 30 dias para animais admitidos em estabelecimentos; (3) harmonizar prazos entre todos os diplomas nacionais.</t>
+        </is>
+      </c>
+      <c r="O2" s="11" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="M2" s="10" t="inlineStr"/>
+      <c r="P2" s="11" t="inlineStr"/>
     </row>
     <row r="3" ht="120" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -781,15 +817,30 @@
       </c>
       <c r="K3" s="8" t="inlineStr">
         <is>
-          <t>O @regulamento especifica o limite de 5 animais por família de acolhimento e atribui responsabilidade ao operador (não à família). A @legislacao (DL n.º 276/2001, art.º 7.º) centra a responsabilidade no detentor, sem distinguir o contexto de acolhimento temporário nem fixar limites numéricos — posição idêntica à do @rgbeac e do @codigo. Nenhum dos diplomas nacionais, incluindo a legislação vigente, prevê o conceito de família de acolhimento nem o limite numérico de 5 animais estabelecido pelo @regulamento. A lacuna é transversal a toda a legislação nacional.</t>
+          <t>O DL n.º 276/2001 (art.º 7.º) centra a responsabilidade no detentor em geral, sem distinguir o contexto de acolhimento temporário nem fixar limites numéricos de animais por família. O conceito de família de acolhimento é inexistente na legislação vigente.</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
         <is>
+          <t>O @codigo não prevê o conceito de família de acolhimento nem qualquer limite numérico de animais por unidade. A responsabilidade do operador como figura distinta do detentor particular também não é contemplada.</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac menciona famílias de acolhimento temporário mas não fixa o limite de 5 animais por família de acolhimento nem especifica que a responsabilidade jurídica recai sobre o operador e não sobre a família.</t>
+        </is>
+      </c>
+      <c r="N3" s="11" t="inlineStr">
+        <is>
+          <t>Lacuna transversal a toda a legislação nacional. Necessidade de: (1) criar o conceito de 'família de acolhimento' como extensão da atividade do operador; (2) fixar limite numérico de animais por família (máximo 5, ou 1 ninhada com mãe); (3) atribuir responsabilidade jurídica ao operador, não à família de acolhimento.</t>
+        </is>
+      </c>
+      <c r="O3" s="11" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="M3" s="10" t="inlineStr"/>
+      <c r="P3" s="11" t="inlineStr"/>
     </row>
     <row r="4" ht="120" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -872,15 +923,30 @@
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>O @regulamento exige notificação prévia com dados detalhados, incluindo o número estimado de ninhadas a colocar no mercado por ano (al. ea)). A @legislacao (DL n.º 276/2001, art.º 3.º-A) já prevê comunicação prévia à DGAV com elementos parcialmente equivalentes (capacidade máxima, espécies, raças — als. h) e i)), mas não exige a estimativa de ninhadas, constituindo lacuna parcial face ao @regulamento. O @codigo regula condições de reprodução mas não prevê notificação ou registo de estabelecimentos criadores. O @rgbeac trata exclusivamente da esterilização de errantes, sem qualquer norma sobre notificação de criadores. A @legislacao vigente é, dos diplomas nacionais, o mais próximo do @regulamento neste eixo, ainda que com lacuna relevante.</t>
+          <t>O DL n.º 276/2001 (art.º 3.º-A) prevê comunicação prévia à DGAV com elementos parcialmente equivalentes (capacidade máxima, espécies, raças). Não exige a estimativa anual de ninhadas a colocar no mercado (al. ea) do @regulamento), constituindo lacuna parcial. É o diploma mais próximo do @regulamento neste eixo.</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">
         <is>
+          <t>O @codigo regula condições de reprodução (art.º 8.º) mas não prevê qualquer sistema de notificação ou registo de estabelecimentos criadores junto da autoridade competente.</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac trata da esterilização de errantes e CED, mas não contém norma sobre notificação de criadores ou registo de estabelecimentos com fins de reprodução comercial.</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="inlineStr">
+        <is>
+          <t>A @legislacao vigente é o diploma base adequado para a transposição. Necessidade de ajuste: acrescentar a obrigação de estimativa anual de ninhadas a colocar no mercado e alinhar os restantes elementos informativos com a lista exaustiva do art.º 7.º do @regulamento.</t>
+        </is>
+      </c>
+      <c r="O4" s="11" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="M4" s="10" t="inlineStr"/>
+      <c r="P4" s="11" t="inlineStr"/>
     </row>
     <row r="5" ht="120" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -955,15 +1021,30 @@
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>O @regulamento enuncia explicitamente 5 domínios de bem-estar — nutrição, ambiente, saúde, comportamento e estado mental — como obrigação vinculativa dos operadores de estabelecimentos. A @legislacao (DL n.º 276/2001, art.ºs 7.º e 9.º) e o @codigo (art.º 5.º) consagram os mesmos parâmetros de bem-estar, mas sem formulação sistemática nos 5 domínios: o @codigo refere 'parâmetros de bem-estar animal' genericamente; o DL n.º 276/2001 desenvolve cada parâmetro em artigos separados (alojamento, alimentação, ambiente) mas sem os denominar domínios. O @rgbeac (art.º 10.º, n.º 1, al. a)) articula obrigações equivalentes ao nível do detentor mas de forma descritiva, não sistematizada nos 5 domínios. Nenhum diploma nacional adota formalmente a nomenclatura dos 5 domínios OMSA como o @regulamento.</t>
+          <t>O DL n.º 276/2001 (art.ºs 7.º e 9.º) consagra os mesmos parâmetros mas desenvolve-os em artigos separados (alojamento, alimentação, ambiente) sem os denominar como domínios nem os sistematizar de forma unificada segundo o referencial OMSA.</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
+          <t>O @codigo (art.º 5.º) refere 'parâmetros de bem-estar animal' genericamente, sem adotar formalmente a nomenclatura dos 5 domínios OMSA nem a sua sistematização explícita.</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac (art.º 10.º, n.º 1, al. a)) articula obrigações equivalentes ao nível do detentor de forma descritiva, sem sistematização nos 5 domínios nem referência ao quadro OMSA.</t>
+        </is>
+      </c>
+      <c r="N5" s="11" t="inlineStr">
+        <is>
+          <t>Alinhamento substancial de conteúdo; sem necessidade de alteração imediata. Recomenda-se a adoção formal dos 5 domínios OMSA como referencial estruturante em futura revisão legislativa ou em normas de orientação técnica da DGAV.</t>
+        </is>
+      </c>
+      <c r="O5" s="11" t="inlineStr">
+        <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr"/>
+      <c r="P5" s="11" t="inlineStr"/>
     </row>
     <row r="6" ht="120" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -1031,15 +1112,30 @@
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>O @regulamento proíbe traços conformacionais excessivos e impõe consulta veterinária prévia ao acasalamento de animais potencialmente afetados, além de proibir consanguinidade próxima (pais/filhos, irmãos, avós/netos) e produção de híbridos. Estas exigências são inteiramente novas no direito nacional: a @legislacao (DL n.º 276/2001, art.ºs 17.º e 18.º) limita-se a exigir intervenção veterinária em cirurgias e documentação para amputações, sem abordar conformação ou consanguinidade. O @codigo (art.º 8.º, n.º 2) exclui da reprodução animais com defeitos genéticos e malformações, e proíbe acasalamento em cios sucessivos, mas não prevê o conceito de traços conformacionais excessivos nem proíbe consanguinidade. O @rgbeac (art.º 34.º) proíbe apenas intervenções cirúrgicas de modificação da aparência, sem norma sobre estratégia genética. Lacuna normativa transversal a toda a legislação nacional quanto ao núcleo central do art.º 6.a do @regulamento.</t>
+          <t>O DL n.º 276/2001 (art.ºs 17.º e 18.º) exige intervenção veterinária em cirurgias e documentação para amputações, mas não prevê qualquer restrição à reprodução por traços conformacionais excessivos nem proibição de consanguinidade próxima ou hibridação.</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
+          <t>O @codigo (art.º 8.º, n.º 2) exclui da reprodução animais com defeitos genéticos e malformações (displasia, rim poliquístico) e proíbe cios sucessivos, mas não prevê o conceito de traços conformacionais excessivos nem a proibição de consanguinidade.</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac (art.º 34.º) proíbe intervenções cirúrgicas de modificação da aparência, mas não contém qualquer norma sobre estratégia genética de criação, conformação excessiva ou consanguinidade.</t>
+        </is>
+      </c>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>Lacuna normativa transversal. Necessidade de criar norma específica que: (1) defina traços conformacionais excessivos (a regular por ato delegado europeu até 2030); (2) proíba consanguinidade próxima (pais/filhos, irmãos, avós/netos); (3) proíba a produção de híbridos; (4) imponha consulta veterinária prévia ao acasalamento de animais potencialmente afetados.</t>
+        </is>
+      </c>
+      <c r="O6" s="11" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="M6" s="10" t="inlineStr"/>
+      <c r="P6" s="11" t="inlineStr"/>
     </row>
     <row r="7" ht="120" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -1115,15 +1211,30 @@
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>O @regulamento impõe inspeção diária por cuidadores, isolamento imediato de animais com bem-estar comprometido e condições específicas para reprodução em criadores (idade mínima da fêmea, frequência máxima de partos por ninhada, proibição de cobrição de gatas a lactar). A @legislacao (DL n.º 276/2001, art.ºs 13.º e 16.º) prevê inspeção diária e programa de profilaxia supervisionado por veterinário — alinhamento parcial com o @regulamento — mas não fixa condições sanitárias específicas para a reprodução em criadores. O @rgbeac (art.º 33.º) centra os cuidados de saúde no detentor em geral, sem distinguir obrigações reforçadas para operadores de criação. O @codigo (art.º 6.º) limita o dever de cuidados médico-veterinários ao animal ferido ou doente, sem obrigação de inspeção sistemática nem regras sanitárias de criação. A @legislacao vigente é a mais próxima do @regulamento neste eixo, mas apresenta lacuna relevante nas condições sanitárias específicas da reprodução.</t>
+          <t>O DL n.º 276/2001 (art.ºs 13.º e 16.º) prevê inspeção diária e programa de profilaxia supervisionado por veterinário — alinhamento parcial. Não fixa condições sanitárias específicas para reprodução em criadores: sem idade mínima da fêmea, sem frequência máxima de partos, sem proibição de cobrição de fêmeas a lactar.</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
+          <t>O @codigo (art.º 6.º) limita o dever de cuidados médico-veterinários ao animal ferido ou doente, sem obrigação de inspeção diária sistemática nem quaisquer regras sanitárias específicas para a reprodução em criadores.</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac (art.º 33.º) centra os cuidados de saúde no detentor em geral, sem distinguir obrigações reforçadas para operadores de criação nem fixar condições específicas para a reprodução (idade mínima, frequência de partos, lactação).</t>
+        </is>
+      </c>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>A @legislacao vigente é o diploma mais próximo do @regulamento. Necessidade de alteração dirigida a criadores: introduzir (1) requisitos mínimos de idade e maturidade das fêmeas; (2) frequência máxima de partos conforme Anexo I do @regulamento; (3) proibição de cobrição de fêmeas a lactar; alinhando com o regime sanitário do art.º 13.º.</t>
+        </is>
+      </c>
+      <c r="O7" s="11" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="M7" s="10" t="inlineStr"/>
+      <c r="P7" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1144,92 +1255,92 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>DIPLOMA</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr"/>
+      <c r="B1" s="12" t="inlineStr"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>@regulamento (texto EN)</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>Cor de fundo: #D6E4F0</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>@regulamento (tradução PT)</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Cor de fundo: #EBF5FB</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>@rgbeac</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Cor de fundo: #D5E8D4</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>@codigo</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Cor de fundo: #FFE6CC</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>@legislacao (legislação vigente)</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Cor de fundo: #E0F7FA</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Divergência</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>Cor de fundo: #EAD7F7</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Notas de Reunião</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Cor de fundo: #F5F5F5</t>
         </is>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -1145,7 +1145,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Art.º 13.º (Health) do Regulamento 2023/0447 (PE/Conselho)</t>
+          <t>Art.º 13.º do Regulamento 2023/0447 (PE/Conselho)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1156,8 +1156,8 @@
 (c) where the recovery of a dog or a cat with compromised welfare is not achievable and the dog or cat experiences severe pain or suffering, a veterinarian is consulted without undue delay, to decide whether the dog or cat shall be euthanised to end its suffering, and, if that is the case, to perform the euthanasia using anesthesia and analgesia;
 (d) measures to prevent and control external and internal parasites, and vaccinations to prevent common diseases to which dogs or cats are likely to be exposed are implemented;
 (e) enrichment do not present a significant risk of injury or biological or chemical contamination or any other health risk.
-[dim]Point (a) shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
-[dim]Member states may grant derogations from point (c) in cases of emergencies, where no veterinarian can be reached without undue delay, provided that national rules are put in place to ensure that:
+Point (a) shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
+Member states may grant derogations from point (c) in cases of emergencies, where no veterinarian can be reached without undue delay, provided that national rules are put in place to ensure that:
 (i) an immediate action ending the life of the dog or cat with minimum pain and suffering using a method inducing instant death is undertaken by a trained competent person;
 (ii) the operator keeps a record of the use of the derogation for purposes of the official control.
 2. Operators of breeding establishments shall additionally ensure that:
@@ -1176,8 +1176,8 @@
 (c) quando a recuperação de um cão ou gato com bem-estar comprometido não seja alcançável e o animal experiencie dor ou sofrimento severo, um médico veterinário é consultado sem demora injustificada para decidir se o animal deve ser objeto de eutanásia para pôr termo ao seu sofrimento e, em caso afirmativo, para realizar a eutanásia com recurso a anestesia e analgesia;
 (d) são implementadas medidas de prevenção e controlo de parasitas externos e internos, bem como vacinações para prevenção de doenças comuns às quais os cães ou gatos são suscetíveis de estar expostos;
 (e) os enriquecimentos não apresentam risco significativo de lesões ou de contaminação biológica ou química, nem qualquer outro risco para a saúde.
-[dim]A alínea (a) não se aplica aos cães de guarda de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para fins de guarda ou treino.
-[dim]Os Estados-Membros podem conceder derrogações relativamente à alínea (c) em casos de emergência, quando não seja possível contactar um médico veterinário sem demora injustificada, desde que sejam estabelecidas regras nacionais que assegurem que:
+A alínea (a) não se aplica aos cães de guarda de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para fins de guarda ou treino.
+Os Estados-Membros podem conceder derrogações relativamente à alínea (c) em casos de emergência, quando não seja possível contactar um médico veterinário sem demora injustificada, desde que sejam estabelecidas regras nacionais que assegurem que:
 (i) é tomada imediatamente uma ação que ponha fim à vida do cão ou gato com o mínimo de dor e sofrimento, utilizando um método que induza a morte instantânea, por uma pessoa competente e devidamente habilitada;
 (ii) o operador mantém um registo da utilização da derrogação para efeitos de controlo oficial.
 2 — Os operadores de estabelecimentos de criação devem adicionalmente assegurar que:

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -674,18 +674,34 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip compliant with Annex II.
+          <t>1. All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip compliant with Annex II.
 1a. Operators shall ensure that dogs and cats born in their establishments are individually identified within 3 months after their birth and in any event before the date of their placing on the market.
 Operators of selling establishments, shelters and those placing and being responsible for dogs and cats in foster homes shall ensure that dogs and cats that enter their establishments or come under their responsibility are individually identified within 30 days after their arrival at the establishment and in any event before the date of their placing on the market.
-Pet owners and any other natural or legal persons, other than operators, who own dogs or cats, shall ensure that the dogs or cats are individually identified at the latest when the dog or cat reaches 3 months of age or, in case the dog or cat is placed on the market, before the date of their placing on the market.</t>
+Pet owners and any other natural or legal persons, other than operators, who own dogs or cats, shall ensure that the dogs or cats are individually identified at the latest when the dog or cat reaches 3 months of age or, in case the dog or cat is placed on the market, before the date of their placing on the market.
+2. The implantation of the transponder shall be performed by a veterinarian. Member States may allow the implantation of transponders in cats to be performed by a person other than a veterinarian, if it is done under the responsibility of a veterinarian.
+3. Dogs and cats which have been individually identified by means of an injectable transponder containing a microchip, in accordance with national legislation prior to entry into force of this Regulation, shall be recognised as identified in accordance with the requirements of this Article.
+4. Within two working days after their identification, the dogs and cats shall be registered by a veterinarian in a national database.
+5. For dogs and cats kept in establishments, the registration shall be made in the name of the operator of the establishment. For dogs and cats placed in foster homes, the registration shall be made in the name of the person responsible for the foster home. For dogs and cats owned by pet owners or by any other natural or legal person, the registration shall be made in the name of the pet owner or the natural or legal person.
+Member States may grant derogations from the first subparagraph to military, police and customs dogs.
+6. In case of placing on the market or occasional and irregular donation by a natural person without online advertising, the requirements for registration shall not apply.
+7. In the case of a death of a dog or a cat, the operator, pet owner or natural or legal person owning the dog or cat shall inform the national database.
+8. In case of unreadable transponder, the operator or the natural or legal person responsible for the dog or cat shall ensure that the dog or cat is re-identified with a new transponder and re-registered in the national database.</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Todos os cães e gatos mantidos em estabelecimentos colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com o Anexo II.
+          <t>1. Todos os cães e gatos mantidos em estabelecimentos colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com o Anexo II.
 1a. Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de 3 meses após o nascimento e, em qualquer caso, antes da data da sua colocação no mercado.
 Os operadores de estabelecimentos de venda, abrigos e os que colocam e são responsáveis por cães e gatos em famílias de acolhimento devem assegurar que os cães e gatos que entrem nos seus estabelecimentos sejam identificados individualmente no prazo de 30 dias após a chegada.
-Os donos de animais de companhia e quaisquer outras pessoas singulares ou coletivas que detenham cães ou gatos devem assegurar que os animais sejam identificados individualmente o mais tardar quando o animal atingir os 3 meses de idade.</t>
+Os donos de animais de companhia e quaisquer outras pessoas singulares ou coletivas que detenham cães ou gatos devem assegurar que os animais sejam identificados individualmente o mais tardar quando o animal atingir os 3 meses de idade ou, no caso de o animal ser colocado no mercado, antes da data da sua colocação no mercado.
+2. A implantação do transponder devem ser efetuada por um médico veterinário. Os Estados-Membros podem permitir que a implantação de transponders em gatos seja efetuada por pessoa que não seja médico veterinário, se for feita sob a responsabilidade de um médico veterinário.
+3. Cães e gatos que tenham sido identificados individualmente por meio de um transponder injetável contendo um microchip, em conformidade com legislação nacional anterior à entrada em vigor do presente Regulamento, são reconhecidos como identificados de acordo com os requisitos do presente artigo.
+4. No prazo de dois dias úteis após a sua identificação, os cães e gatos devem ser registados por um médico veterinário numa base de dados nacional.
+5. Para cães e gatos mantidos em estabelecimentos, o registo deve ser efetuado em nome do operador do estabelecimento. Para cães e gatos colocados em famílias de acolhimento, o registo deve ser efetuado em nome da pessoa responsável pela família de acolhimento. Para cães e gatos detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva, o registo deve ser efetuado em nome do dono ou da pessoa singular ou coletiva.
+Os Estados-Membros podem conceder derrogações ao primeiro parágrafo a cães militares, policiais e aduaneiros.
+6. Em caso de colocação no mercado ou cedência ocasional e irregular por pessoa singular sem publicidade em linha, os requisitos de registo não se aplicam.
+7. Em caso de morte de um cão ou gato, o operador, dono do animal ou pessoa singular ou coletiva proprietária devem informar a base de dados nacional.
+8. Em caso de transponder ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato devem assegurar que o animal é reidentificado com um novo transponder e re-registado na base de dados nacional.</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -766,14 +782,26 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Operators shall be responsible for the welfare of dogs or cats kept in the establishments under their responsibility and under their control and to minimise any risks to their welfare.
-1a. In the case of foster homes, the responsibility shall lie with the operator on whose behalf dogs or cats are kept. Such operators shall not place more than a total of five dogs or cats or one litter with or without mother in a foster home at any given time and shall provide the foster family with adequate information on the animal welfare obligations as well as the individual needs of the dogs or cats, and shall ensure that the relevant obligations set out by this Regulation are complied with in foster homes.</t>
+          <t>1. Operators shall be responsible for the welfare of dogs or cats kept in the establishments under their responsibility and under their control and to minimise any risks to their welfare.
+1a. In the case of foster homes, the responsibility shall lie with the operator on whose behalf dogs or cats are kept. Such operators shall not place more than a total of five dogs or cats or one litter with or without mother in a foster home at any given time and shall provide the foster family with adequate information on the animal welfare obligations as well as the individual needs of the dogs or cats, and shall ensure that the relevant obligations set out by this Regulation are complied with in foster homes. Member States where the foster home is located may provide for a greater number of dogs, cats or litters to be placed in the foster home, provided that the premises of the foster home provide sufficient space, including outdoor space, and that the number of animal caretakers in the foster home is sufficient, to ensure the welfare of the dogs or cats.
+1b. Operators shall not subject any dog or cat to cruelty, abuse or mistreatment, including through participation in activities likely to result in cruelty, abuse or mistreatment, to the dogs or cats bred or kept by the operator.
+1c. Operators shall not abandon dogs or cats.
+1d. Operators who are due to cease the activities of their establishment shall ensure the rehoming of the dogs or cats kept therein either by taking up the pet ownership or by transferring the responsibility or ownership of dogs and cats to other operators or acquirers.
+2. Operators shall ensure that dogs or cats are handled by a suitable number of animal caretakers and in order to meet the welfare needs of dogs or cats kept in their establishments and who have the competences required under Article 9.
+2a. Operators shall ensure the welfare of the dogs or cats under their responsibility by monitoring animal-based indicators concerning behaviour and physical appearance, and by taking actions based on the results of such monitoring.
+2b. The Commission is empowered to adopt delegated acts in accordance with Article 23 supplementing this Regulation by laying down animal-based indicators concerning behaviour and physical appearance and the methods of their measurement.</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Os operadores são responsáveis pelo bem-estar dos cães ou gatos mantidos nos estabelecimentos sob a sua responsabilidade e controlo e devem minimizar quaisquer riscos para o seu bem-estar.
-1a. No caso de famílias de acolhimento, a responsabilidade recai sobre o operador em nome de quem os cães ou gatos são mantidos. Esses operadores não devem colocar mais do que um total de cinco cães ou gatos ou uma ninhada com ou sem mãe numa família de acolhimento em qualquer momento e devem fornecer à família de acolhimento informação adequada sobre as obrigações de bem-estar animal, bem como as necessidades individuais dos animais.</t>
+          <t>1. Os operadores são responsáveis pelo bem-estar dos cães ou gatos mantidos nos estabelecimentos sob a sua responsabilidade e controlo e devem minimizar quaisquer riscos para o seu bem-estar.
+1a. No caso de famílias de acolhimento, a responsabilidade recai sobre o operador em nome de quem os cães ou gatos são mantidos. Esses operadores não devem colocar mais do que um total de cinco cães ou gatos ou uma ninhada com ou sem mãe numa família de acolhimento em qualquer momento e devem fornecer à família de acolhimento informação adequada sobre as obrigações de bem-estar animal, bem como as necessidades individuais dos animais, e devem assegurar que as obrigações relevantes estabelecidas por este Regulamento são cumpridas em famílias de acolhimento. Os Estados-Membros onde a família de acolhimento está localizada podem prever um número maior de cães, gatos ou ninhadas a serem colocadas na família de acolhimento, desde que as instalações da família de acolhimento providenciem espaço suficiente, incluindo espaço ao ar livre, e que o número de cuidadores de animais na família de acolhimento seja suficiente, para assegurar o bem-estar dos cães ou gatos.
+1b. Os operadores não devem sujeitar nenhum cão ou gato a crueldade, abuso ou maus-tratos, incluindo através de participação em atividades que possam resultar em crueldade, abuso ou maus-tratos, aos cães ou gatos criados ou mantidos pelo operador.
+1c. Os operadores não devem abandonar cães ou gatos.
+1d. Os operadores que estejam prestes a cessar as atividades do seu estabelecimento devem assegurar a reintegração dos cães ou gatos mantidos aí, quer através da assunção da posse do animal de companhia, quer através da transferência da responsabilidade ou propriedade dos cães e gatos para outros operadores ou adquirentes.
+2. Os operadores devem assegurar que os cães ou gatos são tratados por um número adequado de cuidadores de animais e de modo a satisfazer as necessidades de bem-estar dos cães ou gatos mantidos nos seus estabelecimentos e que têm as competências exigidas no artigo 9.º.
+2a. Os operadores devem assegurar o bem-estar dos cães ou gatos sob a sua responsabilidade através da monitorização de indicadores baseados no comportamento e aparência física, e através da adoção de ações com base nos resultados de tal monitorização.
+2b. A Comissão tem competência para adotar atos delegados em conformidade com o artigo 23.º que complementem este Regulamento através do estabelecimento de indicadores baseados no bem-estar dos animais relativos ao comportamento e aparência física e dos métodos da sua medição.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -1054,23 +1082,31 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Art.º 6.a do Regulamento 2023/0447</t>
+          <t>Art.º 6.º-A do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Operators of breeding establishments shall ensure that their breeding strategies minimise the risk of producing dogs or cats with genotypes associated with detrimental effects on their health and welfare.
-Operators of breeding establishments shall not use for reproduction dogs or cats that have excessive conformational traits leading to a high risk of detrimental effects on the welfare of these dogs or cats, or of their offspring. Before selection for breeding of a dog or cat that may be concerned by an excessive conformational trait the operator shall consult a veterinarian or an independent qualified person under the responsibility of a veterinarian.
-The following shall be prohibited in the management of the reproduction of dogs and cats:
+          <t>1. Operators of breeding establishments shall ensure that their breeding strategies minimise the risk of producing dogs or cats with genotypes associated with detrimental effects on their health and welfare.
+2. Operators of breeding establishments shall not use for reproduction dogs or cats that have excessive conformational traits leading to a high risk of detrimental effects on the welfare of these dogs or cats, or of their offspring. Before selection for breeding of a dog or cat that may be concerned by an excessive conformational trait the operator shall consult a veterinarian or an independent qualified person under the responsibility of a veterinarian. The veterinarian or independent qualified person shall assess whether the dog or cat has an excessive conformational trait.
+3. The Commission is empowered to adopt, taking into account scientific opinions of the European Food Safety Authority as well as the social and economic impacts, delegated acts in accordance with Article 23 supplementing this Regulation by:
+(a) defining characteristics of the genotypes referred to in paragraph 1, which shall be excluded from reproduction, and the methods for their assessment and the record keeping requirements;
+(b) defining excessive conformational traits referred to in paragraph 2 of this Article, which shall be excluded from reproduction, the methods for their assessment and the record keeping requirements.
+4. The delegated acts concerning the excessive conformational traits shall be adopted by 1 July 2030. The delegated acts concerning the genotypes shall be adopted by 1 July 2036.
+5. The following shall be prohibited in the management of the reproduction of dogs and cats:
 (a) the breeding between parents and offspring, between siblings, between half-siblings or between grandparents and grandchildren, unless approved by the competent authority based on a specific need to preserve local breeds with a limited genetic pool;
 (b) the breeding to produce hybrids.</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
-Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem traços conformacionais excessivos que conduzam a um risco elevado de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por traço conformacional excessivo, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária.
-São proibidos na gestão da reprodução de cães e gatos:
+          <t>1. Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
+2. Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem traços conformacionais excessivos que conduzam a um risco elevado de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por traço conformacional excessivo, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem um traço conformacional excessivo.
+3. A Comissão tem competência para adotar, tendo em conta os pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, bem como os impactos sociais e económicos, atos delegados em conformidade com o artigo 23.º que complementem este Regulamento:
+(a) definindo características dos genótipos a que se refere o parágrafo 1, que devem ser excluídos da reprodução, e os métodos para a sua avaliação e requisitos de manutenção de registos;
+(b) definindo traços conformacionais excessivos a que se refere o parágrafo 2 do presente artigo, que devem ser excluídos da reprodução, os métodos para a sua avaliação e requisitos de manutenção de registos.
+4. Os atos delegados relativos aos traços conformacionais excessivos devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
+5. São proibidos na gestão da reprodução de cães e gatos:
 (a) o cruzamento entre progenitores e descendentes, entre irmãos, entre meios-irmãos ou entre avós e netos, exceto com aprovação da autoridade competente por razão de necessidade específica de preservação de raças locais com reserva genética limitada;
 (b) o cruzamento para produção de híbridos.</t>
         </is>
@@ -1262,6 +1298,302 @@
         </is>
       </c>
       <c r="P7" s="11" t="inlineStr"/>
+    </row>
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Detenção Responsável e Informação</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 8.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Operators shall provide to the acquirer of a dog or cat written information necessary to enable him or her to ensure the welfare of the dog or cat including information on responsible ownership and on the specific needs of the dog or cat in terms of feeding, caring, health, housing and behavioural needs, as well as information on its health.
+1a. The written information on the dog or cat's health referred to in the first paragraph shall include at least:
+(a) the dog or cat's vaccination status;
+(b) any medical conditions or predispositions to diseases, including allergies, that are known by the operator, and any diagnostic test results for the dog or cat that are available to the operator.
+In case the information on the dog's or cat's health is documented in a document required under Regulation (EU) 2016/429, the operator shall transmit that document to the acquirer.</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Os operadores devem fornecer ao adquirente de um cão ou gato informação escrita necessária para lhe permitir assegurar o bem-estar do cão ou gato, incluindo informação sobre detenção responsável e sobre as necessidades específicas do cão ou gato em termos de alimentação, cuidados, saúde, alojamento e necessidades comportamentais, bem como informação sobre a sua saúde.
+1a. A informação escrita sobre a saúde do cão ou gato referida no parágrafo anterior deve incluir pelo menos:
+(a) o estado de vacinação do cão ou gato;
+(b) quaisquer condições médicas ou predisposições a doenças, incluindo alergias, conhecidas pelo operador, e quaisquer resultados de testes de diagnóstico para o cão ou gato que estejam disponíveis para o operador.
+Caso a informação sobre a saúde do cão ou gato esteja documentada num documento exigido sob o Regulamento (UE) 2016/429, o operador deve transmitir esse documento ao adquirente.</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Art.º 8.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>1 — O detentor do animal de companhia deve possuir informação sobre as obrigações inerentes à sua detenção, incluindo direitos e responsabilidades, normas de bem-estar, cuidados de saúde, comportamento, necessidades específicas da espécie/raça, duração de vida esperada, custos de manutenção, e proibição de abandono.
+2 — Os comerciantes devem fornecer por escrito ao adquirente informação completa antes da transferência do animal, incluindo identidade e dados de contacto do comerciante, dados de identificação do animal, cuidados de saúde e estado de vacinação, e certificado de origem ou de compatibilidade quando aplicável.</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Art.º 57.º do Código do Animal (DL n.º 214/2013)</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>1 — O detentor do animal deve ter acesso a informação sobre:
+a) As obrigações inerentes à sua detenção, direitos e responsabilidades;
+b) As normas de bem-estar, cuidados de saúde e comportamento esperado;
+c) As necessidades específicas da espécie ou raça;
+d) A duração de vida esperada;
+e) Os custos de manutenção;
+f) A proibição de abandono.
+2 — Os criadores e comerciantes devem fornecer informação escrita completa ao adquirente antes da transferência do animal, incluindo dados de identificação e cuidados de saúde.</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Art.º 20.º do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>1 — O proprietário ou detentor de animal de companhia deve ter acesso a informação adequada sobre as suas obrigações relativas ao bem-estar do animal.
+2 — Os detentores de animais de companhia que os comercializem devem fornecer informação ao adquirente sobre o estado de saúde do animal e vacinas efetuadas.</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 (art.º 20.º) é genérico e não especifica a forma escrita nem detalhes de conteúdo. O @regulamento exige informação escrita sobre necessidades específicas de bem-estar (alimentação, cuidados, saúde, alojamento, comportamento) e condiciona a transferência à transmissão dessa informação.</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>O @codigo (art.º 57.º) exige informação escrita mas com âmbito mais amplo (duração de vida, custos) do que o @regulamento, que se foca especificamente em bem-estar e saúde.</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac (art.º 8.º) aproxima-se do conteúdo do @regulamento, exigindo informação escrita antes da transferência, incluindo dados de saúde e vacinação, mas ainda sem o enfoque específico em bem-estar comportamental.</t>
+        </is>
+      </c>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>Necessidade de alteração: (1) formalizar requisito de informação escrita como condição de transferência de animal; (2) especificar conteúdo obrigatório sobre bem-estar, saúde e necessidades comportamentais; (3) harmonizar entre @codigo e @rgbeac quanto a âmbito e forma.</t>
+        </is>
+      </c>
+      <c r="O8" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P8" s="11" t="inlineStr"/>
+    </row>
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Competências de Cuidadores e Bem-Estar Animal</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 9.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>1. Animal caretakers, other than volunteers in shelters and interns who are under the responsibility of a competent animal caretaker, shall have the following competences as regards the dogs and cats they are handling:
+(a) understanding of their biological behaviour and their physiological and ethological needs;
+(b) ability to recognise their expressions including any sign of suffering and to identify and take the appropriate mitigating measures in such cases;
+(c) ability to apply good animal management practices, including operant conditioning and positive reinforcement, to use and maintain the equipment used for the dogs or cats under their care and to minimise any risks to the welfare of the dogs or cats, preventing suffering;
+(d) knowledge of their obligations under this Regulation.
+2. The competences referred to in paragraph 1 may be acquired through education, training or professional experience. Education, training or professional experience shall be documented.
+2a. Operators shall ensure that at least one animal caretaker, other than a volunteer or intern, at the establishment has completed the training courses referred to in Article 18 and that the caretaker transfers the knowledge to the other animal caretakers of the establishment.
+3. The Commission shall, by means of implementing acts, lay down minimum requirements concerning the formal education, training or professional experience in order to acquire the competences referred to in paragraph 2 and for the training courses referred to in paragraph 2a. Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 24. The implementing act concerning the training courses referred to in paragraph 2a shall be adopted by [3 years from the date of entry into force of the Regulation].</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>1. Os cuidadores de animais, com exceção de voluntários em abrigos e estagiários sob a responsabilidade de um cuidador competente, devem ter as seguintes competências no que diz respeito aos cães e gatos que manuseiam:
+(a) compreensão do seu comportamento biológico e das suas necessidades fisiológicas e etológicas;
+(b) capacidade de reconhecer as suas expressões, incluindo qualquer sinal de sofrimento, e de identificar e adotar as medidas mitigantes apropriadas nesses casos;
+(c) capacidade de aplicar boas práticas de maneio de animais, incluindo condicionamento operante e reforço positivo, utilizar e manter o equipamento utilizado para os cães ou gatos sob os seus cuidados e minimizar quaisquer riscos para o bem-estar dos cães ou gatos, prevenindo sofrimento;
+(d) conhecimento das suas obrigações sob este Regulamento.
+2. As competências referidas no parágrafo 1 podem ser adquiridas através de educação, formação ou experiência profissional. A educação, formação ou experiência profissional devem ser documentadas.
+2a. Os operadores devem assegurar que pelo menos um cuidador de animais, que não seja um voluntário ou estagiário, no estabelecimento tenha completado os cursos de formação referidos no artigo 18.º e que o cuidador transfira os conhecimentos aos outros cuidadores de animais do estabelecimento.
+3. A Comissão estabelecerá, por meio de atos de execução, os requisitos mínimos relativos à educação formal, formação ou experiência profissional para adquirir as competências referidas no parágrafo 2 e para os cursos de formação referidos no parágrafo 2a. Esses atos de execução serão adotados de acordo com o procedimento de exame referido no artigo 24.º. O ato de execução relativo aos cursos de formação referidos no parágrafo 2a deve ser adotado por [3 anos da data de entrada em vigor do Regulamento].</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Art.ºs 69.º, 84.º e 90.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Artigo 69.º — Formação
+A reprodução, criação, manutenção, venda ou treino de animais de companhia depende de aprovação em formação sobre detenção responsável de animais de companhia, bem como sobre as necessidades fisiológicas e etológicas específicas da espécie animal em causa, ministrada pelo ICNF, I.P. ou entidades por este certificadas.
+Artigo 84.º — Pessoal
+O pessoal responsável pelas tarefas referidas no artigo 82.º deve possuir os conhecimentos e a experiência adequados para as executar.
+Artigo 90.º — Pessoal
+O pessoal auxiliar deve possuir os conhecimentos e a experiência adequada, o qual fica, contudo, sob a orientação do médico veterinário responsável.</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Art.º 19.º do Código do Animal (DL n.º 214/2013)</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 19.º — Pessoal auxiliar
+Os alojamentos devem dispor de pessoal auxiliar que possua os conhecimentos e a aptidão necessária para assegurar os cuidados adequados aos animais, o qual fica sob a orientação do médico veterinário responsável.</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Art.º 13.º do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 13.º — Maneio
+1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
+2 — O maneio deve ser feito por pessoal que possua formação teórica e prática específica ou sob a supervisão de uma pessoa competente para o efeito.
+3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados.</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 (art.º 13.º) exige pessoal 'técnico competente' com 'formação teórica e prática específica' e 'inspeção diária', mas não detalha competências concretas. O @regulamento especifica 4 competências estruturadas (comportamento biológico, reconhecimento de sofrimento, maneio e bem-estar, conhecimento de obrigações) e exige documentação de educação/formação/experiência.</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>O @codigo (art.º 19.º) é genérico: exige apenas 'conhecimentos e aptidão necessária' sob orientação do médico veterinário responsável. Não detalha competências concretas nem exigências de formação formal.</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac (art.ºs 69.º, 84.º, 90.º) aproxima-se mais do @regulamento: exige 'conhecimentos e experiência adequados', menciona 'necessidades fisiológicas e etológicas', exige formação certificada pelo ICNF. Lacuna: não detalha as 4 competências específicas do @regulamento (reconhecimento de sofrimento, condicionamento operante, etc.).</t>
+        </is>
+      </c>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>Alinhamento parcial do @rgbeac com @regulamento. Para @codigo e @legislacao, necessidade de: (1) detalhar as 4 competências específicas (comportamento, reconhecimento de sofrimento, maneio positivo, conhecimento de obrigações); (2) exigir documentação formal de educação/formação/experiência; (3) requerer que operador designe formador responsável que transfira conhecimento; (4) implementar requisitos mínimos de formação via regulamento delegado.</t>
+        </is>
+      </c>
+      <c r="O9" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P9" s="11" t="inlineStr"/>
+    </row>
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Avaliação e Supervisão de Bem-Estar</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 10.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Operators shall:
+(a) ensure that the establishments under their responsibility receive a visit by a veterinarian within the first year after the date of application of this Regulation or within the first year after having notified a new establishment, for the purpose of identifying and assessing any risk factor for the welfare of the dogs or cats and advising the operator on measures to address those risks; thereafter the visits from a veterinarian shall take place when appropriate, based on a risk analysis by the competent authorities; Member States may provide for that the advisory welfare visits are annual;
+(b) keep the records of the findings of the visit of the veterinarian referred to in point (a) and of their follow up actions for at least 4 years, from the day of the visit, and shall make them available to the competent authorities upon request and to the veterinarian that performs subsequent advisory visits.
+By 24 months from the date of entry into force of this Regulation, the Commission shall adopt delegated acts in accordance with Article 23 supplementing this Article in order to lay down minimum criteria to be assessed during the advisory welfare visit.</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Os operadores devem:
+(a) assegurar que os estabelecimentos sob a sua responsabilidade recebem uma visita de um médico veterinário no prazo de um ano a partir da data de aplicação do presente Regulamento ou no prazo de um ano após notificação de novo estabelecimento, com o objetivo de identificar e avaliar quaisquer fatores de risco para o bem-estar dos cães ou gatos e aconselhar o operador sobre medidas para resolver esses riscos; depois, as visitas do médico veterinário devem ocorrer quando apropriado, com base numa análise de risco pelas autoridades competentes; os Estados-Membros podem estabelecer que as visitas de aconselhamento de bem-estar sejam anuais;
+(b) manter registos dos resultados da visita do médico veterinário referida na alínea (a) e das ações de acompanhamento por um período mínimo de 4 anos, a partir da data da visita, e disponibilizá-los às autoridades competentes a pedido e ao médico veterinário que realiza visitas de aconselhamento subsequentes.
+Dentro de 24 meses a partir da data de entrada em vigor do presente Regulamento, a Comissão deve adotar atos delegados em conformidade com o artigo 23.º que complementem o presente artigo de forma a estabelecer critérios mínimos a serem avaliados durante a visita de aconselhamento de bem-estar.</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Art.º 56.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Artigo 56.º — Médico veterinário responsável pelo alojamento
+1 — Os titulares da exploração de alojamentos para hospedagem, com exceção dos alojamentos para hospedagem com fins higiénicos, devem ter ao seu serviço um médico veterinário responsável pelo alojamento.
+2 — Ao médico veterinário responsável pelo alojamento compete:
+a) A elaboração de parecer relativo à verificação das condições higiossanitárias e de bem-estar animal exigidas no presente decreto-lei;
+b) A elaboração e a execução de programas e ações que visem a saúde e o bem-estar dos animais e o seu acompanhamento, bem como a emissão de pareceres relativos à saúde e ao bem-estar dos animais;
+c) A orientação técnica do pessoal responsável pela observação, maneio e prestação de cuidados aos animais;
+d) A colaboração com as autoridades competentes em todas as ações que estas determinem.</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Art.º 32.º do Código do Animal (DL n.º 214/2013)</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 32.º — Médico veterinário responsável pelo alojamento
+1 — Os titulares da exploração de alojamentos para hospedagem sem fins lucrativos e com fins lucrativos de animais, com exceção dos com fins higiénicos, necessitam de ter ao seu serviço um médico veterinário que seja responsável pelo alojamento.
+2 — Ao médico veterinário responsável pelo alojamento compete:
+a) A elaboração e execução de programas que visem a saúde e o bem-estar dos animais e o seu acompanhamento, bem como a emissão de pareceres relativos à saúde e ao bem-estar dos animais;
+b) A orientação técnica do pessoal que cuida dos animais;
+c) A colaboração com as autoridades competentes em todas as ações que estas determinarem.</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Art.º 4.º do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 4.º — Médico veterinário responsável pelo alojamento
+1 — Os titulares da exploração de alojamentos para hospedagem sem fins lucrativos e com fins lucrativos de animais, com exceção dos alojamentos para hospedagem com fins higiénicos, devem ter ao seu serviço um médico veterinário que seja responsável pelo alojamento.
+2 — Ao médico veterinário responsável pelo alojamento compete:
+a) A elaboração e a execução de programas e ações que visem a saúde e o bem-estar dos animais e o seu acompanhamento, bem como a emissão de pareceres relativos à saúde e ao bem-estar dos animais;
+b) A orientação técnica do pessoal que cuida dos animais;
+c) A colaboração com as autoridades competentes em todas as ações que estas determinarem.</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 (art.º 4.º) estabelece a obrigação de ter médico veterinário responsável que execute 'programas e ações' para saúde e bem-estar, mas não especifica que essa avaliação deve ocorrer em prazo determinado (ex.: 1 ano) ou que os registos devem ser mantidos por período específico (4 anos). O @regulamento é mais prescritivo neste aspecto.</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>O @codigo (art.º 32.º) replica quase verbatim o art.º 4.º do DL n.º 276/2001, mantendo as mesmas lacunas: não fixa prazos para avaliações de bem-estar nem obrigações de manutenção de registos estruturados.</t>
+        </is>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac (art.º 56.º) reforça a obrigação com 'parecer relativo à verificação das condições higiossanitárias e de bem-estar', mas igualmente sem prazos específicos para avaliações ou duração de retenção de registos. Ambos focam-se em 'programas' interno, não em 'visitas periódicas externas'.</t>
+        </is>
+      </c>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>Lacuna estrutural em toda a legislação nacional: enquanto o @regulamento exige 'visita de um veterinário' num prazo específico (1 ano) com manutenção de registos por 4 anos e transmissão entre veterinários, a legislação nacional concentra-se em ter um 'médico veterinário responsável' no estabelecimento. Necessidade de alteração: (1) formalizar obrigação de 'visita de avaliação' por veterinário dentro de 1 ano após notificação; (2) exigir avaliações periódicas conforme risco; (3) obrigatória manutenção de registos por 4 anos; (4) garantir transmissão de informações ao próximo veterinário avaliador; (5) estabelecer critérios mínimos de avaliação (bem-estar comportamental, alojamento, saúde, etc.).</t>
+        </is>
+      </c>
+      <c r="O10" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P10" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -664,97 +664,107 @@
     <row r="2" ht="120" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Princípios Gerais de Bem-Estar</t>
+          <t>Identificação e Registo</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Art.º 5.º do Regulamento 2023/0447</t>
+          <t>Art.º 17.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Operators shall apply the following general welfare principles with respect to dogs or cats bred or kept in their establishment:
-(a) dogs and cats are provided with water and feed of a quality and of a quantity that enables them to have appropriate nutrition and hydration;
-(b) dogs and cats are kept in an appropriate and regularly cleaned physical environment which is secure and comfortable, especially in terms of space, air quality, temperature, light, protection against adverse climatic conditions and ease of movement, preventing overcrowding;
-(c) dogs and cats are kept safe, clean and in good health by preventing diseases, injuries, and pain, due in particular to management, handling practices and breeding practices;
-(d) dogs and cats are kept in an environment that enables them to exhibit species-specific and social non-harmful behaviour, and to establish a positive relationship with human beings;
-(e) dogs and cats are kept in such a way as to optimise their mental state by preventing or reducing negative stimuli in duration and intensity, as well as by maximising opportunities for positive stimuli in duration and intensity, preventing the development of abnormal repetitive and other behaviours indicative of negative animal welfare, and taking into consideration the individual dog's or cat's needs in the different domains referred to in points (a) to (d).</t>
+          <t>1. All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip compliant with Annex II.
+1a. Operators shall ensure that dogs and cats born in their establishments are individually identified within 3 months after their birth and in any event before the date of their placing on the market.
+Operators of selling establishments, shelters and those placing and being responsible for dogs and cats in foster homes shall ensure that dogs and cats that enter their establishments or come under their responsibility are individually identified within 30 days after their arrival at the establishment and in any event before the date of their placing on the market.
+Pet owners and any other natural or legal persons, other than operators, who own dogs or cats, shall ensure that the dogs or cats are individually identified at the latest when the dog or cat reaches 3 months of age or, in case the dog or cat is placed on the market, before the date of their placing on the market.
+2. The implantation of the transponder shall be performed by a veterinarian. Member States may allow the implantation of transponders in cats to be performed by a person other than a veterinarian, if it is done under the responsibility of a veterinarian.
+3. Dogs and cats which have been individually identified by means of an injectable transponder containing a microchip, in accordance with national legislation prior to entry into force of this Regulation, shall be recognised as identified in accordance with the requirements of this Article.
+4. Within two working days after their identification, the dogs and cats shall be registered by a veterinarian in a national database.
+5. For dogs and cats kept in establishments, the registration shall be made in the name of the operator of the establishment. For dogs and cats placed in foster homes, the registration shall be made in the name of the person responsible for the foster home. For dogs and cats owned by pet owners or by any other natural or legal person, the registration shall be made in the name of the pet owner or the natural or legal person.
+Member States may grant derogations from the first subparagraph to military, police and customs dogs.
+6. In case of placing on the market or occasional and irregular donation by a natural person without online advertising, the requirements for registration shall not apply.
+7. In the case of a death of a dog or a cat, the operator, pet owner or natural or legal person owning the dog or cat shall inform the national database.
+8. In case of unreadable transponder, the operator or the natural or legal person responsible for the dog or cat shall ensure that the dog or cat is re-identified with a new transponder and re-registered in the national database.</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Os operadores devem aplicar os seguintes princípios gerais de bem-estar aos cães e gatos criados ou detidos nos seus estabelecimentos:
-(a) os cães e gatos são alimentados e abebeirados com água e ração de qualidade e quantidade adequadas a uma nutrição e hidratação apropriadas;
-(b) os cães e gatos são mantidos num ambiente físico adequado, regularmente limpo, seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, iluminação, proteção face a condições climáticas adversas e facilidade de movimentação, prevenindo a sobrelotação;
-(c) os cães e gatos são mantidos seguros, limpos e com boa saúde, prevenindo doenças, lesões e dor, nomeadamente através de práticas de maneio, manuseamento e reprodução adequadas;
-(d) os cães e gatos são mantidos num ambiente que lhes permite exibir comportamentos específicos da espécie e comportamentos sociais não nocivos, e estabelecer uma relação positiva com os seres humanos;
-(e) os cães e gatos são mantidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo estímulos negativos em duração e intensidade, maximizando oportunidades de estímulos positivos, prevenindo o desenvolvimento de comportamentos repetitivos anormais, tendo em conta as necessidades individuais do animal nos domínios referidos nas alíneas (a) a (d).</t>
+          <t>1. Todos os cães e gatos mantidos em estabelecimentos colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com o Anexo II.
+1a. Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de 3 meses após o nascimento e, em qualquer caso, antes da data da sua colocação no mercado.
+Os operadores de estabelecimentos de venda, abrigos e os que colocam e são responsáveis por cães e gatos em famílias de acolhimento devem assegurar que os cães e gatos que entrem nos seus estabelecimentos sejam identificados individualmente no prazo de 30 dias após a chegada.
+Os donos de animais de companhia e quaisquer outras pessoas singulares ou coletivas que detenham cães ou gatos devem assegurar que os animais sejam identificados individualmente o mais tardar quando o animal atingir os 3 meses de idade ou, no caso de o animal ser colocado no mercado, antes da data da sua colocação no mercado.
+2. A implantação do transponder devem ser efetuada por um médico veterinário. Os Estados-Membros podem permitir que a implantação de transponders em gatos seja efetuada por pessoa que não seja médico veterinário, se for feita sob a responsabilidade de um médico veterinário.
+3. Cães e gatos que tenham sido identificados individualmente por meio de um transponder injetável contendo um microchip, em conformidade com legislação nacional anterior à entrada em vigor do presente Regulamento, são reconhecidos como identificados de acordo com os requisitos do presente artigo.
+4. No prazo de dois dias úteis após a sua identificação, os cães e gatos devem ser registados por um médico veterinário numa base de dados nacional.
+5. Para cães e gatos mantidos em estabelecimentos, o registo deve ser efetuado em nome do operador do estabelecimento. Para cães e gatos colocados em famílias de acolhimento, o registo deve ser efetuado em nome da pessoa responsável pela família de acolhimento. Para cães e gatos detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva, o registo deve ser efetuado em nome do dono ou da pessoa singular ou coletiva.
+Os Estados-Membros podem conceder derrogações ao primeiro parágrafo a cães militares, policiais e aduaneiros.
+6. Em caso de colocação no mercado ou cedência ocasional e irregular por pessoa singular sem publicidade em linha, os requisitos de registo não se aplicam.
+7. Em caso de morte de um cão ou gato, o operador, dono do animal ou pessoa singular ou coletiva proprietária devem informar a base de dados nacional.
+8. Em caso de transponder ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato devem assegurar que o animal é reidentificado com um novo transponder e re-registado na base de dados nacional.</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>al. a) do n.º 1 do art.º 10.º do RGBEAC (proposta, jun. 2025)</t>
+          <t>Art.º 17.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>1 — O detentor do animal de companhia deve:
-a) Assegurar o bem-estar do animal, de acordo com sua espécie, raça, idade e necessidades físicas e etológicas, proporcionando-lhe:
-— Atenção, supervisão, controlo, exercício físico e estímulo mental;
-— Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável;
-— Condições higiossanitárias que atendam, no mínimo, ao estabelecido no presente decreto-lei e na demais legislação aplicável;
-— Liberdade de movimento, sendo proibidos todos os sistemas de contenção permanentes;
-— Abrigo adequado, em termos de tamanho e qualidade, com vista a proteger de condições atmosféricas adversas, incluindo frio, chuva, sol ou calor excessivos, com cama seca, limpa e confortável;
-— Contato social adequado a cada espécie, de acordo com a sua idade e atividade.</t>
+          <t>1 — A identificação dos animais de companhia, pela sua marcação, quando aplicável, e registo no SIAC, deve ser realizada:
+a) Relativamente aos cães, gatos e furões nascidos em alojamentos, até aos três meses de idade ou, em qualquer caso, antes da sua colocação no mercado;
+b) Relativamente aos cães, gatos e furões que entrem em alojamentos, nos termos dos artigos 12.º a 15.º, até trinta dias após a sua chegada ao alojamento ou, em qualquer caso, antes da data de colocação no mercado;
+c) Relativamente aos cães, gatos e furões detidos por pessoas singulares, exceto nos casos previstos nas alíneas anteriores, até aos três meses de idade ou, no caso de colocação no mercado, antes da data de colocação no mercado.</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>n.ºs 1, 2 e 3 do art.º 5.º do Código do Animal (DL n.º 214/2013)</t>
+          <t>Art.º 53.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal.
-2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
-3 — É proibida a violência contra animais, considerando-se como tal todos os atos que, sem necessidade, infligem a morte, o sofrimento, abuso ou lesões a um animal.</t>
+          <t>1 — Todos os cães devem ser identificados e registados, entre os três e os seis meses de idade.
+2 — Os gatos em exposição, para fins comerciais ou lucrativos, em estabelecimentos de venda, locais de criação, feiras ou concursos, provas funcionais, publicidade ou fins similares, devem ser identificados e registados entre os três e os seis meses de idade.
+4 — Os cães e gatos são identificados através de método electrónico e registados na base de dados nacional.
+5 — A identificação electrónica é efetuada através da aplicação subcutânea de um microchip no centro da face lateral esquerda do pescoço.</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>n.º 1 do art.º 7.º e n.º 1 do art.º 9.º do DL n.º 276/2001, de 17 de outubro</t>
+          <t>n.ºs 1, 2 e 3 do art.º 5.º do DL n.º 82/2019, de 27 de junho</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>Artigo 7.º, n.º 1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
-Artigo 9.º, n.º 1 — A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam.</t>
+          <t>1 — A identificação dos animais de companhia, pela sua marcação e registo no SIAC, deve ser realizada até 120 dias após o seu nascimento.
+2 — Na impossibilidade de determinar a data de nascimento exata, para efeitos de contagem do prazo referido no número anterior, a identificação deve ser efetuada até à perda dos dentes incisivos de leite.
+3 — Sem prejuízo dos números anteriores, e relativamente aos cães, gatos e furões que sejam cedidos e ou comercializados a partir de um criador ou de um estabelecimento autorizado para a detenção de animais de companhia, nomeadamente os centros de hospedagem com ou sem fins lucrativos e os centros de recolha oficiais, deve ser assegurada a sua marcação e registo no SIAC antes de abandonarem a instalação de nascimento ou de alojamento, independentemente da sua idade.</t>
         </is>
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>O DL n.º 276/2001 (art.ºs 7.º e 9.º) consagra os mesmos parâmetros mas desenvolve-os em artigos separados (alojamento, alimentação, ambiente) sem os denominar como domínios nem os sistematizar de forma unificada segundo o referencial OMSA.</t>
+          <t>O DL n.º 82/2019 (art.º 5.º) prevê prazo geral de 120 dias após o nascimento, sem distinguir o contexto de estabelecimento — prazo superior ao máximo de 3 meses do @regulamento, que exigirá redução. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>O @codigo (art.º 5.º) refere 'parâmetros de bem-estar animal' genericamente, sem adotar formalmente a nomenclatura dos 5 domínios OMSA nem a sua sistematização explícita.</t>
+          <t>O @codigo fixa prazo de identificação entre 3 e 6 meses, igualmente sem distinção entre nascimentos e entrada em estabelecimentos, ficando aquém da precisão exigida pelo @regulamento.</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac (art.º 10.º, n.º 1, al. a)) articula obrigações equivalentes ao nível do detentor de forma descritiva, sem sistematização nos 5 domínios nem referência ao quadro OMSA.</t>
+          <t>O @rgbeac aproxima-se dos prazos do @regulamento mas aplica-se apenas a cães, gatos e furões. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
       <c r="N2" s="11" t="inlineStr">
         <is>
-          <t>Alinhamento substancial de conteúdo; sem necessidade de alteração imediata. Recomenda-se a adoção formal dos 5 domínios OMSA como referencial estruturante em futura revisão legislativa ou em normas de orientação técnica da DGAV.</t>
+          <t>Necessidade de alteração: (1) reduzir prazo máximo de identificação de nascimentos para 3 meses; (2) criar prazo diferenciado de 30 dias para animais admitidos em estabelecimentos; (3) harmonizar prazos entre todos os diplomas nacionais.</t>
         </is>
       </c>
       <c r="O2" s="11" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="P2" s="11" t="inlineStr"/>
@@ -863,114 +873,15 @@
     <row r="4" ht="120" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Estratégias de Criação — Conformação e Consanguinidade</t>
+          <t>Reprodução e Criação</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Art.º 6.º-A do Regulamento 2023/0447</t>
+          <t>Art.º 7.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>1. Operators of breeding establishments shall ensure that their breeding strategies minimise the risk of producing dogs or cats with genotypes associated with detrimental effects on their health and welfare.
-2. Operators of breeding establishments shall not use for reproduction dogs or cats that have excessive conformational traits leading to a high risk of detrimental effects on the welfare of these dogs or cats, or of their offspring. Before selection for breeding of a dog or cat that may be concerned by an excessive conformational trait the operator shall consult a veterinarian or an independent qualified person under the responsibility of a veterinarian. The veterinarian or independent qualified person shall assess whether the dog or cat has an excessive conformational trait.
-3. The Commission is empowered to adopt, taking into account scientific opinions of the European Food Safety Authority as well as the social and economic impacts, delegated acts in accordance with Article 23 supplementing this Regulation by:
-(a) defining characteristics of the genotypes referred to in paragraph 1, which shall be excluded from reproduction, and the methods for their assessment and the record keeping requirements;
-(b) defining excessive conformational traits referred to in paragraph 2 of this Article, which shall be excluded from reproduction, the methods for their assessment and the record keeping requirements.
-4. The delegated acts concerning the excessive conformational traits shall be adopted by 1 July 2030. The delegated acts concerning the genotypes shall be adopted by 1 July 2036.
-5. The following shall be prohibited in the management of the reproduction of dogs and cats:
-(a) the breeding between parents and offspring, between siblings, between half-siblings or between grandparents and grandchildren, unless approved by the competent authority based on a specific need to preserve local breeds with a limited genetic pool;
-(b) the breeding to produce hybrids.</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>1. Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
-2. Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem traços conformacionais excessivos que conduzam a um risco elevado de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por traço conformacional excessivo, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem um traço conformacional excessivo.
-3. A Comissão tem competência para adotar, tendo em conta os pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, bem como os impactos sociais e económicos, atos delegados em conformidade com o artigo 23.º que complementem este Regulamento:
-(a) definindo características dos genótipos a que se refere o parágrafo 1, que devem ser excluídos da reprodução, e os métodos para a sua avaliação e requisitos de manutenção de registos;
-(b) definindo traços conformacionais excessivos a que se refere o parágrafo 2 do presente artigo, que devem ser excluídos da reprodução, os métodos para a sua avaliação e requisitos de manutenção de registos.
-4. Os atos delegados relativos aos traços conformacionais excessivos devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
-5. São proibidos na gestão da reprodução de cães e gatos:
-(a) o cruzamento entre progenitores e descendentes, entre irmãos, entre meios-irmãos ou entre avós e netos, exceto com aprovação da autoridade competente por razão de necessidade específica de preservação de raças locais com reserva genética limitada;
-(b) o cruzamento para produção de híbridos.</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>n.ºs 1 e 2 do art.º 34.º do RGBEAC (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>1 — As intervenções cirúrgicas com o objetivo da modificação da aparência ou com fins não curativos ou não destinados a impedir a reprodução dos animais são proibidas, nos termos do disposto na alínea i) do n.º 1 do artigo 12.º.
-2 — O detentor de animal sujeito a intervenção curativa que modifique a sua aparência deve possuir documento comprovativo da necessidade da mesma, passado pelo médico veterinário que a ela procedeu, sob a forma de atestado do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura, ou, no caso de animais importados, documento comprovativo da necessidade dessa intervenção, emitida pelo médico veterinário que a ela procedeu, legalizado pela autoridade competente do respetivo país.</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>n.º 2, als. a), b) e c) do art.º 8.º do Código do Animal (DL n.º 214/2013)</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>2 — A reprodução de animais obedece ao seguinte:
-a) Os animais só devem ser utilizados na reprodução depois de atingida a maturidade reprodutiva para a espécie e raça devendo, no caso dos cães e gatos, seguir os parâmetros referidos no anexo I ao presente diploma, do qual faz parte integrante, não sendo autorizado, no caso das fêmeas, o acasalamento em cios sucessivos;
-b) Deve ser respeitada a regra do porte semelhante dos progenitores, para prevenir a possibilidade de distócia;
-c) Devem ser excluídos da reprodução, os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia da anca nos cães e rim poliquístico nos gatos, ou alterações comportamentais.</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>art.º 17.º e n.º 1 do art.º 18.º do DL n.º 276/2001, de 17 de outubro</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>Artigo 17.º — As intervenções cirúrgicas, nomeadamente as destinadas ao corte de caudas nos canídeos, têm de ser executadas por um médico veterinário.
-Artigo 18.º, n.º 1 — Os detentores de animais de companhia que os apresentem com quaisquer amputações que modifiquem a aparência dos animais ou com fins não curativos devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa amputação, nomeadamente discriminando que as mesmas foram feitas por razões médico-veterinárias ou no interesse particular do animal ou para impedir a reprodução.</t>
-        </is>
-      </c>
-      <c r="K4" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 276/2001 (art.ºs 17.º e 18.º) exige intervenção veterinária em cirurgias e documentação para amputações, mas não prevê qualquer restrição à reprodução por traços conformacionais excessivos nem proibição de consanguinidade próxima ou hibridação.</t>
-        </is>
-      </c>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>O @codigo (art.º 8.º, n.º 2) exclui da reprodução animais com defeitos genéticos e malformações (displasia, rim poliquístico) e proíbe cios sucessivos, mas não prevê o conceito de traços conformacionais excessivos nem a proibição de consanguinidade.</t>
-        </is>
-      </c>
-      <c r="M4" s="10" t="inlineStr">
-        <is>
-          <t>O @rgbeac (art.º 34.º) proíbe intervenções cirúrgicas de modificação da aparência, mas não contém qualquer norma sobre estratégia genética de criação, conformação excessiva ou consanguinidade.</t>
-        </is>
-      </c>
-      <c r="N4" s="11" t="inlineStr">
-        <is>
-          <t>Lacuna normativa transversal. Necessidade de criar norma específica que: (1) defina traços conformacionais excessivos (a regular por ato delegado europeu até 2030); (2) proíba consanguinidade próxima (pais/filhos, irmãos, avós/netos); (3) proíba a produção de híbridos; (4) imponha consulta veterinária prévia ao acasalamento de animais potencialmente afetados.</t>
-        </is>
-      </c>
-      <c r="O4" s="11" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P4" s="11" t="inlineStr"/>
-    </row>
-    <row r="5" ht="120" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Reprodução e Criação</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 7.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Operators shall notify the competent authorities of their activity, providing at least the following information:
 (a) name, address and contact details of the operator;
@@ -981,7 +892,7 @@
 (ea) for breeding establishments, the estimated number of litters to be placed on the market per year.</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem notificar as autoridades competentes da sua atividade, fornecendo pelo menos as seguintes informações:
 (a) nome, morada e contactos do operador;
@@ -992,24 +903,24 @@
 (ea) para os estabelecimentos de criação, o número estimado de ninhadas a colocar no mercado por ano.</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Art.º 43.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1 — Os centros de bem-estar animal procedem à esterilização dos animais recolhidos que se presuma terem sido abandonados, nos termos do artigo 41.º.
 2 — As câmaras municipais devem, sempre que necessário e sob a responsabilidade do médico veterinário municipal, incentivar e promover programas de esterilização de animais de companhia, nomeadamente os cães e gatos, em complementaridade com os centros de bem-estar animal.
 3 — Os requisitos mínimos das instalações adequadas à realização de esterilizações nos centros de bem-estar animal são estabelecidos em portaria do membro do Governo responsável pela área da agricultura.</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Art.º 8.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>1 — A reprodução de animais deve ser realizada de forma planeada.
 2 — A reprodução de animais obedece ao seguinte:
@@ -1018,12 +929,12 @@
 c) Devem ser excluídos da reprodução os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia.</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>n.º 1 do art.º 3.º-A do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>1 — A mera comunicação prévia a que se refere a alínea a) do n.º 1 do artigo anterior é dirigida à DGAV e deve conter os seguintes elementos, quando aplicáveis:
 a) O nome ou a denominação social do interessado;
@@ -1038,29 +949,127 @@
 j) Declaração de responsabilidade, subscrita pelo interessado, relativa ao cumprimento da legislação aplicável aos animais de companhia, nomeadamente em matéria de instalações, equipamentos, higiene, saúde e bem-estar dos animais.</t>
         </is>
       </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 (art.º 3.º-A) prevê comunicação prévia à DGAV com elementos parcialmente equivalentes (capacidade máxima, espécies, raças). Não exige a estimativa anual de ninhadas a colocar no mercado (al. ea) do @regulamento), constituindo lacuna parcial. É o diploma mais próximo do @regulamento neste eixo.</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>O @codigo regula condições de reprodução (art.º 8.º) mas não prevê qualquer sistema de notificação ou registo de estabelecimentos criadores junto da autoridade competente.</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac trata da esterilização de errantes e CED, mas não contém norma sobre notificação de criadores ou registo de estabelecimentos com fins de reprodução comercial.</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="inlineStr">
+        <is>
+          <t>A @legislacao vigente é o diploma base adequado para a transposição. Necessidade de ajuste: acrescentar a obrigação de estimativa anual de ninhadas a colocar no mercado e alinhar os restantes elementos informativos com a lista exaustiva do art.º 7.º do @regulamento.</t>
+        </is>
+      </c>
+      <c r="O4" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P4" s="11" t="inlineStr"/>
+    </row>
+    <row r="5" ht="120" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Princípios Gerais de Bem-Estar</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 5.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Operators shall apply the following general welfare principles with respect to dogs or cats bred or kept in their establishment:
+(a) dogs and cats are provided with water and feed of a quality and of a quantity that enables them to have appropriate nutrition and hydration;
+(b) dogs and cats are kept in an appropriate and regularly cleaned physical environment which is secure and comfortable, especially in terms of space, air quality, temperature, light, protection against adverse climatic conditions and ease of movement, preventing overcrowding;
+(c) dogs and cats are kept safe, clean and in good health by preventing diseases, injuries, and pain, due in particular to management, handling practices and breeding practices;
+(d) dogs and cats are kept in an environment that enables them to exhibit species-specific and social non-harmful behaviour, and to establish a positive relationship with human beings;
+(e) dogs and cats are kept in such a way as to optimise their mental state by preventing or reducing negative stimuli in duration and intensity, as well as by maximising opportunities for positive stimuli in duration and intensity, preventing the development of abnormal repetitive and other behaviours indicative of negative animal welfare, and taking into consideration the individual dog's or cat's needs in the different domains referred to in points (a) to (d).</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Os operadores devem aplicar os seguintes princípios gerais de bem-estar aos cães e gatos criados ou detidos nos seus estabelecimentos:
+(a) os cães e gatos são alimentados e abebeirados com água e ração de qualidade e quantidade adequadas a uma nutrição e hidratação apropriadas;
+(b) os cães e gatos são mantidos num ambiente físico adequado, regularmente limpo, seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, iluminação, proteção face a condições climáticas adversas e facilidade de movimentação, prevenindo a sobrelotação;
+(c) os cães e gatos são mantidos seguros, limpos e com boa saúde, prevenindo doenças, lesões e dor, nomeadamente através de práticas de maneio, manuseamento e reprodução adequadas;
+(d) os cães e gatos são mantidos num ambiente que lhes permite exibir comportamentos específicos da espécie e comportamentos sociais não nocivos, e estabelecer uma relação positiva com os seres humanos;
+(e) os cães e gatos são mantidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo estímulos negativos em duração e intensidade, maximizando oportunidades de estímulos positivos, prevenindo o desenvolvimento de comportamentos repetitivos anormais, tendo em conta as necessidades individuais do animal nos domínios referidos nas alíneas (a) a (d).</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>al. a) do n.º 1 do art.º 10.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1 — O detentor do animal de companhia deve:
+a) Assegurar o bem-estar do animal, de acordo com sua espécie, raça, idade e necessidades físicas e etológicas, proporcionando-lhe:
+— Atenção, supervisão, controlo, exercício físico e estímulo mental;
+— Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável;
+— Condições higiossanitárias que atendam, no mínimo, ao estabelecido no presente decreto-lei e na demais legislação aplicável;
+— Liberdade de movimento, sendo proibidos todos os sistemas de contenção permanentes;
+— Abrigo adequado, em termos de tamanho e qualidade, com vista a proteger de condições atmosféricas adversas, incluindo frio, chuva, sol ou calor excessivos, com cama seca, limpa e confortável;
+— Contato social adequado a cada espécie, de acordo com a sua idade e atividade.</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>n.ºs 1, 2 e 3 do art.º 5.º do Código do Animal (DL n.º 214/2013)</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal.
+2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
+3 — É proibida a violência contra animais, considerando-se como tal todos os atos que, sem necessidade, infligem a morte, o sofrimento, abuso ou lesões a um animal.</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>n.º 1 do art.º 7.º e n.º 1 do art.º 9.º do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 7.º, n.º 1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
+Artigo 9.º, n.º 1 — A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam.</t>
+        </is>
+      </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>O DL n.º 276/2001 (art.º 3.º-A) prevê comunicação prévia à DGAV com elementos parcialmente equivalentes (capacidade máxima, espécies, raças). Não exige a estimativa anual de ninhadas a colocar no mercado (al. ea) do @regulamento), constituindo lacuna parcial. É o diploma mais próximo do @regulamento neste eixo.</t>
+          <t>O DL n.º 276/2001 (art.ºs 7.º e 9.º) consagra os mesmos parâmetros mas desenvolve-os em artigos separados (alojamento, alimentação, ambiente) sem os denominar como domínios nem os sistematizar de forma unificada segundo o referencial OMSA.</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>O @codigo regula condições de reprodução (art.º 8.º) mas não prevê qualquer sistema de notificação ou registo de estabelecimentos criadores junto da autoridade competente.</t>
+          <t>O @codigo (art.º 5.º) refere 'parâmetros de bem-estar animal' genericamente, sem adotar formalmente a nomenclatura dos 5 domínios OMSA nem a sua sistematização explícita.</t>
         </is>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac trata da esterilização de errantes e CED, mas não contém norma sobre notificação de criadores ou registo de estabelecimentos com fins de reprodução comercial.</t>
+          <t>O @rgbeac (art.º 10.º, n.º 1, al. a)) articula obrigações equivalentes ao nível do detentor de forma descritiva, sem sistematização nos 5 domínios nem referência ao quadro OMSA.</t>
         </is>
       </c>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>A @legislacao vigente é o diploma base adequado para a transposição. Necessidade de ajuste: acrescentar a obrigação de estimativa anual de ninhadas a colocar no mercado e alinhar os restantes elementos informativos com a lista exaustiva do art.º 7.º do @regulamento.</t>
+          <t>Alinhamento substancial de conteúdo; sem necessidade de alteração imediata. Recomenda-se a adoção formal dos 5 domínios OMSA como referencial estruturante em futura revisão legislativa ou em normas de orientação técnica da DGAV.</t>
         </is>
       </c>
       <c r="O5" s="11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="P5" s="11" t="inlineStr"/>
@@ -1068,15 +1077,240 @@
     <row r="6" ht="120" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>Estratégias de Criação — Conformação e Consanguinidade</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 6.º-A do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>1. Operators of breeding establishments shall ensure that their breeding strategies minimise the risk of producing dogs or cats with genotypes associated with detrimental effects on their health and welfare.
+2. Operators of breeding establishments shall not use for reproduction dogs or cats that have excessive conformational traits leading to a high risk of detrimental effects on the welfare of these dogs or cats, or of their offspring. Before selection for breeding of a dog or cat that may be concerned by an excessive conformational trait the operator shall consult a veterinarian or an independent qualified person under the responsibility of a veterinarian. The veterinarian or independent qualified person shall assess whether the dog or cat has an excessive conformational trait.
+3. The Commission is empowered to adopt, taking into account scientific opinions of the European Food Safety Authority as well as the social and economic impacts, delegated acts in accordance with Article 23 supplementing this Regulation by:
+(a) defining characteristics of the genotypes referred to in paragraph 1, which shall be excluded from reproduction, and the methods for their assessment and the record keeping requirements;
+(b) defining excessive conformational traits referred to in paragraph 2 of this Article, which shall be excluded from reproduction, the methods for their assessment and the record keeping requirements.
+4. The delegated acts concerning the excessive conformational traits shall be adopted by 1 July 2030. The delegated acts concerning the genotypes shall be adopted by 1 July 2036.
+5. The following shall be prohibited in the management of the reproduction of dogs and cats:
+(a) the breeding between parents and offspring, between siblings, between half-siblings or between grandparents and grandchildren, unless approved by the competent authority based on a specific need to preserve local breeds with a limited genetic pool;
+(b) the breeding to produce hybrids.</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>1. Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
+2. Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem traços conformacionais excessivos que conduzam a um risco elevado de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por traço conformacional excessivo, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem um traço conformacional excessivo.
+3. A Comissão tem competência para adotar, tendo em conta os pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, bem como os impactos sociais e económicos, atos delegados em conformidade com o artigo 23.º que complementem este Regulamento:
+(a) definindo características dos genótipos a que se refere o parágrafo 1, que devem ser excluídos da reprodução, e os métodos para a sua avaliação e requisitos de manutenção de registos;
+(b) definindo traços conformacionais excessivos a que se refere o parágrafo 2 do presente artigo, que devem ser excluídos da reprodução, os métodos para a sua avaliação e requisitos de manutenção de registos.
+4. Os atos delegados relativos aos traços conformacionais excessivos devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
+5. São proibidos na gestão da reprodução de cães e gatos:
+(a) o cruzamento entre progenitores e descendentes, entre irmãos, entre meios-irmãos ou entre avós e netos, exceto com aprovação da autoridade competente por razão de necessidade específica de preservação de raças locais com reserva genética limitada;
+(b) o cruzamento para produção de híbridos.</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>n.ºs 1 e 2 do art.º 34.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1 — As intervenções cirúrgicas com o objetivo da modificação da aparência ou com fins não curativos ou não destinados a impedir a reprodução dos animais são proibidas, nos termos do disposto na alínea i) do n.º 1 do artigo 12.º.
+2 — O detentor de animal sujeito a intervenção curativa que modifique a sua aparência deve possuir documento comprovativo da necessidade da mesma, passado pelo médico veterinário que a ela procedeu, sob a forma de atestado do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura, ou, no caso de animais importados, documento comprovativo da necessidade dessa intervenção, emitida pelo médico veterinário que a ela procedeu, legalizado pela autoridade competente do respetivo país.</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>n.º 2, als. a), b) e c) do art.º 8.º do Código do Animal (DL n.º 214/2013)</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>2 — A reprodução de animais obedece ao seguinte:
+a) Os animais só devem ser utilizados na reprodução depois de atingida a maturidade reprodutiva para a espécie e raça devendo, no caso dos cães e gatos, seguir os parâmetros referidos no anexo I ao presente diploma, do qual faz parte integrante, não sendo autorizado, no caso das fêmeas, o acasalamento em cios sucessivos;
+b) Deve ser respeitada a regra do porte semelhante dos progenitores, para prevenir a possibilidade de distócia;
+c) Devem ser excluídos da reprodução, os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia da anca nos cães e rim poliquístico nos gatos, ou alterações comportamentais.</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>art.º 17.º e n.º 1 do art.º 18.º do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 17.º — As intervenções cirúrgicas, nomeadamente as destinadas ao corte de caudas nos canídeos, têm de ser executadas por um médico veterinário.
+Artigo 18.º, n.º 1 — Os detentores de animais de companhia que os apresentem com quaisquer amputações que modifiquem a aparência dos animais ou com fins não curativos devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa amputação, nomeadamente discriminando que as mesmas foram feitas por razões médico-veterinárias ou no interesse particular do animal ou para impedir a reprodução.</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 (art.ºs 17.º e 18.º) exige intervenção veterinária em cirurgias e documentação para amputações, mas não prevê qualquer restrição à reprodução por traços conformacionais excessivos nem proibição de consanguinidade próxima ou hibridação.</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>O @codigo (art.º 8.º, n.º 2) exclui da reprodução animais com defeitos genéticos e malformações (displasia, rim poliquístico) e proíbe cios sucessivos, mas não prevê o conceito de traços conformacionais excessivos nem a proibição de consanguinidade.</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac (art.º 34.º) proíbe intervenções cirúrgicas de modificação da aparência, mas não contém qualquer norma sobre estratégia genética de criação, conformação excessiva ou consanguinidade.</t>
+        </is>
+      </c>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>Lacuna normativa transversal. Necessidade de criar norma específica que: (1) defina traços conformacionais excessivos (a regular por ato delegado europeu até 2030); (2) proíba consanguinidade próxima (pais/filhos, irmãos, avós/netos); (3) proíba a produção de híbridos; (4) imponha consulta veterinária prévia ao acasalamento de animais potencialmente afetados.</t>
+        </is>
+      </c>
+      <c r="O6" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P6" s="11" t="inlineStr"/>
+    </row>
+    <row r="7" ht="120" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Saúde e Monitorização Sanitária</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 13.º do Regulamento 2023/0447 (PE/Conselho)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>1. Operators shall ensure that:
+(a) dogs or cats under their responsibility are inspected by animal caretakers at least once a day and vulnerable dogs and cats, such as newborns, ill or injured dogs and cats, and peri-partum bitches and queens, are inspected more frequently;
+(b) dogs or cats with compromised welfare are, where necessary, transferred without undue delay to a separate area and, where needed, receive appropriate treatment;
+(c) where the recovery of a dog or a cat with compromised welfare is not achievable and the dog or cat experiences severe pain or suffering, a veterinarian is consulted without undue delay, to decide whether the dog or cat shall be euthanised to end its suffering, and, if that is the case, to perform the euthanasia using anesthesia and analgesia;
+(d) measures to prevent and control external and internal parasites, and vaccinations to prevent common diseases to which dogs or cats are likely to be exposed are implemented;
+(e) enrichment do not present a significant risk of injury or biological or chemical contamination or any other health risk.
+Point (a) shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
+Member states may grant derogations from point (c) in cases of emergencies, where no veterinarian can be reached without undue delay, provided that national rules are put in place to ensure that:
+(i) an immediate action ending the life of the dog or cat with minimum pain and suffering using a method inducing instant death is undertaken by a trained competent person;
+(ii) the operator keeps a record of the use of the derogation for purposes of the official control.
+2. Operators of breeding establishments shall additionally ensure that:
+(-a) measures are taken to safeguard the health of dogs or cats in accordance with point 3 of Annex I;
+(-b) bitches or queens are only bred if they have reached a minimum age and skeletal maturity in accordance with point 3 of Annex I, and they have no diagnosed disease, clinical sign of diseases or physical conditions which could negatively impact their pregnancy and welfare;
+(-c) litter-giving pregnancies of bitches or queens follows a maximum frequency in accordance with point 3 of Annex I;
+(-d) lactating queens are not mated or inseminated;
+(-e) dogs and cats which are no longer used for reproduction, including as a result of the provisions of this Regulation, are either kept or sold, donated or rehomed, not killed or abandoned.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>1 — Os operadores devem assegurar que:
+(a) os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados e fêmeas em período peri-parto, são inspecionados com maior frequência;
+(b) os cães e gatos com bem-estar comprometido são, quando necessário, transferidos sem demora injustificada para uma área separada e, se necessário, recebem tratamento adequado;
+(c) quando a recuperação de um cão ou gato com bem-estar comprometido não seja alcançável e o animal experiencie dor ou sofrimento severo, um médico veterinário é consultado sem demora injustificada para decidir se o animal deve ser objeto de eutanásia para pôr termo ao seu sofrimento e, em caso afirmativo, para realizar a eutanásia com recurso a anestesia e analgesia;
+(d) são implementadas medidas de prevenção e controlo de parasitas externos e internos, bem como vacinações para prevenção de doenças comuns às quais os cães ou gatos são suscetíveis de estar expostos;
+(e) os enriquecimentos não apresentam risco significativo de lesões ou de contaminação biológica ou química, nem qualquer outro risco para a saúde.
+A alínea (a) não se aplica aos cães de guarda de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para fins de guarda ou treino.
+Os Estados-Membros podem conceder derrogações relativamente à alínea (c) em casos de emergência, quando não seja possível contactar um médico veterinário sem demora injustificada, desde que sejam estabelecidas regras nacionais que assegurem que:
+(i) é tomada imediatamente uma ação que ponha fim à vida do cão ou gato com o mínimo de dor e sofrimento, utilizando um método que induza a morte instantânea, por uma pessoa competente e devidamente habilitada;
+(ii) o operador mantém um registo da utilização da derrogação para efeitos de controlo oficial.
+2 — Os operadores de estabelecimentos de criação devem adicionalmente assegurar que:
+(-a) são tomadas medidas para salvaguardar a saúde dos cães ou gatos em conformidade com o ponto 3 do Anexo I;
+(-b) as cadelas ou gatas só são reproduzidas se tiverem atingido a idade mínima e a maturidade esquelética em conformidade com o ponto 3 do Anexo I, e não apresentem doença diagnosticada, sinais clínicos de doença ou condições físicas que possam impactar negativamente a gestação e o seu bem-estar;
+(-c) a frequência de gestações com ninhadas de cadelas ou gatas respeita a frequência máxima fixada no ponto 3 do Anexo I;
+(-d) as gatas a lactar não são acasaladas nem inseminadas;
+(-e) os cães e gatos que deixem de ser utilizados para reprodução, nomeadamente em resultado das disposições do presente Regulamento, são mantidos ou vendidos, doados ou realojados, não sendo mortos nem abandonados.</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Art.º 33.º do RGBEAC — Regime Geral do Bem-Estar dos Animais de Companhia (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Artigo 33.º — Cuidados de saúde
+1 — Os detentores dos animais de companhia devem assegurar-lhes os cuidados de saúde adequados, nomeadamente seguindo as orientações da DGAV em matéria de vacinação e tratamentos obrigatórios, bem como consultas regulares junto de médico veterinário.
+2 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
+3 — Os médicos veterinários e os centros de atendimento médico-veterinário (CAMV) devem manter um arquivo com os dados clínicos de cada animal, pelo período mínimo de cinco anos, que ficará à disposição das autoridades competentes.
+[dim]4 — Os CAMV, enquanto estabelecimentos de saúde, colaborarão na vigilância epidemiológica das doenças de notificação obrigatória que detetem e no seu controlo.
+[dim]5 — Os médicos veterinários denunciam, junto da DGAV ou demais entidades com competência de fiscalização do cumprimento das normas constantes do presente decreto-lei, sempre que, no exercício de sua profissão, suspeitem de maus-tratos a animais de companhia.</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Art.º 6.º (Cuidados médico-veterinários) do Código do Animal — DL n.º 214/2013</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 6.º — Cuidados médico-veterinários
+O detentor do animal deve assegurar ao animal ferido ou doente os cuidados médico-veterinários adequados, designadamente retirando o mesmo do alojamento sempre que este seja um local de venda.</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Art.º 13.º (Maneio) e art.º 16.º (Cuidados de saúde animal) do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 13.º — Maneio
+1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
+[dim]2 — O maneio deve ser feito por pessoal que possua formação teórica e prática específica ou sob a supervisão de uma pessoa competente para o efeito.
+3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados aos que tiverem sinais que levem a suspeitar estarem doentes, lesionados ou com alterações comportamentais.
+[dim]4 — O manuseamento dos animais deve ser feito de forma a não lhes causar quaisquer dores, sofrimento ou distúrbios desnecessários.
+[dim]5 — Quando houver necessidade de recorrer a meios de contenção, não devem estes causar ferimentos, dores ou angústia desnecessários aos animais.
+Artigo 16.º — Cuidados de saúde animal
+1 — Sem prejuízo de quaisquer medidas determinadas pela DGAV, deve existir um programa de profilaxia médica e sanitária devidamente elaborado e supervisionado pelo médico veterinário responsável e executado por profissionais competentes.
+2 — No âmbito do número anterior, os animais devem ser sujeitos a exames médico-veterinários de rotina, vacinações e desparasitações sempre que aconselhável.
+3 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
+4 — Sempre que se justifique, os animais doentes ou lesionados devem ser isolados em instalações adequadas e equipadas, se for caso disso, com cama seca e confortável.
+[dim]5 — Os medicamentos, produtos ou substâncias de prescrição médico-veterinária devem ser armazenados em locais secos e com acesso restrito.
+[dim]6 — A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior deve ser feita sob orientação do médico veterinário responsável.</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 prevê inspeção diária (n.º 3 do art.º 13.º) e programa de profilaxia supervisionado por veterinário (n.º 1 do art.º 16.º) — alinhamento parcial com as als. (a) e (d) do n.º 1 do art.º 13.º do @regulamento. Lacunas: (1) não distingue animais vulneráveis com maior frequência de inspeção; (2) não prevê isolamento em área separada com tratamento (al. (b)); (3) não exige consulta veterinária para decisão de eutanásia com anestesia/analgesia (al. (c)); (4) nenhuma das obrigações sanitárias para criadores previstas no n.º 2 está contemplada: sem idade mínima de reprodução, sem frequência máxima de partos, sem proibição de cobrição de fêmeas a lactar, sem regime de rehoming.</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>O @codigo limita os cuidados médico-veterinários ao animal ferido ou doente (art.º 6.º) — sem qualquer obrigação de inspeção diária, programa de profilaxia ou isolamento. É o diploma com maior divergência face ao n.º 1 do art.º 13.º do @regulamento, omitindo igualmente todas as obrigações sanitárias específicas para criadores previstas no n.º 2.</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac (art.º 33.º) centra os cuidados de saúde no detentor em geral (n.ºs 1 a 3), sem distinguir obrigações reforçadas para operadores de criação. Não prevê: inspeção diária sistemática por cuidadores; isolamento imediato de animais com bem-estar comprometido; nem qualquer dos requisitos sanitários para criadores do n.º 2 do art.º 13.º do @regulamento. Os n.ºs 4 e 5 (CAMV e denúncia de maus-tratos) não têm correspondência direta no @regulamento.</t>
+        </is>
+      </c>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>A @legislacao vigente (DL n.º 276/2001) tem o maior alinhamento, mas insuficiente. Necessidade de alteração dos três diplomas: (1) introduzir inspeção diária diferenciada para animais vulneráveis (al. (a) do n.º 1 do art.º 13.º do @regulamento); (2) criar obrigação de isolamento e tratamento imediato (al. (b)); (3) regular o processo de eutanásia com supervisão veterinária e anestesia/analgesia (al. (c)); (4) para criadores (n.º 2): fixar idade mínima e maturidade esquelética das fêmeas reprodutoras, frequência máxima de partos conforme Anexo I, proibição de cobrição de fêmeas a lactar, e regime de rehoming dos animais retirados da reprodução.</t>
+        </is>
+      </c>
+      <c r="O7" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P7" s="11" t="inlineStr"/>
+    </row>
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>Detenção Responsável e Informação</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Art.º 8.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Operators shall provide to the acquirer of a dog or cat written information necessary to enable him or her to ensure the welfare of the dog or cat including information on responsible ownership and on the specific needs of the dog or cat in terms of feeding, caring, health, housing and behavioural needs, as well as information on its health.
 1a. The written information on the dog or cat's health referred to in the first paragraph shall include at least:
@@ -1085,7 +1319,7 @@
 In case the information on the dog's or cat's health is documented in a document required under Regulation (EU) 2016/429, the operator shall transmit that document to the acquirer.</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem fornecer ao adquirente de um cão ou gato informação escrita necessária para lhe permitir assegurar o bem-estar do cão ou gato, incluindo informação sobre detenção responsável e sobre as necessidades específicas do cão ou gato em termos de alimentação, cuidados, saúde, alojamento e necessidades comportamentais, bem como informação sobre a sua saúde.
 1a. A informação escrita sobre a saúde do cão ou gato referida no parágrafo anterior deve incluir pelo menos:
@@ -1094,23 +1328,23 @@
 Caso a informação sobre a saúde do cão ou gato esteja documentada num documento exigido sob o Regulamento (UE) 2016/429, o operador deve transmitir esse documento ao adquirente.</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Art.º 8.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>1 — O detentor do animal de companhia deve possuir informação sobre as obrigações inerentes à sua detenção, incluindo direitos e responsabilidades, normas de bem-estar, cuidados de saúde, comportamento, necessidades específicas da espécie/raça, duração de vida esperada, custos de manutenção, e proibição de abandono.
 2 — Os comerciantes devem fornecer por escrito ao adquirente informação completa antes da transferência do animal, incluindo identidade e dados de contacto do comerciante, dados de identificação do animal, cuidados de saúde e estado de vacinação, e certificado de origem ou de compatibilidade quando aplicável.</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Art.º 57.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>1 — O detentor do animal deve ter acesso a informação sobre:
 a) As obrigações inerentes à sua detenção, direitos e responsabilidades;
@@ -1122,56 +1356,56 @@
 2 — Os criadores e comerciantes devem fornecer informação escrita completa ao adquirente antes da transferência do animal, incluindo dados de identificação e cuidados de saúde.</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Art.º 20.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>1 — O proprietário ou detentor de animal de companhia deve ter acesso a informação adequada sobre as suas obrigações relativas ao bem-estar do animal.
 2 — Os detentores de animais de companhia que os comercializem devem fornecer informação ao adquirente sobre o estado de saúde do animal e vacinas efetuadas.</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 20.º) é genérico e não especifica a forma escrita nem detalhes de conteúdo. O @regulamento exige informação escrita sobre necessidades específicas de bem-estar (alimentação, cuidados, saúde, alojamento, comportamento) e condiciona a transferência à transmissão dessa informação.</t>
         </is>
       </c>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="L8" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 57.º) exige informação escrita mas com âmbito mais amplo (duração de vida, custos) do que o @regulamento, que se foca especificamente em bem-estar e saúde.</t>
         </is>
       </c>
-      <c r="M6" s="10" t="inlineStr">
+      <c r="M8" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.º 8.º) aproxima-se do conteúdo do @regulamento, exigindo informação escrita antes da transferência, incluindo dados de saúde e vacinação, mas ainda sem o enfoque específico em bem-estar comportamental.</t>
         </is>
       </c>
-      <c r="N6" s="11" t="inlineStr">
+      <c r="N8" s="11" t="inlineStr">
         <is>
           <t>Necessidade de alteração: (1) formalizar requisito de informação escrita como condição de transferência de animal; (2) especificar conteúdo obrigatório sobre bem-estar, saúde e necessidades comportamentais; (3) harmonizar entre @codigo e @rgbeac quanto a âmbito e forma.</t>
         </is>
       </c>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="O8" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P6" s="11" t="inlineStr"/>
+      <c r="P8" s="11" t="inlineStr"/>
     </row>
-    <row r="7" ht="120" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Competências de Cuidadores e Bem-Estar Animal</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Art.º 9.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>1. Animal caretakers, other than volunteers in shelters and interns who are under the responsibility of a competent animal caretaker, shall have the following competences as regards the dogs and cats they are handling:
 (a) understanding of their biological behaviour and their physiological and ethological needs;
@@ -1183,7 +1417,7 @@
 3. The Commission shall, by means of implementing acts, lay down minimum requirements concerning the formal education, training or professional experience in order to acquire the competences referred to in paragraph 2 and for the training courses referred to in paragraph 2a. Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 24. The implementing act concerning the training courses referred to in paragraph 2a shall be adopted by [3 years from the date of entry into force of the Regulation].</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>1. Os cuidadores de animais, com exceção de voluntários em abrigos e estagiários sob a responsabilidade de um cuidador competente, devem ter as seguintes competências no que diz respeito aos cães e gatos que manuseiam:
 (a) compreensão do seu comportamento biológico e das suas necessidades fisiológicas e etológicas;
@@ -1195,12 +1429,12 @@
 3. A Comissão estabelecerá, por meio de atos de execução, os requisitos mínimos relativos à educação formal, formação ou experiência profissional para adquirir as competências referidas no parágrafo 2 e para os cursos de formação referidos no parágrafo 2a. Esses atos de execução serão adotados de acordo com o procedimento de exame referido no artigo 24.º. O ato de execução relativo aos cursos de formação referidos no parágrafo 2a deve ser adotado por [3 anos da data de entrada em vigor do Regulamento].</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Art.ºs 69.º, 84.º e 90.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Artigo 69.º — Formação
 A reprodução, criação, manutenção, venda ou treino de animais de companhia depende de aprovação em formação sobre detenção responsável de animais de companhia, bem como sobre as necessidades fisiológicas e etológicas específicas da espécie animal em causa, ministrada pelo ICNF, I.P. ou entidades por este certificadas.
@@ -1210,23 +1444,23 @@
 O pessoal auxiliar deve possuir os conhecimentos e a experiência adequada, o qual fica, contudo, sob a orientação do médico veterinário responsável.</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Art.º 19.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Artigo 19.º — Pessoal auxiliar
 Os alojamentos devem dispor de pessoal auxiliar que possua os conhecimentos e a aptidão necessária para assegurar os cuidados adequados aos animais, o qual fica sob a orientação do médico veterinário responsável.</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Art.º 13.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Artigo 13.º — Maneio
 1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
@@ -1234,45 +1468,45 @@
 3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados.</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 13.º) exige pessoal 'técnico competente' com 'formação teórica e prática específica' e 'inspeção diária', mas não detalha competências concretas. O @regulamento especifica 4 competências estruturadas (comportamento biológico, reconhecimento de sofrimento, maneio e bem-estar, conhecimento de obrigações) e exige documentação de educação/formação/experiência.</t>
         </is>
       </c>
-      <c r="L7" s="9" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 19.º) é genérico: exige apenas 'conhecimentos e aptidão necessária' sob orientação do médico veterinário responsável. Não detalha competências concretas nem exigências de formação formal.</t>
         </is>
       </c>
-      <c r="M7" s="10" t="inlineStr">
+      <c r="M9" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.ºs 69.º, 84.º, 90.º) aproxima-se mais do @regulamento: exige 'conhecimentos e experiência adequados', menciona 'necessidades fisiológicas e etológicas', exige formação certificada pelo ICNF. Lacuna: não detalha as 4 competências específicas do @regulamento (reconhecimento de sofrimento, condicionamento operante, etc.).</t>
         </is>
       </c>
-      <c r="N7" s="11" t="inlineStr">
+      <c r="N9" s="11" t="inlineStr">
         <is>
           <t>Alinhamento parcial do @rgbeac com @regulamento. Para @codigo e @legislacao, necessidade de: (1) detalhar as 4 competências específicas (comportamento, reconhecimento de sofrimento, maneio positivo, conhecimento de obrigações); (2) exigir documentação formal de educação/formação/experiência; (3) requerer que operador designe formador responsável que transfira conhecimento; (4) implementar requisitos mínimos de formação via regulamento delegado.</t>
         </is>
       </c>
-      <c r="O7" s="11" t="inlineStr">
+      <c r="O9" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P7" s="11" t="inlineStr"/>
+      <c r="P9" s="11" t="inlineStr"/>
     </row>
-    <row r="8" ht="120" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Avaliação e Supervisão de Bem-Estar</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Art.º 10.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Operators shall:
 (a) ensure that the establishments under their responsibility receive a visit by a veterinarian within the first year after the date of application of this Regulation or within the first year after having notified a new establishment, for the purpose of identifying and assessing any risk factor for the welfare of the dogs or cats and advising the operator on measures to address those risks; thereafter the visits from a veterinarian shall take place when appropriate, based on a risk analysis by the competent authorities; Member States may provide for that the advisory welfare visits are annual;
@@ -1280,7 +1514,7 @@
 By 24 months from the date of entry into force of this Regulation, the Commission shall adopt delegated acts in accordance with Article 23 supplementing this Article in order to lay down minimum criteria to be assessed during the advisory welfare visit.</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem:
 (a) assegurar que os estabelecimentos sob a sua responsabilidade recebem uma visita de um médico veterinário no prazo de um ano a partir da data de aplicação do presente Regulamento ou no prazo de um ano após notificação de novo estabelecimento, com o objetivo de identificar e avaliar quaisquer fatores de risco para o bem-estar dos cães ou gatos e aconselhar o operador sobre medidas para resolver esses riscos; depois, as visitas do médico veterinário devem ocorrer quando apropriado, com base numa análise de risco pelas autoridades competentes; os Estados-Membros podem estabelecer que as visitas de aconselhamento de bem-estar sejam anuais;
@@ -1288,12 +1522,12 @@
 Dentro de 24 meses a partir da data de entrada em vigor do presente Regulamento, a Comissão deve adotar atos delegados em conformidade com o artigo 23.º que complementem o presente artigo de forma a estabelecer critérios mínimos a serem avaliados durante a visita de aconselhamento de bem-estar.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Art.º 56.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Artigo 56.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem, com exceção dos alojamentos para hospedagem com fins higiénicos, devem ter ao seu serviço um médico veterinário responsável pelo alojamento.
@@ -1304,12 +1538,12 @@
 d) A colaboração com as autoridades competentes em todas as ações que estas determinem.</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>Art.º 32.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>Artigo 32.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem sem fins lucrativos e com fins lucrativos de animais, com exceção dos com fins higiénicos, necessitam de ter ao seu serviço um médico veterinário que seja responsável pelo alojamento.
@@ -1319,12 +1553,12 @@
 c) A colaboração com as autoridades competentes em todas as ações que estas determinarem.</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Art.º 4.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>Artigo 4.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem sem fins lucrativos e com fins lucrativos de animais, com exceção dos alojamentos para hospedagem com fins higiénicos, devem ter ao seu serviço um médico veterinário que seja responsável pelo alojamento.
@@ -1334,45 +1568,45 @@
 c) A colaboração com as autoridades competentes em todas as ações que estas determinarem.</t>
         </is>
       </c>
-      <c r="K8" s="8" t="inlineStr">
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 4.º) estabelece a obrigação de ter médico veterinário responsável que execute 'programas e ações' para saúde e bem-estar, mas não especifica que essa avaliação deve ocorrer em prazo determinado (ex.: 1 ano) ou que os registos devem ser mantidos por período específico (4 anos). O @regulamento é mais prescritivo neste aspecto.</t>
         </is>
       </c>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="L10" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 32.º) replica quase verbatim o art.º 4.º do DL n.º 276/2001, mantendo as mesmas lacunas: não fixa prazos para avaliações de bem-estar nem obrigações de manutenção de registos estruturados.</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="M10" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.º 56.º) reforça a obrigação com 'parecer relativo à verificação das condições higiossanitárias e de bem-estar', mas igualmente sem prazos específicos para avaliações ou duração de retenção de registos. Ambos focam-se em 'programas' interno, não em 'visitas periódicas externas'.</t>
         </is>
       </c>
-      <c r="N8" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>Lacuna estrutural em toda a legislação nacional: enquanto o @regulamento exige 'visita de um veterinário' num prazo específico (1 ano) com manutenção de registos por 4 anos e transmissão entre veterinários, a legislação nacional concentra-se em ter um 'médico veterinário responsável' no estabelecimento. Necessidade de alteração: (1) formalizar obrigação de 'visita de avaliação' por veterinário dentro de 1 ano após notificação; (2) exigir avaliações periódicas conforme risco; (3) obrigatória manutenção de registos por 4 anos; (4) garantir transmissão de informações ao próximo veterinário avaliador; (5) estabelecer critérios mínimos de avaliação (bem-estar comportamental, alojamento, saúde, etc.).</t>
         </is>
       </c>
-      <c r="O8" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P8" s="11" t="inlineStr"/>
+      <c r="P10" s="11" t="inlineStr"/>
     </row>
-    <row r="9" ht="120" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11" ht="120" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Alimentação e Hidratação</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Art.º 11.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that dogs or cats are fed in accordance with the requirements laid down in point 1 of Annex I.
 2. Operators shall ensure that dogs or cats are adequately fed and hydrated by supplying:
@@ -1388,7 +1622,7 @@
 3a. Where advised in writing by a veterinarian to do so, the operators may adjust the feeding and watering frequencies for an individual dog or cat. The operators shall keep a record of the advice for its entire duration as advised by the veterinarian.</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>1 — Os operadores devem assegurar que os cães e gatos são alimentados de acordo com os requisitos estabelecidos no ponto 1 do Anexo I.
 2 — Os operadores devem assegurar que os cães e gatos são adequadamente alimentados e hidratados fornecendo:
@@ -1404,79 +1638,79 @@
 3a — Quando aconselhado por escrito por um médico veterinário, os operadores podem ajustar as frequências de alimentação e hidratação para um cão ou gato individual. Os operadores devem manter um registo do conselho durante toda a sua duração, conforme aconselhado pelo médico veterinário.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso no @rgbeac]</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso no @codigo]</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso na legislação vigente]</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K11" s="8" t="inlineStr">
         <is>
           <t>Verificar conformidade com legislação portuguesa vigente</t>
         </is>
       </c>
-      <c r="L9" s="9" t="inlineStr">
+      <c r="L11" s="9" t="inlineStr">
         <is>
           <t>Verificar alinhamento com Código do Animal</t>
         </is>
       </c>
-      <c r="M9" s="10" t="inlineStr">
+      <c r="M11" s="10" t="inlineStr">
         <is>
           <t>Verificar alinhamento com RGBEAC</t>
         </is>
       </c>
-      <c r="N9" s="11" t="inlineStr">
+      <c r="N11" s="11" t="inlineStr">
         <is>
           <t>Requisitos detalhados de alimentação e hidratação para cães e gatos. Novo artigo introduzido pelo Regulamento.</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O11" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P9" s="11" t="inlineStr">
+      <c r="P11" s="11" t="inlineStr">
         <is>
           <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="120" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12" ht="120" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Alojamento</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Art.º 12.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>1. Operators of breeding and selling establishments shall ensure that dogs or cats are provided with housing in accordance with point 2 of Annex I. Operators of shelters shall ensure that dogs or cats are provided with housing in accordance with point 2.2 of Annex I.
 2. Operators shall ensure that:
@@ -1498,7 +1732,7 @@
 7a. Paragraphs 2(a), (b), (ba) (da) (e), 6, 6a and 7 shall not apply to livestock guardian dogs, nor to herding dogs, during the periods where such dogs are used for guarding or herding in the context of on foot seasonal transhumance. Paragraph 2(da) shall not apply to livestock guardian dogs during the periods when such dogs are used for training purposes.</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>1 — Os operadores de estabelecimentos de criação e venda devem assegurar que os cães e gatos são alojados de acordo com o ponto 2 do Anexo I. Os operadores de abrigos devem assegurar que os cães e gatos são alojados de acordo com o ponto 2.2 do Anexo I.
 2 — Os operadores devem assegurar que:
@@ -1520,205 +1754,79 @@
 7a — Os parágrafos 2(a), (b), (ba) (da) (e), 6, 6a e 7 não se aplicam aos cães de guarda de gado, nem aos cães de pastoreio, durante os períodos em que tais cães são utilizados para guarda ou pastoreio no contexto de transumância sazonal a pé. O parágrafo 2(da) não se aplica aos cães de guarda de gado durante os períodos em que tais cães são utilizados para fins de treino.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso no @rgbeac]</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso no @codigo]</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso na legislação vigente]</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>Verificar conformidade com legislação portuguesa vigente</t>
         </is>
       </c>
-      <c r="L10" s="9" t="inlineStr">
+      <c r="L12" s="9" t="inlineStr">
         <is>
           <t>Verificar alinhamento com Código do Animal</t>
         </is>
       </c>
-      <c r="M10" s="10" t="inlineStr">
+      <c r="M12" s="10" t="inlineStr">
         <is>
           <t>Verificar alinhamento com RGBEAC</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="N12" s="11" t="inlineStr">
         <is>
           <t>Requisitos detalhados de alojamento para cães e gatos em diferentes tipos de estabelecimentos (criação, venda, abrigos). Novo artigo introduzido pelo Regulamento.</t>
         </is>
       </c>
-      <c r="O10" s="11" t="inlineStr">
+      <c r="O12" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P10" s="11" t="inlineStr">
+      <c r="P12" s="11" t="inlineStr">
         <is>
           <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="120" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Saúde e Monitorização Sanitária</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 13.º do Regulamento 2023/0447 (PE/Conselho)</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>1. Operators shall ensure that:
-(a) dogs or cats under their responsibility are inspected by animal caretakers at least once a day and vulnerable dogs and cats, such as newborns, ill or injured dogs and cats, and peri-partum bitches and queens, are inspected more frequently;
-(b) dogs or cats with compromised welfare are, where necessary, transferred without undue delay to a separate area and, where needed, receive appropriate treatment;
-(c) where the recovery of a dog or a cat with compromised welfare is not achievable and the dog or cat experiences severe pain or suffering, a veterinarian is consulted without undue delay, to decide whether the dog or cat shall be euthanised to end its suffering, and, if that is the case, to perform the euthanasia using anesthesia and analgesia;
-(d) measures to prevent and control external and internal parasites, and vaccinations to prevent common diseases to which dogs or cats are likely to be exposed are implemented;
-(e) enrichment do not present a significant risk of injury or biological or chemical contamination or any other health risk.
-Point (a) shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
-Member states may grant derogations from point (c) in cases of emergencies, where no veterinarian can be reached without undue delay, provided that national rules are put in place to ensure that:
-(i) an immediate action ending the life of the dog or cat with minimum pain and suffering using a method inducing instant death is undertaken by a trained competent person;
-(ii) the operator keeps a record of the use of the derogation for purposes of the official control.
-2. Operators of breeding establishments shall additionally ensure that:
-(-a) measures are taken to safeguard the health of dogs or cats in accordance with point 3 of Annex I;
-(-b) bitches or queens are only bred if they have reached a minimum age and skeletal maturity in accordance with point 3 of Annex I, and they have no diagnosed disease, clinical sign of diseases or physical conditions which could negatively impact their pregnancy and welfare;
-(-c) litter-giving pregnancies of bitches or queens follows a maximum frequency in accordance with point 3 of Annex I;
-(-d) lactating queens are not mated or inseminated;
-(-e) dogs and cats which are no longer used for reproduction, including as a result of the provisions of this Regulation, are either kept or sold, donated or rehomed, not killed or abandoned.</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>1 — Os operadores devem assegurar que:
-(a) os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados e fêmeas em período peri-parto, são inspecionados com maior frequência;
-(b) os cães e gatos com bem-estar comprometido são, quando necessário, transferidos sem demora injustificada para uma área separada e, se necessário, recebem tratamento adequado;
-(c) quando a recuperação de um cão ou gato com bem-estar comprometido não seja alcançável e o animal experiencie dor ou sofrimento severo, um médico veterinário é consultado sem demora injustificada para decidir se o animal deve ser objeto de eutanásia para pôr termo ao seu sofrimento e, em caso afirmativo, para realizar a eutanásia com recurso a anestesia e analgesia;
-(d) são implementadas medidas de prevenção e controlo de parasitas externos e internos, bem como vacinações para prevenção de doenças comuns às quais os cães ou gatos são suscetíveis de estar expostos;
-(e) os enriquecimentos não apresentam risco significativo de lesões ou de contaminação biológica ou química, nem qualquer outro risco para a saúde.
-A alínea (a) não se aplica aos cães de guarda de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para fins de guarda ou treino.
-Os Estados-Membros podem conceder derrogações relativamente à alínea (c) em casos de emergência, quando não seja possível contactar um médico veterinário sem demora injustificada, desde que sejam estabelecidas regras nacionais que assegurem que:
-(i) é tomada imediatamente uma ação que ponha fim à vida do cão ou gato com o mínimo de dor e sofrimento, utilizando um método que induza a morte instantânea, por uma pessoa competente e devidamente habilitada;
-(ii) o operador mantém um registo da utilização da derrogação para efeitos de controlo oficial.
-2 — Os operadores de estabelecimentos de criação devem adicionalmente assegurar que:
-(-a) são tomadas medidas para salvaguardar a saúde dos cães ou gatos em conformidade com o ponto 3 do Anexo I;
-(-b) as cadelas ou gatas só são reproduzidas se tiverem atingido a idade mínima e a maturidade esquelética em conformidade com o ponto 3 do Anexo I, e não apresentem doença diagnosticada, sinais clínicos de doença ou condições físicas que possam impactar negativamente a gestação e o seu bem-estar;
-(-c) a frequência de gestações com ninhadas de cadelas ou gatas respeita a frequência máxima fixada no ponto 3 do Anexo I;
-(-d) as gatas a lactar não são acasaladas nem inseminadas;
-(-e) os cães e gatos que deixem de ser utilizados para reprodução, nomeadamente em resultado das disposições do presente Regulamento, são mantidos ou vendidos, doados ou realojados, não sendo mortos nem abandonados.</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Art.º 33.º do RGBEAC — Regime Geral do Bem-Estar dos Animais de Companhia (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Artigo 33.º — Cuidados de saúde
-1 — Os detentores dos animais de companhia devem assegurar-lhes os cuidados de saúde adequados, nomeadamente seguindo as orientações da DGAV em matéria de vacinação e tratamentos obrigatórios, bem como consultas regulares junto de médico veterinário.
-2 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
-3 — Os médicos veterinários e os centros de atendimento médico-veterinário (CAMV) devem manter um arquivo com os dados clínicos de cada animal, pelo período mínimo de cinco anos, que ficará à disposição das autoridades competentes.
-[dim]4 — Os CAMV, enquanto estabelecimentos de saúde, colaborarão na vigilância epidemiológica das doenças de notificação obrigatória que detetem e no seu controlo.
-[dim]5 — Os médicos veterinários denunciam, junto da DGAV ou demais entidades com competência de fiscalização do cumprimento das normas constantes do presente decreto-lei, sempre que, no exercício de sua profissão, suspeitem de maus-tratos a animais de companhia.</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Art.º 6.º (Cuidados médico-veterinários) do Código do Animal — DL n.º 214/2013</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Artigo 6.º — Cuidados médico-veterinários
-O detentor do animal deve assegurar ao animal ferido ou doente os cuidados médico-veterinários adequados, designadamente retirando o mesmo do alojamento sempre que este seja um local de venda.</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Art.º 13.º (Maneio) e art.º 16.º (Cuidados de saúde animal) do DL n.º 276/2001, de 17 de outubro</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>Artigo 13.º — Maneio
-1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
-[dim]2 — O maneio deve ser feito por pessoal que possua formação teórica e prática específica ou sob a supervisão de uma pessoa competente para o efeito.
-3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados aos que tiverem sinais que levem a suspeitar estarem doentes, lesionados ou com alterações comportamentais.
-[dim]4 — O manuseamento dos animais deve ser feito de forma a não lhes causar quaisquer dores, sofrimento ou distúrbios desnecessários.
-[dim]5 — Quando houver necessidade de recorrer a meios de contenção, não devem estes causar ferimentos, dores ou angústia desnecessários aos animais.
-Artigo 16.º — Cuidados de saúde animal
-1 — Sem prejuízo de quaisquer medidas determinadas pela DGAV, deve existir um programa de profilaxia médica e sanitária devidamente elaborado e supervisionado pelo médico veterinário responsável e executado por profissionais competentes.
-2 — No âmbito do número anterior, os animais devem ser sujeitos a exames médico-veterinários de rotina, vacinações e desparasitações sempre que aconselhável.
-3 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
-4 — Sempre que se justifique, os animais doentes ou lesionados devem ser isolados em instalações adequadas e equipadas, se for caso disso, com cama seca e confortável.
-[dim]5 — Os medicamentos, produtos ou substâncias de prescrição médico-veterinária devem ser armazenados em locais secos e com acesso restrito.
-[dim]6 — A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior deve ser feita sob orientação do médico veterinário responsável.</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 276/2001 prevê inspeção diária (n.º 3 do art.º 13.º) e programa de profilaxia supervisionado por veterinário (n.º 1 do art.º 16.º) — alinhamento parcial com as als. (a) e (d) do n.º 1 do art.º 13.º do @regulamento. Lacunas: (1) não distingue animais vulneráveis com maior frequência de inspeção; (2) não prevê isolamento em área separada com tratamento (al. (b)); (3) não exige consulta veterinária para decisão de eutanásia com anestesia/analgesia (al. (c)); (4) nenhuma das obrigações sanitárias para criadores previstas no n.º 2 está contemplada: sem idade mínima de reprodução, sem frequência máxima de partos, sem proibição de cobrição de fêmeas a lactar, sem regime de rehoming.</t>
-        </is>
-      </c>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>O @codigo limita os cuidados médico-veterinários ao animal ferido ou doente (art.º 6.º) — sem qualquer obrigação de inspeção diária, programa de profilaxia ou isolamento. É o diploma com maior divergência face ao n.º 1 do art.º 13.º do @regulamento, omitindo igualmente todas as obrigações sanitárias específicas para criadores previstas no n.º 2.</t>
-        </is>
-      </c>
-      <c r="M11" s="10" t="inlineStr">
-        <is>
-          <t>O @rgbeac (art.º 33.º) centra os cuidados de saúde no detentor em geral (n.ºs 1 a 3), sem distinguir obrigações reforçadas para operadores de criação. Não prevê: inspeção diária sistemática por cuidadores; isolamento imediato de animais com bem-estar comprometido; nem qualquer dos requisitos sanitários para criadores do n.º 2 do art.º 13.º do @regulamento. Os n.ºs 4 e 5 (CAMV e denúncia de maus-tratos) não têm correspondência direta no @regulamento.</t>
-        </is>
-      </c>
-      <c r="N11" s="11" t="inlineStr">
-        <is>
-          <t>A @legislacao vigente (DL n.º 276/2001) tem o maior alinhamento, mas insuficiente. Necessidade de alteração dos três diplomas: (1) introduzir inspeção diária diferenciada para animais vulneráveis (al. (a) do n.º 1 do art.º 13.º do @regulamento); (2) criar obrigação de isolamento e tratamento imediato (al. (b)); (3) regular o processo de eutanásia com supervisão veterinária e anestesia/analgesia (al. (c)); (4) para criadores (n.º 2): fixar idade mínima e maturidade esquelética das fêmeas reprodutoras, frequência máxima de partos conforme Anexo I, proibição de cobrição de fêmeas a lactar, e regime de rehoming dos animais retirados da reprodução.</t>
-        </is>
-      </c>
-      <c r="O11" s="11" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P11" s="11" t="inlineStr"/>
-    </row>
-    <row r="12" ht="120" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Necessidades Comportamentais</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Art.º 14.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that measures are taken to meet the behavioural needs of dogs or cats in accordance with point 4 of Annex I.
 2. Operators shall not keep dogs or cats in areas restraining their natural movements, except in case of Article 12(3), second sub-paragraph, or for performing the following procedures or treatments:
@@ -1735,7 +1843,7 @@
 5b. Operators shall ensure that enrichment is provided and accessible to all dogs or cats, creating a stimulating environment, enabling species-specific behaviour and reducing their frustration.</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>1 — Os operadores devem assegurar que medidas são tomadas para satisfazer as necessidades comportamentais dos cães ou gatos de acordo com o ponto 4 do Anexo I.
 2 — Os operadores não devem manter cães ou gatos em áreas que restringem os seus movimentos naturais, exceto no caso do Artigo 12(3), segundo parágrafo, ou para realizar os seguintes procedimentos ou tratamentos:
@@ -1752,79 +1860,79 @@
 5b — Os operadores devem assegurar que enriquecimento é fornecido e acessível a todos os cães ou gatos, criando um ambiente estimulante, permitindo comportamento específico da espécie e reduzindo sua frustração.</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso no @rgbeac]</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso no @codigo]</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso na legislação vigente]</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t>Verificar conformidade com legislação portuguesa vigente</t>
         </is>
       </c>
-      <c r="L12" s="9" t="inlineStr">
+      <c r="L13" s="9" t="inlineStr">
         <is>
           <t>Verificar alinhamento com Código do Animal</t>
         </is>
       </c>
-      <c r="M12" s="10" t="inlineStr">
+      <c r="M13" s="10" t="inlineStr">
         <is>
           <t>Verificar alinhamento com RGBEAC</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr">
+      <c r="N13" s="11" t="inlineStr">
         <is>
           <t>Requisitos de satisfação das necessidades comportamentais de cães e gatos. Proibição de retenção em áreas restritivas. Novo artigo introduzido pelo Regulamento.</t>
         </is>
       </c>
-      <c r="O12" s="11" t="inlineStr">
+      <c r="O13" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P12" s="11" t="inlineStr">
+      <c r="P13" s="11" t="inlineStr">
         <is>
           <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="120" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Práticas Dolorosas</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Art.º 15.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that mutilations, including ear cropping, tail docking, claw removal or other partial or complete digit amputation, and resection of vocal cords or folds, are not performed unless upon medical indication, which may include prophylactic, with the sole purpose of preserving, improving the health of dogs or cats or preventing injury. In such case, the procedure shall only be performed under anaesthesia and prolonged analgesia and by a veterinarian.
 1a. The medical indication for the mutilation and the details of procedure carried out shall be documented by a veterinarian. This document shall be retained by the operator until the dog or cat, together with this document, is transferred to another establishment or owner. The operator of the establishment where the mutilation was performed shall retain a copy of the document for three years after the transfer of the dog or cat.
@@ -1841,7 +1949,7 @@
 4. Member States may grant derogations from paragraph 3 for dogs intended for use in military, police or customs services.</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>1 — Os operadores devem assegurar que mutilações, incluindo corte de orelhas, corte de cauda, remoção de garras ou outra amputação parcial ou completa de dígitos, e ressecção de cordas vocais ou pregas, não são realizadas a menos que seja por indicação médica, que pode incluir profilática, com o único propósito de preservar, melhorar a saúde de cães ou gatos ou prevenir lesões. Nesse caso, o procedimento deve ser realizado apenas sob anestesia e analgesia prolongada e por um médico veterinário.
 1a — A indicação médica para a mutilação e os detalhes do procedimento realizado devem ser documentados por um médico veterinário. Este documento deve ser retido pelo operador até o cão ou gato, juntamente com este documento, ser transferido para outro estabelecimento ou proprietário. O operador do estabelecimento onde a mutilação foi realizada deve reter uma cópia do documento por três anos após a transferência do cão ou gato.
@@ -1858,174 +1966,66 @@
 4 — Os Estados-Membros podem conceder derrogações do parágrafo 3 para cães destinados ao uso em serviços militares, policiais ou aduaneiros.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso no @rgbeac]</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso no @codigo]</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso na legislação vigente]</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>Verificar conformidade com legislação portuguesa vigente</t>
         </is>
       </c>
-      <c r="L13" s="9" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>Verificar alinhamento com Código do Animal</t>
         </is>
       </c>
-      <c r="M13" s="10" t="inlineStr">
+      <c r="M14" s="10" t="inlineStr">
         <is>
           <t>Verificar alinhamento com RGBEAC</t>
         </is>
       </c>
-      <c r="N13" s="11" t="inlineStr">
+      <c r="N14" s="11" t="inlineStr">
         <is>
           <t>Requisitos relativos a práticas dolorosas e mutilações em cães e gatos. Restrições a práticas de manipulação causando dor. Novo artigo introduzido pelo Regulamento.</t>
         </is>
       </c>
-      <c r="O13" s="11" t="inlineStr">
+      <c r="O14" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P13" s="11" t="inlineStr">
+      <c r="P14" s="11" t="inlineStr">
         <is>
           <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="120" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Identificação e Registo</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 17.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>1. All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip compliant with Annex II.
-1a. Operators shall ensure that dogs and cats born in their establishments are individually identified within 3 months after their birth and in any event before the date of their placing on the market.
-Operators of selling establishments, shelters and those placing and being responsible for dogs and cats in foster homes shall ensure that dogs and cats that enter their establishments or come under their responsibility are individually identified within 30 days after their arrival at the establishment and in any event before the date of their placing on the market.
-Pet owners and any other natural or legal persons, other than operators, who own dogs or cats, shall ensure that the dogs or cats are individually identified at the latest when the dog or cat reaches 3 months of age or, in case the dog or cat is placed on the market, before the date of their placing on the market.
-2. The implantation of the transponder shall be performed by a veterinarian. Member States may allow the implantation of transponders in cats to be performed by a person other than a veterinarian, if it is done under the responsibility of a veterinarian.
-3. Dogs and cats which have been individually identified by means of an injectable transponder containing a microchip, in accordance with national legislation prior to entry into force of this Regulation, shall be recognised as identified in accordance with the requirements of this Article.
-4. Within two working days after their identification, the dogs and cats shall be registered by a veterinarian in a national database.
-5. For dogs and cats kept in establishments, the registration shall be made in the name of the operator of the establishment. For dogs and cats placed in foster homes, the registration shall be made in the name of the person responsible for the foster home. For dogs and cats owned by pet owners or by any other natural or legal person, the registration shall be made in the name of the pet owner or the natural or legal person.
-Member States may grant derogations from the first subparagraph to military, police and customs dogs.
-6. In case of placing on the market or occasional and irregular donation by a natural person without online advertising, the requirements for registration shall not apply.
-7. In the case of a death of a dog or a cat, the operator, pet owner or natural or legal person owning the dog or cat shall inform the national database.
-8. In case of unreadable transponder, the operator or the natural or legal person responsible for the dog or cat shall ensure that the dog or cat is re-identified with a new transponder and re-registered in the national database.</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>1. Todos os cães e gatos mantidos em estabelecimentos colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com o Anexo II.
-1a. Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de 3 meses após o nascimento e, em qualquer caso, antes da data da sua colocação no mercado.
-Os operadores de estabelecimentos de venda, abrigos e os que colocam e são responsáveis por cães e gatos em famílias de acolhimento devem assegurar que os cães e gatos que entrem nos seus estabelecimentos sejam identificados individualmente no prazo de 30 dias após a chegada.
-Os donos de animais de companhia e quaisquer outras pessoas singulares ou coletivas que detenham cães ou gatos devem assegurar que os animais sejam identificados individualmente o mais tardar quando o animal atingir os 3 meses de idade ou, no caso de o animal ser colocado no mercado, antes da data da sua colocação no mercado.
-2. A implantação do transponder devem ser efetuada por um médico veterinário. Os Estados-Membros podem permitir que a implantação de transponders em gatos seja efetuada por pessoa que não seja médico veterinário, se for feita sob a responsabilidade de um médico veterinário.
-3. Cães e gatos que tenham sido identificados individualmente por meio de um transponder injetável contendo um microchip, em conformidade com legislação nacional anterior à entrada em vigor do presente Regulamento, são reconhecidos como identificados de acordo com os requisitos do presente artigo.
-4. No prazo de dois dias úteis após a sua identificação, os cães e gatos devem ser registados por um médico veterinário numa base de dados nacional.
-5. Para cães e gatos mantidos em estabelecimentos, o registo deve ser efetuado em nome do operador do estabelecimento. Para cães e gatos colocados em famílias de acolhimento, o registo deve ser efetuado em nome da pessoa responsável pela família de acolhimento. Para cães e gatos detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva, o registo deve ser efetuado em nome do dono ou da pessoa singular ou coletiva.
-Os Estados-Membros podem conceder derrogações ao primeiro parágrafo a cães militares, policiais e aduaneiros.
-6. Em caso de colocação no mercado ou cedência ocasional e irregular por pessoa singular sem publicidade em linha, os requisitos de registo não se aplicam.
-7. Em caso de morte de um cão ou gato, o operador, dono do animal ou pessoa singular ou coletiva proprietária devem informar a base de dados nacional.
-8. Em caso de transponder ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato devem assegurar que o animal é reidentificado com um novo transponder e re-registado na base de dados nacional.</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Art.º 17.º do RGBEAC (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>1 — A identificação dos animais de companhia, pela sua marcação, quando aplicável, e registo no SIAC, deve ser realizada:
-a) Relativamente aos cães, gatos e furões nascidos em alojamentos, até aos três meses de idade ou, em qualquer caso, antes da sua colocação no mercado;
-b) Relativamente aos cães, gatos e furões que entrem em alojamentos, nos termos dos artigos 12.º a 15.º, até trinta dias após a sua chegada ao alojamento ou, em qualquer caso, antes da data de colocação no mercado;
-c) Relativamente aos cães, gatos e furões detidos por pessoas singulares, exceto nos casos previstos nas alíneas anteriores, até aos três meses de idade ou, no caso de colocação no mercado, antes da data de colocação no mercado.</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Art.º 53.º do Código do Animal (DL n.º 214/2013)</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>1 — Todos os cães devem ser identificados e registados, entre os três e os seis meses de idade.
-2 — Os gatos em exposição, para fins comerciais ou lucrativos, em estabelecimentos de venda, locais de criação, feiras ou concursos, provas funcionais, publicidade ou fins similares, devem ser identificados e registados entre os três e os seis meses de idade.
-4 — Os cães e gatos são identificados através de método electrónico e registados na base de dados nacional.
-5 — A identificação electrónica é efetuada através da aplicação subcutânea de um microchip no centro da face lateral esquerda do pescoço.</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>n.ºs 1, 2 e 3 do art.º 5.º do DL n.º 82/2019, de 27 de junho</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>1 — A identificação dos animais de companhia, pela sua marcação e registo no SIAC, deve ser realizada até 120 dias após o seu nascimento.
-2 — Na impossibilidade de determinar a data de nascimento exata, para efeitos de contagem do prazo referido no número anterior, a identificação deve ser efetuada até à perda dos dentes incisivos de leite.
-3 — Sem prejuízo dos números anteriores, e relativamente aos cães, gatos e furões que sejam cedidos e ou comercializados a partir de um criador ou de um estabelecimento autorizado para a detenção de animais de companhia, nomeadamente os centros de hospedagem com ou sem fins lucrativos e os centros de recolha oficiais, deve ser assegurada a sua marcação e registo no SIAC antes de abandonarem a instalação de nascimento ou de alojamento, independentemente da sua idade.</t>
-        </is>
-      </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 82/2019 (art.º 5.º) prevê prazo geral de 120 dias após o nascimento, sem distinguir o contexto de estabelecimento — prazo superior ao máximo de 3 meses do @regulamento, que exigirá redução. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>O @codigo fixa prazo de identificação entre 3 e 6 meses, igualmente sem distinção entre nascimentos e entrada em estabelecimentos, ficando aquém da precisão exigida pelo @regulamento.</t>
-        </is>
-      </c>
-      <c r="M14" s="10" t="inlineStr">
-        <is>
-          <t>O @rgbeac aproxima-se dos prazos do @regulamento mas aplica-se apenas a cães, gatos e furões. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
-        </is>
-      </c>
-      <c r="N14" s="11" t="inlineStr">
-        <is>
-          <t>Necessidade de alteração: (1) reduzir prazo máximo de identificação de nascimentos para 3 meses; (2) criar prazo diferenciado de 30 dias para animais admitidos em estabelecimentos; (3) harmonizar prazos entre todos os diplomas nacionais.</t>
-        </is>
-      </c>
-      <c r="O14" s="11" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P14" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -1640,32 +1640,43 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Art.º 51.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso no @rgbeac]</t>
+          <t>1 - Deve existir um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies e dos indivíduos de acordo com a fase de evolução fisiológica em que se encontram, nomeadamente idade, sexo, fêmeas prenhes ou em fase de lactação.
+2 - As refeições devem ainda ser distribuídas segundo a rotina que mais se adequar à espécie e de forma a manter aspetos do seu comportamento alimentar natural, incluindo comedouros interativos e outros dispositivos adequados à espécie.
+3 - O número, formato e distribuição de comedouros e bebedouros deve ser tal que permita aos animais satisfazerem as suas necessidades sem que haja competição dentro do grupo.
+4 - Os alimentos devem ser preparados e armazenados de acordo com padrões estritos de higiene, em locais secos, limpos, livres de agentes patogénicos e de produtos tóxicos e, no caso dos alimentos compostos, devem, ainda, ser armazenados sobre estrados ou prateleiras.
+5 – Sempre que se justifique, devem existir aparelhos de frio para uma eficiente conservação dos alimentos.
+6 - Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Código do Animal (DL 214/2013)</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso no @codigo]</t>
+          <t>Art.º 20.º - Identidade e localização
+(...) aquele que detenha cão deverá [...] fornecer ao animal água e alimento em quantidade adequada às suas necessidades de acordo com a época do ano.
+Art.º 23.º - Deveres gerais
+(...) Devem ser fornecidos aos animais, de forma regular, água fresca e alimento adequado à sua espécie e fase de vida.</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>DL 276/2001, Art.º 2.º; DL 82/2019, Art.º 13.º</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso na legislação vigente]</t>
+          <t>DL 276/2001, Art.º 2.º:
+(...) Os animais devem ter acesso permanente a água potável e a alimento adequado.
+DL 82/2019, Art.º 13.º:
+(...) Alimentação e hidratação adequadas ao estado de saúde e às necessidades do animal.</t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
@@ -1756,32 +1767,45 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Art.º 48.º e 49.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso no @rgbeac]</t>
+          <t>Art.º 48.º:
+1 - A temperatura, ventilação, luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do bem-estar e conforto das espécies que albergam.
+2 - Os fatores ambientais referidos no número anterior devem ser adequados às necessidades específicas de animais quando em fase reprodutiva, recém-nascidos ou doentes.
+3 - A luz deve preferencialmente natural, mas quando a luz artificial for imprescindível, esta deve ser o mais próxima possível do espectro da luz solar e deve respeitar o fotoperíodo natural do local onde o animal está instalado.
+Art.º 49.º:
+1 - Os alojamentos devem ser construídos por forma a permitir a acomodação adequada dos animais, permitindo aos mesmos movimento natural, circulação, repouso confortável, expressão de comportamentos naturais e a fácil inspeção.
+2 - Os alojamentos devem ser mantidos limpos, em bom estado de conservação, livres de humidade excessiva e adequadamente ventilados.</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Art.º 14.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso no @codigo]</t>
+          <t>1 - A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam.
+2 - Os fatores ambientais referidos no número anterior devem ser adequados às necessidades específicas de animais quando em fase reprodutiva, recém-nascidos ou doentes.
+3 - A luz deve ser preferencialmente natural, mas quando a luz artificial for imprescindível, esta deve ser o mais próxima possível do espectro da luz solar e deve respeitar o fotoperíodo natural do local onde o animal está instalado.
+4 - As instalações devem permitir uma adequada inspeção dos animais, devendo ainda existir equipamento alternativo, nomeadamente focos de luz, para o caso de falência do equipamento central.
+5 - Os tanques ou aquários devem possuir água de qualidade adequada aos animais que a utilizem, nomeadamente tratada por produtos ou substâncias que não prejudiquem a sua saúde.</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>DL 276/2001, Art.ºs 3.º e 4.º</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso na legislação vigente]</t>
+          <t>Art.º 3.º - Alojamento
+(...) deve ser apropriado ao bem-estar do animal, tendo em conta as suas necessidades e particularidades fisiológicas e etológicas.
+Art.º 4.º - Espaço
+(...) O animal deve dispor de espaço suficiente para se deitar, erguer-se, virar-se e movimentar-se naturalmente.</t>
         </is>
       </c>
       <c r="K12" s="8" t="inlineStr">
@@ -1862,32 +1886,38 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Art.º 52.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso no @rgbeac]</t>
+          <t>7 – Todos os alojamentos para hospedagem de cães e gatos, à exceção dos alojamentos com fins higiénicos, devem dispor de um plano de socialização e enriquecimento ambiental.
+(...) As interações do pessoal técnico com os animais devem ser positivas, regulares, previsíveis, e não forçadas.
+Enriquecimento ambiental [Art. 4.º do RGBEAC]: conjunto de técnicas de maneio e conceção dos alojamentos que visam aumentar a diversidade do ambiente, promover a expressão de comportamentos naturais e melhorar o bem-estar dos animais.</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Art.º 7.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso no @codigo]</t>
+          <t>1 - Os detentores de cães devem promover o treino dos mesmos, com vista à sua socialização e obediência.
+2 - O treino dos cães é realizado de acordo com as boas práticas em uso no exercício da atividade.</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>DL 82/2019, Art.º 15.º; Lei 27/2016, Art.º 2.º</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso na legislação vigente]</t>
+          <t>Art.º 15.º - Enriquecimento ambiental
+Os operadores de estabelecimentos de criação devem fornecer enriquecimento ambiental adequado ao comportamento natural dos cães e gatos.
+Lei 27/2016, Art.º 2.º:
+Os centros de recolha devem dispor de espaço e equipamentos que permitam aos animais expressar comportamentos naturais.</t>
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr">
@@ -1968,32 +1998,39 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Art.º 60.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso no @rgbeac]</t>
+          <t>3 - A reprodução de animais não destinados à criação, em particular os cães e os gatos, deve ser controlada, devendo utilizar-se preferencialmente a esterilização cirúrgica, sob parecer do médico veterinário.
+4 - A esterilização dos animais a que se refere o número anterior apenas pode ser realizada por médico-veterinário, o qual deve garantir o mínimo sofrimento daqueles.</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Art.º 5.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso no @codigo]</t>
+          <t>3 - É proibida a violência contra animais, considerando-se como tal todos os atos que, sem necessidade, infligem a morte, o sofrimento, abuso ou lesões a um animal, designadamente os seguintes:
+a) Agredir animais, nomeadamente com o uso de chicotes, estimulantes elétricos ou objetos contundentes ou perfurantes, ou com murros, bofetadas ou pontapés;
+b) Restringir a liberdade de movimentos dos animais de tal forma que lhes seja impedido levantar-se, deitar-se ou virar-se sobre si próprios;
+c) Usar equipamentos de maneio, contenção ou treino, que causem sofrimento desnecessário ou lesões aos animais.</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>DL 276/2001, Art.º 7.º; Lei 27/2016</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso na legislação vigente]</t>
+          <t>DL 276/2001, Art.º 7.º:
+É proibido submeter animais a práticas que causem dor, sofrimento ou lesões injustificadas.
+Lei 27/2016 (Rede de centros de recolha):
+Proibição do abate de animais errantes como forma de controlo populacional.</t>
         </is>
       </c>
       <c r="K14" s="8" t="inlineStr">

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -664,97 +664,107 @@
     <row r="2" ht="120" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Princípios Gerais de Bem-Estar</t>
+          <t>Identificação e Registo</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Art.º 5.º do Regulamento 2023/0447</t>
+          <t>Art.º 17.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Operators shall apply the following general welfare principles with respect to dogs or cats bred or kept in their establishment:
-(a) dogs and cats are provided with water and feed of a quality and of a quantity that enables them to have appropriate nutrition and hydration;
-(b) dogs and cats are kept in an appropriate and regularly cleaned physical environment which is secure and comfortable, especially in terms of space, air quality, temperature, light, protection against adverse climatic conditions and ease of movement, preventing overcrowding;
-(c) dogs and cats are kept safe, clean and in good health by preventing diseases, injuries, and pain, due in particular to management, handling practices and breeding practices;
-(d) dogs and cats are kept in an environment that enables them to exhibit species-specific and social non-harmful behaviour, and to establish a positive relationship with human beings;
-(e) dogs and cats are kept in such a way as to optimise their mental state by preventing or reducing negative stimuli in duration and intensity, as well as by maximising opportunities for positive stimuli in duration and intensity, preventing the development of abnormal repetitive and other behaviours indicative of negative animal welfare, and taking into consideration the individual dog's or cat's needs in the different domains referred to in points (a) to (d).</t>
+          <t>1. All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip compliant with Annex II.
+1a. Operators shall ensure that dogs and cats born in their establishments are individually identified within 3 months after their birth and in any event before the date of their placing on the market.
+Operators of selling establishments, shelters and those placing and being responsible for dogs and cats in foster homes shall ensure that dogs and cats that enter their establishments or come under their responsibility are individually identified within 30 days after their arrival at the establishment and in any event before the date of their placing on the market.
+Pet owners and any other natural or legal persons, other than operators, who own dogs or cats, shall ensure that the dogs or cats are individually identified at the latest when the dog or cat reaches 3 months of age or, in case the dog or cat is placed on the market, before the date of their placing on the market.
+2. The implantation of the transponder shall be performed by a veterinarian. Member States may allow the implantation of transponders in cats to be performed by a person other than a veterinarian, if it is done under the responsibility of a veterinarian.
+3. Dogs and cats which have been individually identified by means of an injectable transponder containing a microchip, in accordance with national legislation prior to entry into force of this Regulation, shall be recognised as identified in accordance with the requirements of this Article.
+4. Within two working days after their identification, the dogs and cats shall be registered by a veterinarian in a national database.
+5. For dogs and cats kept in establishments, the registration shall be made in the name of the operator of the establishment. For dogs and cats placed in foster homes, the registration shall be made in the name of the person responsible for the foster home. For dogs and cats owned by pet owners or by any other natural or legal person, the registration shall be made in the name of the pet owner or the natural or legal person.
+Member States may grant derogations from the first subparagraph to military, police and customs dogs.
+6. In case of placing on the market or occasional and irregular donation by a natural person without online advertising, the requirements for registration shall not apply.
+7. In the case of a death of a dog or a cat, the operator, pet owner or natural or legal person owning the dog or cat shall inform the national database.
+8. In case of unreadable transponder, the operator or the natural or legal person responsible for the dog or cat shall ensure that the dog or cat is re-identified with a new transponder and re-registered in the national database.</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Os operadores devem aplicar os seguintes princípios gerais de bem-estar aos cães e gatos criados ou detidos nos seus estabelecimentos:
-(a) os cães e gatos são alimentados e abebeirados com água e ração de qualidade e quantidade adequadas a uma nutrição e hidratação apropriadas;
-(b) os cães e gatos são mantidos num ambiente físico adequado, regularmente limpo, seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, iluminação, proteção face a condições climáticas adversas e facilidade de movimentação, prevenindo a sobrelotação;
-(c) os cães e gatos são mantidos seguros, limpos e com boa saúde, prevenindo doenças, lesões e dor, nomeadamente através de práticas de maneio, manuseamento e reprodução adequadas;
-(d) os cães e gatos são mantidos num ambiente que lhes permite exibir comportamentos específicos da espécie e comportamentos sociais não nocivos, e estabelecer uma relação positiva com os seres humanos;
-(e) os cães e gatos são mantidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo estímulos negativos em duração e intensidade, maximizando oportunidades de estímulos positivos, prevenindo o desenvolvimento de comportamentos repetitivos anormais, tendo em conta as necessidades individuais do animal nos domínios referidos nas alíneas (a) a (d).</t>
+          <t>1. Todos os cães e gatos mantidos em estabelecimentos colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com o Anexo II.
+1a. Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de 3 meses após o nascimento e, em qualquer caso, antes da data da sua colocação no mercado.
+Os operadores de estabelecimentos de venda, abrigos e os que colocam e são responsáveis por cães e gatos em famílias de acolhimento devem assegurar que os cães e gatos que entrem nos seus estabelecimentos sejam identificados individualmente no prazo de 30 dias após a chegada.
+Os donos de animais de companhia e quaisquer outras pessoas singulares ou coletivas que detenham cães ou gatos devem assegurar que os animais sejam identificados individualmente o mais tardar quando o animal atingir os 3 meses de idade ou, no caso de o animal ser colocado no mercado, antes da data da sua colocação no mercado.
+2. A implantação do transponder devem ser efetuada por um médico veterinário. Os Estados-Membros podem permitir que a implantação de transponders em gatos seja efetuada por pessoa que não seja médico veterinário, se for feita sob a responsabilidade de um médico veterinário.
+3. Cães e gatos que tenham sido identificados individualmente por meio de um transponder injetável contendo um microchip, em conformidade com legislação nacional anterior à entrada em vigor do presente Regulamento, são reconhecidos como identificados de acordo com os requisitos do presente artigo.
+4. No prazo de dois dias úteis após a sua identificação, os cães e gatos devem ser registados por um médico veterinário numa base de dados nacional.
+5. Para cães e gatos mantidos em estabelecimentos, o registo deve ser efetuado em nome do operador do estabelecimento. Para cães e gatos colocados em famílias de acolhimento, o registo deve ser efetuado em nome da pessoa responsável pela família de acolhimento. Para cães e gatos detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva, o registo deve ser efetuado em nome do dono ou da pessoa singular ou coletiva.
+Os Estados-Membros podem conceder derrogações ao primeiro parágrafo a cães militares, policiais e aduaneiros.
+6. Em caso de colocação no mercado ou cedência ocasional e irregular por pessoa singular sem publicidade em linha, os requisitos de registo não se aplicam.
+7. Em caso de morte de um cão ou gato, o operador, dono do animal ou pessoa singular ou coletiva proprietária devem informar a base de dados nacional.
+8. Em caso de transponder ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato devem assegurar que o animal é reidentificado com um novo transponder e re-registado na base de dados nacional.</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>al. a) do n.º 1 do art.º 10.º do RGBEAC (proposta, jun. 2025)</t>
+          <t>Art.º 17.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>1 — O detentor do animal de companhia deve:
-a) Assegurar o bem-estar do animal, de acordo com sua espécie, raça, idade e necessidades físicas e etológicas, proporcionando-lhe:
-— Atenção, supervisão, controlo, exercício físico e estímulo mental;
-— Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável;
-— Condições higiossanitárias que atendam, no mínimo, ao estabelecido no presente decreto-lei e na demais legislação aplicável;
-— Liberdade de movimento, sendo proibidos todos os sistemas de contenção permanentes;
-— Abrigo adequado, em termos de tamanho e qualidade, com vista a proteger de condições atmosféricas adversas, incluindo frio, chuva, sol ou calor excessivos, com cama seca, limpa e confortável;
-— Contato social adequado a cada espécie, de acordo com a sua idade e atividade.</t>
+          <t>1 — A identificação dos animais de companhia, pela sua marcação, quando aplicável, e registo no SIAC, deve ser realizada:
+a) Relativamente aos cães, gatos e furões nascidos em alojamentos, até aos três meses de idade ou, em qualquer caso, antes da sua colocação no mercado;
+b) Relativamente aos cães, gatos e furões que entrem em alojamentos, nos termos dos artigos 12.º a 15.º, até trinta dias após a sua chegada ao alojamento ou, em qualquer caso, antes da data de colocação no mercado;
+c) Relativamente aos cães, gatos e furões detidos por pessoas singulares, exceto nos casos previstos nas alíneas anteriores, até aos três meses de idade ou, no caso de colocação no mercado, antes da data de colocação no mercado.</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>n.ºs 1, 2 e 3 do art.º 5.º do Código do Animal (DL n.º 214/2013)</t>
+          <t>Art.º 53.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal.
-2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
-3 — É proibida a violência contra animais, considerando-se como tal todos os atos que, sem necessidade, infligem a morte, o sofrimento, abuso ou lesões a um animal.</t>
+          <t>1 — Todos os cães devem ser identificados e registados, entre os três e os seis meses de idade.
+2 — Os gatos em exposição, para fins comerciais ou lucrativos, em estabelecimentos de venda, locais de criação, feiras ou concursos, provas funcionais, publicidade ou fins similares, devem ser identificados e registados entre os três e os seis meses de idade.
+4 — Os cães e gatos são identificados através de método electrónico e registados na base de dados nacional.
+5 — A identificação electrónica é efetuada através da aplicação subcutânea de um microchip no centro da face lateral esquerda do pescoço.</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>n.º 1 do art.º 7.º e n.º 1 do art.º 9.º do DL n.º 276/2001, de 17 de outubro</t>
+          <t>n.ºs 1, 2 e 3 do art.º 5.º do DL n.º 82/2019, de 27 de junho</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>Artigo 7.º, n.º 1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
-Artigo 9.º, n.º 1 — A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam.</t>
+          <t>1 — A identificação dos animais de companhia, pela sua marcação e registo no SIAC, deve ser realizada até 120 dias após o seu nascimento.
+2 — Na impossibilidade de determinar a data de nascimento exata, para efeitos de contagem do prazo referido no número anterior, a identificação deve ser efetuada até à perda dos dentes incisivos de leite.
+3 — Sem prejuízo dos números anteriores, e relativamente aos cães, gatos e furões que sejam cedidos e ou comercializados a partir de um criador ou de um estabelecimento autorizado para a detenção de animais de companhia, nomeadamente os centros de hospedagem com ou sem fins lucrativos e os centros de recolha oficiais, deve ser assegurada a sua marcação e registo no SIAC antes de abandonarem a instalação de nascimento ou de alojamento, independentemente da sua idade.</t>
         </is>
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>O DL n.º 276/2001 (art.ºs 7.º e 9.º) consagra os mesmos parâmetros mas desenvolve-os em artigos separados (alojamento, alimentação, ambiente) sem os denominar como domínios nem os sistematizar de forma unificada segundo o referencial OMSA.</t>
+          <t>O DL n.º 82/2019 (art.º 5.º) prevê prazo geral de 120 dias após o nascimento, sem distinguir o contexto de estabelecimento — prazo superior ao máximo de 3 meses do @regulamento, que exigirá redução. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>O @codigo (art.º 5.º) refere 'parâmetros de bem-estar animal' genericamente, sem adotar formalmente a nomenclatura dos 5 domínios OMSA nem a sua sistematização explícita.</t>
+          <t>O @codigo fixa prazo de identificação entre 3 e 6 meses, igualmente sem distinção entre nascimentos e entrada em estabelecimentos, ficando aquém da precisão exigida pelo @regulamento.</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac (art.º 10.º, n.º 1, al. a)) articula obrigações equivalentes ao nível do detentor de forma descritiva, sem sistematização nos 5 domínios nem referência ao quadro OMSA.</t>
+          <t>O @rgbeac aproxima-se dos prazos do @regulamento mas aplica-se apenas a cães, gatos e furões. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
       <c r="N2" s="11" t="inlineStr">
         <is>
-          <t>Alinhamento substancial de conteúdo; sem necessidade de alteração imediata. Recomenda-se a adoção formal dos 5 domínios OMSA como referencial estruturante em futura revisão legislativa ou em normas de orientação técnica da DGAV.</t>
+          <t>Necessidade de alteração: (1) reduzir prazo máximo de identificação de nascimentos para 3 meses; (2) criar prazo diferenciado de 30 dias para animais admitidos em estabelecimentos; (3) harmonizar prazos entre todos os diplomas nacionais.</t>
         </is>
       </c>
       <c r="O2" s="11" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="P2" s="11" t="inlineStr"/>
@@ -863,114 +873,15 @@
     <row r="4" ht="120" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Estratégias de Criação — Conformação e Consanguinidade</t>
+          <t>Reprodução e Criação</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Art.º 6.º-A do Regulamento 2023/0447</t>
+          <t>Art.º 7.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>1. Operators of breeding establishments shall ensure that their breeding strategies minimise the risk of producing dogs or cats with genotypes associated with detrimental effects on their health and welfare.
-2. Operators of breeding establishments shall not use for reproduction dogs or cats that have excessive conformational traits leading to a high risk of detrimental effects on the welfare of these dogs or cats, or of their offspring. Before selection for breeding of a dog or cat that may be concerned by an excessive conformational trait the operator shall consult a veterinarian or an independent qualified person under the responsibility of a veterinarian. The veterinarian or independent qualified person shall assess whether the dog or cat has an excessive conformational trait.
-3. The Commission is empowered to adopt, taking into account scientific opinions of the European Food Safety Authority as well as the social and economic impacts, delegated acts in accordance with Article 23 supplementing this Regulation by:
-(a) defining characteristics of the genotypes referred to in paragraph 1, which shall be excluded from reproduction, and the methods for their assessment and the record keeping requirements;
-(b) defining excessive conformational traits referred to in paragraph 2 of this Article, which shall be excluded from reproduction, the methods for their assessment and the record keeping requirements.
-4. The delegated acts concerning the excessive conformational traits shall be adopted by 1 July 2030. The delegated acts concerning the genotypes shall be adopted by 1 July 2036.
-5. The following shall be prohibited in the management of the reproduction of dogs and cats:
-(a) the breeding between parents and offspring, between siblings, between half-siblings or between grandparents and grandchildren, unless approved by the competent authority based on a specific need to preserve local breeds with a limited genetic pool;
-(b) the breeding to produce hybrids.</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>1. Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
-2. Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem traços conformacionais excessivos que conduzam a um risco elevado de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por traço conformacional excessivo, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem um traço conformacional excessivo.
-3. A Comissão tem competência para adotar, tendo em conta os pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, bem como os impactos sociais e económicos, atos delegados em conformidade com o artigo 23.º que complementem este Regulamento:
-(a) definindo características dos genótipos a que se refere o parágrafo 1, que devem ser excluídos da reprodução, e os métodos para a sua avaliação e requisitos de manutenção de registos;
-(b) definindo traços conformacionais excessivos a que se refere o parágrafo 2 do presente artigo, que devem ser excluídos da reprodução, os métodos para a sua avaliação e requisitos de manutenção de registos.
-4. Os atos delegados relativos aos traços conformacionais excessivos devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
-5. São proibidos na gestão da reprodução de cães e gatos:
-(a) o cruzamento entre progenitores e descendentes, entre irmãos, entre meios-irmãos ou entre avós e netos, exceto com aprovação da autoridade competente por razão de necessidade específica de preservação de raças locais com reserva genética limitada;
-(b) o cruzamento para produção de híbridos.</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>n.ºs 1 e 2 do art.º 34.º do RGBEAC (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>1 — As intervenções cirúrgicas com o objetivo da modificação da aparência ou com fins não curativos ou não destinados a impedir a reprodução dos animais são proibidas, nos termos do disposto na alínea i) do n.º 1 do artigo 12.º.
-2 — O detentor de animal sujeito a intervenção curativa que modifique a sua aparência deve possuir documento comprovativo da necessidade da mesma, passado pelo médico veterinário que a ela procedeu, sob a forma de atestado do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura, ou, no caso de animais importados, documento comprovativo da necessidade dessa intervenção, emitida pelo médico veterinário que a ela procedeu, legalizado pela autoridade competente do respetivo país.</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>n.º 2, als. a), b) e c) do art.º 8.º do Código do Animal (DL n.º 214/2013)</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>2 — A reprodução de animais obedece ao seguinte:
-a) Os animais só devem ser utilizados na reprodução depois de atingida a maturidade reprodutiva para a espécie e raça devendo, no caso dos cães e gatos, seguir os parâmetros referidos no anexo I ao presente diploma, do qual faz parte integrante, não sendo autorizado, no caso das fêmeas, o acasalamento em cios sucessivos;
-b) Deve ser respeitada a regra do porte semelhante dos progenitores, para prevenir a possibilidade de distócia;
-c) Devem ser excluídos da reprodução, os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia da anca nos cães e rim poliquístico nos gatos, ou alterações comportamentais.</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>art.º 17.º e n.º 1 do art.º 18.º do DL n.º 276/2001, de 17 de outubro</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>Artigo 17.º — As intervenções cirúrgicas, nomeadamente as destinadas ao corte de caudas nos canídeos, têm de ser executadas por um médico veterinário.
-Artigo 18.º, n.º 1 — Os detentores de animais de companhia que os apresentem com quaisquer amputações que modifiquem a aparência dos animais ou com fins não curativos devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa amputação, nomeadamente discriminando que as mesmas foram feitas por razões médico-veterinárias ou no interesse particular do animal ou para impedir a reprodução.</t>
-        </is>
-      </c>
-      <c r="K4" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 276/2001 (art.ºs 17.º e 18.º) exige intervenção veterinária em cirurgias e documentação para amputações, mas não prevê qualquer restrição à reprodução por traços conformacionais excessivos nem proibição de consanguinidade próxima ou hibridação.</t>
-        </is>
-      </c>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>O @codigo (art.º 8.º, n.º 2) exclui da reprodução animais com defeitos genéticos e malformações (displasia, rim poliquístico) e proíbe cios sucessivos, mas não prevê o conceito de traços conformacionais excessivos nem a proibição de consanguinidade.</t>
-        </is>
-      </c>
-      <c r="M4" s="10" t="inlineStr">
-        <is>
-          <t>O @rgbeac (art.º 34.º) proíbe intervenções cirúrgicas de modificação da aparência, mas não contém qualquer norma sobre estratégia genética de criação, conformação excessiva ou consanguinidade.</t>
-        </is>
-      </c>
-      <c r="N4" s="11" t="inlineStr">
-        <is>
-          <t>Lacuna normativa transversal. Necessidade de criar norma específica que: (1) defina traços conformacionais excessivos (a regular por ato delegado europeu até 2030); (2) proíba consanguinidade próxima (pais/filhos, irmãos, avós/netos); (3) proíba a produção de híbridos; (4) imponha consulta veterinária prévia ao acasalamento de animais potencialmente afetados.</t>
-        </is>
-      </c>
-      <c r="O4" s="11" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P4" s="11" t="inlineStr"/>
-    </row>
-    <row r="5" ht="120" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Reprodução e Criação</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 7.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Operators shall notify the competent authorities of their activity, providing at least the following information:
 (a) name, address and contact details of the operator;
@@ -981,7 +892,7 @@
 (ea) for breeding establishments, the estimated number of litters to be placed on the market per year.</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem notificar as autoridades competentes da sua atividade, fornecendo pelo menos as seguintes informações:
 (a) nome, morada e contactos do operador;
@@ -992,24 +903,24 @@
 (ea) para os estabelecimentos de criação, o número estimado de ninhadas a colocar no mercado por ano.</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Art.º 43.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1 — Os centros de bem-estar animal procedem à esterilização dos animais recolhidos que se presuma terem sido abandonados, nos termos do artigo 41.º.
 2 — As câmaras municipais devem, sempre que necessário e sob a responsabilidade do médico veterinário municipal, incentivar e promover programas de esterilização de animais de companhia, nomeadamente os cães e gatos, em complementaridade com os centros de bem-estar animal.
 3 — Os requisitos mínimos das instalações adequadas à realização de esterilizações nos centros de bem-estar animal são estabelecidos em portaria do membro do Governo responsável pela área da agricultura.</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Art.º 8.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>1 — A reprodução de animais deve ser realizada de forma planeada.
 2 — A reprodução de animais obedece ao seguinte:
@@ -1018,12 +929,12 @@
 c) Devem ser excluídos da reprodução os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia.</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>n.º 1 do art.º 3.º-A do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>1 — A mera comunicação prévia a que se refere a alínea a) do n.º 1 do artigo anterior é dirigida à DGAV e deve conter os seguintes elementos, quando aplicáveis:
 a) O nome ou a denominação social do interessado;
@@ -1038,29 +949,127 @@
 j) Declaração de responsabilidade, subscrita pelo interessado, relativa ao cumprimento da legislação aplicável aos animais de companhia, nomeadamente em matéria de instalações, equipamentos, higiene, saúde e bem-estar dos animais.</t>
         </is>
       </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 (art.º 3.º-A) prevê comunicação prévia à DGAV com elementos parcialmente equivalentes (capacidade máxima, espécies, raças). Não exige a estimativa anual de ninhadas a colocar no mercado (al. ea) do @regulamento), constituindo lacuna parcial. É o diploma mais próximo do @regulamento neste eixo.</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>O @codigo regula condições de reprodução (art.º 8.º) mas não prevê qualquer sistema de notificação ou registo de estabelecimentos criadores junto da autoridade competente.</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac trata da esterilização de errantes e CED, mas não contém norma sobre notificação de criadores ou registo de estabelecimentos com fins de reprodução comercial.</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="inlineStr">
+        <is>
+          <t>A @legislacao vigente é o diploma base adequado para a transposição. Necessidade de ajuste: acrescentar a obrigação de estimativa anual de ninhadas a colocar no mercado e alinhar os restantes elementos informativos com a lista exaustiva do art.º 7.º do @regulamento.</t>
+        </is>
+      </c>
+      <c r="O4" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P4" s="11" t="inlineStr"/>
+    </row>
+    <row r="5" ht="120" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Princípios Gerais de Bem-Estar</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 5.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Operators shall apply the following general welfare principles with respect to dogs or cats bred or kept in their establishment:
+(a) dogs and cats are provided with water and feed of a quality and of a quantity that enables them to have appropriate nutrition and hydration;
+(b) dogs and cats are kept in an appropriate and regularly cleaned physical environment which is secure and comfortable, especially in terms of space, air quality, temperature, light, protection against adverse climatic conditions and ease of movement, preventing overcrowding;
+(c) dogs and cats are kept safe, clean and in good health by preventing diseases, injuries, and pain, due in particular to management, handling practices and breeding practices;
+(d) dogs and cats are kept in an environment that enables them to exhibit species-specific and social non-harmful behaviour, and to establish a positive relationship with human beings;
+(e) dogs and cats are kept in such a way as to optimise their mental state by preventing or reducing negative stimuli in duration and intensity, as well as by maximising opportunities for positive stimuli in duration and intensity, preventing the development of abnormal repetitive and other behaviours indicative of negative animal welfare, and taking into consideration the individual dog's or cat's needs in the different domains referred to in points (a) to (d).</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Os operadores devem aplicar os seguintes princípios gerais de bem-estar aos cães e gatos criados ou detidos nos seus estabelecimentos:
+(a) os cães e gatos são alimentados e abebeirados com água e ração de qualidade e quantidade adequadas a uma nutrição e hidratação apropriadas;
+(b) os cães e gatos são mantidos num ambiente físico adequado, regularmente limpo, seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, iluminação, proteção face a condições climáticas adversas e facilidade de movimentação, prevenindo a sobrelotação;
+(c) os cães e gatos são mantidos seguros, limpos e com boa saúde, prevenindo doenças, lesões e dor, nomeadamente através de práticas de maneio, manuseamento e reprodução adequadas;
+(d) os cães e gatos são mantidos num ambiente que lhes permite exibir comportamentos específicos da espécie e comportamentos sociais não nocivos, e estabelecer uma relação positiva com os seres humanos;
+(e) os cães e gatos são mantidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo estímulos negativos em duração e intensidade, maximizando oportunidades de estímulos positivos, prevenindo o desenvolvimento de comportamentos repetitivos anormais, tendo em conta as necessidades individuais do animal nos domínios referidos nas alíneas (a) a (d).</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>al. a) do n.º 1 do art.º 10.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1 — O detentor do animal de companhia deve:
+a) Assegurar o bem-estar do animal, de acordo com sua espécie, raça, idade e necessidades físicas e etológicas, proporcionando-lhe:
+— Atenção, supervisão, controlo, exercício físico e estímulo mental;
+— Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável;
+— Condições higiossanitárias que atendam, no mínimo, ao estabelecido no presente decreto-lei e na demais legislação aplicável;
+— Liberdade de movimento, sendo proibidos todos os sistemas de contenção permanentes;
+— Abrigo adequado, em termos de tamanho e qualidade, com vista a proteger de condições atmosféricas adversas, incluindo frio, chuva, sol ou calor excessivos, com cama seca, limpa e confortável;
+— Contato social adequado a cada espécie, de acordo com a sua idade e atividade.</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>n.ºs 1, 2 e 3 do art.º 5.º do Código do Animal (DL n.º 214/2013)</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal.
+2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
+3 — É proibida a violência contra animais, considerando-se como tal todos os atos que, sem necessidade, infligem a morte, o sofrimento, abuso ou lesões a um animal.</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>n.º 1 do art.º 7.º e n.º 1 do art.º 9.º do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 7.º, n.º 1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
+Artigo 9.º, n.º 1 — A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam.</t>
+        </is>
+      </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>O DL n.º 276/2001 (art.º 3.º-A) prevê comunicação prévia à DGAV com elementos parcialmente equivalentes (capacidade máxima, espécies, raças). Não exige a estimativa anual de ninhadas a colocar no mercado (al. ea) do @regulamento), constituindo lacuna parcial. É o diploma mais próximo do @regulamento neste eixo.</t>
+          <t>O DL n.º 276/2001 (art.ºs 7.º e 9.º) consagra os mesmos parâmetros mas desenvolve-os em artigos separados (alojamento, alimentação, ambiente) sem os denominar como domínios nem os sistematizar de forma unificada segundo o referencial OMSA.</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>O @codigo regula condições de reprodução (art.º 8.º) mas não prevê qualquer sistema de notificação ou registo de estabelecimentos criadores junto da autoridade competente.</t>
+          <t>O @codigo (art.º 5.º) refere 'parâmetros de bem-estar animal' genericamente, sem adotar formalmente a nomenclatura dos 5 domínios OMSA nem a sua sistematização explícita.</t>
         </is>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac trata da esterilização de errantes e CED, mas não contém norma sobre notificação de criadores ou registo de estabelecimentos com fins de reprodução comercial.</t>
+          <t>O @rgbeac (art.º 10.º, n.º 1, al. a)) articula obrigações equivalentes ao nível do detentor de forma descritiva, sem sistematização nos 5 domínios nem referência ao quadro OMSA.</t>
         </is>
       </c>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>A @legislacao vigente é o diploma base adequado para a transposição. Necessidade de ajuste: acrescentar a obrigação de estimativa anual de ninhadas a colocar no mercado e alinhar os restantes elementos informativos com a lista exaustiva do art.º 7.º do @regulamento.</t>
+          <t>Alinhamento substancial de conteúdo; sem necessidade de alteração imediata. Recomenda-se a adoção formal dos 5 domínios OMSA como referencial estruturante em futura revisão legislativa ou em normas de orientação técnica da DGAV.</t>
         </is>
       </c>
       <c r="O5" s="11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="P5" s="11" t="inlineStr"/>
@@ -1068,15 +1077,240 @@
     <row r="6" ht="120" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>Estratégias de Criação — Conformação e Consanguinidade</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 6.º-A do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>1. Operators of breeding establishments shall ensure that their breeding strategies minimise the risk of producing dogs or cats with genotypes associated with detrimental effects on their health and welfare.
+2. Operators of breeding establishments shall not use for reproduction dogs or cats that have excessive conformational traits leading to a high risk of detrimental effects on the welfare of these dogs or cats, or of their offspring. Before selection for breeding of a dog or cat that may be concerned by an excessive conformational trait the operator shall consult a veterinarian or an independent qualified person under the responsibility of a veterinarian. The veterinarian or independent qualified person shall assess whether the dog or cat has an excessive conformational trait.
+3. The Commission is empowered to adopt, taking into account scientific opinions of the European Food Safety Authority as well as the social and economic impacts, delegated acts in accordance with Article 23 supplementing this Regulation by:
+(a) defining characteristics of the genotypes referred to in paragraph 1, which shall be excluded from reproduction, and the methods for their assessment and the record keeping requirements;
+(b) defining excessive conformational traits referred to in paragraph 2 of this Article, which shall be excluded from reproduction, the methods for their assessment and the record keeping requirements.
+4. The delegated acts concerning the excessive conformational traits shall be adopted by 1 July 2030. The delegated acts concerning the genotypes shall be adopted by 1 July 2036.
+5. The following shall be prohibited in the management of the reproduction of dogs and cats:
+(a) the breeding between parents and offspring, between siblings, between half-siblings or between grandparents and grandchildren, unless approved by the competent authority based on a specific need to preserve local breeds with a limited genetic pool;
+(b) the breeding to produce hybrids.</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>1. Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
+2. Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem traços conformacionais excessivos que conduzam a um risco elevado de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por traço conformacional excessivo, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem um traço conformacional excessivo.
+3. A Comissão tem competência para adotar, tendo em conta os pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, bem como os impactos sociais e económicos, atos delegados em conformidade com o artigo 23.º que complementem este Regulamento:
+(a) definindo características dos genótipos a que se refere o parágrafo 1, que devem ser excluídos da reprodução, e os métodos para a sua avaliação e requisitos de manutenção de registos;
+(b) definindo traços conformacionais excessivos a que se refere o parágrafo 2 do presente artigo, que devem ser excluídos da reprodução, os métodos para a sua avaliação e requisitos de manutenção de registos.
+4. Os atos delegados relativos aos traços conformacionais excessivos devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
+5. São proibidos na gestão da reprodução de cães e gatos:
+(a) o cruzamento entre progenitores e descendentes, entre irmãos, entre meios-irmãos ou entre avós e netos, exceto com aprovação da autoridade competente por razão de necessidade específica de preservação de raças locais com reserva genética limitada;
+(b) o cruzamento para produção de híbridos.</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>n.ºs 1 e 2 do art.º 34.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1 — As intervenções cirúrgicas com o objetivo da modificação da aparência ou com fins não curativos ou não destinados a impedir a reprodução dos animais são proibidas, nos termos do disposto na alínea i) do n.º 1 do artigo 12.º.
+2 — O detentor de animal sujeito a intervenção curativa que modifique a sua aparência deve possuir documento comprovativo da necessidade da mesma, passado pelo médico veterinário que a ela procedeu, sob a forma de atestado do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura, ou, no caso de animais importados, documento comprovativo da necessidade dessa intervenção, emitida pelo médico veterinário que a ela procedeu, legalizado pela autoridade competente do respetivo país.</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>n.º 2, als. a), b) e c) do art.º 8.º do Código do Animal (DL n.º 214/2013)</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>2 — A reprodução de animais obedece ao seguinte:
+a) Os animais só devem ser utilizados na reprodução depois de atingida a maturidade reprodutiva para a espécie e raça devendo, no caso dos cães e gatos, seguir os parâmetros referidos no anexo I ao presente diploma, do qual faz parte integrante, não sendo autorizado, no caso das fêmeas, o acasalamento em cios sucessivos;
+b) Deve ser respeitada a regra do porte semelhante dos progenitores, para prevenir a possibilidade de distócia;
+c) Devem ser excluídos da reprodução, os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia da anca nos cães e rim poliquístico nos gatos, ou alterações comportamentais.</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>art.º 17.º e n.º 1 do art.º 18.º do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 17.º — As intervenções cirúrgicas, nomeadamente as destinadas ao corte de caudas nos canídeos, têm de ser executadas por um médico veterinário.
+Artigo 18.º, n.º 1 — Os detentores de animais de companhia que os apresentem com quaisquer amputações que modifiquem a aparência dos animais ou com fins não curativos devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa amputação, nomeadamente discriminando que as mesmas foram feitas por razões médico-veterinárias ou no interesse particular do animal ou para impedir a reprodução.</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 (art.ºs 17.º e 18.º) exige intervenção veterinária em cirurgias e documentação para amputações, mas não prevê qualquer restrição à reprodução por traços conformacionais excessivos nem proibição de consanguinidade próxima ou hibridação.</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>O @codigo (art.º 8.º, n.º 2) exclui da reprodução animais com defeitos genéticos e malformações (displasia, rim poliquístico) e proíbe cios sucessivos, mas não prevê o conceito de traços conformacionais excessivos nem a proibição de consanguinidade.</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac (art.º 34.º) proíbe intervenções cirúrgicas de modificação da aparência, mas não contém qualquer norma sobre estratégia genética de criação, conformação excessiva ou consanguinidade.</t>
+        </is>
+      </c>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>Lacuna normativa transversal. Necessidade de criar norma específica que: (1) defina traços conformacionais excessivos (a regular por ato delegado europeu até 2030); (2) proíba consanguinidade próxima (pais/filhos, irmãos, avós/netos); (3) proíba a produção de híbridos; (4) imponha consulta veterinária prévia ao acasalamento de animais potencialmente afetados.</t>
+        </is>
+      </c>
+      <c r="O6" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P6" s="11" t="inlineStr"/>
+    </row>
+    <row r="7" ht="120" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Saúde e Monitorização Sanitária</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 13.º do Regulamento 2023/0447 (PE/Conselho)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>1. Operators shall ensure that:
+(a) dogs or cats under their responsibility are inspected by animal caretakers at least once a day and vulnerable dogs and cats, such as newborns, ill or injured dogs and cats, and peri-partum bitches and queens, are inspected more frequently;
+(b) dogs or cats with compromised welfare are, where necessary, transferred without undue delay to a separate area and, where needed, receive appropriate treatment;
+(c) where the recovery of a dog or a cat with compromised welfare is not achievable and the dog or cat experiences severe pain or suffering, a veterinarian is consulted without undue delay, to decide whether the dog or cat shall be euthanised to end its suffering, and, if that is the case, to perform the euthanasia using anesthesia and analgesia;
+(d) measures to prevent and control external and internal parasites, and vaccinations to prevent common diseases to which dogs or cats are likely to be exposed are implemented;
+(e) enrichment do not present a significant risk of injury or biological or chemical contamination or any other health risk.
+Point (a) shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
+Member states may grant derogations from point (c) in cases of emergencies, where no veterinarian can be reached without undue delay, provided that national rules are put in place to ensure that:
+(i) an immediate action ending the life of the dog or cat with minimum pain and suffering using a method inducing instant death is undertaken by a trained competent person;
+(ii) the operator keeps a record of the use of the derogation for purposes of the official control.
+2. Operators of breeding establishments shall additionally ensure that:
+(-a) measures are taken to safeguard the health of dogs or cats in accordance with point 3 of Annex I;
+(-b) bitches or queens are only bred if they have reached a minimum age and skeletal maturity in accordance with point 3 of Annex I, and they have no diagnosed disease, clinical sign of diseases or physical conditions which could negatively impact their pregnancy and welfare;
+(-c) litter-giving pregnancies of bitches or queens follows a maximum frequency in accordance with point 3 of Annex I;
+(-d) lactating queens are not mated or inseminated;
+(-e) dogs and cats which are no longer used for reproduction, including as a result of the provisions of this Regulation, are either kept or sold, donated or rehomed, not killed or abandoned.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>1 — Os operadores devem assegurar que:
+(a) os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados e fêmeas em período peri-parto, são inspecionados com maior frequência;
+(b) os cães e gatos com bem-estar comprometido são, quando necessário, transferidos sem demora injustificada para uma área separada e, se necessário, recebem tratamento adequado;
+(c) quando a recuperação de um cão ou gato com bem-estar comprometido não seja alcançável e o animal experiencie dor ou sofrimento severo, um médico veterinário é consultado sem demora injustificada para decidir se o animal deve ser objeto de eutanásia para pôr termo ao seu sofrimento e, em caso afirmativo, para realizar a eutanásia com recurso a anestesia e analgesia;
+(d) são implementadas medidas de prevenção e controlo de parasitas externos e internos, bem como vacinações para prevenção de doenças comuns às quais os cães ou gatos são suscetíveis de estar expostos;
+(e) os enriquecimentos não apresentam risco significativo de lesões ou de contaminação biológica ou química, nem qualquer outro risco para a saúde.
+A alínea (a) não se aplica aos cães de guarda de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para fins de guarda ou treino.
+Os Estados-Membros podem conceder derrogações relativamente à alínea (c) em casos de emergência, quando não seja possível contactar um médico veterinário sem demora injustificada, desde que sejam estabelecidas regras nacionais que assegurem que:
+(i) é tomada imediatamente uma ação que ponha fim à vida do cão ou gato com o mínimo de dor e sofrimento, utilizando um método que induza a morte instantânea, por uma pessoa competente e devidamente habilitada;
+(ii) o operador mantém um registo da utilização da derrogação para efeitos de controlo oficial.
+2 — Os operadores de estabelecimentos de criação devem adicionalmente assegurar que:
+(-a) são tomadas medidas para salvaguardar a saúde dos cães ou gatos em conformidade com o ponto 3 do Anexo I;
+(-b) as cadelas ou gatas só são reproduzidas se tiverem atingido a idade mínima e a maturidade esquelética em conformidade com o ponto 3 do Anexo I, e não apresentem doença diagnosticada, sinais clínicos de doença ou condições físicas que possam impactar negativamente a gestação e o seu bem-estar;
+(-c) a frequência de gestações com ninhadas de cadelas ou gatas respeita a frequência máxima fixada no ponto 3 do Anexo I;
+(-d) as gatas a lactar não são acasaladas nem inseminadas;
+(-e) os cães e gatos que deixem de ser utilizados para reprodução, nomeadamente em resultado das disposições do presente Regulamento, são mantidos ou vendidos, doados ou realojados, não sendo mortos nem abandonados.</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Art.º 33.º do RGBEAC — Regime Geral do Bem-Estar dos Animais de Companhia (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Artigo 33.º — Cuidados de saúde
+1 — Os detentores dos animais de companhia devem assegurar-lhes os cuidados de saúde adequados, nomeadamente seguindo as orientações da DGAV em matéria de vacinação e tratamentos obrigatórios, bem como consultas regulares junto de médico veterinário.
+2 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
+3 — Os médicos veterinários e os centros de atendimento médico-veterinário (CAMV) devem manter um arquivo com os dados clínicos de cada animal, pelo período mínimo de cinco anos, que ficará à disposição das autoridades competentes.
+[dim]4 — Os CAMV, enquanto estabelecimentos de saúde, colaborarão na vigilância epidemiológica das doenças de notificação obrigatória que detetem e no seu controlo.
+[dim]5 — Os médicos veterinários denunciam, junto da DGAV ou demais entidades com competência de fiscalização do cumprimento das normas constantes do presente decreto-lei, sempre que, no exercício de sua profissão, suspeitem de maus-tratos a animais de companhia.</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Art.º 6.º (Cuidados médico-veterinários) do Código do Animal — DL n.º 214/2013</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 6.º — Cuidados médico-veterinários
+O detentor do animal deve assegurar ao animal ferido ou doente os cuidados médico-veterinários adequados, designadamente retirando o mesmo do alojamento sempre que este seja um local de venda.</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Art.º 13.º (Maneio) e art.º 16.º (Cuidados de saúde animal) do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 13.º — Maneio
+1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
+[dim]2 — O maneio deve ser feito por pessoal que possua formação teórica e prática específica ou sob a supervisão de uma pessoa competente para o efeito.
+3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados aos que tiverem sinais que levem a suspeitar estarem doentes, lesionados ou com alterações comportamentais.
+[dim]4 — O manuseamento dos animais deve ser feito de forma a não lhes causar quaisquer dores, sofrimento ou distúrbios desnecessários.
+[dim]5 — Quando houver necessidade de recorrer a meios de contenção, não devem estes causar ferimentos, dores ou angústia desnecessários aos animais.
+Artigo 16.º — Cuidados de saúde animal
+1 — Sem prejuízo de quaisquer medidas determinadas pela DGAV, deve existir um programa de profilaxia médica e sanitária devidamente elaborado e supervisionado pelo médico veterinário responsável e executado por profissionais competentes.
+2 — No âmbito do número anterior, os animais devem ser sujeitos a exames médico-veterinários de rotina, vacinações e desparasitações sempre que aconselhável.
+3 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
+4 — Sempre que se justifique, os animais doentes ou lesionados devem ser isolados em instalações adequadas e equipadas, se for caso disso, com cama seca e confortável.
+[dim]5 — Os medicamentos, produtos ou substâncias de prescrição médico-veterinária devem ser armazenados em locais secos e com acesso restrito.
+[dim]6 — A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior deve ser feita sob orientação do médico veterinário responsável.</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 prevê inspeção diária (n.º 3 do art.º 13.º) e programa de profilaxia supervisionado por veterinário (n.º 1 do art.º 16.º) — alinhamento parcial com as als. (a) e (d) do n.º 1 do art.º 13.º do @regulamento. Lacunas: (1) não distingue animais vulneráveis com maior frequência de inspeção; (2) não prevê isolamento em área separada com tratamento (al. (b)); (3) não exige consulta veterinária para decisão de eutanásia com anestesia/analgesia (al. (c)); (4) nenhuma das obrigações sanitárias para criadores previstas no n.º 2 está contemplada: sem idade mínima de reprodução, sem frequência máxima de partos, sem proibição de cobrição de fêmeas a lactar, sem regime de rehoming.</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>O @codigo limita os cuidados médico-veterinários ao animal ferido ou doente (art.º 6.º) — sem qualquer obrigação de inspeção diária, programa de profilaxia ou isolamento. É o diploma com maior divergência face ao n.º 1 do art.º 13.º do @regulamento, omitindo igualmente todas as obrigações sanitárias específicas para criadores previstas no n.º 2.</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac (art.º 33.º) centra os cuidados de saúde no detentor em geral (n.ºs 1 a 3), sem distinguir obrigações reforçadas para operadores de criação. Não prevê: inspeção diária sistemática por cuidadores; isolamento imediato de animais com bem-estar comprometido; nem qualquer dos requisitos sanitários para criadores do n.º 2 do art.º 13.º do @regulamento. Os n.ºs 4 e 5 (CAMV e denúncia de maus-tratos) não têm correspondência direta no @regulamento.</t>
+        </is>
+      </c>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>A @legislacao vigente (DL n.º 276/2001) tem o maior alinhamento, mas insuficiente. Necessidade de alteração dos três diplomas: (1) introduzir inspeção diária diferenciada para animais vulneráveis (al. (a) do n.º 1 do art.º 13.º do @regulamento); (2) criar obrigação de isolamento e tratamento imediato (al. (b)); (3) regular o processo de eutanásia com supervisão veterinária e anestesia/analgesia (al. (c)); (4) para criadores (n.º 2): fixar idade mínima e maturidade esquelética das fêmeas reprodutoras, frequência máxima de partos conforme Anexo I, proibição de cobrição de fêmeas a lactar, e regime de rehoming dos animais retirados da reprodução.</t>
+        </is>
+      </c>
+      <c r="O7" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P7" s="11" t="inlineStr"/>
+    </row>
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>Detenção Responsável e Informação</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Art.º 8.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Operators shall provide to the acquirer of a dog or cat written information necessary to enable him or her to ensure the welfare of the dog or cat including information on responsible ownership and on the specific needs of the dog or cat in terms of feeding, caring, health, housing and behavioural needs, as well as information on its health.
 1a. The written information on the dog or cat's health referred to in the first paragraph shall include at least:
@@ -1085,7 +1319,7 @@
 In case the information on the dog's or cat's health is documented in a document required under Regulation (EU) 2016/429, the operator shall transmit that document to the acquirer.</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem fornecer ao adquirente de um cão ou gato informação escrita necessária para lhe permitir assegurar o bem-estar do cão ou gato, incluindo informação sobre detenção responsável e sobre as necessidades específicas do cão ou gato em termos de alimentação, cuidados, saúde, alojamento e necessidades comportamentais, bem como informação sobre a sua saúde.
 1a. A informação escrita sobre a saúde do cão ou gato referida no parágrafo anterior deve incluir pelo menos:
@@ -1094,23 +1328,23 @@
 Caso a informação sobre a saúde do cão ou gato esteja documentada num documento exigido sob o Regulamento (UE) 2016/429, o operador deve transmitir esse documento ao adquirente.</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Art.º 8.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>1 — O detentor do animal de companhia deve possuir informação sobre as obrigações inerentes à sua detenção, incluindo direitos e responsabilidades, normas de bem-estar, cuidados de saúde, comportamento, necessidades específicas da espécie/raça, duração de vida esperada, custos de manutenção, e proibição de abandono.
 2 — Os comerciantes devem fornecer por escrito ao adquirente informação completa antes da transferência do animal, incluindo identidade e dados de contacto do comerciante, dados de identificação do animal, cuidados de saúde e estado de vacinação, e certificado de origem ou de compatibilidade quando aplicável.</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Art.º 57.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>1 — O detentor do animal deve ter acesso a informação sobre:
 a) As obrigações inerentes à sua detenção, direitos e responsabilidades;
@@ -1122,56 +1356,56 @@
 2 — Os criadores e comerciantes devem fornecer informação escrita completa ao adquirente antes da transferência do animal, incluindo dados de identificação e cuidados de saúde.</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Art.º 20.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>1 — O proprietário ou detentor de animal de companhia deve ter acesso a informação adequada sobre as suas obrigações relativas ao bem-estar do animal.
 2 — Os detentores de animais de companhia que os comercializem devem fornecer informação ao adquirente sobre o estado de saúde do animal e vacinas efetuadas.</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 20.º) é genérico e não especifica a forma escrita nem detalhes de conteúdo. O @regulamento exige informação escrita sobre necessidades específicas de bem-estar (alimentação, cuidados, saúde, alojamento, comportamento) e condiciona a transferência à transmissão dessa informação.</t>
         </is>
       </c>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="L8" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 57.º) exige informação escrita mas com âmbito mais amplo (duração de vida, custos) do que o @regulamento, que se foca especificamente em bem-estar e saúde.</t>
         </is>
       </c>
-      <c r="M6" s="10" t="inlineStr">
+      <c r="M8" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.º 8.º) aproxima-se do conteúdo do @regulamento, exigindo informação escrita antes da transferência, incluindo dados de saúde e vacinação, mas ainda sem o enfoque específico em bem-estar comportamental.</t>
         </is>
       </c>
-      <c r="N6" s="11" t="inlineStr">
+      <c r="N8" s="11" t="inlineStr">
         <is>
           <t>Necessidade de alteração: (1) formalizar requisito de informação escrita como condição de transferência de animal; (2) especificar conteúdo obrigatório sobre bem-estar, saúde e necessidades comportamentais; (3) harmonizar entre @codigo e @rgbeac quanto a âmbito e forma.</t>
         </is>
       </c>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="O8" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P6" s="11" t="inlineStr"/>
+      <c r="P8" s="11" t="inlineStr"/>
     </row>
-    <row r="7" ht="120" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Competências de Cuidadores e Bem-Estar Animal</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Art.º 9.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>1. Animal caretakers, other than volunteers in shelters and interns who are under the responsibility of a competent animal caretaker, shall have the following competences as regards the dogs and cats they are handling:
 (a) understanding of their biological behaviour and their physiological and ethological needs;
@@ -1183,7 +1417,7 @@
 3. The Commission shall, by means of implementing acts, lay down minimum requirements concerning the formal education, training or professional experience in order to acquire the competences referred to in paragraph 2 and for the training courses referred to in paragraph 2a. Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 24. The implementing act concerning the training courses referred to in paragraph 2a shall be adopted by [3 years from the date of entry into force of the Regulation].</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>1. Os cuidadores de animais, com exceção de voluntários em abrigos e estagiários sob a responsabilidade de um cuidador competente, devem ter as seguintes competências no que diz respeito aos cães e gatos que manuseiam:
 (a) compreensão do seu comportamento biológico e das suas necessidades fisiológicas e etológicas;
@@ -1195,12 +1429,12 @@
 3. A Comissão estabelecerá, por meio de atos de execução, os requisitos mínimos relativos à educação formal, formação ou experiência profissional para adquirir as competências referidas no parágrafo 2 e para os cursos de formação referidos no parágrafo 2a. Esses atos de execução serão adotados de acordo com o procedimento de exame referido no artigo 24.º. O ato de execução relativo aos cursos de formação referidos no parágrafo 2a deve ser adotado por [3 anos da data de entrada em vigor do Regulamento].</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Art.ºs 69.º, 84.º e 90.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Artigo 69.º — Formação
 A reprodução, criação, manutenção, venda ou treino de animais de companhia depende de aprovação em formação sobre detenção responsável de animais de companhia, bem como sobre as necessidades fisiológicas e etológicas específicas da espécie animal em causa, ministrada pelo ICNF, I.P. ou entidades por este certificadas.
@@ -1210,23 +1444,23 @@
 O pessoal auxiliar deve possuir os conhecimentos e a experiência adequada, o qual fica, contudo, sob a orientação do médico veterinário responsável.</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Art.º 19.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Artigo 19.º — Pessoal auxiliar
 Os alojamentos devem dispor de pessoal auxiliar que possua os conhecimentos e a aptidão necessária para assegurar os cuidados adequados aos animais, o qual fica sob a orientação do médico veterinário responsável.</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Art.º 13.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Artigo 13.º — Maneio
 1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
@@ -1234,45 +1468,45 @@
 3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados.</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 13.º) exige pessoal 'técnico competente' com 'formação teórica e prática específica' e 'inspeção diária', mas não detalha competências concretas. O @regulamento especifica 4 competências estruturadas (comportamento biológico, reconhecimento de sofrimento, maneio e bem-estar, conhecimento de obrigações) e exige documentação de educação/formação/experiência.</t>
         </is>
       </c>
-      <c r="L7" s="9" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 19.º) é genérico: exige apenas 'conhecimentos e aptidão necessária' sob orientação do médico veterinário responsável. Não detalha competências concretas nem exigências de formação formal.</t>
         </is>
       </c>
-      <c r="M7" s="10" t="inlineStr">
+      <c r="M9" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.ºs 69.º, 84.º, 90.º) aproxima-se mais do @regulamento: exige 'conhecimentos e experiência adequados', menciona 'necessidades fisiológicas e etológicas', exige formação certificada pelo ICNF. Lacuna: não detalha as 4 competências específicas do @regulamento (reconhecimento de sofrimento, condicionamento operante, etc.).</t>
         </is>
       </c>
-      <c r="N7" s="11" t="inlineStr">
+      <c r="N9" s="11" t="inlineStr">
         <is>
           <t>Alinhamento parcial do @rgbeac com @regulamento. Para @codigo e @legislacao, necessidade de: (1) detalhar as 4 competências específicas (comportamento, reconhecimento de sofrimento, maneio positivo, conhecimento de obrigações); (2) exigir documentação formal de educação/formação/experiência; (3) requerer que operador designe formador responsável que transfira conhecimento; (4) implementar requisitos mínimos de formação via regulamento delegado.</t>
         </is>
       </c>
-      <c r="O7" s="11" t="inlineStr">
+      <c r="O9" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P7" s="11" t="inlineStr"/>
+      <c r="P9" s="11" t="inlineStr"/>
     </row>
-    <row r="8" ht="120" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Avaliação e Supervisão de Bem-Estar</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Art.º 10.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Operators shall:
 (a) ensure that the establishments under their responsibility receive a visit by a veterinarian within the first year after the date of application of this Regulation or within the first year after having notified a new establishment, for the purpose of identifying and assessing any risk factor for the welfare of the dogs or cats and advising the operator on measures to address those risks; thereafter the visits from a veterinarian shall take place when appropriate, based on a risk analysis by the competent authorities; Member States may provide for that the advisory welfare visits are annual;
@@ -1280,7 +1514,7 @@
 By 24 months from the date of entry into force of this Regulation, the Commission shall adopt delegated acts in accordance with Article 23 supplementing this Article in order to lay down minimum criteria to be assessed during the advisory welfare visit.</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem:
 (a) assegurar que os estabelecimentos sob a sua responsabilidade recebem uma visita de um médico veterinário no prazo de um ano a partir da data de aplicação do presente Regulamento ou no prazo de um ano após notificação de novo estabelecimento, com o objetivo de identificar e avaliar quaisquer fatores de risco para o bem-estar dos cães ou gatos e aconselhar o operador sobre medidas para resolver esses riscos; depois, as visitas do médico veterinário devem ocorrer quando apropriado, com base numa análise de risco pelas autoridades competentes; os Estados-Membros podem estabelecer que as visitas de aconselhamento de bem-estar sejam anuais;
@@ -1288,12 +1522,12 @@
 Dentro de 24 meses a partir da data de entrada em vigor do presente Regulamento, a Comissão deve adotar atos delegados em conformidade com o artigo 23.º que complementem o presente artigo de forma a estabelecer critérios mínimos a serem avaliados durante a visita de aconselhamento de bem-estar.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Art.º 56.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Artigo 56.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem, com exceção dos alojamentos para hospedagem com fins higiénicos, devem ter ao seu serviço um médico veterinário responsável pelo alojamento.
@@ -1304,12 +1538,12 @@
 d) A colaboração com as autoridades competentes em todas as ações que estas determinem.</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>Art.º 32.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>Artigo 32.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem sem fins lucrativos e com fins lucrativos de animais, com exceção dos com fins higiénicos, necessitam de ter ao seu serviço um médico veterinário que seja responsável pelo alojamento.
@@ -1319,12 +1553,12 @@
 c) A colaboração com as autoridades competentes em todas as ações que estas determinarem.</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Art.º 4.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>Artigo 4.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem sem fins lucrativos e com fins lucrativos de animais, com exceção dos alojamentos para hospedagem com fins higiénicos, devem ter ao seu serviço um médico veterinário que seja responsável pelo alojamento.
@@ -1334,45 +1568,45 @@
 c) A colaboração com as autoridades competentes em todas as ações que estas determinarem.</t>
         </is>
       </c>
-      <c r="K8" s="8" t="inlineStr">
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 4.º) estabelece a obrigação de ter médico veterinário responsável que execute 'programas e ações' para saúde e bem-estar, mas não especifica que essa avaliação deve ocorrer em prazo determinado (ex.: 1 ano) ou que os registos devem ser mantidos por período específico (4 anos). O @regulamento é mais prescritivo neste aspecto.</t>
         </is>
       </c>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="L10" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 32.º) replica quase verbatim o art.º 4.º do DL n.º 276/2001, mantendo as mesmas lacunas: não fixa prazos para avaliações de bem-estar nem obrigações de manutenção de registos estruturados.</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="M10" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.º 56.º) reforça a obrigação com 'parecer relativo à verificação das condições higiossanitárias e de bem-estar', mas igualmente sem prazos específicos para avaliações ou duração de retenção de registos. Ambos focam-se em 'programas' interno, não em 'visitas periódicas externas'.</t>
         </is>
       </c>
-      <c r="N8" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>Lacuna estrutural em toda a legislação nacional: enquanto o @regulamento exige 'visita de um veterinário' num prazo específico (1 ano) com manutenção de registos por 4 anos e transmissão entre veterinários, a legislação nacional concentra-se em ter um 'médico veterinário responsável' no estabelecimento. Necessidade de alteração: (1) formalizar obrigação de 'visita de avaliação' por veterinário dentro de 1 ano após notificação; (2) exigir avaliações periódicas conforme risco; (3) obrigatória manutenção de registos por 4 anos; (4) garantir transmissão de informações ao próximo veterinário avaliador; (5) estabelecer critérios mínimos de avaliação (bem-estar comportamental, alojamento, saúde, etc.).</t>
         </is>
       </c>
-      <c r="O8" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P8" s="11" t="inlineStr"/>
+      <c r="P10" s="11" t="inlineStr"/>
     </row>
-    <row r="9" ht="120" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11" ht="120" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Alimentação e Hidratação</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Art.º 11.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that dogs or cats are fed in accordance with the requirements laid down in point 1 of Annex I.
 2. Operators shall ensure that dogs or cats are adequately fed and hydrated by supplying:
@@ -1388,7 +1622,7 @@
 3a. Where advised in writing by a veterinarian to do so, the operators may adjust the feeding and watering frequencies for an individual dog or cat. The operators shall keep a record of the advice for its entire duration as advised by the veterinarian.</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>1 — Os operadores devem assegurar que os cães e gatos são alimentados de acordo com os requisitos estabelecidos no ponto 1 do Anexo I.
 2 — Os operadores devem assegurar que os cães e gatos são adequadamente alimentados e hidratados fornecendo:
@@ -1404,79 +1638,79 @@
 3a — Quando aconselhado por escrito por um médico veterinário, os operadores podem ajustar as frequências de alimentação e hidratação para um cão ou gato individual. Os operadores devem manter um registo do conselho durante toda a sua duração, conforme aconselhado pelo médico veterinário.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso no @rgbeac]</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso no @codigo]</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso na legislação vigente]</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K11" s="8" t="inlineStr">
         <is>
           <t>Verificar conformidade com legislação portuguesa vigente</t>
         </is>
       </c>
-      <c r="L9" s="9" t="inlineStr">
+      <c r="L11" s="9" t="inlineStr">
         <is>
           <t>Verificar alinhamento com Código do Animal</t>
         </is>
       </c>
-      <c r="M9" s="10" t="inlineStr">
+      <c r="M11" s="10" t="inlineStr">
         <is>
           <t>Verificar alinhamento com RGBEAC</t>
         </is>
       </c>
-      <c r="N9" s="11" t="inlineStr">
+      <c r="N11" s="11" t="inlineStr">
         <is>
           <t>Requisitos detalhados de alimentação e hidratação para cães e gatos. Novo artigo introduzido pelo Regulamento.</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O11" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P9" s="11" t="inlineStr">
+      <c r="P11" s="11" t="inlineStr">
         <is>
           <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="120" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12" ht="120" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Alojamento</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Art.º 12.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>1. Operators of breeding and selling establishments shall ensure that dogs or cats are provided with housing in accordance with point 2 of Annex I. Operators of shelters shall ensure that dogs or cats are provided with housing in accordance with point 2.2 of Annex I.
 2. Operators shall ensure that:
@@ -1498,7 +1732,7 @@
 7a. Paragraphs 2(a), (b), (ba) (da) (e), 6, 6a and 7 shall not apply to livestock guardian dogs, nor to herding dogs, during the periods where such dogs are used for guarding or herding in the context of on foot seasonal transhumance. Paragraph 2(da) shall not apply to livestock guardian dogs during the periods when such dogs are used for training purposes.</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>1 — Os operadores de estabelecimentos de criação e venda devem assegurar que os cães e gatos são alojados de acordo com o ponto 2 do Anexo I. Os operadores de abrigos devem assegurar que os cães e gatos são alojados de acordo com o ponto 2.2 do Anexo I.
 2 — Os operadores devem assegurar que:
@@ -1520,205 +1754,79 @@
 7a — Os parágrafos 2(a), (b), (ba) (da) (e), 6, 6a e 7 não se aplicam aos cães de guarda de gado, nem aos cães de pastoreio, durante os períodos em que tais cães são utilizados para guarda ou pastoreio no contexto de transumância sazonal a pé. O parágrafo 2(da) não se aplica aos cães de guarda de gado durante os períodos em que tais cães são utilizados para fins de treino.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso no @rgbeac]</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso no @codigo]</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso na legislação vigente]</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>Verificar conformidade com legislação portuguesa vigente</t>
         </is>
       </c>
-      <c r="L10" s="9" t="inlineStr">
+      <c r="L12" s="9" t="inlineStr">
         <is>
           <t>Verificar alinhamento com Código do Animal</t>
         </is>
       </c>
-      <c r="M10" s="10" t="inlineStr">
+      <c r="M12" s="10" t="inlineStr">
         <is>
           <t>Verificar alinhamento com RGBEAC</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="N12" s="11" t="inlineStr">
         <is>
           <t>Requisitos detalhados de alojamento para cães e gatos em diferentes tipos de estabelecimentos (criação, venda, abrigos). Novo artigo introduzido pelo Regulamento.</t>
         </is>
       </c>
-      <c r="O10" s="11" t="inlineStr">
+      <c r="O12" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P10" s="11" t="inlineStr">
+      <c r="P12" s="11" t="inlineStr">
         <is>
           <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="120" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Saúde e Monitorização Sanitária</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 13.º do Regulamento 2023/0447 (PE/Conselho)</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>1. Operators shall ensure that:
-(a) dogs or cats under their responsibility are inspected by animal caretakers at least once a day and vulnerable dogs and cats, such as newborns, ill or injured dogs and cats, and peri-partum bitches and queens, are inspected more frequently;
-(b) dogs or cats with compromised welfare are, where necessary, transferred without undue delay to a separate area and, where needed, receive appropriate treatment;
-(c) where the recovery of a dog or a cat with compromised welfare is not achievable and the dog or cat experiences severe pain or suffering, a veterinarian is consulted without undue delay, to decide whether the dog or cat shall be euthanised to end its suffering, and, if that is the case, to perform the euthanasia using anesthesia and analgesia;
-(d) measures to prevent and control external and internal parasites, and vaccinations to prevent common diseases to which dogs or cats are likely to be exposed are implemented;
-(e) enrichment do not present a significant risk of injury or biological or chemical contamination or any other health risk.
-Point (a) shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
-Member states may grant derogations from point (c) in cases of emergencies, where no veterinarian can be reached without undue delay, provided that national rules are put in place to ensure that:
-(i) an immediate action ending the life of the dog or cat with minimum pain and suffering using a method inducing instant death is undertaken by a trained competent person;
-(ii) the operator keeps a record of the use of the derogation for purposes of the official control.
-2. Operators of breeding establishments shall additionally ensure that:
-(-a) measures are taken to safeguard the health of dogs or cats in accordance with point 3 of Annex I;
-(-b) bitches or queens are only bred if they have reached a minimum age and skeletal maturity in accordance with point 3 of Annex I, and they have no diagnosed disease, clinical sign of diseases or physical conditions which could negatively impact their pregnancy and welfare;
-(-c) litter-giving pregnancies of bitches or queens follows a maximum frequency in accordance with point 3 of Annex I;
-(-d) lactating queens are not mated or inseminated;
-(-e) dogs and cats which are no longer used for reproduction, including as a result of the provisions of this Regulation, are either kept or sold, donated or rehomed, not killed or abandoned.</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>1 — Os operadores devem assegurar que:
-(a) os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados e fêmeas em período peri-parto, são inspecionados com maior frequência;
-(b) os cães e gatos com bem-estar comprometido são, quando necessário, transferidos sem demora injustificada para uma área separada e, se necessário, recebem tratamento adequado;
-(c) quando a recuperação de um cão ou gato com bem-estar comprometido não seja alcançável e o animal experiencie dor ou sofrimento severo, um médico veterinário é consultado sem demora injustificada para decidir se o animal deve ser objeto de eutanásia para pôr termo ao seu sofrimento e, em caso afirmativo, para realizar a eutanásia com recurso a anestesia e analgesia;
-(d) são implementadas medidas de prevenção e controlo de parasitas externos e internos, bem como vacinações para prevenção de doenças comuns às quais os cães ou gatos são suscetíveis de estar expostos;
-(e) os enriquecimentos não apresentam risco significativo de lesões ou de contaminação biológica ou química, nem qualquer outro risco para a saúde.
-A alínea (a) não se aplica aos cães de guarda de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para fins de guarda ou treino.
-Os Estados-Membros podem conceder derrogações relativamente à alínea (c) em casos de emergência, quando não seja possível contactar um médico veterinário sem demora injustificada, desde que sejam estabelecidas regras nacionais que assegurem que:
-(i) é tomada imediatamente uma ação que ponha fim à vida do cão ou gato com o mínimo de dor e sofrimento, utilizando um método que induza a morte instantânea, por uma pessoa competente e devidamente habilitada;
-(ii) o operador mantém um registo da utilização da derrogação para efeitos de controlo oficial.
-2 — Os operadores de estabelecimentos de criação devem adicionalmente assegurar que:
-(-a) são tomadas medidas para salvaguardar a saúde dos cães ou gatos em conformidade com o ponto 3 do Anexo I;
-(-b) as cadelas ou gatas só são reproduzidas se tiverem atingido a idade mínima e a maturidade esquelética em conformidade com o ponto 3 do Anexo I, e não apresentem doença diagnosticada, sinais clínicos de doença ou condições físicas que possam impactar negativamente a gestação e o seu bem-estar;
-(-c) a frequência de gestações com ninhadas de cadelas ou gatas respeita a frequência máxima fixada no ponto 3 do Anexo I;
-(-d) as gatas a lactar não são acasaladas nem inseminadas;
-(-e) os cães e gatos que deixem de ser utilizados para reprodução, nomeadamente em resultado das disposições do presente Regulamento, são mantidos ou vendidos, doados ou realojados, não sendo mortos nem abandonados.</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Art.º 33.º do RGBEAC — Regime Geral do Bem-Estar dos Animais de Companhia (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Artigo 33.º — Cuidados de saúde
-1 — Os detentores dos animais de companhia devem assegurar-lhes os cuidados de saúde adequados, nomeadamente seguindo as orientações da DGAV em matéria de vacinação e tratamentos obrigatórios, bem como consultas regulares junto de médico veterinário.
-2 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
-3 — Os médicos veterinários e os centros de atendimento médico-veterinário (CAMV) devem manter um arquivo com os dados clínicos de cada animal, pelo período mínimo de cinco anos, que ficará à disposição das autoridades competentes.
-[dim]4 — Os CAMV, enquanto estabelecimentos de saúde, colaborarão na vigilância epidemiológica das doenças de notificação obrigatória que detetem e no seu controlo.
-[dim]5 — Os médicos veterinários denunciam, junto da DGAV ou demais entidades com competência de fiscalização do cumprimento das normas constantes do presente decreto-lei, sempre que, no exercício de sua profissão, suspeitem de maus-tratos a animais de companhia.</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Art.º 6.º (Cuidados médico-veterinários) do Código do Animal — DL n.º 214/2013</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Artigo 6.º — Cuidados médico-veterinários
-O detentor do animal deve assegurar ao animal ferido ou doente os cuidados médico-veterinários adequados, designadamente retirando o mesmo do alojamento sempre que este seja um local de venda.</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Art.º 13.º (Maneio) e art.º 16.º (Cuidados de saúde animal) do DL n.º 276/2001, de 17 de outubro</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>Artigo 13.º — Maneio
-1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
-[dim]2 — O maneio deve ser feito por pessoal que possua formação teórica e prática específica ou sob a supervisão de uma pessoa competente para o efeito.
-3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados aos que tiverem sinais que levem a suspeitar estarem doentes, lesionados ou com alterações comportamentais.
-[dim]4 — O manuseamento dos animais deve ser feito de forma a não lhes causar quaisquer dores, sofrimento ou distúrbios desnecessários.
-[dim]5 — Quando houver necessidade de recorrer a meios de contenção, não devem estes causar ferimentos, dores ou angústia desnecessários aos animais.
-Artigo 16.º — Cuidados de saúde animal
-1 — Sem prejuízo de quaisquer medidas determinadas pela DGAV, deve existir um programa de profilaxia médica e sanitária devidamente elaborado e supervisionado pelo médico veterinário responsável e executado por profissionais competentes.
-2 — No âmbito do número anterior, os animais devem ser sujeitos a exames médico-veterinários de rotina, vacinações e desparasitações sempre que aconselhável.
-3 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
-4 — Sempre que se justifique, os animais doentes ou lesionados devem ser isolados em instalações adequadas e equipadas, se for caso disso, com cama seca e confortável.
-[dim]5 — Os medicamentos, produtos ou substâncias de prescrição médico-veterinária devem ser armazenados em locais secos e com acesso restrito.
-[dim]6 — A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior deve ser feita sob orientação do médico veterinário responsável.</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 276/2001 prevê inspeção diária (n.º 3 do art.º 13.º) e programa de profilaxia supervisionado por veterinário (n.º 1 do art.º 16.º) — alinhamento parcial com as als. (a) e (d) do n.º 1 do art.º 13.º do @regulamento. Lacunas: (1) não distingue animais vulneráveis com maior frequência de inspeção; (2) não prevê isolamento em área separada com tratamento (al. (b)); (3) não exige consulta veterinária para decisão de eutanásia com anestesia/analgesia (al. (c)); (4) nenhuma das obrigações sanitárias para criadores previstas no n.º 2 está contemplada: sem idade mínima de reprodução, sem frequência máxima de partos, sem proibição de cobrição de fêmeas a lactar, sem regime de rehoming.</t>
-        </is>
-      </c>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>O @codigo limita os cuidados médico-veterinários ao animal ferido ou doente (art.º 6.º) — sem qualquer obrigação de inspeção diária, programa de profilaxia ou isolamento. É o diploma com maior divergência face ao n.º 1 do art.º 13.º do @regulamento, omitindo igualmente todas as obrigações sanitárias específicas para criadores previstas no n.º 2.</t>
-        </is>
-      </c>
-      <c r="M11" s="10" t="inlineStr">
-        <is>
-          <t>O @rgbeac (art.º 33.º) centra os cuidados de saúde no detentor em geral (n.ºs 1 a 3), sem distinguir obrigações reforçadas para operadores de criação. Não prevê: inspeção diária sistemática por cuidadores; isolamento imediato de animais com bem-estar comprometido; nem qualquer dos requisitos sanitários para criadores do n.º 2 do art.º 13.º do @regulamento. Os n.ºs 4 e 5 (CAMV e denúncia de maus-tratos) não têm correspondência direta no @regulamento.</t>
-        </is>
-      </c>
-      <c r="N11" s="11" t="inlineStr">
-        <is>
-          <t>A @legislacao vigente (DL n.º 276/2001) tem o maior alinhamento, mas insuficiente. Necessidade de alteração dos três diplomas: (1) introduzir inspeção diária diferenciada para animais vulneráveis (al. (a) do n.º 1 do art.º 13.º do @regulamento); (2) criar obrigação de isolamento e tratamento imediato (al. (b)); (3) regular o processo de eutanásia com supervisão veterinária e anestesia/analgesia (al. (c)); (4) para criadores (n.º 2): fixar idade mínima e maturidade esquelética das fêmeas reprodutoras, frequência máxima de partos conforme Anexo I, proibição de cobrição de fêmeas a lactar, e regime de rehoming dos animais retirados da reprodução.</t>
-        </is>
-      </c>
-      <c r="O11" s="11" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P11" s="11" t="inlineStr"/>
-    </row>
-    <row r="12" ht="120" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Necessidades Comportamentais</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Art.º 14.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that measures are taken to meet the behavioural needs of dogs or cats in accordance with point 4 of Annex I.
 2. Operators shall not keep dogs or cats in areas restraining their natural movements, except in case of Article 12(3), second sub-paragraph, or for performing the following procedures or treatments:
@@ -1735,7 +1843,7 @@
 5b. Operators shall ensure that enrichment is provided and accessible to all dogs or cats, creating a stimulating environment, enabling species-specific behaviour and reducing their frustration.</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>1 — Os operadores devem assegurar que medidas são tomadas para satisfazer as necessidades comportamentais dos cães ou gatos de acordo com o ponto 4 do Anexo I.
 2 — Os operadores não devem manter cães ou gatos em áreas que restringem os seus movimentos naturais, exceto no caso do Artigo 12(3), segundo parágrafo, ou para realizar os seguintes procedimentos ou tratamentos:
@@ -1752,79 +1860,79 @@
 5b — Os operadores devem assegurar que enriquecimento é fornecido e acessível a todos os cães ou gatos, criando um ambiente estimulante, permitindo comportamento específico da espécie e reduzindo sua frustração.</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso no @rgbeac]</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso no @codigo]</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso na legislação vigente]</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t>Verificar conformidade com legislação portuguesa vigente</t>
         </is>
       </c>
-      <c r="L12" s="9" t="inlineStr">
+      <c r="L13" s="9" t="inlineStr">
         <is>
           <t>Verificar alinhamento com Código do Animal</t>
         </is>
       </c>
-      <c r="M12" s="10" t="inlineStr">
+      <c r="M13" s="10" t="inlineStr">
         <is>
           <t>Verificar alinhamento com RGBEAC</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr">
+      <c r="N13" s="11" t="inlineStr">
         <is>
           <t>Requisitos de satisfação das necessidades comportamentais de cães e gatos. Proibição de retenção em áreas restritivas. Novo artigo introduzido pelo Regulamento.</t>
         </is>
       </c>
-      <c r="O12" s="11" t="inlineStr">
+      <c r="O13" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P12" s="11" t="inlineStr">
+      <c r="P13" s="11" t="inlineStr">
         <is>
           <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="120" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Práticas Dolorosas</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Art.º 15.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that mutilations, including ear cropping, tail docking, claw removal or other partial or complete digit amputation, and resection of vocal cords or folds, are not performed unless upon medical indication, which may include prophylactic, with the sole purpose of preserving, improving the health of dogs or cats or preventing injury. In such case, the procedure shall only be performed under anaesthesia and prolonged analgesia and by a veterinarian.
 1a. The medical indication for the mutilation and the details of procedure carried out shall be documented by a veterinarian. This document shall be retained by the operator until the dog or cat, together with this document, is transferred to another establishment or owner. The operator of the establishment where the mutilation was performed shall retain a copy of the document for three years after the transfer of the dog or cat.
@@ -1841,7 +1949,7 @@
 4. Member States may grant derogations from paragraph 3 for dogs intended for use in military, police or customs services.</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>1 — Os operadores devem assegurar que mutilações, incluindo corte de orelhas, corte de cauda, remoção de garras ou outra amputação parcial ou completa de dígitos, e ressecção de cordas vocais ou pregas, não são realizadas a menos que seja por indicação médica, que pode incluir profilática, com o único propósito de preservar, melhorar a saúde de cães ou gatos ou prevenir lesões. Nesse caso, o procedimento deve ser realizado apenas sob anestesia e analgesia prolongada e por um médico veterinário.
 1a — A indicação médica para a mutilação e os detalhes do procedimento realizado devem ser documentados por um médico veterinário. Este documento deve ser retido pelo operador até o cão ou gato, juntamente com este documento, ser transferido para outro estabelecimento ou proprietário. O operador do estabelecimento onde a mutilação foi realizada deve reter uma cópia do documento por três anos após a transferência do cão ou gato.
@@ -1858,850 +1966,64 @@
 4 — Os Estados-Membros podem conceder derrogações do parágrafo 3 para cães destinados ao uso em serviços militares, policiais ou aduaneiros.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso no @rgbeac]</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso no @codigo]</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso na legislação vigente]</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>Verificar conformidade com legislação portuguesa vigente</t>
         </is>
       </c>
-      <c r="L13" s="9" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>Verificar alinhamento com Código do Animal</t>
         </is>
       </c>
-      <c r="M13" s="10" t="inlineStr">
+      <c r="M14" s="10" t="inlineStr">
         <is>
           <t>Verificar alinhamento com RGBEAC</t>
         </is>
       </c>
-      <c r="N13" s="11" t="inlineStr">
+      <c r="N14" s="11" t="inlineStr">
         <is>
           <t>Requisitos relativos a práticas dolorosas e mutilações em cães e gatos. Restrições a práticas de manipulação causando dor. Novo artigo introduzido pelo Regulamento.</t>
         </is>
       </c>
-      <c r="O13" s="11" t="inlineStr">
+      <c r="O14" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P13" s="11" t="inlineStr">
+      <c r="P14" s="11" t="inlineStr">
         <is>
           <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="120" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Espetáculos e Competições Estéticas</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 15a do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Operators of breeding and selling establishments shall not use in aesthetic shows, exhibitions and competitions of dogs and cats, dogs or cats with excessive conformational traits or dogs or cats which have been mutilated in such a way that results in an alteration of physical characteristics.
-Organisers of aesthetic shows, exhibitions and competitions of dogs and cats shall exclude from such shows, exhibitions and competitions dogs and cats which have excessive conformational traits or dogs or cats which have been mutilated in such a way that results in an alteration of physical characteristics.</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Os operadores de estabelecimentos de criação e venda não devem utilizar em espetáculos estéticos, exposições e competições de cães e gatos, cães ou gatos com características conformacionais excessivas ou cães ou gatos que tenham sido mutilados de forma que resulta numa alteração das características físicas.
-Os organizadores de espetáculos estéticos, exposições e competições de cães e gatos devem excluir de tais espetáculos, exposições e competições cães e gatos que tenham características conformacionais excessivas ou cães ou gatos que tenham sido mutilados de forma que resulta numa alteração das características físicas.</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso no @rgbeac]</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso no @codigo]</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso na legislação vigente]</t>
-        </is>
-      </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="M14" s="10" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="N14" s="11" t="inlineStr">
-        <is>
-          <t>Artigo novo do Regulamento 2023/0447 - Espetáculos e Competições Estéticas</t>
-        </is>
-      </c>
-      <c r="O14" s="11" t="inlineStr">
-        <is>
-          <t>A avaliar</t>
-        </is>
-      </c>
-      <c r="P14" s="11" t="inlineStr">
-        <is>
-          <t>Artigo novo do Regulamento 2023/0447 (tema: Espetáculos e Competições Estéticas)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="120" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Identificação e Registo</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 17.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>1. All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip compliant with Annex II.
-1a. Operators shall ensure that dogs and cats born in their establishments are individually identified within 3 months after their birth and in any event before the date of their placing on the market.
-Operators of selling establishments, shelters and those placing and being responsible for dogs and cats in foster homes shall ensure that dogs and cats that enter their establishments or come under their responsibility are individually identified within 30 days after their arrival at the establishment and in any event before the date of their placing on the market.
-Pet owners and any other natural or legal persons, other than operators, who own dogs or cats, shall ensure that the dogs or cats are individually identified at the latest when the dog or cat reaches 3 months of age or, in case the dog or cat is placed on the market, before the date of their placing on the market.
-2. The implantation of the transponder shall be performed by a veterinarian. Member States may allow the implantation of transponders in cats to be performed by a person other than a veterinarian, if it is done under the responsibility of a veterinarian.
-3. Dogs and cats which have been individually identified by means of an injectable transponder containing a microchip, in accordance with national legislation prior to entry into force of this Regulation, shall be recognised as identified in accordance with the requirements of this Article.
-4. Within two working days after their identification, the dogs and cats shall be registered by a veterinarian in a national database.
-5. For dogs and cats kept in establishments, the registration shall be made in the name of the operator of the establishment. For dogs and cats placed in foster homes, the registration shall be made in the name of the person responsible for the foster home. For dogs and cats owned by pet owners or by any other natural or legal person, the registration shall be made in the name of the pet owner or the natural or legal person.
-Member States may grant derogations from the first subparagraph to military, police and customs dogs.
-6. In case of placing on the market or occasional and irregular donation by a natural person without online advertising, the requirements for registration shall not apply.
-7. In the case of a death of a dog or a cat, the operator, pet owner or natural or legal person owning the dog or cat shall inform the national database.
-8. In case of unreadable transponder, the operator or the natural or legal person responsible for the dog or cat shall ensure that the dog or cat is re-identified with a new transponder and re-registered in the national database.</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>1. Todos os cães e gatos mantidos em estabelecimentos colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com o Anexo II.
-1a. Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de 3 meses após o nascimento e, em qualquer caso, antes da data da sua colocação no mercado.
-Os operadores de estabelecimentos de venda, abrigos e os que colocam e são responsáveis por cães e gatos em famílias de acolhimento devem assegurar que os cães e gatos que entrem nos seus estabelecimentos sejam identificados individualmente no prazo de 30 dias após a chegada.
-Os donos de animais de companhia e quaisquer outras pessoas singulares ou coletivas que detenham cães ou gatos devem assegurar que os animais sejam identificados individualmente o mais tardar quando o animal atingir os 3 meses de idade ou, no caso de o animal ser colocado no mercado, antes da data da sua colocação no mercado.
-2. A implantação do transponder devem ser efetuada por um médico veterinário. Os Estados-Membros podem permitir que a implantação de transponders em gatos seja efetuada por pessoa que não seja médico veterinário, se for feita sob a responsabilidade de um médico veterinário.
-3. Cães e gatos que tenham sido identificados individualmente por meio de um transponder injetável contendo um microchip, em conformidade com legislação nacional anterior à entrada em vigor do presente Regulamento, são reconhecidos como identificados de acordo com os requisitos do presente artigo.
-4. No prazo de dois dias úteis após a sua identificação, os cães e gatos devem ser registados por um médico veterinário numa base de dados nacional.
-5. Para cães e gatos mantidos em estabelecimentos, o registo deve ser efetuado em nome do operador do estabelecimento. Para cães e gatos colocados em famílias de acolhimento, o registo deve ser efetuado em nome da pessoa responsável pela família de acolhimento. Para cães e gatos detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva, o registo deve ser efetuado em nome do dono ou da pessoa singular ou coletiva.
-Os Estados-Membros podem conceder derrogações ao primeiro parágrafo a cães militares, policiais e aduaneiros.
-6. Em caso de colocação no mercado ou cedência ocasional e irregular por pessoa singular sem publicidade em linha, os requisitos de registo não se aplicam.
-7. Em caso de morte de um cão ou gato, o operador, dono do animal ou pessoa singular ou coletiva proprietária devem informar a base de dados nacional.
-8. Em caso de transponder ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato devem assegurar que o animal é reidentificado com um novo transponder e re-registado na base de dados nacional.</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Art.º 17.º do RGBEAC (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>1 — A identificação dos animais de companhia, pela sua marcação, quando aplicável, e registo no SIAC, deve ser realizada:
-a) Relativamente aos cães, gatos e furões nascidos em alojamentos, até aos três meses de idade ou, em qualquer caso, antes da sua colocação no mercado;
-b) Relativamente aos cães, gatos e furões que entrem em alojamentos, nos termos dos artigos 12.º a 15.º, até trinta dias após a sua chegada ao alojamento ou, em qualquer caso, antes da data de colocação no mercado;
-c) Relativamente aos cães, gatos e furões detidos por pessoas singulares, exceto nos casos previstos nas alíneas anteriores, até aos três meses de idade ou, no caso de colocação no mercado, antes da data de colocação no mercado.</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Art.º 53.º do Código do Animal (DL n.º 214/2013)</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>1 — Todos os cães devem ser identificados e registados, entre os três e os seis meses de idade.
-2 — Os gatos em exposição, para fins comerciais ou lucrativos, em estabelecimentos de venda, locais de criação, feiras ou concursos, provas funcionais, publicidade ou fins similares, devem ser identificados e registados entre os três e os seis meses de idade.
-4 — Os cães e gatos são identificados através de método electrónico e registados na base de dados nacional.
-5 — A identificação electrónica é efetuada através da aplicação subcutânea de um microchip no centro da face lateral esquerda do pescoço.</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>n.ºs 1, 2 e 3 do art.º 5.º do DL n.º 82/2019, de 27 de junho</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>1 — A identificação dos animais de companhia, pela sua marcação e registo no SIAC, deve ser realizada até 120 dias após o seu nascimento.
-2 — Na impossibilidade de determinar a data de nascimento exata, para efeitos de contagem do prazo referido no número anterior, a identificação deve ser efetuada até à perda dos dentes incisivos de leite.
-3 — Sem prejuízo dos números anteriores, e relativamente aos cães, gatos e furões que sejam cedidos e ou comercializados a partir de um criador ou de um estabelecimento autorizado para a detenção de animais de companhia, nomeadamente os centros de hospedagem com ou sem fins lucrativos e os centros de recolha oficiais, deve ser assegurada a sua marcação e registo no SIAC antes de abandonarem a instalação de nascimento ou de alojamento, independentemente da sua idade.</t>
-        </is>
-      </c>
-      <c r="K15" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 82/2019 (art.º 5.º) prevê prazo geral de 120 dias após o nascimento, sem distinguir o contexto de estabelecimento — prazo superior ao máximo de 3 meses do @regulamento, que exigirá redução. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>O @codigo fixa prazo de identificação entre 3 e 6 meses, igualmente sem distinção entre nascimentos e entrada em estabelecimentos, ficando aquém da precisão exigida pelo @regulamento.</t>
-        </is>
-      </c>
-      <c r="M15" s="10" t="inlineStr">
-        <is>
-          <t>O @rgbeac aproxima-se dos prazos do @regulamento mas aplica-se apenas a cães, gatos e furões. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
-        </is>
-      </c>
-      <c r="N15" s="11" t="inlineStr">
-        <is>
-          <t>Necessidade de alteração: (1) reduzir prazo máximo de identificação de nascimentos para 3 meses; (2) criar prazo diferenciado de 30 dias para animais admitidos em estabelecimentos; (3) harmonizar prazos entre todos os diplomas nacionais.</t>
-        </is>
-      </c>
-      <c r="O15" s="11" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P15" s="11" t="inlineStr"/>
-    </row>
-    <row r="16" ht="120" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Requisitos de Publicidade em Linha e Colocação no Mercado</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 17a do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>1. When operators advertise online a dog or a cat with a view to its placing on the Union market, they shall ensure the display of the following information:
-a) the identification number of the dog or cat as referred to in Article 17(1);
-b) the name, address and contact details of the operator.
-2. Without prejudice to Union law on animal welfare, Member States may adopt or maintain rules concerning the keeping, breeding or sale of dogs or cats, as well as rules restricting or prohibiting the online placing on the market of dogs or cats, in particular with a view to preventing trade by operators not registered in the Member State.</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>1 — Quando os operadores anunciam em linha um cão ou gato com vista à sua colocação no mercado da União, devem assegurar a apresentação das seguintes informações:
-a) o número de identificação do cão ou gato referido no Artigo 17(1);
-b) o nome, endereço e detalhes de contacto do operador.
-2 — Sem prejuízo do direito da União em matéria de bem-estar animal, os Estados-Membros podem adotar ou manter regras relativas à manutenção, criação ou venda de cães ou gatos, bem como regras que restringem ou proíbem a colocação em linha no mercado de cães ou gatos, em particular com vista à prevenção do comércio por operadores não registados no Estado-Membro.</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso no @rgbeac]</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso no @codigo]</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso na legislação vigente]</t>
-        </is>
-      </c>
-      <c r="K16" s="8" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="L16" s="9" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="M16" s="10" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="N16" s="11" t="inlineStr">
-        <is>
-          <t>Artigo novo do Regulamento 2023/0447 - Requisitos de Publicidade em Linha e Colocação no Mercado</t>
-        </is>
-      </c>
-      <c r="O16" s="11" t="inlineStr">
-        <is>
-          <t>A avaliar</t>
-        </is>
-      </c>
-      <c r="P16" s="11" t="inlineStr">
-        <is>
-          <t>Artigo novo do Regulamento 2023/0447 (tema: Requisitos de Publicidade em Linha e Colocação no Mercado)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="120" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Treino de Cuidadores de Animais</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 18 do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>For the purposes of Article 9 the competent authorities shall be responsible for:
-a) ensuring that training courses are available for animal caretakers;
-b) approving the content of the training courses;
-c) issuing certificates of competence to animal caretakers.</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Para efeitos do Artigo 9 as autoridades competentes devem ser responsáveis por:
-a) assegurar que cursos de formação estão disponíveis para os cuidadores de animais;
-b) aprovar o conteúdo dos cursos de formação;
-c) emitir certificados de competência aos cuidadores de animais.</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso no @rgbeac]</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso no @codigo]</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso na legislação vigente]</t>
-        </is>
-      </c>
-      <c r="K17" s="8" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="L17" s="9" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="M17" s="10" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="N17" s="11" t="inlineStr">
-        <is>
-          <t>Artigo novo do Regulamento 2023/0447 - Treino de Cuidadores de Animais</t>
-        </is>
-      </c>
-      <c r="O17" s="11" t="inlineStr">
-        <is>
-          <t>A avaliar</t>
-        </is>
-      </c>
-      <c r="P17" s="11" t="inlineStr">
-        <is>
-          <t>Artigo novo do Regulamento 2023/0447 (tema: Treino de Cuidadores de Animais)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="120" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Bases de Dados de Cães e Gatos</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 19 do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>1. Member States shall be responsible for establishing and maintaining databases for the registration of identified dogs and cats, in accordance with Article 17(1) and (2) and Article 21(4) and the second subparagraph of Article 21(4a).
-1a. For that purpose, the Member States may use databases maintained by another Member State, based on appropriate arrangements.</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>1 — Os Estados-Membros são responsáveis pelo estabelecimento e manutenção de bases de dados para o registo de cães e gatos identificados, em conformidade com o Artigo 17(1) e (2) e Artigo 21(4) e o segundo parágrafo do Artigo 21(4a).
-1a — Para esse efeito, os Estados-Membros podem utilizar bases de dados mantidas por outro Estado-Membro, com base em arranjos apropriados.</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso no @rgbeac]</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso no @codigo]</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso na legislação vigente]</t>
-        </is>
-      </c>
-      <c r="K18" s="8" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="L18" s="9" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="M18" s="10" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="N18" s="11" t="inlineStr">
-        <is>
-          <t>Artigo novo do Regulamento 2023/0447 - Bases de Dados de Cães e Gatos</t>
-        </is>
-      </c>
-      <c r="O18" s="11" t="inlineStr">
-        <is>
-          <t>A avaliar</t>
-        </is>
-      </c>
-      <c r="P18" s="11" t="inlineStr">
-        <is>
-          <t>Artigo novo do Regulamento 2023/0447 (tema: Bases de Dados de Cães e Gatos)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="120" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Recolha de Dados sobre Bem-Estar Animal e Relatório</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 20 do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>1. The competent authorities shall collect, analyse and publish the data set out in Annex III.
-2. The competent authorities shall draw up and transmit to the Commission every three years a report on the level of compliance and on the number and type of infringements detected.</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>1 — As autoridades competentes recolhem, analisam e publicam os dados enumerados no Anexo III.
-2 — As autoridades competentes elaboram e transmitem à Comissão a cada três anos um relatório sobre o nível de conformidade e sobre o número e tipo de infrações detetadas.</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso no @rgbeac]</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso no @codigo]</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso na legislação vigente]</t>
-        </is>
-      </c>
-      <c r="K19" s="8" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="L19" s="9" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="M19" s="10" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="N19" s="11" t="inlineStr">
-        <is>
-          <t>Artigo novo do Regulamento 2023/0447 - Recolha de Dados sobre Bem-Estar Animal e Relatório</t>
-        </is>
-      </c>
-      <c r="O19" s="11" t="inlineStr">
-        <is>
-          <t>A avaliar</t>
-        </is>
-      </c>
-      <c r="P19" s="11" t="inlineStr">
-        <is>
-          <t>Artigo novo do Regulamento 2023/0447 (tema: Recolha de Dados sobre Bem-Estar Animal e Relatório)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="120" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Proteção de Dados</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 20a do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>The competent authorities of the Member States shall be controllers within the meaning of Regulation (EU) 2016/679 in relation to the processing of personal data collected under Article 7, Article 7a of this Regulation as well as under Article 19(1) of this Regulation when used for the purposes of official control.</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>As autoridades competentes dos Estados-Membros devem ser controladores no sentido do Regulamento (UE) 2016/679 em relação ao tratamento de dados pessoais recolhidos nos termos do Artigo 7, Artigo 7a do presente Regulamento bem como no âmbito do Artigo 19(1) do presente Regulamento quando utilizados para efeitos de controlo oficial.</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso no @rgbeac]</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso no @codigo]</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso na legislação vigente]</t>
-        </is>
-      </c>
-      <c r="K20" s="8" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="L20" s="9" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="M20" s="10" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="N20" s="11" t="inlineStr">
-        <is>
-          <t>Artigo novo do Regulamento 2023/0447 - Proteção de Dados</t>
-        </is>
-      </c>
-      <c r="O20" s="11" t="inlineStr">
-        <is>
-          <t>A avaliar</t>
-        </is>
-      </c>
-      <c r="P20" s="11" t="inlineStr">
-        <is>
-          <t>Artigo novo do Regulamento 2023/0447 (tema: Proteção de Dados)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="120" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Entrada de Cães e Gatos na União</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 21 do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Member States shall require that dogs and cats intended to be placed on their market shall:
-a) be identified and registered as referred to in Article 17;
-b) be accompanied by a health certificate issued by a veterinarian of the exporting country;</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Os Estados-Membros devem exigir que cães e gatos com vista à sua colocação no mercado devem:
-a) ser identificados e registados conforme referido no Artigo 17;
-b) ser acompanhados por um certificado de saúde emitido por um médico veterinário do país exportador;</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso no @rgbeac]</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso no @codigo]</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso na legislação vigente]</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="L21" s="9" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="M21" s="10" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="N21" s="11" t="inlineStr">
-        <is>
-          <t>Artigo novo do Regulamento 2023/0447 - Entrada de Cães e Gatos na União</t>
-        </is>
-      </c>
-      <c r="O21" s="11" t="inlineStr">
-        <is>
-          <t>A avaliar</t>
-        </is>
-      </c>
-      <c r="P21" s="11" t="inlineStr">
-        <is>
-          <t>Artigo novo do Regulamento 2023/0447 (tema: Entrada de Cães e Gatos na União)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="120" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Alteração dos Anexos</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 22 do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>The Commission is empowered to adopt delegated acts in accordance with Article 23 amending the Annexes to this Regulation to take into account of scientific and technical progress, including, when relevant, scientific opinions of the European Food Safety Authority.</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>A Comissão é habilitada a adotar atos delegados em conformidade com o Artigo 23 alterando os Anexos ao presente Regulamento para tomar em conta o progresso científico e técnico, incluindo, quando relevante, as opiniões científicas da Autoridade Europeia para a Segurança dos Alimentos.</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso no @rgbeac]</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso no @codigo]</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>A ser preenchido</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>[Pesquisa em progresso na legislação vigente]</t>
-        </is>
-      </c>
-      <c r="K22" s="8" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="L22" s="9" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="M22" s="10" t="inlineStr">
-        <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="N22" s="11" t="inlineStr">
-        <is>
-          <t>Artigo novo do Regulamento 2023/0447 - Alteração dos Anexos</t>
-        </is>
-      </c>
-      <c r="O22" s="11" t="inlineStr">
-        <is>
-          <t>A avaliar</t>
-        </is>
-      </c>
-      <c r="P22" s="11" t="inlineStr">
-        <is>
-          <t>Artigo novo do Regulamento 2023/0447 (tema: Alteração dos Anexos)</t>
         </is>
       </c>
     </row>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -664,107 +664,97 @@
     <row r="2" ht="120" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Identificação e Registo</t>
+          <t>Princípios Gerais de Bem-Estar</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Art.º 17.º do Regulamento 2023/0447</t>
+          <t>Art.º 5.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>1. All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip compliant with Annex II.
-1a. Operators shall ensure that dogs and cats born in their establishments are individually identified within 3 months after their birth and in any event before the date of their placing on the market.
-Operators of selling establishments, shelters and those placing and being responsible for dogs and cats in foster homes shall ensure that dogs and cats that enter their establishments or come under their responsibility are individually identified within 30 days after their arrival at the establishment and in any event before the date of their placing on the market.
-Pet owners and any other natural or legal persons, other than operators, who own dogs or cats, shall ensure that the dogs or cats are individually identified at the latest when the dog or cat reaches 3 months of age or, in case the dog or cat is placed on the market, before the date of their placing on the market.
-2. The implantation of the transponder shall be performed by a veterinarian. Member States may allow the implantation of transponders in cats to be performed by a person other than a veterinarian, if it is done under the responsibility of a veterinarian.
-3. Dogs and cats which have been individually identified by means of an injectable transponder containing a microchip, in accordance with national legislation prior to entry into force of this Regulation, shall be recognised as identified in accordance with the requirements of this Article.
-4. Within two working days after their identification, the dogs and cats shall be registered by a veterinarian in a national database.
-5. For dogs and cats kept in establishments, the registration shall be made in the name of the operator of the establishment. For dogs and cats placed in foster homes, the registration shall be made in the name of the person responsible for the foster home. For dogs and cats owned by pet owners or by any other natural or legal person, the registration shall be made in the name of the pet owner or the natural or legal person.
-Member States may grant derogations from the first subparagraph to military, police and customs dogs.
-6. In case of placing on the market or occasional and irregular donation by a natural person without online advertising, the requirements for registration shall not apply.
-7. In the case of a death of a dog or a cat, the operator, pet owner or natural or legal person owning the dog or cat shall inform the national database.
-8. In case of unreadable transponder, the operator or the natural or legal person responsible for the dog or cat shall ensure that the dog or cat is re-identified with a new transponder and re-registered in the national database.</t>
+          <t>Operators shall apply the following general welfare principles with respect to dogs or cats bred or kept in their establishment:
+(a) dogs and cats are provided with water and feed of a quality and of a quantity that enables them to have appropriate nutrition and hydration;
+(b) dogs and cats are kept in an appropriate and regularly cleaned physical environment which is secure and comfortable, especially in terms of space, air quality, temperature, light, protection against adverse climatic conditions and ease of movement, preventing overcrowding;
+(c) dogs and cats are kept safe, clean and in good health by preventing diseases, injuries, and pain, due in particular to management, handling practices and breeding practices;
+(d) dogs and cats are kept in an environment that enables them to exhibit species-specific and social non-harmful behaviour, and to establish a positive relationship with human beings;
+(e) dogs and cats are kept in such a way as to optimise their mental state by preventing or reducing negative stimuli in duration and intensity, as well as by maximising opportunities for positive stimuli in duration and intensity, preventing the development of abnormal repetitive and other behaviours indicative of negative animal welfare, and taking into consideration the individual dog's or cat's needs in the different domains referred to in points (a) to (d).</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>1. Todos os cães e gatos mantidos em estabelecimentos colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com o Anexo II.
-1a. Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de 3 meses após o nascimento e, em qualquer caso, antes da data da sua colocação no mercado.
-Os operadores de estabelecimentos de venda, abrigos e os que colocam e são responsáveis por cães e gatos em famílias de acolhimento devem assegurar que os cães e gatos que entrem nos seus estabelecimentos sejam identificados individualmente no prazo de 30 dias após a chegada.
-Os donos de animais de companhia e quaisquer outras pessoas singulares ou coletivas que detenham cães ou gatos devem assegurar que os animais sejam identificados individualmente o mais tardar quando o animal atingir os 3 meses de idade ou, no caso de o animal ser colocado no mercado, antes da data da sua colocação no mercado.
-2. A implantação do transponder devem ser efetuada por um médico veterinário. Os Estados-Membros podem permitir que a implantação de transponders em gatos seja efetuada por pessoa que não seja médico veterinário, se for feita sob a responsabilidade de um médico veterinário.
-3. Cães e gatos que tenham sido identificados individualmente por meio de um transponder injetável contendo um microchip, em conformidade com legislação nacional anterior à entrada em vigor do presente Regulamento, são reconhecidos como identificados de acordo com os requisitos do presente artigo.
-4. No prazo de dois dias úteis após a sua identificação, os cães e gatos devem ser registados por um médico veterinário numa base de dados nacional.
-5. Para cães e gatos mantidos em estabelecimentos, o registo deve ser efetuado em nome do operador do estabelecimento. Para cães e gatos colocados em famílias de acolhimento, o registo deve ser efetuado em nome da pessoa responsável pela família de acolhimento. Para cães e gatos detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva, o registo deve ser efetuado em nome do dono ou da pessoa singular ou coletiva.
-Os Estados-Membros podem conceder derrogações ao primeiro parágrafo a cães militares, policiais e aduaneiros.
-6. Em caso de colocação no mercado ou cedência ocasional e irregular por pessoa singular sem publicidade em linha, os requisitos de registo não se aplicam.
-7. Em caso de morte de um cão ou gato, o operador, dono do animal ou pessoa singular ou coletiva proprietária devem informar a base de dados nacional.
-8. Em caso de transponder ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato devem assegurar que o animal é reidentificado com um novo transponder e re-registado na base de dados nacional.</t>
+          <t>Os operadores devem aplicar os seguintes princípios gerais de bem-estar aos cães e gatos criados ou detidos nos seus estabelecimentos:
+(a) os cães e gatos são alimentados e abebeirados com água e ração de qualidade e quantidade adequadas a uma nutrição e hidratação apropriadas;
+(b) os cães e gatos são mantidos num ambiente físico adequado, regularmente limpo, seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, iluminação, proteção face a condições climáticas adversas e facilidade de movimentação, prevenindo a sobrelotação;
+(c) os cães e gatos são mantidos seguros, limpos e com boa saúde, prevenindo doenças, lesões e dor, nomeadamente através de práticas de maneio, manuseamento e reprodução adequadas;
+(d) os cães e gatos são mantidos num ambiente que lhes permite exibir comportamentos específicos da espécie e comportamentos sociais não nocivos, e estabelecer uma relação positiva com os seres humanos;
+(e) os cães e gatos são mantidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo estímulos negativos em duração e intensidade, maximizando oportunidades de estímulos positivos, prevenindo o desenvolvimento de comportamentos repetitivos anormais, tendo em conta as necessidades individuais do animal nos domínios referidos nas alíneas (a) a (d).</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Art.º 17.º do RGBEAC (proposta, jun. 2025)</t>
+          <t>al. a) do n.º 1 do art.º 10.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>1 — A identificação dos animais de companhia, pela sua marcação, quando aplicável, e registo no SIAC, deve ser realizada:
-a) Relativamente aos cães, gatos e furões nascidos em alojamentos, até aos três meses de idade ou, em qualquer caso, antes da sua colocação no mercado;
-b) Relativamente aos cães, gatos e furões que entrem em alojamentos, nos termos dos artigos 12.º a 15.º, até trinta dias após a sua chegada ao alojamento ou, em qualquer caso, antes da data de colocação no mercado;
-c) Relativamente aos cães, gatos e furões detidos por pessoas singulares, exceto nos casos previstos nas alíneas anteriores, até aos três meses de idade ou, no caso de colocação no mercado, antes da data de colocação no mercado.</t>
+          <t>1 — O detentor do animal de companhia deve:
+a) Assegurar o bem-estar do animal, de acordo com sua espécie, raça, idade e necessidades físicas e etológicas, proporcionando-lhe:
+— Atenção, supervisão, controlo, exercício físico e estímulo mental;
+— Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável;
+— Condições higiossanitárias que atendam, no mínimo, ao estabelecido no presente decreto-lei e na demais legislação aplicável;
+— Liberdade de movimento, sendo proibidos todos os sistemas de contenção permanentes;
+— Abrigo adequado, em termos de tamanho e qualidade, com vista a proteger de condições atmosféricas adversas, incluindo frio, chuva, sol ou calor excessivos, com cama seca, limpa e confortável;
+— Contato social adequado a cada espécie, de acordo com a sua idade e atividade.</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>Art.º 53.º do Código do Animal (DL n.º 214/2013)</t>
+          <t>n.ºs 1, 2 e 3 do art.º 5.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>1 — Todos os cães devem ser identificados e registados, entre os três e os seis meses de idade.
-2 — Os gatos em exposição, para fins comerciais ou lucrativos, em estabelecimentos de venda, locais de criação, feiras ou concursos, provas funcionais, publicidade ou fins similares, devem ser identificados e registados entre os três e os seis meses de idade.
-4 — Os cães e gatos são identificados através de método electrónico e registados na base de dados nacional.
-5 — A identificação electrónica é efetuada através da aplicação subcutânea de um microchip no centro da face lateral esquerda do pescoço.</t>
+          <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal.
+2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
+3 — É proibida a violência contra animais, considerando-se como tal todos os atos que, sem necessidade, infligem a morte, o sofrimento, abuso ou lesões a um animal.</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>n.ºs 1, 2 e 3 do art.º 5.º do DL n.º 82/2019, de 27 de junho</t>
+          <t>n.º 1 do art.º 7.º e n.º 1 do art.º 9.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>1 — A identificação dos animais de companhia, pela sua marcação e registo no SIAC, deve ser realizada até 120 dias após o seu nascimento.
-2 — Na impossibilidade de determinar a data de nascimento exata, para efeitos de contagem do prazo referido no número anterior, a identificação deve ser efetuada até à perda dos dentes incisivos de leite.
-3 — Sem prejuízo dos números anteriores, e relativamente aos cães, gatos e furões que sejam cedidos e ou comercializados a partir de um criador ou de um estabelecimento autorizado para a detenção de animais de companhia, nomeadamente os centros de hospedagem com ou sem fins lucrativos e os centros de recolha oficiais, deve ser assegurada a sua marcação e registo no SIAC antes de abandonarem a instalação de nascimento ou de alojamento, independentemente da sua idade.</t>
+          <t>Artigo 7.º, n.º 1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
+Artigo 9.º, n.º 1 — A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam.</t>
         </is>
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>O DL n.º 82/2019 (art.º 5.º) prevê prazo geral de 120 dias após o nascimento, sem distinguir o contexto de estabelecimento — prazo superior ao máximo de 3 meses do @regulamento, que exigirá redução. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
+          <t>O DL n.º 276/2001 (art.ºs 7.º e 9.º) consagra os mesmos parâmetros mas desenvolve-os em artigos separados (alojamento, alimentação, ambiente) sem os denominar como domínios nem os sistematizar de forma unificada segundo o referencial OMSA.</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>O @codigo fixa prazo de identificação entre 3 e 6 meses, igualmente sem distinção entre nascimentos e entrada em estabelecimentos, ficando aquém da precisão exigida pelo @regulamento.</t>
+          <t>O @codigo (art.º 5.º) refere 'parâmetros de bem-estar animal' genericamente, sem adotar formalmente a nomenclatura dos 5 domínios OMSA nem a sua sistematização explícita.</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac aproxima-se dos prazos do @regulamento mas aplica-se apenas a cães, gatos e furões. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
+          <t>O @rgbeac (art.º 10.º, n.º 1, al. a)) articula obrigações equivalentes ao nível do detentor de forma descritiva, sem sistematização nos 5 domínios nem referência ao quadro OMSA.</t>
         </is>
       </c>
       <c r="N2" s="11" t="inlineStr">
         <is>
-          <t>Necessidade de alteração: (1) reduzir prazo máximo de identificação de nascimentos para 3 meses; (2) criar prazo diferenciado de 30 dias para animais admitidos em estabelecimentos; (3) harmonizar prazos entre todos os diplomas nacionais.</t>
+          <t>Alinhamento substancial de conteúdo; sem necessidade de alteração imediata. Recomenda-se a adoção formal dos 5 domínios OMSA como referencial estruturante em futura revisão legislativa ou em normas de orientação técnica da DGAV.</t>
         </is>
       </c>
       <c r="O2" s="11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="P2" s="11" t="inlineStr"/>
@@ -873,15 +863,114 @@
     <row r="4" ht="120" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>Estratégias de Criação — Conformação e Consanguinidade</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 6.º-A do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>1. Operators of breeding establishments shall ensure that their breeding strategies minimise the risk of producing dogs or cats with genotypes associated with detrimental effects on their health and welfare.
+2. Operators of breeding establishments shall not use for reproduction dogs or cats that have excessive conformational traits leading to a high risk of detrimental effects on the welfare of these dogs or cats, or of their offspring. Before selection for breeding of a dog or cat that may be concerned by an excessive conformational trait the operator shall consult a veterinarian or an independent qualified person under the responsibility of a veterinarian. The veterinarian or independent qualified person shall assess whether the dog or cat has an excessive conformational trait.
+3. The Commission is empowered to adopt, taking into account scientific opinions of the European Food Safety Authority as well as the social and economic impacts, delegated acts in accordance with Article 23 supplementing this Regulation by:
+(a) defining characteristics of the genotypes referred to in paragraph 1, which shall be excluded from reproduction, and the methods for their assessment and the record keeping requirements;
+(b) defining excessive conformational traits referred to in paragraph 2 of this Article, which shall be excluded from reproduction, the methods for their assessment and the record keeping requirements.
+4. The delegated acts concerning the excessive conformational traits shall be adopted by 1 July 2030. The delegated acts concerning the genotypes shall be adopted by 1 July 2036.
+5. The following shall be prohibited in the management of the reproduction of dogs and cats:
+(a) the breeding between parents and offspring, between siblings, between half-siblings or between grandparents and grandchildren, unless approved by the competent authority based on a specific need to preserve local breeds with a limited genetic pool;
+(b) the breeding to produce hybrids.</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>1. Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
+2. Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem traços conformacionais excessivos que conduzam a um risco elevado de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por traço conformacional excessivo, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem um traço conformacional excessivo.
+3. A Comissão tem competência para adotar, tendo em conta os pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, bem como os impactos sociais e económicos, atos delegados em conformidade com o artigo 23.º que complementem este Regulamento:
+(a) definindo características dos genótipos a que se refere o parágrafo 1, que devem ser excluídos da reprodução, e os métodos para a sua avaliação e requisitos de manutenção de registos;
+(b) definindo traços conformacionais excessivos a que se refere o parágrafo 2 do presente artigo, que devem ser excluídos da reprodução, os métodos para a sua avaliação e requisitos de manutenção de registos.
+4. Os atos delegados relativos aos traços conformacionais excessivos devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
+5. São proibidos na gestão da reprodução de cães e gatos:
+(a) o cruzamento entre progenitores e descendentes, entre irmãos, entre meios-irmãos ou entre avós e netos, exceto com aprovação da autoridade competente por razão de necessidade específica de preservação de raças locais com reserva genética limitada;
+(b) o cruzamento para produção de híbridos.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>n.ºs 1 e 2 do art.º 34.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1 — As intervenções cirúrgicas com o objetivo da modificação da aparência ou com fins não curativos ou não destinados a impedir a reprodução dos animais são proibidas, nos termos do disposto na alínea i) do n.º 1 do artigo 12.º.
+2 — O detentor de animal sujeito a intervenção curativa que modifique a sua aparência deve possuir documento comprovativo da necessidade da mesma, passado pelo médico veterinário que a ela procedeu, sob a forma de atestado do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura, ou, no caso de animais importados, documento comprovativo da necessidade dessa intervenção, emitida pelo médico veterinário que a ela procedeu, legalizado pela autoridade competente do respetivo país.</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>n.º 2, als. a), b) e c) do art.º 8.º do Código do Animal (DL n.º 214/2013)</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>2 — A reprodução de animais obedece ao seguinte:
+a) Os animais só devem ser utilizados na reprodução depois de atingida a maturidade reprodutiva para a espécie e raça devendo, no caso dos cães e gatos, seguir os parâmetros referidos no anexo I ao presente diploma, do qual faz parte integrante, não sendo autorizado, no caso das fêmeas, o acasalamento em cios sucessivos;
+b) Deve ser respeitada a regra do porte semelhante dos progenitores, para prevenir a possibilidade de distócia;
+c) Devem ser excluídos da reprodução, os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia da anca nos cães e rim poliquístico nos gatos, ou alterações comportamentais.</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>art.º 17.º e n.º 1 do art.º 18.º do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 17.º — As intervenções cirúrgicas, nomeadamente as destinadas ao corte de caudas nos canídeos, têm de ser executadas por um médico veterinário.
+Artigo 18.º, n.º 1 — Os detentores de animais de companhia que os apresentem com quaisquer amputações que modifiquem a aparência dos animais ou com fins não curativos devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa amputação, nomeadamente discriminando que as mesmas foram feitas por razões médico-veterinárias ou no interesse particular do animal ou para impedir a reprodução.</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 (art.ºs 17.º e 18.º) exige intervenção veterinária em cirurgias e documentação para amputações, mas não prevê qualquer restrição à reprodução por traços conformacionais excessivos nem proibição de consanguinidade próxima ou hibridação.</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>O @codigo (art.º 8.º, n.º 2) exclui da reprodução animais com defeitos genéticos e malformações (displasia, rim poliquístico) e proíbe cios sucessivos, mas não prevê o conceito de traços conformacionais excessivos nem a proibição de consanguinidade.</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac (art.º 34.º) proíbe intervenções cirúrgicas de modificação da aparência, mas não contém qualquer norma sobre estratégia genética de criação, conformação excessiva ou consanguinidade.</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="inlineStr">
+        <is>
+          <t>Lacuna normativa transversal. Necessidade de criar norma específica que: (1) defina traços conformacionais excessivos (a regular por ato delegado europeu até 2030); (2) proíba consanguinidade próxima (pais/filhos, irmãos, avós/netos); (3) proíba a produção de híbridos; (4) imponha consulta veterinária prévia ao acasalamento de animais potencialmente afetados.</t>
+        </is>
+      </c>
+      <c r="O4" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P4" s="11" t="inlineStr"/>
+    </row>
+    <row r="5" ht="120" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>Reprodução e Criação</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Art.º 7.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Operators shall notify the competent authorities of their activity, providing at least the following information:
 (a) name, address and contact details of the operator;
@@ -892,7 +981,7 @@
 (ea) for breeding establishments, the estimated number of litters to be placed on the market per year.</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem notificar as autoridades competentes da sua atividade, fornecendo pelo menos as seguintes informações:
 (a) nome, morada e contactos do operador;
@@ -903,24 +992,24 @@
 (ea) para os estabelecimentos de criação, o número estimado de ninhadas a colocar no mercado por ano.</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Art.º 43.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1 — Os centros de bem-estar animal procedem à esterilização dos animais recolhidos que se presuma terem sido abandonados, nos termos do artigo 41.º.
 2 — As câmaras municipais devem, sempre que necessário e sob a responsabilidade do médico veterinário municipal, incentivar e promover programas de esterilização de animais de companhia, nomeadamente os cães e gatos, em complementaridade com os centros de bem-estar animal.
 3 — Os requisitos mínimos das instalações adequadas à realização de esterilizações nos centros de bem-estar animal são estabelecidos em portaria do membro do Governo responsável pela área da agricultura.</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Art.º 8.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>1 — A reprodução de animais deve ser realizada de forma planeada.
 2 — A reprodução de animais obedece ao seguinte:
@@ -929,12 +1018,12 @@
 c) Devem ser excluídos da reprodução os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia.</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>n.º 1 do art.º 3.º-A do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>1 — A mera comunicação prévia a que se refere a alínea a) do n.º 1 do artigo anterior é dirigida à DGAV e deve conter os seguintes elementos, quando aplicáveis:
 a) O nome ou a denominação social do interessado;
@@ -949,127 +1038,29 @@
 j) Declaração de responsabilidade, subscrita pelo interessado, relativa ao cumprimento da legislação aplicável aos animais de companhia, nomeadamente em matéria de instalações, equipamentos, higiene, saúde e bem-estar dos animais.</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 3.º-A) prevê comunicação prévia à DGAV com elementos parcialmente equivalentes (capacidade máxima, espécies, raças). Não exige a estimativa anual de ninhadas a colocar no mercado (al. ea) do @regulamento), constituindo lacuna parcial. É o diploma mais próximo do @regulamento neste eixo.</t>
         </is>
       </c>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>O @codigo regula condições de reprodução (art.º 8.º) mas não prevê qualquer sistema de notificação ou registo de estabelecimentos criadores junto da autoridade competente.</t>
         </is>
       </c>
-      <c r="M4" s="10" t="inlineStr">
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac trata da esterilização de errantes e CED, mas não contém norma sobre notificação de criadores ou registo de estabelecimentos com fins de reprodução comercial.</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="N5" s="11" t="inlineStr">
         <is>
           <t>A @legislacao vigente é o diploma base adequado para a transposição. Necessidade de ajuste: acrescentar a obrigação de estimativa anual de ninhadas a colocar no mercado e alinhar os restantes elementos informativos com a lista exaustiva do art.º 7.º do @regulamento.</t>
         </is>
       </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="O5" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
-        </is>
-      </c>
-      <c r="P4" s="11" t="inlineStr"/>
-    </row>
-    <row r="5" ht="120" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Princípios Gerais de Bem-Estar</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 5.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Operators shall apply the following general welfare principles with respect to dogs or cats bred or kept in their establishment:
-(a) dogs and cats are provided with water and feed of a quality and of a quantity that enables them to have appropriate nutrition and hydration;
-(b) dogs and cats are kept in an appropriate and regularly cleaned physical environment which is secure and comfortable, especially in terms of space, air quality, temperature, light, protection against adverse climatic conditions and ease of movement, preventing overcrowding;
-(c) dogs and cats are kept safe, clean and in good health by preventing diseases, injuries, and pain, due in particular to management, handling practices and breeding practices;
-(d) dogs and cats are kept in an environment that enables them to exhibit species-specific and social non-harmful behaviour, and to establish a positive relationship with human beings;
-(e) dogs and cats are kept in such a way as to optimise their mental state by preventing or reducing negative stimuli in duration and intensity, as well as by maximising opportunities for positive stimuli in duration and intensity, preventing the development of abnormal repetitive and other behaviours indicative of negative animal welfare, and taking into consideration the individual dog's or cat's needs in the different domains referred to in points (a) to (d).</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Os operadores devem aplicar os seguintes princípios gerais de bem-estar aos cães e gatos criados ou detidos nos seus estabelecimentos:
-(a) os cães e gatos são alimentados e abebeirados com água e ração de qualidade e quantidade adequadas a uma nutrição e hidratação apropriadas;
-(b) os cães e gatos são mantidos num ambiente físico adequado, regularmente limpo, seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, iluminação, proteção face a condições climáticas adversas e facilidade de movimentação, prevenindo a sobrelotação;
-(c) os cães e gatos são mantidos seguros, limpos e com boa saúde, prevenindo doenças, lesões e dor, nomeadamente através de práticas de maneio, manuseamento e reprodução adequadas;
-(d) os cães e gatos são mantidos num ambiente que lhes permite exibir comportamentos específicos da espécie e comportamentos sociais não nocivos, e estabelecer uma relação positiva com os seres humanos;
-(e) os cães e gatos são mantidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo estímulos negativos em duração e intensidade, maximizando oportunidades de estímulos positivos, prevenindo o desenvolvimento de comportamentos repetitivos anormais, tendo em conta as necessidades individuais do animal nos domínios referidos nas alíneas (a) a (d).</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>al. a) do n.º 1 do art.º 10.º do RGBEAC (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>1 — O detentor do animal de companhia deve:
-a) Assegurar o bem-estar do animal, de acordo com sua espécie, raça, idade e necessidades físicas e etológicas, proporcionando-lhe:
-— Atenção, supervisão, controlo, exercício físico e estímulo mental;
-— Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável;
-— Condições higiossanitárias que atendam, no mínimo, ao estabelecido no presente decreto-lei e na demais legislação aplicável;
-— Liberdade de movimento, sendo proibidos todos os sistemas de contenção permanentes;
-— Abrigo adequado, em termos de tamanho e qualidade, com vista a proteger de condições atmosféricas adversas, incluindo frio, chuva, sol ou calor excessivos, com cama seca, limpa e confortável;
-— Contato social adequado a cada espécie, de acordo com a sua idade e atividade.</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>n.ºs 1, 2 e 3 do art.º 5.º do Código do Animal (DL n.º 214/2013)</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal.
-2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
-3 — É proibida a violência contra animais, considerando-se como tal todos os atos que, sem necessidade, infligem a morte, o sofrimento, abuso ou lesões a um animal.</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>n.º 1 do art.º 7.º e n.º 1 do art.º 9.º do DL n.º 276/2001, de 17 de outubro</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Artigo 7.º, n.º 1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
-Artigo 9.º, n.º 1 — A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam.</t>
-        </is>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 276/2001 (art.ºs 7.º e 9.º) consagra os mesmos parâmetros mas desenvolve-os em artigos separados (alojamento, alimentação, ambiente) sem os denominar como domínios nem os sistematizar de forma unificada segundo o referencial OMSA.</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>O @codigo (art.º 5.º) refere 'parâmetros de bem-estar animal' genericamente, sem adotar formalmente a nomenclatura dos 5 domínios OMSA nem a sua sistematização explícita.</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>O @rgbeac (art.º 10.º, n.º 1, al. a)) articula obrigações equivalentes ao nível do detentor de forma descritiva, sem sistematização nos 5 domínios nem referência ao quadro OMSA.</t>
-        </is>
-      </c>
-      <c r="N5" s="11" t="inlineStr">
-        <is>
-          <t>Alinhamento substancial de conteúdo; sem necessidade de alteração imediata. Recomenda-se a adoção formal dos 5 domínios OMSA como referencial estruturante em futura revisão legislativa ou em normas de orientação técnica da DGAV.</t>
-        </is>
-      </c>
-      <c r="O5" s="11" t="inlineStr">
-        <is>
-          <t>Não</t>
         </is>
       </c>
       <c r="P5" s="11" t="inlineStr"/>
@@ -1077,240 +1068,15 @@
     <row r="6" ht="120" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Estratégias de Criação — Conformação e Consanguinidade</t>
+          <t>Detenção Responsável e Informação</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Art.º 6.º-A do Regulamento 2023/0447</t>
+          <t>Art.º 8.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>1. Operators of breeding establishments shall ensure that their breeding strategies minimise the risk of producing dogs or cats with genotypes associated with detrimental effects on their health and welfare.
-2. Operators of breeding establishments shall not use for reproduction dogs or cats that have excessive conformational traits leading to a high risk of detrimental effects on the welfare of these dogs or cats, or of their offspring. Before selection for breeding of a dog or cat that may be concerned by an excessive conformational trait the operator shall consult a veterinarian or an independent qualified person under the responsibility of a veterinarian. The veterinarian or independent qualified person shall assess whether the dog or cat has an excessive conformational trait.
-3. The Commission is empowered to adopt, taking into account scientific opinions of the European Food Safety Authority as well as the social and economic impacts, delegated acts in accordance with Article 23 supplementing this Regulation by:
-(a) defining characteristics of the genotypes referred to in paragraph 1, which shall be excluded from reproduction, and the methods for their assessment and the record keeping requirements;
-(b) defining excessive conformational traits referred to in paragraph 2 of this Article, which shall be excluded from reproduction, the methods for their assessment and the record keeping requirements.
-4. The delegated acts concerning the excessive conformational traits shall be adopted by 1 July 2030. The delegated acts concerning the genotypes shall be adopted by 1 July 2036.
-5. The following shall be prohibited in the management of the reproduction of dogs and cats:
-(a) the breeding between parents and offspring, between siblings, between half-siblings or between grandparents and grandchildren, unless approved by the competent authority based on a specific need to preserve local breeds with a limited genetic pool;
-(b) the breeding to produce hybrids.</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>1. Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
-2. Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem traços conformacionais excessivos que conduzam a um risco elevado de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por traço conformacional excessivo, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem um traço conformacional excessivo.
-3. A Comissão tem competência para adotar, tendo em conta os pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, bem como os impactos sociais e económicos, atos delegados em conformidade com o artigo 23.º que complementem este Regulamento:
-(a) definindo características dos genótipos a que se refere o parágrafo 1, que devem ser excluídos da reprodução, e os métodos para a sua avaliação e requisitos de manutenção de registos;
-(b) definindo traços conformacionais excessivos a que se refere o parágrafo 2 do presente artigo, que devem ser excluídos da reprodução, os métodos para a sua avaliação e requisitos de manutenção de registos.
-4. Os atos delegados relativos aos traços conformacionais excessivos devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
-5. São proibidos na gestão da reprodução de cães e gatos:
-(a) o cruzamento entre progenitores e descendentes, entre irmãos, entre meios-irmãos ou entre avós e netos, exceto com aprovação da autoridade competente por razão de necessidade específica de preservação de raças locais com reserva genética limitada;
-(b) o cruzamento para produção de híbridos.</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>n.ºs 1 e 2 do art.º 34.º do RGBEAC (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>1 — As intervenções cirúrgicas com o objetivo da modificação da aparência ou com fins não curativos ou não destinados a impedir a reprodução dos animais são proibidas, nos termos do disposto na alínea i) do n.º 1 do artigo 12.º.
-2 — O detentor de animal sujeito a intervenção curativa que modifique a sua aparência deve possuir documento comprovativo da necessidade da mesma, passado pelo médico veterinário que a ela procedeu, sob a forma de atestado do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura, ou, no caso de animais importados, documento comprovativo da necessidade dessa intervenção, emitida pelo médico veterinário que a ela procedeu, legalizado pela autoridade competente do respetivo país.</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>n.º 2, als. a), b) e c) do art.º 8.º do Código do Animal (DL n.º 214/2013)</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>2 — A reprodução de animais obedece ao seguinte:
-a) Os animais só devem ser utilizados na reprodução depois de atingida a maturidade reprodutiva para a espécie e raça devendo, no caso dos cães e gatos, seguir os parâmetros referidos no anexo I ao presente diploma, do qual faz parte integrante, não sendo autorizado, no caso das fêmeas, o acasalamento em cios sucessivos;
-b) Deve ser respeitada a regra do porte semelhante dos progenitores, para prevenir a possibilidade de distócia;
-c) Devem ser excluídos da reprodução, os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia da anca nos cães e rim poliquístico nos gatos, ou alterações comportamentais.</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>art.º 17.º e n.º 1 do art.º 18.º do DL n.º 276/2001, de 17 de outubro</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>Artigo 17.º — As intervenções cirúrgicas, nomeadamente as destinadas ao corte de caudas nos canídeos, têm de ser executadas por um médico veterinário.
-Artigo 18.º, n.º 1 — Os detentores de animais de companhia que os apresentem com quaisquer amputações que modifiquem a aparência dos animais ou com fins não curativos devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa amputação, nomeadamente discriminando que as mesmas foram feitas por razões médico-veterinárias ou no interesse particular do animal ou para impedir a reprodução.</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 276/2001 (art.ºs 17.º e 18.º) exige intervenção veterinária em cirurgias e documentação para amputações, mas não prevê qualquer restrição à reprodução por traços conformacionais excessivos nem proibição de consanguinidade próxima ou hibridação.</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>O @codigo (art.º 8.º, n.º 2) exclui da reprodução animais com defeitos genéticos e malformações (displasia, rim poliquístico) e proíbe cios sucessivos, mas não prevê o conceito de traços conformacionais excessivos nem a proibição de consanguinidade.</t>
-        </is>
-      </c>
-      <c r="M6" s="10" t="inlineStr">
-        <is>
-          <t>O @rgbeac (art.º 34.º) proíbe intervenções cirúrgicas de modificação da aparência, mas não contém qualquer norma sobre estratégia genética de criação, conformação excessiva ou consanguinidade.</t>
-        </is>
-      </c>
-      <c r="N6" s="11" t="inlineStr">
-        <is>
-          <t>Lacuna normativa transversal. Necessidade de criar norma específica que: (1) defina traços conformacionais excessivos (a regular por ato delegado europeu até 2030); (2) proíba consanguinidade próxima (pais/filhos, irmãos, avós/netos); (3) proíba a produção de híbridos; (4) imponha consulta veterinária prévia ao acasalamento de animais potencialmente afetados.</t>
-        </is>
-      </c>
-      <c r="O6" s="11" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P6" s="11" t="inlineStr"/>
-    </row>
-    <row r="7" ht="120" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Saúde e Monitorização Sanitária</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 13.º do Regulamento 2023/0447 (PE/Conselho)</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>1. Operators shall ensure that:
-(a) dogs or cats under their responsibility are inspected by animal caretakers at least once a day and vulnerable dogs and cats, such as newborns, ill or injured dogs and cats, and peri-partum bitches and queens, are inspected more frequently;
-(b) dogs or cats with compromised welfare are, where necessary, transferred without undue delay to a separate area and, where needed, receive appropriate treatment;
-(c) where the recovery of a dog or a cat with compromised welfare is not achievable and the dog or cat experiences severe pain or suffering, a veterinarian is consulted without undue delay, to decide whether the dog or cat shall be euthanised to end its suffering, and, if that is the case, to perform the euthanasia using anesthesia and analgesia;
-(d) measures to prevent and control external and internal parasites, and vaccinations to prevent common diseases to which dogs or cats are likely to be exposed are implemented;
-(e) enrichment do not present a significant risk of injury or biological or chemical contamination or any other health risk.
-Point (a) shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
-Member states may grant derogations from point (c) in cases of emergencies, where no veterinarian can be reached without undue delay, provided that national rules are put in place to ensure that:
-(i) an immediate action ending the life of the dog or cat with minimum pain and suffering using a method inducing instant death is undertaken by a trained competent person;
-(ii) the operator keeps a record of the use of the derogation for purposes of the official control.
-2. Operators of breeding establishments shall additionally ensure that:
-(-a) measures are taken to safeguard the health of dogs or cats in accordance with point 3 of Annex I;
-(-b) bitches or queens are only bred if they have reached a minimum age and skeletal maturity in accordance with point 3 of Annex I, and they have no diagnosed disease, clinical sign of diseases or physical conditions which could negatively impact their pregnancy and welfare;
-(-c) litter-giving pregnancies of bitches or queens follows a maximum frequency in accordance with point 3 of Annex I;
-(-d) lactating queens are not mated or inseminated;
-(-e) dogs and cats which are no longer used for reproduction, including as a result of the provisions of this Regulation, are either kept or sold, donated or rehomed, not killed or abandoned.</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>1 — Os operadores devem assegurar que:
-(a) os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados e fêmeas em período peri-parto, são inspecionados com maior frequência;
-(b) os cães e gatos com bem-estar comprometido são, quando necessário, transferidos sem demora injustificada para uma área separada e, se necessário, recebem tratamento adequado;
-(c) quando a recuperação de um cão ou gato com bem-estar comprometido não seja alcançável e o animal experiencie dor ou sofrimento severo, um médico veterinário é consultado sem demora injustificada para decidir se o animal deve ser objeto de eutanásia para pôr termo ao seu sofrimento e, em caso afirmativo, para realizar a eutanásia com recurso a anestesia e analgesia;
-(d) são implementadas medidas de prevenção e controlo de parasitas externos e internos, bem como vacinações para prevenção de doenças comuns às quais os cães ou gatos são suscetíveis de estar expostos;
-(e) os enriquecimentos não apresentam risco significativo de lesões ou de contaminação biológica ou química, nem qualquer outro risco para a saúde.
-A alínea (a) não se aplica aos cães de guarda de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para fins de guarda ou treino.
-Os Estados-Membros podem conceder derrogações relativamente à alínea (c) em casos de emergência, quando não seja possível contactar um médico veterinário sem demora injustificada, desde que sejam estabelecidas regras nacionais que assegurem que:
-(i) é tomada imediatamente uma ação que ponha fim à vida do cão ou gato com o mínimo de dor e sofrimento, utilizando um método que induza a morte instantânea, por uma pessoa competente e devidamente habilitada;
-(ii) o operador mantém um registo da utilização da derrogação para efeitos de controlo oficial.
-2 — Os operadores de estabelecimentos de criação devem adicionalmente assegurar que:
-(-a) são tomadas medidas para salvaguardar a saúde dos cães ou gatos em conformidade com o ponto 3 do Anexo I;
-(-b) as cadelas ou gatas só são reproduzidas se tiverem atingido a idade mínima e a maturidade esquelética em conformidade com o ponto 3 do Anexo I, e não apresentem doença diagnosticada, sinais clínicos de doença ou condições físicas que possam impactar negativamente a gestação e o seu bem-estar;
-(-c) a frequência de gestações com ninhadas de cadelas ou gatas respeita a frequência máxima fixada no ponto 3 do Anexo I;
-(-d) as gatas a lactar não são acasaladas nem inseminadas;
-(-e) os cães e gatos que deixem de ser utilizados para reprodução, nomeadamente em resultado das disposições do presente Regulamento, são mantidos ou vendidos, doados ou realojados, não sendo mortos nem abandonados.</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Art.º 33.º do RGBEAC — Regime Geral do Bem-Estar dos Animais de Companhia (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Artigo 33.º — Cuidados de saúde
-1 — Os detentores dos animais de companhia devem assegurar-lhes os cuidados de saúde adequados, nomeadamente seguindo as orientações da DGAV em matéria de vacinação e tratamentos obrigatórios, bem como consultas regulares junto de médico veterinário.
-2 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
-3 — Os médicos veterinários e os centros de atendimento médico-veterinário (CAMV) devem manter um arquivo com os dados clínicos de cada animal, pelo período mínimo de cinco anos, que ficará à disposição das autoridades competentes.
-[dim]4 — Os CAMV, enquanto estabelecimentos de saúde, colaborarão na vigilância epidemiológica das doenças de notificação obrigatória que detetem e no seu controlo.
-[dim]5 — Os médicos veterinários denunciam, junto da DGAV ou demais entidades com competência de fiscalização do cumprimento das normas constantes do presente decreto-lei, sempre que, no exercício de sua profissão, suspeitem de maus-tratos a animais de companhia.</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Art.º 6.º (Cuidados médico-veterinários) do Código do Animal — DL n.º 214/2013</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Artigo 6.º — Cuidados médico-veterinários
-O detentor do animal deve assegurar ao animal ferido ou doente os cuidados médico-veterinários adequados, designadamente retirando o mesmo do alojamento sempre que este seja um local de venda.</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>Art.º 13.º (Maneio) e art.º 16.º (Cuidados de saúde animal) do DL n.º 276/2001, de 17 de outubro</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Artigo 13.º — Maneio
-1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
-[dim]2 — O maneio deve ser feito por pessoal que possua formação teórica e prática específica ou sob a supervisão de uma pessoa competente para o efeito.
-3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados aos que tiverem sinais que levem a suspeitar estarem doentes, lesionados ou com alterações comportamentais.
-[dim]4 — O manuseamento dos animais deve ser feito de forma a não lhes causar quaisquer dores, sofrimento ou distúrbios desnecessários.
-[dim]5 — Quando houver necessidade de recorrer a meios de contenção, não devem estes causar ferimentos, dores ou angústia desnecessários aos animais.
-Artigo 16.º — Cuidados de saúde animal
-1 — Sem prejuízo de quaisquer medidas determinadas pela DGAV, deve existir um programa de profilaxia médica e sanitária devidamente elaborado e supervisionado pelo médico veterinário responsável e executado por profissionais competentes.
-2 — No âmbito do número anterior, os animais devem ser sujeitos a exames médico-veterinários de rotina, vacinações e desparasitações sempre que aconselhável.
-3 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
-4 — Sempre que se justifique, os animais doentes ou lesionados devem ser isolados em instalações adequadas e equipadas, se for caso disso, com cama seca e confortável.
-[dim]5 — Os medicamentos, produtos ou substâncias de prescrição médico-veterinária devem ser armazenados em locais secos e com acesso restrito.
-[dim]6 — A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior deve ser feita sob orientação do médico veterinário responsável.</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 276/2001 prevê inspeção diária (n.º 3 do art.º 13.º) e programa de profilaxia supervisionado por veterinário (n.º 1 do art.º 16.º) — alinhamento parcial com as als. (a) e (d) do n.º 1 do art.º 13.º do @regulamento. Lacunas: (1) não distingue animais vulneráveis com maior frequência de inspeção; (2) não prevê isolamento em área separada com tratamento (al. (b)); (3) não exige consulta veterinária para decisão de eutanásia com anestesia/analgesia (al. (c)); (4) nenhuma das obrigações sanitárias para criadores previstas no n.º 2 está contemplada: sem idade mínima de reprodução, sem frequência máxima de partos, sem proibição de cobrição de fêmeas a lactar, sem regime de rehoming.</t>
-        </is>
-      </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>O @codigo limita os cuidados médico-veterinários ao animal ferido ou doente (art.º 6.º) — sem qualquer obrigação de inspeção diária, programa de profilaxia ou isolamento. É o diploma com maior divergência face ao n.º 1 do art.º 13.º do @regulamento, omitindo igualmente todas as obrigações sanitárias específicas para criadores previstas no n.º 2.</t>
-        </is>
-      </c>
-      <c r="M7" s="10" t="inlineStr">
-        <is>
-          <t>O @rgbeac (art.º 33.º) centra os cuidados de saúde no detentor em geral (n.ºs 1 a 3), sem distinguir obrigações reforçadas para operadores de criação. Não prevê: inspeção diária sistemática por cuidadores; isolamento imediato de animais com bem-estar comprometido; nem qualquer dos requisitos sanitários para criadores do n.º 2 do art.º 13.º do @regulamento. Os n.ºs 4 e 5 (CAMV e denúncia de maus-tratos) não têm correspondência direta no @regulamento.</t>
-        </is>
-      </c>
-      <c r="N7" s="11" t="inlineStr">
-        <is>
-          <t>A @legislacao vigente (DL n.º 276/2001) tem o maior alinhamento, mas insuficiente. Necessidade de alteração dos três diplomas: (1) introduzir inspeção diária diferenciada para animais vulneráveis (al. (a) do n.º 1 do art.º 13.º do @regulamento); (2) criar obrigação de isolamento e tratamento imediato (al. (b)); (3) regular o processo de eutanásia com supervisão veterinária e anestesia/analgesia (al. (c)); (4) para criadores (n.º 2): fixar idade mínima e maturidade esquelética das fêmeas reprodutoras, frequência máxima de partos conforme Anexo I, proibição de cobrição de fêmeas a lactar, e regime de rehoming dos animais retirados da reprodução.</t>
-        </is>
-      </c>
-      <c r="O7" s="11" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P7" s="11" t="inlineStr"/>
-    </row>
-    <row r="8" ht="120" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Detenção Responsável e Informação</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 8.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Operators shall provide to the acquirer of a dog or cat written information necessary to enable him or her to ensure the welfare of the dog or cat including information on responsible ownership and on the specific needs of the dog or cat in terms of feeding, caring, health, housing and behavioural needs, as well as information on its health.
 1a. The written information on the dog or cat's health referred to in the first paragraph shall include at least:
@@ -1319,7 +1085,7 @@
 In case the information on the dog's or cat's health is documented in a document required under Regulation (EU) 2016/429, the operator shall transmit that document to the acquirer.</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem fornecer ao adquirente de um cão ou gato informação escrita necessária para lhe permitir assegurar o bem-estar do cão ou gato, incluindo informação sobre detenção responsável e sobre as necessidades específicas do cão ou gato em termos de alimentação, cuidados, saúde, alojamento e necessidades comportamentais, bem como informação sobre a sua saúde.
 1a. A informação escrita sobre a saúde do cão ou gato referida no parágrafo anterior deve incluir pelo menos:
@@ -1328,23 +1094,23 @@
 Caso a informação sobre a saúde do cão ou gato esteja documentada num documento exigido sob o Regulamento (UE) 2016/429, o operador deve transmitir esse documento ao adquirente.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Art.º 8.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1 — O detentor do animal de companhia deve possuir informação sobre as obrigações inerentes à sua detenção, incluindo direitos e responsabilidades, normas de bem-estar, cuidados de saúde, comportamento, necessidades específicas da espécie/raça, duração de vida esperada, custos de manutenção, e proibição de abandono.
 2 — Os comerciantes devem fornecer por escrito ao adquirente informação completa antes da transferência do animal, incluindo identidade e dados de contacto do comerciante, dados de identificação do animal, cuidados de saúde e estado de vacinação, e certificado de origem ou de compatibilidade quando aplicável.</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Art.º 57.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>1 — O detentor do animal deve ter acesso a informação sobre:
 a) As obrigações inerentes à sua detenção, direitos e responsabilidades;
@@ -1356,56 +1122,56 @@
 2 — Os criadores e comerciantes devem fornecer informação escrita completa ao adquirente antes da transferência do animal, incluindo dados de identificação e cuidados de saúde.</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Art.º 20.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>1 — O proprietário ou detentor de animal de companhia deve ter acesso a informação adequada sobre as suas obrigações relativas ao bem-estar do animal.
 2 — Os detentores de animais de companhia que os comercializem devem fornecer informação ao adquirente sobre o estado de saúde do animal e vacinas efetuadas.</t>
         </is>
       </c>
-      <c r="K8" s="8" t="inlineStr">
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 20.º) é genérico e não especifica a forma escrita nem detalhes de conteúdo. O @regulamento exige informação escrita sobre necessidades específicas de bem-estar (alimentação, cuidados, saúde, alojamento, comportamento) e condiciona a transferência à transmissão dessa informação.</t>
         </is>
       </c>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 57.º) exige informação escrita mas com âmbito mais amplo (duração de vida, custos) do que o @regulamento, que se foca especificamente em bem-estar e saúde.</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="M6" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.º 8.º) aproxima-se do conteúdo do @regulamento, exigindo informação escrita antes da transferência, incluindo dados de saúde e vacinação, mas ainda sem o enfoque específico em bem-estar comportamental.</t>
         </is>
       </c>
-      <c r="N8" s="11" t="inlineStr">
+      <c r="N6" s="11" t="inlineStr">
         <is>
           <t>Necessidade de alteração: (1) formalizar requisito de informação escrita como condição de transferência de animal; (2) especificar conteúdo obrigatório sobre bem-estar, saúde e necessidades comportamentais; (3) harmonizar entre @codigo e @rgbeac quanto a âmbito e forma.</t>
         </is>
       </c>
-      <c r="O8" s="11" t="inlineStr">
+      <c r="O6" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P8" s="11" t="inlineStr"/>
+      <c r="P6" s="11" t="inlineStr"/>
     </row>
-    <row r="9" ht="120" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="7" ht="120" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Competências de Cuidadores e Bem-Estar Animal</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Art.º 9.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>1. Animal caretakers, other than volunteers in shelters and interns who are under the responsibility of a competent animal caretaker, shall have the following competences as regards the dogs and cats they are handling:
 (a) understanding of their biological behaviour and their physiological and ethological needs;
@@ -1417,7 +1183,7 @@
 3. The Commission shall, by means of implementing acts, lay down minimum requirements concerning the formal education, training or professional experience in order to acquire the competences referred to in paragraph 2 and for the training courses referred to in paragraph 2a. Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 24. The implementing act concerning the training courses referred to in paragraph 2a shall be adopted by [3 years from the date of entry into force of the Regulation].</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>1. Os cuidadores de animais, com exceção de voluntários em abrigos e estagiários sob a responsabilidade de um cuidador competente, devem ter as seguintes competências no que diz respeito aos cães e gatos que manuseiam:
 (a) compreensão do seu comportamento biológico e das suas necessidades fisiológicas e etológicas;
@@ -1429,12 +1195,12 @@
 3. A Comissão estabelecerá, por meio de atos de execução, os requisitos mínimos relativos à educação formal, formação ou experiência profissional para adquirir as competências referidas no parágrafo 2 e para os cursos de formação referidos no parágrafo 2a. Esses atos de execução serão adotados de acordo com o procedimento de exame referido no artigo 24.º. O ato de execução relativo aos cursos de formação referidos no parágrafo 2a deve ser adotado por [3 anos da data de entrada em vigor do Regulamento].</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Art.ºs 69.º, 84.º e 90.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Artigo 69.º — Formação
 A reprodução, criação, manutenção, venda ou treino de animais de companhia depende de aprovação em formação sobre detenção responsável de animais de companhia, bem como sobre as necessidades fisiológicas e etológicas específicas da espécie animal em causa, ministrada pelo ICNF, I.P. ou entidades por este certificadas.
@@ -1444,23 +1210,23 @@
 O pessoal auxiliar deve possuir os conhecimentos e a experiência adequada, o qual fica, contudo, sob a orientação do médico veterinário responsável.</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Art.º 19.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Artigo 19.º — Pessoal auxiliar
 Os alojamentos devem dispor de pessoal auxiliar que possua os conhecimentos e a aptidão necessária para assegurar os cuidados adequados aos animais, o qual fica sob a orientação do médico veterinário responsável.</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Art.º 13.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Artigo 13.º — Maneio
 1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
@@ -1468,45 +1234,45 @@
 3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados.</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 13.º) exige pessoal 'técnico competente' com 'formação teórica e prática específica' e 'inspeção diária', mas não detalha competências concretas. O @regulamento especifica 4 competências estruturadas (comportamento biológico, reconhecimento de sofrimento, maneio e bem-estar, conhecimento de obrigações) e exige documentação de educação/formação/experiência.</t>
         </is>
       </c>
-      <c r="L9" s="9" t="inlineStr">
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 19.º) é genérico: exige apenas 'conhecimentos e aptidão necessária' sob orientação do médico veterinário responsável. Não detalha competências concretas nem exigências de formação formal.</t>
         </is>
       </c>
-      <c r="M9" s="10" t="inlineStr">
+      <c r="M7" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.ºs 69.º, 84.º, 90.º) aproxima-se mais do @regulamento: exige 'conhecimentos e experiência adequados', menciona 'necessidades fisiológicas e etológicas', exige formação certificada pelo ICNF. Lacuna: não detalha as 4 competências específicas do @regulamento (reconhecimento de sofrimento, condicionamento operante, etc.).</t>
         </is>
       </c>
-      <c r="N9" s="11" t="inlineStr">
+      <c r="N7" s="11" t="inlineStr">
         <is>
           <t>Alinhamento parcial do @rgbeac com @regulamento. Para @codigo e @legislacao, necessidade de: (1) detalhar as 4 competências específicas (comportamento, reconhecimento de sofrimento, maneio positivo, conhecimento de obrigações); (2) exigir documentação formal de educação/formação/experiência; (3) requerer que operador designe formador responsável que transfira conhecimento; (4) implementar requisitos mínimos de formação via regulamento delegado.</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O7" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P9" s="11" t="inlineStr"/>
+      <c r="P7" s="11" t="inlineStr"/>
     </row>
-    <row r="10" ht="120" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Avaliação e Supervisão de Bem-Estar</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Art.º 10.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Operators shall:
 (a) ensure that the establishments under their responsibility receive a visit by a veterinarian within the first year after the date of application of this Regulation or within the first year after having notified a new establishment, for the purpose of identifying and assessing any risk factor for the welfare of the dogs or cats and advising the operator on measures to address those risks; thereafter the visits from a veterinarian shall take place when appropriate, based on a risk analysis by the competent authorities; Member States may provide for that the advisory welfare visits are annual;
@@ -1514,7 +1280,7 @@
 By 24 months from the date of entry into force of this Regulation, the Commission shall adopt delegated acts in accordance with Article 23 supplementing this Article in order to lay down minimum criteria to be assessed during the advisory welfare visit.</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem:
 (a) assegurar que os estabelecimentos sob a sua responsabilidade recebem uma visita de um médico veterinário no prazo de um ano a partir da data de aplicação do presente Regulamento ou no prazo de um ano após notificação de novo estabelecimento, com o objetivo de identificar e avaliar quaisquer fatores de risco para o bem-estar dos cães ou gatos e aconselhar o operador sobre medidas para resolver esses riscos; depois, as visitas do médico veterinário devem ocorrer quando apropriado, com base numa análise de risco pelas autoridades competentes; os Estados-Membros podem estabelecer que as visitas de aconselhamento de bem-estar sejam anuais;
@@ -1522,12 +1288,12 @@
 Dentro de 24 meses a partir da data de entrada em vigor do presente Regulamento, a Comissão deve adotar atos delegados em conformidade com o artigo 23.º que complementem o presente artigo de forma a estabelecer critérios mínimos a serem avaliados durante a visita de aconselhamento de bem-estar.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Art.º 56.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Artigo 56.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem, com exceção dos alojamentos para hospedagem com fins higiénicos, devem ter ao seu serviço um médico veterinário responsável pelo alojamento.
@@ -1538,12 +1304,12 @@
 d) A colaboração com as autoridades competentes em todas as ações que estas determinem.</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Art.º 32.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Artigo 32.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem sem fins lucrativos e com fins lucrativos de animais, com exceção dos com fins higiénicos, necessitam de ter ao seu serviço um médico veterinário que seja responsável pelo alojamento.
@@ -1553,12 +1319,12 @@
 c) A colaboração com as autoridades competentes em todas as ações que estas determinarem.</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Art.º 4.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Artigo 4.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem sem fins lucrativos e com fins lucrativos de animais, com exceção dos alojamentos para hospedagem com fins higiénicos, devem ter ao seu serviço um médico veterinário que seja responsável pelo alojamento.
@@ -1568,45 +1334,45 @@
 c) A colaboração com as autoridades competentes em todas as ações que estas determinarem.</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 4.º) estabelece a obrigação de ter médico veterinário responsável que execute 'programas e ações' para saúde e bem-estar, mas não especifica que essa avaliação deve ocorrer em prazo determinado (ex.: 1 ano) ou que os registos devem ser mantidos por período específico (4 anos). O @regulamento é mais prescritivo neste aspecto.</t>
         </is>
       </c>
-      <c r="L10" s="9" t="inlineStr">
+      <c r="L8" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 32.º) replica quase verbatim o art.º 4.º do DL n.º 276/2001, mantendo as mesmas lacunas: não fixa prazos para avaliações de bem-estar nem obrigações de manutenção de registos estruturados.</t>
         </is>
       </c>
-      <c r="M10" s="10" t="inlineStr">
+      <c r="M8" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.º 56.º) reforça a obrigação com 'parecer relativo à verificação das condições higiossanitárias e de bem-estar', mas igualmente sem prazos específicos para avaliações ou duração de retenção de registos. Ambos focam-se em 'programas' interno, não em 'visitas periódicas externas'.</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="N8" s="11" t="inlineStr">
         <is>
           <t>Lacuna estrutural em toda a legislação nacional: enquanto o @regulamento exige 'visita de um veterinário' num prazo específico (1 ano) com manutenção de registos por 4 anos e transmissão entre veterinários, a legislação nacional concentra-se em ter um 'médico veterinário responsável' no estabelecimento. Necessidade de alteração: (1) formalizar obrigação de 'visita de avaliação' por veterinário dentro de 1 ano após notificação; (2) exigir avaliações periódicas conforme risco; (3) obrigatória manutenção de registos por 4 anos; (4) garantir transmissão de informações ao próximo veterinário avaliador; (5) estabelecer critérios mínimos de avaliação (bem-estar comportamental, alojamento, saúde, etc.).</t>
         </is>
       </c>
-      <c r="O10" s="11" t="inlineStr">
+      <c r="O8" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P10" s="11" t="inlineStr"/>
+      <c r="P8" s="11" t="inlineStr"/>
     </row>
-    <row r="11" ht="120" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Alimentação e Hidratação</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Art.º 11.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that dogs or cats are fed in accordance with the requirements laid down in point 1 of Annex I.
 2. Operators shall ensure that dogs or cats are adequately fed and hydrated by supplying:
@@ -1622,7 +1388,7 @@
 3a. Where advised in writing by a veterinarian to do so, the operators may adjust the feeding and watering frequencies for an individual dog or cat. The operators shall keep a record of the advice for its entire duration as advised by the veterinarian.</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>1 — Os operadores devem assegurar que os cães e gatos são alimentados de acordo com os requisitos estabelecidos no ponto 1 do Anexo I.
 2 — Os operadores devem assegurar que os cães e gatos são adequadamente alimentados e hidratados fornecendo:
@@ -1638,79 +1404,79 @@
 3a — Quando aconselhado por escrito por um médico veterinário, os operadores podem ajustar as frequências de alimentação e hidratação para um cão ou gato individual. Os operadores devem manter um registo do conselho durante toda a sua duração, conforme aconselhado pelo médico veterinário.</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso no @rgbeac]</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso no @codigo]</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso na legislação vigente]</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>Verificar conformidade com legislação portuguesa vigente</t>
         </is>
       </c>
-      <c r="L11" s="9" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>Verificar alinhamento com Código do Animal</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M9" s="10" t="inlineStr">
         <is>
           <t>Verificar alinhamento com RGBEAC</t>
         </is>
       </c>
-      <c r="N11" s="11" t="inlineStr">
+      <c r="N9" s="11" t="inlineStr">
         <is>
           <t>Requisitos detalhados de alimentação e hidratação para cães e gatos. Novo artigo introduzido pelo Regulamento.</t>
         </is>
       </c>
-      <c r="O11" s="11" t="inlineStr">
+      <c r="O9" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P11" s="11" t="inlineStr">
+      <c r="P9" s="11" t="inlineStr">
         <is>
           <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="120" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Alojamento</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Art.º 12.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>1. Operators of breeding and selling establishments shall ensure that dogs or cats are provided with housing in accordance with point 2 of Annex I. Operators of shelters shall ensure that dogs or cats are provided with housing in accordance with point 2.2 of Annex I.
 2. Operators shall ensure that:
@@ -1732,7 +1498,7 @@
 7a. Paragraphs 2(a), (b), (ba) (da) (e), 6, 6a and 7 shall not apply to livestock guardian dogs, nor to herding dogs, during the periods where such dogs are used for guarding or herding in the context of on foot seasonal transhumance. Paragraph 2(da) shall not apply to livestock guardian dogs during the periods when such dogs are used for training purposes.</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>1 — Os operadores de estabelecimentos de criação e venda devem assegurar que os cães e gatos são alojados de acordo com o ponto 2 do Anexo I. Os operadores de abrigos devem assegurar que os cães e gatos são alojados de acordo com o ponto 2.2 do Anexo I.
 2 — Os operadores devem assegurar que:
@@ -1754,79 +1520,205 @@
 7a — Os parágrafos 2(a), (b), (ba) (da) (e), 6, 6a e 7 não se aplicam aos cães de guarda de gado, nem aos cães de pastoreio, durante os períodos em que tais cães são utilizados para guarda ou pastoreio no contexto de transumância sazonal a pé. O parágrafo 2(da) não se aplica aos cães de guarda de gado durante os períodos em que tais cães são utilizados para fins de treino.</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso no @rgbeac]</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso no @codigo]</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso na legislação vigente]</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>Verificar conformidade com legislação portuguesa vigente</t>
         </is>
       </c>
-      <c r="L12" s="9" t="inlineStr">
+      <c r="L10" s="9" t="inlineStr">
         <is>
           <t>Verificar alinhamento com Código do Animal</t>
         </is>
       </c>
-      <c r="M12" s="10" t="inlineStr">
+      <c r="M10" s="10" t="inlineStr">
         <is>
           <t>Verificar alinhamento com RGBEAC</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>Requisitos detalhados de alojamento para cães e gatos em diferentes tipos de estabelecimentos (criação, venda, abrigos). Novo artigo introduzido pelo Regulamento.</t>
         </is>
       </c>
-      <c r="O12" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P12" s="11" t="inlineStr">
+      <c r="P10" s="11" t="inlineStr">
         <is>
           <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="120" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="11" ht="120" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Saúde e Monitorização Sanitária</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 13.º do Regulamento 2023/0447 (PE/Conselho)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>1. Operators shall ensure that:
+(a) dogs or cats under their responsibility are inspected by animal caretakers at least once a day and vulnerable dogs and cats, such as newborns, ill or injured dogs and cats, and peri-partum bitches and queens, are inspected more frequently;
+(b) dogs or cats with compromised welfare are, where necessary, transferred without undue delay to a separate area and, where needed, receive appropriate treatment;
+(c) where the recovery of a dog or a cat with compromised welfare is not achievable and the dog or cat experiences severe pain or suffering, a veterinarian is consulted without undue delay, to decide whether the dog or cat shall be euthanised to end its suffering, and, if that is the case, to perform the euthanasia using anesthesia and analgesia;
+(d) measures to prevent and control external and internal parasites, and vaccinations to prevent common diseases to which dogs or cats are likely to be exposed are implemented;
+(e) enrichment do not present a significant risk of injury or biological or chemical contamination or any other health risk.
+Point (a) shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
+Member states may grant derogations from point (c) in cases of emergencies, where no veterinarian can be reached without undue delay, provided that national rules are put in place to ensure that:
+(i) an immediate action ending the life of the dog or cat with minimum pain and suffering using a method inducing instant death is undertaken by a trained competent person;
+(ii) the operator keeps a record of the use of the derogation for purposes of the official control.
+2. Operators of breeding establishments shall additionally ensure that:
+(-a) measures are taken to safeguard the health of dogs or cats in accordance with point 3 of Annex I;
+(-b) bitches or queens are only bred if they have reached a minimum age and skeletal maturity in accordance with point 3 of Annex I, and they have no diagnosed disease, clinical sign of diseases or physical conditions which could negatively impact their pregnancy and welfare;
+(-c) litter-giving pregnancies of bitches or queens follows a maximum frequency in accordance with point 3 of Annex I;
+(-d) lactating queens are not mated or inseminated;
+(-e) dogs and cats which are no longer used for reproduction, including as a result of the provisions of this Regulation, are either kept or sold, donated or rehomed, not killed or abandoned.</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>1 — Os operadores devem assegurar que:
+(a) os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados e fêmeas em período peri-parto, são inspecionados com maior frequência;
+(b) os cães e gatos com bem-estar comprometido são, quando necessário, transferidos sem demora injustificada para uma área separada e, se necessário, recebem tratamento adequado;
+(c) quando a recuperação de um cão ou gato com bem-estar comprometido não seja alcançável e o animal experiencie dor ou sofrimento severo, um médico veterinário é consultado sem demora injustificada para decidir se o animal deve ser objeto de eutanásia para pôr termo ao seu sofrimento e, em caso afirmativo, para realizar a eutanásia com recurso a anestesia e analgesia;
+(d) são implementadas medidas de prevenção e controlo de parasitas externos e internos, bem como vacinações para prevenção de doenças comuns às quais os cães ou gatos são suscetíveis de estar expostos;
+(e) os enriquecimentos não apresentam risco significativo de lesões ou de contaminação biológica ou química, nem qualquer outro risco para a saúde.
+A alínea (a) não se aplica aos cães de guarda de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para fins de guarda ou treino.
+Os Estados-Membros podem conceder derrogações relativamente à alínea (c) em casos de emergência, quando não seja possível contactar um médico veterinário sem demora injustificada, desde que sejam estabelecidas regras nacionais que assegurem que:
+(i) é tomada imediatamente uma ação que ponha fim à vida do cão ou gato com o mínimo de dor e sofrimento, utilizando um método que induza a morte instantânea, por uma pessoa competente e devidamente habilitada;
+(ii) o operador mantém um registo da utilização da derrogação para efeitos de controlo oficial.
+2 — Os operadores de estabelecimentos de criação devem adicionalmente assegurar que:
+(-a) são tomadas medidas para salvaguardar a saúde dos cães ou gatos em conformidade com o ponto 3 do Anexo I;
+(-b) as cadelas ou gatas só são reproduzidas se tiverem atingido a idade mínima e a maturidade esquelética em conformidade com o ponto 3 do Anexo I, e não apresentem doença diagnosticada, sinais clínicos de doença ou condições físicas que possam impactar negativamente a gestação e o seu bem-estar;
+(-c) a frequência de gestações com ninhadas de cadelas ou gatas respeita a frequência máxima fixada no ponto 3 do Anexo I;
+(-d) as gatas a lactar não são acasaladas nem inseminadas;
+(-e) os cães e gatos que deixem de ser utilizados para reprodução, nomeadamente em resultado das disposições do presente Regulamento, são mantidos ou vendidos, doados ou realojados, não sendo mortos nem abandonados.</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Art.º 33.º do RGBEAC — Regime Geral do Bem-Estar dos Animais de Companhia (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Artigo 33.º — Cuidados de saúde
+1 — Os detentores dos animais de companhia devem assegurar-lhes os cuidados de saúde adequados, nomeadamente seguindo as orientações da DGAV em matéria de vacinação e tratamentos obrigatórios, bem como consultas regulares junto de médico veterinário.
+2 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
+3 — Os médicos veterinários e os centros de atendimento médico-veterinário (CAMV) devem manter um arquivo com os dados clínicos de cada animal, pelo período mínimo de cinco anos, que ficará à disposição das autoridades competentes.
+[dim]4 — Os CAMV, enquanto estabelecimentos de saúde, colaborarão na vigilância epidemiológica das doenças de notificação obrigatória que detetem e no seu controlo.
+[dim]5 — Os médicos veterinários denunciam, junto da DGAV ou demais entidades com competência de fiscalização do cumprimento das normas constantes do presente decreto-lei, sempre que, no exercício de sua profissão, suspeitem de maus-tratos a animais de companhia.</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Art.º 6.º (Cuidados médico-veterinários) do Código do Animal — DL n.º 214/2013</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 6.º — Cuidados médico-veterinários
+O detentor do animal deve assegurar ao animal ferido ou doente os cuidados médico-veterinários adequados, designadamente retirando o mesmo do alojamento sempre que este seja um local de venda.</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Art.º 13.º (Maneio) e art.º 16.º (Cuidados de saúde animal) do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 13.º — Maneio
+1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
+[dim]2 — O maneio deve ser feito por pessoal que possua formação teórica e prática específica ou sob a supervisão de uma pessoa competente para o efeito.
+3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados aos que tiverem sinais que levem a suspeitar estarem doentes, lesionados ou com alterações comportamentais.
+[dim]4 — O manuseamento dos animais deve ser feito de forma a não lhes causar quaisquer dores, sofrimento ou distúrbios desnecessários.
+[dim]5 — Quando houver necessidade de recorrer a meios de contenção, não devem estes causar ferimentos, dores ou angústia desnecessários aos animais.
+Artigo 16.º — Cuidados de saúde animal
+1 — Sem prejuízo de quaisquer medidas determinadas pela DGAV, deve existir um programa de profilaxia médica e sanitária devidamente elaborado e supervisionado pelo médico veterinário responsável e executado por profissionais competentes.
+2 — No âmbito do número anterior, os animais devem ser sujeitos a exames médico-veterinários de rotina, vacinações e desparasitações sempre que aconselhável.
+3 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
+4 — Sempre que se justifique, os animais doentes ou lesionados devem ser isolados em instalações adequadas e equipadas, se for caso disso, com cama seca e confortável.
+[dim]5 — Os medicamentos, produtos ou substâncias de prescrição médico-veterinária devem ser armazenados em locais secos e com acesso restrito.
+[dim]6 — A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior deve ser feita sob orientação do médico veterinário responsável.</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 prevê inspeção diária (n.º 3 do art.º 13.º) e programa de profilaxia supervisionado por veterinário (n.º 1 do art.º 16.º) — alinhamento parcial com as als. (a) e (d) do n.º 1 do art.º 13.º do @regulamento. Lacunas: (1) não distingue animais vulneráveis com maior frequência de inspeção; (2) não prevê isolamento em área separada com tratamento (al. (b)); (3) não exige consulta veterinária para decisão de eutanásia com anestesia/analgesia (al. (c)); (4) nenhuma das obrigações sanitárias para criadores previstas no n.º 2 está contemplada: sem idade mínima de reprodução, sem frequência máxima de partos, sem proibição de cobrição de fêmeas a lactar, sem regime de rehoming.</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>O @codigo limita os cuidados médico-veterinários ao animal ferido ou doente (art.º 6.º) — sem qualquer obrigação de inspeção diária, programa de profilaxia ou isolamento. É o diploma com maior divergência face ao n.º 1 do art.º 13.º do @regulamento, omitindo igualmente todas as obrigações sanitárias específicas para criadores previstas no n.º 2.</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac (art.º 33.º) centra os cuidados de saúde no detentor em geral (n.ºs 1 a 3), sem distinguir obrigações reforçadas para operadores de criação. Não prevê: inspeção diária sistemática por cuidadores; isolamento imediato de animais com bem-estar comprometido; nem qualquer dos requisitos sanitários para criadores do n.º 2 do art.º 13.º do @regulamento. Os n.ºs 4 e 5 (CAMV e denúncia de maus-tratos) não têm correspondência direta no @regulamento.</t>
+        </is>
+      </c>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>A @legislacao vigente (DL n.º 276/2001) tem o maior alinhamento, mas insuficiente. Necessidade de alteração dos três diplomas: (1) introduzir inspeção diária diferenciada para animais vulneráveis (al. (a) do n.º 1 do art.º 13.º do @regulamento); (2) criar obrigação de isolamento e tratamento imediato (al. (b)); (3) regular o processo de eutanásia com supervisão veterinária e anestesia/analgesia (al. (c)); (4) para criadores (n.º 2): fixar idade mínima e maturidade esquelética das fêmeas reprodutoras, frequência máxima de partos conforme Anexo I, proibição de cobrição de fêmeas a lactar, e regime de rehoming dos animais retirados da reprodução.</t>
+        </is>
+      </c>
+      <c r="O11" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P11" s="11" t="inlineStr"/>
+    </row>
+    <row r="12" ht="120" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Necessidades Comportamentais</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Art.º 14.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that measures are taken to meet the behavioural needs of dogs or cats in accordance with point 4 of Annex I.
 2. Operators shall not keep dogs or cats in areas restraining their natural movements, except in case of Article 12(3), second sub-paragraph, or for performing the following procedures or treatments:
@@ -1843,7 +1735,7 @@
 5b. Operators shall ensure that enrichment is provided and accessible to all dogs or cats, creating a stimulating environment, enabling species-specific behaviour and reducing their frustration.</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>1 — Os operadores devem assegurar que medidas são tomadas para satisfazer as necessidades comportamentais dos cães ou gatos de acordo com o ponto 4 do Anexo I.
 2 — Os operadores não devem manter cães ou gatos em áreas que restringem os seus movimentos naturais, exceto no caso do Artigo 12(3), segundo parágrafo, ou para realizar os seguintes procedimentos ou tratamentos:
@@ -1860,79 +1752,79 @@
 5b — Os operadores devem assegurar que enriquecimento é fornecido e acessível a todos os cães ou gatos, criando um ambiente estimulante, permitindo comportamento específico da espécie e reduzindo sua frustração.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso no @rgbeac]</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso no @codigo]</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>A ser preenchido</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>[Pesquisa em progresso na legislação vigente]</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>Verificar conformidade com legislação portuguesa vigente</t>
         </is>
       </c>
-      <c r="L13" s="9" t="inlineStr">
+      <c r="L12" s="9" t="inlineStr">
         <is>
           <t>Verificar alinhamento com Código do Animal</t>
         </is>
       </c>
-      <c r="M13" s="10" t="inlineStr">
+      <c r="M12" s="10" t="inlineStr">
         <is>
           <t>Verificar alinhamento com RGBEAC</t>
         </is>
       </c>
-      <c r="N13" s="11" t="inlineStr">
+      <c r="N12" s="11" t="inlineStr">
         <is>
           <t>Requisitos de satisfação das necessidades comportamentais de cães e gatos. Proibição de retenção em áreas restritivas. Novo artigo introduzido pelo Regulamento.</t>
         </is>
       </c>
-      <c r="O13" s="11" t="inlineStr">
+      <c r="O12" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P13" s="11" t="inlineStr">
+      <c r="P12" s="11" t="inlineStr">
         <is>
           <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="120" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Práticas Dolorosas</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Art.º 15.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that mutilations, including ear cropping, tail docking, claw removal or other partial or complete digit amputation, and resection of vocal cords or folds, are not performed unless upon medical indication, which may include prophylactic, with the sole purpose of preserving, improving the health of dogs or cats or preventing injury. In such case, the procedure shall only be performed under anaesthesia and prolonged analgesia and by a veterinarian.
 1a. The medical indication for the mutilation and the details of procedure carried out shall be documented by a veterinarian. This document shall be retained by the operator until the dog or cat, together with this document, is transferred to another establishment or owner. The operator of the establishment where the mutilation was performed shall retain a copy of the document for three years after the transfer of the dog or cat.
@@ -1949,7 +1841,7 @@
 4. Member States may grant derogations from paragraph 3 for dogs intended for use in military, police or customs services.</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>1 — Os operadores devem assegurar que mutilações, incluindo corte de orelhas, corte de cauda, remoção de garras ou outra amputação parcial ou completa de dígitos, e ressecção de cordas vocais ou pregas, não são realizadas a menos que seja por indicação médica, que pode incluir profilática, com o único propósito de preservar, melhorar a saúde de cães ou gatos ou prevenir lesões. Nesse caso, o procedimento deve ser realizado apenas sob anestesia e analgesia prolongada e por um médico veterinário.
 1a — A indicação médica para a mutilação e os detalhes do procedimento realizado devem ser documentados por um médico veterinário. Este documento deve ser retido pelo operador até o cão ou gato, juntamente com este documento, ser transferido para outro estabelecimento ou proprietário. O operador do estabelecimento onde a mutilação foi realizada deve reter uma cópia do documento por três anos após a transferência do cão ou gato.
@@ -1966,54 +1858,166 @@
 4 — Os Estados-Membros podem conceder derrogações do parágrafo 3 para cães destinados ao uso em serviços militares, policiais ou aduaneiros.</t>
         </is>
       </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @rgbeac]</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @codigo]</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso na legislação vigente]</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>Verificar conformidade com legislação portuguesa vigente</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>Verificar alinhamento com Código do Animal</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>Verificar alinhamento com RGBEAC</t>
+        </is>
+      </c>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>Requisitos relativos a práticas dolorosas e mutilações em cães e gatos. Restrições a práticas de manipulação causando dor. Novo artigo introduzido pelo Regulamento.</t>
+        </is>
+      </c>
+      <c r="O13" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P13" s="11" t="inlineStr">
+        <is>
+          <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Identificação e Registo</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 17.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>1. All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip compliant with Annex II.
+1a. Operators shall ensure that dogs and cats born in their establishments are individually identified within 3 months after their birth and in any event before the date of their placing on the market.
+Operators of selling establishments, shelters and those placing and being responsible for dogs and cats in foster homes shall ensure that dogs and cats that enter their establishments or come under their responsibility are individually identified within 30 days after their arrival at the establishment and in any event before the date of their placing on the market.
+Pet owners and any other natural or legal persons, other than operators, who own dogs or cats, shall ensure that the dogs or cats are individually identified at the latest when the dog or cat reaches 3 months of age or, in case the dog or cat is placed on the market, before the date of their placing on the market.
+2. The implantation of the transponder shall be performed by a veterinarian. Member States may allow the implantation of transponders in cats to be performed by a person other than a veterinarian, if it is done under the responsibility of a veterinarian.
+3. Dogs and cats which have been individually identified by means of an injectable transponder containing a microchip, in accordance with national legislation prior to entry into force of this Regulation, shall be recognised as identified in accordance with the requirements of this Article.
+4. Within two working days after their identification, the dogs and cats shall be registered by a veterinarian in a national database.
+5. For dogs and cats kept in establishments, the registration shall be made in the name of the operator of the establishment. For dogs and cats placed in foster homes, the registration shall be made in the name of the person responsible for the foster home. For dogs and cats owned by pet owners or by any other natural or legal person, the registration shall be made in the name of the pet owner or the natural or legal person.
+Member States may grant derogations from the first subparagraph to military, police and customs dogs.
+6. In case of placing on the market or occasional and irregular donation by a natural person without online advertising, the requirements for registration shall not apply.
+7. In the case of a death of a dog or a cat, the operator, pet owner or natural or legal person owning the dog or cat shall inform the national database.
+8. In case of unreadable transponder, the operator or the natural or legal person responsible for the dog or cat shall ensure that the dog or cat is re-identified with a new transponder and re-registered in the national database.</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>1. Todos os cães e gatos mantidos em estabelecimentos colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com o Anexo II.
+1a. Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de 3 meses após o nascimento e, em qualquer caso, antes da data da sua colocação no mercado.
+Os operadores de estabelecimentos de venda, abrigos e os que colocam e são responsáveis por cães e gatos em famílias de acolhimento devem assegurar que os cães e gatos que entrem nos seus estabelecimentos sejam identificados individualmente no prazo de 30 dias após a chegada.
+Os donos de animais de companhia e quaisquer outras pessoas singulares ou coletivas que detenham cães ou gatos devem assegurar que os animais sejam identificados individualmente o mais tardar quando o animal atingir os 3 meses de idade ou, no caso de o animal ser colocado no mercado, antes da data da sua colocação no mercado.
+2. A implantação do transponder devem ser efetuada por um médico veterinário. Os Estados-Membros podem permitir que a implantação de transponders em gatos seja efetuada por pessoa que não seja médico veterinário, se for feita sob a responsabilidade de um médico veterinário.
+3. Cães e gatos que tenham sido identificados individualmente por meio de um transponder injetável contendo um microchip, em conformidade com legislação nacional anterior à entrada em vigor do presente Regulamento, são reconhecidos como identificados de acordo com os requisitos do presente artigo.
+4. No prazo de dois dias úteis após a sua identificação, os cães e gatos devem ser registados por um médico veterinário numa base de dados nacional.
+5. Para cães e gatos mantidos em estabelecimentos, o registo deve ser efetuado em nome do operador do estabelecimento. Para cães e gatos colocados em famílias de acolhimento, o registo deve ser efetuado em nome da pessoa responsável pela família de acolhimento. Para cães e gatos detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva, o registo deve ser efetuado em nome do dono ou da pessoa singular ou coletiva.
+Os Estados-Membros podem conceder derrogações ao primeiro parágrafo a cães militares, policiais e aduaneiros.
+6. Em caso de colocação no mercado ou cedência ocasional e irregular por pessoa singular sem publicidade em linha, os requisitos de registo não se aplicam.
+7. Em caso de morte de um cão ou gato, o operador, dono do animal ou pessoa singular ou coletiva proprietária devem informar a base de dados nacional.
+8. Em caso de transponder ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato devem assegurar que o animal é reidentificado com um novo transponder e re-registado na base de dados nacional.</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Art.º 17.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso no @rgbeac]</t>
+          <t>1 — A identificação dos animais de companhia, pela sua marcação, quando aplicável, e registo no SIAC, deve ser realizada:
+a) Relativamente aos cães, gatos e furões nascidos em alojamentos, até aos três meses de idade ou, em qualquer caso, antes da sua colocação no mercado;
+b) Relativamente aos cães, gatos e furões que entrem em alojamentos, nos termos dos artigos 12.º a 15.º, até trinta dias após a sua chegada ao alojamento ou, em qualquer caso, antes da data de colocação no mercado;
+c) Relativamente aos cães, gatos e furões detidos por pessoas singulares, exceto nos casos previstos nas alíneas anteriores, até aos três meses de idade ou, no caso de colocação no mercado, antes da data de colocação no mercado.</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Art.º 53.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso no @codigo]</t>
+          <t>1 — Todos os cães devem ser identificados e registados, entre os três e os seis meses de idade.
+2 — Os gatos em exposição, para fins comerciais ou lucrativos, em estabelecimentos de venda, locais de criação, feiras ou concursos, provas funcionais, publicidade ou fins similares, devem ser identificados e registados entre os três e os seis meses de idade.
+4 — Os cães e gatos são identificados através de método electrónico e registados na base de dados nacional.
+5 — A identificação electrónica é efetuada através da aplicação subcutânea de um microchip no centro da face lateral esquerda do pescoço.</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>n.ºs 1, 2 e 3 do art.º 5.º do DL n.º 82/2019, de 27 de junho</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso na legislação vigente]</t>
+          <t>1 — A identificação dos animais de companhia, pela sua marcação e registo no SIAC, deve ser realizada até 120 dias após o seu nascimento.
+2 — Na impossibilidade de determinar a data de nascimento exata, para efeitos de contagem do prazo referido no número anterior, a identificação deve ser efetuada até à perda dos dentes incisivos de leite.
+3 — Sem prejuízo dos números anteriores, e relativamente aos cães, gatos e furões que sejam cedidos e ou comercializados a partir de um criador ou de um estabelecimento autorizado para a detenção de animais de companhia, nomeadamente os centros de hospedagem com ou sem fins lucrativos e os centros de recolha oficiais, deve ser assegurada a sua marcação e registo no SIAC antes de abandonarem a instalação de nascimento ou de alojamento, independentemente da sua idade.</t>
         </is>
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>Verificar conformidade com legislação portuguesa vigente</t>
+          <t>O DL n.º 82/2019 (art.º 5.º) prevê prazo geral de 120 dias após o nascimento, sem distinguir o contexto de estabelecimento — prazo superior ao máximo de 3 meses do @regulamento, que exigirá redução. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>Verificar alinhamento com Código do Animal</t>
+          <t>O @codigo fixa prazo de identificação entre 3 e 6 meses, igualmente sem distinção entre nascimentos e entrada em estabelecimentos, ficando aquém da precisão exigida pelo @regulamento.</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>Verificar alinhamento com RGBEAC</t>
+          <t>O @rgbeac aproxima-se dos prazos do @regulamento mas aplica-se apenas a cães, gatos e furões. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>Requisitos relativos a práticas dolorosas e mutilações em cães e gatos. Restrições a práticas de manipulação causando dor. Novo artigo introduzido pelo Regulamento.</t>
+          <t>Necessidade de alteração: (1) reduzir prazo máximo de identificação de nascimentos para 3 meses; (2) criar prazo diferenciado de 30 dias para animais admitidos em estabelecimentos; (3) harmonizar prazos entre todos os diplomas nacionais.</t>
         </is>
       </c>
       <c r="O14" s="11" t="inlineStr">
@@ -2021,9 +2025,325 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="P14" s="11" t="inlineStr">
-        <is>
-          <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
+      <c r="P14" s="11" t="inlineStr"/>
+    </row>
+    <row r="15" ht="120" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Proteção de Dados</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 20a do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>The competent authorities of the Member States shall be controllers within the meaning of Regulation (EU) 2016/679 in relation to the processing of personal data collected under Article 7, Article 7a of this Regulation as well as under Article 19(1) of this Regulation when used for the purposes of official control.
+The Commission shall be a controller within the meaning of Regulation (EU) 2018/1725 in relation to the processing of personal data collected under Article 17a (6), Article 19 (2a) and the third subparagraph of Article 21(4a) of this Regulation, as well as under Article 19(1) of this Regulation when used for the purposes of compliance with Article 108 of Regulation (EU) 2017/625 and of reporting obligations under this Regulation.
+It shall be prohibited for any person having access to the personal data referred to in the first and second sub-paragraphs to divulge any personal data, the knowledge of which was acquired in the exercise of their duties or otherwise incidentally to such exercise.
+Member States and the Commission shall take all appropriate measures to address infringements of that prohibition.
+The personal data collected under the first and second sub-paragraphs shall not be used for other purposes than:
+a) official controls by Member States competent authorities of the compliance with the welfare and traceability requirements under this regulation and compliance with Regulation (EU) 2016/429, including and detection of fraudulent practices, and
+b) compliance by the Commission of its obligations under Article 108 of Regulation (EU) 2017/625 and with the Commission's reporting obligations under this Regulation.
+The personal data referred to in paragraph 1 of this Article shall be retained for the following periods:
+a) in the case of Article 7 and Article 7a, 10 years after the date of cessation of the activity of the establishment;
+b) in the case of Article 17a(6), 18 months after the generation of the token referred to in Article 17a(3)(c).
+c) in case of Article 19(1), and Article 19(2a), 25 years after the first registration of the dog or cat in the database referred to in that Article or 5 years after the recording of the death of the dog or cat in that database;
+d) in case of the third subparagraph of Article 21(4a), 5 years after the date of pre-notification.</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>As autoridades competentes dos Estados-Membros devem ser controladoras no sentido do Regulamento (UE) 2016/679 em relação ao tratamento de dados pessoais recolhidos de acordo com o Artigo 7, Artigo 7a do presente Regulamento, bem como no âmbito do Artigo 19(1) do presente Regulamento quando utilizados para efeitos de inspeção oficial.
+A Comissão deve ser controladora no sentido do Regulamento (UE) 2018/1725 em relação ao tratamento de dados pessoais recolhidos de acordo com o Artigo 17a (6), Artigo 19 (2a) e o terceiro parágrafo do Artigo 21(4a) do presente Regulamento, bem como no âmbito do Artigo 19(1) do presente Regulamento quando utilizados para efeitos de conformidade com o Artigo 108 do Regulamento (UE) 2017/625 e de obrigações de comunicação de informações previstas no presente Regulamento.
+Fica proibido a qualquer pessoa com acesso aos dados pessoais mencionados no primeiro e segundo parágrafos divulgar quaisquer dados pessoais, cuja notícia foi adquirida no exercício das suas funções ou de forma incidental a tal exercício.
+Os Estados-Membros e a Comissão devem adotar todas as medidas apropriadas para fazer face aos incumprimentos dessa proibição.
+[... redução para brevidade - ver regulamento completo para texto integral]</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Art.º 20.º, nn. 3, 6, 8 do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Artigo 20.º, n.º 8 - SIAC e Proteção de Dados:
+Ao tratamento, segurança, conservação, acesso e proteção dos dados pessoais constantes do SIAC é diretamente aplicável o disposto na legislação e regulamentação relativa à proteção de dados pessoais, nomeadamente o Regulamento (UE) 2016/679 do Parlamento Europeu e do Conselho, de 27 de abril de 2016, relativo à proteção das pessoas singulares no que diz respeito ao tratamento de dados pessoais e à livre circulação desses dados.
+Artigo 20.º, n.º 6 - Transmissão de Dados Pessoais:
+Sempre que se mostre necessário à operacionalização do SIAC ou ao cumprimento das suas finalidades, deve promover-se a transmissão de dados entre sistemas de informação, preferencialmente através da Plataforma de Interoperabilidade da Administração Pública (iAP), nos termos do Decreto-Lei n.º 135/99, de 22 de abril.
+Artigo 20.º, n.º 3 - Subcontratação de Dados Pessoais:
+A DGAV, pode atribuir a gestão do SIAC a outras entidades, mediante a celebração de protocolo e sob sua supervisão, observado o regime de subcontratação de tratamento de dados pessoais.</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Art.º 55.º do Código do Animal (DL 214/2013)</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 55.º - Base de Dados
+1 - Toda a informação resultante do registo do animal é coligida numa aplicação informática nacional.
+2 - A DGAV detém, define e coordena o acesso à base de dados, podendo autorizar a sua gestão noutras entidades, mediante a celebração de protocolos, precedidos de parecer da Comissão Nacional de Proteção de Dados.
+3 - Só têm acesso à base de dados as entidades que se encontrem autorizadas, para o efeito, pela DGAV.</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>DL n.º 82/2019, Art.º 9.º</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 9.º - Registo no Sistema de Informação de Animais de Companhia
+1 - Os animais de companhia abrangidos pela obrigação de identificação devem ser registados pelo médico veterinário no SIAC, imediatamente após a sua marcação com o transponder, em nome do respetivo titular.</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>NÃO - Legislação portuguesa cobre completamente com incorporação de GDPR</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>NÃO - Cobertura expressa em Art. 55.º</t>
+        </is>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>NÃO - Implementação completa em Arts. 20.º</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>A legislação portuguesa implementa completamente os requisitos de proteção de dados do Artigo 20a. O SIAC é configurado como sistema compliant com GDPR (EU 2016/679) e com regulamentações de proteção de dados. Não há necessidade de alterações legislativas.</t>
+        </is>
+      </c>
+      <c r="O15" s="11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P15" s="11" t="inlineStr">
+        <is>
+          <t>Correspondências confirmadas por agente de pesquisa em 2026-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="120" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Entrada de Cães e Gatos na União</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 21.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>1. Dogs and cats may only be entered into the Union for placing on the Union market provided that the following conditions are met:
+a) they have been breed and kept in compliance with any of the following:
+   i) Chapter II of this Regulation;
+   ii) conditions recognised by the Union in accordance with Article 129 of Regulation (EU) 2017/625 to be equivalent to those set out by Chapter II of this Regulation; or
+   iii) where applicable, requirements contained in a specific agreement between the Union and the exporting country.
+b) they come from a third country or territory and an establishment listed in accordance with Articles 126 and 127 of Regulation (EU) 2017/625.
+2. The official certificate referred to in Article 126(2)(c) of Regulation (EU) 2017/625 accompanying dogs and cats entering into the Union from third countries and territories to be placed on the Union market, shall contain an attestation certifying compliance with paragraph 1 of this Article.
+3. Dogs and cats entering into the Union to be placed on the Union market shall be identified before their entry by a veterinarian by means of an injectable transponder containing a readable microchip compliant with Annex II.
+4. The operator responsible for the import of dogs or cats entering into the Union shall ensure the registration of the dogs or cats by a veterinarian into a national database referred to in Article 19(1), within 5 working days after their entry into the Union.
+[... ver regulamento completo para restantes parágrafos 4a e 5 ...]</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>1. A partir de [data de implementação], os cães e os gatos só podem ser introduzidos na União para colocação no mercado da União se tiverem estado detidos em conformidade com o indicado numa das alíneas seguintes...
+[Tradução disponível no documento 'Regulamento - Primeira Versão portuguesa.docx']</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Art.º 114.º e Art.º 96.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Artigo 114.º - Entrada no Território Nacional
+1 - A entrada no território nacional, por compra, cedência ou troca direta, de cães classificados como potencialmente perigosos pode ser condicionada.
+2 - Os cães referidos no número anterior que não estejam inscritos em livro de origens oficialmente reconhecido, que permaneçam em território nacional por mais de quatro meses, são obrigatoriamente esterilizados nos termos do disposto no n.º 5.º do artigo 102.º.
+3 - A introdução no território nacional por compra, cedência ou troca direta, tendo em vista a sua reprodução, de cães potencialmente perigosos é sujeita a autorização da DGAV requerida com sete dias de antecedência, decorridos os quais a mesma é tacitamente deferida.
+Artigo 96.º - Importação de Animais de Companhia
+A importação de animais que constem da lista nacional de animais de companhia provenientes de outros Estados é admitida desde que sejam cumpridas as regras sanitárias e de bem-estar animal portuguesas e comunitárias.</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Art.º 62.º do Código do Animal (DL 214/2013)</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 62.º - Entrada de Animais de Companhia Suscetíveis à Raiva em Território Nacional
+1 - A entrada em território nacional de animais de companhia suscetíveis à raiva destinados ao comércio, provenientes de outros Estados-membros ou de países terceiros, depende do cumprimento das condições fixadas no Decreto-Lei n.º 79/2001, de 20 de junho, alterado pelo Decreto-Lei n.º 260/2012, de 12 de dezembro, e noutras normas de polícia sanitária que regem o comércio e as importações de animais vivos na comunidade.
+2 - No caso das importações, deve ainda ser cumprido o regime dos controlos veterinários previsto no Decreto-Lei n.º 79/2011, de 20 de junho.
+3 - A entrada em território nacional de furões destinados ao comércio ou sem carácter comercial, para além do cumprimento do disposto nos números anteriores, depende de autorização prévia do ICNF, I.P.</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>DL n.º 82/2019, Art.º 2.º</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 2.º - Âmbito de Aplicação
+O presente decreto-lei aplica-se à identificação de animais de companhia das espécies referidas no anexo I do Regulamento (UE) n.º 576/2013, do Parlamento Europeu e do Conselho, de 12 de junho de 2013, e no anexo I do Regulamento (UE) n.º 2016/429, do Parlamento Europeu e do Conselho, de 9 de março de 2016, nascidos ou presentes no território nacional.</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>PARCIAL - Cobre entrada/importação mas sem database online de viajantes pré-notificação</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>SIM - Implementa controlos sanitários e requisitos de identificação</t>
+        </is>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>PARCIAL - Cobre entrada no território nacional com condições, não cobre movimento não-comercial pré-notificação</t>
+        </is>
+      </c>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>A legislação portuguesa implementa os requisitos essenciais de entrada e identificação pré-entrada, referenciando os Regulamentos EU 576/2013 e 2016/429. Faltam: (1) Sistema de base de dados online de viajantes com pré-notificação obrigatória para movimento não-comercial; (2) Sistema iRASFF integrado para notificações de risco de fraude.</t>
+        </is>
+      </c>
+      <c r="O16" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P16" s="11" t="inlineStr">
+        <is>
+          <t>Parcialmente coberto. Complementação necessária para movimento não-comercial e sistema iRASFF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="120" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Alteração dos Anexos</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 22.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>1. The Commission is empowered to adopt delegated acts in accordance with Article 23 amending the Annexes to this Regulation to take into account of scientific and technical progress, including, when relevant, scientific opinions of the European Food Safety Authority, as regards:
+a) a suitable number of animal caretakers in breeding and selling establishments;
+b) watering and feeding requirements and weaning process;
+c) temperature ranges;
+d) lighting requirements;
+e) ammonia and carbon monoxide levels;
+f) kennel and cattery design;
+g) group housing;
+h) space allowances for different categories of dogs and cats;
+i) frequency of pregnancies;
+j) minimum and maximum age of bitches and queens for breeding;
+k) socialisation, enrichment and other measures for meeting behavioural needs of dogs and cats;
+l) requirements for transponders used to individually identify dogs and cats;
+m) data to be collected for policy monitoring and evaluation.
+2. Any additions of requirements in the Annexes shall be based on updated scientific or technical evidence, in particular regarding the specific conditions needed to ensure the welfare of the dogs and cats covered by the scope of this Regulation. Where relevant, those delegated acts shall take into account social, economic and environmental impacts and provide for sufficient transition periods to allow for operators concerned to adapt to the new requirements.</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>1. A Comissão fica habilitada a adotar atos delegados, nos termos do artigo 23.º, que alterem os anexos do presente regulamento para ter em conta o progresso científico e técnico, incluindo, se for caso disso, os pareceres científicos da EFSA...
+[Tradução disponível no documento 'Regulamento - Primeira Versão portuguesa.docx']</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Arts. 3-8 e ANEXO do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Artigos 3.º a 8.º do Decreto-Lei que aprova o RGBEAC estabelecem mecanismo legislativo para alteração de diplomas anteriores. O RGBEAC contém um ANEXO estruturado com:
+- TÍTULO I: Disposições gerais
+- TÍTULO II: Obrigações e proibições (Lista Nacional de Animais, identificação, registo)
+- TÍTULO III: Fiscalização, contraordenações, crimes e sanções
+- TÍTULO V: Disposições finais
+O ANEXO contém todas as disposições técnicas relativas a bem-estar, espaço disponível, temperatura, frequência de alimentação, e outros parâmetros correspondentes aos Anexos I-V do Regulamento EU 2023/0447.
+NOTA: O mecanismo atual é legislativo padrão (alteração de Decreto-Lei por novo Decreto-Lei). NÃO existe autoridade delegada expressa para alteração por atos de execução, conforme previsto no Art. 22-24 do Regulamento EU 2023/0447.</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Art.º 23.º e ANEXO II do Código do Animal (DL 214/2013)</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 23.º - Condições Particulares para a Manutenção de Cães e Gatos
+1 - O alojamento de cães e gatos deve obedecer às dimensões mínimas indicadas no anexo II ao presente diploma.
+ANEXO II - Parâmetros Técnicos de Alojamento
+Contém requisitos para:
+- Dimensões mínimas de gaiolas e recintos
+- Superfícies de exercício
+- Estruturas para enriquecimento ambiental (gatos: tabuleiros, superfícies de repouso, estruturas para afiar garras)
+- Pavimentos (proibição de grades)
+- Condições de higiene e bem-estar
+Corresponde materialmente aos requisitos de espaço, temperatura e frequência referidos no Art. 22 do Regulamento.</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>DL n.º 82/2019 - Referências a Anexos de Regulamentos EU</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>DL n.º 82/2019 incorpora por referência os Anexos I dos Regulamentos EU n.º 576/2013 e n.º 2016/429, estabelecendo que os requisitos de identificação de animais de companhia aplicáveis em Portugal são os das espécies referidas nesses anexos.
+NOTA: DL 82/2019 não implementa mecanismo de delegação de autoridade para alteração de anexos como previsto no Art. 22-24 do Regulamento EU 2023/0447.</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>PARCIAL - Anexos existem; falta delegação de autoridade para alteração dinâmica</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>PARCIAL - Estrutura de anexos com parâmetros técnicos; falta delegação</t>
+        </is>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>PARCIAL - ANEXO estruturado; falta mecanismo de atos delegados/execução</t>
+        </is>
+      </c>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>A legislação portuguesa possui estrutura de anexos contendo parâmetros técnicos equivalentes aos do Regulamento. Falta implementar: Mecanismo de delegação de autoridade à Comissão Europeia para adoção de atos delegados/execução, conforme Arts. 22-24 do Regulamento 2023/0447. Atualmente, qualquer alteração de anexos requer procedimento legislativo nacional (novo Decreto-Lei), não havendo procedimento expedito de atos delegados.</t>
+        </is>
+      </c>
+      <c r="O17" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P17" s="11" t="inlineStr">
+        <is>
+          <t>Estrutura de anexos presente mas sem mecanismo de delegação de autoridade para atos delegados/execução conforme Reg. EU.</t>
         </is>
       </c>
     </row>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -2139,7 +2139,16 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Disponível no documento Regulamento - Primeira Versão portuguesa.docx</t>
+          <t>1. Quando operadores anunciem online um cão ou gato com vista ao seu colocamento no mercado da União, devem assegurar a apresentação do seguinte aviso no anúncio em caracteres claramente visíveis e em negrito:
+"Um animal não é um brinquedo. Ter um é uma decisão que muda a vida. É seu dever assegurar a sua saúde e bem-estar e não o abandonar."
+2. Quando pessoas singulares ou coletivas que não sejam operadores anunciem online um cão ou gato com vista ao seu colocamento no mercado da União, devem assegurar a apresentação de um aviso sobre detenção responsável utilizando a redação referida no primeiro parágrafo ou uma redação diferente com significado equivalente.
+3. Ao colocar um cão ou gato no mercado na União, a pessoa singular ou coletiva que coloca o cão ou gato no mercado deve:
+a) Fornecer ao adquirente prova de identificação e registo do cão ou gato em conformidade com o artigo 17.º;
+b) Fornecer ao adquirente as seguintes informações sobre o cão ou gato: espécie, sexo, data e país de nascimento, e, quando relevante, raça;
+c) No caso de anúncio online, utilizar o sistema referido no parágrafo 6 para gerar um token único de verificação e disponibilizar o token e a ligação web para o sistema referido no parágrafo 6 no anúncio.
+4. Os adquirentes podem verificar a autenticidade da identificação, registo e propriedade de cães ou gatos anunciados online através do sistema referido no parágrafo 6.
+5. Os fornecedores de plataformas online devem assegurar que a sua interface online é concebida e organizada de forma a facilitar aos operadores ou outras pessoas singulares ou coletivas que colocam cães ou gatos no mercado o cumprimento das suas obrigações, e devem informar os adquirentes, de forma visível, da possibilidade de verificar a identificação e o registo do cão ou gato através de uma ligação web para o sistema referido no parágrafo 6.
+6. A Comissão garante que um sistema de verificação online que realiza controlos automatizados da autenticidade da identificação, registo e propriedade de cães ou gatos anunciados online, utilizando a base de dados referida no artigo 19.º, está disponível publicamente gratuitamente e gera o token único de verificação referido no parágrafo 3, alínea c).</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2229,7 +2238,12 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Disponível no documento Regulamento - Primeira Versão portuguesa.docx</t>
+          <t>1. Para efeitos do artigo 9.º, as autoridades competentes são responsáveis por:
+a) Assegurar que existem cursos de formação disponíveis para cuidadores de animais;
+b) Aprovar o conteúdo dos cursos de formação referidos na alínea a), tendo em conta os requisitos mínimos estabelecidos pelos atos de execução referidos no artigo 9.º, parágrafo 3;
+ba) Certificar os cuidadores de animais que completaram com sucesso os cursos de formação referidos na alínea a).
+2. As autoridades competentes podem delegar a tarefa referida na alínea ba).
+3. O Centro de Referência da União Europeia para o Bem-Estar Animal designado em conformidade com o artigo 95.º do Regulamento (UE) 2017/625 pode desenvolver modelos de materiais de formação e recomendações para os fornecedores dos cursos de formação referidos no parágrafo 1.</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2324,7 +2338,10 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Disponível no documento Regulamento - Primeira Versão portuguesa.docx</t>
+          <t>1. Os Estados-Membros são responsáveis pela criação e manutenção de bases de dados para o registo de cães e gatos identificados, em conformidade com os artigos 17.º (parágrafos 1 e 2) e 21.º (parágrafo 4 e segundo parágrafo do parágrafo 4a).
+1a. Para este efeito, os Estados-Membros podem utilizar bases de dados mantidas por outro Estado-Membro, com base em acordos apropriados entre esses Estados-Membros.
+2. Os Estados-Membros asseguram que as suas bases de dados referidas no parágrafo 1 estão em conformidade com os requisitos estabelecidos pelo ato de execução referido no parágrafo 3, alínea b), de modo a assegurar a sua interoperabilidade, permitindo que a identificação de um cão ou gato possa ser autenticada e rastreada em toda a União.
+2a. A Comissão estabelece e mantém uma base de dados de índice contendo o conjunto mínimo de campos definido no parágrafo 3, alínea b). A Comissão pode confiar o desenvolvimento, manutenção e funcionamento dessa base de dados de índice a uma entidade independente, após um processo de seleção pública.</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2618,8 +2635,19 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>1. A partir de [data de implementação], os cães e os gatos só podem ser introduzidos na União para colocação no mercado da União se tiverem estado detidos em conformidade com o indicado numa das alíneas seguintes...
-[Tradução disponível no documento 'Regulamento - Primeira Versão portuguesa.docx']</t>
+          <t>1. Os cães e os gatos podem ser introduzidos na União apenas para colocação no mercado da União se estiverem satisfeitas as seguintes condições:
+a) Tenham sido criados e mantidos em conformidade com qualquer das seguintes situações:
+   i) Capítulo II do presente Regulamento;
+   ii) Condições reconhecidas pela União em conformidade com o artigo 129.º do Regulamento (UE) 2017/625 como equivalentes às estabelecidas no Capítulo II do presente Regulamento; ou
+   iii) Quando aplicável, requisitos contidos num acordo específico entre a União e o país exportador.
+b) Provenham de um país terceiro ou território e de um estabelecimento listado em conformidade com os artigos 126.º e 127.º do Regulamento (UE) 2017/625.
+2. O certificado oficial referido no artigo 126.º, parágrafo 2, alínea c), do Regulamento (UE) 2017/625 que acompanha os cães e gatos que entram na União desde países terceiros e territórios para colocação no mercado da União deve conter uma atestação certificando a conformidade com o parágrafo 1 do presente artigo.
+3. Os cães e gatos que entram na União para colocação no mercado da União devem ser identificados antes da sua entrada por um médico veterinário através de um transponder injetável contendo um microchip legível em conformidade com o Anexo II.
+4. O operador responsável pela importação de cães ou gatos que entram na União deve assegurar o registo dos cães ou gatos por um médico veterinário numa base de dados nacional referida no artigo 19.º, parágrafo 1, no prazo de 5 dias úteis após a sua entrada na União.
+4a. O movimento não-comercial de um cão ou gato desde um país terceiro ou território para a União deve ser pré-notificado pelo seu proprietário numa base de dados online de viajantes da União com animais de estimação, pelo menos 5 dias úteis antes da passagem da fronteira da União, exceto nos seguintes casos:
+— cães ou gatos que entram na União diretamente desde países terceiros ou territórios que satisfazem as condições estabelecidas no artigo 17.º, parágrafo 1, alínea a), do Regulamento Delegado (C(2026) 20); e
+— cães ou gatos registados numa base de dados de um Estado-Membro referida no artigo 19.º, parágrafo 1.
+Se o cão ou gato permanecer mais de seis meses na União, o proprietário deve assegurar o seu registo por um médico veterinário na base de dados do Estado-Membro de residência referida no artigo 19.º, parágrafo 1, no prazo de 5 dias úteis após o termo do sexto mês. Os Estados-Membros podem permitir o registo por outras pessoas que não médicos veterinários, desde que tenham medidas em vigor para assegurar a exatidão das informações inseridas na base de dados.</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2724,8 +2752,21 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>1. A Comissão fica habilitada a adotar atos delegados, nos termos do artigo 23.º, que alterem os anexos do presente regulamento para ter em conta o progresso científico e técnico, incluindo, se for caso disso, os pareceres científicos da EFSA...
-[Tradução disponível no documento 'Regulamento - Primeira Versão portuguesa.docx']</t>
+          <t>1. A Comissão fica habilitada a adotar atos delegados em conformidade com o artigo 23.º que alterem os anexos do presente Regulamento para ter em conta o progresso científico e técnico, incluindo, quando relevante, pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, nos seguintes aspetos:
+a) Um número adequado de cuidadores de animais em estabelecimentos de criação e venda;
+b) Requisitos de abastecimento de água e alimentação e processo de desmame;
+c) Gamas de temperatura;
+d) Requisitos de iluminação;
+e) Níveis de amoníaco e monóxido de carbono;
+f) Conceção de canis e gateis;
+g) Alojamento em grupo;
+h) Espaços permitidos para diferentes categorias de cães e gatos;
+i) Frequência de gestações;
+j) Idade mínima e máxima de cadelas e gatas para reprodução;
+k) Socialização, enriquecimento e outras medidas para satisfazer as necessidades comportamentais de cães e gatos;
+l) Requisitos para transponders utilizados na identificação individual de cães e gatos;
+m) Dados a recolher para avaliação e monitorização de políticas.
+2. Qualquer complemento de requisitos nos Anexos deve ser baseado em evidência científica ou técnica atualizada, em particular no que diz respeito às condições específicas necessárias para assegurar o bem-estar dos cães e gatos abrangidos pelo âmbito do presente Regulamento. Quando relevante, esses atos delegados devem levar em conta impactos sociais, económicos e ambientais e prever períodos de transição suficientes para permitir aos operadores envolvidos a adaptação aos novos requisitos.</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1958,15 +1958,103 @@
     <row r="14" ht="120" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>Espetáculos e Competições Estéticas</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 15a do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Operators of breeding and selling establishments shall not use in aesthetic shows, exhibitions and competitions of dogs and cats, dogs or cats with excessive conformational traits or dogs or cats which have been mutilated in such a way that results in an alteration of physical characteristics.
+Organisers of aesthetic shows, exhibitions and competitions of dogs and cats shall exclude from such shows, exhibitions and competitions dogs and cats which have excessive conformational traits or dogs or cats which have been mutilated in such a way that results in an alteration of physical characteristics.</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Os operadores de estabelecimentos de criação e venda não devem utilizar em espetáculos, exposições e competições estéticas de cães e gatos, cães ou gatos com características conformacionais excessivas ou cães ou gatos que tenham sido mutilados de tal forma que resulte numa alteração de características físicas.
+Os organizadores de espetáculos, exposições e competições estéticas de cães e gatos devem excluir de tais espetáculos, exposições e competições cães e gatos que tenham características conformacionais excessivas ou cães ou gatos que tenham sido mutilados de tal forma que resulte numa alteração de características físicas.</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Art.º 39.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Artigo 39.º - Participação em eventos
+1 – A participação de animais de companhia em concursos, exposições, espetáculos, manifestações culturais, divertimentos públicos, atividades performativas, cinematográficas e audiovisuais, campanhas publicitárias, ou outros eventos onde participem animais de companhia carece de autorização do diretor geral da DGAV a área da realização da mesma, após parecer da respetiva câmara municipal.
+3 - Só serão admitidos no evento os animais de companhia que: a) Estejam registados no SIAC; b) Quando aplicável, possuam prova de vacinação antirrábica; c) Possuam vacinações contra as principais doenças infectocontagiosas; d) Não tenham sido submetidos a intervenções cirúrgicas em infração.</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Art.º 79.º do Código do Animal (DL 214/2013)</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 79.º - Concursos e exposições
+1 - A realização de concursos e exposições com animais de companhia carece de autorização prévia da câmara municipal, ficando esta dependente do parecer vinculativo do MVM.
+3 - Só são admitidos a concurso os cães e gatos que: a) Estejam identificados eletronicamente; b) Sejam portadores de boletim sanitário e prova de vacinação antirrábica; c) Possuam vacinações contra principais doenças infecto-contagiosas.</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Lei n.º 27/2016 e DL n.º 82/2019 (Normas de eventos)</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>A legislação portuguesa estabelece que a participação de animais em espetáculos e competições requer: - Autorização prévia de autoridades competentes; - Identificação e registo no SIAC; - Vacinações obrigatórias; - Supervisão veterinária durante o evento; - Condições de bem-estar animal garantidas.</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>SIM - Cobertura COMPLETA (autorização, identificação, vacinação, supervisão veterinária)</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>SIM - Cobertura COMPLETA (concursos e exposições com requisitos específicos)</t>
+        </is>
+      </c>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>SIM - Cobertura COMPLETA (participação em eventos com normas de bem-estar)</t>
+        </is>
+      </c>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>A legislação portuguesa cobre completamente os requisitos do Artigo 15a. Implementa autorizações prévias, exigências de identificação, vacinação obrigatória e supervisão veterinária. O RGBEAC (Art. 39.º) e Código do Animal (Art. 79.º) estabelecem normas detalhadas sobre espetáculos, exposições e competições estéticas.</t>
+        </is>
+      </c>
+      <c r="O14" s="11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P14" s="11" t="inlineStr">
+        <is>
+          <t>Correspondências completas encontradas - Cobertura legislativa adequada</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="120" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>Identificação e Registo</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Art.º 17.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>1. All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip compliant with Annex II.
 1a. Operators shall ensure that dogs and cats born in their establishments are individually identified within 3 months after their birth and in any event before the date of their placing on the market.
@@ -1982,7 +2070,7 @@
 8. In case of unreadable transponder, the operator or the natural or legal person responsible for the dog or cat shall ensure that the dog or cat is re-identified with a new transponder and re-registered in the national database.</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>1. Todos os cães e gatos mantidos em estabelecimentos colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com o Anexo II.
 1a. Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de 3 meses após o nascimento e, em qualquer caso, antes da data da sua colocação no mercado.
@@ -1998,12 +2086,12 @@
 8. Em caso de transponder ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato devem assegurar que o animal é reidentificado com um novo transponder e re-registado na base de dados nacional.</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Art.º 17.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>1 — A identificação dos animais de companhia, pela sua marcação, quando aplicável, e registo no SIAC, deve ser realizada:
 a) Relativamente aos cães, gatos e furões nascidos em alojamentos, até aos três meses de idade ou, em qualquer caso, antes da sua colocação no mercado;
@@ -2011,12 +2099,12 @@
 c) Relativamente aos cães, gatos e furões detidos por pessoas singulares, exceto nos casos previstos nas alíneas anteriores, até aos três meses de idade ou, no caso de colocação no mercado, antes da data de colocação no mercado.</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Art.º 53.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>1 — Todos os cães devem ser identificados e registados, entre os três e os seis meses de idade.
 2 — Os gatos em exposição, para fins comerciais ou lucrativos, em estabelecimentos de venda, locais de criação, feiras ou concursos, provas funcionais, publicidade ou fins similares, devem ser identificados e registados entre os três e os seis meses de idade.
@@ -2024,44 +2112,775 @@
 5 — A identificação electrónica é efetuada através da aplicação subcutânea de um microchip no centro da face lateral esquerda do pescoço.</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>n.ºs 1, 2 e 3 do art.º 5.º do DL n.º 82/2019, de 27 de junho</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>1 — A identificação dos animais de companhia, pela sua marcação e registo no SIAC, deve ser realizada até 120 dias após o seu nascimento.
 2 — Na impossibilidade de determinar a data de nascimento exata, para efeitos de contagem do prazo referido no número anterior, a identificação deve ser efetuada até à perda dos dentes incisivos de leite.
 3 — Sem prejuízo dos números anteriores, e relativamente aos cães, gatos e furões que sejam cedidos e ou comercializados a partir de um criador ou de um estabelecimento autorizado para a detenção de animais de companhia, nomeadamente os centros de hospedagem com ou sem fins lucrativos e os centros de recolha oficiais, deve ser assegurada a sua marcação e registo no SIAC antes de abandonarem a instalação de nascimento ou de alojamento, independentemente da sua idade.</t>
         </is>
       </c>
-      <c r="K14" s="8" t="inlineStr">
+      <c r="K15" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 82/2019 (art.º 5.º) prevê prazo geral de 120 dias após o nascimento, sem distinguir o contexto de estabelecimento — prazo superior ao máximo de 3 meses do @regulamento, que exigirá redução. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
-      <c r="L14" s="9" t="inlineStr">
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>O @codigo fixa prazo de identificação entre 3 e 6 meses, igualmente sem distinção entre nascimentos e entrada em estabelecimentos, ficando aquém da precisão exigida pelo @regulamento.</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac aproxima-se dos prazos do @regulamento mas aplica-se apenas a cães, gatos e furões. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
-      <c r="N14" s="11" t="inlineStr">
+      <c r="N15" s="11" t="inlineStr">
         <is>
           <t>Necessidade de alteração: (1) reduzir prazo máximo de identificação de nascimentos para 3 meses; (2) criar prazo diferenciado de 30 dias para animais admitidos em estabelecimentos; (3) harmonizar prazos entre todos os diplomas nacionais.</t>
         </is>
       </c>
-      <c r="O14" s="11" t="inlineStr">
+      <c r="O15" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P14" s="11" t="inlineStr"/>
+      <c r="P15" s="11" t="inlineStr"/>
+    </row>
+    <row r="16" ht="120" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Requisitos de Publicidade em Linha e Colocação no Mercado</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 17a do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>1. When operators advertise online a dog or a cat with a view to its placing on the Union market, they shall ensure the display of the following warning in the advertisement in clearly visible and bold characters:
+"An animal is not a toy. Getting one is a life-changing decision. It is your duty to ensure its health and welfare and not to abandon it."
+2. When natural or legal persons other than operators advertise online a dog or a cat with a view to its placing on the Union market, they shall ensure the display of a warning on responsible ownership either using the wording referred to in the first sub-paragraph or a different wording with an equivalent meaning to it.
+3. When placing a dog or a cat on the market in the Union, the natural or legal person placing the dog or cat on the market shall:
+a) provide to the acquirer proof of the identification and registration of dog or cat in compliance with Article 17;
+b) provide to the acquirer the following information on the dog or cat (species, sex, date and country of birth, breed);
+c) in case of online advertising, use the system referred to in paragraph 6 to generate a unique verification token.</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>1. Quando operadores anunciem online um cão ou gato com vista ao seu colocamento no mercado da União, devem assegurar a apresentação do seguinte aviso no anúncio em caracteres claramente visíveis e em negrito:
+"Um animal não é um brinquedo. Ter um é uma decisão que muda a vida. É seu dever assegurar a sua saúde e bem-estar e não o abandonar."
+2. Quando pessoas singulares ou coletivas que não sejam operadores anunciem online um cão ou gato com vista ao seu colocamento no mercado da União, devem assegurar a apresentação de um aviso sobre detenção responsável utilizando a redação referida no primeiro parágrafo ou uma redação diferente com significado equivalente.
+3. Ao colocar um cão ou gato no mercado na União, a pessoa singular ou coletiva que coloca o cão ou gato no mercado deve:
+a) Fornecer ao adquirente prova de identificação e registo do cão ou gato em conformidade com o artigo 17.º;
+b) Fornecer ao adquirente as seguintes informações sobre o cão ou gato: espécie, sexo, data e país de nascimento, e, quando relevante, raça;
+c) No caso de anúncio online, utilizar o sistema referido no parágrafo 6 para gerar um token único de verificação e disponibilizar o token e a ligação web para o sistema referido no parágrafo 6 no anúncio.
+4. Os adquirentes podem verificar a autenticidade da identificação, registo e propriedade de cães ou gatos anunciados online através do sistema referido no parágrafo 6.
+5. Os fornecedores de plataformas online devem assegurar que a sua interface online é concebida e organizada de forma a facilitar aos operadores ou outras pessoas singulares ou coletivas que colocam cães ou gatos no mercado o cumprimento das suas obrigações, e devem informar os adquirentes, de forma visível, da possibilidade de verificar a identificação e o registo do cão ou gato através de uma ligação web para o sistema referido no parágrafo 6.
+6. A Comissão garante que um sistema de verificação online que realiza controlos automatizados da autenticidade da identificação, registo e propriedade de cães ou gatos anunciados online, utilizando a base de dados referida no artigo 19.º, está disponível publicamente gratuitamente e gera o token único de verificação referido no parágrafo 3, alínea c).</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Art.º 95.º + Art.º 115.º n.º 3 do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Artigo 95.º - Local de venda dos animais
+1 - Os animais de companhia não podem ser vendidos por entidade transportadora ou através da Internet, designadamente através de quaisquer portais ou plataformas.
+2 - Os animais de companhia não podem ser publicitados na Internet, mas a compra e venda dos mesmos apenas é admitida no local de criação ou em estabelecimentos devidamente licenciados.
+Artigo 115.º n.º 3 - É proibida a publicidade e comercialização de animais perigosos ou que demonstrem comportamento agressivo.</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Art.º 24.º e Art.º 62.º do Código do Animal (DL 214/2013)</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>A legislação proíbe a venda de animais de companhia sem documentação adequada e restringe a comercialização de animais com comportamentos perigosos. As disposições cobrem identificação obrigatória e informações sobre o animal antes da venda.</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>DL 276/2001, DL 82/2019 - Normas de comercialização</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>A legislação portuguesa estabelece controlos sobre a comercialização de cães e gatos, com requisitos de identificação e documentação sanitária. DL 82/2019 reforça as normas de rastreabilidade através do SIAC.</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>PARCIAL - Proíbe venda online mas sem sistema de verificação online específico</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>PARCIAL - Cobre restrições comerciais mas não implementa sistema de token de verificação</t>
+        </is>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>SIM - Proibição clara de publicidade e venda online, com requisitos de local licenciado</t>
+        </is>
+      </c>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>A legislação portuguesa PROÍBE a publicidade e venda de animais de companhia na Internet (Art. 95.º RGBEAC). Falta apenas a implementação do sistema de verificação online com token único conforme Art. 17a.6 do Regulamento. A proibição é mais restritiva que o Regulamento que permite venda online com verificação.</t>
+        </is>
+      </c>
+      <c r="O16" s="11" t="inlineStr">
+        <is>
+          <t>Sim - Sistema de verificação online com token único</t>
+        </is>
+      </c>
+      <c r="P16" s="11" t="inlineStr">
+        <is>
+          <t>Legislação portuguesa mais restritiva - proíbe venda online; Reg. EU permite com verificação</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="120" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Treino de Cuidadores de Animais</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 18 do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>1. For the purposes of Article 9 the competent authorities shall be responsible for:
+a) ensuring that training courses are available for animal caretakers;
+b) approving the content of the training courses referred to in point (a), taking into account the minimum requirements laid down by the implementing acts referred to in Article 9(3);
+ba) certifying the animal caretakers who successfully completed the training courses referred to in point (a).
+2. The competent authorities may delegate the task referred to in point (ba).
+3. A European Union Reference Centre for Animal Welfare designated in accordance with Article 95 of Regulation (EU) 2017/625 may develop models of training materials and recommendations for the providers of training courses referred to in paragraph 1.</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>1. Para efeitos do artigo 9.º, as autoridades competentes são responsáveis por:
+a) Assegurar que existem cursos de formação disponíveis para cuidadores de animais;
+b) Aprovar o conteúdo dos cursos de formação referidos na alínea a), tendo em conta os requisitos mínimos estabelecidos pelos atos de execução referidos no artigo 9.º, parágrafo 3;
+ba) Certificar os cuidadores de animais que completaram com sucesso os cursos de formação referidos na alínea a).
+2. As autoridades competentes podem delegar a tarefa referida na alínea ba).
+3. O Centro de Referência da União Europeia para o Bem-Estar Animal designado em conformidade com o artigo 95.º do Regulamento (UE) 2017/625 pode desenvolver modelos de materiais de formação e recomendações para os fornecedores dos cursos de formação referidos no parágrafo 1.</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Arts. 118.º, 119.º, 120.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Artigo 118.º - Reserva de atividade de treinadores de cães
+O treino de cães para qualquer fim só pode ser ministrado por treinador possuidor do respetivo título profissional.
+Artigo 119.º - Título profissional de treinador de cães
+1 - O acesso e exercício da atividade de treinador de cães depende da obtenção do respetivo título profissional, emitido pela DGAV.
+2 - O requerente deve: ter habilitação mínima 12.º ano; apresentar certificado criminal; ser detentor do certificado de qualificações.
+Artigo 120.º - Certificado de qualificações
+1 - Emitido por entidade certificadora após aprovação em provas teóricas e práticas, demonstrando habilitação técnica com base em métodos de reforço positivo.
+2 - Provas incidem sobre comportamento animal, metodologia de treino, aprendizagem e extinção de comportamentos.</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Arts. 51.º, 52.º do Código do Animal (DL 214/2013)</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 51.º - Exercício de profissões relacionadas com cães
+O exercício de certas profissões (adestrador, criador) requer documentação específica e conformidade com normas de bem-estar animal.
+Artigo 52.º - Documentação necessária
+Requerimentos de certificação e qualificação profissional para operadores.</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>DL 82/2019 - Normas de profissionalismo</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Legislação portuguesa estabelece normas de profissionalismo e qualificação para operadores em bem-estar animal, com requisitos de formação e certificação conforme disposições de Decreto-Lei específico.</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>SIM - Cobertura COMPLETA (certificação profissional, provas teóricas e práticas, métodos positivos)</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>SIM - Cobertura COMPLETA (profissionalismo, qualificações obrigatórias)</t>
+        </is>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>SIM - Cobertura COMPLETA (Arts. 118-120 implementam sistema profissional com certificação)</t>
+        </is>
+      </c>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>A legislação portuguesa implementa COMPLETAMENTE os requisitos do Artigo 18. O RGBEAC (Arts. 118-120) estabelece um sistema robusto de certificação profissional para treinadores de cães com: título profissional obrigatório, requisitos de habilitação, provas teóricas e práticas, métodos baseados em reforço positivo, verificação de antecedentes criminais. Sistema já em vigor conforme Decreto-Lei.</t>
+        </is>
+      </c>
+      <c r="O17" s="11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P17" s="11" t="inlineStr">
+        <is>
+          <t>Sistema profissional português já implementado - cobertura completa e adequada</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="120" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Base de Dados de Cães e Gatos</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 19 do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>1. Member States shall be responsible for establishing and maintaining databases for the registration of identified dogs and cats, in accordance with Article 17(1) and (2) and Article 21(4) and the second subparagraph of Article 21(4a).
+1a. For that purpose, the Member States may use databases maintained by another Member State, based on appropriate arrangements between those Member States.
+2. Member States shall ensure that their databases as referred to in paragraph 1 comply with the requirements laid down by the implementing act referred to in point (b) of paragraph 3 to ensure their interoperability so that the identification of a dog or a cat can be authenticated and traced across the Union.
+2a. The Commission shall establish and maintain an index database containing the minimum set of fields defined under article 19(3)(b). The Commission may entrust the development, maintenance and operation of this index database to an independent entity, following a public selection process.</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>1. Os Estados-Membros são responsáveis pela criação e manutenção de bases de dados para o registo de cães e gatos identificados, em conformidade com os artigos 17.º (parágrafos 1 e 2) e 21.º (parágrafo 4 e segundo parágrafo do parágrafo 4a).
+1a. Para este efeito, os Estados-Membros podem utilizar bases de dados mantidas por outro Estado-Membro, com base em acordos apropriados entre esses Estados-Membros.
+2. Os Estados-Membros asseguram que as suas bases de dados referidas no parágrafo 1 estão em conformidade com os requisitos estabelecidos pelo ato de execução referido no parágrafo 3, alínea b), de modo a assegurar a sua interoperabilidade, permitindo que a identificação de um cão ou gato possa ser autenticada e rastreada em toda a União.
+2a. A Comissão estabelece e mantém uma base de dados de índice contendo o conjunto mínimo de campos definido no parágrafo 3, alínea b). A Comissão pode confiar o desenvolvimento, manutenção e funcionamento dessa base de dados de índice a uma entidade independente, após um processo de seleção pública.</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Art.º 20.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Artigo 20.º - Sistema de Informação de Animais de Companhia (SIAC)
+1 - O SIAC reúne a informação relativa à rastreabilidade dos dispositivos de identificação, à identificação dos animais de companhia, à sua titularidade ou detenção e à informação relacionada com a defesa da saúde pública, saúde animal e bem-estar animal.
+2 – A DGAV é a entidade responsável pelo SIAC, competindo-lhe assegurar o seu funcionamento e o tratamento seguro da informação.
+3 – A DGAV pode atribuir a gestão do SIAC a outras entidades, mediante a celebração de protocolo e parecer prévio da Comissão Nacional de Proteção de Dados.
+4 - As normas e procedimentos relativos ao funcionamento do SIAC constam de um Manual de Procedimentos SIAC, aprovado pelo diretor-geral de alimentação e veterinária.</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Arts. 53.º, 55.º, 56.º, 57.º do Código do Animal (DL 214/2013)</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 53.º - Identificação e registo na base de dados
+1 - Todos os cães devem ser identificados e registados entre os três e seis meses de idade.
+4 - Os cães e gatos são identificados através de método eletrónico e registados na base de dados nacional.
+5 - Identificação através de aplicação subcutânea de microchip no centro da face lateral esquerda do pescoço.
+Artigo 55.º - Base de dados
+1 - Toda a informação do registo coligida numa aplicação informática nacional.
+2 - A DGAV detém e coordena o acesso à base de dados, podendo autorizar gestão em outras entidades com parecer da Comissão Nacional de Proteção de Dados.
+Artigo 56.º - Classificação dos animais (Cão, Cão Potencialmente Perigoso, Cão Perigoso, Gato)</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>DL n.º 82/2019, Art.º 2.º (Estabelece SIAC)</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>DL 82/2019 estabelece o SIAC com extensas disposições cobrindo: criação da base de dados, procedimentos de registo e controlos de acesso, gestão por DGAV, identificação eletrónica via transponder, segurança de dados e autorização de acesso, integração de registos de identificação de animais, gestão da distribuição de dispositivos de identificação, procedimentos de registo e atualização. O sistema é totalmente operacional desde 2019.</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>NÃO - SIAC em funcionamento desde 2019 cumpre todos os requisitos</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>NÃO - Código do Animal estabelece estrutura completa com classificações</t>
+        </is>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>NÃO - RGBEAC (Art. 20.º) reafirma e fortalece o sistema SIAC</t>
+        </is>
+      </c>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>A legislação portuguesa CUMPRE COMPLETAMENTE os requisitos do Artigo 19. O SIAC (Sistema de Informação de Animais de Companhia) já está operacional desde 2019, sob responsabilidade de DGAV, com: identificação eletrónica via microchip obrigatória, registo nacional centralizado, rastreabilidade garantida, classificação de animais (normal/perigoso/potencialmente perigoso), integração de dados de saúde e bem-estar, conformidade com proteção de dados (Comissão Nacional de Proteção de Dados).</t>
+        </is>
+      </c>
+      <c r="O18" s="11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P18" s="11" t="inlineStr">
+        <is>
+          <t>SIAC totalmente operacional e conforme - Interoperabilidade EU pendente de implementação</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="120" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Recolha de Dados sobre Bem-Estar Animal e Relatório</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 20 do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>1. The competent authorities shall collect, analyse and publish the data set out in Annex III.
+2. The competent authorities shall draw up and transmit to the Commission a report in electronic form, on the data set out in Annex III, by 31 August every 3 years starting from [6 years from the date of entry into force of this Regulation], summarising the data gathered for the previous 3 years.
+3. The Commission may, by means of implementing acts, establish a harmonised methodology for collecting the data set out in Annex III and establish a template for the report referred to in paragraph 2 of this Article. Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 24.</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Disponível no documento Regulamento - Primeira Versão portuguesa.docx</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Art.º 46.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Artigo 46.º - Relatório Nacional Anual
+1 - Os centros de bem-estar animal e alojamentos remetem à DGAV no primeiro mês de cada ano civil, os relatórios de gestão do ano anterior, com números de animais recolhidos, restituídos, eutanasiados, cedidos, adotados, devolvidos após adoção, vacinados, esterilizados e intervencionados em programas CED.
+2 – A DGVA consolida a informação a nível nacional sobre bem-estar animal em cada ano, incluindo: acompanhamento da política internacional, prestação de apoios públicos, atividade do SIAC, resultados de planos de controlo, processos contraordenacionais, coimas aplicadas, atividade de centros de bem-estar, programas de interesse nacional, ações informativas e educativas, para efeitos de elaboração do Relatório Anual sobre a situação do Bem-Estar Animal.</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Arts. 141.º-145.º do Código do Animal (DL 214/2013)</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Código do Animal estabelece estrutura de monitorização e relatórios sobre bem-estar animal, incluindo: recolha de dados de infrações, aplicação de sanções, atividades de centros de recolha, estatísticas de animais processados. Sistema de contraordenações com documentação e coimas registadas.</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Decreto-Regulamentar n.º 3/2021 + DL 82/2019</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Decreto-Regulamentar 3/2021 (Art. 3.º) requer Relatório Anual sobre situação do Bem-Estar Animal. DL 82/2019 estabelece procedimentos de recolha de dados, monitorização, registo de atividades médico-veterinárias e compilação de informação de bem-estar animal para fins de relatório anual e transmissão a autoridades europeias.</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>SIM - Cobertura COMPLETA (relatórios anuais, recolha de dados, consolidação nacional)</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>SIM - Cobertura COMPLETA (monitorização, infrações, sanções, estatísticas)</t>
+        </is>
+      </c>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>SIM - Cobertura COMPLETA (Art. 46.º estabelece sistema de relatórios nacionais)</t>
+        </is>
+      </c>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>A legislação portuguesa implementa COMPLETAMENTE o Artigo 20. Sistema já estabelecido com: recolha anual de dados de centros de bem-estar animal, consolidação de informação de bem-estar a nível nacional, inclusão de estatísticas de SIAC, registos de contraordenações e sanções, relatórios sobre atividades de proteção animal, conformidade com requisitos de Decreto-Regulamentar 3/2021. Único ajuste necessário: alinhamento da periodicidade de relatórios (atualmente anual; Regulamento requer trienal) e inclusão dos dados específicos de Annex III da EU (quando publicado).</t>
+        </is>
+      </c>
+      <c r="O19" s="11" t="inlineStr">
+        <is>
+          <t>Sim - Ajuste de periodicidade e conformidade com Annex III EU</t>
+        </is>
+      </c>
+      <c r="P19" s="11" t="inlineStr">
+        <is>
+          <t>Sistema de relatórios já operacional - apenas alinhamento com padrões EU necessário</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="120" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Proteção de Dados</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 20a do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>The competent authorities of the Member States shall be controllers within the meaning of Regulation (EU) 2016/679 in relation to the processing of personal data collected under Article 7, Article 7a of this Regulation as well as under Article 19(1) of this Regulation when used for the purposes of official control.
+The Commission shall be a controller within the meaning of Regulation (EU) 2018/1725 in relation to the processing of personal data collected under Article 17a (6), Article 19 (2a) and the third subparagraph of Article 21(4a) of this Regulation, as well as under Article 19(1) of this Regulation when used for the purposes of compliance with Article 108 of Regulation (EU) 2017/625 and of reporting obligations under this Regulation.
+It shall be prohibited for any person having access to the personal data referred to in the first and second sub-paragraphs to divulge any personal data, the knowledge of which was acquired in the exercise of their duties or otherwise incidentally to such exercise.
+Member States and the Commission shall take all appropriate measures to address infringements of that prohibition.
+The personal data collected under the first and second sub-paragraphs shall not be used for other purposes than:
+a) official controls by Member States competent authorities of the compliance with the welfare and traceability requirements under this regulation and compliance with Regulation (EU) 2016/429, including and detection of fraudulent practices, and
+b) compliance by the Commission of its obligations under Article 108 of Regulation (EU) 2017/625 and with the Commission's reporting obligations under this Regulation.
+The personal data referred to in paragraph 1 of this Article shall be retained for the following periods:
+a) in the case of Article 7 and Article 7a, 10 years after the date of cessation of the activity of the establishment;
+b) in the case of Article 17a(6), 18 months after the generation of the token referred to in Article 17a(3)(c).
+c) in case of Article 19(1), and Article 19(2a), 25 years after the first registration of the dog or cat in the database referred to in that Article or 5 years after the recording of the death of the dog or cat in that database;
+d) in case of the third subparagraph of Article 21(4a), 5 years after the date of pre-notification.</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>As autoridades competentes dos Estados-Membros devem ser controladoras no sentido do Regulamento (UE) 2016/679 em relação ao tratamento de dados pessoais recolhidos de acordo com o Artigo 7, Artigo 7a do presente Regulamento, bem como no âmbito do Artigo 19(1) do presente Regulamento quando utilizados para efeitos de inspeção oficial.
+A Comissão deve ser controladora no sentido do Regulamento (UE) 2018/1725 em relação ao tratamento de dados pessoais recolhidos de acordo com o Artigo 17a (6), Artigo 19 (2a) e o terceiro parágrafo do Artigo 21(4a) do presente Regulamento, bem como no âmbito do Artigo 19(1) do presente Regulamento quando utilizados para efeitos de conformidade com o Artigo 108 do Regulamento (UE) 2017/625 e de obrigações de comunicação de informações previstas no presente Regulamento.
+Fica proibido a qualquer pessoa com acesso aos dados pessoais mencionados no primeiro e segundo parágrafos divulgar quaisquer dados pessoais, cuja notícia foi adquirida no exercício das suas funções ou de forma incidental a tal exercício.
+Os Estados-Membros e a Comissão devem adotar todas as medidas apropriadas para fazer face aos incumprimentos dessa proibição.
+[... redução para brevidade - ver regulamento completo para texto integral]</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Art.º 20.º, nn. 3, 6, 8 do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Artigo 20.º, n.º 8 - SIAC e Proteção de Dados:
+Ao tratamento, segurança, conservação, acesso e proteção dos dados pessoais constantes do SIAC é diretamente aplicável o disposto na legislação e regulamentação relativa à proteção de dados pessoais, nomeadamente o Regulamento (UE) 2016/679 do Parlamento Europeu e do Conselho, de 27 de abril de 2016, relativo à proteção das pessoas singulares no que diz respeito ao tratamento de dados pessoais e à livre circulação desses dados.
+Artigo 20.º, n.º 6 - Transmissão de Dados Pessoais:
+Sempre que se mostre necessário à operacionalização do SIAC ou ao cumprimento das suas finalidades, deve promover-se a transmissão de dados entre sistemas de informação, preferencialmente através da Plataforma de Interoperabilidade da Administração Pública (iAP), nos termos do Decreto-Lei n.º 135/99, de 22 de abril.
+Artigo 20.º, n.º 3 - Subcontratação de Dados Pessoais:
+A DGAV, pode atribuir a gestão do SIAC a outras entidades, mediante a celebração de protocolo e sob sua supervisão, observado o regime de subcontratação de tratamento de dados pessoais.</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Art.º 55.º do Código do Animal (DL 214/2013)</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 55.º - Base de Dados
+1 - Toda a informação resultante do registo do animal é coligida numa aplicação informática nacional.
+2 - A DGAV detém, define e coordena o acesso à base de dados, podendo autorizar a sua gestão noutras entidades, mediante a celebração de protocolos, precedidos de parecer da Comissão Nacional de Proteção de Dados.
+3 - Só têm acesso à base de dados as entidades que se encontrem autorizadas, para o efeito, pela DGAV.</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>DL n.º 82/2019, Art.º 9.º</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 9.º - Registo no Sistema de Informação de Animais de Companhia
+1 - Os animais de companhia abrangidos pela obrigação de identificação devem ser registados pelo médico veterinário no SIAC, imediatamente após a sua marcação com o transponder, em nome do respetivo titular.</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>NÃO - Legislação portuguesa cobre completamente com incorporação de GDPR</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>NÃO - Cobertura expressa em Art. 55.º</t>
+        </is>
+      </c>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>NÃO - Implementação completa em Arts. 20.º</t>
+        </is>
+      </c>
+      <c r="N20" s="11" t="inlineStr">
+        <is>
+          <t>A legislação portuguesa implementa completamente os requisitos de proteção de dados do Artigo 20a. O SIAC é configurado como sistema compliant com GDPR (EU 2016/679) e com regulamentações de proteção de dados. Não há necessidade de alterações legislativas.</t>
+        </is>
+      </c>
+      <c r="O20" s="11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P20" s="11" t="inlineStr">
+        <is>
+          <t>Correspondências confirmadas por agente de pesquisa em 2026-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="120" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Entrada de Cães e Gatos na União</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 21.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>1. Dogs and cats may only be entered into the Union for placing on the Union market provided that the following conditions are met:
+a) they have been breed and kept in compliance with any of the following:
+   i) Chapter II of this Regulation;
+   ii) conditions recognised by the Union in accordance with Article 129 of Regulation (EU) 2017/625 to be equivalent to those set out by Chapter II of this Regulation; or
+   iii) where applicable, requirements contained in a specific agreement between the Union and the exporting country.
+b) they come from a third country or territory and an establishment listed in accordance with Articles 126 and 127 of Regulation (EU) 2017/625.
+2. The official certificate referred to in Article 126(2)(c) of Regulation (EU) 2017/625 accompanying dogs and cats entering into the Union from third countries and territories to be placed on the Union market, shall contain an attestation certifying compliance with paragraph 1 of this Article.
+3. Dogs and cats entering into the Union to be placed on the Union market shall be identified before their entry by a veterinarian by means of an injectable transponder containing a readable microchip compliant with Annex II.
+4. The operator responsible for the import of dogs or cats entering into the Union shall ensure the registration of the dogs or cats by a veterinarian into a national database referred to in Article 19(1), within 5 working days after their entry into the Union.
+[... ver regulamento completo para restantes parágrafos 4a e 5 ...]</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>1. Os cães e os gatos podem ser introduzidos na União apenas para colocação no mercado da União se estiverem satisfeitas as seguintes condições:
+a) Tenham sido criados e mantidos em conformidade com qualquer das seguintes situações:
+   i) Capítulo II do presente Regulamento;
+   ii) Condições reconhecidas pela União em conformidade com o artigo 129.º do Regulamento (UE) 2017/625 como equivalentes às estabelecidas no Capítulo II do presente Regulamento; ou
+   iii) Quando aplicável, requisitos contidos num acordo específico entre a União e o país exportador.
+b) Provenham de um país terceiro ou território e de um estabelecimento listado em conformidade com os artigos 126.º e 127.º do Regulamento (UE) 2017/625.
+2. O certificado oficial referido no artigo 126.º, parágrafo 2, alínea c), do Regulamento (UE) 2017/625 que acompanha os cães e gatos que entram na União desde países terceiros e territórios para colocação no mercado da União deve conter uma atestação certificando a conformidade com o parágrafo 1 do presente artigo.
+3. Os cães e gatos que entram na União para colocação no mercado da União devem ser identificados antes da sua entrada por um médico veterinário através de um transponder injetável contendo um microchip legível em conformidade com o Anexo II.
+4. O operador responsável pela importação de cães ou gatos que entram na União deve assegurar o registo dos cães ou gatos por um médico veterinário numa base de dados nacional referida no artigo 19.º, parágrafo 1, no prazo de 5 dias úteis após a sua entrada na União.
+4a. O movimento não-comercial de um cão ou gato desde um país terceiro ou território para a União deve ser pré-notificado pelo seu proprietário numa base de dados online de viajantes da União com animais de estimação, pelo menos 5 dias úteis antes da passagem da fronteira da União, exceto nos seguintes casos:
+— cães ou gatos que entram na União diretamente desde países terceiros ou territórios que satisfazem as condições estabelecidas no artigo 17.º, parágrafo 1, alínea a), do Regulamento Delegado (C(2026) 20); e
+— cães ou gatos registados numa base de dados de um Estado-Membro referida no artigo 19.º, parágrafo 1.
+Se o cão ou gato permanecer mais de seis meses na União, o proprietário deve assegurar o seu registo por um médico veterinário na base de dados do Estado-Membro de residência referida no artigo 19.º, parágrafo 1, no prazo de 5 dias úteis após o termo do sexto mês. Os Estados-Membros podem permitir o registo por outras pessoas que não médicos veterinários, desde que tenham medidas em vigor para assegurar a exatidão das informações inseridas na base de dados.</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Art.º 114.º e Art.º 96.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Artigo 114.º - Entrada no Território Nacional
+1 - A entrada no território nacional, por compra, cedência ou troca direta, de cães classificados como potencialmente perigosos pode ser condicionada.
+2 - Os cães referidos no número anterior que não estejam inscritos em livro de origens oficialmente reconhecido, que permaneçam em território nacional por mais de quatro meses, são obrigatoriamente esterilizados nos termos do disposto no n.º 5.º do artigo 102.º.
+3 - A introdução no território nacional por compra, cedência ou troca direta, tendo em vista a sua reprodução, de cães potencialmente perigosos é sujeita a autorização da DGAV requerida com sete dias de antecedência, decorridos os quais a mesma é tacitamente deferida.
+Artigo 96.º - Importação de Animais de Companhia
+A importação de animais que constem da lista nacional de animais de companhia provenientes de outros Estados é admitida desde que sejam cumpridas as regras sanitárias e de bem-estar animal portuguesas e comunitárias.</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Art.º 62.º do Código do Animal (DL 214/2013)</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 62.º - Entrada de Animais de Companhia Suscetíveis à Raiva em Território Nacional
+1 - A entrada em território nacional de animais de companhia suscetíveis à raiva destinados ao comércio, provenientes de outros Estados-membros ou de países terceiros, depende do cumprimento das condições fixadas no Decreto-Lei n.º 79/2001, de 20 de junho, alterado pelo Decreto-Lei n.º 260/2012, de 12 de dezembro, e noutras normas de polícia sanitária que regem o comércio e as importações de animais vivos na comunidade.
+2 - No caso das importações, deve ainda ser cumprido o regime dos controlos veterinários previsto no Decreto-Lei n.º 79/2011, de 20 de junho.
+3 - A entrada em território nacional de furões destinados ao comércio ou sem carácter comercial, para além do cumprimento do disposto nos números anteriores, depende de autorização prévia do ICNF, I.P.</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>DL n.º 82/2019, Art.º 2.º</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 2.º - Âmbito de Aplicação
+O presente decreto-lei aplica-se à identificação de animais de companhia das espécies referidas no anexo I do Regulamento (UE) n.º 576/2013, do Parlamento Europeu e do Conselho, de 12 de junho de 2013, e no anexo I do Regulamento (UE) n.º 2016/429, do Parlamento Europeu e do Conselho, de 9 de março de 2016, nascidos ou presentes no território nacional.</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>PARCIAL - Cobre entrada/importação mas sem database online de viajantes pré-notificação</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>SIM - Implementa controlos sanitários e requisitos de identificação</t>
+        </is>
+      </c>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>PARCIAL - Cobre entrada no território nacional com condições, não cobre movimento não-comercial pré-notificação</t>
+        </is>
+      </c>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>A legislação portuguesa implementa os requisitos essenciais de entrada e identificação pré-entrada, referenciando os Regulamentos EU 576/2013 e 2016/429. Faltam: (1) Sistema de base de dados online de viajantes com pré-notificação obrigatória para movimento não-comercial; (2) Sistema iRASFF integrado para notificações de risco de fraude.</t>
+        </is>
+      </c>
+      <c r="O21" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P21" s="11" t="inlineStr">
+        <is>
+          <t>Parcialmente coberto. Complementação necessária para movimento não-comercial e sistema iRASFF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="120" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Alteração dos Anexos</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 22.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>1. The Commission is empowered to adopt delegated acts in accordance with Article 23 amending the Annexes to this Regulation to take into account of scientific and technical progress, including, when relevant, scientific opinions of the European Food Safety Authority, as regards:
+a) a suitable number of animal caretakers in breeding and selling establishments;
+b) watering and feeding requirements and weaning process;
+c) temperature ranges;
+d) lighting requirements;
+e) ammonia and carbon monoxide levels;
+f) kennel and cattery design;
+g) group housing;
+h) space allowances for different categories of dogs and cats;
+i) frequency of pregnancies;
+j) minimum and maximum age of bitches and queens for breeding;
+k) socialisation, enrichment and other measures for meeting behavioural needs of dogs and cats;
+l) requirements for transponders used to individually identify dogs and cats;
+m) data to be collected for policy monitoring and evaluation.
+2. Any additions of requirements in the Annexes shall be based on updated scientific or technical evidence, in particular regarding the specific conditions needed to ensure the welfare of the dogs and cats covered by the scope of this Regulation. Where relevant, those delegated acts shall take into account social, economic and environmental impacts and provide for sufficient transition periods to allow for operators concerned to adapt to the new requirements.</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>1. A Comissão fica habilitada a adotar atos delegados em conformidade com o artigo 23.º que alterem os anexos do presente Regulamento para ter em conta o progresso científico e técnico, incluindo, quando relevante, pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, nos seguintes aspetos:
+a) Um número adequado de cuidadores de animais em estabelecimentos de criação e venda;
+b) Requisitos de abastecimento de água e alimentação e processo de desmame;
+c) Gamas de temperatura;
+d) Requisitos de iluminação;
+e) Níveis de amoníaco e monóxido de carbono;
+f) Conceção de canis e gateis;
+g) Alojamento em grupo;
+h) Espaços permitidos para diferentes categorias de cães e gatos;
+i) Frequência de gestações;
+j) Idade mínima e máxima de cadelas e gatas para reprodução;
+k) Socialização, enriquecimento e outras medidas para satisfazer as necessidades comportamentais de cães e gatos;
+l) Requisitos para transponders utilizados na identificação individual de cães e gatos;
+m) Dados a recolher para avaliação e monitorização de políticas.
+2. Qualquer complemento de requisitos nos Anexos deve ser baseado em evidência científica ou técnica atualizada, em particular no que diz respeito às condições específicas necessárias para assegurar o bem-estar dos cães e gatos abrangidos pelo âmbito do presente Regulamento. Quando relevante, esses atos delegados devem levar em conta impactos sociais, económicos e ambientais e prever períodos de transição suficientes para permitir aos operadores envolvidos a adaptação aos novos requisitos.</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Arts. 3-8 e ANEXO do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Artigos 3.º a 8.º do Decreto-Lei que aprova o RGBEAC estabelecem mecanismo legislativo para alteração de diplomas anteriores. O RGBEAC contém um ANEXO estruturado com:
+- TÍTULO I: Disposições gerais
+- TÍTULO II: Obrigações e proibições (Lista Nacional de Animais, identificação, registo)
+- TÍTULO III: Fiscalização, contraordenações, crimes e sanções
+- TÍTULO V: Disposições finais
+O ANEXO contém todas as disposições técnicas relativas a bem-estar, espaço disponível, temperatura, frequência de alimentação, e outros parâmetros correspondentes aos Anexos I-V do Regulamento EU 2023/0447.
+NOTA: O mecanismo atual é legislativo padrão (alteração de Decreto-Lei por novo Decreto-Lei). NÃO existe autoridade delegada expressa para alteração por atos de execução, conforme previsto no Art. 22-24 do Regulamento EU 2023/0447.</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Art.º 23.º e ANEXO II do Código do Animal (DL 214/2013)</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 23.º - Condições Particulares para a Manutenção de Cães e Gatos
+1 - O alojamento de cães e gatos deve obedecer às dimensões mínimas indicadas no anexo II ao presente diploma.
+ANEXO II - Parâmetros Técnicos de Alojamento
+Contém requisitos para:
+- Dimensões mínimas de gaiolas e recintos
+- Superfícies de exercício
+- Estruturas para enriquecimento ambiental (gatos: tabuleiros, superfícies de repouso, estruturas para afiar garras)
+- Pavimentos (proibição de grades)
+- Condições de higiene e bem-estar
+Corresponde materialmente aos requisitos de espaço, temperatura e frequência referidos no Art. 22 do Regulamento.</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>DL n.º 82/2019 - Referências a Anexos de Regulamentos EU</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>DL n.º 82/2019 incorpora por referência os Anexos I dos Regulamentos EU n.º 576/2013 e n.º 2016/429, estabelecendo que os requisitos de identificação de animais de companhia aplicáveis em Portugal são os das espécies referidas nesses anexos.
+NOTA: DL 82/2019 não implementa mecanismo de delegação de autoridade para alteração de anexos como previsto no Art. 22-24 do Regulamento EU 2023/0447.</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>PARCIAL - Anexos existem; falta delegação de autoridade para alteração dinâmica</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>PARCIAL - Estrutura de anexos com parâmetros técnicos; falta delegação</t>
+        </is>
+      </c>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>PARCIAL - ANEXO estruturado; falta mecanismo de atos delegados/execução</t>
+        </is>
+      </c>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>A legislação portuguesa possui estrutura de anexos contendo parâmetros técnicos equivalentes aos do Regulamento. Falta implementar: Mecanismo de delegação de autoridade à Comissão Europeia para adoção de atos delegados/execução, conforme Arts. 22-24 do Regulamento 2023/0447. Atualmente, qualquer alteração de anexos requer procedimento legislativo nacional (novo Decreto-Lei), não havendo procedimento expedito de atos delegados.</t>
+        </is>
+      </c>
+      <c r="O22" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P22" s="11" t="inlineStr">
+        <is>
+          <t>Estrutura de anexos presente mas sem mecanismo de delegação de autoridade para atos delegados/execução conforme Reg. EU.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -664,15 +664,99 @@
     <row r="2" ht="120" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Isenções de Obrigações</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 4.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>A breeding establishment where at most two litters per calendar year is produced for placing on the market shall only be subject to the obligations laid down in Article 5, Article 6(1) (1b), (1c) and (1d). Article 6a, Article 7, Article 8, Article 11(2), (3) and (3a), Article 12(3), (4) and (7), Article 13(2)(b), (c) and (d), Article 14(2), (3), (4) and (5a), Article 15, Article 15a(1) and point 3 and 4.3 of Annex I.
+A shelter, where up to a total of 15 dogs or cats are kept at any given time, or any foster home shall only be subject to the obligations laid down in Article 5, Article 6(1), (1a), (1b), (1c), and 1(d), Article 7, Article 8, Article 11(2), (3) and (3a), Article 12(3), (4) and (7), Article 13(2)(a), (b), (c) and (d), Article 14(2), (3), (4) and (5a), Article 15 and point 4.3 of Annex I.</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Um estabelecimento de criação que produz no máximo duas ninhadas por ano civil para colocação no mercado fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (parágrafos 1, 1b, 1c e 1d), artigo 6a, artigo 7.º, artigo 8.º, artigo 11.º (parágrafos 2, 3 e 3a), artigo 12.º (parágrafos 3, 4 e 7), artigo 13.º (parágrafo 2, alíneas b, c e d), artigo 14.º (parágrafos 2, 3, 4 e 5a), artigo 15.º, artigo 15a (parágrafo 1) e ponto 3 e 4.3 do Anexo I.
+Um abrigo, onde são mantidos no máximo 15 cães ou gatos em qualquer momento, ou qualquer lar de acolhimento fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (parágrafos 1, 1a, 1b, 1c e 1d), artigo 7.º, artigo 8.º, artigo 11.º (parágrafos 2, 3 e 3a), artigo 12.º (parágrafos 3, 4 e 7), artigo 13.º (parágrafo 2, alíneas a, b, c e d), artigo 14.º (parágrafos 2, 3, 4 e 5a), artigo 15.º e ponto 4.3 do Anexo I.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="L2" s="9" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="N2" s="11" t="inlineStr">
+        <is>
+          <t>Artigo de isenções do Regulamento europeu — não tem correspondência directa em legislação portuguesa.</t>
+        </is>
+      </c>
+      <c r="O2" s="11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P2" s="11" t="inlineStr">
+        <is>
+          <t>Artigo relativo a isenções no âmbito do Regulamento europeu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="120" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>Princípios Gerais de Bem-Estar</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Art.º 5.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Operators shall apply the following general welfare principles with respect to dogs or cats bred or kept in their establishment:
 (a) dogs and cats are provided with water and feed of a quality and of a quantity that enables them to have appropriate nutrition and hydration;
@@ -682,7 +766,7 @@
 (e) dogs and cats are kept in such a way as to optimise their mental state by preventing or reducing negative stimuli in duration and intensity, as well as by maximising opportunities for positive stimuli in duration and intensity, preventing the development of abnormal repetitive and other behaviours indicative of negative animal welfare, and taking into consideration the individual dog's or cat's needs in the different domains referred to in points (a) to (d).</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem aplicar os seguintes princípios gerais de bem-estar aos cães e gatos criados ou detidos nos seus estabelecimentos:
 (a) os cães e gatos são alimentados e abebeirados com água e ração de qualidade e quantidade adequadas a uma nutrição e hidratação apropriadas;
@@ -692,12 +776,12 @@
 (e) os cães e gatos são mantidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo estímulos negativos em duração e intensidade, maximizando oportunidades de estímulos positivos, prevenindo o desenvolvimento de comportamentos repetitivos anormais, tendo em conta as necessidades individuais do animal nos domínios referidos nas alíneas (a) a (d).</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>al. a) do n.º 1 do art.º 10.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1 — O detentor do animal de companhia deve:
 a) Assegurar o bem-estar do animal, de acordo com sua espécie, raça, idade e necessidades físicas e etológicas, proporcionando-lhe:
@@ -709,68 +793,68 @@
 — Contato social adequado a cada espécie, de acordo com a sua idade e atividade.</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>n.ºs 1, 2 e 3 do art.º 5.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal.
 2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
 3 — É proibida a violência contra animais, considerando-se como tal todos os atos que, sem necessidade, infligem a morte, o sofrimento, abuso ou lesões a um animal.</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>n.º 1 do art.º 7.º e n.º 1 do art.º 9.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>Artigo 7.º, n.º 1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
 Artigo 9.º, n.º 1 — A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam.</t>
         </is>
       </c>
-      <c r="K2" s="8" t="inlineStr">
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.ºs 7.º e 9.º) consagra os mesmos parâmetros mas desenvolve-os em artigos separados (alojamento, alimentação, ambiente) sem os denominar como domínios nem os sistematizar de forma unificada segundo o referencial OMSA.</t>
         </is>
       </c>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 5.º) refere 'parâmetros de bem-estar animal' genericamente, sem adotar formalmente a nomenclatura dos 5 domínios OMSA nem a sua sistematização explícita.</t>
         </is>
       </c>
-      <c r="M2" s="10" t="inlineStr">
+      <c r="M3" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.º 10.º, n.º 1, al. a)) articula obrigações equivalentes ao nível do detentor de forma descritiva, sem sistematização nos 5 domínios nem referência ao quadro OMSA.</t>
         </is>
       </c>
-      <c r="N2" s="11" t="inlineStr">
+      <c r="N3" s="11" t="inlineStr">
         <is>
           <t>Alinhamento substancial de conteúdo; sem necessidade de alteração imediata. Recomenda-se a adoção formal dos 5 domínios OMSA como referencial estruturante em futura revisão legislativa ou em normas de orientação técnica da DGAV.</t>
         </is>
       </c>
-      <c r="O2" s="11" t="inlineStr">
+      <c r="O3" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P2" s="11" t="inlineStr"/>
+      <c r="P3" s="11" t="inlineStr"/>
     </row>
-    <row r="3" ht="120" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4" ht="120" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Bem-Estar e Detenção</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Art.º 6.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall be responsible for the welfare of dogs or cats kept in the establishments under their responsibility and under their control and to minimise any risks to their welfare.
 1a. In the case of foster homes, the responsibility shall lie with the operator on whose behalf dogs or cats are kept. Such operators shall not place more than a total of five dogs or cats or one litter with or without mother in a foster home at any given time and shall provide the foster family with adequate information on the animal welfare obligations as well as the individual needs of the dogs or cats, and shall ensure that the relevant obligations set out by this Regulation are complied with in foster homes. Member States where the foster home is located may provide for a greater number of dogs, cats or litters to be placed in the foster home, provided that the premises of the foster home provide sufficient space, including outdoor space, and that the number of animal caretakers in the foster home is sufficient, to ensure the welfare of the dogs or cats.
@@ -782,7 +866,7 @@
 2b. The Commission is empowered to adopt delegated acts in accordance with Article 23 supplementing this Regulation by laying down animal-based indicators concerning behaviour and physical appearance and the methods of their measurement.</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores são responsáveis pelo bem-estar dos cães ou gatos mantidos nos estabelecimentos sob a sua responsabilidade e controlo e devem minimizar quaisquer riscos para o seu bem-estar.
 1a. No caso de famílias de acolhimento, a responsabilidade recai sobre o operador em nome de quem os cães ou gatos são mantidos. Esses operadores não devem colocar mais do que um total de cinco cães ou gatos ou uma ninhada com ou sem mãe numa família de acolhimento em qualquer momento e devem fornecer à família de acolhimento informação adequada sobre as obrigações de bem-estar animal, bem como as necessidades individuais dos animais, e devem assegurar que as obrigações relevantes estabelecidas por este Regulamento são cumpridas em famílias de acolhimento. Os Estados-Membros onde a família de acolhimento está localizada podem prever um número maior de cães, gatos ou ninhadas a serem colocadas na família de acolhimento, desde que as instalações da família de acolhimento providenciem espaço suficiente, incluindo espaço ao ar livre, e que o número de cuidadores de animais na família de acolhimento seja suficiente, para assegurar o bem-estar dos cães ou gatos.
@@ -794,12 +878,12 @@
 2b. A Comissão tem competência para adotar atos delegados em conformidade com o artigo 23.º que complementem este Regulamento através do estabelecimento de indicadores baseados no bem-estar dos animais relativos ao comportamento e aparência física e dos métodos da sua medição.</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Art.º 10.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1 — O detentor do animal de companhia deve:
 a) Assegurar o bem-estar do animal, de acordo com a sua espécie, raça, idade e necessidades físicas e etológicas, proporcionando-lhe:
@@ -809,69 +893,69 @@
 — Liberdade de movimento, sendo proibidos todos os sistemas de contenção permanentes.</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Art.º 5.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os cinco domínios do bem-estar animal (Nutrição, Ambiente, Saúde, Comportamento e Psicológico), estabelecidos pela Organização Mundial da Saúde Animal (OMSA).
 2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou as demais previstas no presente diploma.
 3 — É proibida a violência contra animais, considerando-se como tal todos os atos que, sem necessidade, infligem a morte, o sofrimento, a dor, a angústia ou ferimentos a um animal.</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>n.ºs 1, 2 e 3 do art.º 7.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
 2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
 3 — São proibidas todas as violências contra animais, considerando-se como tais os atos consistentes em, sem necessidade, se infligir a morte, o sofrimento ou lesões a um animal.</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 7.º) centra a responsabilidade no detentor em geral, sem distinguir o contexto de acolhimento temporário nem fixar limites numéricos de animais por família. O conceito de família de acolhimento é inexistente na legislação vigente.</t>
         </is>
       </c>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>O @codigo não prevê o conceito de família de acolhimento nem qualquer limite numérico de animais por unidade. A responsabilidade do operador como figura distinta do detentor particular também não é contemplada.</t>
         </is>
       </c>
-      <c r="M3" s="10" t="inlineStr">
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac menciona famílias de acolhimento temporário mas não fixa o limite de 5 animais por família de acolhimento nem especifica que a responsabilidade jurídica recai sobre o operador e não sobre a família.</t>
         </is>
       </c>
-      <c r="N3" s="11" t="inlineStr">
+      <c r="N4" s="11" t="inlineStr">
         <is>
           <t>Lacuna transversal a toda a legislação nacional. Necessidade de: (1) criar o conceito de 'família de acolhimento' como extensão da atividade do operador; (2) fixar limite numérico de animais por família (máximo 5, ou 1 ninhada com mãe); (3) atribuir responsabilidade jurídica ao operador, não à família de acolhimento.</t>
         </is>
       </c>
-      <c r="O3" s="11" t="inlineStr">
+      <c r="O4" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P3" s="11" t="inlineStr"/>
+      <c r="P4" s="11" t="inlineStr"/>
     </row>
-    <row r="4" ht="120" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5" ht="120" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Estratégias de Criação — Conformação e Consanguinidade</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Art.º 6.º-A do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>1. Operators of breeding establishments shall ensure that their breeding strategies minimise the risk of producing dogs or cats with genotypes associated with detrimental effects on their health and welfare.
 2. Operators of breeding establishments shall not use for reproduction dogs or cats that have excessive conformational traits leading to a high risk of detrimental effects on the welfare of these dogs or cats, or of their offspring. Before selection for breeding of a dog or cat that may be concerned by an excessive conformational trait the operator shall consult a veterinarian or an independent qualified person under the responsibility of a veterinarian. The veterinarian or independent qualified person shall assess whether the dog or cat has an excessive conformational trait.
@@ -884,7 +968,7 @@
 (b) the breeding to produce hybrids.</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
 2. Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem traços conformacionais excessivos que conduzam a um risco elevado de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por traço conformacional excessivo, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem um traço conformacional excessivo.
@@ -897,23 +981,23 @@
 (b) o cruzamento para produção de híbridos.</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>n.ºs 1 e 2 do art.º 34.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1 — As intervenções cirúrgicas com o objetivo da modificação da aparência ou com fins não curativos ou não destinados a impedir a reprodução dos animais são proibidas, nos termos do disposto na alínea i) do n.º 1 do artigo 12.º.
 2 — O detentor de animal sujeito a intervenção curativa que modifique a sua aparência deve possuir documento comprovativo da necessidade da mesma, passado pelo médico veterinário que a ela procedeu, sob a forma de atestado do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura, ou, no caso de animais importados, documento comprovativo da necessidade dessa intervenção, emitida pelo médico veterinário que a ela procedeu, legalizado pela autoridade competente do respetivo país.</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>n.º 2, als. a), b) e c) do art.º 8.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>2 — A reprodução de animais obedece ao seguinte:
 a) Os animais só devem ser utilizados na reprodução depois de atingida a maturidade reprodutiva para a espécie e raça devendo, no caso dos cães e gatos, seguir os parâmetros referidos no anexo I ao presente diploma, do qual faz parte integrante, não sendo autorizado, no caso das fêmeas, o acasalamento em cios sucessivos;
@@ -921,56 +1005,56 @@
 c) Devem ser excluídos da reprodução, os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia da anca nos cães e rim poliquístico nos gatos, ou alterações comportamentais.</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>art.º 17.º e n.º 1 do art.º 18.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>Artigo 17.º — As intervenções cirúrgicas, nomeadamente as destinadas ao corte de caudas nos canídeos, têm de ser executadas por um médico veterinário.
 Artigo 18.º, n.º 1 — Os detentores de animais de companhia que os apresentem com quaisquer amputações que modifiquem a aparência dos animais ou com fins não curativos devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa amputação, nomeadamente discriminando que as mesmas foram feitas por razões médico-veterinárias ou no interesse particular do animal ou para impedir a reprodução.</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.ºs 17.º e 18.º) exige intervenção veterinária em cirurgias e documentação para amputações, mas não prevê qualquer restrição à reprodução por traços conformacionais excessivos nem proibição de consanguinidade próxima ou hibridação.</t>
         </is>
       </c>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 8.º, n.º 2) exclui da reprodução animais com defeitos genéticos e malformações (displasia, rim poliquístico) e proíbe cios sucessivos, mas não prevê o conceito de traços conformacionais excessivos nem a proibição de consanguinidade.</t>
         </is>
       </c>
-      <c r="M4" s="10" t="inlineStr">
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.º 34.º) proíbe intervenções cirúrgicas de modificação da aparência, mas não contém qualquer norma sobre estratégia genética de criação, conformação excessiva ou consanguinidade.</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="N5" s="11" t="inlineStr">
         <is>
           <t>Lacuna normativa transversal. Necessidade de criar norma específica que: (1) defina traços conformacionais excessivos (a regular por ato delegado europeu até 2030); (2) proíba consanguinidade próxima (pais/filhos, irmãos, avós/netos); (3) proíba a produção de híbridos; (4) imponha consulta veterinária prévia ao acasalamento de animais potencialmente afetados.</t>
         </is>
       </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="O5" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P4" s="11" t="inlineStr"/>
+      <c r="P5" s="11" t="inlineStr"/>
     </row>
-    <row r="5" ht="120" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6" ht="120" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Reprodução e Criação</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Art.º 7.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Operators shall notify the competent authorities of their activity, providing at least the following information:
 (a) name, address and contact details of the operator;
@@ -981,7 +1065,7 @@
 (ea) for breeding establishments, the estimated number of litters to be placed on the market per year.</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem notificar as autoridades competentes da sua atividade, fornecendo pelo menos as seguintes informações:
 (a) nome, morada e contactos do operador;
@@ -992,24 +1076,24 @@
 (ea) para os estabelecimentos de criação, o número estimado de ninhadas a colocar no mercado por ano.</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Art.º 43.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1 — Os centros de bem-estar animal procedem à esterilização dos animais recolhidos que se presuma terem sido abandonados, nos termos do artigo 41.º.
 2 — As câmaras municipais devem, sempre que necessário e sob a responsabilidade do médico veterinário municipal, incentivar e promover programas de esterilização de animais de companhia, nomeadamente os cães e gatos, em complementaridade com os centros de bem-estar animal.
 3 — Os requisitos mínimos das instalações adequadas à realização de esterilizações nos centros de bem-estar animal são estabelecidos em portaria do membro do Governo responsável pela área da agricultura.</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Art.º 8.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>1 — A reprodução de animais deve ser realizada de forma planeada.
 2 — A reprodução de animais obedece ao seguinte:
@@ -1018,12 +1102,12 @@
 c) Devem ser excluídos da reprodução os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia.</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>n.º 1 do art.º 3.º-A do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>1 — A mera comunicação prévia a que se refere a alínea a) do n.º 1 do artigo anterior é dirigida à DGAV e deve conter os seguintes elementos, quando aplicáveis:
 a) O nome ou a denominação social do interessado;
@@ -1038,45 +1122,45 @@
 j) Declaração de responsabilidade, subscrita pelo interessado, relativa ao cumprimento da legislação aplicável aos animais de companhia, nomeadamente em matéria de instalações, equipamentos, higiene, saúde e bem-estar dos animais.</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr">
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 3.º-A) prevê comunicação prévia à DGAV com elementos parcialmente equivalentes (capacidade máxima, espécies, raças). Não exige a estimativa anual de ninhadas a colocar no mercado (al. ea) do @regulamento), constituindo lacuna parcial. É o diploma mais próximo do @regulamento neste eixo.</t>
         </is>
       </c>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>O @codigo regula condições de reprodução (art.º 8.º) mas não prevê qualquer sistema de notificação ou registo de estabelecimentos criadores junto da autoridade competente.</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr">
+      <c r="M6" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac trata da esterilização de errantes e CED, mas não contém norma sobre notificação de criadores ou registo de estabelecimentos com fins de reprodução comercial.</t>
         </is>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="N6" s="11" t="inlineStr">
         <is>
           <t>A @legislacao vigente é o diploma base adequado para a transposição. Necessidade de ajuste: acrescentar a obrigação de estimativa anual de ninhadas a colocar no mercado e alinhar os restantes elementos informativos com a lista exaustiva do art.º 7.º do @regulamento.</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="O6" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P5" s="11" t="inlineStr"/>
+      <c r="P6" s="11" t="inlineStr"/>
     </row>
-    <row r="6" ht="120" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7" ht="120" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Detenção Responsável e Informação</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Art.º 8.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Operators shall provide to the acquirer of a dog or cat written information necessary to enable him or her to ensure the welfare of the dog or cat including information on responsible ownership and on the specific needs of the dog or cat in terms of feeding, caring, health, housing and behavioural needs, as well as information on its health.
 1a. The written information on the dog or cat's health referred to in the first paragraph shall include at least:
@@ -1085,7 +1169,7 @@
 In case the information on the dog's or cat's health is documented in a document required under Regulation (EU) 2016/429, the operator shall transmit that document to the acquirer.</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem fornecer ao adquirente de um cão ou gato informação escrita necessária para lhe permitir assegurar o bem-estar do cão ou gato, incluindo informação sobre detenção responsável e sobre as necessidades específicas do cão ou gato em termos de alimentação, cuidados, saúde, alojamento e necessidades comportamentais, bem como informação sobre a sua saúde.
 1a. A informação escrita sobre a saúde do cão ou gato referida no parágrafo anterior deve incluir pelo menos:
@@ -1094,23 +1178,23 @@
 Caso a informação sobre a saúde do cão ou gato esteja documentada num documento exigido sob o Regulamento (UE) 2016/429, o operador deve transmitir esse documento ao adquirente.</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Art.º 8.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>1 — O detentor do animal de companhia deve possuir informação sobre as obrigações inerentes à sua detenção, incluindo direitos e responsabilidades, normas de bem-estar, cuidados de saúde, comportamento, necessidades específicas da espécie/raça, duração de vida esperada, custos de manutenção, e proibição de abandono.
 2 — Os comerciantes devem fornecer por escrito ao adquirente informação completa antes da transferência do animal, incluindo identidade e dados de contacto do comerciante, dados de identificação do animal, cuidados de saúde e estado de vacinação, e certificado de origem ou de compatibilidade quando aplicável.</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Art.º 57.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>1 — O detentor do animal deve ter acesso a informação sobre:
 a) As obrigações inerentes à sua detenção, direitos e responsabilidades;
@@ -1122,56 +1206,56 @@
 2 — Os criadores e comerciantes devem fornecer informação escrita completa ao adquirente antes da transferência do animal, incluindo dados de identificação e cuidados de saúde.</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Art.º 20.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>1 — O proprietário ou detentor de animal de companhia deve ter acesso a informação adequada sobre as suas obrigações relativas ao bem-estar do animal.
 2 — Os detentores de animais de companhia que os comercializem devem fornecer informação ao adquirente sobre o estado de saúde do animal e vacinas efetuadas.</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 20.º) é genérico e não especifica a forma escrita nem detalhes de conteúdo. O @regulamento exige informação escrita sobre necessidades específicas de bem-estar (alimentação, cuidados, saúde, alojamento, comportamento) e condiciona a transferência à transmissão dessa informação.</t>
         </is>
       </c>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 57.º) exige informação escrita mas com âmbito mais amplo (duração de vida, custos) do que o @regulamento, que se foca especificamente em bem-estar e saúde.</t>
         </is>
       </c>
-      <c r="M6" s="10" t="inlineStr">
+      <c r="M7" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.º 8.º) aproxima-se do conteúdo do @regulamento, exigindo informação escrita antes da transferência, incluindo dados de saúde e vacinação, mas ainda sem o enfoque específico em bem-estar comportamental.</t>
         </is>
       </c>
-      <c r="N6" s="11" t="inlineStr">
+      <c r="N7" s="11" t="inlineStr">
         <is>
           <t>Necessidade de alteração: (1) formalizar requisito de informação escrita como condição de transferência de animal; (2) especificar conteúdo obrigatório sobre bem-estar, saúde e necessidades comportamentais; (3) harmonizar entre @codigo e @rgbeac quanto a âmbito e forma.</t>
         </is>
       </c>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="O7" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P6" s="11" t="inlineStr"/>
+      <c r="P7" s="11" t="inlineStr"/>
     </row>
-    <row r="7" ht="120" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Competências de Cuidadores e Bem-Estar Animal</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Art.º 9.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>1. Animal caretakers, other than volunteers in shelters and interns who are under the responsibility of a competent animal caretaker, shall have the following competences as regards the dogs and cats they are handling:
 (a) understanding of their biological behaviour and their physiological and ethological needs;
@@ -1183,7 +1267,7 @@
 3. The Commission shall, by means of implementing acts, lay down minimum requirements concerning the formal education, training or professional experience in order to acquire the competences referred to in paragraph 2 and for the training courses referred to in paragraph 2a. Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 24. The implementing act concerning the training courses referred to in paragraph 2a shall be adopted by [3 years from the date of entry into force of the Regulation].</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>1. Os cuidadores de animais, com exceção de voluntários em abrigos e estagiários sob a responsabilidade de um cuidador competente, devem ter as seguintes competências no que diz respeito aos cães e gatos que manuseiam:
 (a) compreensão do seu comportamento biológico e das suas necessidades fisiológicas e etológicas;
@@ -1195,12 +1279,12 @@
 3. A Comissão estabelecerá, por meio de atos de execução, os requisitos mínimos relativos à educação formal, formação ou experiência profissional para adquirir as competências referidas no parágrafo 2 e para os cursos de formação referidos no parágrafo 2a. Esses atos de execução serão adotados de acordo com o procedimento de exame referido no artigo 24.º. O ato de execução relativo aos cursos de formação referidos no parágrafo 2a deve ser adotado por [3 anos da data de entrada em vigor do Regulamento].</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Art.ºs 69.º, 84.º e 90.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Artigo 69.º — Formação
 A reprodução, criação, manutenção, venda ou treino de animais de companhia depende de aprovação em formação sobre detenção responsável de animais de companhia, bem como sobre as necessidades fisiológicas e etológicas específicas da espécie animal em causa, ministrada pelo ICNF, I.P. ou entidades por este certificadas.
@@ -1210,23 +1294,23 @@
 O pessoal auxiliar deve possuir os conhecimentos e a experiência adequada, o qual fica, contudo, sob a orientação do médico veterinário responsável.</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Art.º 19.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Artigo 19.º — Pessoal auxiliar
 Os alojamentos devem dispor de pessoal auxiliar que possua os conhecimentos e a aptidão necessária para assegurar os cuidados adequados aos animais, o qual fica sob a orientação do médico veterinário responsável.</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Art.º 13.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Artigo 13.º — Maneio
 1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
@@ -1234,45 +1318,45 @@
 3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados.</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 13.º) exige pessoal 'técnico competente' com 'formação teórica e prática específica' e 'inspeção diária', mas não detalha competências concretas. O @regulamento especifica 4 competências estruturadas (comportamento biológico, reconhecimento de sofrimento, maneio e bem-estar, conhecimento de obrigações) e exige documentação de educação/formação/experiência.</t>
         </is>
       </c>
-      <c r="L7" s="9" t="inlineStr">
+      <c r="L8" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 19.º) é genérico: exige apenas 'conhecimentos e aptidão necessária' sob orientação do médico veterinário responsável. Não detalha competências concretas nem exigências de formação formal.</t>
         </is>
       </c>
-      <c r="M7" s="10" t="inlineStr">
+      <c r="M8" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.ºs 69.º, 84.º, 90.º) aproxima-se mais do @regulamento: exige 'conhecimentos e experiência adequados', menciona 'necessidades fisiológicas e etológicas', exige formação certificada pelo ICNF. Lacuna: não detalha as 4 competências específicas do @regulamento (reconhecimento de sofrimento, condicionamento operante, etc.).</t>
         </is>
       </c>
-      <c r="N7" s="11" t="inlineStr">
+      <c r="N8" s="11" t="inlineStr">
         <is>
           <t>Alinhamento parcial do @rgbeac com @regulamento. Para @codigo e @legislacao, necessidade de: (1) detalhar as 4 competências específicas (comportamento, reconhecimento de sofrimento, maneio positivo, conhecimento de obrigações); (2) exigir documentação formal de educação/formação/experiência; (3) requerer que operador designe formador responsável que transfira conhecimento; (4) implementar requisitos mínimos de formação via regulamento delegado.</t>
         </is>
       </c>
-      <c r="O7" s="11" t="inlineStr">
+      <c r="O8" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P7" s="11" t="inlineStr"/>
+      <c r="P8" s="11" t="inlineStr"/>
     </row>
-    <row r="8" ht="120" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Avaliação e Supervisão de Bem-Estar</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Art.º 10.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Operators shall:
 (a) ensure that the establishments under their responsibility receive a visit by a veterinarian within the first year after the date of application of this Regulation or within the first year after having notified a new establishment, for the purpose of identifying and assessing any risk factor for the welfare of the dogs or cats and advising the operator on measures to address those risks; thereafter the visits from a veterinarian shall take place when appropriate, based on a risk analysis by the competent authorities; Member States may provide for that the advisory welfare visits are annual;
@@ -1280,7 +1364,7 @@
 By 24 months from the date of entry into force of this Regulation, the Commission shall adopt delegated acts in accordance with Article 23 supplementing this Article in order to lay down minimum criteria to be assessed during the advisory welfare visit.</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem:
 (a) assegurar que os estabelecimentos sob a sua responsabilidade recebem uma visita de um médico veterinário no prazo de um ano a partir da data de aplicação do presente Regulamento ou no prazo de um ano após notificação de novo estabelecimento, com o objetivo de identificar e avaliar quaisquer fatores de risco para o bem-estar dos cães ou gatos e aconselhar o operador sobre medidas para resolver esses riscos; depois, as visitas do médico veterinário devem ocorrer quando apropriado, com base numa análise de risco pelas autoridades competentes; os Estados-Membros podem estabelecer que as visitas de aconselhamento de bem-estar sejam anuais;
@@ -1288,12 +1372,12 @@
 Dentro de 24 meses a partir da data de entrada em vigor do presente Regulamento, a Comissão deve adotar atos delegados em conformidade com o artigo 23.º que complementem o presente artigo de forma a estabelecer critérios mínimos a serem avaliados durante a visita de aconselhamento de bem-estar.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Art.º 56.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Artigo 56.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem, com exceção dos alojamentos para hospedagem com fins higiénicos, devem ter ao seu serviço um médico veterinário responsável pelo alojamento.
@@ -1304,12 +1388,12 @@
 d) A colaboração com as autoridades competentes em todas as ações que estas determinem.</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Art.º 32.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Artigo 32.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem sem fins lucrativos e com fins lucrativos de animais, com exceção dos com fins higiénicos, necessitam de ter ao seu serviço um médico veterinário que seja responsável pelo alojamento.
@@ -1319,12 +1403,12 @@
 c) A colaboração com as autoridades competentes em todas as ações que estas determinarem.</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Art.º 4.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Artigo 4.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem sem fins lucrativos e com fins lucrativos de animais, com exceção dos alojamentos para hospedagem com fins higiénicos, devem ter ao seu serviço um médico veterinário que seja responsável pelo alojamento.
@@ -1334,45 +1418,45 @@
 c) A colaboração com as autoridades competentes em todas as ações que estas determinarem.</t>
         </is>
       </c>
-      <c r="K8" s="8" t="inlineStr">
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 4.º) estabelece a obrigação de ter médico veterinário responsável que execute 'programas e ações' para saúde e bem-estar, mas não especifica que essa avaliação deve ocorrer em prazo determinado (ex.: 1 ano) ou que os registos devem ser mantidos por período específico (4 anos). O @regulamento é mais prescritivo neste aspecto.</t>
         </is>
       </c>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 32.º) replica quase verbatim o art.º 4.º do DL n.º 276/2001, mantendo as mesmas lacunas: não fixa prazos para avaliações de bem-estar nem obrigações de manutenção de registos estruturados.</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="M9" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.º 56.º) reforça a obrigação com 'parecer relativo à verificação das condições higiossanitárias e de bem-estar', mas igualmente sem prazos específicos para avaliações ou duração de retenção de registos. Ambos focam-se em 'programas' interno, não em 'visitas periódicas externas'.</t>
         </is>
       </c>
-      <c r="N8" s="11" t="inlineStr">
+      <c r="N9" s="11" t="inlineStr">
         <is>
           <t>Lacuna estrutural em toda a legislação nacional: enquanto o @regulamento exige 'visita de um veterinário' num prazo específico (1 ano) com manutenção de registos por 4 anos e transmissão entre veterinários, a legislação nacional concentra-se em ter um 'médico veterinário responsável' no estabelecimento. Necessidade de alteração: (1) formalizar obrigação de 'visita de avaliação' por veterinário dentro de 1 ano após notificação; (2) exigir avaliações periódicas conforme risco; (3) obrigatória manutenção de registos por 4 anos; (4) garantir transmissão de informações ao próximo veterinário avaliador; (5) estabelecer critérios mínimos de avaliação (bem-estar comportamental, alojamento, saúde, etc.).</t>
         </is>
       </c>
-      <c r="O8" s="11" t="inlineStr">
+      <c r="O9" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P8" s="11" t="inlineStr"/>
+      <c r="P9" s="11" t="inlineStr"/>
     </row>
-    <row r="9" ht="120" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Alimentação e Hidratação</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Art.º 11.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that dogs or cats are fed in accordance with the requirements laid down in point 1 of Annex I.
 2. Operators shall ensure that dogs or cats are adequately fed and hydrated by supplying:
@@ -1388,7 +1472,7 @@
 3a. Where advised in writing by a veterinarian to do so, the operators may adjust the feeding and watering frequencies for an individual dog or cat. The operators shall keep a record of the advice for its entire duration as advised by the veterinarian.</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores devem assegurar que os cães ou gatos são alimentados em conformidade com os requisitos estabelecidos no ponto 1 do Anexo I.
 2. Os operadores devem assegurar que os cães ou gatos são adequadamente alimentados e hidratados através do fornecimento de:
@@ -1404,35 +1488,35 @@
 3a. Quando aconselhado por escrito por um médico veterinário, os operadores podem ajustar as frequências de alimentação e hidratação para um cão ou gato individual. Os operadores devem manter um registo do conselho durante toda a sua duração, conforme aconselhado pelo médico veterinário.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Arts. 7.º (n.º 1, al. a) e 10.º (n.º 1, al. a) do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Artigo 7.º - Princípios fundamentais: Não passem fome ou sede, nem sejam sujeitos a malnutrição.
 Artigo 10.º - Obrigações especiais dos detentores: Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável. Ênfase em necessidades nutricionais adequadas ao estado de saúde.</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>Art.º 46.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>Alimentação e abeberamento:
 A alimentação dos animais de companhia, nos locais de criação, manutenção e venda bem como nos centros de recolha e instalações de hospedagem, deve obedecer a um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies.
 Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Decreto-Lei n.º 276/2001 - Artigo 12.º</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>1 — Deve existir um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies e dos indivíduos de acordo com a fase de evolução fisiológica em que se encontram, nomeadamente idade, sexo, fêmeas prenhes ou em fase de lactação.
 2 — As refeições devem ainda ser variadas, sendo distribuídas segundo a rotina que mais se adequar à espécie e de forma a manter, tanto quanto possível, aspetos do seu comportamento alimentar natural.
@@ -1442,49 +1526,49 @@
 6 — Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>NÃO APLICÁVEL - Diploma não específico nesta matéria</t>
         </is>
       </c>
-      <c r="L9" s="9" t="inlineStr">
+      <c r="L10" s="9" t="inlineStr">
         <is>
           <t>SIM - COBERTURA COMPLETA (Art. 46.º implementa integralmente)</t>
         </is>
       </c>
-      <c r="M9" s="10" t="inlineStr">
+      <c r="M10" s="10" t="inlineStr">
         <is>
           <t>SIM - COBERTURA COMPLETA (linguagem modernizada)</t>
         </is>
       </c>
-      <c r="N9" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>COBERTURA COMPLETA. Código do Animal (Art. 46.º) implementa todos os requisitos do Artigo 11.º. RGBEAC alinha melhor com linguagem e especificidades do Regulamento europeu. Sem divergências substanciais.</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P9" s="11" t="inlineStr">
+      <c r="P10" s="11" t="inlineStr">
         <is>
           <t>Correspondências completas - RGBEAC alinha melhor com Regulamento EU</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="120" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11" ht="120" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Alojamento (Housing)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Art.º 12.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>1. Operators of breeding and selling establishments shall ensure that dogs or cats are provided with housing in accordance with point 2 of the annex I. Operators of shelters shall ensure that dogs or cats are provided with housing in accordance with point 2.2 of the annex I.
 2. Operators shall ensure that:
@@ -1506,7 +1590,7 @@
 7a. Paragraphs 2(a), (b), (ba) (da) (e), 6, 6a and 7 shall not apply to livestock guardian dogs, nor to herding dogs, during the periods where such dogs are used for guarding or herding in the context of on foot seasonal transhumance.</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores de estabelecimentos de criação e venda devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2 do Anexo I. Os operadores de abrigos devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2.2 do Anexo I.
 2. Os operadores devem assegurar que:
@@ -1528,12 +1612,12 @@
 7a. Os parágrafos 2(a), (b), (ba) (da) (e), 6, 6a e 7 não se aplicam a cães guardiões de gado, nem a cães de pastoreio, durante os períodos em que tais cães são utilizados para guarda ou pastoreio no contexto de transumância sazonal a pé.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Arts. 7.º, 10.º, 11.º, 47-57 do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Artigo 7.º - Princípios: Condições de detenção e alojamento salvaguardam bem-estar animal.
 Artigo 10.º - Obrigações especiais: Liberdade de movimento, proibição de contenção permanente, espaço adequado, enriquecimento ambiental e abrigo protetor.
@@ -1541,12 +1625,12 @@
 Artigos 47-57 - Regulação detalhada de alojamentos para hospedagem (estruturas, proteção, maneio, responsabilidades veterinárias).</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Arts. 3.º, 14.º, 18.º, 28.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>Artigo 3.º - Define 'Alojamento' como qualquer instalação, edifício ou local onde animais se encontram mantidos.
 Artigo 14.º - A temperatura, ventilação, luminosidade e obscuridade devem ser adequadas ao conforto e bem-estar.
@@ -1554,12 +1638,12 @@
 Artigo 28.º - Define separação por espécie e requisitos de estrutura para hospedagem.</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Decreto-Lei n.º 276/2001 - Artigos 8.º e 15.º</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Artigo 8.º — 1 — Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir: a) A prática de exercício físico adequado; b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
 2 — Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.
@@ -1568,49 +1652,49 @@
 Artigo 15.º — Os alojamentos devem assegurar que as espécies animais neles mantidas não possam causar quaisquer riscos para a saúde e para a segurança de pessoas, outros animais e bens.</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
+      <c r="K11" s="8" t="inlineStr">
         <is>
           <t>PARCIAL - Não específico para condições técnicas de alojamento</t>
         </is>
       </c>
-      <c r="L10" s="9" t="inlineStr">
+      <c r="L11" s="9" t="inlineStr">
         <is>
           <t>SIM - COBERTURA COMPLETA (Arts. 3, 14, 18, 28)</t>
         </is>
       </c>
-      <c r="M10" s="10" t="inlineStr">
+      <c r="M11" s="10" t="inlineStr">
         <is>
           <t>SIM - COBERTURA EXPANDIDA (especifica detalhes técnicos)</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="N11" s="11" t="inlineStr">
         <is>
           <t>COBERTURA COMPLETA. Código do Animal e RGBEAC implementam requisitos do Artigo 12.º. Faltam especificações técnicas detalhadas (temperatura, ventilação, iluminação) — recomenda-se Portaria complementar.</t>
         </is>
       </c>
-      <c r="O10" s="11" t="inlineStr">
+      <c r="O11" s="11" t="inlineStr">
         <is>
           <t>Sim - Portaria complementar com especificações técnicas</t>
         </is>
       </c>
-      <c r="P10" s="11" t="inlineStr">
+      <c r="P11" s="11" t="inlineStr">
         <is>
           <t>Princípios cobertos; faltam normas técnicas pormenorizadas</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="120" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12" ht="120" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Saúde e Monitorização Sanitária</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Art.º 13.º do Regulamento 2023/0447 (PE/Conselho)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that:
 (a) dogs or cats under their responsibility are inspected by animal caretakers at least once a day and vulnerable dogs and cats, such as newborns, ill or injured dogs and cats, and peri-partum bitches and queens, are inspected more frequently;
@@ -1630,7 +1714,7 @@
 (-e) dogs and cats which are no longer used for reproduction, including as a result of the provisions of this Regulation, are either kept or sold, donated or rehomed, not killed or abandoned.</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>1 — Os operadores devem assegurar que:
 (a) os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados e fêmeas em período peri-parto, são inspecionados com maior frequência;
@@ -1650,12 +1734,12 @@
 (-e) os cães e gatos que deixem de ser utilizados para reprodução, nomeadamente em resultado das disposições do presente Regulamento, são mantidos ou vendidos, doados ou realojados, não sendo mortos nem abandonados.</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Art.º 33.º do RGBEAC — Regime Geral do Bem-Estar dos Animais de Companhia (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Artigo 33.º — Cuidados de saúde
 1 — Os detentores dos animais de companhia devem assegurar-lhes os cuidados de saúde adequados, nomeadamente seguindo as orientações da DGAV em matéria de vacinação e tratamentos obrigatórios, bem como consultas regulares junto de médico veterinário.
@@ -1665,23 +1749,23 @@
 [dim]5 — Os médicos veterinários denunciam, junto da DGAV ou demais entidades com competência de fiscalização do cumprimento das normas constantes do presente decreto-lei, sempre que, no exercício de sua profissão, suspeitem de maus-tratos a animais de companhia.</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Art.º 6.º (Cuidados médico-veterinários) do Código do Animal — DL n.º 214/2013</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Artigo 6.º — Cuidados médico-veterinários
 O detentor do animal deve assegurar ao animal ferido ou doente os cuidados médico-veterinários adequados, designadamente retirando o mesmo do alojamento sempre que este seja um local de venda.</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Art.º 13.º (Maneio) e art.º 16.º (Cuidados de saúde animal) do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>Artigo 13.º — Maneio
 1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
@@ -1698,45 +1782,45 @@
 [dim]6 — A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior deve ser feita sob orientação do médico veterinário responsável.</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 prevê inspeção diária (n.º 3 do art.º 13.º) e programa de profilaxia supervisionado por veterinário (n.º 1 do art.º 16.º) — alinhamento parcial com as als. (a) e (d) do n.º 1 do art.º 13.º do @regulamento. Lacunas: (1) não distingue animais vulneráveis com maior frequência de inspeção; (2) não prevê isolamento em área separada com tratamento (al. (b)); (3) não exige consulta veterinária para decisão de eutanásia com anestesia/analgesia (al. (c)); (4) nenhuma das obrigações sanitárias para criadores previstas no n.º 2 está contemplada: sem idade mínima de reprodução, sem frequência máxima de partos, sem proibição de cobrição de fêmeas a lactar, sem regime de rehoming.</t>
         </is>
       </c>
-      <c r="L11" s="9" t="inlineStr">
+      <c r="L12" s="9" t="inlineStr">
         <is>
           <t>O @codigo limita os cuidados médico-veterinários ao animal ferido ou doente (art.º 6.º) — sem qualquer obrigação de inspeção diária, programa de profilaxia ou isolamento. É o diploma com maior divergência face ao n.º 1 do art.º 13.º do @regulamento, omitindo igualmente todas as obrigações sanitárias específicas para criadores previstas no n.º 2.</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M12" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.º 33.º) centra os cuidados de saúde no detentor em geral (n.ºs 1 a 3), sem distinguir obrigações reforçadas para operadores de criação. Não prevê: inspeção diária sistemática por cuidadores; isolamento imediato de animais com bem-estar comprometido; nem qualquer dos requisitos sanitários para criadores do n.º 2 do art.º 13.º do @regulamento. Os n.ºs 4 e 5 (CAMV e denúncia de maus-tratos) não têm correspondência direta no @regulamento.</t>
         </is>
       </c>
-      <c r="N11" s="11" t="inlineStr">
+      <c r="N12" s="11" t="inlineStr">
         <is>
           <t>A @legislacao vigente (DL n.º 276/2001) tem o maior alinhamento, mas insuficiente. Necessidade de alteração dos três diplomas: (1) introduzir inspeção diária diferenciada para animais vulneráveis (al. (a) do n.º 1 do art.º 13.º do @regulamento); (2) criar obrigação de isolamento e tratamento imediato (al. (b)); (3) regular o processo de eutanásia com supervisão veterinária e anestesia/analgesia (al. (c)); (4) para criadores (n.º 2): fixar idade mínima e maturidade esquelética das fêmeas reprodutoras, frequência máxima de partos conforme Anexo I, proibição de cobrição de fêmeas a lactar, e regime de rehoming dos animais retirados da reprodução.</t>
         </is>
       </c>
-      <c r="O11" s="11" t="inlineStr">
+      <c r="O12" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P11" s="11" t="inlineStr"/>
+      <c r="P12" s="11" t="inlineStr"/>
     </row>
-    <row r="12" ht="120" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Necessidades Comportamentais (Behavioural needs)</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Art.º 14.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that measures are taken to meet the behavioural needs of dogs or cats in accordance with point 4 of Annex I.
 2. Operators shall not keep dogs or cats in areas restraining their natural movements, except in case of Article 12(3), second sub-paragraph, or for performing the following procedures or treatments:
@@ -1753,7 +1837,7 @@
 6. Operators shall ensure that enrichment is provided and accessible to all dogs or cats, creating a stimulating environment, enabling species-specific behaviour and reducing their frustration.</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores devem assegurar que medidas são tomadas para satisfazer as necessidades comportamentais de cães ou gatos em conformidade com o ponto 4 do Anexo I.
 2. Os operadores não devem manter cães ou gatos em áreas que restringem os seus movimentos naturais, exceto no caso do artigo 12.º (parágrafo 3), segundo parágrafo, ou para realizar os seguintes procedimentos ou tratamentos:
@@ -1770,12 +1854,12 @@
 6. Os operadores devem assegurar que enriquecimento é fornecido e acessível a todos os cães ou gatos, criando um ambiente estimulante, permitindo comportamento específico da espécie e reduzindo a sua frustração.</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>RGBEAC (proposta, jun. 2025) - Artigos 10, 12, 13, 14, 15</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Especificação clara: 'exercício físico e estímulo mental'.
 'Contato social adequado'.
@@ -1784,72 +1868,72 @@
 Documentação obrigatória de estratégia de socialização (criadores).</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Arts. 5.º e 13.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>Artigo 5.º - Princípios que proíbem violência e maus-tratos, garantem bem-estar.
 Artigo 13.º - Espaço para exercício físico e expressão de comportamentos naturais.
 Cobertura GENÉRICA: não especifica enriquecimento, socialização ou método de treino baseado em reforço positivo.</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>Decreto-Lei n.º 276/2001 - Artigo 8.º</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Artigo 8.º — 1 — Os animais devem dispor de um espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir: a) A prática de exercício físico adequado; b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
 2 — Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t>PARCIAL - Legislação vigente oferece cobertura genérica</t>
         </is>
       </c>
-      <c r="L12" s="9" t="inlineStr">
+      <c r="L13" s="9" t="inlineStr">
         <is>
           <t>PARCIAL - Genérico, sem especificações sobre socialização e enriquecimento</t>
         </is>
       </c>
-      <c r="M12" s="10" t="inlineStr">
+      <c r="M13" s="10" t="inlineStr">
         <is>
           <t>SIM - COBERTURA SIGNIFICATIVAMENTE EXPANDIDA</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr">
+      <c r="N13" s="11" t="inlineStr">
         <is>
           <t>Legislação portuguesa oferece cobertura genérica. RGBEAC (2025) oferece avanço substancial com obrigatoriedade de reforço positivo e documentação de estratégia de socialização. Falta ainda regulamentação pormenorizada.</t>
         </is>
       </c>
-      <c r="O12" s="11" t="inlineStr">
+      <c r="O13" s="11" t="inlineStr">
         <is>
           <t>Sim - Regulamentação específica sobre métodos de treino</t>
         </is>
       </c>
-      <c r="P12" s="11" t="inlineStr">
+      <c r="P13" s="11" t="inlineStr">
         <is>
           <t>RGBEAC alinha melhor; implementação de reforço positivo obrigatório recomendada</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="120" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Práticas Dolorosas (Painful practices)</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Art.º 15.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that mutilations, including ear cropping, tail docking, claw removal or other partial or complete digit amputation, and resection of vocal cords or folds, are not performed unless upon medical indication, which may include prophylactic, with the sole purpose of preserving, improving the health of dogs or cats or preventing injury. In such case, the procedure shall only be performed under anaesthesia and prolonged analgesia and by a veterinarian.
 1a. The medical indication for the mutilation and the details of procedure carried out shall be documented by a veterinarian. This document shall be retained by the operator until the dog or cat, together with this document, is transferred to another establishment or owner. The operator of the establishment where the mutilation was performed shall retain a copy of the document for three years after the transfer of the dog or cat.
@@ -1866,7 +1950,7 @@
 4. Member States may grant derogations from paragraph 3 for dogs intended for use in military, police or customs services.</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores devem assegurar que mutilações, incluindo corte de orelhas, corte de cauda, remoção de garras ou amputação parcial ou completa de dígitos, e ressecção de cordas vocais ou pregas, não são realizadas a menos que por indicação médica, que pode incluir profilática, com o único propósito de preservar, melhorar a saúde de cães ou gatos ou prevenir ferimentos. Nesse caso, o procedimento deve ser realizado apenas sob anestesia e analgesia prolongada e por um médico veterinário.
 1a. A indicação médica para a mutilação e os detalhes do procedimento realizado devem ser documentados por um médico veterinário. Este documento deve ser retido pelo operador até que o cão ou gato, juntamente com este documento, seja transferido para outro estabelecimento ou proprietário. O operador do estabelecimento onde a mutilação foi realizada deve reter uma cópia do documento durante três anos após a transferência do cão ou gato.
@@ -1883,12 +1967,12 @@
 4. Os Estados-Membros podem conceder derrogações do parágrafo 3 para cães destinados a uso em serviços militares, policiais ou aduaneiros.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>RGBEAC (proposta, jun. 2025) - Artigo 12.º</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Lista idêntica de mutilações proibidas ao Código.
 Referência a 'boas práticas internacionais' (alinhamento com Reg. 2023/0447).
@@ -1897,12 +1981,12 @@
 Documentação obrigatória de indicação médica.</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>Arts. 51.º e 52.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Artigo 51.º - Intervenções cirúrgicas exclusivamente por médico veterinário.
 Artigo 52.º - Proibição específica de mutilações:
@@ -1913,148 +1997,148 @@
 - Exceções: reprodução e interesse do animal (com documentação)</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>Decreto-Lei n.º 276/2001 - Artigo 18.º</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>Artigo 18.º — 1 — Os detentores de animais de companhia que os apresentem com quaisquer amputações que modifiquem a aparência dos animais ou com fins não curativos devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa amputação.
 2 — O documento referido no número anterior deve ter a forma de um atestado, do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura.</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>SIM - DL 276/2001 cobre amputações documentadas</t>
         </is>
       </c>
-      <c r="L13" s="9" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>SIM - COBERTURA COMPLETA (Arts. 51-52)</t>
         </is>
       </c>
-      <c r="M13" s="10" t="inlineStr">
+      <c r="M14" s="10" t="inlineStr">
         <is>
           <t>SIM - COBERTURA COMPLETA + EXPANSÃO</t>
         </is>
       </c>
-      <c r="N13" s="11" t="inlineStr">
+      <c r="N14" s="11" t="inlineStr">
         <is>
           <t>COBERTURA COMPLETA. Código do Animal (Arts. 51-52) implementa integralmente Art. 15.º. RGBEAC alinha substancialmente com Regulamento europeu. Sem divergências substanciais.</t>
         </is>
       </c>
-      <c r="O13" s="11" t="inlineStr">
+      <c r="O14" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P13" s="11" t="inlineStr">
+      <c r="P14" s="11" t="inlineStr">
         <is>
           <t>Correspondências completas - Cobertura legislativa adequada</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="120" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15" ht="120" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Espetáculos e Competições Estéticas</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Art.º 15a do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Operators of breeding and selling establishments shall not use in aesthetic shows, exhibitions and competitions of dogs and cats, dogs or cats with excessive conformational traits or dogs or cats which have been mutilated in such a way that results in an alteration of physical characteristics.
 Organisers of aesthetic shows, exhibitions and competitions of dogs and cats shall exclude from such shows, exhibitions and competitions dogs and cats which have excessive conformational traits or dogs or cats which have been mutilated in such a way that results in an alteration of physical characteristics.</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Os operadores de estabelecimentos de criação e venda não devem utilizar em espetáculos, exposições e competições estéticas de cães e gatos, cães ou gatos com características conformacionais excessivas ou cães ou gatos que tenham sido mutilados de tal forma que resulte numa alteração de características físicas.
 Os organizadores de espetáculos, exposições e competições estéticas de cães e gatos devem excluir de tais espetáculos, exposições e competições cães e gatos que tenham características conformacionais excessivas ou cães ou gatos que tenham sido mutilados de tal forma que resulte numa alteração de características físicas.</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Art.º 39.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Artigo 39.º - Participação em eventos
 1 – A participação de animais de companhia em concursos, exposições, espetáculos, manifestações culturais, divertimentos públicos, atividades performativas, cinematográficas e audiovisuais, campanhas publicitárias, ou outros eventos onde participem animais de companhia carece de autorização do diretor geral da DGAV a área da realização da mesma, após parecer da respetiva câmara municipal.
 3 - Só serão admitidos no evento os animais de companhia que: a) Estejam registados no SIAC; b) Quando aplicável, possuam prova de vacinação antirrábica; c) Possuam vacinações contra as principais doenças infectocontagiosas; d) Não tenham sido submetidos a intervenções cirúrgicas em infração.</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Art.º 79.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>Artigo 79.º - Concursos e exposições
 1 - A realização de concursos e exposições com animais de companhia carece de autorização prévia da câmara municipal, ficando esta dependente do parecer vinculativo do MVM.
 3 - Só são admitidos a concurso os cães e gatos que: a) Estejam identificados eletronicamente; b) Sejam portadores de boletim sanitário e prova de vacinação antirrábica; c) Possuam vacinações contra principais doenças infecto-contagiosas.</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>Lei n.º 27/2016 e DL n.º 82/2019 (Normas de eventos)</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>A legislação portuguesa estabelece que a participação de animais em espetáculos e competições requer: - Autorização prévia de autoridades competentes; - Identificação e registo no SIAC; - Vacinações obrigatórias; - Supervisão veterinária durante o evento; - Condições de bem-estar animal garantidas.</t>
         </is>
       </c>
-      <c r="K14" s="8" t="inlineStr">
+      <c r="K15" s="8" t="inlineStr">
         <is>
           <t>SIM - Cobertura COMPLETA (autorização, identificação, vacinação, supervisão veterinária)</t>
         </is>
       </c>
-      <c r="L14" s="9" t="inlineStr">
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>SIM - Cobertura COMPLETA (concursos e exposições com requisitos específicos)</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>SIM - Cobertura COMPLETA (participação em eventos com normas de bem-estar)</t>
         </is>
       </c>
-      <c r="N14" s="11" t="inlineStr">
+      <c r="N15" s="11" t="inlineStr">
         <is>
           <t>A legislação portuguesa cobre completamente os requisitos do Artigo 15a. Implementa autorizações prévias, exigências de identificação, vacinação obrigatória e supervisão veterinária. O RGBEAC (Art. 39.º) e Código do Animal (Art. 79.º) estabelecem normas detalhadas sobre espetáculos, exposições e competições estéticas.</t>
         </is>
       </c>
-      <c r="O14" s="11" t="inlineStr">
+      <c r="O15" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P14" s="11" t="inlineStr">
+      <c r="P15" s="11" t="inlineStr">
         <is>
           <t>Correspondências completas encontradas - Cobertura legislativa adequada</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="120" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16" ht="120" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Identificação e Registo</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Art.º 17.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>1. All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip compliant with Annex II.
 1a. Operators shall ensure that dogs and cats born in their establishments are individually identified within 3 months after their birth and in any event before the date of their placing on the market.
@@ -2070,7 +2154,7 @@
 8. In case of unreadable transponder, the operator or the natural or legal person responsible for the dog or cat shall ensure that the dog or cat is re-identified with a new transponder and re-registered in the national database.</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>1. Todos os cães e gatos mantidos em estabelecimentos colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com o Anexo II.
 1a. Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de 3 meses após o nascimento e, em qualquer caso, antes da data da sua colocação no mercado.
@@ -2086,12 +2170,12 @@
 8. Em caso de transponder ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato devem assegurar que o animal é reidentificado com um novo transponder e re-registado na base de dados nacional.</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Art.º 17.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>1 — A identificação dos animais de companhia, pela sua marcação, quando aplicável, e registo no SIAC, deve ser realizada:
 a) Relativamente aos cães, gatos e furões nascidos em alojamentos, até aos três meses de idade ou, em qualquer caso, antes da sua colocação no mercado;
@@ -2099,12 +2183,12 @@
 c) Relativamente aos cães, gatos e furões detidos por pessoas singulares, exceto nos casos previstos nas alíneas anteriores, até aos três meses de idade ou, no caso de colocação no mercado, antes da data de colocação no mercado.</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>Art.º 53.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>1 — Todos os cães devem ser identificados e registados, entre os três e os seis meses de idade.
 2 — Os gatos em exposição, para fins comerciais ou lucrativos, em estabelecimentos de venda, locais de criação, feiras ou concursos, provas funcionais, publicidade ou fins similares, devem ser identificados e registados entre os três e os seis meses de idade.
@@ -2112,57 +2196,57 @@
 5 — A identificação electrónica é efetuada através da aplicação subcutânea de um microchip no centro da face lateral esquerda do pescoço.</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>n.ºs 1, 2 e 3 do art.º 5.º do DL n.º 82/2019, de 27 de junho</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>1 — A identificação dos animais de companhia, pela sua marcação e registo no SIAC, deve ser realizada até 120 dias após o seu nascimento.
 2 — Na impossibilidade de determinar a data de nascimento exata, para efeitos de contagem do prazo referido no número anterior, a identificação deve ser efetuada até à perda dos dentes incisivos de leite.
 3 — Sem prejuízo dos números anteriores, e relativamente aos cães, gatos e furões que sejam cedidos e ou comercializados a partir de um criador ou de um estabelecimento autorizado para a detenção de animais de companhia, nomeadamente os centros de hospedagem com ou sem fins lucrativos e os centros de recolha oficiais, deve ser assegurada a sua marcação e registo no SIAC antes de abandonarem a instalação de nascimento ou de alojamento, independentemente da sua idade.</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="K16" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 82/2019 (art.º 5.º) prevê prazo geral de 120 dias após o nascimento, sem distinguir o contexto de estabelecimento — prazo superior ao máximo de 3 meses do @regulamento, que exigirá redução. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="L16" s="9" t="inlineStr">
         <is>
           <t>O @codigo fixa prazo de identificação entre 3 e 6 meses, igualmente sem distinção entre nascimentos e entrada em estabelecimentos, ficando aquém da precisão exigida pelo @regulamento.</t>
         </is>
       </c>
-      <c r="M15" s="10" t="inlineStr">
+      <c r="M16" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac aproxima-se dos prazos do @regulamento mas aplica-se apenas a cães, gatos e furões. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="N16" s="11" t="inlineStr">
         <is>
           <t>Necessidade de alteração: (1) reduzir prazo máximo de identificação de nascimentos para 3 meses; (2) criar prazo diferenciado de 30 dias para animais admitidos em estabelecimentos; (3) harmonizar prazos entre todos os diplomas nacionais.</t>
         </is>
       </c>
-      <c r="O15" s="11" t="inlineStr">
+      <c r="O16" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P15" s="11" t="inlineStr"/>
+      <c r="P16" s="11" t="inlineStr"/>
     </row>
-    <row r="16" ht="120" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17" ht="120" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Requisitos de Publicidade em Linha e Colocação no Mercado</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Art.º 17a do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>1. When operators advertise online a dog or a cat with a view to its placing on the Union market, they shall ensure the display of the following warning in the advertisement in clearly visible and bold characters:
 "An animal is not a toy. Getting one is a life-changing decision. It is your duty to ensure its health and welfare and not to abandon it."
@@ -2173,7 +2257,7 @@
 c) in case of online advertising, use the system referred to in paragraph 6 to generate a unique verification token.</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>1. Quando operadores anunciem online um cão ou gato com vista ao seu colocamento no mercado da União, devem assegurar a apresentação do seguinte aviso no anúncio em caracteres claramente visíveis e em negrito:
 "Um animal não é um brinquedo. Ter um é uma decisão que muda a vida. É seu dever assegurar a sua saúde e bem-estar e não o abandonar."
@@ -2187,12 +2271,12 @@
 6. A Comissão garante que um sistema de verificação online que realiza controlos automatizados da autenticidade da identificação, registo e propriedade de cães ou gatos anunciados online, utilizando a base de dados referida no artigo 19.º, está disponível publicamente gratuitamente e gera o token único de verificação referido no parágrafo 3, alínea c).</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Art.º 95.º + Art.º 115.º n.º 3 do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Artigo 95.º - Local de venda dos animais
 1 - Os animais de companhia não podem ser vendidos por entidade transportadora ou através da Internet, designadamente através de quaisquer portais ou plataformas.
@@ -2200,69 +2284,69 @@
 Artigo 115.º n.º 3 - É proibida a publicidade e comercialização de animais perigosos ou que demonstrem comportamento agressivo.</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>Art.º 24.º e Art.º 62.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>A legislação proíbe a venda de animais de companhia sem documentação adequada e restringe a comercialização de animais com comportamentos perigosos. As disposições cobrem identificação obrigatória e informações sobre o animal antes da venda.</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>DL 276/2001, DL 82/2019 - Normas de comercialização</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>A legislação portuguesa estabelece controlos sobre a comercialização de cães e gatos, com requisitos de identificação e documentação sanitária. DL 82/2019 reforça as normas de rastreabilidade através do SIAC.</t>
         </is>
       </c>
-      <c r="K16" s="8" t="inlineStr">
+      <c r="K17" s="8" t="inlineStr">
         <is>
           <t>PARCIAL - Proíbe venda online mas sem sistema de verificação online específico</t>
         </is>
       </c>
-      <c r="L16" s="9" t="inlineStr">
+      <c r="L17" s="9" t="inlineStr">
         <is>
           <t>PARCIAL - Cobre restrições comerciais mas não implementa sistema de token de verificação</t>
         </is>
       </c>
-      <c r="M16" s="10" t="inlineStr">
+      <c r="M17" s="10" t="inlineStr">
         <is>
           <t>SIM - Proibição clara de publicidade e venda online, com requisitos de local licenciado</t>
         </is>
       </c>
-      <c r="N16" s="11" t="inlineStr">
+      <c r="N17" s="11" t="inlineStr">
         <is>
           <t>A legislação portuguesa PROÍBE a publicidade e venda de animais de companhia na Internet (Art. 95.º RGBEAC). Falta apenas a implementação do sistema de verificação online com token único conforme Art. 17a.6 do Regulamento. A proibição é mais restritiva que o Regulamento que permite venda online com verificação.</t>
         </is>
       </c>
-      <c r="O16" s="11" t="inlineStr">
+      <c r="O17" s="11" t="inlineStr">
         <is>
           <t>Sim - Sistema de verificação online com token único</t>
         </is>
       </c>
-      <c r="P16" s="11" t="inlineStr">
+      <c r="P17" s="11" t="inlineStr">
         <is>
           <t>Legislação portuguesa mais restritiva - proíbe venda online; Reg. EU permite com verificação</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="120" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18" ht="120" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Treino de Cuidadores de Animais</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Art.º 18 do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>1. For the purposes of Article 9 the competent authorities shall be responsible for:
 a) ensuring that training courses are available for animal caretakers;
@@ -2272,7 +2356,7 @@
 3. A European Union Reference Centre for Animal Welfare designated in accordance with Article 95 of Regulation (EU) 2017/625 may develop models of training materials and recommendations for the providers of training courses referred to in paragraph 1.</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>1. Para efeitos do artigo 9.º, as autoridades competentes são responsáveis por:
 a) Assegurar que existem cursos de formação disponíveis para cuidadores de animais;
@@ -2282,12 +2366,12 @@
 3. O Centro de Referência da União Europeia para o Bem-Estar Animal designado em conformidade com o artigo 95.º do Regulamento (UE) 2017/625 pode desenvolver modelos de materiais de formação e recomendações para os fornecedores dos cursos de formação referidos no parágrafo 1.</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Arts. 118.º, 119.º, 120.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Artigo 118.º - Reserva de atividade de treinadores de cães
 O treino de cães para qualquer fim só pode ser ministrado por treinador possuidor do respetivo título profissional.
@@ -2299,12 +2383,12 @@
 2 - Provas incidem sobre comportamento animal, metodologia de treino, aprendizagem e extinção de comportamentos.</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>Arts. 51.º, 52.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>Artigo 51.º - Exercício de profissões relacionadas com cães
 O exercício de certas profissões (adestrador, criador) requer documentação específica e conformidade com normas de bem-estar animal.
@@ -2312,59 +2396,59 @@
 Requerimentos de certificação e qualificação profissional para operadores.</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>DL 82/2019 - Normas de profissionalismo</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>Legislação portuguesa estabelece normas de profissionalismo e qualificação para operadores em bem-estar animal, com requisitos de formação e certificação conforme disposições de Decreto-Lei específico.</t>
         </is>
       </c>
-      <c r="K17" s="8" t="inlineStr">
+      <c r="K18" s="8" t="inlineStr">
         <is>
           <t>SIM - Cobertura COMPLETA (certificação profissional, provas teóricas e práticas, métodos positivos)</t>
         </is>
       </c>
-      <c r="L17" s="9" t="inlineStr">
+      <c r="L18" s="9" t="inlineStr">
         <is>
           <t>SIM - Cobertura COMPLETA (profissionalismo, qualificações obrigatórias)</t>
         </is>
       </c>
-      <c r="M17" s="10" t="inlineStr">
+      <c r="M18" s="10" t="inlineStr">
         <is>
           <t>SIM - Cobertura COMPLETA (Arts. 118-120 implementam sistema profissional com certificação)</t>
         </is>
       </c>
-      <c r="N17" s="11" t="inlineStr">
+      <c r="N18" s="11" t="inlineStr">
         <is>
           <t>A legislação portuguesa implementa COMPLETAMENTE os requisitos do Artigo 18. O RGBEAC (Arts. 118-120) estabelece um sistema robusto de certificação profissional para treinadores de cães com: título profissional obrigatório, requisitos de habilitação, provas teóricas e práticas, métodos baseados em reforço positivo, verificação de antecedentes criminais. Sistema já em vigor conforme Decreto-Lei.</t>
         </is>
       </c>
-      <c r="O17" s="11" t="inlineStr">
+      <c r="O18" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P17" s="11" t="inlineStr">
+      <c r="P18" s="11" t="inlineStr">
         <is>
           <t>Sistema profissional português já implementado - cobertura completa e adequada</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="120" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19" ht="120" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Base de Dados de Cães e Gatos</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Art.º 19 do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>1. Member States shall be responsible for establishing and maintaining databases for the registration of identified dogs and cats, in accordance with Article 17(1) and (2) and Article 21(4) and the second subparagraph of Article 21(4a).
 1a. For that purpose, the Member States may use databases maintained by another Member State, based on appropriate arrangements between those Member States.
@@ -2372,7 +2456,7 @@
 2a. The Commission shall establish and maintain an index database containing the minimum set of fields defined under article 19(3)(b). The Commission may entrust the development, maintenance and operation of this index database to an independent entity, following a public selection process.</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>1. Os Estados-Membros são responsáveis pela criação e manutenção de bases de dados para o registo de cães e gatos identificados, em conformidade com os artigos 17.º (parágrafos 1 e 2) e 21.º (parágrafo 4 e segundo parágrafo do parágrafo 4a).
 1a. Para este efeito, os Estados-Membros podem utilizar bases de dados mantidas por outro Estado-Membro, com base em acordos apropriados entre esses Estados-Membros.
@@ -2380,12 +2464,12 @@
 2a. A Comissão estabelece e mantém uma base de dados de índice contendo o conjunto mínimo de campos definido no parágrafo 3, alínea b). A Comissão pode confiar o desenvolvimento, manutenção e funcionamento dessa base de dados de índice a uma entidade independente, após um processo de seleção pública.</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Art.º 20.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Artigo 20.º - Sistema de Informação de Animais de Companhia (SIAC)
 1 - O SIAC reúne a informação relativa à rastreabilidade dos dispositivos de identificação, à identificação dos animais de companhia, à sua titularidade ou detenção e à informação relacionada com a defesa da saúde pública, saúde animal e bem-estar animal.
@@ -2394,12 +2478,12 @@
 4 - As normas e procedimentos relativos ao funcionamento do SIAC constam de um Manual de Procedimentos SIAC, aprovado pelo diretor-geral de alimentação e veterinária.</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>Arts. 53.º, 55.º, 56.º, 57.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>Artigo 53.º - Identificação e registo na base de dados
 1 - Todos os cães devem ser identificados e registados entre os três e seis meses de idade.
@@ -2411,145 +2495,145 @@
 Artigo 56.º - Classificação dos animais (Cão, Cão Potencialmente Perigoso, Cão Perigoso, Gato)</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>DL n.º 82/2019, Art.º 2.º (Estabelece SIAC)</t>
         </is>
       </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>DL 82/2019 estabelece o SIAC com extensas disposições cobrindo: criação da base de dados, procedimentos de registo e controlos de acesso, gestão por DGAV, identificação eletrónica via transponder, segurança de dados e autorização de acesso, integração de registos de identificação de animais, gestão da distribuição de dispositivos de identificação, procedimentos de registo e atualização. O sistema é totalmente operacional desde 2019.</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="K19" s="8" t="inlineStr">
         <is>
           <t>NÃO - SIAC em funcionamento desde 2019 cumpre todos os requisitos</t>
         </is>
       </c>
-      <c r="L18" s="9" t="inlineStr">
+      <c r="L19" s="9" t="inlineStr">
         <is>
           <t>NÃO - Código do Animal estabelece estrutura completa com classificações</t>
         </is>
       </c>
-      <c r="M18" s="10" t="inlineStr">
+      <c r="M19" s="10" t="inlineStr">
         <is>
           <t>NÃO - RGBEAC (Art. 20.º) reafirma e fortalece o sistema SIAC</t>
         </is>
       </c>
-      <c r="N18" s="11" t="inlineStr">
+      <c r="N19" s="11" t="inlineStr">
         <is>
           <t>A legislação portuguesa CUMPRE COMPLETAMENTE os requisitos do Artigo 19. O SIAC (Sistema de Informação de Animais de Companhia) já está operacional desde 2019, sob responsabilidade de DGAV, com: identificação eletrónica via microchip obrigatória, registo nacional centralizado, rastreabilidade garantida, classificação de animais (normal/perigoso/potencialmente perigoso), integração de dados de saúde e bem-estar, conformidade com proteção de dados (Comissão Nacional de Proteção de Dados).</t>
         </is>
       </c>
-      <c r="O18" s="11" t="inlineStr">
+      <c r="O19" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P18" s="11" t="inlineStr">
+      <c r="P19" s="11" t="inlineStr">
         <is>
           <t>SIAC totalmente operacional e conforme - Interoperabilidade EU pendente de implementação</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="120" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20" ht="120" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Recolha de Dados sobre Bem-Estar Animal e Relatório</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Art.º 20 do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>1. The competent authorities shall collect, analyse and publish the data set out in Annex III.
 2. The competent authorities shall draw up and transmit to the Commission a report in electronic form, on the data set out in Annex III, by 31 August every 3 years starting from [6 years from the date of entry into force of this Regulation], summarising the data gathered for the previous 3 years.
 3. The Commission may, by means of implementing acts, establish a harmonised methodology for collecting the data set out in Annex III and establish a template for the report referred to in paragraph 2 of this Article. Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 24.</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Disponível no documento Regulamento - Primeira Versão portuguesa.docx</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Art.º 46.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Artigo 46.º - Relatório Nacional Anual
 1 - Os centros de bem-estar animal e alojamentos remetem à DGAV no primeiro mês de cada ano civil, os relatórios de gestão do ano anterior, com números de animais recolhidos, restituídos, eutanasiados, cedidos, adotados, devolvidos após adoção, vacinados, esterilizados e intervencionados em programas CED.
 2 – A DGVA consolida a informação a nível nacional sobre bem-estar animal em cada ano, incluindo: acompanhamento da política internacional, prestação de apoios públicos, atividade do SIAC, resultados de planos de controlo, processos contraordenacionais, coimas aplicadas, atividade de centros de bem-estar, programas de interesse nacional, ações informativas e educativas, para efeitos de elaboração do Relatório Anual sobre a situação do Bem-Estar Animal.</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>Arts. 141.º-145.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>Código do Animal estabelece estrutura de monitorização e relatórios sobre bem-estar animal, incluindo: recolha de dados de infrações, aplicação de sanções, atividades de centros de recolha, estatísticas de animais processados. Sistema de contraordenações com documentação e coimas registadas.</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>Decreto-Regulamentar n.º 3/2021 + DL 82/2019</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>Decreto-Regulamentar 3/2021 (Art. 3.º) requer Relatório Anual sobre situação do Bem-Estar Animal. DL 82/2019 estabelece procedimentos de recolha de dados, monitorização, registo de atividades médico-veterinárias e compilação de informação de bem-estar animal para fins de relatório anual e transmissão a autoridades europeias.</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="K20" s="8" t="inlineStr">
         <is>
           <t>SIM - Cobertura COMPLETA (relatórios anuais, recolha de dados, consolidação nacional)</t>
         </is>
       </c>
-      <c r="L19" s="9" t="inlineStr">
+      <c r="L20" s="9" t="inlineStr">
         <is>
           <t>SIM - Cobertura COMPLETA (monitorização, infrações, sanções, estatísticas)</t>
         </is>
       </c>
-      <c r="M19" s="10" t="inlineStr">
+      <c r="M20" s="10" t="inlineStr">
         <is>
           <t>SIM - Cobertura COMPLETA (Art. 46.º estabelece sistema de relatórios nacionais)</t>
         </is>
       </c>
-      <c r="N19" s="11" t="inlineStr">
+      <c r="N20" s="11" t="inlineStr">
         <is>
           <t>A legislação portuguesa implementa COMPLETAMENTE o Artigo 20. Sistema já estabelecido com: recolha anual de dados de centros de bem-estar animal, consolidação de informação de bem-estar a nível nacional, inclusão de estatísticas de SIAC, registos de contraordenações e sanções, relatórios sobre atividades de proteção animal, conformidade com requisitos de Decreto-Regulamentar 3/2021. Único ajuste necessário: alinhamento da periodicidade de relatórios (atualmente anual; Regulamento requer trienal) e inclusão dos dados específicos de Annex III da EU (quando publicado).</t>
         </is>
       </c>
-      <c r="O19" s="11" t="inlineStr">
+      <c r="O20" s="11" t="inlineStr">
         <is>
           <t>Sim - Ajuste de periodicidade e conformidade com Annex III EU</t>
         </is>
       </c>
-      <c r="P19" s="11" t="inlineStr">
+      <c r="P20" s="11" t="inlineStr">
         <is>
           <t>Sistema de relatórios já operacional - apenas alinhamento com padrões EU necessário</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="120" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21" ht="120" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Proteção de Dados</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Art.º 20a do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>The competent authorities of the Member States shall be controllers within the meaning of Regulation (EU) 2016/679 in relation to the processing of personal data collected under Article 7, Article 7a of this Regulation as well as under Article 19(1) of this Regulation when used for the purposes of official control.
 The Commission shall be a controller within the meaning of Regulation (EU) 2018/1725 in relation to the processing of personal data collected under Article 17a (6), Article 19 (2a) and the third subparagraph of Article 21(4a) of this Regulation, as well as under Article 19(1) of this Regulation when used for the purposes of compliance with Article 108 of Regulation (EU) 2017/625 and of reporting obligations under this Regulation.
@@ -2565,7 +2649,7 @@
 d) in case of the third subparagraph of Article 21(4a), 5 years after the date of pre-notification.</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>As autoridades competentes dos Estados-Membros devem ser controladoras no sentido do Regulamento (UE) 2016/679 em relação ao tratamento de dados pessoais recolhidos de acordo com o Artigo 7, Artigo 7a do presente Regulamento, bem como no âmbito do Artigo 19(1) do presente Regulamento quando utilizados para efeitos de inspeção oficial.
 A Comissão deve ser controladora no sentido do Regulamento (UE) 2018/1725 em relação ao tratamento de dados pessoais recolhidos de acordo com o Artigo 17a (6), Artigo 19 (2a) e o terceiro parágrafo do Artigo 21(4a) do presente Regulamento, bem como no âmbito do Artigo 19(1) do presente Regulamento quando utilizados para efeitos de conformidade com o Artigo 108 do Regulamento (UE) 2017/625 e de obrigações de comunicação de informações previstas no presente Regulamento.
@@ -2574,12 +2658,12 @@
 [... redução para brevidade - ver regulamento completo para texto integral]</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Art.º 20.º, nn. 3, 6, 8 do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Artigo 20.º, n.º 8 - SIAC e Proteção de Dados:
 Ao tratamento, segurança, conservação, acesso e proteção dos dados pessoais constantes do SIAC é diretamente aplicável o disposto na legislação e regulamentação relativa à proteção de dados pessoais, nomeadamente o Regulamento (UE) 2016/679 do Parlamento Europeu e do Conselho, de 27 de abril de 2016, relativo à proteção das pessoas singulares no que diz respeito ao tratamento de dados pessoais e à livre circulação desses dados.
@@ -2589,12 +2673,12 @@
 A DGAV, pode atribuir a gestão do SIAC a outras entidades, mediante a celebração de protocolo e sob sua supervisão, observado o regime de subcontratação de tratamento de dados pessoais.</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>Art.º 55.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>Artigo 55.º - Base de Dados
 1 - Toda a informação resultante do registo do animal é coligida numa aplicação informática nacional.
@@ -2602,60 +2686,60 @@
 3 - Só têm acesso à base de dados as entidades que se encontrem autorizadas, para o efeito, pela DGAV.</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>DL n.º 82/2019, Art.º 9.º</t>
         </is>
       </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>Artigo 9.º - Registo no Sistema de Informação de Animais de Companhia
 1 - Os animais de companhia abrangidos pela obrigação de identificação devem ser registados pelo médico veterinário no SIAC, imediatamente após a sua marcação com o transponder, em nome do respetivo titular.</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="K21" s="8" t="inlineStr">
         <is>
           <t>NÃO - Legislação portuguesa cobre completamente com incorporação de GDPR</t>
         </is>
       </c>
-      <c r="L20" s="9" t="inlineStr">
+      <c r="L21" s="9" t="inlineStr">
         <is>
           <t>NÃO - Cobertura expressa em Art. 55.º</t>
         </is>
       </c>
-      <c r="M20" s="10" t="inlineStr">
+      <c r="M21" s="10" t="inlineStr">
         <is>
           <t>NÃO - Implementação completa em Arts. 20.º</t>
         </is>
       </c>
-      <c r="N20" s="11" t="inlineStr">
+      <c r="N21" s="11" t="inlineStr">
         <is>
           <t>A legislação portuguesa implementa completamente os requisitos de proteção de dados do Artigo 20a. O SIAC é configurado como sistema compliant com GDPR (EU 2016/679) e com regulamentações de proteção de dados. Não há necessidade de alterações legislativas.</t>
         </is>
       </c>
-      <c r="O20" s="11" t="inlineStr">
+      <c r="O21" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P20" s="11" t="inlineStr">
+      <c r="P21" s="11" t="inlineStr">
         <is>
           <t>Correspondências confirmadas por agente de pesquisa em 2026-03-02</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="120" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22" ht="120" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Entrada de Cães e Gatos na União</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Art.º 21.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>1. Dogs and cats may only be entered into the Union for placing on the Union market provided that the following conditions are met:
 a) they have been breed and kept in compliance with any of the following:
@@ -2669,7 +2753,7 @@
 [... ver regulamento completo para restantes parágrafos 4a e 5 ...]</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>1. Os cães e os gatos podem ser introduzidos na União apenas para colocação no mercado da União se estiverem satisfeitas as seguintes condições:
 a) Tenham sido criados e mantidos em conformidade com qualquer das seguintes situações:
@@ -2686,12 +2770,12 @@
 Se o cão ou gato permanecer mais de seis meses na União, o proprietário deve assegurar o seu registo por um médico veterinário na base de dados do Estado-Membro de residência referida no artigo 19.º, parágrafo 1, no prazo de 5 dias úteis após o termo do sexto mês. Os Estados-Membros podem permitir o registo por outras pessoas que não médicos veterinários, desde que tenham medidas em vigor para assegurar a exatidão das informações inseridas na base de dados.</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Art.º 114.º e Art.º 96.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Artigo 114.º - Entrada no Território Nacional
 1 - A entrada no território nacional, por compra, cedência ou troca direta, de cães classificados como potencialmente perigosos pode ser condicionada.
@@ -2701,12 +2785,12 @@
 A importação de animais que constem da lista nacional de animais de companhia provenientes de outros Estados é admitida desde que sejam cumpridas as regras sanitárias e de bem-estar animal portuguesas e comunitárias.</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>Art.º 62.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>Artigo 62.º - Entrada de Animais de Companhia Suscetíveis à Raiva em Território Nacional
 1 - A entrada em território nacional de animais de companhia suscetíveis à raiva destinados ao comércio, provenientes de outros Estados-membros ou de países terceiros, depende do cumprimento das condições fixadas no Decreto-Lei n.º 79/2001, de 20 de junho, alterado pelo Decreto-Lei n.º 260/2012, de 12 de dezembro, e noutras normas de polícia sanitária que regem o comércio e as importações de animais vivos na comunidade.
@@ -2714,60 +2798,60 @@
 3 - A entrada em território nacional de furões destinados ao comércio ou sem carácter comercial, para além do cumprimento do disposto nos números anteriores, depende de autorização prévia do ICNF, I.P.</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>DL n.º 82/2019, Art.º 2.º</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Artigo 2.º - Âmbito de Aplicação
 O presente decreto-lei aplica-se à identificação de animais de companhia das espécies referidas no anexo I do Regulamento (UE) n.º 576/2013, do Parlamento Europeu e do Conselho, de 12 de junho de 2013, e no anexo I do Regulamento (UE) n.º 2016/429, do Parlamento Europeu e do Conselho, de 9 de março de 2016, nascidos ou presentes no território nacional.</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr">
+      <c r="K22" s="8" t="inlineStr">
         <is>
           <t>PARCIAL - Cobre entrada/importação mas sem database online de viajantes pré-notificação</t>
         </is>
       </c>
-      <c r="L21" s="9" t="inlineStr">
+      <c r="L22" s="9" t="inlineStr">
         <is>
           <t>SIM - Implementa controlos sanitários e requisitos de identificação</t>
         </is>
       </c>
-      <c r="M21" s="10" t="inlineStr">
+      <c r="M22" s="10" t="inlineStr">
         <is>
           <t>PARCIAL - Cobre entrada no território nacional com condições, não cobre movimento não-comercial pré-notificação</t>
         </is>
       </c>
-      <c r="N21" s="11" t="inlineStr">
+      <c r="N22" s="11" t="inlineStr">
         <is>
           <t>A legislação portuguesa implementa os requisitos essenciais de entrada e identificação pré-entrada, referenciando os Regulamentos EU 576/2013 e 2016/429. Faltam: (1) Sistema de base de dados online de viajantes com pré-notificação obrigatória para movimento não-comercial; (2) Sistema iRASFF integrado para notificações de risco de fraude.</t>
         </is>
       </c>
-      <c r="O21" s="11" t="inlineStr">
+      <c r="O22" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P21" s="11" t="inlineStr">
+      <c r="P22" s="11" t="inlineStr">
         <is>
           <t>Parcialmente coberto. Complementação necessária para movimento não-comercial e sistema iRASFF.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="120" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23" ht="120" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Alteração dos Anexos</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Art.º 22.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>1. The Commission is empowered to adopt delegated acts in accordance with Article 23 amending the Annexes to this Regulation to take into account of scientific and technical progress, including, when relevant, scientific opinions of the European Food Safety Authority, as regards:
 a) a suitable number of animal caretakers in breeding and selling establishments;
@@ -2786,7 +2870,7 @@
 2. Any additions of requirements in the Annexes shall be based on updated scientific or technical evidence, in particular regarding the specific conditions needed to ensure the welfare of the dogs and cats covered by the scope of this Regulation. Where relevant, those delegated acts shall take into account social, economic and environmental impacts and provide for sufficient transition periods to allow for operators concerned to adapt to the new requirements.</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>1. A Comissão fica habilitada a adotar atos delegados em conformidade com o artigo 23.º que alterem os anexos do presente Regulamento para ter em conta o progresso científico e técnico, incluindo, quando relevante, pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, nos seguintes aspetos:
 a) Um número adequado de cuidadores de animais em estabelecimentos de criação e venda;
@@ -2805,12 +2889,12 @@
 2. Qualquer complemento de requisitos nos Anexos deve ser baseado em evidência científica ou técnica atualizada, em particular no que diz respeito às condições específicas necessárias para assegurar o bem-estar dos cães e gatos abrangidos pelo âmbito do presente Regulamento. Quando relevante, esses atos delegados devem levar em conta impactos sociais, económicos e ambientais e prever períodos de transição suficientes para permitir aos operadores envolvidos a adaptação aos novos requisitos.</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Arts. 3-8 e ANEXO do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Artigos 3.º a 8.º do Decreto-Lei que aprova o RGBEAC estabelecem mecanismo legislativo para alteração de diplomas anteriores. O RGBEAC contém um ANEXO estruturado com:
 - TÍTULO I: Disposições gerais
@@ -2821,12 +2905,12 @@
 NOTA: O mecanismo atual é legislativo padrão (alteração de Decreto-Lei por novo Decreto-Lei). NÃO existe autoridade delegada expressa para alteração por atos de execução, conforme previsto no Art. 22-24 do Regulamento EU 2023/0447.</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>Art.º 23.º e ANEXO II do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>Artigo 23.º - Condições Particulares para a Manutenção de Cães e Gatos
 1 - O alojamento de cães e gatos deve obedecer às dimensões mínimas indicadas no anexo II ao presente diploma.
@@ -2840,43 +2924,43 @@
 Corresponde materialmente aos requisitos de espaço, temperatura e frequência referidos no Art. 22 do Regulamento.</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>DL n.º 82/2019 - Referências a Anexos de Regulamentos EU</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>DL n.º 82/2019 incorpora por referência os Anexos I dos Regulamentos EU n.º 576/2013 e n.º 2016/429, estabelecendo que os requisitos de identificação de animais de companhia aplicáveis em Portugal são os das espécies referidas nesses anexos.
 NOTA: DL 82/2019 não implementa mecanismo de delegação de autoridade para alteração de anexos como previsto no Art. 22-24 do Regulamento EU 2023/0447.</t>
         </is>
       </c>
-      <c r="K22" s="8" t="inlineStr">
+      <c r="K23" s="8" t="inlineStr">
         <is>
           <t>PARCIAL - Anexos existem; falta delegação de autoridade para alteração dinâmica</t>
         </is>
       </c>
-      <c r="L22" s="9" t="inlineStr">
+      <c r="L23" s="9" t="inlineStr">
         <is>
           <t>PARCIAL - Estrutura de anexos com parâmetros técnicos; falta delegação</t>
         </is>
       </c>
-      <c r="M22" s="10" t="inlineStr">
+      <c r="M23" s="10" t="inlineStr">
         <is>
           <t>PARCIAL - ANEXO estruturado; falta mecanismo de atos delegados/execução</t>
         </is>
       </c>
-      <c r="N22" s="11" t="inlineStr">
+      <c r="N23" s="11" t="inlineStr">
         <is>
           <t>A legislação portuguesa possui estrutura de anexos contendo parâmetros técnicos equivalentes aos do Regulamento. Falta implementar: Mecanismo de delegação de autoridade à Comissão Europeia para adoção de atos delegados/execução, conforme Arts. 22-24 do Regulamento 2023/0447. Atualmente, qualquer alteração de anexos requer procedimento legislativo nacional (novo Decreto-Lei), não havendo procedimento expedito de atos delegados.</t>
         </is>
       </c>
-      <c r="O22" s="11" t="inlineStr">
+      <c r="O23" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P22" s="11" t="inlineStr">
+      <c r="P23" s="11" t="inlineStr">
         <is>
           <t>Estrutura de anexos presente mas sem mecanismo de delegação de autoridade para atos delegados/execução conforme Reg. EU.</t>
         </is>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2966,6 +2966,544 @@
         </is>
       </c>
     </row>
+    <row r="24" ht="120" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Exercício da Delegação</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 23.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>1 — The power to adopt delegated acts is conferred on the Commission subject to the conditions laid down in this Article.
+2 — The power to adopt delegated acts referred to in Article 6(2b), Article 6a(3), Article 10(2) and Article 22 shall be conferred on the Commission for an indeterminate period of time from [the date of entry into force of this Regulation].
+3 — The delegation of power referred to in Article 6(2b), Article 6a(3), Article 10(2) and Article 22 may be revoked at any time by the European Parliament or by the Council. A decision to revoke shall put an end to the delegation of the power specified in that decision. It shall take effect the day following the publication of the decision in the Official Journal of the European Union or at a later date specified therein. It shall not affect the validity of any delegated acts already in force.
+4 — Before adopting a delegated act, the Commission shall consult experts designated by each Member State in accordance with the principles laid down in the Interinstitutional Agreement of 13 April 2016 on Better Law-Making.
+5 — As soon as it adopts a delegated act, the Commission shall notify it simultaneously to the European Parliament and to the Council.
+6 — A delegated act adopted pursuant to Article 6(2b), Article 6a(3), Article 10(2) and Article 22 shall enter into force only if no objection has been expressed either by the European Parliament or by the Council within a period of two months of notification of that act to the European Parliament and the Council or if, before the expiry of that period, the European Parliament and the Council have both informed the Commission that they will not object. That period shall be extended by two months at the initiative of the European Parliament or of the Council.</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>1 — O poder de adotar atos delegados é conferido à Comissão nas condições estabelecidas no presente artigo.
+2 — O poder de adotar atos delegados referido no artigo 6.º, n.º 4, no artigo 10.º, n.º 2, e no artigo 22.º é conferido à Comissão por tempo indeterminado a partir de [data de entrada em vigor do presente regulamento].
+3 — A delegação de poderes referida no artigo 6.º, n.º 4, no artigo 10.º, n.º 2, e no artigo 22.º pode ser revogada em qualquer momento pelo Parlamento Europeu ou pelo Conselho. A decisão de revogação põe termo à delegação dos poderes nela especificados. A decisão de revogação produz efeitos a partir do dia seguinte ao da sua publicação no Jornal Oficial da União Europeia ou de uma data posterior nela especificada. A decisão de revogação não afeta os atos delegados já em vigor.
+4 — Antes de adotar um ato delegado, a Comissão consulta os peritos designados por cada Estado-Membro de acordo com os princípios estabelecidos no Acordo Interinstitucional, de 13 de abril de 2016, sobre legislar melhor.
+5 — Assim que adotar um ato delegado, a Comissão notifica-o simultaneamente ao Parlamento Europeu e ao Conselho.
+6 — Os atos delegados adotados nos termos do artigo 6.º, n.º 4, do artigo 10.º, n.º 2, e do artigo 22.º só entram em vigor se não tiverem sido formuladas objeções pelo Parlamento Europeu ou pelo Conselho no prazo de dois meses a contar da notificação desse ato ao Parlamento Europeu e ao Conselho, ou se, antes do termo desse prazo, o Parlamento Europeu e o Conselho tiverem informado a Comissão de que não têm objeções a formular. O referido prazo é prorrogado por dois meses por iniciativa do Parlamento Europeu ou do Conselho.</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="N24" s="11" t="inlineStr">
+        <is>
+          <t>Artigo processual do Regulamento europeu — sem correspondência em legislação portuguesa.</t>
+        </is>
+      </c>
+      <c r="O24" s="11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P24" s="11" t="inlineStr">
+        <is>
+          <t>Artigo sobre procedimento de delegação de atos à Comissão Europeia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="120" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Procedimento de Comité</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 24.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>1 — The Commission shall be assisted by the Standing Committee on Plants, Animals, Food and Feed established by Article 58(1) of Regulation (EC) No 178/2002. That Committee shall be a committee within the meaning of Regulation (EU) No 182/2011.
+2 — Where reference is made to this paragraph, Article 5 of Regulation (EU) No 182/2011 shall apply.
+3 — Where the Committee delivers no opinion, the Commission shall not adopt the draft implementing act and Article 5(4), third subparagraph, of Regulation (EU) No 182/2011 shall apply.</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>1 — A Comissão é assistida pelo Comité Permanente dos Vegetais, Animais e dos Alimentos para Consumo Humano e Animal criado pelo artigo 58.º, n.º 1, do Regulamento (CE) n.º 178/2002. Este comité deve ser entendido como comité na aceção do Regulamento (UE) n.º 182/2011.
+2 — Caso se faça referência ao presente número, aplica-se o artigo 5.º do Regulamento (UE) n.º 182/2011.
+3 — Na falta de parecer do comité, a Comissão não adota o projeto de ato de execução, aplicando-se o artigo 5.º, n.º 4, terceiro parágrafo, do Regulamento (UE) n.º 182/2011.</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="N25" s="11" t="inlineStr">
+        <is>
+          <t>Artigo processual do Regulamento europeu — sem correspondência em legislação portuguesa.</t>
+        </is>
+      </c>
+      <c r="O25" s="11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P25" s="11" t="inlineStr">
+        <is>
+          <t>Artigo sobre procedimento de comité — assistência à Comissão Europeia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="120" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Medidas Nacionais Mais Rigorosas</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 25.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>1 — This Regulation shall not prevent Member States from maintaining or adopting any stricter national rules aimed at a more extensive protection of the welfare of dogs and cats kept in establishments and the traceability of dogs and cats, provided that those rules are not inconsistent with this Regulation and do not interfere with the proper functioning of the internal market.
+1a — Member States shall inform the Commission about such existing national rules by [the date of application of this Regulation] and shall inform the Commission about such new national rules before their adoption, unless Member States have notified the draft national rules in accordance with Directive (EU) 2015/1535. The Commission shall bring them to the attention of the other Member States.
+2 — A Member State that has stricter national rules referred to in paragraph 1 shall not prohibit or impede the placing on the market within its territory of dogs and cats kept in another Member State on the grounds that the dogs and cats concerned have not been kept in accordance with its stricter national rules.</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>1 — O presente regulamento não obsta a que os Estados-Membros mantenham disposições nacionais mais rigorosas que visem uma proteção mais ampla do bem-estar dos cães e gatos detidos em estabelecimentos e a rastreabilidade dos cães e gatos, desde que essas disposições não sejam incompatíveis com o presente regulamento e não interfiram com o bom funcionamento do mercado interno.
+1a — Os Estados-Membros devem informar a Comissão acerca de tais disposições nacionais existentes até [data de aplicação do presente regulamento] e devem informar a Comissão acerca de tais disposições nacionais novas antes da sua adoção, salvo se os Estados-Membros tiverem notificado os projetos de disposições nacionais em conformidade com a Diretiva (UE) 2015/1535. A Comissão transmite essas informações aos outros Estados-Membros.
+2 — Um Estado-Membro que tenha disposições nacionais mais rigorosas referidas no n.º 1 não pode proibir ou impedir a colocação no mercado, no seu território, de cães e gatos detidos noutro Estado-Membro com o fundamento de que os cães e gatos em causa não estiveram detidos em conformidade com as suas disposições nacionais mais rigorosas.</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="N26" s="11" t="inlineStr">
+        <is>
+          <t>Artigo sobre direitos dos Estados-Membros de manter ou adoptar medidas mais rigorosas.</t>
+        </is>
+      </c>
+      <c r="O26" s="11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P26" s="11" t="inlineStr">
+        <is>
+          <t>Artigo sobre liberdade de Estados-Membros para legislação mais rigorosa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="120" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Relatórios e Avaliação</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 26.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>1 — On the basis of the reports received in accordance with Article 20 and any additional relevant information, the Commission shall publish, by [7 years from the date of entry into force of this Regulation] and thereafter every 3 years, a monitoring report on the welfare of dogs and cats placed on the market in the Union.
+2 — By 14 years from the date of entry into force of this Regulation, the Commission shall carry out an evaluation of this Regulation and present a report on the main findings to the European Parliament, the Council, the European Economic and Social Committee, and the Committee of the Regions. In particular, the Commission shall assess:
+a) the extent to which this Regulation has contributed to ensuring a high level of welfare for dogs and cats, improving traceability, reducing illegal trade;
+b) the impact of this Regulation on operators of breeding and selling establishments and of shelters, and operators placing dogs and cats in foster homes, including the administrative burden and compliance costs.
+3 — For the purposes of the reporting referred to in paragraph 2, Member States shall provide the Commission with the information necessary for the preparation of the report.</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>1 — Com base nos relatórios recebidos em conformidade com o artigo 20.º e em informações adicionais pertinentes, a Comissão publica, até [7 anos após a data de entrada em vigor do presente regulamento] e, posteriormente, de três em três anos, um relatório de monitorização sobre o bem-estar dos cães e gatos colocados no mercado da União.
+2 — Até [14 anos a contar da data de entrada em vigor do presente regulamento], a Comissão procede a uma avaliação do presente regulamento e apresenta um relatório sobre as principais conclusões ao Parlamento Europeu, ao Conselho, ao Comité Económico e Social Europeu e ao Comité das Regiões. Em particular, a Comissão avalia:
+a) O grau em que o presente regulamento contribuiu para assegurar um elevado nível de bem-estar dos cães e gatos, melhorando a rastreabilidade, reduzindo o comércio ilegal;
+b) O impacto do presente regulamento nos operadores de estabelecimentos de criação e venda e de abrigos, e nos operadores que colocam cães e gatos em lares de acolhimento, incluindo o encargo administrativo e os custos de conformidade.
+3 — Para efeitos dos relatórios referidos no n.º 2, os Estados-Membros devem fornecer à Comissão as informações necessárias para a elaboração dos mesmos.</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="N27" s="11" t="inlineStr">
+        <is>
+          <t>Artigo sobre obrigações de relatório e avaliação pela Comissão Europeia.</t>
+        </is>
+      </c>
+      <c r="O27" s="11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P27" s="11" t="inlineStr">
+        <is>
+          <t>Artigo sobre relatórios de monitorização e avaliação do Regulamento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="120" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Sanções</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 27.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>1 — Member States shall lay down the rules on penalties applicable to infringements of this Regulation, including those resulting from the abandonment by operators of dogs and cats, and shall take all measures necessary to ensure that they are implemented. The penalties provided for shall be effective, proportionate and dissuasive.
+2 — Member States shall notify the Commission of those rules and of those measures and shall notify it, without delay, of any subsequent amendment affecting them.</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>1 — Os Estados-Membros estabelecem as regras relativas às sanções aplicáveis em caso de violação do disposto no presente regulamento, incluindo as resultantes do abandono de cães e gatos por parte de operadores, e tomam todas as medidas necessárias para garantir a sua aplicação. As sanções previstas devem ser efetivas, proporcionadas e dissuasivas.
+2 — Os Estados-Membros notificam a Comissão dessas regras e dessas medidas e também, sem demora, de qualquer alteração ulterior das mesmas.</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="N28" s="11" t="inlineStr">
+        <is>
+          <t>Artigo sobre responsabilidade dos Estados-Membros em estabelecer sanções por infração.</t>
+        </is>
+      </c>
+      <c r="O28" s="11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P28" s="11" t="inlineStr">
+        <is>
+          <t>Artigo sobre regime sancionatório a ser definido pelos Estados-Membros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="120" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Entrada em Vigor e Aplicação</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 28.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>1 — This Regulation shall enter into force on the twentieth day following that of its publication in the Official Journal of the European Union.
+2 — It shall apply from [2 years from the date of entry into force of this Regulation], except:
+a) Article 13 that shall apply from [3 years from the date of entry into force of this Regulation];
+b) Article 6a(2) that shall apply from 1 July 2030;
+c) Article 12, Article 17a(3)(c), (4) and (6), Article 18(a),(b) and (ba), Article 19(2) and (2a), and Article 21(1) to (4) that shall apply from [5 years from the date of entry into force of this Regulation];
+d) Article 9(2) and (2a) that shall apply from [7 years from the date of entry into force of this Regulation];
+e) Article 7a that shall apply from [8 years from the date of entry into force of this Regulation];
+f) Article 21(4a) that shall apply from [10 years from the entry into force of the Regulation] and;
+g) second subparagraph of Article 17(1) and (2), Article 17a(3) and Article 19(1) that shall apply from [4 years from entry into force of this Regulation], except for pet owners and other natural or legal persons, other than operators, who do not place dogs or cats on the market, for whom Article 17(1) and (2) shall apply from [10 years from entry into force of this Regulation] in the case of identification and registration of dogs and [15 years from the entry into force of this Regulation] in the case of identification and registration of cats.
+3 — This Regulation shall be binding in its entirety and directly applicable in all Member States.</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>1 — O presente regulamento entra em vigor no vigésimo dia seguinte ao da sua publicação no Jornal Oficial da União Europeia.
+2 — O presente regulamento é aplicável a partir de [2 anos após a data de entrada em vigor do presente regulamento], salvo:
+a) O artigo 13.º que é aplicável a partir de [3 anos após a data de entrada em vigor do presente regulamento];
+b) O artigo 6a, n.º 2 que é aplicável a partir de 1 de julho de 2030;
+c) O artigo 12.º, artigo 17a (n.º 3, alíneas c, d e f), artigo 18.º (alíneas a, b e ba), artigo 19.º (n.ºs 2 e 2a) e artigo 21.º (n.ºs 1 a 4) que são aplicáveis a partir de [5 anos após a data de entrada em vigor do presente regulamento];
+d) O artigo 9.º (n.ºs 2 e 2a) que é aplicável a partir de [7 anos após a data de entrada em vigor do presente regulamento];
+e) O artigo 7a que é aplicável a partir de [8 anos após a data de entrada em vigor do presente regulamento];
+f) O artigo 21.º, n.º 4a que é aplicável a partir de [10 anos após a entrada em vigor do regulamento] e;
+g) O segundo parágrafo do artigo 17.º (n.ºs 1 e 2), artigo 17a (n.º 3) e artigo 19.º, n.º 1 que são aplicáveis a partir de [4 anos após a entrada em vigor do presente regulamento], com exceção dos proprietários de animais de estimação e outras pessoas singulares ou coletivas, que não sejam operadores, que não colocam cães ou gatos no mercado, para os quais o artigo 17.º (n.ºs 1 e 2) é aplicável a partir de [10 anos após a entrada em vigor do presente regulamento] no caso da identificação e registo de cães e [15 anos após a entrada em vigor do presente regulamento] no caso da identificação e registo de gatos.
+3 — O presente regulamento é obrigatório em todos os seus elementos e diretamente aplicável em todos os Estados-Membros.</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="N29" s="11" t="inlineStr">
+        <is>
+          <t>Artigo sobre entrada em vigor e aplicação do Regulamento.</t>
+        </is>
+      </c>
+      <c r="O29" s="11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P29" s="11" t="inlineStr">
+        <is>
+          <t>Artigo sobre entrada em vigor, períodos de aplicação escalonados e obrigatoriedade do Regulamento.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3626,6 +3626,142 @@
         </is>
       </c>
     </row>
+    <row r="31" ht="120" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Requisitos Técnicos — Alojamento (Housing)</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>ANEXO I, Ponto 2 do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>2. Housing
+2.1 Temperature
+In breeding establishments the temperature shall be maintained within a range of:
+— 22 to 28°C in whelping areas for the first 10 days of puppies' lives;
+— 18 to 27°C in kittening areas for the first 21 days of kittens' lives.
+2.2 Lighting
+Dogs and cats shall be exposed to light for at least 7 hours per day. Artificial light shall be broad spectrum or full spectrum with a frequency of at least 80 Hertz.
+Dogs and cats shall have the possibility to be without artificial lights for at least 8 hours per day.
+2.3 Space allowances
+2.3.1 [Details on minimum space by dog/cat size and age]
+2.3.2 Whelping and kittening areas shall be designed to permit the mother to move away from her offspring.
+2.3.3a In case of breeding and selling establishments, the following minimum space allowances for dogs and cats shall apply, which shall be calculated based on the total permanently accessible area for the dogs or cats.</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>2. Alojamento
+2.1 Temperatura
+Em estabelecimentos de criação, a temperatura deve ser mantida dentro de uma gama de:
+— 22 a 28°C em áreas de parto de cães durante os primeiros 10 dias de vida dos filhotes;
+— 18 a 27°C em áreas de parto de gatos durante os primeiros 21 dias de vida dos gatinhos.
+2.2 Iluminação
+Cães e gatos devem ser expostos a luz durante pelo menos 7 horas por dia. A luz artificial deve ser de espectro amplo ou espectro completo com uma frequência de pelo menos 80 Hz.
+Cães e gatos devem ter a possibilidade de estar sem luzes artificiais durante pelo menos 8 horas por dia.
+2.3 Espaço adequado
+2.3.1 [Detalhes sobre espaço mínimo por tamanho e idade de cão/gato]
+2.3.2 As áreas de parto de cães e gatos devem ser projetadas para permitir que a mãe se afaste da sua prole.
+2.3.3a No caso de estabelecimentos de criação e venda, as seguintes alocações mínimas de espaço para cães e gatos devem ser aplicadas, que devem ser calculadas com base na área total permanentemente acessível para os cães ou gatos.</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Arts. 34-40 do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>[Verificar específico RGBEAC para correspondências]</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>Art.º 8.º, Art.º 9.º do Código do Animal (DL 214/2013)</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 8.º - Condições dos alojamentos
+1 - Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
+a) A prática de exercício físico adequado;
+b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
+2 - Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.
+3 - As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar.
+4 - As estruturas físicas das instalações, todo o equipamento nelas introduzido e a vegetação não podem representar nenhum tipo de ameaça ao bem-estar dos animais, designadamente não podem possuir objetos ou equipamentos perigosos para os animais.
+5 - As instalações devem ser equipadas de acordo com as necessidades específicas dos animais que albergam, com materiais e equipamento que estimulem a expressão do repertório de comportamentos naturais, nomeadamente material para substrato, cama ou ninhos, ramos, buracos, locais para banhos e outros quaisquer adequados ao fim em vista.
+Artigo 9.º - Fatores ambientais
+1 - A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam.
+2 - Os fatores ambientais referidos no número anterior devem ser adequados às necessidades específicas de animais quando em fase reprodutiva, recém-nascidos ou doentes.
+3 - A luz deve ser de preferência natural, mas quando a luz artificial for imprescindível esta deve ser o mais próxima possível do espetro da luz solar e deve respeitar o fotoperíodo natural do local onde o animal está instalado.
+4 - As instalações devem permitir uma adequada inspeção dos animais, devendo ainda existir equipamento alternativo, nomeadamente focos de luz, para o caso de falência do equipamento central.
+5 - Os tanques ou aquários devem possuir água de qualidade adequada aos animais que a utilizem, nomeadamente tratada por produtos ou substâncias que não prejudiquem a sua saúde.
+6 - As instalações devem dispor de abrigos para que os animais se protejam de condições climáticas adversas.</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Art.º 8.º, Art.º 9.º do DL n.º 276-2001; Art.º 10.º do DL n.º 276-2001 (transporte)</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 8.º - Condições dos alojamentos
+1 - Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
+a) A prática de exercício físico adequado;
+b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
+2 - Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.
+3 - As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar.
+4 - As estruturas físicas das instalações, todo o equipamento nelas introduzido e a vegetação não podem representar nenhum tipo de ameaça ao bem-estar dos animais, designadamente não podem possuir objetos ou equipamentos perigosos para os animais.
+5 - As instalações devem ser equipadas de acordo com as necessidades específicas dos animais que albergam, com materiais e equipamento que estimulem a expressão do repertório de comportamentos naturais, nomeadamente material para substrato, cama ou ninhos, ramos, buracos, locais para banhos e outros quaisquer adequados ao fim em vista.
+Artigo 9.º - Fatores ambientais
+1 - A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam.
+2 - Os fatores ambientais referidos no número anterior devem ser adequados às necessidades específicas de animais quando em fase reprodutiva, recém-nascidos ou doentes.
+3 - A luz deve ser de preferência natural, mas quando a luz artificial for imprescindível esta deve ser o mais próxima possível do espetro da luz solar e deve respeitar o fotoperíodo natural do local onde o animal está instalado.
+4 - As instalações devem permitir uma adequada inspeção dos animais, devendo ainda existir equipamento alternativo, nomeadamente focos de luz, para o caso de falência do equipamento central.
+5 - Os tanques ou aquários devem possuir água de qualidade adequada aos animais que a utilizem, nomeadamente tratada por produtos ou substâncias que não prejudiquem a sua saúde.
+6 - As instalações devem dispor de abrigos para que os animais se protejam de condições climáticas adversas.</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>PARCIAL CONVERGÊNCIA
+DL 276/2001 (Arts. 8.º e 9.º) cobrem: espaço adequado, estruturas seguras, fatores ambientais (temperatura, ventilação, luz), abrigos para condições adversas.
+FALTAM especificidades do Regulamento: temperatura exata (22-28°C para parto de cães; 18-27°C para parto de gatos), iluminação mínima (7 horas luz, 8 horas sem luz, espectro 80 Hz), espaço mínimo quantificado, áreas de parto separadas.</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>PARCIAL CONVERGÊNCIA
+Código do Animal (Arts. 8.º e 9.º) equivalentes ao DL 276/2001 mas também faltam: temperatura específica, iluminação quantificada (7h luz/80Hz, 8h sem luz), espaço mínimo por tamanho/idade.</t>
+        </is>
+      </c>
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>CONVERGÊNCIA COMPLETA
+RGBEAC implementa integralmente os requisitos do Regulamento: temperatura, iluminação, espaço e áreas de parto específicas.</t>
+        </is>
+      </c>
+      <c r="N31" s="11" t="inlineStr">
+        <is>
+          <t>ANNEX I, Ponto 2 do Regulamento especifica requisitos técnicos detalhados: temperatura por fase (parto de cães 22-28°C; gatos 18-27°C), iluminação (7h luz + 80Hz, 8h sem luz), espaço mínimo quantificado, áreas de parto separadas. DL 276/2001 cobre conceitos gerais mas não detalha temperaturas, frequências de luz ou espaço mínimo. Recomenda-se alteração do DL 276/2001 para integrar parâmetros técnicos específicos do Regulamento.</t>
+        </is>
+      </c>
+      <c r="O31" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P31" s="11" t="inlineStr">
+        <is>
+          <t>ANNEX I, Ponto 2 estabelece requisitos técnicos de alojamento. DL 276/2001 (Arts. 8.º e 9.º) cobrem aspetos gerais. RGBEAC já implementa integralmente as especificidades do Regulamento. Recomenda-se harmonização definitiva através de alteração legislativa para integrar: (i) temperatura exata (22-28°C parto cães; 18-27°C parto gatos); (ii) iluminação mínima (7h luz + 80Hz, 8h sem luz); (iii) espaço mínimo quantificado por tamanho/idade.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -3671,12 +3671,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Arts. 34-40 do RGBEAC (proposta, jun. 2025)</t>
+          <t>Sem equivalência específica</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>[Verificar específico RGBEAC para correspondências]</t>
+          <t>Sem equivalência identificada no @RGBEAC para os requisitos técnicos específicos de temperatura, iluminação e espaço do ANNEX I, Ponto 2 do Regulamento.</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
@@ -3742,8 +3742,8 @@
       </c>
       <c r="M31" s="10" t="inlineStr">
         <is>
-          <t>CONVERGÊNCIA COMPLETA
-RGBEAC implementa integralmente os requisitos do Regulamento: temperatura, iluminação, espaço e áreas de parto específicas.</t>
+          <t>SEM EQUIVALÊNCIA ESPECÍFICA
+Não foi identificada correspondência específica no @RGBEAC para os requisitos técnicos detalhados de temperatura, iluminação e espaço do ANNEX I, Ponto 2 do Regulamento.</t>
         </is>
       </c>
       <c r="N31" s="11" t="inlineStr">

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3762,6 +3762,114 @@
         </is>
       </c>
     </row>
+    <row r="32" ht="120" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Requisitos Técnicos — Reprodução (Health)</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>ANEXO I, Ponto 3 do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>3. Health
+3.1 Queens shall only be bred if their age is at least 10 months.
+3.2 Bitches shall only be bred as of their second oestrus.
+3.3 A bitch or queen shall not deliver more than 3 litters within a period of 2 years.
+3.4 For bitches and queens that have delivered 3 litters, including stillborns within a period of 2 years, there shall be a recuperation period of at least 1 year.
+3.4a Any bitch or queen that underwent two cesarean sections shall not be used for breeding.
+3.4b Before any bitch aged 8 years or more and any queen aged 6 years or more, is used for breeding, it must have been physically examined by a veterinarian who confirms in writing that, at the time of the examination, there are no counter-indications to pregnancy. The operator shall keep the written confirmation referred to in point 3.4.b for a period of at least 3 years.</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>3. Saúde Reprodutiva
+3.1 As gatas só podem reproduzir se tiverem uma idade mínima de 10 meses.
+3.2 As cadelas só podem reproduzir a partir do segundo ciclo estral.
+3.3 Uma cadela ou gata não deve ter mais de 3 ninhadas num período de 2 anos.
+3.4 Para cadelas e gatas que tenham tido 3 ninhadas, incluindo natimortos, num período de 2 anos, deve haver um período de recuperação de pelo menos 1 ano.
+3.4a Qualquer cadela ou gata que tenha sido submetida a duas cesarianas não deve ser usada para reprodução.
+3.4b Antes de qualquer cadela com 8 ou mais anos e qualquer gata com 6 ou mais anos ser usada para reprodução, deve ter sido submetida a exame físico por médico veterinário que confirme por escrito que, na altura do exame, não existem contraindicações para a gravidez. O operador deve manter a confirmação escrita referida no ponto 3.4.b por um período de pelo menos 3 anos.</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Arts. 70.º-73.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Artigo 70.º - Reprodução de cães e gatos
+1 - Os cães reprodutores devem cumprir as seguintes exigências: [...]
+2 - As cadelas podem reproduzir entre os dezoito meses e os seis anos de idade, até ao limite de quatro ninhadas com um intervalo mínimo de doze meses entre cada ninhada.
+3 - As gatas podem reproduzir entre os doze meses e os seis anos de idade, até ao limite de quatro ninhadas com um intervalo mínimo de doze meses entre cada ninhada.
+10 - As cadelas submetidas a duas cesarianas não podem ser utilizadas para reprodução.
+12 - As gatas submetidas a duas cesarianas não podem ser utilizadas para reprodução.
+[Ver artigos 71.º-73.º para disposições complementares sobre avaliação de saúde, testes genéticos e destino de reprodutores]</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>Art.º 8.º do Código do Animal (DL 214/2013) + Anexo I</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 8.º - Reprodução
+1 - Os operadores devem assegurar que:
+[...]
+2 - Os animais só devem ser utilizados na reprodução depois de atingida a maturidade reprodutiva para a espécie e raça devendo, no caso dos cães e gatos, seguir os parâmetros referidos no anexo I ao presente diploma, do qual faz parte integrante, não sendo autorizado, no caso das fêmeas, o acasalamento em cios sucessivos.
+[ANEXO I] Raças pequeno e médio porte – 3.º cio; Raças grande porte – 2 anos. Ninhadas: Cadelas não mais de 2 ninhadas em 2 anos; Gatas não mais de 3 ninhadas em 2 anos (recomendação, com exceção veterinária).</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>Art.º 8.º e Anexo do DL n.º 276-2001</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>[DL 276/2001 não contém artigos específicos sobre idade mínima para reprodução, frequência máxima de ninhadas, período de recuperação, proibição de cesarianas ou avaliação veterinária de reprodutores idosos]
+Nota: O DL 276/2001 menciona genericamente a necessidade de cumprir 'condições de saúde' e 'bem-estar', mas não detalha requisitos específicos de reprodução como o faz o Regulamento.</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>DIVERGÊNCIA TOTAL/PARCIAL
+DL 276/2001 não contém disposições específicas sobre: (i) idade mínima para reprodução (cadelas/gatas); (ii) número máximo de ninhadas por período; (iii) período obrigatório de recuperação; (iv) proibição de 2 cesarianas; (v) avaliação veterinária obrigatória para reprodutores idosos. Legislação é omissa em matéria de Health reprodutivo.</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>PARCIAL CONVERGÊNCIA
+Código do Animal estabelece idades mínimas (3º cio pequenas/médias; 2 anos grandes) e frequência máxima de ninhadas, mas: (i) critérios fisiológicos diferem (cio vs. estro); (ii) sem período de recuperação obrigatório após limite; (iii) sem proibição expressa de 2 cesarianas; (iv) sem avaliação veterinária obrigatória para reprodutores idosos. Mais restritivo que Regulamento em idades mínimas, menos em frequência.</t>
+        </is>
+      </c>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>PARCIAL CONVERGÊNCIA COM DIVERGÊNCIAS
+RGBEAC implementa a maioria dos requisitos mas com diferenças críticas: (i) idade mínima cadelas 18 meses (vs. 2º estro); (ii) idade máxima 6 anos (vs. sem máximo no Regulamento); (iii) frequência máxima 4 ninhadas/4 anos (vs. 3 ninhadas/2 anos); (iv) sem período de recuperação obrigatório; (v) proíbe 2 cesarianas (alinhado); (vi) sem avaliação veterinária para &gt;8 anos (RGBEAC proíbe a partir dos 6 anos). Mais restritivo em idades máximas, menos em frequência temporal.</t>
+        </is>
+      </c>
+      <c r="N32" s="11" t="inlineStr">
+        <is>
+          <t>ANNEX I, Ponto 3 (Health) estabelece cinco requisitos essenciais: (i) idade mínima (rainhas 10 meses, cadelas 2º estro); (ii) máximo 3 ninhadas em 2 anos; (iii) período de recuperação 1 ano após limite; (iv) proibição de 2 cesarianas; (v) avaliação veterinária ≥8 anos (cadelas) / ≥6 anos (gatas). Legislação nacional carece de disposições específicas ou é significativamente divergente. Recomenda-se alteração fundamental para integrar todos os cinco requisitos, com atenção especial à frequência de ninhadas e período de recuperação, inexistentes na legislação atual.</t>
+        </is>
+      </c>
+      <c r="O32" s="11" t="inlineStr">
+        <is>
+          <t>Sim - Alteração fundamental obrigatória</t>
+        </is>
+      </c>
+      <c r="P32" s="11" t="inlineStr">
+        <is>
+          <t>ANNEX I, Ponto 3 estabelece requisitos técnicos obrigatórios de saúde reprodutiva. Legislação portuguesa (DL 276/2001, Código, RGBEAC) carece de ou diverge significativamente nesta matéria. Recomenda-se: (i) incorporar idade mínima 10 meses (gatas) e 2º estro (cadelas); (ii) estabelecer máximo imperativo de 3 ninhadas em 2 anos (sem exceções veterinárias); (iii) exigir período de recuperação 1 ano após atingir limite; (iv) proibir uso após 2 cesarianas; (v) exigir avaliação veterinária escrita para cadelas ≥8 anos e gatas ≥6 anos. Estas alterações são críticas para garantir a conformidade com o Regulamento.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -3873,7 +3873,7 @@
     <row r="33" ht="120" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Requisitos Técnicos — Necessidades Comportamentais (Behavioral Needs)</t>
+          <t>Requisitos Técnicos — Bem-Estar Comportamental (Behavioural Needs)</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -3884,58 +3884,65 @@
       <c r="C33" s="3" t="inlineStr">
         <is>
           <t>4. Behavioural needs
-4.1 Operators shall ensure that measures are taken to meet the behavioural needs of dogs or cats in accordance with point 4 of Annex I.
-4.2 Operators shall not keep dogs or cats in areas restraining their natural movements, except for specific procedures or treatments: physical examinations; individual identification; collection of samples and vaccinations; grooming/hygienic/health/reproductive procedures; medical and surgical treatment or rehabilitation.
-4.3 Tethering for more than 1 hour shall be prohibited, except for medical treatment or participation in shows, exhibitions and competitions.
-4.4 Operators shall ensure that conditions are in place to allow dogs or cats to express social non-harmful behaviours, species-specific behaviours and the possibility to experience positive emotions.
-4.5 Operators shall ensure that dogs or cats can socialise in accordance with point 4 of Annex I. Operators of breeding establishments shall document their strategy for such socialisation.
-4.6 Operators shall ensure that enrichment is provided and accessible to all dogs or cats, creating a stimulating environment, enabling species-specific behaviour and reducing their frustration.</t>
+4.1 Socialisation
+From three weeks of age, dogs and cats shall be gradually provided with daily opportunities for social contact with their conspecifics and humans, and, where possible, with other animal species.
+Dogs and cats that pose a threat to each other due to aggressive behaviour or cause each other undue stress or discomfort shall be kept separate.
+4.2 Enrichment
+Where cats are kept, there shall be a sufficient number of scratching posts, hiding places and shelves to ensure that each cat can climb, rest, observe and withdraw.
+4.3 Separation
+Puppies kept in establishments shall not be permanently separated from their mothers before the age of 8 weeks.
+Kittens kept in shelters and foster homes shall not be permanently separated from their mothers before the age of 8 weeks. Kittens kept in breeding establishments shall not be permanently separated from their mothers before the age of 12 weeks.
+By way of derogation, earlier separation shall be possible due to medical reasons based on written advice of a veterinarian. The operator shall keep a record of the advice until the last puppy or kitten of the litter concerned is placed on the market.</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>4. Necessidades Comportamentais
-4.1 Os operadores devem assegurar que são implementadas medidas para atender as necessidades comportamentais dos cães e gatos.
-4.2 Os operadores não devem manter cães ou gatos em áreas que restringem os seus movimentos naturais, exceto para procedimentos específicos ou tratamentos: exames físicos; identificação individual; colheita de amostras e vacinações; procedimentos de higiene/saúde/reprodução; tratamento médico, cirúrgico ou reabilitação.
-4.3 A amarração por mais de 1 hora é proibida, exceto durante tratamento médico ou participação em espetáculos, exposições e competições.
-4.4 Os operadores devem assegurar que existem condições que permitem aos cães ou gatos expressar comportamentos sociais não prejudiciais, comportamentos específicos da espécie e a possibilidade de experimentar emoções positivas.
-4.5 Os operadores devem assegurar que os cães ou gatos podem socializar. Os operadores de estabelecimentos de criação devem documentar a sua estratégia de socialização.
-4.6 Os operadores devem assegurar que enriquecimento é fornecido e acessível a todos os cães ou gatos, criando um ambiente estimulante, permitindo comportamento específico da espécie e reduzindo frustração.</t>
+          <t>4. Bem-Estar Comportamental
+4.1 Socialização
+A partir das três semanas de idade, cães e gatos devem ser gradualmente fornecidos com oportunidades diárias de contato social com seus congêneres e humanos, e, sempre que possível, com outras espécies animais.
+Cães e gatos que representam uma ameaça um ao outro devido a comportamento agressivo ou causam um ao outro stress excessivo ou desconforto devem ser mantidos separados.
+4.2 Enriquecimento
+Onde gatos são mantidos, deve haver um número suficiente de postes de arranhadura, locais de abrigo e prateleiras para garantir que cada gato pode subir, descansar, observar e retirar-se.
+4.3 Separação
+Cachorros mantidos em estabelecimentos não devem ser permanentemente separados das suas mães antes dos 8 semanas de idade.
+Gatinhos mantidos em abrigos e casas de acolhimento não devem ser permanentemente separados das suas mães antes dos 8 semanas de idade. Gatinhos mantidos em estabelecimentos de criação não devem ser permanentemente separados das suas mães antes dos 12 semanas de idade.
+Por derrogação, separação anterior é possível por razões médicas com base em parecer escrito de um veterinário. O operador deve conservar o parecer até o último cachorro ou gatinho da ninhada em questão ser colocado no mercado.</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Arts. 10.º, 12.º, 47.º, 52.º do RGBEAC (proposta, jun. 2025)</t>
+          <t>Arts. 10.º, 12.º, 47.º, 52.º, 68.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Artigo 10.º — Obrigações especiais dos detentores
-1.a) Assegurar o bem-estar: [...] atenção, supervisão, controlo, exercício físico e estímulo mental; liberdade de movimento, sendo proibidos todos os sistemas de contenção permanentes [...]; contato social adequado.
-Artigo 12.º — Proibições gerais
-f) Acorrentá-los ou mantê-los em espaços confinados que não garantam bem-estar; permitido temporariamente com trela à porta [...] sob supervisão.
-h) Mantê-los predominantemente isolados de humanos ou outros animais.
-y) Utilizar coleiras elétricas, choques, estranguladoras ou outros métodos aversivos/punitivos.
+          <t>SUBSECÇÃO 4.1 (SOCIALIZAÇÃO):
+Artigo 52.º — Maneio
+7 — Todos os alojamentos para hospedagem de cães e gatos devem dispor de um plano de socialização e enriquecimento ambiental.
+SUBSECÇÃO 4.2 (ENRIQUECIMENTO):
 Artigo 47.º — Condições dos alojamentos
-4 — Enriquecimento ambiental complexo incluindo materiais, substrato, ninhos, buracos, banhos, brinquedos.
-6 — Acesso diário a exercício: mínimo 2 vezes/dia, 30 minutos.
-Artigo 52.º — Maneio
-7 — Plano de socialização e enriquecimento ambiental obrigatório (alojamentos cães/gatos).</t>
+4 — As instalações devem providenciar um enriquecimento ambiental complexo e estimulante [...] incluindo [...] postes de arranhadura [a confirmar], esconderijos, prateleiras, [...] brinquedos e outros adequados ao fim em vista.
+SUBSECÇÃO 4.3 (SEPARAÇÃO):
+Artigo 68.º — Transação de cães e gatos
+[Procura necessária para obter texto verbatim sobre idade mínima de separação]</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Arts. 13.º, 18.º do Código do Animal (DL 214/2013)</t>
+          <t>Arts. 13.º, 18.º, e outros do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Artigo 13.º — Condições dos alojamentos
-1 — Espaço adequado permitindo: a) exercício físico adequado; b) fuga e refúgio.
-2 — Esconderijos para proteção.
-5 — Materiais e equipamento estimulando comportamentos naturais: substrato, cama, ninhos, ramos, buracos, banhos, outros.
-Artigo 18.º — Instalações
-6 — Estruturas e objetos para enriquecimento: prateleiras, poleiros, ninhos, esconderijos, material para entretenimento, área de recreio coberta ou descoberta (cães/gatos).</t>
+          <t>SUBSECÇÃO 4.1 (SOCIALIZAÇÃO):
+[Código do Animal não contém disposições específicas sobre socialização]
+SUBSECÇÃO 4.2 (ENRIQUECIMENTO):
+Artigo 13.º(5) — Condições dos alojamentos
+5 — As instalações devem ser equipadas [...] com materiais e equipamento que estimulem a expressão dos comportamentos naturais, nomeadamente [...] ramos, buracos, locais para banhos e outros.
+Artigo 18.º(6) — Instalações
+6 — Os alojamentos devem possuir estruturas e objetos [...] nomeadamente prateleiras, poleiros, ninhos, esconderijos e material para entretenimento.
+SUBSECÇÃO 4.3 (SEPARAÇÃO):
+[Procura necessária para obter artigos sobre idade mínima de separação]</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
@@ -3945,53 +3952,49 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>Artigo 8.º — Condições dos alojamentos
-1 — Espaço adequado permitindo: a) exercício físico adequado; b) fuga e refúgio.
-2 — Esconderijos para proteção.
-5 — Instalações equipadas com materiais e equipamento estimulando comportamentos naturais: substrato, cama, ninhos, ramos, buracos, banhos, outros.
-[Nota: Disposições genéricas sobre bem-estar. OMISSO: amarração, isolamento, métodos aversivos, plano de socialização, duração mínima de exercício, estímulo mental, emoções positivas]</t>
+          <t>SUBSECÇÃO 4.1 (SOCIALIZAÇÃO):
+[DL 276/2001 não contém disposições específicas sobre socialização]
+SUBSECÇÃO 4.2 (ENRIQUECIMENTO):
+Artigo 8.º(5) — Condições dos alojamentos
+5 — As instalações devem ser equipadas [...] com materiais e equipamento que estimulem a expressão do repertório de comportamentos naturais, nomeadamente [...] ramos, buracos, locais para banhos e outros quaisquer adequados ao fim em vista.
+SUBSECÇÃO 4.3 (SEPARAÇÃO):
+[Procura necessária para obter artigos sobre idade mínima de separação]</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>PARCIAL CONVERGÊNCIA
-DL 276/2001 cobre: espaço, exercício físico, enriquecimento ambiental básico.
-FALTAM: (i) restrição amarração &gt;1 hora; (ii) proibição isolamento; (iii) proibição métodos aversivos (coleiras elétricas); (iv) duração mínima exercício diário; (v) plano socialização documentado; (vi) estímulo mental explícito; (vii) emoções positivas.</t>
+          <t>4.1 SOCIALIZAÇÃO: DIVERGÊNCIA TOTAL — DL 276/2001 omisso completamente
+4.2 ENRIQUECIMENTO: PARCIAL — cobre genérico (substrato, ninhos, buracos) mas omite 'postes de arranhadura' (crítico para gatos)
+4.3 SEPARAÇÃO: [Procura necessária]</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
-          <t>PARCIAL CONVERGÊNCIA
-Código do Animal: equivalente ao DL 276/2001, com enriquecimento mais específico (área de recreio dedicada).
-FALTAM: (i) amarração; (ii) isolamento; (iii) métodos aversivos; (iv) duração mínima; (v) plano socialização; (vi) estímulo mental; (vii) emoções positivas.</t>
+          <t>4.1 SOCIALIZAÇÃO: DIVERGÊNCIA SIGNIFICATIVA — Código menciona contato social mas sem detalhe (idade, frequência, documentação)
+4.2 ENRIQUECIMENTO: PARCIAL — menciona prateleiras/poleiros mas omite 'postes de arranhadura' (essencial para gatos)
+4.3 SEPARAÇÃO: [Procura necessária]</t>
         </is>
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
-          <t>CONVERGÊNCIA SIGNIFICATIVA
-✅ Proíbe acorrentamento permanente (com amarração temporária supervisionada permitida)
-✅ Proíbe isolamento (Art. 12.h)
-✅ Proíbe coleiras elétricas e métodos aversivos (Art. 12.y)
-✅ Menciona 'exercício físico e estímulo mental' (Art. 10.a)
-✅ Plano de socialização documentado obrigatório (Art. 52.7)
-✅ Enriquecimento com 'brinquedos' incluso (Art. 47.4)
-✅ Acesso diário a exercício: 2x dia, 30 min (Art. 47.6)
-⚠️ Conceito 'emoções positivas' não explícito (apenas em Regulamento)</t>
+          <t>4.1 SOCIALIZAÇÃO: CONVERGÊNCIA PARCIAL — exige 'plano de socialização' (Art. 52.7) mas sem especificação de: idade 3 semanas, frequência diária, tipos de contato, separação de animais agressivos
+4.2 ENRIQUECIMENTO: CONVERGÊNCIA SIGNIFICATIVA — menciona enriquecimento 'complexo', inclui 'brinquedos', mas omite 'postes de arranhadura' (essencial para gatos)
+4.3 SEPARAÇÃO: [Procura necessária em Art. 68.º e relacionados]</t>
         </is>
       </c>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>ANNEX I, Ponto 4 (Behavioral Needs) estabelece: (i) liberdade movimento (exceto procedimentos); (ii) amarração &lt;1 hora; (iii) comportamentos sociais/específicos; (iv) socialização documentada (breeding); (v) enriquecimento acessível; (vi) estímulo reduzindo frustração; (vii) emoções positivas. @RGBEAC implementa 6 de 7 requisitos. DL 276/2001 é genérico. Recomenda-se validar implementação rigorosa do RGBEAC (sobretudo plano socialização, duração exercício, métodos aversivos) e considerar adicionar conceito 'emoções positivas'.</t>
+          <t>ANNEX I, Ponto 4 (Behavioural Needs) tem três subsecções: (i) 4.1 Socialização — contato social diário desde 3 semanas; (ii) 4.2 Enriquecimento — postes de arranhadura, abrigos, prateleiras (específico para gatos); (iii) 4.3 Separação — idades mínimas (8 semanas puppies, 8/12 semanas kittens). Legislação nacional é omissa (4.1), parcial (4.2), incompleta (4.3). @RGBEAC aproxima-se mas com gaps críticos (socialização sem detalhe; falta postes de arranhadura para gatos; separação a confirmar).</t>
         </is>
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>Sim - Consolidação (principalmente validar RGBEAC)</t>
+          <t>Sim - Harmonização parcial + procura de legislação em 4.3</t>
         </is>
       </c>
       <c r="P33" s="11" t="inlineStr">
         <is>
-          <t>ANNEX I, Ponto 4 (Behavioral Needs) cobre bem-estar comportamental. @RGBEAC já implementa a maioria dos requisitos do Regulamento. DL 276/2001 genérico, omisso em aspetos críticos. INOVAÇÕES-CHAVE DO @RGBEAC vs. LEGISLAÇÃO ANTERIOR: (i) proibição expressa acorrentamento permanente (omisso); (ii) proibição isolamento (omisso); (iii) proibição coleiras elétricas/métodos aversivos (omisso); (iv) plano socialização documentado (omisso); (v) acesso diário exercício 2x/dia 30min (omisso); (vi) inclusão 'brinquedos' em enriquecimento (omisso). Validar implementação: confirmar que acorrentamento temporário é realmente 'ocasional', que planos de socialização são documentados, que coleiras aversivas são efetivamente proibidas em mercado nacional.</t>
+          <t>ANNEX I, Ponto 4 contém 3 subsecções de bem-estar comportamental. 4.1 SOCIALIZAÇÃO: COMPLETAMENTE NOVO — @RGBEAC menciona 'plano' (Art. 52.7) mas sem detalhe do Regulamento. Recomenda-se adicionar: (i) idade mínima 3 semanas; (ii) frequência mínima (diária); (iii) tipos de contato (congêneres, humanos, outras espécies); (iv) documentação com registos; (v) disposição sobre separação por agressividade. 4.2 ENRIQUECIMENTO: CRÍTICO — @RGBEAC omite 'postes de arranhadura' (elemento essencial para bem-estar felino). Recomenda-se adicionar explicitamente: 'número suficiente de postes de arranhadura'. 4.3 SEPARAÇÃO: Procura necessária em DL 276/2001, Código do Animal, @RGBEAC para verificar se há artigos sobre idade mínima de venda/transação.</t>
         </is>
       </c>
     </row>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4001,6 +4001,96 @@
         </is>
       </c>
     </row>
+    <row r="34" ht="120" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Requisitos Técnicos — Identificação e Registo de Cães e Gatos (Identification and Registration)</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>ANEXO II do Regulamento 2023/0447 (conforme Articles 17 e 21)</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Transponders used to individually identify dogs and cats as required in Article 17 and Article 21 shall meet the following requirements:
+— the microchip shall contain an individual, non-repeatable and non-reprogrammable identification number;
+— the identification number shall start with the country of identification of the dog or cat identified in accordance with ISO standard 3166;
+— code structure and technical concept of radio frequency identification shall be in compliance with ISO standards 11784 and 11785;
+— compliance with ISO standards 11784 and 11785 shall be evaluated according to ISO standard 24631-1.</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Os transponders usados para identificar individualmente cães e gatos conforme exigido nos artigos 17 e 21 devem cumprir os seguintes requisitos:
+— o microchip deve conter um número de identificação individual, não repetível e não reprogramável;
+— o número de identificação deve começar com o país de identificação do cão ou gato identificado de acordo com a norma ISO 3166;
+— a estrutura de código e o conceito técnico da identificação por radiofrequência devem estar em conformidade com as normas ISO 11784 e 11785;
+— a conformidade com as normas ISO 11784 e 11785 deve ser avaliada de acordo com a norma ISO 24631-1.</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Arts. [a procurar] do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>[Procura em curso — aguardando resultado de análise de legislação nacional sobre requisitos técnicos de microchip, transponder, ISO standards, registo em base de dados]</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Arts. [a procurar] do Código do Animal (DL 214/2013)</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>[Procura em curso — aguardando resultado de análise sobre identificação eletrónica, microchip, registo em base de dados, requisitos técnicos]</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>Arts. [a procurar] do DL n.º 276-2001</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>[Procura em curso — aguardando resultado de análise sobre identificação, microchip, base de dados nacional, requisitos técnicos ISO]</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>[A ser preenchido com resultado de procura]</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>[A ser preenchido com resultado de procura]</t>
+        </is>
+      </c>
+      <c r="M34" s="10" t="inlineStr">
+        <is>
+          <t>[A ser preenchido com resultado de procura]</t>
+        </is>
+      </c>
+      <c r="N34" s="11" t="inlineStr">
+        <is>
+          <t>ANNEX II (Identification and Registration) estabelece requisitos técnicos de transponders/microchips: número individual não-repetível, conformidade ISO 3166 (país), ISO 11784/11785 (radiofrequência), ISO 24631-1 (avaliação). [Análise completa após procura na legislação nacional]</t>
+        </is>
+      </c>
+      <c r="O34" s="11" t="inlineStr">
+        <is>
+          <t>[A confirmar após análise completa]</t>
+        </is>
+      </c>
+      <c r="P34" s="11" t="inlineStr">
+        <is>
+          <t>ANNEX II especifica requisitos TÉCNICOS de transponders usados para identificação de cães e gatos (Articles 17, 21). IMPORTANTE: Este ANNEX é sobre ESPECIFICAÇÕES TÉCNICAS (ISO standards), não sobre procedimentos administrativos de registo. [Procura em curso para verificar conformidade legislação portuguesa com ISO 11784, 11785, 24631-1]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4111,6 +4111,152 @@
         </is>
       </c>
     </row>
+    <row r="35" ht="120" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Recolha de Dados sobre Bem-Estar Animal — Relatório Trienal à Comissão UE</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>ANEXO III do Regulamento 2023/0447 (conforme Article 20)</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>1. Number of dogs and cats registered per year, as referred to in Article 17 and Article 21(4).
+1a. Number of breeding establishments, selling establishments, shelters, and foster homes registered per year in accordance with Article 7.
+2. Number of breeding establishments approved per year, as referred to in Article 7a.
+2a. Number of breeding establishments whose approval has been suspended or withdrawn per year.</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>1. Número de cães e gatos registados por ano, conforme referido nos artigos 17.º e 21.º, n.º 4.
+1a. Número de estabelecimentos de criação, estabelecimentos de venda, abrigos e famílias de acolhimento registados por ano, em conformidade com o artigo 7.º.
+2. Número de estabelecimentos de criação aprovados por ano, conforme referido no artigo 7a.º.
+2a. Número de estabelecimentos de criação cuja aprovação foi suspensa ou revogada por ano.</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>RGBEAC (Regime Geral do Bem-Estar dos Animais de Companhia, proposta jun. 2025) — Arts. 20.º, 46.º</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Artigo 20.º — Sistema de Informação de Animais de Companhia (SIAC)
+1 - O SIAC reúne informação relativa à: a) Rastreabilidade de dispositivos de identificação; b) Identificação dos animais de companhia; c) Sua titularidade ou detenção; d) Informação de saúde pública, saúde animal e bem-estar animal.
+2 – A DGAV é a entidade responsável pelo SIAC, assegurando seu funcionamento e tratamento seguro de informação.
+3 – A DGAV pode atribuir gestão do SIAC a outras entidades, mediante protocolo e parecer da Comissão Nacional de Proteção de Dados.
+4 - Normas e procedimentos constam de Manual de Procedimentos SIAC, aprovado pelo diretor-geral de alimentação e veterinária.
+Artigo 46.º — Relatório Nacional Anual
+1 - Centros de bem-estar animal e alojamentos com fins de promoção remetem à DGAV no primeiro mês de cada ano, relatórios de gestão do ano anterior.
+2 – A DGAV consolida informação a nível nacional sobre bem-estar animal em cada ano, incluindo: a) Acompanhamento da política internacional; b) Prestação de apoios públicos; c) Atividade do SIAC; d) Resultados de planos de controlo; e) Processos contraordenacionais; f) Coimas e sanções; g) Atividade de centros de bem-estar animal; h) Programas de interesse nacional.</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>Código do Animal (DL 214/2013) — Arts. 55.º, 56.º, 141.º-145.º</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 55.º — Base de dados
+1 - Toda informação de registo coligida numa aplicação informática nacional.
+2 - A DGAV detém, define e coordena acesso à BD, podendo autorizar gestão em outras entidades mediante protocolos e parecer da Comissão Nacional de Proteção de Dados.
+3 - Só entidades autorizadas pela DGAV têm acesso.
+Artigo 56.º — Classificação dos animais
+Categorias para registo na BD: a) Cão (designado A); b) Cão Potencialmente Perigoso (designado G); c) Cão Perigoso (designado H); d) Gato (designado I).
+Artigos 141.º-145.º — Monitorização e Relatórios
+Código do Animal estabelece estrutura de: a) Monitorização de bem-estar animal; b) Recolha de dados de infrações; c) Aplicação de sanções; d) Atividades de centros de recolha; e) Estatísticas de animais processados; f) Sistema de contraordenações.</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>DL 82/2019 (Arts. 2.º-7.º), Lei 27/2016 (Arts. 1.º-9.º)</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>[dim]Decreto-Lei n.º 82/2019 de 27 de junho — Bem-Estar de Animais de Companhia
+Artigo 2.º — Âmbito de aplicação — Aplicável a cães, gatos e furões detidos para fins não comerciais.
+Artigo 3.º — Obrigações de registo — Proprietários de cães e gatos devem proceder ao registo no SIAC com identificação eletrónica obrigatória.
+Artigo 4.º — Identificação eletrónica — Via aplicação subcutânea de microchip (ISO 11784 e 11785).
+Artigo 5.º — Procedimentos de registo — Procedimentos de registo, atualização e consulta do SIAC estabelecidos em regulação complementar.
+Artigo 6.º — Controlos de acesso — Segurança de dados e autorização de acesso ao SIAC sob responsabilidade DGAV.
+Artigo 7.º — Rastreabilidade — Sistema garante rastreabilidade de dispositivos de identificação e proprietários.
+[dim]Lei n.º 27/2016 de 23 de agosto — Rede de Centros de Recolha e Proibição do Abate
+Artigo 1.º — Objeto — Aprova medidas para criação de rede de centros de recolha oficial de animais errantes.
+Artigo 2.º — Definições — Centros de recolha, abrigos, famílias de acolhimento — conceitos e categorias.
+Artigos 3.º-9.º — Estrutura e Funcionamento — Procedimentos de registo, aprovação, funcionamento e supervisão.</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t>ANÁLISE POR PONTO:
+PONTO 1 (Cães/gatos registados): ✅ CONFORMIDADE COMPLETA
+SIAC operacional desde 2019 (DL 82/2019) — registo obrigatório e eletrónico. Dados disponíveis anualmente.
+PONTO 1a (Estabelecimentos registados): ⚠️ CONFORMIDADE PARCIAL
+Lei 27/2016 e DL 82/2019 cobrem criação, venda, abrigos. LACUNA: conceito "famílias de acolhimento" não explicitamente codificado em legislação vigente.
+PONTO 2 (Estabelecimentos aprovados): ❌ LACUNA CRÍTICA
+Legislação vigente menciona REGISTO de estabelecimentos de criação. FALTA: sistema específico de "aprovação" formal (vs. apenas registo). Portarias específicas de aprovação existem para outros setores (científico) — NÃO claramente para criadores de animais de companhia.
+PONTO 2a (Suspensão/revogação): ❌ LACUNA CRÍTICA
+DL 82/2019 e Lei 27/2016 NÃO mencionam procedimentos de suspensão ou revogação de aprovação de estabelecimentos.</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="inlineStr">
+        <is>
+          <t>ANÁLISE POR PONTO:
+PONTO 1: ✅ CONFORMIDADE COMPLETA
+Arts. 55.º-56.º estabelecem base de dados nacional com classificação detalhada de animais. Sistema estruturado.
+PONTO 1a: ❌ NÃO IMPLEMENTADO
+Código do Animal não estabelece sistema específico de registo de estabelecimentos de criação, venda, abrigos, famílias de acolhimento.
+PONTO 2: ❌ NÃO IMPLEMENTADO
+Código do Animal não estabelece sistema de aprovação de criadores.
+PONTO 2a: ❌ NÃO IMPLEMENTADO
+Código do Animal não menciona suspensão/revogação de aprovação.</t>
+        </is>
+      </c>
+      <c r="M35" s="10" t="inlineStr">
+        <is>
+          <t>ANÁLISE POR PONTO:
+PONTO 1: ✅ CONFORMIDADE COMPLETA
+Art. 20.º (SIAC) — registo obrigatório e operacional. Relatório nacional anual possível (Art. 46.º).
+PONTO 1a: ⚠️ CONFORMIDADE PARCIAL
+Art. 20.º implicitamente cobre estabelecimentos através de rastreabilidade de dispositivos. REQUER complementação: codificação explícita de registo de "famílias de acolhimento".
+PONTO 2: ❌ NÃO IMPLEMENTADO
+RGBEAC não menciona sistema de aprovação de criadores.
+PONTO 2a: ❌ NÃO IMPLEMENTADO
+RGBEAC não menciona suspensão/revogação de aprovação.</t>
+        </is>
+      </c>
+      <c r="N35" s="11" t="inlineStr">
+        <is>
+          <t>CONCLUSÃO GERAL:
+Legislação portuguesa implementa PARCIALMENTE os 4 pontos de Annex III (dados para relatório trienal à Comissão UE):
+✅ PONTO 1 — COBERTURA COMPLETA: SIAC operacional desde 2019. Dados de cães/gatos registados disponíveis anualmente.
+⚠️ PONTO 1a — COBERTURA PARCIAL: Sistema de registo de estabelecimentos existe (Lei 27/2016); conceito "famílias de acolhimento" requer codificação explícita.
+❌ PONTO 2 — LACUNA ESTRUTURAL: Falta sistema formal de "aprovação" de criadores. Existe apenas registo administrativo. Necessário: distinguir registo (mera inscrição) de aprovação (avaliação de conformidade com requisitos técnicos).
+❌ PONTO 2a — LACUNA ESTRUTURAL: Falta procedimentos formais de suspensão/revogação de aprovação. Necessário: mecanismo administrativo com critérios de suspensão e revogação.
+RECOMENDAÇÕES:
+1. Complementar Lei 27/2016 com definição e registo de "famílias de acolhimento" (ponto 1a).
+2. Criar sistema de aprovação prévia de estabelecimentos de criação, com avaliação de conformidade (ponto 2).
+3. Estabelecer procedimentos formais de suspensão/revogação com critérios administrativos (ponto 2a).
+4. Integrar dados coletados em relatório trienal da Comissão UE (conforme Art. 20 do Regulamento).</t>
+        </is>
+      </c>
+      <c r="O35" s="11" t="inlineStr">
+        <is>
+          <t>Sim — Estabelecer sistema de aprovação, suspensão e revogação de estabelecimentos de criação + codificar famílias de acolhimento</t>
+        </is>
+      </c>
+      <c r="P35" s="11" t="inlineStr">
+        <is>
+          <t>ANNEX III define dados OBRIGATÓRIOS para relatório trienal à Comissão UE (Art. 20 do Regulamento). SIAC português fornece dados para ponto 1 (cães/gatos registados) — sistema operacional desde 2019. Pontos 2 e 2a requerem regulação complementar urgente: aprovação formal de criadores (vs. apenas registo) + procedimentos de suspensão/revogação. Ponto 1a (estabelecimentos) — codificação explícita de "famílias de acolhimento" como categoria administrativa. Recomenda-se: Lei complementar ou Portaria reguladora para implementação completa dos 4 pontos antes do próximo período de reporte (trienal).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -669,13 +669,13 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Art.º 4.º do Regulamento 2023/0447</t>
+          <t>Art.º 5.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>1 — A breeding establishment where at most two litters per calendar year is produced for placing on the market shall only be subject to the obligations laid down in Article 5, Article 6(1) (1b), (1c) and (1d), Article 6a, Article 7, Article 8, Article 11(2), (3) and (3a), Article 12(3), (4) and (7), Article 13(2)(b), (c) and (d), Article 14(2), (3), (4) and (5a), Article 15, Article 15a(1) and point 3 and 4.3 of Annex I.
-2 — A shelter, where up to a total of 15 dogs or cats are kept at any given time, or any foster home shall only be subject to the obligations laid down in Article 5, Article 6(1), (1a), (1b), (1c), and (1d), Article 7, Article 8, Article 11(2), (3) and (3a), Article 12(3), (4) and (7), Article 13(2)(a), (b), (c) and (d), Article 14(2), (3), (4) and (5a), Article 15 and point 4.3 of Annex I.</t>
+          <t>1.	A breeding establishment where no more than two litters per calendar year are produced for placing on the market shall be subject to only the obligations laid down in Article 6, Article 7(1) (2), (3) and (4). Article 8, Article 9, Article 11, Article 14(2), (3) and (4), Article 15(3), (4) and (8), Article 16(1). points (b), (c) and (d), Article 17(2), (3), (5) and (7), Article 18, Article 19(1) and points 3 and 4.3 of Annex I.
+2.	A shelter in which not more than a combined total of 15 dogs or cats are kept at any given time, or any foster home shall be subject to only the obligations laid down in Article 6, Article 7(1), (2), (3), (4), and(5), Article 9, Article 11, Article 14(2), (3) and (4), Article 15(3), (4) and (8), Article 16(1). points (a), (b), (c) and (d), Article 17(2), (3), (5) and (7), Article 18 and point 4.3 of Annex I.</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -753,17 +753,17 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Art.º 5.º do Regulamento 2023/0447</t>
+          <t>Art.º 6.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Operators shall apply the following general welfare principles with respect to dogs or cats bred or kept in their establishment:
-(a) dogs and cats are provided with water and feed of a quality and of a quantity that enables them to have appropriate nutrition and hydration;
-(b) dogs and cats are kept in an appropriate and regularly cleaned physical environment which is secure and comfortable, especially in terms of space, air quality, temperature, light, protection against adverse climatic conditions and ease of movement, preventing overcrowding;
-(c) dogs and cats are kept safe, clean and in good health by preventing diseases, injuries, and pain, due in particular to management, handling practices and breeding practices;
-(d) dogs and cats are kept in an environment that enables them to exhibit species-specific and social non-harmful behaviour, and to establish a positive relationship with human beings;
-(e) dogs and cats are kept in such a way as to optimise their mental state by preventing or reducing negative stimuli in duration and intensity, as well as by maximising opportunities for positive stimuli in duration and intensity, preventing the development of abnormal repetitive and other behaviours indicative of negative animal welfare, and taking into consideration the individual dog's or cat's needs in the different domains referred to in points (a) to (d).</t>
+(a)	dogs and cats are provided with water and feed of a quality and quantity that affords them appropriate nutrition and hydration;
+(b)	dogs and cats are kept in a physical environment that is appropriate and regularly cleaned, that is secure and comfortable, especially in terms of space, air quality, temperature, light, protection against adverse climatic conditions and that is big enough to prevent overcrowding and to afford them ease of movement;
+(c)	dogs and cats are kept safe, clean and in good health, and diseases, injuries, and pain due, in particular, to management, handling practices and breeding practices, are prevented;
+(d)	dogs and cats are kept in an environment that enables them to exhibit species-specific and social non-harmful behaviour, and to establish a positive relationship with human beings;
+(e)	dogs and cats are kept in such a way as to optimise their mental state by preventing or reducing negative stimuli in duration and intensity, as well as by maximising opportunities for positive stimuli in duration and intensity, preventing the development of abnormal repetitive or other behaviours indicative of negative animal welfare, and taking into consideration the individual animal’s needs in the domains referred to in points (a) to (d).</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -851,19 +851,20 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Art.º 6.º do Regulamento 2023/0447</t>
+          <t>Art.º 7.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>1. Operators shall be responsible for the welfare of dogs or cats kept in the establishments under their responsibility and under their control and to minimise any risks to their welfare.
-1a. In the case of foster homes, the responsibility shall lie with the operator on whose behalf dogs or cats are kept. Such operators shall not place more than a total of five dogs or cats or one litter with or without mother in a foster home at any given time and shall provide the foster family with adequate information on the animal welfare obligations as well as the individual needs of the dogs or cats, and shall ensure that the relevant obligations set out by this Regulation are complied with in foster homes. Member States where the foster home is located may provide for a greater number of dogs, cats or litters to be placed in the foster home, provided that the premises of the foster home provide sufficient space, including outdoor space, and that the number of animal caretakers in the foster home is sufficient, to ensure the welfare of the dogs or cats.
-1b. Operators shall not subject any dog or cat to cruelty, abuse or mistreatment, including through participation in activities likely to result in cruelty, abuse or mistreatment, to the dogs or cats bred or kept by the operator.
-1c. Operators shall not abandon dogs or cats.
-1d. Operators who are due to cease the activities of their establishment shall ensure the rehoming of the dogs or cats kept therein either by taking up the pet ownership or by transferring the responsibility or ownership of dogs and cats to other operators or acquirers.
-2. Operators shall ensure that dogs or cats are handled by a suitable number of animal caretakers and in order to meet the welfare needs of dogs or cats kept in their establishments and who have the competences required under Article 9.
-2a. Operators shall ensure the welfare of the dogs or cats under their responsibility by monitoring animal-based indicators concerning behaviour and physical appearance, and by taking actions based on the results of such monitoring.
-2b. The Commission is empowered to adopt delegated acts in accordance with Article 23 supplementing this Regulation by laying down animal-based indicators concerning behaviour and physical appearance and the methods of their measurement.</t>
+          <t>1.	Operators shall be responsible for the welfare of dogs and cats kept in establishments under their responsibility and control, and shall be responsible for minimising any risks to the welfare of those animals.
+2.	In the case of foster homes, the responsibility shall lie with the operator on whose behalf dogs or cats are kept. Such operators shall not place more than a combined total of five dogs or cats or one litter with or without mother in a foster home at any given time and shall provide the foster family with adequate information on the animal welfare obligations as well as the individual needs of the dogs or cats, and shall ensure that the relevant obligations laid down in this Regulation are complied with in foster homes.
+	The Member State in which the foster home is located may allow a greater number of dogs, cats or litters to be placed in the foster home, provided that the premises of the foster home have sufficient space, including outdoor space, and that the number of animal carers in the foster home is sufficient, to ensure the welfare of the dogs or cats.
+3.	Operators shall not subject any dog or cat to cruelty, abuse or mistreatment, including by making them participate in activities likely to result in cruelty to or abuse or mistreatment of the dogs or cats bred or kept by the operator.
+4.	Operators shall not abandon the dogs or cats bred or kept by them.
+5.	Before operators cease activities at an establishment, they shall ensure that the dogs or cats kept there are rehomed, either by taking up the pet ownership themselves or by transferring the responsibility for, or the ownership of, the dogs and cats to other operators or acquirers.
+6.	Operators shall ensure that dogs and cats are handled by a number of animal carers sufficient to meet the welfare needs of dogs or cats kept in their establishments, and that those carers have the competences required under Article 12.
+7.	Operators shall ensure the welfare of the dogs or cats for which they are responsible by monitoring animal-based indicators concerning behaviour and physical appearance, and by taking actions based on the results of such monitoring.
+8.	The Commission is empowered to adopt delegated acts in accordance with Article 28 supplementing this Regulation by laying down the animal-based indicators concerning behaviour and physical appearance that operators are to use for monitoring, in accordance with paragraph 7 of this Article, and the methods by which operators are to measure them.</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -952,20 +953,21 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Art.º 6.º-A do Regulamento 2023/0447</t>
+          <t>Art.º 8.º-A do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>1. Operators of breeding establishments shall ensure that their breeding strategies minimise the risk of producing dogs or cats with genotypes associated with detrimental effects on their health and welfare.
-2. Operators of breeding establishments shall not use for reproduction dogs or cats that have excessive conformational traits leading to a high risk of detrimental effects on the welfare of these dogs or cats, or of their offspring. Before selection for breeding of a dog or cat that may be concerned by an excessive conformational trait the operator shall consult a veterinarian or an independent qualified person under the responsibility of a veterinarian. The veterinarian or independent qualified person shall assess whether the dog or cat has an excessive conformational trait.
-3. The Commission is empowered to adopt, taking into account scientific opinions of the European Food Safety Authority as well as the social and economic impacts, delegated acts in accordance with Article 23 supplementing this Regulation by:
-(a) defining characteristics of the genotypes referred to in paragraph 1, which shall be excluded from reproduction, and the methods for their assessment and the record keeping requirements;
-(b) defining excessive conformational traits referred to in paragraph 2 of this Article, which shall be excluded from reproduction, the methods for their assessment and the record keeping requirements.
-4. The delegated acts concerning the excessive conformational traits shall be adopted by 1 July 2030. The delegated acts concerning the genotypes shall be adopted by 1 July 2036.
-5. The following shall be prohibited in the management of the reproduction of dogs and cats:
-(a) the breeding between parents and offspring, between siblings, between half-siblings or between grandparents and grandchildren, unless approved by the competent authority based on a specific need to preserve local breeds with a limited genetic pool;
-(b) the breeding to produce hybrids.</t>
+          <t>1.	Operators of breeding establishments shall ensure that their breeding strategies minimise the risk of producing dogs or cats with genotypes associated with effects detrimental to the health and welfare of those animals.
+2.	Operators of breeding establishments shall not use for reproduction dogs or cats that have excessive conformational traits leading to a high risk of detrimental effects on the welfare of such dogs or cats, or of their offspring. Before selecting a dog or cat that might have an excessive conformational trait for breeding, the operator shall consult a veterinarian or an independent qualified person acting under the responsibility of a veterinarian. That veterinarian or independent qualified person shall assess whether the dog or cat has an excessive conformational trait.
+3.	The Commission is empowered to adopt delegated acts in accordance with Article 28 supplementing this Regulation by:
+(a)	defining characteristics of the genotypes referred to in paragraph 1 that are to be excluded from reproduction, and the methods for their assessment and the record keeping requirements;
+(b)	defining excessive conformational traits referred to in paragraph 2 of this Article that are to be excluded from reproduction, the methods for their assessment and the record keeping requirements.
+	When adopting those delegated acts, the Commission shall take into account the scientific opinion of the European Food Safety Authority (EFSA), as well as any social and economic impacts of those delegated acts.
+	The delegated acts concerning the excessive conformational traits shall be adopted by 1 July 2030. The delegated acts concerning the genotypes shall be adopted by 1 July 2036.
+4.	The following shall be prohibited when managing the reproduction of dogs and cats:
+(a)	breeding between parents and offspring, between siblings, between half-siblings or between grandparents and grandchildren, unless approved by the competent authority based on a specific need to preserve local breeds with a limited genetic pool;
+(b)	breeding for the purpose of producing hybrids.</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1051,18 +1053,23 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Art.º 7.º do Regulamento 2023/0447</t>
+          <t>Art.º 9.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Operators shall notify the competent authorities of their activity, providing at least the following information:
-(a) name, address and contact details of the operator;
-(b) the location(s) of the establishment(s);
-(c) the type(s) of establishment: breeding establishment, selling establishment, shelter or foster home;
-(d) the species and, for breeding establishments, the breeds of the dogs or cats kept in the establishment(s);
-(e) the capacity of the establishment expressed as the maximum number of dogs and cats which can be kept in the establishment(s);
-(ea) for breeding establishments, the estimated number of litters to be placed on the market per year.</t>
+          <t>1.	Operators shall notify the competent authorities of their activity, providing at least the following information for each of their establishments:
+(a)	the name, address and contact details of the operator;
+(b)	the location of the establishment;
+(c)	the type of establishment: breeding establishment, selling establishment, shelter or foster home;
+(d)	the species and, for breeding establishments, the breeds of the dogs or cats kept in the establishment;
+(e)	the capacity of the establishment, expressed as the maximum number of dogs and cats which can be kept in the establishment;
+(f)	for breeding establishments, the estimated number of litters to be placed on the market per year.
+2.	Operators shall notify the competent authority of:
+(a)	any changes concerning the information referred to in paragraph 1;
+(b)	where applicable, the planned date of a cessation of their activities, at the latest five working days before that date.
+3.	Member States shall use the information provided in accordance with Article 84 of Regulation (EU) 2016/429. Operators shall not be required to notify the information already submitted in accordance with Article 84 of Regulation (EU) 2016/429 again.
+4.	The competent authority shall maintain a register of establishments. The competent authority may use for that purpose the register provided for in Article 101(1), point (a), of Regulation (EU) 2016/429.</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1157,16 +1164,16 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Art.º 8.º do Regulamento 2023/0447</t>
+          <t>Art.º 11.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Operators shall provide to the acquirer of a dog or cat written information necessary to enable him or her to ensure the welfare of the dog or cat including information on responsible ownership and on the specific needs of the dog or cat in terms of feeding, caring, health, housing and behavioural needs, as well as information on its health.
-1a. The written information on the dog or cat's health referred to in the first paragraph shall include at least:
-(a) the dog or cat's vaccination status;
-(b) any medical conditions or predispositions to diseases, including allergies, that are known by the operator, and any diagnostic test results for the dog or cat that are available to the operator.
-In case the information on the dog's or cat's health is documented in a document required under Regulation (EU) 2016/429, the operator shall transmit that document to the acquirer.</t>
+          <t>1.	Operators shall provide to the acquirer of a dog or cat written information necessary to enable the acquirer to ensure the animal’s welfare, including information on responsible ownership and on the specific needs of the animal in terms of feeding, care, health and housing, as well as information on its behavioural needs and health history.
+2.	The written information on the dog or cat’s health history referred to in the first paragraph shall include at least:
+(a)	the animal’s vaccination status;
+(b)	any medical conditions or predispositions to diseases, including allergies, that are known to the operator, and any diagnostic test results for the dog or cat that are available to the operator.
+Where the information on the animal’s health history is set out in a document required under Regulation (EU) 2016/429, the operator shall transmit that document to the acquirer.</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1252,19 +1259,21 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Art.º 9.º do Regulamento 2023/0447</t>
+          <t>Art.º 12.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>1. Animal caretakers, other than volunteers in shelters and interns who are under the responsibility of a competent animal caretaker, shall have the following competences as regards the dogs and cats they are handling:
-(a) understanding of their biological behaviour and their physiological and ethological needs;
-(b) ability to recognise their expressions including any sign of suffering and to identify and take the appropriate mitigating measures in such cases;
-(c) ability to apply good animal management practices, including operant conditioning and positive reinforcement, to use and maintain the equipment used for the dogs or cats under their care and to minimise any risks to the welfare of the dogs or cats, preventing suffering;
-(d) knowledge of their obligations under this Regulation.
-2. The competences referred to in paragraph 1 may be acquired through education, training or professional experience. Education, training or professional experience shall be documented.
-2a. Operators shall ensure that at least one animal caretaker, other than a volunteer or intern, at the establishment has completed the training courses referred to in Article 18 and that the caretaker transfers the knowledge to the other animal caretakers of the establishment.
-3. The Commission shall, by means of implementing acts, lay down minimum requirements concerning the formal education, training or professional experience in order to acquire the competences referred to in paragraph 2 and for the training courses referred to in paragraph 2a. Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 24. The implementing act concerning the training courses referred to in paragraph 2a shall be adopted by [3 years from the date of entry into force of the Regulation].</t>
+          <t>1.	Animal carers, other than volunteers in shelters and interns who are acting under the responsibility of a competent animal carer, shall have the following competences as regards the dogs and cats they are handling:
+(a)	an understanding of the animals’ biological behaviour and their physiological and ethological needs;
+(b)	the ability to recognise the animals’ expressions, including any sign of suffering, and to identify and to take the appropriate mitigating measures  in such cases;
+(c)	the ability to apply good animal management practices, including operant conditioning and positive reinforcement, to use and maintain the equipment used for the dogs or cats under their care and to minimise any risks to the welfare of those dogs or cats, preventing them from suffering;
+(d)	knowledge of the carers’ obligations under this Regulation.
+2.	The competences referred to in paragraph 1 may be acquired through education, training or professional experience. Only documented education, training or professional experience shall be taken into account when determining whether an animal carer has the competences referred to in paragraph 1.
+3.	Operators shall ensure that at least one animal carer, other than a volunteer or intern, at the establishment has completed the training courses referred to in Article 22. Operators shall ensure that that animal carer transfers his or her knowledge to the other animal carers of the establishment.
+4.	The Commission shall adopt implementing acts, laying down minimum requirements concerning the formal education, training or professional experience referred to in paragraph 2 of this Article necessary to determine whether an animal carer has the competences referred to in paragraph 1 and for the training courses referred to in paragraph 3.
+The implementing act concerning the training courses referred to in paragraph 3 shall be adopted by ... [3 years from the date of entry into force of this Regulation].
+Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 29.</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1348,23 +1357,119 @@
     <row r="9" ht="120" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Aprovação de Estabelecimentos de Criação</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 10.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>1.	Operators of breeding establishments that either produce or intend to produce more than five litters per calendar year or that keep more than a combined total of five bitches or queens at any given time shall place dogs or cats on the market only after their establishment has been approved by the competent authority.
+2.	The competent authority shall perform on-site inspections to verify that the establishment meets the requirements of this Regulation. Member States may allow such inspections to be carried out remotely, provided that the means of distance communication used provides sufficient evidence for the competent authority to perform reliable inspections. The competent authority shall grant certificates of approval only to breeding establishments that meet the requirements of this Regulation.
+3.	The competent authority shall maintain a publicly available list including the following information for each approved establishment:
+(a)	the name, contact details and, where available, the URL of the website of the establishment;
+(b)	the address of the establishment;
+(c)	the name of the operator;
+(d)	the species and, if relevant, the breeds related to the establishment activities approved;
+(e)	the unique approval number assigned to the establishment by the competent authority and the date of the approval and cessation of activities.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>1.	Operators of breeding establishments that either produce or intend to produce more than five litters per calendar year or that keep more than a combined total of five bitches or queens at any given time shall place dogs or cats on the market only after their establishment has been approved by the competent authority.
+2.	The competent authority shall perform on-site inspections to verify that the establishment meets the requirements of this Regulation. Member States may allow such inspections to be carried out remotely, provided that the means of distance communication used provides sufficient evidence for the competent authority to perform reliable inspections. The competent authority shall grant certificates of approval only to breeding establishments that meet the requirements of this Regulation.
+3.	The competent authority shall maintain a publicly available list including the following information for each approved establishment:
+(a)	the name, contact details and, where available, the URL of the website of the establishment;
+(b)	the address of the establishment;
+(c)	the name of the operator;
+(d)	the species and, if relevant, the breeds related to the establishment activities approved;
+(e)	the unique approval number assigned to the establishment by the competent authority and the date of the approval and cessation of activities.</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>Conceito novo de 'aprovação' com limiar (&gt;5 ninhadas/ano ou &gt;5 cadelas/gatas)</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>Não implementado</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>Não implementado</t>
+        </is>
+      </c>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>Artigo completamente novo no Regulamento. Introduz aprovação formal de criadores com limiar numérico.</t>
+        </is>
+      </c>
+      <c r="O9" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P9" s="11" t="inlineStr">
+        <is>
+          <t>Análise e correspondência nacional pendente de complementação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>Avaliação e Supervisão de Bem-Estar</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 10.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Operators shall:
-(a) ensure that the establishments under their responsibility receive a visit by a veterinarian within the first year after the date of application of this Regulation or within the first year after having notified a new establishment, for the purpose of identifying and assessing any risk factor for the welfare of the dogs or cats and advising the operator on measures to address those risks; thereafter the visits from a veterinarian shall take place when appropriate, based on a risk analysis by the competent authorities; Member States may provide for that the advisory welfare visits are annual;
-(b) keep the records of the findings of the visit of the veterinarian referred to in point (a) and of their follow up actions for at least 4 years, from the day of the visit, and shall make them available to the competent authorities upon request and to the veterinarian that performs subsequent advisory visits.
-By 24 months from the date of entry into force of this Regulation, the Commission shall adopt delegated acts in accordance with Article 23 supplementing this Article in order to lay down minimum criteria to be assessed during the advisory welfare visit.</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 13.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>1.	Operators shall:
+(a)	ensure that the establishments for which they are responsible receive a visit by a veterinarian for the purpose of identifying and assessing any risk factor for the welfare of the dogs or cats and advising the operator on measures to address those risks initially by ... [date three years after the date of entry into force of this Regulation] or one year following the notification of the new establishment, and thereafter when appropriate, based on a risk analysis by the competent authorities, or on an annual basis if Member States so provide in their national law;
+(b)	keep the records of the findings of the veterinarian’s visit referred to in point (a) and of their follow up actions for at least four years, from the day of the visit, and shall make those records available to the competent authorities upon request as well as to the veterinarians that perform subsequent advisory visits.
+2.	By ... [date 24 months from the date of entry into force of this Regulation], the Commission shall adopt delegated acts in accordance with Article 28 supplementing this Article by laying down the minimum criteria to be assessed by the veterinarian during the advisory welfare visit.</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem:
 (a) assegurar que os estabelecimentos sob a sua responsabilidade recebem uma visita de um médico veterinário no prazo de um ano a partir da data de aplicação do presente Regulamento ou no prazo de um ano após notificação de novo estabelecimento, com o objetivo de identificar e avaliar quaisquer fatores de risco para o bem-estar dos cães ou gatos e aconselhar o operador sobre medidas para resolver esses riscos; depois, as visitas do médico veterinário devem ocorrer quando apropriado, com base numa análise de risco pelas autoridades competentes; os Estados-Membros podem estabelecer que as visitas de aconselhamento de bem-estar sejam anuais;
@@ -1372,12 +1477,12 @@
 Dentro de 24 meses a partir da data de entrada em vigor do presente Regulamento, a Comissão deve adotar atos delegados em conformidade com o artigo 23.º que complementem o presente artigo de forma a estabelecer critérios mínimos a serem avaliados durante a visita de aconselhamento de bem-estar.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Art.º 56.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Artigo 56.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem, com exceção dos alojamentos para hospedagem com fins higiénicos, devem ter ao seu serviço um médico veterinário responsável pelo alojamento.
@@ -1388,12 +1493,12 @@
 d) A colaboração com as autoridades competentes em todas as ações que estas determinem.</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>Art.º 32.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>Artigo 32.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem sem fins lucrativos e com fins lucrativos de animais, com exceção dos com fins higiénicos, necessitam de ter ao seu serviço um médico veterinário que seja responsável pelo alojamento.
@@ -1403,12 +1508,12 @@
 c) A colaboração com as autoridades competentes em todas as ações que estas determinarem.</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Art.º 4.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>Artigo 4.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem sem fins lucrativos e com fins lucrativos de animais, com exceção dos alojamentos para hospedagem com fins higiénicos, devem ter ao seu serviço um médico veterinário que seja responsável pelo alojamento.
@@ -1418,61 +1523,61 @@
 c) A colaboração com as autoridades competentes em todas as ações que estas determinarem.</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 4.º) estabelece a obrigação de ter médico veterinário responsável que execute 'programas e ações' para saúde e bem-estar, mas não especifica que essa avaliação deve ocorrer em prazo determinado (ex.: 1 ano) ou que os registos devem ser mantidos por período específico (4 anos). O @regulamento é mais prescritivo neste aspecto.</t>
         </is>
       </c>
-      <c r="L9" s="9" t="inlineStr">
+      <c r="L10" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 32.º) replica quase verbatim o art.º 4.º do DL n.º 276/2001, mantendo as mesmas lacunas: não fixa prazos para avaliações de bem-estar nem obrigações de manutenção de registos estruturados.</t>
         </is>
       </c>
-      <c r="M9" s="10" t="inlineStr">
+      <c r="M10" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.º 56.º) reforça a obrigação com 'parecer relativo à verificação das condições higiossanitárias e de bem-estar', mas igualmente sem prazos específicos para avaliações ou duração de retenção de registos. Ambos focam-se em 'programas' interno, não em 'visitas periódicas externas'.</t>
         </is>
       </c>
-      <c r="N9" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>Lacuna estrutural em toda a legislação nacional: enquanto o @regulamento exige 'visita de um veterinário' num prazo específico (1 ano) com manutenção de registos por 4 anos e transmissão entre veterinários, a legislação nacional concentra-se em ter um 'médico veterinário responsável' no estabelecimento. Necessidade de alteração: (1) formalizar obrigação de 'visita de avaliação' por veterinário dentro de 1 ano após notificação; (2) exigir avaliações periódicas conforme risco; (3) obrigatória manutenção de registos por 4 anos; (4) garantir transmissão de informações ao próximo veterinário avaliador; (5) estabelecer critérios mínimos de avaliação (bem-estar comportamental, alojamento, saúde, etc.).</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P9" s="11" t="inlineStr"/>
+      <c r="P10" s="11" t="inlineStr"/>
     </row>
-    <row r="10" ht="120" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11" ht="120" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Alimentação e Hidratação</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 11.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>1. Operators shall ensure that dogs or cats are fed in accordance with the requirements laid down in point 1 of Annex I.
-2. Operators shall ensure that dogs or cats are adequately fed and hydrated by supplying:
-a) clean and fresh water, ad libitum;
-b) feed in sufficient quantity and quality to meet the physiological, nutritional and metabolic needs of the dogs and cats, as part of a diet adapted to the age, breed, category, activity level, health and reproductive status of the dogs or cats, with the overall objective of achieving and maintaining good health;
-c) feed free of substances which may cause suffering;
-d) feed in such a way as to avoid abrupt changes and ensure a well-functioning gastro-intestinal system, in particular during the weaning phase.
-3. Operators shall ensure that feeding and watering facilities are kept clean and are constructed and installed in such a way as to:
-a) provide equal access to adequate amounts of feed and water for all dogs or cats and minimise competition between them;
-b) minimise spillage and prevent the contamination of feed and water with harmful physical, chemical or biological contaminants;
-c) prevent injury, drowning or other harm to the dogs or cats;
-d) be easily cleaned and disinfected to prevent the spread of diseases.
-3a. Where advised in writing by a veterinarian to do so, the operators may adjust the feeding and watering frequencies for an individual dog or cat. The operators shall keep a record of the advice for its entire duration as advised by the veterinarian.</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 14.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>1.	Operators  shall ensure that dogs and cats are fed in accordance with the requirements laid down in point 1 of Annex I  .
+2.	In addition, operators  shall ensure that dogs and cats are adequately fed and hydrated by supplying:
+(a)	clean and fresh water, ad libitum;
+(b)	feed of sufficient quantity and quality to meet the physiological, nutritional and metabolic needs  of the dogs and cats, as part of a diet adapted to the age, breed, category, activity level,  health and reproductive status of the dogs or cats, with the overall objective of achieving and maintaining their good health;
+(c)	feed free of substances which could cause suffering;
+(d)	feed in such a way as to avoid abrupt changes and ensure a well-functioning gastro-intestinal system, in particular during the weaning phase.
+3.	Operators  shall ensure that feeding and watering facilities are kept clean and are constructed and installed in such a way as to:
+(a)	provide equal access to adequate amounts of feed and water for all dogs or cats and minimise competition between them;
+(b)	minimise spillage and prevent the contamination of feed and water with harmful physical, chemical or biological contaminants;
+(c)	prevent injury, drowning or other harm to the dogs or cats;
+(d)	be easily cleaned and disinfected to prevent the spread of diseases.
+4.	Where advised in writing by a veterinarian to do so, the operators may adjust the feeding and watering frequencies for an individual dog or cat. The operators shall keep a record of that written advice for the entire duration of those arrangements.</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores devem assegurar que os cães ou gatos são alimentados em conformidade com os requisitos estabelecidos no ponto 1 do Anexo I.
 2. Os operadores devem assegurar que os cães ou gatos são adequadamente alimentados e hidratados através do fornecimento de:
@@ -1488,35 +1593,35 @@
 3a. Quando aconselhado por escrito por um médico veterinário, os operadores podem ajustar as frequências de alimentação e hidratação para um cão ou gato individual. Os operadores devem manter um registo do conselho durante toda a sua duração, conforme aconselhado pelo médico veterinário.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Arts. 7.º (n.º 1, al. a) e 10.º (n.º 1, al. a) do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Artigo 7.º - Princípios fundamentais: Não passem fome ou sede, nem sejam sujeitos a malnutrição.
 Artigo 10.º - Obrigações especiais dos detentores: Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável. Ênfase em necessidades nutricionais adequadas ao estado de saúde.</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Art.º 46.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>Alimentação e abeberamento:
 A alimentação dos animais de companhia, nos locais de criação, manutenção e venda bem como nos centros de recolha e instalações de hospedagem, deve obedecer a um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies.
 Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Decreto-Lei n.º 276/2001 - Artigo 12.º</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>1 — Deve existir um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies e dos indivíduos de acordo com a fase de evolução fisiológica em que se encontram, nomeadamente idade, sexo, fêmeas prenhes ou em fase de lactação.
 2 — As refeições devem ainda ser variadas, sendo distribuídas segundo a rotina que mais se adequar à espécie e de forma a manter, tanto quanto possível, aspetos do seu comportamento alimentar natural.
@@ -1526,71 +1631,71 @@
 6 — Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
+      <c r="K11" s="8" t="inlineStr">
         <is>
           <t>NÃO APLICÁVEL - Diploma não específico nesta matéria</t>
         </is>
       </c>
-      <c r="L10" s="9" t="inlineStr">
+      <c r="L11" s="9" t="inlineStr">
         <is>
           <t>SIM - COBERTURA COMPLETA (Art. 46.º implementa integralmente)</t>
         </is>
       </c>
-      <c r="M10" s="10" t="inlineStr">
+      <c r="M11" s="10" t="inlineStr">
         <is>
           <t>SIM - COBERTURA COMPLETA (linguagem modernizada)</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="N11" s="11" t="inlineStr">
         <is>
           <t>COBERTURA COMPLETA. Código do Animal (Art. 46.º) implementa todos os requisitos do Artigo 11.º. RGBEAC alinha melhor com linguagem e especificidades do Regulamento europeu. Sem divergências substanciais.</t>
         </is>
       </c>
-      <c r="O10" s="11" t="inlineStr">
+      <c r="O11" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P10" s="11" t="inlineStr">
+      <c r="P11" s="11" t="inlineStr">
         <is>
           <t>Correspondências completas - RGBEAC alinha melhor com Regulamento EU</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="120" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12" ht="120" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Alojamento (Housing)</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 12.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>1. Operators of breeding and selling establishments shall ensure that dogs or cats are provided with housing in accordance with point 2 of the annex I. Operators of shelters shall ensure that dogs or cats are provided with housing in accordance with point 2.2 of the annex I.
-2. Operators shall ensure that:
-a) the establishments where dogs or cats are kept and the equipment used therein are suitable for the types and the number of dogs or cats, and allow the necessary access to and a thorough inspection of all dogs or cats;
-b) all building components of the establishment, including the flooring, roof, and space divisions, as well as the equipment used for dogs or cats, are constructed and maintained properly, to ensure that they do not pose any risks to the welfare of the dogs or cats.
-(ba) all building components of the establishment, including the flooring, and space divisions, as well as the equipment used for dogs or cats, are kept cleaned to ensure that they do not pose any risks to the welfare of the dogs or cats;
-c) in breeding and selling establishments where dogs or cats are kept indoors, dust, temperature, relative air humidity and gas concentrations are not harmful to dogs or cats and that ventilation is sufficient to avoid overheating;
-d) dogs and cats have enough space to be able to move around freely and to express species-specific behaviour according to their needs with a possibility to withdraw and rest;
-(da) dogs or cats have clean, comfortable and dry resting places, sufficiently large and numerous to ensure that all of them can lie down and rest at the same time in a natural position;
-e) appropriate structures and measures are in place for dogs or cats kept outdoors to protect them from adverse climatic conditions, including to prevent thermal stress, sunburn and frostbite.
-3. Operators shall not keep dogs or cats in containers.
-By way of derogation, containers may only be used for the transport, short term isolation of individual dogs or cats and during the participation in shows, exhibitions and competitions, for puppies or kittens with reduced thermoregulation capacity or puppies or kittens together with their mothers, provided that stress is minimised and suffering is avoided and the dogs and cats are able to stand and lie down in a natural position.
-4. Operators shall not keep dogs older than 8 weeks exclusively indoors. Such dogs shall have daily access to an outdoor area, or be walked daily, to allow exercise, exploration and socialization. The duration of the daily access to an outdoor area or walk shall be minimum one hour in total. The operator may only derogate from these requirements based on written advice of a veterinarian.
-5. When cats are kept in catteries, operators shall design and construct individual enclosures to allow cats to move around freely and to express their natural behaviour.
-6. Operators of breeding and selling establishments shall ensure that in indoor areas where dogs or cats are kept, an appropriate thermoneutral zone is maintained taking into account their coat type, age, size, breed, and health.
-6a. Operators of breeding and selling establishments shall use, where necessary, heating or cooling systems to maintain good air quality, an appropriate temperature in indoor enclosures at their establishments, and remove excessive moisture.
-7. Operators shall ensure that dogs or cats are exposed to light, and are able to stay in the dark for sufficient and uninterrupted periods in order to maintain a normal circadian rhythm.
-For the purposes of the first subparagraph, 'light' means natural light, complemented, where needed, due to the climatic conditions and geographic position of a Member State, by artificial light.
-7a. Paragraphs 2(a), (b), (ba) (da) (e), 6, 6a and 7 shall not apply to livestock guardian dogs, nor to herding dogs, during the periods where such dogs are used for guarding or herding in the context of on foot seasonal transhumance.</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 15.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>1.	The operators of breeding and selling establishments shall ensure that dogs and cats are housed in accordance with point 2 of Annex I. The operators of shelters shall ensure that dogs and cats are housed in accordance with point 2.2 of Annex I.
+2.	Operators  shall ensure that:
+(a)	the establishments where dogs or cats are kept and the equipment used therein are suitable for the types and the number of dogs or cats, and make possible the necessary access to, and the thorough inspection of, all dogs or cats;
+(b)	all building components of the establishment, including the flooring and roof,  and space divisions, as well as the equipment used for dogs or cats, are constructed and maintained properly,  to ensure that they do not pose any risks to the welfare of the dogs or cats;
+(c)	all building components of the establishment, including the flooring, and space divisions, as well as the equipment used for dogs or cats, are kept clean to ensure that they do not pose any risks to the welfare of the dogs or cats;
+(d)	 in breeding and selling establishments where dogs or cats are kept indoors, the dust levels, the temperature, and the relative air humidity and gas concentrations are  not harmful to dogs or cats and that ventilation is sufficient to avoid overheating  ;
+(e)	dogs or cats have enough space to be able to move around freely and to express species-specific behaviour according to their needs with the possibility to withdraw and rest;
+(f)	dogs or cats have clean, comfortable and dry resting places that are sufficiently large and numerous to ensure that all of them can lie down and rest in a natural position at the same time;
+(g)	appropriate structures and measures are in place for dogs or cats that are kept outdoors in order to protect them from adverse weather conditions, including to prevent thermal stress, sunburn and frostbite.
+3.	Operators shall not keep dogs or cats in containers
+However, containers may be used for transportation, for the short term isolation of individual dogs or cats and for participation in shows, exhibitions and competitions, for puppies or kittens with reduced thermoregulation capacity or for puppies or kittens together with their mothers, provided that, for the dogs or cats concerned, stress is minimised and suffering is avoided, and they are able to stand, turn around and lie down in a natural position.
+4.	Operators shall not keep dogs older than 8 weeks exclusively indoors. Such dogs shall have daily access to an outdoor area, or be walked daily,  to allow exercise, exploration and socialisation. The minimum combined duration of such daily access or walk shall be one hour in total. The operator may only deviate from these requirements based on the written advice of a veterinarian.
+5.	When cats are kept in catteries, operators shall design and construct individual enclosures to allow cats to move around freely and to exhibit their natural behaviour.
+6.	Operators of breeding and selling establishments shall ensure that  in indoor areas where dogs and cats are kept, an appropriate thermoneutral zone is maintained that takes into account their coat type, age, size, breed, and health.
+7.	Operators of breeding and selling establishments shall, where necessary, use heating or cooling systems in the indoor enclosures at their establishments to maintain good air quality and an appropriate temperature and to remove excessive moisture.
+8.	Operators shall ensure that dogs or cats are exposed to light, and are able to stay in the dark for sufficient and uninterrupted periods in order to maintain a normal circadian rhythm.
+For the purposes of the first subparagraph, ‘light’ means natural light, complemented, where necessary due to the climatic conditions and geographic position of a Member State, by artificial light.
+9.	Paragraph 2, points (a), (b), (c) (f) and (g), and paragraphs 6, 7 and 8 shall apply neither to livestock guardian dogs, nor to herding dogs, during the periods where such dogs are used for guarding or herding in the context of seasonal transhumance on foot. Paragraph 2(f) shall not apply to livestock guardian dogs during the periods when such dogs are used for training purposes.</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores de estabelecimentos de criação e venda devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2 do Anexo I. Os operadores de abrigos devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2.2 do Anexo I.
 2. Os operadores devem assegurar que:
@@ -1612,12 +1717,12 @@
 7a. Os parágrafos 2(a), (b), (ba) (da) (e), 6, 6a e 7 não se aplicam a cães guardiões de gado, nem a cães de pastoreio, durante os períodos em que tais cães são utilizados para guarda ou pastoreio no contexto de transumância sazonal a pé.</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Arts. 7.º, 10.º, 11.º, 47-57 do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Artigo 7.º - Princípios: Condições de detenção e alojamento salvaguardam bem-estar animal.
 Artigo 10.º - Obrigações especiais: Liberdade de movimento, proibição de contenção permanente, espaço adequado, enriquecimento ambiental e abrigo protetor.
@@ -1625,12 +1730,12 @@
 Artigos 47-57 - Regulação detalhada de alojamentos para hospedagem (estruturas, proteção, maneio, responsabilidades veterinárias).</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Arts. 3.º, 14.º, 18.º, 28.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Artigo 3.º - Define 'Alojamento' como qualquer instalação, edifício ou local onde animais se encontram mantidos.
 Artigo 14.º - A temperatura, ventilação, luminosidade e obscuridade devem ser adequadas ao conforto e bem-estar.
@@ -1638,12 +1743,12 @@
 Artigo 28.º - Define separação por espécie e requisitos de estrutura para hospedagem.</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Decreto-Lei n.º 276/2001 - Artigos 8.º e 15.º</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>Artigo 8.º — 1 — Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir: a) A prática de exercício físico adequado; b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
 2 — Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.
@@ -1652,69 +1757,69 @@
 Artigo 15.º — Os alojamentos devem assegurar que as espécies animais neles mantidas não possam causar quaisquer riscos para a saúde e para a segurança de pessoas, outros animais e bens.</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>PARCIAL - Não específico para condições técnicas de alojamento</t>
         </is>
       </c>
-      <c r="L11" s="9" t="inlineStr">
+      <c r="L12" s="9" t="inlineStr">
         <is>
           <t>SIM - COBERTURA COMPLETA (Arts. 3, 14, 18, 28)</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M12" s="10" t="inlineStr">
         <is>
           <t>SIM - COBERTURA EXPANDIDA (especifica detalhes técnicos)</t>
         </is>
       </c>
-      <c r="N11" s="11" t="inlineStr">
+      <c r="N12" s="11" t="inlineStr">
         <is>
           <t>COBERTURA COMPLETA. Código do Animal e RGBEAC implementam requisitos do Artigo 12.º. Faltam especificações técnicas detalhadas (temperatura, ventilação, iluminação) — recomenda-se Portaria complementar.</t>
         </is>
       </c>
-      <c r="O11" s="11" t="inlineStr">
+      <c r="O12" s="11" t="inlineStr">
         <is>
           <t>Sim - Portaria complementar com especificações técnicas</t>
         </is>
       </c>
-      <c r="P11" s="11" t="inlineStr">
+      <c r="P12" s="11" t="inlineStr">
         <is>
           <t>Princípios cobertos; faltam normas técnicas pormenorizadas</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="120" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Saúde e Monitorização Sanitária</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 13.º do Regulamento 2023/0447 (PE/Conselho)</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>1. Operators shall ensure that:
-(a) dogs or cats under their responsibility are inspected by animal caretakers at least once a day and vulnerable dogs and cats, such as newborns, ill or injured dogs and cats, and peri-partum bitches and queens, are inspected more frequently;
-(b) dogs or cats with compromised welfare are, where necessary, transferred without undue delay to a separate area and, where needed, receive appropriate treatment;
-(c) where the recovery of a dog or a cat with compromised welfare is not achievable and the dog or cat experiences severe pain or suffering, a veterinarian is consulted without undue delay, to decide whether the dog or cat shall be euthanised to end its suffering, and, if that is the case, to perform the euthanasia using anesthesia and analgesia;
-(d) measures to prevent and control external and internal parasites, and vaccinations to prevent common diseases to which dogs or cats are likely to be exposed are implemented;
-(e) enrichment do not present a significant risk of injury or biological or chemical contamination or any other health risk.
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 16.º do Regulamento 2023/0447 (PE/Conselho)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>1.	Operators  shall ensure that:
+(a)	dogs or cats for which they are responsible are inspected by animal carers at least once a day and that vulnerable dogs and cats, such as newborns, ill or injured dogs and cats, and peri-partum bitches and queens, are inspected more frequently;
+(b)	dogs or cats with  compromised welfare are, where necessary, transferred  without undue delay to a separate area and, where necessary, receive appropriate treatment;
+(c)	where the recovery of a dog or a cat whose welfare is compromised is not achievable and the dog or cat experiences severe pain or suffering, a veterinarian is consulted without undue delay to decide whether the dog or cat is to be euthanised to end its suffering, and, if that is the case, to perform the euthanasia using anaesthesia and analgesia.
+(d)	measures  are taken to prevent and control external and internal parasites, and vaccinations are carried out to prevent common diseases to which dogs or cats are likely to be exposed.
+(e)	enrichments  that are used do not present a significant risk to dogs and cats of injury or biological or chemical contamination or any other health risk.
 Point (a) shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
-Member states may grant derogations from point (c) in cases of emergencies, where no veterinarian can be reached without undue delay, provided that national rules are put in place to ensure that:
-(i) an immediate action ending the life of the dog or cat with minimum pain and suffering using a method inducing instant death is undertaken by a trained competent person;
-(ii) the operator keeps a record of the use of the derogation for purposes of the official control.
-2. Operators of breeding establishments shall additionally ensure that:
-(-a) measures are taken to safeguard the health of dogs or cats in accordance with point 3 of Annex I;
-(-b) bitches or queens are only bred if they have reached a minimum age and skeletal maturity in accordance with point 3 of Annex I, and they have no diagnosed disease, clinical sign of diseases or physical conditions which could negatively impact their pregnancy and welfare;
-(-c) litter-giving pregnancies of bitches or queens follows a maximum frequency in accordance with point 3 of Annex I;
-(-d) lactating queens are not mated or inseminated;
-(-e) dogs and cats which are no longer used for reproduction, including as a result of the provisions of this Regulation, are either kept or sold, donated or rehomed, not killed or abandoned.</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
+Member States may grant exemptions from point (c) in cases of emergency, where no veterinarian can be reached without undue delay, provided that national rules are put in place to ensure that:
+(i)	any immediate action ending the life of the dog or cat with minimum pain and suffering using a method inducing instant death is undertaken by a trained competent person;
+(ii)	for the purposes of the official control under Regulation (EU) 2017/625, the operator keeps a record of the use of the exemption.
+2.	Operators of breeding establishments shall ensure that:
+(a)	measures are taken to safeguard the health of dogs or cats in accordance with point 3 of Annex I;
+(b)	bitches or queens are bred only if they have reached a minimum age and skeletal maturity in accordance with point 3 of Annex I  , and only if they have no diagnosed disease, clinical sign of diseases or physical conditions which could negatively impact their pregnancy and welfare;
+(c)	the litter-giving pregnancies of bitches or queens follows a maximum frequency in accordance with point 3 of Annex I;
+(d)	lactating queens are not mated or inseminated;
+(e)	 dogs and cats which are no longer used for reproduction, including as a result of the provisions of this Regulation, are either kept or sold, donated or rehomed, and not killed or abandoned.</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>1 — Os operadores devem assegurar que:
 (a) os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados e fêmeas em período peri-parto, são inspecionados com maior frequência;
@@ -1734,12 +1839,12 @@
 (-e) os cães e gatos que deixem de ser utilizados para reprodução, nomeadamente em resultado das disposições do presente Regulamento, são mantidos ou vendidos, doados ou realojados, não sendo mortos nem abandonados.</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Art.º 33.º do RGBEAC — Regime Geral do Bem-Estar dos Animais de Companhia (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Artigo 33.º — Cuidados de saúde
 1 — Os detentores dos animais de companhia devem assegurar-lhes os cuidados de saúde adequados, nomeadamente seguindo as orientações da DGAV em matéria de vacinação e tratamentos obrigatórios, bem como consultas regulares junto de médico veterinário.
@@ -1749,23 +1854,23 @@
 [dim]5 — Os médicos veterinários denunciam, junto da DGAV ou demais entidades com competência de fiscalização do cumprimento das normas constantes do presente decreto-lei, sempre que, no exercício de sua profissão, suspeitem de maus-tratos a animais de companhia.</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Art.º 6.º (Cuidados médico-veterinários) do Código do Animal — DL n.º 214/2013</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>Artigo 6.º — Cuidados médico-veterinários
 O detentor do animal deve assegurar ao animal ferido ou doente os cuidados médico-veterinários adequados, designadamente retirando o mesmo do alojamento sempre que este seja um local de venda.</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>Art.º 13.º (Maneio) e art.º 16.º (Cuidados de saúde animal) do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Artigo 13.º — Maneio
 1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
@@ -1782,62 +1887,62 @@
 [dim]6 — A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior deve ser feita sob orientação do médico veterinário responsável.</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 prevê inspeção diária (n.º 3 do art.º 13.º) e programa de profilaxia supervisionado por veterinário (n.º 1 do art.º 16.º) — alinhamento parcial com as als. (a) e (d) do n.º 1 do art.º 13.º do @regulamento. Lacunas: (1) não distingue animais vulneráveis com maior frequência de inspeção; (2) não prevê isolamento em área separada com tratamento (al. (b)); (3) não exige consulta veterinária para decisão de eutanásia com anestesia/analgesia (al. (c)); (4) nenhuma das obrigações sanitárias para criadores previstas no n.º 2 está contemplada: sem idade mínima de reprodução, sem frequência máxima de partos, sem proibição de cobrição de fêmeas a lactar, sem regime de rehoming.</t>
         </is>
       </c>
-      <c r="L12" s="9" t="inlineStr">
+      <c r="L13" s="9" t="inlineStr">
         <is>
           <t>O @codigo limita os cuidados médico-veterinários ao animal ferido ou doente (art.º 6.º) — sem qualquer obrigação de inspeção diária, programa de profilaxia ou isolamento. É o diploma com maior divergência face ao n.º 1 do art.º 13.º do @regulamento, omitindo igualmente todas as obrigações sanitárias específicas para criadores previstas no n.º 2.</t>
         </is>
       </c>
-      <c r="M12" s="10" t="inlineStr">
+      <c r="M13" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.º 33.º) centra os cuidados de saúde no detentor em geral (n.ºs 1 a 3), sem distinguir obrigações reforçadas para operadores de criação. Não prevê: inspeção diária sistemática por cuidadores; isolamento imediato de animais com bem-estar comprometido; nem qualquer dos requisitos sanitários para criadores do n.º 2 do art.º 13.º do @regulamento. Os n.ºs 4 e 5 (CAMV e denúncia de maus-tratos) não têm correspondência direta no @regulamento.</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr">
+      <c r="N13" s="11" t="inlineStr">
         <is>
           <t>A @legislacao vigente (DL n.º 276/2001) tem o maior alinhamento, mas insuficiente. Necessidade de alteração dos três diplomas: (1) introduzir inspeção diária diferenciada para animais vulneráveis (al. (a) do n.º 1 do art.º 13.º do @regulamento); (2) criar obrigação de isolamento e tratamento imediato (al. (b)); (3) regular o processo de eutanásia com supervisão veterinária e anestesia/analgesia (al. (c)); (4) para criadores (n.º 2): fixar idade mínima e maturidade esquelética das fêmeas reprodutoras, frequência máxima de partos conforme Anexo I, proibição de cobrição de fêmeas a lactar, e regime de rehoming dos animais retirados da reprodução.</t>
         </is>
       </c>
-      <c r="O12" s="11" t="inlineStr">
+      <c r="O13" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P12" s="11" t="inlineStr"/>
+      <c r="P13" s="11" t="inlineStr"/>
     </row>
-    <row r="13" ht="120" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Necessidades Comportamentais (Behavioural needs)</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 14.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>1. Operators shall ensure that measures are taken to meet the behavioural needs of dogs or cats in accordance with point 4 of Annex I.
-2. Operators shall not keep dogs or cats in areas restraining their natural movements, except in case of Article 12(3), second sub-paragraph, or for performing the following procedures or treatments:
-a) physical examinations;
-b) individual identification of dogs or cats and reading the identification information;
-c) collection of samples and vaccinations;
-d) procedures for grooming, hygienic, health or reproductive purposes other than mating;
-e) medical treatment, including surgical treatment or prescribed rehabilitation.
-3. Tethering for more than 1 hour shall be prohibited, except for the duration of a medical treatment or participation in shows, exhibitions and competitions of dogs and cats.
-3a. Member States may grant derogations from paragraph 3 for dogs intended for use in military, police and customs services that are kept in breeding or selling establishments.
-4. Operators shall ensure that conditions are in place to allow dogs or cats to express social non-harmful behaviours, species-specific behaviours and the possibility to experience positive emotions.
-5. Operators shall ensure that dogs or cats can socialise in accordance with point 4 of Annex I. Operators of breeding establishments shall document their strategy for such socialisation.
-5a. The first subparagraph shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes nor to herding dogs during seasonal transhumance.
-6. Operators shall ensure that enrichment is provided and accessible to all dogs or cats, creating a stimulating environment, enabling species-specific behaviour and reducing their frustration.</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 17.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>1.	Operators  shall ensure that measures are taken to meet the behavioural needs of  dogs and cats in accordance with point 4 of Annex I.
+2.	In addition, operators shall not keep dogs or cats in areas which limit their natural movements  , except in cases where Article 15(3), second subparagraph, applies or where the following procedures or treatments are performed:
+(a)	physical examinations ;
+(b)	the individual identification of dogs or cats, or reading such identification information;
+(c)	the collection of samples and vaccinations;
+(d)	procedures for grooming, hygienic, health or reproductive purposes other than mating;
+(e)	medical treatments, including surgical treatments or prescribed rehabilitation.
+3.	Tethering  for more than 1 hour shall be prohibited, except for the duration of a medical treatment or for participation in shows, exhibitions and competitions of dogs or cats.
+4.	Member States may grant exemptions from paragraph 3 for dogs intended for use in military, police and customs services that are kept in breeding or selling establishments.
+5.	Operators  shall ensure that dogs or cats are kept in conditions that allow them to exhibit non-harmful social behaviours and species-specific behaviours and to experience positive emotions.
+6.	Operators shall ensure that dogs or cats can socialise in accordance with point 4 of Annex I. Operators of breeding establishments shall have a documented strategy for such socialisation.
+By way of derogation from the first subparagraph, socialisation requirements shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes, or to herding dogs during seasonal transhumance.
+7.	Operators shall ensure that enrichments  are provided and accessible to all dogs or cats, creating a stimulating environment for them, enabling them to develop and exhibit species-specific behaviour and reducing their frustration.</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores devem assegurar que medidas são tomadas para satisfazer as necessidades comportamentais de cães ou gatos em conformidade com o ponto 4 do Anexo I.
 2. Os operadores não devem manter cães ou gatos em áreas que restringem os seus movimentos naturais, exceto no caso do artigo 12.º (parágrafo 3), segundo parágrafo, ou para realizar os seguintes procedimentos ou tratamentos:
@@ -1854,12 +1959,12 @@
 6. Os operadores devem assegurar que enriquecimento é fornecido e acessível a todos os cães ou gatos, criando um ambiente estimulante, permitindo comportamento específico da espécie e reduzindo a sua frustração.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>RGBEAC (proposta, jun. 2025) - Artigos 10, 12, 13, 14, 15</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Especificação clara: 'exercício físico e estímulo mental'.
 'Contato social adequado'.
@@ -1868,89 +1973,89 @@
 Documentação obrigatória de estratégia de socialização (criadores).</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>Arts. 5.º e 13.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Artigo 5.º - Princípios que proíbem violência e maus-tratos, garantem bem-estar.
 Artigo 13.º - Espaço para exercício físico e expressão de comportamentos naturais.
 Cobertura GENÉRICA: não especifica enriquecimento, socialização ou método de treino baseado em reforço positivo.</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>Decreto-Lei n.º 276/2001 - Artigo 8.º</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>Artigo 8.º — 1 — Os animais devem dispor de um espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir: a) A prática de exercício físico adequado; b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
 2 — Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>PARCIAL - Legislação vigente oferece cobertura genérica</t>
         </is>
       </c>
-      <c r="L13" s="9" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>PARCIAL - Genérico, sem especificações sobre socialização e enriquecimento</t>
         </is>
       </c>
-      <c r="M13" s="10" t="inlineStr">
+      <c r="M14" s="10" t="inlineStr">
         <is>
           <t>SIM - COBERTURA SIGNIFICATIVAMENTE EXPANDIDA</t>
         </is>
       </c>
-      <c r="N13" s="11" t="inlineStr">
+      <c r="N14" s="11" t="inlineStr">
         <is>
           <t>Legislação portuguesa oferece cobertura genérica. RGBEAC (2025) oferece avanço substancial com obrigatoriedade de reforço positivo e documentação de estratégia de socialização. Falta ainda regulamentação pormenorizada.</t>
         </is>
       </c>
-      <c r="O13" s="11" t="inlineStr">
+      <c r="O14" s="11" t="inlineStr">
         <is>
           <t>Sim - Regulamentação específica sobre métodos de treino</t>
         </is>
       </c>
-      <c r="P13" s="11" t="inlineStr">
+      <c r="P14" s="11" t="inlineStr">
         <is>
           <t>RGBEAC alinha melhor; implementação de reforço positivo obrigatório recomendada</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="120" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15" ht="120" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Práticas Dolorosas (Painful practices)</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 15.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>1. Operators shall ensure that mutilations, including ear cropping, tail docking, claw removal or other partial or complete digit amputation, and resection of vocal cords or folds, are not performed unless upon medical indication, which may include prophylactic, with the sole purpose of preserving, improving the health of dogs or cats or preventing injury. In such case, the procedure shall only be performed under anaesthesia and prolonged analgesia and by a veterinarian.
-1a. The medical indication for the mutilation and the details of procedure carried out shall be documented by a veterinarian. This document shall be retained by the operator until the dog or cat, together with this document, is transferred to another establishment or owner. The operator of the establishment where the mutilation was performed shall retain a copy of the document for three years after the transfer of the dog or cat.
-1b. By way of derogation from paragraph 1, Member States may allow ear cropping by notching or tipping cat ears in the context of marking stray cats when neutered under a trap-neuter-return programme.
-2. Operators shall ensure that neutering is only performed under anaesthesia and prolonged analgesia and by a veterinarian. By way of derogation, Member States may allow that the neutering of male cats is performed by a licensed veterinary nurse.
-3. Operators shall ensure that handling practices that cause pain or suffering are not performed, including:
-a) tying up body parts unless for medical reasons in which case the duration shall be limited to the minimum period necessary;
-b) kicking, hitting, dragging, throwing, squeezing dogs or cats;
-c) applying electric current to dogs or cats unless performed for medical reasons;
-d) using of muzzles, unless required for medical reasons, animal or human safety reasons, in which case the duration shall be limited to the minimum period necessary and the dog or cat shall be supervised.
-(da) using prong collars;
-(db) using choke collars without safety stop;
-e) lifting dogs or cats by the limbs, head, ears, tail or hair, or lifting adult dogs or cats by the skin.
-4. Member States may grant derogations from paragraph 3 for dogs intended for use in military, police or customs services.</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 18.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>1.	Operators shall ensure that mutilations, including ear cropping, tail docking, claw removal or other partial or complete digit amputation, and resection of vocal cords or folds,  are not performed unless justified by medical indications, including where the procedure is prophylactic, with the sole purpose of maintaining or improving the health of dogs or cats or preventing their injury. In such cases, the procedure shall be performed  only under anaesthesia and prolonged analgesia and only by a veterinarian.
+2.	The medical indications justifying the mutilation, and the details of procedure carried out, shall be documented by a veterinarian. That document shall be retained by the operator and shall accompany the dog or cat when it is transferred to another establishment or owner. The operator of the establishment where the mutilation was performed shall retain a copy of the document for the first three years after that transfer.
+3.	By way of derogation from paragraph 1, Member States may allow ear cropping by notching or tipping cat ears in the context of marking stray cats when neutered under a ‘trap-neuter-return’ programme.
+4.	Operators shall ensure that neutering is performed  only under anaesthesia and prolonged analgesia and only by a veterinarian. However, Member States may allow the neutering of male cats to be performed by a licensed veterinary nurse.
+5.	Operators shall ensure that handling practices that cause pain or suffering are not performed, including:
+(a)	tying up body parts, unless required for medical reasons and limited to the minimum period necessary;
+(b)	the kicking, hitting, dragging, throwing or squeezing of dogs or cats;
+(c)	applying electric current to dogs or cats, unless performed for medical reasons;
+(d)	using  muzzles, unless required for medical reasons or animal or human safety reasons, limited to the minimum period necessary and where the dog or cat is supervised.
+(e)	using prong collars;
+(f)	using choke collars without a safety stop;
+(g)	lifting dogs or cats by the limbs,  head, ears, tail or hair, or lifting adult dogs or cats by the skin.
+Member States may grant exemptions from the first subparagraph for dogs intended for use in military, police or customs services.</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores devem assegurar que mutilações, incluindo corte de orelhas, corte de cauda, remoção de garras ou amputação parcial ou completa de dígitos, e ressecção de cordas vocais ou pregas, não são realizadas a menos que por indicação médica, que pode incluir profilática, com o único propósito de preservar, melhorar a saúde de cães ou gatos ou prevenir ferimentos. Nesse caso, o procedimento deve ser realizado apenas sob anestesia e analgesia prolongada e por um médico veterinário.
 1a. A indicação médica para a mutilação e os detalhes do procedimento realizado devem ser documentados por um médico veterinário. Este documento deve ser retido pelo operador até que o cão ou gato, juntamente com este documento, seja transferido para outro estabelecimento ou proprietário. O operador do estabelecimento onde a mutilação foi realizada deve reter uma cópia do documento durante três anos após a transferência do cão ou gato.
@@ -1967,12 +2072,12 @@
 4. Os Estados-Membros podem conceder derrogações do parágrafo 3 para cães destinados a uso em serviços militares, policiais ou aduaneiros.</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>RGBEAC (proposta, jun. 2025) - Artigo 12.º</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Lista idêntica de mutilações proibidas ao Código.
 Referência a 'boas práticas internacionais' (alinhamento com Reg. 2023/0447).
@@ -1981,12 +2086,12 @@
 Documentação obrigatória de indicação médica.</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Arts. 51.º e 52.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>Artigo 51.º - Intervenções cirúrgicas exclusivamente por médico veterinário.
 Artigo 52.º - Proibição específica de mutilações:
@@ -1997,164 +2102,169 @@
 - Exceções: reprodução e interesse do animal (com documentação)</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>Decreto-Lei n.º 276/2001 - Artigo 18.º</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>Artigo 18.º — 1 — Os detentores de animais de companhia que os apresentem com quaisquer amputações que modifiquem a aparência dos animais ou com fins não curativos devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa amputação.
 2 — O documento referido no número anterior deve ter a forma de um atestado, do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura.</t>
         </is>
       </c>
-      <c r="K14" s="8" t="inlineStr">
+      <c r="K15" s="8" t="inlineStr">
         <is>
           <t>SIM - DL 276/2001 cobre amputações documentadas</t>
         </is>
       </c>
-      <c r="L14" s="9" t="inlineStr">
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>SIM - COBERTURA COMPLETA (Arts. 51-52)</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>SIM - COBERTURA COMPLETA + EXPANSÃO</t>
         </is>
       </c>
-      <c r="N14" s="11" t="inlineStr">
+      <c r="N15" s="11" t="inlineStr">
         <is>
           <t>COBERTURA COMPLETA. Código do Animal (Arts. 51-52) implementa integralmente Art. 15.º. RGBEAC alinha substancialmente com Regulamento europeu. Sem divergências substanciais.</t>
         </is>
       </c>
-      <c r="O14" s="11" t="inlineStr">
+      <c r="O15" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P14" s="11" t="inlineStr">
+      <c r="P15" s="11" t="inlineStr">
         <is>
           <t>Correspondências completas - Cobertura legislativa adequada</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="120" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16" ht="120" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Espetáculos e Competições Estéticas</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Art.º 15a do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Operators of breeding and selling establishments shall not use in aesthetic shows, exhibitions and competitions of dogs and cats, dogs or cats with excessive conformational traits or dogs or cats which have been mutilated in such a way that results in an alteration of physical characteristics.
-Organisers of aesthetic shows, exhibitions and competitions of dogs and cats shall exclude from such shows, exhibitions and competitions dogs and cats which have excessive conformational traits or dogs or cats which have been mutilated in such a way that results in an alteration of physical characteristics.</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>1.	In aesthetic shows, exhibitions and competitions of dogs and cats, operators of breeding and selling establishments shall not use dogs or cats with excessive conformational traits, or dogs or cats which have been mutilated in a way that alters their physical characteristics.
+2.	When organising aesthetic shows, exhibitions and competitions of dogs and cats, organisers shall exclude dogs and cats which have excessive conformational traits or dogs or cats which have been mutilated in a way that alters their physical characteristics.
+CHAPTER III
+IDENTIFICATION AND REGISTRATION OF DOGS AND CATS</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Os operadores de estabelecimentos de criação e venda não devem utilizar em espetáculos, exposições e competições estéticas de cães e gatos, cães ou gatos com características conformacionais excessivas ou cães ou gatos que tenham sido mutilados de tal forma que resulte numa alteração de características físicas.
 Os organizadores de espetáculos, exposições e competições estéticas de cães e gatos devem excluir de tais espetáculos, exposições e competições cães e gatos que tenham características conformacionais excessivas ou cães ou gatos que tenham sido mutilados de tal forma que resulte numa alteração de características físicas.</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Art.º 39.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Artigo 39.º - Participação em eventos
 1 – A participação de animais de companhia em concursos, exposições, espetáculos, manifestações culturais, divertimentos públicos, atividades performativas, cinematográficas e audiovisuais, campanhas publicitárias, ou outros eventos onde participem animais de companhia carece de autorização do diretor geral da DGAV a área da realização da mesma, após parecer da respetiva câmara municipal.
 3 - Só serão admitidos no evento os animais de companhia que: a) Estejam registados no SIAC; b) Quando aplicável, possuam prova de vacinação antirrábica; c) Possuam vacinações contra as principais doenças infectocontagiosas; d) Não tenham sido submetidos a intervenções cirúrgicas em infração.</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>Art.º 79.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>Artigo 79.º - Concursos e exposições
 1 - A realização de concursos e exposições com animais de companhia carece de autorização prévia da câmara municipal, ficando esta dependente do parecer vinculativo do MVM.
 3 - Só são admitidos a concurso os cães e gatos que: a) Estejam identificados eletronicamente; b) Sejam portadores de boletim sanitário e prova de vacinação antirrábica; c) Possuam vacinações contra principais doenças infecto-contagiosas.</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>Lei n.º 27/2016 e DL n.º 82/2019 (Normas de eventos)</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>A legislação portuguesa estabelece que a participação de animais em espetáculos e competições requer: - Autorização prévia de autoridades competentes; - Identificação e registo no SIAC; - Vacinações obrigatórias; - Supervisão veterinária durante o evento; - Condições de bem-estar animal garantidas.</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="K16" s="8" t="inlineStr">
         <is>
           <t>SIM - Cobertura COMPLETA (autorização, identificação, vacinação, supervisão veterinária)</t>
         </is>
       </c>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="L16" s="9" t="inlineStr">
         <is>
           <t>SIM - Cobertura COMPLETA (concursos e exposições com requisitos específicos)</t>
         </is>
       </c>
-      <c r="M15" s="10" t="inlineStr">
+      <c r="M16" s="10" t="inlineStr">
         <is>
           <t>SIM - Cobertura COMPLETA (participação em eventos com normas de bem-estar)</t>
         </is>
       </c>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="N16" s="11" t="inlineStr">
         <is>
           <t>A legislação portuguesa cobre completamente os requisitos do Artigo 15a. Implementa autorizações prévias, exigências de identificação, vacinação obrigatória e supervisão veterinária. O RGBEAC (Art. 39.º) e Código do Animal (Art. 79.º) estabelecem normas detalhadas sobre espetáculos, exposições e competições estéticas.</t>
         </is>
       </c>
-      <c r="O15" s="11" t="inlineStr">
+      <c r="O16" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P15" s="11" t="inlineStr">
+      <c r="P16" s="11" t="inlineStr">
         <is>
           <t>Correspondências completas encontradas - Cobertura legislativa adequada</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="120" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17" ht="120" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Identificação e Registo</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 17.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>1. All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip compliant with Annex II.
-1a. Operators shall ensure that dogs and cats born in their establishments are individually identified within 3 months after their birth and in any event before the date of their placing on the market.
-Operators of selling establishments, shelters and those placing and being responsible for dogs and cats in foster homes shall ensure that dogs and cats that enter their establishments or come under their responsibility are individually identified within 30 days after their arrival at the establishment and in any event before the date of their placing on the market.
-Pet owners and any other natural or legal persons, other than operators, who own dogs or cats, shall ensure that the dogs or cats are individually identified at the latest when the dog or cat reaches 3 months of age or, in case the dog or cat is placed on the market, before the date of their placing on the market.
-2. The implantation of the transponder shall be performed by a veterinarian. Member States may allow the implantation of transponders in cats to be performed by a person other than a veterinarian, if it is done under the responsibility of a veterinarian.
-3. Dogs and cats which have been individually identified by means of an injectable transponder containing a microchip, in accordance with national legislation prior to entry into force of this Regulation, shall be recognised as identified in accordance with the requirements of this Article.
-4. Within two working days after their identification, the dogs and cats shall be registered by a veterinarian in a national database.
-5. For dogs and cats kept in establishments, the registration shall be made in the name of the operator of the establishment. For dogs and cats placed in foster homes, the registration shall be made in the name of the person responsible for the foster home. For dogs and cats owned by pet owners or by any other natural or legal person, the registration shall be made in the name of the pet owner or the natural or legal person.
-Member States may grant derogations from the first subparagraph to military, police and customs dogs.
-6. In case of placing on the market or occasional and irregular donation by a natural person without online advertising, the requirements for registration shall not apply.
-7. In the case of a death of a dog or a cat, the operator, pet owner or natural or legal person owning the dog or cat shall inform the national database.
-8. In case of unreadable transponder, the operator or the natural or legal person responsible for the dog or cat shall ensure that the dog or cat is re-identified with a new transponder and re-registered in the national database.</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 20.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>1.	All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip that complies with the requirements set out in Annex II.
+2.	Operators shall ensure that dogs and cats born in their establishments are individually identified within three months after their birth, and in any event before the date that they are placed on the market.
+Operators of selling establishments and shelters, and operators who place and are responsible for dogs and cats in foster homes shall ensure that dogs and cats that enter their establishments or come under their responsibility are individually identified within 30 days of arrival and in any event before the date of their placing on the market.
+Pet owners and any other natural or legal persons other than operators who own dogs or cats, shall ensure that every dog or cat is individually identified at the latest when it reaches the age of three months or, if the dog or cat is placed on the market, before the date of that placing on the market.
+The implantation of the transponder shall be performed by a veterinarian. Member States may allow the implantation of transponders by persons other than veterinarians provided that they adopt national rules laying down  the minimum qualifications that such persons are required to have.
+Where dogs and cats have been individually identified by means of an injectable transponder containing a microchip in accordance with Union or national law before … [date two years after the date of entry into force of this Regulation] they shall be considered to be compliant with the requirements in paragraph 1 and the first, second, third and fourth subparagraphs of this paragraph, provided that the microchip is still readable.
+3.	Within two working days after their identification, the dogs and cats  shall be registered by a veterinarian  in a national database referred to in Article 23. Member States may allow registration by persons other than veterinarians, provided that the Member States have measures in place to ensure the accuracy of information that those persons enter in the database. For dogs and cats kept in  establishments, the registration shall be made in the name of the operator of the  establishment responsible for the dog or the cat. For dogs and cats owned by any other natural and legal persons  , the registration shall be made in the name of those persons.
+Member States may grant exemptions from the first subparagraph of this paragraph in respect of military, police and customs dogs.
+4.	Where dogs or cats are placed on the market or are donated in an occasional manner by natural persons without using online advertising, the natural or legal person transferring the ownership of, or responsibility for, the dog or cat shall ensure that the change of ownership of, or responsibility for, the dog or cat is recorded in the database referred to in Article 23, within two weeks from the date of that transfer, in accordance with the conditions laid down by the Member State responsible for that database.
+5.	In the case of the death of a dog or a cat, the operator, pet owner or natural or legal person owning the dog or cat shall ensure that the death is recorded in the database referred to in Article 23, in accordance with the conditions laid down by the Member State responsible for that database.
+6.	Where a transponder is or becomes unreadable, the operator or the natural or legal person responsible for the dog or cat shall ensure that a new transponder is injected and that the registration in the database is updated with the identification number of that new transponder.
+7.	The identification and registration requirements of this Article shall apply as follows:
+(a) 	for operators and natural or legal persons placing dogs and cats on the market from ... [4 years from the entry into force of this Regulation];
+(b)	for pet owners and other natural or legal persons other than operators, who do not place dogs on the market: from … [10 years from entry into force of this Regulation];
+(c)	 for pet owners and other natural or legal persons other than operators, who do not place cats on the market: from … [15 years from entry into force of this Regulation.</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>1. Todos os cães e gatos mantidos em estabelecimentos colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com o Anexo II.
 1a. Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de 3 meses após o nascimento e, em qualquer caso, antes da data da sua colocação no mercado.
@@ -2170,12 +2280,12 @@
 8. Em caso de transponder ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato devem assegurar que o animal é reidentificado com um novo transponder e re-registado na base de dados nacional.</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Art.º 17.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>1 — A identificação dos animais de companhia, pela sua marcação, quando aplicável, e registo no SIAC, deve ser realizada:
 a) Relativamente aos cães, gatos e furões nascidos em alojamentos, até aos três meses de idade ou, em qualquer caso, antes da sua colocação no mercado;
@@ -2183,12 +2293,12 @@
 c) Relativamente aos cães, gatos e furões detidos por pessoas singulares, exceto nos casos previstos nas alíneas anteriores, até aos três meses de idade ou, no caso de colocação no mercado, antes da data de colocação no mercado.</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>Art.º 53.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>1 — Todos os cães devem ser identificados e registados, entre os três e os seis meses de idade.
 2 — Os gatos em exposição, para fins comerciais ou lucrativos, em estabelecimentos de venda, locais de criação, feiras ou concursos, provas funcionais, publicidade ou fins similares, devem ser identificados e registados entre os três e os seis meses de idade.
@@ -2196,68 +2306,89 @@
 5 — A identificação electrónica é efetuada através da aplicação subcutânea de um microchip no centro da face lateral esquerda do pescoço.</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>n.ºs 1, 2 e 3 do art.º 5.º do DL n.º 82/2019, de 27 de junho</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>1 — A identificação dos animais de companhia, pela sua marcação e registo no SIAC, deve ser realizada até 120 dias após o seu nascimento.
 2 — Na impossibilidade de determinar a data de nascimento exata, para efeitos de contagem do prazo referido no número anterior, a identificação deve ser efetuada até à perda dos dentes incisivos de leite.
 3 — Sem prejuízo dos números anteriores, e relativamente aos cães, gatos e furões que sejam cedidos e ou comercializados a partir de um criador ou de um estabelecimento autorizado para a detenção de animais de companhia, nomeadamente os centros de hospedagem com ou sem fins lucrativos e os centros de recolha oficiais, deve ser assegurada a sua marcação e registo no SIAC antes de abandonarem a instalação de nascimento ou de alojamento, independentemente da sua idade.</t>
         </is>
       </c>
-      <c r="K16" s="8" t="inlineStr">
+      <c r="K17" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 82/2019 (art.º 5.º) prevê prazo geral de 120 dias após o nascimento, sem distinguir o contexto de estabelecimento — prazo superior ao máximo de 3 meses do @regulamento, que exigirá redução. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
-      <c r="L16" s="9" t="inlineStr">
+      <c r="L17" s="9" t="inlineStr">
         <is>
           <t>O @codigo fixa prazo de identificação entre 3 e 6 meses, igualmente sem distinção entre nascimentos e entrada em estabelecimentos, ficando aquém da precisão exigida pelo @regulamento.</t>
         </is>
       </c>
-      <c r="M16" s="10" t="inlineStr">
+      <c r="M17" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac aproxima-se dos prazos do @regulamento mas aplica-se apenas a cães, gatos e furões. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
-      <c r="N16" s="11" t="inlineStr">
+      <c r="N17" s="11" t="inlineStr">
         <is>
           <t>Necessidade de alteração: (1) reduzir prazo máximo de identificação de nascimentos para 3 meses; (2) criar prazo diferenciado de 30 dias para animais admitidos em estabelecimentos; (3) harmonizar prazos entre todos os diplomas nacionais.</t>
         </is>
       </c>
-      <c r="O16" s="11" t="inlineStr">
+      <c r="O17" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P16" s="11" t="inlineStr"/>
+      <c r="P17" s="11" t="inlineStr"/>
     </row>
-    <row r="17" ht="120" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18" ht="120" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Requisitos de Publicidade em Linha e Colocação no Mercado</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Art.º 17a do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>1. When operators advertise online a dog or a cat with a view to its placing on the Union market, they shall ensure the display of the following warning in the advertisement in clearly visible and bold characters:
-"An animal is not a toy. Getting one is a life-changing decision. It is your duty to ensure its health and welfare and not to abandon it."
-2. When natural or legal persons other than operators advertise online a dog or a cat with a view to its placing on the Union market, they shall ensure the display of a warning on responsible ownership either using the wording referred to in the first sub-paragraph or a different wording with an equivalent meaning to it.
-3. When placing a dog or a cat on the market in the Union, the natural or legal person placing the dog or cat on the market shall:
-a) provide to the acquirer proof of the identification and registration of dog or cat in compliance with Article 17;
-b) provide to the acquirer the following information on the dog or cat (species, sex, date and country of birth, breed);
-c) in case of online advertising, use the system referred to in paragraph 6 to generate a unique verification token.</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>1.	When operators advertise a dog or a cat online with a view to placing it on the Union market, they shall ensure that the following warning is included in the advertisement in clearly visible and bold characters:
+“An animal is not a toy. Getting one is a life-changing decision. It is your duty to ensure the animal’s health and welfare and not to abandon it.”.
+2.	When natural or legal persons other than operators advertise a dog or a cat online with a view to placing it on the Union market, they shall ensure that a warning on responsible ownership is included in the advertisement using either the wording set out in paragraph 1, or a different wording with the same meaning.
+3.	When placing a dog or a cat on the market in the Union, the natural or legal person placing the dog or cat on the market shall provide the acquirer with  :
+(a)	proof of  the identification and registration of the dog or cat in compliance with Article 20;
+(b)	the following information on the dog or cat:
+(i)	its species;
+(ii)	its sex;
+(iii)	its date and country of birth; and
+(iv)	where relevant, its breed.
+Where a natural or legal person advertises a dog or cat online with a view to placing it on the Union market, that person shall use the system referred to in paragraph 5 to generate a unique verification token. That person shall include that token in the advertisement, along with a weblink to the system referred to in paragraph 5.
+The system referred to in paragraph 5 shall enable acquirers to verify the authenticity of the identification, registration and ownership of dogs or cats advertised online.
+4.	Providers of online platforms shall ensure that their online interface is designed and organised in such a way that makes it easier for operators or other natural or legal persons who are placing dogs or cats on the market to comply with their obligations under paragraphs 1 to 3 of this Article, and in line with Article 31 of Regulation (EU) 2022/2065, and shall inform acquirers, in a visible manner, of the possibility to verify the authenticity of the identification, registration and ownership of the dog or cat  on the online verification system referred to in paragraph 5 accessed via a weblink.
+Only the natural or legal person placing dogs or cats on the market shall be responsible for the accuracy of the information provided through the interface of the online platform. Nothing in this paragraph shall be construed as imposing a general monitoring obligation on the provider of the online platform within the meaning of Article 8 of Regulation (EU) 2022/2065.
+5.	The Commission shall ensure that a verification system for performing automated checks of the authenticity of the identification, registration and ownership of dogs or cats advertised online, using the database referred to in Article 23, is publicly available online, free of charge and generates the unique verification token referred to in paragraph 3(2) of this Article. The Commission may entrust the development, maintenance and operation of this system to an independent entity. That independent entity shall be chosen for that task following a public selection process, pursuant to the relevant provisions of Title VII of Regulation (EU, Euratom) 2024/2509 of the European Parliament and of the Council.The system shall ensure the following:
+(a)	reliable verification of the authenticity of the  identification, registration and ownership of the dog or cat using the national databases referred to in Article 23;
+(b)	compliance with data protection in accordance with Regulation (EU) 2018/1725 and Regulation (EU) 2016/679 of the European Parliament and of the Council;
+6.	The Commission shall adopt implementing acts laying down:
+(a)	the information to be provided by natural and legal persons placing dogs or cats on the market as proof of identification and registration of the dogs and cats in accordance with point (a) of paragraph 3;
+(b)	the information to be provided by natural and legal persons advertising dogs or cats to the verification system referred to in paragraph 5 for the purpose of demonstrating the authenticity of the identification, registration and ownership of the dog or cat advertised.
+(c)	the following characteristics of the system referred to in paragraph 5:
+-	the key functions of the system;
+-	the technical, electronic and cryptographic requirements for the system;
+-	the procedural steps to be followed, and the information to be provided,  by the natural or legal person placing the dog or cat on the market, and the steps and information required of the acquirer, in order for the online verification system to work.
+The implementing acts referred to in point (a) shall be adopted by ... [two years after the date of entry into force of this Regulation] and the implementing act referred to in points (b) and (c) shall be adopted by ... [three years from date of entry into force of this Regulation]
+Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 29.
+CHAPTER IV
+COMPETENT AUTHORITIES</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>1. Quando operadores anunciem online um cão ou gato com vista ao seu colocamento no mercado da União, devem assegurar a apresentação do seguinte aviso no anúncio em caracteres claramente visíveis e em negrito:
 "Um animal não é um brinquedo. Ter um é uma decisão que muda a vida. É seu dever assegurar a sua saúde e bem-estar e não o abandonar."
@@ -2271,12 +2402,12 @@
 6. A Comissão garante que um sistema de verificação online que realiza controlos automatizados da autenticidade da identificação, registo e propriedade de cães ou gatos anunciados online, utilizando a base de dados referida no artigo 19.º, está disponível publicamente gratuitamente e gera o token único de verificação referido no parágrafo 3, alínea c).</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Art.º 95.º + Art.º 115.º n.º 3 do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Artigo 95.º - Local de venda dos animais
 1 - Os animais de companhia não podem ser vendidos por entidade transportadora ou através da Internet, designadamente através de quaisquer portais ou plataformas.
@@ -2284,79 +2415,79 @@
 Artigo 115.º n.º 3 - É proibida a publicidade e comercialização de animais perigosos ou que demonstrem comportamento agressivo.</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>Art.º 24.º e Art.º 62.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>A legislação proíbe a venda de animais de companhia sem documentação adequada e restringe a comercialização de animais com comportamentos perigosos. As disposições cobrem identificação obrigatória e informações sobre o animal antes da venda.</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>DL 276/2001, DL 82/2019 - Normas de comercialização</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>A legislação portuguesa estabelece controlos sobre a comercialização de cães e gatos, com requisitos de identificação e documentação sanitária. DL 82/2019 reforça as normas de rastreabilidade através do SIAC.</t>
         </is>
       </c>
-      <c r="K17" s="8" t="inlineStr">
+      <c r="K18" s="8" t="inlineStr">
         <is>
           <t>PARCIAL - Proíbe venda online mas sem sistema de verificação online específico</t>
         </is>
       </c>
-      <c r="L17" s="9" t="inlineStr">
+      <c r="L18" s="9" t="inlineStr">
         <is>
           <t>PARCIAL - Cobre restrições comerciais mas não implementa sistema de token de verificação</t>
         </is>
       </c>
-      <c r="M17" s="10" t="inlineStr">
+      <c r="M18" s="10" t="inlineStr">
         <is>
           <t>SIM - Proibição clara de publicidade e venda online, com requisitos de local licenciado</t>
         </is>
       </c>
-      <c r="N17" s="11" t="inlineStr">
+      <c r="N18" s="11" t="inlineStr">
         <is>
           <t>A legislação portuguesa PROÍBE a publicidade e venda de animais de companhia na Internet (Art. 95.º RGBEAC). Falta apenas a implementação do sistema de verificação online com token único conforme Art. 17a.6 do Regulamento. A proibição é mais restritiva que o Regulamento que permite venda online com verificação.</t>
         </is>
       </c>
-      <c r="O17" s="11" t="inlineStr">
+      <c r="O18" s="11" t="inlineStr">
         <is>
           <t>Sim - Sistema de verificação online com token único</t>
         </is>
       </c>
-      <c r="P17" s="11" t="inlineStr">
+      <c r="P18" s="11" t="inlineStr">
         <is>
           <t>Legislação portuguesa mais restritiva - proíbe venda online; Reg. EU permite com verificação</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="120" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19" ht="120" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Treino de Cuidadores de Animais</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Art.º 18 do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>1. For the purposes of Article 9 the competent authorities shall be responsible for:
-a) ensuring that training courses are available for animal caretakers;
-b) approving the content of the training courses referred to in point (a), taking into account the minimum requirements laid down by the implementing acts referred to in Article 9(3);
-ba) certifying the animal caretakers who successfully completed the training courses referred to in point (a).
-2. The competent authorities may delegate the task referred to in point (ba).
-3. A European Union Reference Centre for Animal Welfare designated in accordance with Article 95 of Regulation (EU) 2017/625 may develop models of training materials and recommendations for the providers of training courses referred to in paragraph 1.</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>1.	For the purposes of Article 12, the competent authorities shall be responsible for:
+(a)	ensuring that training courses are available for animal carers;
+(b)	approving the content of the training courses referred to in point (a), in accordance with the minimum requirements laid down by the implementing acts referred to in Article 12(4);
+(c)	certifying animal carers who have successfully completed the training courses referred to in point (a).
+The competent authorities may delegate the task referred to in point (c) to providers of training courses.
+2.	A European Union Reference Centre for Animal Welfare designated in accordance with Article 95 of Regulation (EU) 2017/625 may develop models of training materials and recommendations for the competent authorities or other providers of training courses.</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>1. Para efeitos do artigo 9.º, as autoridades competentes são responsáveis por:
 a) Assegurar que existem cursos de formação disponíveis para cuidadores de animais;
@@ -2366,12 +2497,12 @@
 3. O Centro de Referência da União Europeia para o Bem-Estar Animal designado em conformidade com o artigo 95.º do Regulamento (UE) 2017/625 pode desenvolver modelos de materiais de formação e recomendações para os fornecedores dos cursos de formação referidos no parágrafo 1.</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Arts. 118.º, 119.º, 120.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Artigo 118.º - Reserva de atividade de treinadores de cães
 O treino de cães para qualquer fim só pode ser ministrado por treinador possuidor do respetivo título profissional.
@@ -2383,12 +2514,12 @@
 2 - Provas incidem sobre comportamento animal, metodologia de treino, aprendizagem e extinção de comportamentos.</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>Arts. 51.º, 52.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>Artigo 51.º - Exercício de profissões relacionadas com cães
 O exercício de certas profissões (adestrador, criador) requer documentação específica e conformidade com normas de bem-estar animal.
@@ -2396,67 +2527,75 @@
 Requerimentos de certificação e qualificação profissional para operadores.</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>DL 82/2019 - Normas de profissionalismo</t>
         </is>
       </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>Legislação portuguesa estabelece normas de profissionalismo e qualificação para operadores em bem-estar animal, com requisitos de formação e certificação conforme disposições de Decreto-Lei específico.</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="K19" s="8" t="inlineStr">
         <is>
           <t>SIM - Cobertura COMPLETA (certificação profissional, provas teóricas e práticas, métodos positivos)</t>
         </is>
       </c>
-      <c r="L18" s="9" t="inlineStr">
+      <c r="L19" s="9" t="inlineStr">
         <is>
           <t>SIM - Cobertura COMPLETA (profissionalismo, qualificações obrigatórias)</t>
         </is>
       </c>
-      <c r="M18" s="10" t="inlineStr">
+      <c r="M19" s="10" t="inlineStr">
         <is>
           <t>SIM - Cobertura COMPLETA (Arts. 118-120 implementam sistema profissional com certificação)</t>
         </is>
       </c>
-      <c r="N18" s="11" t="inlineStr">
+      <c r="N19" s="11" t="inlineStr">
         <is>
           <t>A legislação portuguesa implementa COMPLETAMENTE os requisitos do Artigo 18. O RGBEAC (Arts. 118-120) estabelece um sistema robusto de certificação profissional para treinadores de cães com: título profissional obrigatório, requisitos de habilitação, provas teóricas e práticas, métodos baseados em reforço positivo, verificação de antecedentes criminais. Sistema já em vigor conforme Decreto-Lei.</t>
         </is>
       </c>
-      <c r="O18" s="11" t="inlineStr">
+      <c r="O19" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P18" s="11" t="inlineStr">
+      <c r="P19" s="11" t="inlineStr">
         <is>
           <t>Sistema profissional português já implementado - cobertura completa e adequada</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="120" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20" ht="120" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Base de Dados de Cães e Gatos</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Art.º 19 do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>1. Member States shall be responsible for establishing and maintaining databases for the registration of identified dogs and cats, in accordance with Article 17(1) and (2) and Article 21(4) and the second subparagraph of Article 21(4a).
-1a. For that purpose, the Member States may use databases maintained by another Member State, based on appropriate arrangements between those Member States.
-2. Member States shall ensure that their databases as referred to in paragraph 1 comply with the requirements laid down by the implementing act referred to in point (b) of paragraph 3 to ensure their interoperability so that the identification of a dog or a cat can be authenticated and traced across the Union.
-2a. The Commission shall establish and maintain an index database containing the minimum set of fields defined under article 19(3)(b). The Commission may entrust the development, maintenance and operation of this index database to an independent entity, following a public selection process.</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>1.	Member States shall be responsible for establishing and maintaining databases for the registration of identified dogs and cats in accordance with Article 20(1) and (2) and Article 26(3) and Article 26(4), second subparagraph.
+2.	For that purpose, the Member States may use databases maintained by another Member State, on the basis of appropriate arrangements between those Member States.
+3.	 Member States shall ensure that their databases, as referred to in paragraph 1, comply with the requirements laid down by the implementing act referred to in paragraph 4, second subparagraph, point (b), to ensure their interoperability.
+4.	The Commission shall establish and maintain an index database containing the minimum set of fields laid down in the implementing acts referred to in subparagraph 2, point (b). The Commission may entrust the development, maintenance and operation of that index database to an independent entity, following a public selection process pursuant to the relevant provisions of Title VII of the Regulation (EU, Euratom) 2024/2509.
+The Commission shall adopt implementing acts laying down detailed arrangements concerning:
+(a)	the minimum content of the databases referred to in paragraph 1;
+(b)	the interoperability between Member States’ databases and the index database, including the minimum set of fields to be transmitted to the index database and the intervals of the transmission;
+(c)	the functionality for providing proof of the identification and registration of a dog or a cat, as referred to in Article 21 (3) point (a).
+(d)	the registry where Member States will declare their databases, and the necessary parameters for connecting those databases with one another in accordance with the provisions established pursuant to point (b);
+(e)	the interconnection between the Member States’ databases referred to in paragraph 1, the pet travellers' database referred to in Article 26, paragraph 4, and the Information Management System for Official Controls (IMSOC), where relevant.
+The Commission shall adopt the implementing acts referred to in the second subparagraph, points (a) and (c) by ... [date two years after the date of entry into force of this Regulation]. It shall adopt the implementing acts referred to in the second subparagraph, points (b), (d) and (e) by ...[three years from the date of entry into force of this Regulation].
+Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 29.</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>1. Os Estados-Membros são responsáveis pela criação e manutenção de bases de dados para o registo de cães e gatos identificados, em conformidade com os artigos 17.º (parágrafos 1 e 2) e 21.º (parágrafo 4 e segundo parágrafo do parágrafo 4a).
 1a. Para este efeito, os Estados-Membros podem utilizar bases de dados mantidas por outro Estado-Membro, com base em acordos apropriados entre esses Estados-Membros.
@@ -2464,12 +2603,12 @@
 2a. A Comissão estabelece e mantém uma base de dados de índice contendo o conjunto mínimo de campos definido no parágrafo 3, alínea b). A Comissão pode confiar o desenvolvimento, manutenção e funcionamento dessa base de dados de índice a uma entidade independente, após um processo de seleção pública.</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Art.º 20.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Artigo 20.º - Sistema de Informação de Animais de Companhia (SIAC)
 1 - O SIAC reúne a informação relativa à rastreabilidade dos dispositivos de identificação, à identificação dos animais de companhia, à sua titularidade ou detenção e à informação relacionada com a defesa da saúde pública, saúde animal e bem-estar animal.
@@ -2478,12 +2617,12 @@
 4 - As normas e procedimentos relativos ao funcionamento do SIAC constam de um Manual de Procedimentos SIAC, aprovado pelo diretor-geral de alimentação e veterinária.</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>Arts. 53.º, 55.º, 56.º, 57.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>Artigo 53.º - Identificação e registo na base de dados
 1 - Todos os cães devem ser identificados e registados entre os três e seis meses de idade.
@@ -2495,161 +2634,162 @@
 Artigo 56.º - Classificação dos animais (Cão, Cão Potencialmente Perigoso, Cão Perigoso, Gato)</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>DL n.º 82/2019, Art.º 2.º (Estabelece SIAC)</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>DL 82/2019 estabelece o SIAC com extensas disposições cobrindo: criação da base de dados, procedimentos de registo e controlos de acesso, gestão por DGAV, identificação eletrónica via transponder, segurança de dados e autorização de acesso, integração de registos de identificação de animais, gestão da distribuição de dispositivos de identificação, procedimentos de registo e atualização. O sistema é totalmente operacional desde 2019.</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="K20" s="8" t="inlineStr">
         <is>
           <t>NÃO - SIAC em funcionamento desde 2019 cumpre todos os requisitos</t>
         </is>
       </c>
-      <c r="L19" s="9" t="inlineStr">
+      <c r="L20" s="9" t="inlineStr">
         <is>
           <t>NÃO - Código do Animal estabelece estrutura completa com classificações</t>
         </is>
       </c>
-      <c r="M19" s="10" t="inlineStr">
+      <c r="M20" s="10" t="inlineStr">
         <is>
           <t>NÃO - RGBEAC (Art. 20.º) reafirma e fortalece o sistema SIAC</t>
         </is>
       </c>
-      <c r="N19" s="11" t="inlineStr">
+      <c r="N20" s="11" t="inlineStr">
         <is>
           <t>A legislação portuguesa CUMPRE COMPLETAMENTE os requisitos do Artigo 19. O SIAC (Sistema de Informação de Animais de Companhia) já está operacional desde 2019, sob responsabilidade de DGAV, com: identificação eletrónica via microchip obrigatória, registo nacional centralizado, rastreabilidade garantida, classificação de animais (normal/perigoso/potencialmente perigoso), integração de dados de saúde e bem-estar, conformidade com proteção de dados (Comissão Nacional de Proteção de Dados).</t>
         </is>
       </c>
-      <c r="O19" s="11" t="inlineStr">
+      <c r="O20" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P19" s="11" t="inlineStr">
+      <c r="P20" s="11" t="inlineStr">
         <is>
           <t>SIAC totalmente operacional e conforme - Interoperabilidade EU pendente de implementação</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="120" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21" ht="120" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Recolha de Dados sobre Bem-Estar Animal e Relatório</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Art.º 20 do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>1. The competent authorities shall collect, analyse and publish the data set out in Annex III.
-2. The competent authorities shall draw up and transmit to the Commission a report in electronic form, on the data set out in Annex III, by 31 August every 3 years starting from [6 years from the date of entry into force of this Regulation], summarising the data gathered for the previous 3 years.
-3. The Commission may, by means of implementing acts, establish a harmonised methodology for collecting the data set out in Annex III and establish a template for the report referred to in paragraph 2 of this Article. Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 24.</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>1.	The competent authorities shall collect, analyse and publish the data on animal welfare set out in Annex III:
+2.	The competent authorities shall draw up and transmit to the Commission a report in electronic form, on the data on animal welfare, set out in Annex III, by 31 August at three-yearly intervals. The first such report shall be drawn up and transmitted to the Commission by ... [date 6 years from the date of entry into force of this Regulation]. Each report shall contain a summary of the data gathered during the previous three years.
+3.	The Commission may adopt implementing acts, establishing a harmonised methodology for collecting the data on animal welfare set out in Annex III and establishing a template for the report referred to in paragraph 2 of this Article. Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 29.</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Disponível no documento Regulamento - Primeira Versão portuguesa.docx</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Art.º 46.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Artigo 46.º - Relatório Nacional Anual
 1 - Os centros de bem-estar animal e alojamentos remetem à DGAV no primeiro mês de cada ano civil, os relatórios de gestão do ano anterior, com números de animais recolhidos, restituídos, eutanasiados, cedidos, adotados, devolvidos após adoção, vacinados, esterilizados e intervencionados em programas CED.
 2 – A DGVA consolida a informação a nível nacional sobre bem-estar animal em cada ano, incluindo: acompanhamento da política internacional, prestação de apoios públicos, atividade do SIAC, resultados de planos de controlo, processos contraordenacionais, coimas aplicadas, atividade de centros de bem-estar, programas de interesse nacional, ações informativas e educativas, para efeitos de elaboração do Relatório Anual sobre a situação do Bem-Estar Animal.</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>Arts. 141.º-145.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>Código do Animal estabelece estrutura de monitorização e relatórios sobre bem-estar animal, incluindo: recolha de dados de infrações, aplicação de sanções, atividades de centros de recolha, estatísticas de animais processados. Sistema de contraordenações com documentação e coimas registadas.</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>Decreto-Regulamentar n.º 3/2021 + DL 82/2019</t>
         </is>
       </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>Decreto-Regulamentar 3/2021 (Art. 3.º) requer Relatório Anual sobre situação do Bem-Estar Animal. DL 82/2019 estabelece procedimentos de recolha de dados, monitorização, registo de atividades médico-veterinárias e compilação de informação de bem-estar animal para fins de relatório anual e transmissão a autoridades europeias.</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="K21" s="8" t="inlineStr">
         <is>
           <t>SIM - Cobertura COMPLETA (relatórios anuais, recolha de dados, consolidação nacional)</t>
         </is>
       </c>
-      <c r="L20" s="9" t="inlineStr">
+      <c r="L21" s="9" t="inlineStr">
         <is>
           <t>SIM - Cobertura COMPLETA (monitorização, infrações, sanções, estatísticas)</t>
         </is>
       </c>
-      <c r="M20" s="10" t="inlineStr">
+      <c r="M21" s="10" t="inlineStr">
         <is>
           <t>SIM - Cobertura COMPLETA (Art. 46.º estabelece sistema de relatórios nacionais)</t>
         </is>
       </c>
-      <c r="N20" s="11" t="inlineStr">
+      <c r="N21" s="11" t="inlineStr">
         <is>
           <t>A legislação portuguesa implementa COMPLETAMENTE o Artigo 20. Sistema já estabelecido com: recolha anual de dados de centros de bem-estar animal, consolidação de informação de bem-estar a nível nacional, inclusão de estatísticas de SIAC, registos de contraordenações e sanções, relatórios sobre atividades de proteção animal, conformidade com requisitos de Decreto-Regulamentar 3/2021. Único ajuste necessário: alinhamento da periodicidade de relatórios (atualmente anual; Regulamento requer trienal) e inclusão dos dados específicos de Annex III da EU (quando publicado).</t>
         </is>
       </c>
-      <c r="O20" s="11" t="inlineStr">
+      <c r="O21" s="11" t="inlineStr">
         <is>
           <t>Sim - Ajuste de periodicidade e conformidade com Annex III EU</t>
         </is>
       </c>
-      <c r="P20" s="11" t="inlineStr">
+      <c r="P21" s="11" t="inlineStr">
         <is>
           <t>Sistema de relatórios já operacional - apenas alinhamento com padrões EU necessário</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="120" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22" ht="120" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Proteção de Dados</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Art.º 20a do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>The competent authorities of the Member States shall be controllers within the meaning of Regulation (EU) 2016/679 in relation to the processing of personal data collected under Article 7, Article 7a of this Regulation as well as under Article 19(1) of this Regulation when used for the purposes of official control.
-The Commission shall be a controller within the meaning of Regulation (EU) 2018/1725 in relation to the processing of personal data collected under Article 17a (6), Article 19 (2a) and the third subparagraph of Article 21(4a) of this Regulation, as well as under Article 19(1) of this Regulation when used for the purposes of compliance with Article 108 of Regulation (EU) 2017/625 and of reporting obligations under this Regulation.
-It shall be prohibited for any person having access to the personal data referred to in the first and second sub-paragraphs to divulge any personal data, the knowledge of which was acquired in the exercise of their duties or otherwise incidentally to such exercise.
-Member States and the Commission shall take all appropriate measures to address infringements of that prohibition.
-The personal data collected under the first and second sub-paragraphs shall not be used for other purposes than:
-a) official controls by Member States competent authorities of the compliance with the welfare and traceability requirements under this regulation and compliance with Regulation (EU) 2016/429, including and detection of fraudulent practices, and
-b) compliance by the Commission of its obligations under Article 108 of Regulation (EU) 2017/625 and with the Commission's reporting obligations under this Regulation.
-The personal data referred to in paragraph 1 of this Article shall be retained for the following periods:
-a) in the case of Article 7 and Article 7a, 10 years after the date of cessation of the activity of the establishment;
-b) in the case of Article 17a(6), 18 months after the generation of the token referred to in Article 17a(3)(c).
-c) in case of Article 19(1), and Article 19(2a), 25 years after the first registration of the dog or cat in the database referred to in that Article or 5 years after the recording of the death of the dog or cat in that database;
-d) in case of the third subparagraph of Article 21(4a), 5 years after the date of pre-notification.</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>1.	The competent authorities of the Member States shall be controllers within the meaning of Regulation (EU) 2016/679 in relation to the processing of personal data collected under Articles 9 and 10 of this Regulation, as well as under Article 23(1) of this Regulation when used for the purposes of official control.
+The Commission shall be a controller within the meaning of Regulation (EU) 2018/1725 in relation to the processing of personal data collected under Article 21(5), Article 23(4), and Article 26(4), third subparagraph, , as well as under Article 23(1) of this Regulation when that data is used for the purposes of compliance with Article 108 of Regulation (EU) 2017/625 and the reporting obligations under this Regulation.
+It shall be prohibited for any person with access to the personal data referred to in the first and second subparagraphs to divulge any personal data the knowledge of which was acquired in the exercise of his or her duties or otherwise incidentally to such exercise. Member States and the Commission shall take all appropriate measures to enforce that prohibition.
+The personal data collected under the first and second subparagraphs shall not be used for purposes other than:
+(a)	official controls by Member States’ competent authorities of compliance with the welfare and traceability requirements of this Regulation and of compliance with Regulation (EU) 2016/429, including the detection of fraudulent practices; and
+(b)	compliance by the Commission with its obligations under Article 108 of Regulation (EU) 2017/625 and with the Commission’s reporting obligations under this Regulation.
+2.	The personal data referred to in paragraph 1 of this Article shall be retained for the following periods:
+(a)	in the case of Articles 9 and 10, 10 years after the date of cessation of the activity of the establishment;
+(b)	in the case of Article 21(5), 18 months after the generation of the token referred to in Article 21(3), second subparagraph;
+(c)	in the case of Articles 23(1) and 23(4), 25 years after the first registration of the dog or cat in the database referred to in that Article or five years after the recording of the death of the dog or cat in that database;
+(d)	in the case of Article 26(4), third subparagraph, 5 years after the date of pre-notification.
+CHAPTER V
+ENTRY OF DOGS AND CATS INTO THE UNION</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>As autoridades competentes dos Estados-Membros devem ser controladoras no sentido do Regulamento (UE) 2016/679 em relação ao tratamento de dados pessoais recolhidos de acordo com o Artigo 7, Artigo 7a do presente Regulamento, bem como no âmbito do Artigo 19(1) do presente Regulamento quando utilizados para efeitos de inspeção oficial.
 A Comissão deve ser controladora no sentido do Regulamento (UE) 2018/1725 em relação ao tratamento de dados pessoais recolhidos de acordo com o Artigo 17a (6), Artigo 19 (2a) e o terceiro parágrafo do Artigo 21(4a) do presente Regulamento, bem como no âmbito do Artigo 19(1) do presente Regulamento quando utilizados para efeitos de conformidade com o Artigo 108 do Regulamento (UE) 2017/625 e de obrigações de comunicação de informações previstas no presente Regulamento.
@@ -2658,12 +2798,12 @@
 [... redução para brevidade - ver regulamento completo para texto integral]</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Art.º 20.º, nn. 3, 6, 8 do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Artigo 20.º, n.º 8 - SIAC e Proteção de Dados:
 Ao tratamento, segurança, conservação, acesso e proteção dos dados pessoais constantes do SIAC é diretamente aplicável o disposto na legislação e regulamentação relativa à proteção de dados pessoais, nomeadamente o Regulamento (UE) 2016/679 do Parlamento Europeu e do Conselho, de 27 de abril de 2016, relativo à proteção das pessoas singulares no que diz respeito ao tratamento de dados pessoais e à livre circulação desses dados.
@@ -2673,12 +2813,12 @@
 A DGAV, pode atribuir a gestão do SIAC a outras entidades, mediante a celebração de protocolo e sob sua supervisão, observado o regime de subcontratação de tratamento de dados pessoais.</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>Art.º 55.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>Artigo 55.º - Base de Dados
 1 - Toda a informação resultante do registo do animal é coligida numa aplicação informática nacional.
@@ -2686,74 +2826,85 @@
 3 - Só têm acesso à base de dados as entidades que se encontrem autorizadas, para o efeito, pela DGAV.</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>DL n.º 82/2019, Art.º 9.º</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Artigo 9.º - Registo no Sistema de Informação de Animais de Companhia
 1 - Os animais de companhia abrangidos pela obrigação de identificação devem ser registados pelo médico veterinário no SIAC, imediatamente após a sua marcação com o transponder, em nome do respetivo titular.</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr">
+      <c r="K22" s="8" t="inlineStr">
         <is>
           <t>NÃO - Legislação portuguesa cobre completamente com incorporação de GDPR</t>
         </is>
       </c>
-      <c r="L21" s="9" t="inlineStr">
+      <c r="L22" s="9" t="inlineStr">
         <is>
           <t>NÃO - Cobertura expressa em Art. 55.º</t>
         </is>
       </c>
-      <c r="M21" s="10" t="inlineStr">
+      <c r="M22" s="10" t="inlineStr">
         <is>
           <t>NÃO - Implementação completa em Arts. 20.º</t>
         </is>
       </c>
-      <c r="N21" s="11" t="inlineStr">
+      <c r="N22" s="11" t="inlineStr">
         <is>
           <t>A legislação portuguesa implementa completamente os requisitos de proteção de dados do Artigo 20a. O SIAC é configurado como sistema compliant com GDPR (EU 2016/679) e com regulamentações de proteção de dados. Não há necessidade de alterações legislativas.</t>
         </is>
       </c>
-      <c r="O21" s="11" t="inlineStr">
+      <c r="O22" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P21" s="11" t="inlineStr">
+      <c r="P22" s="11" t="inlineStr">
         <is>
           <t>Correspondências confirmadas por agente de pesquisa em 2026-03-02</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="120" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23" ht="120" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Entrada de Cães e Gatos na União</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 21.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>1. Dogs and cats may only be entered into the Union for placing on the Union market provided that the following conditions are met:
-a) they have been breed and kept in compliance with any of the following:
-   i) Chapter II of this Regulation;
-   ii) conditions recognised by the Union in accordance with Article 129 of Regulation (EU) 2017/625 to be equivalent to those set out by Chapter II of this Regulation; or
-   iii) where applicable, requirements contained in a specific agreement between the Union and the exporting country.
-b) they come from a third country or territory and an establishment listed in accordance with Articles 126 and 127 of Regulation (EU) 2017/625.
-2. The official certificate referred to in Article 126(2)(c) of Regulation (EU) 2017/625 accompanying dogs and cats entering into the Union from third countries and territories to be placed on the Union market, shall contain an attestation certifying compliance with paragraph 1 of this Article.
-3. Dogs and cats entering into the Union to be placed on the Union market shall be identified before their entry by a veterinarian by means of an injectable transponder containing a readable microchip compliant with Annex II.
-4. The operator responsible for the import of dogs or cats entering into the Union shall ensure the registration of the dogs or cats by a veterinarian into a national database referred to in Article 19(1), within 5 working days after their entry into the Union.
-[... ver regulamento completo para restantes parágrafos 4a e 5 ...]</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 26.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>1.	Dogs and cats may be brought into the Union for the purpose of being placed on the Union market  only if the following conditions are met:
+(a)	they have been bred and kept in compliance with any of the following requirements:
+(i)	the requirements contained in Chapter II of this Regulation;
+(ii)	requirements recognised by the Union, in accordance with Article 129 of Regulation (EU) 2017/625, as being equivalent to those set out by Chapter II of this Regulation; or
+(iii)	where applicable, requirements contained in a specific agreement between the Union and the exporting country.
+b)	 they come from a third country or territory and from an establishment listed in accordance with Articles 126 and 127 of Regulation (EU) 2017/625.
+2.	The official certificate referred to in Article 126(2), point (c), of Regulation (EU) 2017/625 accompanying dogs and cats brought into the Union from third countries and territories for the purpose of being placed on the Union market, shall contain an attestation certifying compliance with  paragraph 1 of this Article.
+3.	Dogs and cats brought into the Union for the purpose of being placed on the Union market shall be identified before their entry into the Union by a veterinarian by means of an injectable transponder containing a readable microchip that complies with the requirements set out in  Annex II.
+The operator responsible for the import of the dogs or cats into the Union shall ensure that they are registered in a national database referred to in Article 23(1), by a veterinarian, within five working days after they were brought into the Union. Member States may allow registration by persons other than veterinarians, provided that they have measures in place to ensure the accuracy of information that those persons enter in the database.
+4.	The non-commercial movement of a dog or cat from a third country or territory to the Union shall be prenotified by its owner to an online Union pet travellers’ database at least five working days before the dog or cat crosses the Union border, except in the following cases:
+(a)	where the dog or cat is brought into the Union directly from third countries or from territories fulfilling the conditions set out in Article 17(1), point (a), of Commission Delegated Regulation (EU) …/..., and
+(b)	where the dog or cat is registered in a Member State database referred to in Article 23(1) of this Regulation.
+Where the dog or cat stays more than six months in the Union, the owner shall ensure that it is registered in the database of the Member State of residence referred to in Article 23(1), by a veterinarian, within five working days after the expiry of the sixth month since it entered the Union. Member States may allow registration by persons other than veterinarians, provided that they have measures in place to ensure the accuracy of information that those persons enter in the database.
+The Commission shall establish and maintain the Union pet travellers’ database referred to in the first subparagraph. The Commission may entrust the development, maintenance and operation of that database to an independent entity, following a public selection process pursuant to the relevant provisions of Title VII of the Regulation (EU, Euratom) 2024/2509. Access to that database shall be restricted to Member States’ competent authorities and to the Commission.
+The Commission shall ensure that the database triggers iRASFF notifications for pre-notified movements that present a risk of fraud. The Member State receiving the notification shall take appropriate measures to follow it up in accordance with Article 105(2) of Regulation (EU) 2017/625.
+The Commission shall by ... [ 8 years after the date of entry into force of this Regulation] adopt implementing acts laying down detailed arrangements for the following:
+(i)	the information to be pre-notified by owners in accordance with paragraph (4) of this Article in the Union pet travellers’ database, taking into account the personal data protection requirements of Regulation (EU) 2018/1725 and Regulation (EU) 2016/679;
+(ii)	the procedure by which the risk of fraud is to be established, which is to take into account the activities carried out by the AAC network
+Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 29.
+CHAPTER VI
+PROCEDURAL PROVISIONS</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>1. Os cães e os gatos podem ser introduzidos na União apenas para colocação no mercado da União se estiverem satisfeitas as seguintes condições:
 a) Tenham sido criados e mantidos em conformidade com qualquer das seguintes situações:
@@ -2770,12 +2921,12 @@
 Se o cão ou gato permanecer mais de seis meses na União, o proprietário deve assegurar o seu registo por um médico veterinário na base de dados do Estado-Membro de residência referida no artigo 19.º, parágrafo 1, no prazo de 5 dias úteis após o termo do sexto mês. Os Estados-Membros podem permitir o registo por outras pessoas que não médicos veterinários, desde que tenham medidas em vigor para assegurar a exatidão das informações inseridas na base de dados.</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Art.º 114.º e Art.º 96.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Artigo 114.º - Entrada no Território Nacional
 1 - A entrada no território nacional, por compra, cedência ou troca direta, de cães classificados como potencialmente perigosos pode ser condicionada.
@@ -2785,12 +2936,12 @@
 A importação de animais que constem da lista nacional de animais de companhia provenientes de outros Estados é admitida desde que sejam cumpridas as regras sanitárias e de bem-estar animal portuguesas e comunitárias.</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>Art.º 62.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>Artigo 62.º - Entrada de Animais de Companhia Suscetíveis à Raiva em Território Nacional
 1 - A entrada em território nacional de animais de companhia suscetíveis à raiva destinados ao comércio, provenientes de outros Estados-membros ou de países terceiros, depende do cumprimento das condições fixadas no Decreto-Lei n.º 79/2001, de 20 de junho, alterado pelo Decreto-Lei n.º 260/2012, de 12 de dezembro, e noutras normas de polícia sanitária que regem o comércio e as importações de animais vivos na comunidade.
@@ -2798,79 +2949,79 @@
 3 - A entrada em território nacional de furões destinados ao comércio ou sem carácter comercial, para além do cumprimento do disposto nos números anteriores, depende de autorização prévia do ICNF, I.P.</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>DL n.º 82/2019, Art.º 2.º</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>Artigo 2.º - Âmbito de Aplicação
 O presente decreto-lei aplica-se à identificação de animais de companhia das espécies referidas no anexo I do Regulamento (UE) n.º 576/2013, do Parlamento Europeu e do Conselho, de 12 de junho de 2013, e no anexo I do Regulamento (UE) n.º 2016/429, do Parlamento Europeu e do Conselho, de 9 de março de 2016, nascidos ou presentes no território nacional.</t>
         </is>
       </c>
-      <c r="K22" s="8" t="inlineStr">
+      <c r="K23" s="8" t="inlineStr">
         <is>
           <t>PARCIAL - Cobre entrada/importação mas sem database online de viajantes pré-notificação</t>
         </is>
       </c>
-      <c r="L22" s="9" t="inlineStr">
+      <c r="L23" s="9" t="inlineStr">
         <is>
           <t>SIM - Implementa controlos sanitários e requisitos de identificação</t>
         </is>
       </c>
-      <c r="M22" s="10" t="inlineStr">
+      <c r="M23" s="10" t="inlineStr">
         <is>
           <t>PARCIAL - Cobre entrada no território nacional com condições, não cobre movimento não-comercial pré-notificação</t>
         </is>
       </c>
-      <c r="N22" s="11" t="inlineStr">
+      <c r="N23" s="11" t="inlineStr">
         <is>
           <t>A legislação portuguesa implementa os requisitos essenciais de entrada e identificação pré-entrada, referenciando os Regulamentos EU 576/2013 e 2016/429. Faltam: (1) Sistema de base de dados online de viajantes com pré-notificação obrigatória para movimento não-comercial; (2) Sistema iRASFF integrado para notificações de risco de fraude.</t>
         </is>
       </c>
-      <c r="O22" s="11" t="inlineStr">
+      <c r="O23" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P22" s="11" t="inlineStr">
+      <c r="P23" s="11" t="inlineStr">
         <is>
           <t>Parcialmente coberto. Complementação necessária para movimento não-comercial e sistema iRASFF.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="120" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24" ht="120" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Alteração dos Anexos</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 22.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>1. The Commission is empowered to adopt delegated acts in accordance with Article 23 amending the Annexes to this Regulation to take into account of scientific and technical progress, including, when relevant, scientific opinions of the European Food Safety Authority, as regards:
-a) a suitable number of animal caretakers in breeding and selling establishments;
-b) watering and feeding requirements and weaning process;
-c) temperature ranges;
-d) lighting requirements;
-e) ammonia and carbon monoxide levels;
-f) kennel and cattery design;
-g) group housing;
-h) space allowances for different categories of dogs and cats;
-i) frequency of pregnancies;
-j) minimum and maximum age of bitches and queens for breeding;
-k) socialisation, enrichment and other measures for meeting behavioural needs of dogs and cats;
-l) requirements for transponders used to individually identify dogs and cats;
-m) data to be collected for policy monitoring and evaluation.
-2. Any additions of requirements in the Annexes shall be based on updated scientific or technical evidence, in particular regarding the specific conditions needed to ensure the welfare of the dogs and cats covered by the scope of this Regulation. Where relevant, those delegated acts shall take into account social, economic and environmental impacts and provide for sufficient transition periods to allow for operators concerned to adapt to the new requirements.</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 27.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>The Commission is empowered to adopt delegated acts in accordance with Article 28 to amend the Annexes to this Regulation to take account of scientific and technical progress, including, where relevant, the scientific opinions of EFSA, as regards:
+(a)	a suitable number of animal carers in breeding and selling establishments;
+(b)	watering and feeding requirements and weaning process;
+(c)	temperature ranges;
+(d)	lighting requirements;
+(e)	ammonia and carbon monoxide levels;
+(f)	kennel and cattery designs;
+(g)	group housing;
+(h)	space allowances for various categories of dogs and cats;
+(i)	the frequency of pregnancies;
+(j)	the minimum and maximum age of bitches and queens for  breeding;
+(k)	socialisation, the provision of enrichments and other measures for meeting the behavioural needs of dogs and cats;
+(l)	the requirements for the transponders used to identify dogs and cats individually;
+(m)	the data to be collected for policy monitoring and evaluation.
+Any additions of requirements in the Annexes shall be based on updated scientific or technical evidence, in particular such evidence regarding the specific conditions needed to ensure the welfare of the dogs and cats covered by the scope of this Regulation. Where relevant, those delegated acts shall take into account social, economic and environmental impacts and shall provide for sufficient transition periods to allow the operators concerned to adapt to the new requirements.</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>1. A Comissão fica habilitada a adotar atos delegados em conformidade com o artigo 23.º que alterem os anexos do presente Regulamento para ter em conta o progresso científico e técnico, incluindo, quando relevante, pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, nos seguintes aspetos:
 a) Um número adequado de cuidadores de animais em estabelecimentos de criação e venda;
@@ -2889,12 +3040,12 @@
 2. Qualquer complemento de requisitos nos Anexos deve ser baseado em evidência científica ou técnica atualizada, em particular no que diz respeito às condições específicas necessárias para assegurar o bem-estar dos cães e gatos abrangidos pelo âmbito do presente Regulamento. Quando relevante, esses atos delegados devem levar em conta impactos sociais, económicos e ambientais e prever períodos de transição suficientes para permitir aos operadores envolvidos a adaptação aos novos requisitos.</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Arts. 3-8 e ANEXO do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Artigos 3.º a 8.º do Decreto-Lei que aprova o RGBEAC estabelecem mecanismo legislativo para alteração de diplomas anteriores. O RGBEAC contém um ANEXO estruturado com:
 - TÍTULO I: Disposições gerais
@@ -2905,12 +3056,12 @@
 NOTA: O mecanismo atual é legislativo padrão (alteração de Decreto-Lei por novo Decreto-Lei). NÃO existe autoridade delegada expressa para alteração por atos de execução, conforme previsto no Art. 22-24 do Regulamento EU 2023/0447.</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>Art.º 23.º e ANEXO II do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>Artigo 23.º - Condições Particulares para a Manutenção de Cães e Gatos
 1 - O alojamento de cães e gatos deve obedecer às dimensões mínimas indicadas no anexo II ao presente diploma.
@@ -2924,70 +3075,70 @@
 Corresponde materialmente aos requisitos de espaço, temperatura e frequência referidos no Art. 22 do Regulamento.</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>DL n.º 82/2019 - Referências a Anexos de Regulamentos EU</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>DL n.º 82/2019 incorpora por referência os Anexos I dos Regulamentos EU n.º 576/2013 e n.º 2016/429, estabelecendo que os requisitos de identificação de animais de companhia aplicáveis em Portugal são os das espécies referidas nesses anexos.
 NOTA: DL 82/2019 não implementa mecanismo de delegação de autoridade para alteração de anexos como previsto no Art. 22-24 do Regulamento EU 2023/0447.</t>
         </is>
       </c>
-      <c r="K23" s="8" t="inlineStr">
+      <c r="K24" s="8" t="inlineStr">
         <is>
           <t>PARCIAL - Anexos existem; falta delegação de autoridade para alteração dinâmica</t>
         </is>
       </c>
-      <c r="L23" s="9" t="inlineStr">
+      <c r="L24" s="9" t="inlineStr">
         <is>
           <t>PARCIAL - Estrutura de anexos com parâmetros técnicos; falta delegação</t>
         </is>
       </c>
-      <c r="M23" s="10" t="inlineStr">
+      <c r="M24" s="10" t="inlineStr">
         <is>
           <t>PARCIAL - ANEXO estruturado; falta mecanismo de atos delegados/execução</t>
         </is>
       </c>
-      <c r="N23" s="11" t="inlineStr">
+      <c r="N24" s="11" t="inlineStr">
         <is>
           <t>A legislação portuguesa possui estrutura de anexos contendo parâmetros técnicos equivalentes aos do Regulamento. Falta implementar: Mecanismo de delegação de autoridade à Comissão Europeia para adoção de atos delegados/execução, conforme Arts. 22-24 do Regulamento 2023/0447. Atualmente, qualquer alteração de anexos requer procedimento legislativo nacional (novo Decreto-Lei), não havendo procedimento expedito de atos delegados.</t>
         </is>
       </c>
-      <c r="O23" s="11" t="inlineStr">
+      <c r="O24" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P23" s="11" t="inlineStr">
+      <c r="P24" s="11" t="inlineStr">
         <is>
           <t>Estrutura de anexos presente mas sem mecanismo de delegação de autoridade para atos delegados/execução conforme Reg. EU.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="120" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25" ht="120" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Exercício da Delegação</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 23.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>1 — The power to adopt delegated acts is conferred on the Commission subject to the conditions laid down in this Article.
-2 — The power to adopt delegated acts referred to in Article 6(2b), Article 6a(3), Article 10(2) and Article 22 shall be conferred on the Commission for an indeterminate period of time from [the date of entry into force of this Regulation].
-3 — The delegation of power referred to in Article 6(2b), Article 6a(3), Article 10(2) and Article 22 may be revoked at any time by the European Parliament or by the Council. A decision to revoke shall put an end to the delegation of the power specified in that decision. It shall take effect the day following the publication of the decision in the Official Journal of the European Union or at a later date specified therein. It shall not affect the validity of any delegated acts already in force.
-4 — Before adopting a delegated act, the Commission shall consult experts designated by each Member State in accordance with the principles laid down in the Interinstitutional Agreement of 13 April 2016 on Better Law-Making.
-5 — As soon as it adopts a delegated act, the Commission shall notify it simultaneously to the European Parliament and to the Council.
-6 — A delegated act adopted pursuant to Article 6(2b), Article 6a(3), Article 10(2) and Article 22 shall enter into force only if no objection has been expressed either by the European Parliament or by the Council within a period of two months of notification of that act to the European Parliament and the Council or if, before the expiry of that period, the European Parliament and the Council have both informed the Commission that they will not object. That period shall be extended by two months at the initiative of the European Parliament or of the Council.</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 28.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>1.	The power to adopt delegated acts is conferred on the Commission subject to the conditions laid down in this Article.
+2.	The power to adopt delegated acts referred to in Article 7(8), Article 8(3), Article 13(2) and Article 27 shall be conferred on the Commission for an indeterminate period of time from … [the date of entry into force of this Regulation].
+3.	The delegation of power referred to in Article 7(8), Article 8(3), Article 13(2) and Article 27may be revoked at any time by the European Parliament or by the Council. A decision to revoke shall put an end to the delegation of the power specified in that decision. It shall take effect the day following the publication of the decision in the Official Journal of the European Union or at a later date specified therein. It shall not affect the validity of any delegated acts already in force.
+4.	Before adopting a delegated act, the Commission shall consult experts designated by each Member State in accordance with the principles laid down in the Interinstitutional Agreement of 13 April 2016 on Better Law-Making.
+5.	As soon as it adopts a delegated act, the Commission shall notify it simultaneously to the European Parliament and to the Council.
+6.	A delegated act adopted pursuant to Article 7(8), Article 8(3), Article 13(2) or Article 27 shall enter into force only if no objection has been expressed either by the European Parliament or by the Council within a period of two months of notification of that act to the European Parliament and the Council or if, before the expiry of that period, the European Parliament and the Council have both informed the Commission that they will not object. That period shall be extended by two months at the initiative of the European Parliament or of the Council</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>1 — O poder de adotar atos delegados é conferido à Comissão nas condições estabelecidas no presente artigo.
 2 — O poder de adotar atos delegados referido no artigo 6.º, n.º 4, no artigo 10.º, n.º 2, e no artigo 22.º é conferido à Comissão por tempo indeterminado a partir de [data de entrada em vigor do presente regulamento].
@@ -2997,260 +3148,262 @@
 6 — Os atos delegados adotados nos termos do artigo 6.º, n.º 4, do artigo 10.º, n.º 2, e do artigo 22.º só entram em vigor se não tiverem sido formuladas objeções pelo Parlamento Europeu ou pelo Conselho no prazo de dois meses a contar da notificação desse ato ao Parlamento Europeu e ao Conselho, ou se, antes do termo desse prazo, o Parlamento Europeu e o Conselho tiverem informado a Comissão de que não têm objeções a formular. O referido prazo é prorrogado por dois meses por iniciativa do Parlamento Europeu ou do Conselho.</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="K24" s="8" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="L24" s="9" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="M24" s="10" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="N24" s="11" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="N25" s="11" t="inlineStr">
         <is>
           <t>Artigo processual do Regulamento europeu — sem correspondência em legislação portuguesa.</t>
         </is>
       </c>
-      <c r="O24" s="11" t="inlineStr">
+      <c r="O25" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P24" s="11" t="inlineStr">
+      <c r="P25" s="11" t="inlineStr">
         <is>
           <t>Artigo sobre procedimento de delegação de atos à Comissão Europeia.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="120" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26" ht="120" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Procedimento de Comité</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 24.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>1 — The Commission shall be assisted by the Standing Committee on Plants, Animals, Food and Feed established by Article 58(1) of Regulation (EC) No 178/2002. That Committee shall be a committee within the meaning of Regulation (EU) No 182/2011.
-2 — Where reference is made to this paragraph, Article 5 of Regulation (EU) No 182/2011 shall apply.
-3 — Where the Committee delivers no opinion, the Commission shall not adopt the draft implementing act and Article 5(4), third subparagraph, of Regulation (EU) No 182/2011 shall apply.</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 29.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>1.	The Commission shall be assisted by the Standing Committee on Plants, Animals, Food and Feed established by Article 58(1) of Regulation (EC) No 178/2002. That Committee shall be a committee within the meaning of Regulation (EU) No 182/2011.
+2.	Where reference is made to this paragraph, Article 5 of Regulation (EU) No 182/2011 shall apply.
+Where the Committee delivers no opinion, the Commission shall not adopt the draft implementing act, and Article 5(4), third subparagraph, of Regulation (EU) No 182/2011 shall apply.
+CHAPTER VII
+STRICTER NATIONAL RULES AND FINAL PROVISIONS</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>1 — A Comissão é assistida pelo Comité Permanente dos Vegetais, Animais e dos Alimentos para Consumo Humano e Animal criado pelo artigo 58.º, n.º 1, do Regulamento (CE) n.º 178/2002. Este comité deve ser entendido como comité na aceção do Regulamento (UE) n.º 182/2011.
 2 — Caso se faça referência ao presente número, aplica-se o artigo 5.º do Regulamento (UE) n.º 182/2011.
 3 — Na falta de parecer do comité, a Comissão não adota o projeto de ato de execução, aplicando-se o artigo 5.º, n.º 4, terceiro parágrafo, do Regulamento (UE) n.º 182/2011.</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="K25" s="8" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="L25" s="9" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="M25" s="10" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="N25" s="11" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="N26" s="11" t="inlineStr">
         <is>
           <t>Artigo processual do Regulamento europeu — sem correspondência em legislação portuguesa.</t>
         </is>
       </c>
-      <c r="O25" s="11" t="inlineStr">
+      <c r="O26" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P25" s="11" t="inlineStr">
+      <c r="P26" s="11" t="inlineStr">
         <is>
           <t>Artigo sobre procedimento de comité — assistência à Comissão Europeia.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="120" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27" ht="120" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Medidas Nacionais Mais Rigorosas</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 25.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>1 — This Regulation shall not prevent Member States from maintaining or adopting any stricter national rules aimed at a more extensive protection of the welfare of dogs and cats kept in establishments and the traceability of dogs and cats, provided that those rules are not inconsistent with this Regulation and do not interfere with the proper functioning of the internal market.
-1a — Member States shall inform the Commission about such existing national rules by [the date of application of this Regulation] and shall inform the Commission about such new national rules before their adoption, unless Member States have notified the draft national rules in accordance with Directive (EU) 2015/1535. The Commission shall bring them to the attention of the other Member States.
-2 — A Member State that has stricter national rules referred to in paragraph 1 shall not prohibit or impede the placing on the market within its territory of dogs and cats kept in another Member State on the grounds that the dogs and cats concerned have not been kept in accordance with its stricter national rules.</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 30.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>1.	This Regulation shall not prevent Member States from maintaining or adopting stricter national rules aimed at providing more extensive protection of the welfare of dogs and cats kept in establishments, and a greater traceability of dogs and cats, provided that those rules are not inconsistent with this Regulation and do not interfere with the proper functioning of the internal market.
+2.	Member States shall, by ... [two years after the date of entry into force of this Regulation], inform the Commission about any existing stricter national rules that they intend to maintain in accordance with paragraph 1. Thereafter, Member States shall inform the Commission about stricter national rules before their adoption, unless the Member States have already notified the draft national rules as a draft technical regulation under Article 5 of Directive (EU) 2015/1535 of the European Parliament and of the Council. The Commission shall bring them to the attention of the other Member States.
+3.	A Member State that has stricter national rules referred to in paragraph 1 shall not prohibit or impede the placing on the market within its territory of dogs and cats kept in another Member State on the grounds that the dogs and cats concerned have not been kept in accordance with its stricter national rules  .</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>1 — O presente regulamento não obsta a que os Estados-Membros mantenham disposições nacionais mais rigorosas que visem uma proteção mais ampla do bem-estar dos cães e gatos detidos em estabelecimentos e a rastreabilidade dos cães e gatos, desde que essas disposições não sejam incompatíveis com o presente regulamento e não interfiram com o bom funcionamento do mercado interno.
 1a — Os Estados-Membros devem informar a Comissão acerca de tais disposições nacionais existentes até [data de aplicação do presente regulamento] e devem informar a Comissão acerca de tais disposições nacionais novas antes da sua adoção, salvo se os Estados-Membros tiverem notificado os projetos de disposições nacionais em conformidade com a Diretiva (UE) 2015/1535. A Comissão transmite essas informações aos outros Estados-Membros.
 2 — Um Estado-Membro que tenha disposições nacionais mais rigorosas referidas no n.º 1 não pode proibir ou impedir a colocação no mercado, no seu território, de cães e gatos detidos noutro Estado-Membro com o fundamento de que os cães e gatos em causa não estiveram detidos em conformidade com as suas disposições nacionais mais rigorosas.</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="L26" s="9" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="M26" s="10" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="N26" s="11" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="N27" s="11" t="inlineStr">
         <is>
           <t>Artigo sobre direitos dos Estados-Membros de manter ou adoptar medidas mais rigorosas.</t>
         </is>
       </c>
-      <c r="O26" s="11" t="inlineStr">
+      <c r="O27" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P26" s="11" t="inlineStr">
+      <c r="P27" s="11" t="inlineStr">
         <is>
           <t>Artigo sobre liberdade de Estados-Membros para legislação mais rigorosa.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="120" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28" ht="120" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Relatórios e Avaliação</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 26.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>1 — On the basis of the reports received in accordance with Article 20 and any additional relevant information, the Commission shall publish, by [7 years from the date of entry into force of this Regulation] and thereafter every 3 years, a monitoring report on the welfare of dogs and cats placed on the market in the Union.
-2 — By 14 years from the date of entry into force of this Regulation, the Commission shall carry out an evaluation of this Regulation and present a report on the main findings to the European Parliament, the Council, the European Economic and Social Committee, and the Committee of the Regions. In particular, the Commission shall assess:
-a) the extent to which this Regulation has contributed to ensuring a high level of welfare for dogs and cats, improving traceability, reducing illegal trade;
-b) the impact of this Regulation on operators of breeding and selling establishments and of shelters, and operators placing dogs and cats in foster homes, including the administrative burden and compliance costs.
-3 — For the purposes of the reporting referred to in paragraph 2, Member States shall provide the Commission with the information necessary for the preparation of the report.</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 31.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>1.	On the basis of the reports received in accordance with Article 24 and any additional relevant information, the Commission shall publish, by ... [7 years from the date of entry into force of this Regulation] and thereafter at three-yearly intervals, a monitoring report on the welfare of dogs and cats placed on the market in the Union.
+2.	By … [14 years from the date of entry into force of this Regulation ] , the Commission shall carry out an evaluation of this Regulation  and present a report on the main findings to the European Parliament, the Council, the European Economic and Social Committee, and the Committee of the Regions. In that evaluation and report the Commission shall assess, in particular:
+(a)	the extent to which this Regulation has contributed to ensuring a high level of welfare for dogs and cats, improving their traceability, and reducing the illegal trade in them;
+(b)	the impact that this Regulation has had on operators of breeding and selling establishments and shelters, and of operators who place dogs and cats in foster homes, taking into account inter alia the administrative burden and compliance costs.
+3.	For the purposes of the reporting referred to in paragraph 2, Member States shall provide the Commission with the information necessary for the preparation of its report.</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>1 — Com base nos relatórios recebidos em conformidade com o artigo 20.º e em informações adicionais pertinentes, a Comissão publica, até [7 anos após a data de entrada em vigor do presente regulamento] e, posteriormente, de três em três anos, um relatório de monitorização sobre o bem-estar dos cães e gatos colocados no mercado da União.
 2 — Até [14 anos a contar da data de entrada em vigor do presente regulamento], a Comissão procede a uma avaliação do presente regulamento e apresenta um relatório sobre as principais conclusões ao Parlamento Europeu, ao Conselho, ao Comité Económico e Social Europeu e ao Comité das Regiões. Em particular, a Comissão avalia:
@@ -3259,177 +3412,232 @@
 3 — Para efeitos dos relatórios referidos no n.º 2, os Estados-Membros devem fornecer à Comissão as informações necessárias para a elaboração dos mesmos.</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="K27" s="8" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="L27" s="9" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="M27" s="10" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="N27" s="11" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="N28" s="11" t="inlineStr">
         <is>
           <t>Artigo sobre obrigações de relatório e avaliação pela Comissão Europeia.</t>
         </is>
       </c>
-      <c r="O27" s="11" t="inlineStr">
+      <c r="O28" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P27" s="11" t="inlineStr">
+      <c r="P28" s="11" t="inlineStr">
         <is>
           <t>Artigo sobre relatórios de monitorização e avaliação do Regulamento.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="120" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Sanções</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 27.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>1 — Member States shall lay down the rules on penalties applicable to infringements of this Regulation, including those resulting from the abandonment by operators of dogs and cats, and shall take all measures necessary to ensure that they are implemented. The penalties provided for shall be effective, proportionate and dissuasive.
-2 — Member States shall notify the Commission of those rules and of those measures and shall notify it, without delay, of any subsequent amendment affecting them.</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>1 — Os Estados-Membros estabelecem as regras relativas às sanções aplicáveis em caso de violação do disposto no presente regulamento, incluindo as resultantes do abandono de cães e gatos por parte de operadores, e tomam todas as medidas necessárias para garantir a sua aplicação. As sanções previstas devem ser efetivas, proporcionadas e dissuasivas.
-2 — Os Estados-Membros notificam a Comissão dessas regras e dessas medidas e também, sem demora, de qualquer alteração ulterior das mesmas.</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="K28" s="8" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="L28" s="9" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="M28" s="10" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="N28" s="11" t="inlineStr">
-        <is>
-          <t>Artigo sobre responsabilidade dos Estados-Membros em estabelecer sanções por infração.</t>
-        </is>
-      </c>
-      <c r="O28" s="11" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="P28" s="11" t="inlineStr">
-        <is>
-          <t>Artigo sobre regime sancionatório a ser definido pelos Estados-Membros.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="120" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>Sanções</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 32.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Member States shall lay down the rules on penalties applicable to infringements of this Regulation, including those resulting from the abandonment by operators of dogs and cats, and shall take all measures necessary to ensure that they are implemented. The penalties provided for shall be effective, proportionate and dissuasive.
+Member States shall notify the Commission of those rules and of those measures and shall notify it, without delay, of any subsequent amendments affecting them.</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>1 — Os Estados-Membros estabelecem as regras relativas às sanções aplicáveis em caso de violação do disposto no presente regulamento, incluindo as resultantes do abandono de cães e gatos por parte de operadores, e tomam todas as medidas necessárias para garantir a sua aplicação. As sanções previstas devem ser efetivas, proporcionadas e dissuasivas.
+2 — Os Estados-Membros notificam a Comissão dessas regras e dessas medidas e também, sem demora, de qualquer alteração ulterior das mesmas.</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="N29" s="11" t="inlineStr">
+        <is>
+          <t>Artigo sobre responsabilidade dos Estados-Membros em estabelecer sanções por infração.</t>
+        </is>
+      </c>
+      <c r="O29" s="11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P29" s="11" t="inlineStr">
+        <is>
+          <t>Artigo sobre regime sancionatório a ser definido pelos Estados-Membros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="120" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
           <t>Entrada em Vigor e Aplicação</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 28.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>1 — This Regulation shall enter into force on the twentieth day following that of its publication in the Official Journal of the European Union.
-2 — It shall apply from [2 years from the date of entry into force of this Regulation], except:
-a) Article 13 that shall apply from [3 years from the date of entry into force of this Regulation];
-b) Article 6a(2) that shall apply from 1 July 2030;
-c) Article 12, Article 17a(3)(c), (4) and (6), Article 18(a),(b) and (ba), Article 19(2) and (2a), and Article 21(1) to (4) that shall apply from [5 years from the date of entry into force of this Regulation];
-d) Article 9(2) and (2a) that shall apply from [7 years from the date of entry into force of this Regulation];
-e) Article 7a that shall apply from [8 years from the date of entry into force of this Regulation];
-f) Article 21(4a) that shall apply from [10 years from the entry into force of the Regulation] and;
-g) second subparagraph of Article 17(1) and (2), Article 17a(3) and Article 19(1) that shall apply from [4 years from entry into force of this Regulation], except for pet owners and other natural or legal persons, other than operators, who do not place dogs or cats on the market, for whom Article 17(1) and (2) shall apply from [10 years from entry into force of this Regulation] in the case of identification and registration of dogs and [15 years from the entry into force of this Regulation] in the case of identification and registration of cats.
-3 — This Regulation shall be binding in its entirety and directly applicable in all Member States.</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 33.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>This Regulation shall enter into force on the twentieth day following that of its publication in the Official Journal of the European Union.
+It shall apply from ... [two years from the date of entry into force of this Regulation]. However,
+(i)	Article 16 shall apply from … [three years from the date of entry into force of this Regulation];
+(ii)	 Article 21(3) and Article 23(1) shall apply from … [four years from entry into force of this Regulation];
+(iii)	Article 8(1) shall apply from 1 July 2036 and Article 8(2) shall apply from 1 July 2030;
+(iv)	Article 15, Article 21(3), second subparagraph, (4) and (5), Article 22(1), points (a),(b) and (c), Article 23(3) and (4), and Article 26(1), (2) and (3) shall apply from … [five years from the date of entry into force of this Regulation];
+(v)	Article 12(2) and (3) shall apply from … [seven years from the date of entry into force of this Regulation];
+(vi)	Article 10 shall apply from … [eight years from the date of entry into force of this Regulation]; and
+(vii)	Article 26(4) shall apply from … [10 years from the entry into force of the Regulation].
+This Regulation shall be binding in its entirety and directly applicable in all Member States.
+Done at …,
+For the European Parliament	For the Council
+The President	The President
+Annex I
+Requirements applicable to establishments
+1.	Feeding and watering
+1.1.	Dogs and cats shall be fed at least twice per day. Puppies and kittens shall be fed more frequently.
+However, those requirements shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
+1.2.	Each puppy or kitten shall be fed with colostrum during at least the first two days of its life. Thereafter, it shall be fed with milk from its mother or a lactating bitch or queen. If that is not possible, because the mother is ill or is otherwise unable to feed her offspring or unable to provide sufficient milk, the puppy or kitten shall be fed with a milk replacer that has been designed for puppies and kittens . The frequency of such feeding shall comply with the manufacturer’s instructions or those of a veterinarian.
+1.3.	All unweaned puppies and kittens shall be fed enough milk, milk replacer or a combination of both, to allow them to gain bodyweight steadily.
+1.4.	Weaning shall be performed by the gradual introduction of solid feed over a period that is not shorter than seven days and shall not be completed before the age of six weeks for puppies and kittens alike.
+2.	Housing
+2.1.	Temperature:
+In breeding establishments, the temperature shall be maintained within a range of:
+(a)	22 to 28°C in whelping areas for the first 10 days of puppies’ lives;
+(b)	18 to 27°C in kittening areas for the first 21 days of kittens’ lives.
+2.2.	Lighting
+2.2.1.	Dogs and cats shall be exposed to light for at least 7 hours per day.
+2.2.2.	Artificial light shall be broad spectrum or full spectrum with a frequency of at least 80 Hertz.
+2.2.3.	Dogs and cats shall have the possibility to be without artificial lighting for at least 8 hours per day.
+2.3.	Space allowances
+2.3.1.	Whelping and kittening areas shall be designed to allow the mother to move away from her offspring.
+2.3.2,	In the case of breeding and selling establishments, the following minimum space allowances for dogs and cats shall apply, based on the total permanently accessible area for the dogs or cats:
+2.3.3,
+3.	Health
+3.1.	Queens shall be bred from only if their age is at least 10 months;
+3.2.	Bitches shall not be used for breeding from before their second oestrus.
+3.3.	A bitch or queen shall not produce more than three litters within a period of two years.
+3.4.	For bitches and queens that have produced 3 litters, including stillborns, within a period of two years, there shall be a recuperation  period of at least one year.
+3.5.	Any bitch or queen that has undergone two caesarean sections shall no longer be used for breeding.
+3.6.	Before any bitch aged eight years or more, or any queen aged six years or more, is used for breeding, it must be physically examined by a veterinarian who confirms in writing that, at the time of the examination, there are no medical indications that argue against the use of that bitch or queen for breeding.
+The operator shall keep the written confirmation referred to in the first subparagraph for a period of at least three years.
+4.	Behavioural needs
+4.1.	Socialisation
+4.1.1.	From three weeks of age, dogs and cats shall be gradually provided with daily opportunities for social contact with other animals of the same species and humans, and, where possible, with animals of other species.
+4.1.2.	Dogs or cats that pose a threat to each other due to aggressive behaviour, or that cause each other undue stress or discomfort shall be kept separate.
+4.2.	Enrichment
+4.2.1.	Cats shall be provided with a sufficient number of scratching posts, hiding places and shelves to ensure that each cat can climb, rest, observe and withdraw.
+4.3.	Separation
+Puppies kept in establishments shall not be permanently separated from their mothers before the age of eight weeks.
+Kittens kept in shelters and foster homes shall not be permanently separated from their mothers before the age of eight weeks. Kittens kept in breeding establishments shall not be permanently separated from their mothers before the age of 12 weeks.
+However, earlier separation from mothers shall be possible for medical reasons based on the written advice of a veterinarian. The operator shall keep a record of such advice until the last puppy or kitten of the litter concerned is placed on the market.
+Annex II
+Identification and registration of dogs and cats
+Transponders used to individually identify dogs and cats as required in Article 20 and Article 26 shall meet the following requirements:
+(a)	the microchip shall contain an individual, non-repeatable and non-reprogrammable identification number;
+(b)	the identification number shall start with the country of identification of the dog or cat identified in accordance with ISO standard 3166;
+(c)	the code structure and technical concept of the radio frequency identification shall be in compliance with ISO standards 11784 and 11785;
+(d)	compliance with ISO standards 11784 and 11785 shall be evaluated in accordance with ISO standard 24631-1.
+Annex III
+Data on animal welfare
+1.	The number of dogs and cats registered per year, as referred to in Article 20 and Article 26(3).
+2.	The number of breeding establishments, selling establishments, shelters and foster homes registered per year in accordance with Article 9.
+3.	The number of breeding establishments approved per year, as referred to in Article 10.
+4.	The number of breeding establishments approval of which has been suspended or withdrawn per year.</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>1 — O presente regulamento entra em vigor no vigésimo dia seguinte ao da sua publicação no Jornal Oficial da União Europeia.
 2 — O presente regulamento é aplicável a partir de [2 anos após a data de entrada em vigor do presente regulamento], salvo:
@@ -3443,79 +3651,79 @@
 3 — O presente regulamento é obrigatório em todos os seus elementos e diretamente aplicável em todos os Estados-Membros.</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="K29" s="8" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="L29" s="9" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="M29" s="10" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="N29" s="11" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="N30" s="11" t="inlineStr">
         <is>
           <t>Artigo sobre entrada em vigor e aplicação do Regulamento.</t>
         </is>
       </c>
-      <c r="O29" s="11" t="inlineStr">
+      <c r="O30" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P29" s="11" t="inlineStr">
+      <c r="P30" s="11" t="inlineStr">
         <is>
           <t>Artigo sobre entrada em vigor, períodos de aplicação escalonados e obrigatoriedade do Regulamento.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="120" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31" ht="120" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Requisitos Técnicos — Alimentação e Abeberamento</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>ANEXO I, Ponto 1 do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>1. Feeding and watering
 1.1 Dogs and cats shall be fed at least twice per day. Puppies and kittens shall be fed more frequently.
@@ -3525,7 +3733,7 @@
 1.5 Weaning shall be performed with gradual introduction of firm feed, in a process not shorter than 7 days and shall not be completed before 6 weeks of age for puppies and kittens alike.</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>1. Alimentação e abeberamento
 1.1 Os cães e gatos devem ser alimentados pelo menos duas vezes por dia. Os filhotes de cão e gato devem ser alimentados com maior frequência.
@@ -3535,12 +3743,12 @@
 1.5 O desmame deve ser realizado com introdução gradual de alimentos sólidos, num processo que não seja inferior a 7 dias e não deve ser concluído antes dos 6 semanas de idade para filhotes de cão e gato.</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Art.º 33.º, Arts. 38-40 do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Artigo 33.º - Alimentação
 1 - Deve existir um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades fisiológicas, nutricionais e metabólicas dos cães e gatos, consoante a edad, raça, categoria, nível de atividade e estado de saúde.
@@ -3551,12 +3759,12 @@
 6 - Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>Art.º 18.º (n.º 1), Art.º 46.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr">
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>Artigo 18.º - Instalações
 n.º 1 - Os alojamentos que se destinem à reprodução, criação, manutenção ou venda de animais de companhia, devem possuir instalações individualizadas destinadas à armazenagem de alimentos e equipamento limpo e à lavagem e recolha de material.
@@ -3570,12 +3778,12 @@
 n.º 7 - É proibido alimentar animais com restos de comida, produtos de pastelaria e desperdícios da indústria alimentar e de restauração.</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>Art.º 12.º, Art.º 49.º do DL n.º 276-2001, de 17 de outubro; Art.º 5.º, n.º 5 da Portaria n.º 146/2017</t>
         </is>
       </c>
-      <c r="J30" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>Artigo 12.º — Alimentação e abeberamento
 1 - Deve existir um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies e dos indivíduos de acordo com a fase de evolução fisiológica em que se encontram, nomeadamente idade, sexo, fêmeas prenhes ou em fase de lactação.
@@ -3590,54 +3798,54 @@
 [/dim]</t>
         </is>
       </c>
-      <c r="K30" s="8" t="inlineStr">
+      <c r="K31" s="8" t="inlineStr">
         <is>
           <t>PARCIAL CONVERGÊNCIA
 DL 276/2001 (Art. 12.º) cobre: programa alimentar, padrões de higiene, água potável, variação de refeições, equipamentos (comedouros, bebedouros, frio).
 FALTAM especificidades do Regulamento: frequência mínima (2x/dia para cães e gatos), colostro (mínimo 2 dias), leite materno, desmame gradual (mínimo 7 dias, não antes 6 semanas), disposições específicas para filhotes.</t>
         </is>
       </c>
-      <c r="L30" s="9" t="inlineStr">
+      <c r="L31" s="9" t="inlineStr">
         <is>
           <t>PARCIAL CONVERGÊNCIA
 O Código do Animal (DL 214/2013, Art. 46) cobre: programa alimentar, padrões de higiene, água potável, proibições de restos.
 FALTAM especificidades do Regulamento: frequência mínima (2x/dia), colostro (mínimo 2 dias), leite materno, desmame gradual (mínimo 7 dias, não antes 6 semanas).</t>
         </is>
       </c>
-      <c r="M30" s="10" t="inlineStr">
+      <c r="M31" s="10" t="inlineStr">
         <is>
           <t>CONVERGÊNCIA COMPLETA
 RGBEAC (Art. 33) espelha integralmente os requisitos do Regulamento: programa definido, frequências, padrões de higiene, água potável, refrigeração, alimentos saudáveis e adequados.</t>
         </is>
       </c>
-      <c r="N30" s="11" t="inlineStr">
+      <c r="N31" s="11" t="inlineStr">
         <is>
           <t>ANNEX I, Ponto 1 do Regulamento especifica requisitos técnicos mínimos: frequência 2x/dia, colostro (2 dias), leite materno, desmame gradual (7 dias). DL 276/2001 (Art. 12.º) cobre aspetos gerais (programa, higiene, água, equipamentos) mas não detalha frequências, colostro, desmame. Código do Animal (Art. 46) é convergente com DL 276/2001. RGBEAC já incorpora todas as especificidades. Recomenda-se alteração do DL 276/2001 e/ou Código do Animal para integrar especificidades técnicas do Regulamento (frequências, colostro, desmame).</t>
         </is>
       </c>
-      <c r="O30" s="11" t="inlineStr">
+      <c r="O31" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P30" s="11" t="inlineStr">
+      <c r="P31" s="11" t="inlineStr">
         <is>
           <t>ANNEX I, Ponto 1 estabelece requisitos técnicos de alimentação. DL 276/2001 (Art. 12.º) e Código do Animal (Art. 46) cobrem aspetos gerais. RGBEAC já implementa integralmente as especificidades do Regulamento. Recomenda-se harmonização definitiva através de alteração legislativa para integrar: (i) frequência mínima 2x/dia; (ii) colostro (mínimo 2 dias); (iii) desmame gradual (mínimo 7 dias, não antes 6 semanas).</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="120" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32" ht="120" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Requisitos Técnicos — Alojamento (Housing)</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>ANEXO I, Ponto 2 do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>2. Housing
 2.1 Temperature
@@ -3653,7 +3861,7 @@
 2.3.3a In case of breeding and selling establishments, the following minimum space allowances for dogs and cats shall apply, which shall be calculated based on the total permanently accessible area for the dogs or cats.</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>2. Alojamento
 2.1 Temperatura
@@ -3669,22 +3877,22 @@
 2.3.3a No caso de estabelecimentos de criação e venda, as seguintes alocações mínimas de espaço para cães e gatos devem ser aplicadas, que devem ser calculadas com base na área total permanentemente acessível para os cães ou gatos.</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Sem equivalência específica</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>Sem equivalência identificada no @RGBEAC para os requisitos técnicos específicos de temperatura, iluminação e espaço do ANNEX I, Ponto 2 do Regulamento.</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>Art.º 8.º, Art.º 9.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>Artigo 8.º - Condições dos alojamentos
 1 - Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
@@ -3703,12 +3911,12 @@
 6 - As instalações devem dispor de abrigos para que os animais se protejam de condições climáticas adversas.</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>Art.º 8.º, Art.º 9.º do DL n.º 276-2001; Art.º 10.º do DL n.º 276-2001 (transporte)</t>
         </is>
       </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>Artigo 8.º - Condições dos alojamentos
 1 - Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
@@ -3727,53 +3935,53 @@
 6 - As instalações devem dispor de abrigos para que os animais se protejam de condições climáticas adversas.</t>
         </is>
       </c>
-      <c r="K31" s="8" t="inlineStr">
+      <c r="K32" s="8" t="inlineStr">
         <is>
           <t>PARCIAL CONVERGÊNCIA
 DL 276/2001 (Arts. 8.º e 9.º) cobrem: espaço adequado, estruturas seguras, fatores ambientais (temperatura, ventilação, luz), abrigos para condições adversas.
 FALTAM especificidades do Regulamento: temperatura exata (22-28°C para parto de cães; 18-27°C para parto de gatos), iluminação mínima (7 horas luz, 8 horas sem luz, espectro 80 Hz), espaço mínimo quantificado, áreas de parto separadas.</t>
         </is>
       </c>
-      <c r="L31" s="9" t="inlineStr">
+      <c r="L32" s="9" t="inlineStr">
         <is>
           <t>PARCIAL CONVERGÊNCIA
 Código do Animal (Arts. 8.º e 9.º) equivalentes ao DL 276/2001 mas também faltam: temperatura específica, iluminação quantificada (7h luz/80Hz, 8h sem luz), espaço mínimo por tamanho/idade.</t>
         </is>
       </c>
-      <c r="M31" s="10" t="inlineStr">
+      <c r="M32" s="10" t="inlineStr">
         <is>
           <t>SEM EQUIVALÊNCIA ESPECÍFICA
 Não foi identificada correspondência específica no @RGBEAC para os requisitos técnicos detalhados de temperatura, iluminação e espaço do ANNEX I, Ponto 2 do Regulamento.</t>
         </is>
       </c>
-      <c r="N31" s="11" t="inlineStr">
+      <c r="N32" s="11" t="inlineStr">
         <is>
           <t>ANNEX I, Ponto 2 do Regulamento especifica requisitos técnicos detalhados: temperatura por fase (parto de cães 22-28°C; gatos 18-27°C), iluminação (7h luz + 80Hz, 8h sem luz), espaço mínimo quantificado, áreas de parto separadas. DL 276/2001 cobre conceitos gerais mas não detalha temperaturas, frequências de luz ou espaço mínimo. Recomenda-se alteração do DL 276/2001 para integrar parâmetros técnicos específicos do Regulamento.</t>
         </is>
       </c>
-      <c r="O31" s="11" t="inlineStr">
+      <c r="O32" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P31" s="11" t="inlineStr">
+      <c r="P32" s="11" t="inlineStr">
         <is>
           <t>ANNEX I, Ponto 2 estabelece requisitos técnicos de alojamento. DL 276/2001 (Arts. 8.º e 9.º) cobrem aspetos gerais. RGBEAC já implementa integralmente as especificidades do Regulamento. Recomenda-se harmonização definitiva através de alteração legislativa para integrar: (i) temperatura exata (22-28°C parto cães; 18-27°C parto gatos); (ii) iluminação mínima (7h luz + 80Hz, 8h sem luz); (iii) espaço mínimo quantificado por tamanho/idade.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="120" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33" ht="120" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Requisitos Técnicos — Reprodução (Health)</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>ANEXO I, Ponto 3 do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>3. Health
 3.1 Queens shall only be bred if their age is at least 10 months.
@@ -3784,7 +3992,7 @@
 3.4b Before any bitch aged 8 years or more and any queen aged 6 years or more, is used for breeding, it must have been physically examined by a veterinarian who confirms in writing that, at the time of the examination, there are no counter-indications to pregnancy. The operator shall keep the written confirmation referred to in point 3.4.b for a period of at least 3 years.</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>3. Saúde Reprodutiva
 3.1 As gatas só podem reproduzir se tiverem uma idade mínima de 10 meses.
@@ -3795,12 +4003,12 @@
 3.4b Antes de qualquer cadela com 8 ou mais anos e qualquer gata com 6 ou mais anos ser usada para reprodução, deve ter sido submetida a exame físico por médico veterinário que confirme por escrito que, na altura do exame, não existem contraindicações para a gravidez. O operador deve manter a confirmação escrita referida no ponto 3.4.b por um período de pelo menos 3 anos.</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Arts. 70.º-73.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Artigo 70.º - Reprodução de cães e gatos
 1 - Os cães reprodutores devem cumprir as seguintes exigências: [...]
@@ -3811,12 +4019,12 @@
 [Ver artigos 71.º-73.º para disposições complementares sobre avaliação de saúde, testes genéticos e destino de reprodutores]</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>Art.º 8.º do Código do Animal (DL 214/2013) + Anexo I</t>
         </is>
       </c>
-      <c r="H32" s="6" t="inlineStr">
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>Artigo 8.º - Reprodução
 1 - Os operadores devem assegurar que:
@@ -3825,63 +4033,63 @@
 [ANEXO I] Raças pequeno e médio porte – 3.º cio; Raças grande porte – 2 anos. Ninhadas: Cadelas não mais de 2 ninhadas em 2 anos; Gatas não mais de 3 ninhadas em 2 anos (recomendação, com exceção veterinária).</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>Art.º 8.º e Anexo do DL n.º 276-2001</t>
         </is>
       </c>
-      <c r="J32" s="7" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>[DL 276/2001 não contém artigos específicos sobre idade mínima para reprodução, frequência máxima de ninhadas, período de recuperação, proibição de cesarianas ou avaliação veterinária de reprodutores idosos]
 Nota: O DL 276/2001 menciona genericamente a necessidade de cumprir 'condições de saúde' e 'bem-estar', mas não detalha requisitos específicos de reprodução como o faz o Regulamento.</t>
         </is>
       </c>
-      <c r="K32" s="8" t="inlineStr">
+      <c r="K33" s="8" t="inlineStr">
         <is>
           <t>DIVERGÊNCIA TOTAL/PARCIAL
 DL 276/2001 não contém disposições específicas sobre: (i) idade mínima para reprodução (cadelas/gatas); (ii) número máximo de ninhadas por período; (iii) período obrigatório de recuperação; (iv) proibição de 2 cesarianas; (v) avaliação veterinária obrigatória para reprodutores idosos. Legislação é omissa em matéria de Health reprodutivo.</t>
         </is>
       </c>
-      <c r="L32" s="9" t="inlineStr">
+      <c r="L33" s="9" t="inlineStr">
         <is>
           <t>PARCIAL CONVERGÊNCIA
 Código do Animal estabelece idades mínimas (3º cio pequenas/médias; 2 anos grandes) e frequência máxima de ninhadas, mas: (i) critérios fisiológicos diferem (cio vs. estro); (ii) sem período de recuperação obrigatório após limite; (iii) sem proibição expressa de 2 cesarianas; (iv) sem avaliação veterinária obrigatória para reprodutores idosos. Mais restritivo que Regulamento em idades mínimas, menos em frequência.</t>
         </is>
       </c>
-      <c r="M32" s="10" t="inlineStr">
+      <c r="M33" s="10" t="inlineStr">
         <is>
           <t>PARCIAL CONVERGÊNCIA COM DIVERGÊNCIAS
 RGBEAC implementa a maioria dos requisitos mas com diferenças críticas: (i) idade mínima cadelas 18 meses (vs. 2º estro); (ii) idade máxima 6 anos (vs. sem máximo no Regulamento); (iii) frequência máxima 4 ninhadas/4 anos (vs. 3 ninhadas/2 anos); (iv) sem período de recuperação obrigatório; (v) proíbe 2 cesarianas (alinhado); (vi) sem avaliação veterinária para &gt;8 anos (RGBEAC proíbe a partir dos 6 anos). Mais restritivo em idades máximas, menos em frequência temporal.</t>
         </is>
       </c>
-      <c r="N32" s="11" t="inlineStr">
+      <c r="N33" s="11" t="inlineStr">
         <is>
           <t>ANNEX I, Ponto 3 (Health) estabelece cinco requisitos essenciais: (i) idade mínima (rainhas 10 meses, cadelas 2º estro); (ii) máximo 3 ninhadas em 2 anos; (iii) período de recuperação 1 ano após limite; (iv) proibição de 2 cesarianas; (v) avaliação veterinária ≥8 anos (cadelas) / ≥6 anos (gatas). Legislação nacional carece de disposições específicas ou é significativamente divergente. Recomenda-se alteração fundamental para integrar todos os cinco requisitos, com atenção especial à frequência de ninhadas e período de recuperação, inexistentes na legislação atual.</t>
         </is>
       </c>
-      <c r="O32" s="11" t="inlineStr">
+      <c r="O33" s="11" t="inlineStr">
         <is>
           <t>Sim - Alteração fundamental obrigatória</t>
         </is>
       </c>
-      <c r="P32" s="11" t="inlineStr">
+      <c r="P33" s="11" t="inlineStr">
         <is>
           <t>ANNEX I, Ponto 3 estabelece requisitos técnicos obrigatórios de saúde reprodutiva. Legislação portuguesa (DL 276/2001, Código, RGBEAC) carece de ou diverge significativamente nesta matéria. Recomenda-se: (i) incorporar idade mínima 10 meses (gatas) e 2º estro (cadelas); (ii) estabelecer máximo imperativo de 3 ninhadas em 2 anos (sem exceções veterinárias); (iii) exigir período de recuperação 1 ano após atingir limite; (iv) proibir uso após 2 cesarianas; (v) exigir avaliação veterinária escrita para cadelas ≥8 anos e gatas ≥6 anos. Estas alterações são críticas para garantir a conformidade com o Regulamento.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="120" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34" ht="120" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Requisitos Técnicos — Bem-Estar Comportamental (Behavioural Needs)</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>ANEXO I, Ponto 4 do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>4. Behavioural needs
 4.1 Socialisation
@@ -3895,7 +4103,7 @@
 By way of derogation, earlier separation shall be possible due to medical reasons based on written advice of a veterinarian. The operator shall keep a record of the advice until the last puppy or kitten of the litter concerned is placed on the market.</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>4. Bem-Estar Comportamental
 4.1 Socialização
@@ -3909,12 +4117,12 @@
 Por derrogação, separação anterior é possível por razões médicas com base em parecer escrito de um veterinário. O operador deve conservar o parecer até o último cachorro ou gatinho da ninhada em questão ser colocado no mercado.</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Arts. 10.º, 12.º, 47.º, 52.º, 68.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>SUBSECÇÃO 4.1 (SOCIALIZAÇÃO):
 Artigo 52.º — Maneio
@@ -3927,12 +4135,12 @@
 5 — As crias não podem ser separadas da progenitora antes da décima semana de idade, no caso dos cães, e antes da décima segunda semana de idade, no caso dos gatos, salvaguardado um período de desmame gradual.</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>Arts. 13.º, 18.º, e outros do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H33" s="6" t="inlineStr">
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>SUBSECÇÃO 4.1 (SOCIALIZAÇÃO):
 [Código do Animal não contém disposições específicas sobre socialização]
@@ -3948,12 +4156,12 @@
 2 — [...] devendo os animais: [...] Ter idade superior a oito semanas.</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>Art.º 8.º do DL n.º 276-2001</t>
         </is>
       </c>
-      <c r="J33" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>SUBSECÇÃO 4.1 (SOCIALIZAÇÃO):
 [DL 276/2001 não contém disposições específicas sobre socialização]
@@ -3964,55 +4172,55 @@
 [DL 276/2001 não contém disposições específicas sobre idade mínima de separação de mãe ou exposição em locais de venda]</t>
         </is>
       </c>
-      <c r="K33" s="8" t="inlineStr">
+      <c r="K34" s="8" t="inlineStr">
         <is>
           <t>4.1 SOCIALIZAÇÃO: DIVERGÊNCIA TOTAL — DL 276/2001 omisso completamente
 4.2 ENRIQUECIMENTO: PARCIAL — cobre genérico (substrato, ninhos, buracos) mas omite 'postes de arranhadura' (crítico para gatos)
 4.3 SEPARAÇÃO: DIVERGÊNCIA TOTAL — DL 276/2001 omisso; Regulamento exige mínimo 8-12 semanas, DL não especifica</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr">
+      <c r="L34" s="9" t="inlineStr">
         <is>
           <t>4.1 SOCIALIZAÇÃO: DIVERGÊNCIA SIGNIFICATIVA — Código menciona contato social mas sem detalhe (idade, frequência, documentação)
 4.2 ENRIQUECIMENTO: PARCIAL — menciona prateleiras/poleiros mas omite 'postes de arranhadura' (essencial para gatos)
 4.3 SEPARAÇÃO: DIVERGÊNCIA SIGNIFICATIVA — Código exige 8 semanas (Arts. 23.º, 82.º) para EXPOSIÇÃO em venda; Regulamento exige 8 semanas (puppies, kittens abrigos) e 12 semanas (kittens breeding) para SEPARAÇÃO de mãe — conceitos distintos</t>
         </is>
       </c>
-      <c r="M33" s="10" t="inlineStr">
+      <c r="M34" s="10" t="inlineStr">
         <is>
           <t>4.1 SOCIALIZAÇÃO: CONVERGÊNCIA PARCIAL — exige 'plano de socialização' (Art. 52.7) mas sem especificação de: idade 3 semanas, frequência diária, tipos de contato, separação de animais agressivos
 4.2 ENRIQUECIMENTO: CONVERGÊNCIA SIGNIFICATIVA — menciona enriquecimento 'complexo', inclui 'brinquedos', mas omite 'postes de arranhadura' (essencial para gatos)
 4.3 SEPARAÇÃO: CONVERGÊNCIA SIGNIFICATIVA — @RGBEAC (Art. 70.5) exige 10 semanas (cães) / 12 semanas (gatos) com desmame gradual (MAIS RESTRITIVO que Regulamento 8-12 semanas)</t>
         </is>
       </c>
-      <c r="N33" s="11" t="inlineStr">
+      <c r="N34" s="11" t="inlineStr">
         <is>
           <t>ANNEX I, Ponto 4 (Behavioural Needs) tem três subsecções: (i) 4.1 Socialização — contato social diário desde 3 semanas (NOVO); (ii) 4.2 Enriquecimento — postes de arranhadura, abrigos, prateleiras para gatos (PARCIAL na legislação); (iii) 4.3 Separação — 8 semanas (puppies, kittens abrigos), 12 semanas (kittens breeding). DL 276/2001 é omisso em 4.1 e 4.3, parcial em 4.2. Código implementa 8 semanas para exposição (4.3) mas não separação maternal. @RGBEAC é mais restritivo (10-12 semanas separação) e cobre 4.1 (plano) e 4.2 (enriquecimento) com gaps específicos.</t>
         </is>
       </c>
-      <c r="O33" s="11" t="inlineStr">
+      <c r="O34" s="11" t="inlineStr">
         <is>
           <t>Sim - Harmonização fundamental (4.1) + clarificação (4.2 postes arranhadura) + ajuste (4.3 separação vs. exposição)</t>
         </is>
       </c>
-      <c r="P33" s="11" t="inlineStr">
+      <c r="P34" s="11" t="inlineStr">
         <is>
           <t>ANNEX I, Ponto 4 contém 3 subsecções críticas de bem-estar comportamental. 4.1 SOCIALIZAÇÃO: COMPLETAMENTE NOVO — DL 276/2001 omisso. @RGBEAC menciona 'plano' (Art. 52.7) mas sem detalhe do Regulamento (3 semanas, frequência diária, tipos contato, documentação). IMPLEMENTAR: idade, frequência, contatos, registos, separação agressivos. 4.2 ENRIQUECIMENTO: CRÍTICO PARA GATOS — DL 276/2001 genérico, omite 'postes de arranhadura'. Código do Animal menciona 'prateleiras, poleiros' mas não especifica 'postes de arranhadura'. @RGBEAC omite completamente. IMPLEMENTAR: 'número suficiente de postes de arranhadura' (essencial bem-estar felino). 4.3 SEPARAÇÃO: DIVERGÊNCIA CONCEITUAL — Regulamento estabelece idade separação de MÃE (8-12 semanas); Código do Animal refere EXPOSIÇÃO em venda (8 semanas); @RGBEAC mais restritivo (10-12 semanas separação com desmame gradual). CLARIFICAR: 4.3 refere separação maternal, não comercialização.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="120" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35" ht="120" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Requisitos Técnicos — Identificação e Registo de Cães e Gatos (Identification and Registration)</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>ANEXO II do Regulamento 2023/0447 (conforme Articles 17 e 21)</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>Transponders used to individually identify dogs and cats as required in Article 17 and Article 21 shall meet the following requirements:
 — the microchip shall contain an individual, non-repeatable and non-reprogrammable identification number;
@@ -4021,7 +4229,7 @@
 — compliance with ISO standards 11784 and 11785 shall be evaluated according to ISO standard 24631-1.</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Os transponders usados para identificar individualmente cães e gatos conforme exigido nos artigos 17 e 21 devem cumprir os seguintes requisitos:
 — o microchip deve conter um número de identificação individual, não repetível e não reprogramável;
@@ -4030,22 +4238,22 @@
 — a conformidade com as normas ISO 11784 e 11785 deve ser avaliada de acordo com a norma ISO 24631-1.</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Capítulo II — Sistema de Informação de Animais de Companhia (SIAC) do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>O RGBEAC prevê a Lista Nacional de Animais de Companhia como instrumento de proteção, integrando o Sistema de Informação de Animais de Companhia (SIAC), anteriormente previsto no DL n.º 82/2019, de 27 de junho. O registo passa a ser obrigatório para TODOS os animais de companhia como medida de valorização, prevenção do abandono e melhoria do acompanhamento e proteção. [Detalhe técnico sobre ISO standards pendente de análise do texto completo do Capítulo II do RGBEAC]</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>Arts. 53.º a 59.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H34" s="6" t="inlineStr">
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>Artigo 53.º — Identificação e registo na base de dados
 1 - Todos os cães devem ser identificados e registados, entre os três e os seis meses de idade.
@@ -4058,25 +4266,25 @@
 2 - A DGAV detém, define e coordena o acesso à base de dados.</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>DL n.º 82/2019, de 27 de junho (LEGISLAÇÃO VIGENTE) + DL n.º 276-2001</t>
         </is>
       </c>
-      <c r="J34" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>[DL n.º 82/2019, de 27 de junho — LEGISLAÇÃO VIGENTE RELEVANTE]
 Este diploma contém o regime atual de identificação e registo de animais de companhia, incluindo Sistema de Informação de Animais de Companhia (SIAC). REMETE PARA: Análise detalhada online de DL 82/2019 consolidado (dre.pt ou eur-lex) — CRÍTICO para comparação com ANNEX II do Regulamento.
 [DL 276/2001 — legislação anterior, sem disposições operacionais específicas sobre identificação eletrónica]</t>
         </is>
       </c>
-      <c r="K34" s="8" t="inlineStr">
+      <c r="K35" s="8" t="inlineStr">
         <is>
           <t>REVOGAÇÃO TOTAL
 DL 276/2001 foi revogado pelo Código do Animal (DL 214/2013). Sem disposições sobre ISO standards ou requisitos técnicos de microchip.</t>
         </is>
       </c>
-      <c r="L34" s="9" t="inlineStr">
+      <c r="L35" s="9" t="inlineStr">
         <is>
           <t>CONVERGÊNCIA SIGNIFICATIVA
 ✅ Código exige conformidade ISO 11784 (Art. 53.6)
@@ -4086,7 +4294,7 @@
 ⚠️ Prazos diferentes: Código 3-6 meses; Regulamento 3 meses (proprietários), 30 dias (operadores)</t>
         </is>
       </c>
-      <c r="M34" s="10" t="inlineStr">
+      <c r="M35" s="10" t="inlineStr">
         <is>
           <t>CONVERGÊNCIA PARCIAL
 ✅ Integra Sistema de Informação de Animais de Companhia (SIAC) — mais robusto que Código
@@ -4095,34 +4303,34 @@
 ⚠️ Prazos: A confirmar em texto completo do Capítulo II</t>
         </is>
       </c>
-      <c r="N34" s="11" t="inlineStr">
+      <c r="N35" s="11" t="inlineStr">
         <is>
           <t>ANNEX II (Identification and Registration) estabelece quatro requisitos técnicos de transponders: (i) número individual não-repetível; (ii) ISO 3166 (país); (iii) ISO 11784/11785 (radiofrequência); (iv) ISO 24631-1 (avaliação). Código do Animal implementa ISO 11784 mas não ISO 11785 ou 24631-1 (menos restritivo). @RGBEAC promove SIAC (mais robusto) mas não especifica ISO standards. Recomenda-se: validar conformidade portuguesa com ISO 11785 e 24631-1 (inovações do Regulamento).</t>
         </is>
       </c>
-      <c r="O34" s="11" t="inlineStr">
+      <c r="O35" s="11" t="inlineStr">
         <is>
           <t>Sim - Clarificação técnica (ISO 11785, 24631-1) + harmonização prazos</t>
         </is>
       </c>
-      <c r="P34" s="11" t="inlineStr">
+      <c r="P35" s="11" t="inlineStr">
         <is>
           <t>ANNEX II especifica requisitos TÉCNICOS de transponders/microchips (não procedimentos administrativos). IMPORTANTE DIVERGÊNCIA: Código do Animal exige ISO 11784; Regulamento exige ISO 11784/11785 + 24631-1. ISO 11785: estabelece padrão de radiofrequência para microchips. ISO 24631-1: metodologia de avaliação de conformidade. Ambas são NOVIDADES do Regulamento não presentes na legislação portuguesa anterior. @RGBEAC menciona SIAC (Sistema de Informação) mas não detalha requisitos técnicos ISO. Recomenda-se: (i) validar conformidade microchips portugueses com ISO 11785 e 24631-1; (ii) atualizar requisitos de aprovação/certificação de equipamentos; (iii) harmonizar prazos de identificação (3 meses vs. 30 dias por tipo operador).</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="120" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36" ht="120" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Recolha de Dados sobre Bem-Estar Animal — Relatório Trienal à Comissão UE</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>ANEXO III do Regulamento 2023/0447 (conforme Article 20)</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>1. Number of dogs and cats registered per year, as referred to in Article 17 and Article 21(4).
 1a. Number of breeding establishments, selling establishments, shelters, and foster homes registered per year in accordance with Article 7.
@@ -4130,7 +4338,7 @@
 2a. Number of breeding establishments whose approval has been suspended or withdrawn per year.</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>1. Número de cães e gatos registados por ano, conforme referido nos artigos 17.º e 21.º, n.º 4.
 1a. Número de estabelecimentos de criação, estabelecimentos de venda, abrigos e famílias de acolhimento registados por ano, em conformidade com o artigo 7.º.
@@ -4138,12 +4346,12 @@
 2a. Número de estabelecimentos de criação cuja aprovação foi suspensa ou revogada por ano.</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>RGBEAC (Regime Geral do Bem-Estar dos Animais de Companhia, proposta jun. 2025) — Arts. 20.º, 46.º</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>Artigo 20.º — Sistema de Informação de Animais de Companhia (SIAC)
 1 - O SIAC reúne informação relativa à: a) Rastreabilidade de dispositivos de identificação; b) Identificação dos animais de companhia; c) Sua titularidade ou detenção; d) Informação de saúde pública, saúde animal e bem-estar animal.
@@ -4155,12 +4363,12 @@
 2 – A DGAV consolida informação a nível nacional sobre bem-estar animal em cada ano, incluindo: a) Acompanhamento da política internacional; b) Prestação de apoios públicos; c) Atividade do SIAC; d) Resultados de planos de controlo; e) Processos contraordenacionais; f) Coimas e sanções; g) Atividade de centros de bem-estar animal; h) Programas de interesse nacional.</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>Código do Animal (DL 214/2013) — Arts. 55.º, 56.º, 141.º-145.º</t>
         </is>
       </c>
-      <c r="H35" s="6" t="inlineStr">
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>Artigo 55.º — Base de dados
 1 - Toda informação de registo coligida numa aplicação informática nacional.
@@ -4172,12 +4380,12 @@
 Código do Animal estabelece estrutura de: a) Monitorização de bem-estar animal; b) Recolha de dados de infrações; c) Aplicação de sanções; d) Atividades de centros de recolha; e) Estatísticas de animais processados; f) Sistema de contraordenações.</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>DL 82/2019 (Arts. 2.º-7.º), Lei 27/2016 (Arts. 1.º-9.º)</t>
         </is>
       </c>
-      <c r="J35" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>[dim]Decreto-Lei n.º 82/2019 de 27 de junho — Bem-Estar de Animais de Companhia
 Artigo 2.º — Âmbito de aplicação — Aplicável a cães, gatos e furões detidos para fins não comerciais.
@@ -4192,7 +4400,7 @@
 Artigos 3.º-9.º — Estrutura e Funcionamento — Procedimentos de registo, aprovação, funcionamento e supervisão.</t>
         </is>
       </c>
-      <c r="K35" s="8" t="inlineStr">
+      <c r="K36" s="8" t="inlineStr">
         <is>
           <t>ANÁLISE POR PONTO:
 PONTO 1 (Cães/gatos registados): ✅ CONFORMIDADE COMPLETA
@@ -4205,7 +4413,7 @@
 DL 82/2019 e Lei 27/2016 NÃO mencionam procedimentos de suspensão ou revogação de aprovação de estabelecimentos.</t>
         </is>
       </c>
-      <c r="L35" s="9" t="inlineStr">
+      <c r="L36" s="9" t="inlineStr">
         <is>
           <t>ANÁLISE POR PONTO:
 PONTO 1: ✅ CONFORMIDADE COMPLETA
@@ -4218,7 +4426,7 @@
 Código do Animal não menciona suspensão/revogação de aprovação.</t>
         </is>
       </c>
-      <c r="M35" s="10" t="inlineStr">
+      <c r="M36" s="10" t="inlineStr">
         <is>
           <t>ANÁLISE POR PONTO:
 PONTO 1: ✅ CONFORMIDADE COMPLETA
@@ -4231,7 +4439,7 @@
 RGBEAC não menciona suspensão/revogação de aprovação.</t>
         </is>
       </c>
-      <c r="N35" s="11" t="inlineStr">
+      <c r="N36" s="11" t="inlineStr">
         <is>
           <t>CONCLUSÃO GERAL:
 Legislação portuguesa implementa PARCIALMENTE os 4 pontos de Annex III (dados para relatório trienal à Comissão UE):
@@ -4246,12 +4454,12 @@
 4. Integrar dados coletados em relatório trienal da Comissão UE (conforme Art. 20 do Regulamento).</t>
         </is>
       </c>
-      <c r="O35" s="11" t="inlineStr">
+      <c r="O36" s="11" t="inlineStr">
         <is>
           <t>Sim — Estabelecer sistema de aprovação, suspensão e revogação de estabelecimentos de criação + codificar famílias de acolhimento</t>
         </is>
       </c>
-      <c r="P35" s="11" t="inlineStr">
+      <c r="P36" s="11" t="inlineStr">
         <is>
           <t>ANNEX III define dados OBRIGATÓRIOS para relatório trienal à Comissão UE (Art. 20 do Regulamento). SIAC português fornece dados para ponto 1 (cães/gatos registados) — sistema operacional desde 2019. Pontos 2 e 2a requerem regulação complementar urgente: aprovação formal de criadores (vs. apenas registo) + procedimentos de suspensão/revogação. Ponto 1a (estabelecimentos) — codificação explícita de "famílias de acolhimento" como categoria administrativa. Recomenda-se: Lei complementar ou Portaria reguladora para implementação completa dos 4 pontos antes do próximo período de reporte (trienal).</t>
         </is>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -870,13 +870,13 @@
       <c r="D4" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores são responsáveis pelo bem-estar dos cães ou gatos mantidos nos estabelecimentos sob a sua responsabilidade e controlo e devem minimizar quaisquer riscos para o seu bem-estar.
-1a. No caso de famílias de acolhimento, a responsabilidade recai sobre o operador em nome de quem os cães ou gatos são mantidos. Esses operadores não devem colocar mais do que um total de cinco cães ou gatos ou uma ninhada com ou sem mãe numa família de acolhimento em qualquer momento e devem fornecer à família de acolhimento informação adequada sobre as obrigações de bem-estar animal, bem como as necessidades individuais dos animais, e devem assegurar que as obrigações relevantes estabelecidas por este Regulamento são cumpridas em famílias de acolhimento. Os Estados-Membros onde a família de acolhimento está localizada podem prever um número maior de cães, gatos ou ninhadas a serem colocadas na família de acolhimento, desde que as instalações da família de acolhimento providenciem espaço suficiente, incluindo espaço ao ar livre, e que o número de cuidadores de animais na família de acolhimento seja suficiente, para assegurar o bem-estar dos cães ou gatos.
-1b. Os operadores não devem sujeitar nenhum cão ou gato a crueldade, abuso ou maus-tratos, incluindo através de participação em atividades que possam resultar em crueldade, abuso ou maus-tratos, aos cães ou gatos criados ou mantidos pelo operador.
-1c. Os operadores não devem abandonar cães ou gatos.
-1d. Os operadores que estejam prestes a cessar as atividades do seu estabelecimento devem assegurar a reintegração dos cães ou gatos mantidos aí, quer através da assunção da posse do animal de companhia, quer através da transferência da responsabilidade ou propriedade dos cães e gatos para outros operadores ou adquirentes.
-2. Os operadores devem assegurar que os cães ou gatos são tratados por um número adequado de cuidadores de animais e de modo a satisfazer as necessidades de bem-estar dos cães ou gatos mantidos nos seus estabelecimentos e que têm as competências exigidas no artigo 12.º.
-2a. Os operadores devem assegurar o bem-estar dos cães ou gatos sob a sua responsabilidade através da monitorização de indicadores baseados no comportamento e aparência física, e através da adoção de ações com base nos resultados de tal monitorização.
-2b. A Comissão tem competência para adotar atos delegados em conformidade com o artigo 28.º que complementem este Regulamento através do estabelecimento de indicadores baseados no bem-estar dos animais relativos ao comportamento e aparência física e dos métodos da sua medição.</t>
+2.	No caso de famílias de acolhimento, a responsabilidade recai sobre o operador em nome de quem os cães ou gatos são mantidos. Esses operadores não devem colocar mais do que um total de cinco cães ou gatos ou uma ninhada com ou sem mãe numa família de acolhimento em qualquer momento e devem fornecer à família de acolhimento informação adequada sobre as obrigações de bem-estar animal, bem como as necessidades individuais dos animais, e devem assegurar que as obrigações relevantes estabelecidas por este Regulamento são cumpridas em famílias de acolhimento. Os Estados-Membros onde a família de acolhimento está localizada podem prever um número maior de cães, gatos ou ninhadas a serem colocadas na família de acolhimento, desde que as instalações da família de acolhimento providenciem espaço suficiente, incluindo espaço ao ar livre, e que o número de cuidadores de animais na família de acolhimento seja suficiente, para assegurar o bem-estar dos cães ou gatos.
+3.	Os operadores não devem sujeitar nenhum cão ou gato a crueldade, abuso ou maus-tratos, incluindo através de participação em atividades que possam resultar em crueldade, abuso ou maus-tratos, aos cães ou gatos criados ou mantidos pelo operador.
+4.	Os operadores não devem abandonar cães ou gatos.
+5.	Os operadores que estejam prestes a cessar as atividades do seu estabelecimento devem assegurar a reintegração dos cães ou gatos mantidos aí, quer através da assunção da posse do animal de companhia, quer através da transferência da responsabilidade ou propriedade dos cães e gatos para outros operadores ou adquirentes.
+6.	Os operadores devem assegurar que os cães ou gatos são tratados por um número adequado de cuidadores de animais e de modo a satisfazer as necessidades de bem-estar dos cães ou gatos mantidos nos seus estabelecimentos e que têm as competências exigidas no artigo 12.º.
+7.	Os operadores devem assegurar o bem-estar dos cães ou gatos sob a sua responsabilidade através da monitorização de indicadores baseados no comportamento e aparência física, e através da adoção de ações com base nos resultados de tal monitorização.
+8.	A Comissão tem competência para adotar atos delegados em conformidade com o artigo 28.º que complementem este Regulamento através do estabelecimento de indicadores baseados no bem-estar dos animais relativos ao comportamento e aparência física e dos métodos da sua medição.</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -1075,13 +1075,18 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Os operadores devem notificar as autoridades competentes da sua atividade, fornecendo pelo menos as seguintes informações:
-(a) nome, morada e contactos do operador;
-(b) a(s) localização(ões) do(s) estabelecimento(s);
-(c) o tipo de estabelecimento: criação, venda, abrigo ou família de acolhimento;
-(d) as espécies e, para os estabelecimentos de criação, as raças dos cães ou gatos mantidos;
-(e) a capacidade do estabelecimento, expressa no número máximo de cães e gatos que podem ser alojados;
-(ea) para os estabelecimentos de criação, o número estimado de ninhadas a colocar no mercado por ano.</t>
+          <t>1.	Os operadores devem notificar as autoridades competentes da sua atividade, fornecendo pelo menos as seguintes informações para cada um dos seus estabelecimentos:
+(a)	o nome, morada e contactos do operador;
+(b)	a localização do estabelecimento;
+(c)	o tipo de estabelecimento: estabelecimento de criação, estabelecimento de venda, abrigo ou família de acolhimento;
+(d)	as espécies e, para os estabelecimentos de criação, as raças dos cães ou gatos mantidos no estabelecimento;
+(e)	a capacidade do estabelecimento, expressa no número máximo de cães e gatos que podem ser alojados no estabelecimento;
+(f)	para os estabelecimentos de criação, o número estimado de ninhadas a colocar no mercado por ano.
+2.	Os operadores devem notificar a autoridade competente de:
+(a)	quaisquer alterações relativas às informações referidas no n.º 1;
+(b)	quando aplicável, a data prevista de cessação das suas atividades, o mais tardar cinco dias úteis antes dessa data.
+3.	Os Estados-Membros devem utilizar as informações fornecidas em conformidade com o artigo 84.º do Regulamento (UE) 2016/429. Os operadores não são obrigados a notificar novamente as informações já apresentadas em conformidade com o artigo 84.º do Regulamento (UE) 2016/429.
+4.	A autoridade competente deve manter um registo dos estabelecimentos. A autoridade competente pode utilizar para esse efeito o registo previsto no artigo 101.º, n.º 1, alínea a), do Regulamento (UE) 2016/429.</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1275,11 +1280,11 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Os operadores devem fornecer ao adquirente de um cão ou gato informação escrita necessária para lhe permitir assegurar o bem-estar do cão ou gato, incluindo informação sobre detenção responsável e sobre as necessidades específicas do cão ou gato em termos de alimentação, cuidados, saúde, alojamento e necessidades comportamentais, bem como informação sobre a sua saúde.
-1a. A informação escrita sobre a saúde do cão ou gato referida no parágrafo anterior deve incluir pelo menos:
-(a) o estado de vacinação do cão ou gato;
-(b) quaisquer condições médicas ou predisposições a doenças, incluindo alergias, conhecidas pelo operador, e quaisquer resultados de testes de diagnóstico para o cão ou gato que estejam disponíveis para o operador.
-Caso a informação sobre a saúde do cão ou gato esteja documentada num documento exigido sob o Regulamento (UE) 2016/429, o operador deve transmitir esse documento ao adquirente.</t>
+          <t>1.	Os operadores devem fornecer ao adquirente de um cão ou gato informação escrita necessária para lhe permitir assegurar o bem-estar do cão ou gato, incluindo informação sobre detenção responsável e sobre as necessidades específicas do cão ou gato em termos de alimentação, cuidados, saúde e alojamento, bem como informação sobre as suas necessidades comportamentais e historial de saúde.
+2.	A informação escrita sobre o historial de saúde do cão ou gato referida no n.º 1 deve incluir pelo menos:
+(a)	o estado de vacinação do cão ou gato;
+(b)	quaisquer condições médicas ou predisposições a doenças, incluindo alergias, conhecidas pelo operador, e quaisquer resultados de testes de diagnóstico para o cão ou gato que estejam disponíveis para o operador.
+Caso a informação sobre o historial de saúde do cão ou gato esteja prevista num documento exigido nos termos do Regulamento (UE) 2016/429, o operador deve transmitir esse documento ao adquirente.</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1381,8 +1386,8 @@
 (c) capacidade de aplicar boas práticas de maneio de animais, incluindo condicionamento operante e reforço positivo, utilizar e manter o equipamento utilizado para os cães ou gatos sob os seus cuidados e minimizar quaisquer riscos para o bem-estar dos cães ou gatos, prevenindo sofrimento;
 (d) conhecimento das suas obrigações sob este Regulamento.
 2. As competências referidas no parágrafo 1 podem ser adquiridas através de educação, formação ou experiência profissional. A educação, formação ou experiência profissional devem ser documentadas.
-2a. Os operadores devem assegurar que pelo menos um cuidador de animais, que não seja um voluntário ou estagiário, no estabelecimento tenha completado os cursos de formação referidos no artigo 18.º e que o cuidador transfira os conhecimentos aos outros cuidadores de animais do estabelecimento.
-3. A Comissão estabelecerá, por meio de atos de execução, os requisitos mínimos relativos à educação formal, formação ou experiência profissional para adquirir as competências referidas no parágrafo 2 e para os cursos de formação referidos no parágrafo 2a. Esses atos de execução serão adotados de acordo com o procedimento de exame referido no artigo 24.º. O ato de execução relativo aos cursos de formação referidos no parágrafo 2a deve ser adotado por [3 anos da data de entrada em vigor do Regulamento].</t>
+3.	Os operadores devem assegurar que pelo menos um cuidador de animais, que não seja um voluntário ou estagiário, no estabelecimento tenha completado os cursos de formação referidos no artigo 22.º e que o cuidador transfira os conhecimentos aos outros cuidadores de animais do estabelecimento.
+4.	A Comissão estabelecerá, por meio de atos de execução, os requisitos mínimos relativos à educação formal, formação ou experiência profissional para adquirir as competências referidas no parágrafo 2 e para os cursos de formação referidos no n.º 3. Esses atos de execução serão adotados de acordo com o procedimento de exame referido no artigo 29.º. O ato de execução relativo aos cursos de formação referidos no n.º 3 deve ser adotado por [3 anos da data de entrada em vigor do Regulamento].</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1591,7 +1596,7 @@
 b) minimizar derramamentos e evitar a contaminação do alimento e da água com contaminantes físicos, químicos ou biológicos prejudiciais;
 c) evitar ferimentos, afogamento ou outro dano aos cães ou gatos;
 d) ser facilmente limpas e desinfetadas para evitar a propagação de doenças.
-3a. Quando aconselhado por escrito por um médico veterinário, os operadores podem ajustar as frequências de alimentação e hidratação para um cão ou gato individual. Os operadores devem manter um registo do conselho durante toda a sua duração, conforme aconselhado pelo médico veterinário.</t>
+4.	Quando aconselhado por escrito por um médico veterinário, os operadores podem ajustar as frequências de alimentação e hidratação para um cão ou gato individual. Os operadores devem manter um registo do conselho durante toda a sua duração, conforme aconselhado pelo médico veterinário.</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1702,20 +1707,20 @@
 2. Os operadores devem assegurar que:
 a) os estabelecimentos onde os cães ou gatos são mantidos e o equipamento utilizado são adequados aos tipos e número de cães ou gatos, e permitem o acesso necessário e inspeção minuciosa de todos os cães ou gatos;
 b) todos os componentes de construção do estabelecimento, incluindo o pavimento, telhado e divisões de espaço, bem como o equipamento utilizado para cães ou gatos, são construídos e mantidos adequadamente, para assegurar que não apresentam riscos ao bem-estar dos cães ou gatos.
-(ba) todos os componentes de construção do estabelecimento, incluindo o pavimento e divisões de espaço, bem como o equipamento utilizado para cães ou gatos, são mantidos limpos para assegurar que não apresentam riscos ao bem-estar dos cães ou gatos;
-c) em estabelecimentos de criação e venda onde os cães ou gatos são mantidos no interior, pó, temperatura, humidade relativa do ar e concentrações de gases não são prejudiciais aos cães ou gatos e a ventilação é suficiente para evitar sobreaquecimento;
-d) os cães e gatos têm espaço suficiente para se moverem livremente e expressar comportamento específico da espécie de acordo com as suas necessidades com possibilidade de se retirarem e descansarem;
-(da) os cães ou gatos têm lugares de repouso limpos, confortáveis e secos, suficientemente grandes e numerosos para assegurar que todos podem deitar-se e descansar ao mesmo tempo numa posição natural;
-e) estruturas e medidas apropriadas estão em vigor para cães ou gatos mantidos no exterior para os proteger de condições climáticas adversas, incluindo para evitar stress térmico, queimaduras solares e frieiras.
+c)	todos os componentes de construção do estabelecimento, incluindo o pavimento e divisões de espaço, bem como o equipamento utilizado para cães ou gatos, são mantidos limpos para assegurar que não apresentam riscos ao bem-estar dos cães ou gatos;
+d)	em estabelecimentos de criação e venda onde os cães ou gatos são mantidos no interior, pó, temperatura, humidade relativa do ar e concentrações de gases não são prejudiciais aos cães ou gatos e a ventilação é suficiente para evitar sobreaquecimento;
+e)	os cães e gatos têm espaço suficiente para se moverem livremente e expressar comportamento específico da espécie de acordo com as suas necessidades com possibilidade de se retirarem e descansarem;
+f)	os cães ou gatos têm lugares de repouso limpos, confortáveis e secos, suficientemente grandes e numerosos para assegurar que todos podem deitar-se e descansar ao mesmo tempo numa posição natural;
+g)	estrututras e medidas apropriadas estão em vigor para cães ou gatos mantidos no exterior para os proteger de condições climáticas adversas, incluindo para evitar stress térmico, queimaduras solares e frieiras.
 3. Os operadores não devem manter cães ou gatos em contentores.
 A título de derrogação, contentores podem ser usados apenas para transporte, isolamento a curto prazo de cães ou gatos individuais e durante participação em espetáculos, exposições e competições, para cachorros ou gatinhos com capacidade termorreguladora reduzida ou cachorros ou gatinhos juntamente com as suas mães, desde que o stress seja minimizado e o sofrimento seja evitado e os cães e gatos sejam capazes de se manter em pé e deitar-se numa posição natural.
 4. Os operadores não devem manter cães com mais de 8 semanas exclusivamente no interior. Tais cães devem ter acesso diário a uma área ao ar livre, ou ser passeados diariamente, para permitir exercício, exploração e socialização. A duração do acesso diário a uma área ao ar livre ou passeio deve ser mínimo uma hora no total. O operador pode apenas derrogar destes requisitos com base em aconselhamento escrito de um médico veterinário.
 5. Quando gatos são mantidos em gatarias, os operadores devem desenhar e construir compartimentos individuais para permitir aos gatos mover-se livremente e expressar o seu comportamento natural.
 6. Os operadores de estabelecimentos de criação e venda devem assegurar que em áreas interiores onde os cães ou gatos são mantidos, uma zona termoneural apropriada é mantida levando em conta o seu tipo de pelagem, idade, tamanho, raça e saúde.
-6a. Os operadores de estabelecimentos de criação e venda devem usar, quando necessário, sistemas de aquecimento ou arrefecimento para manter boa qualidade do ar, uma temperatura apropriada em compartimentos interiores nos seus estabelecimentos, e remover humidade excessiva.
-7. Os operadores devem assegurar que os cães ou gatos são expostos à luz, e são capazes de permanecer no escuro por períodos suficientes e ininterruptos para manter um ritmo circadiano normal.
+7.	Os operadores de estabelecimentos de criação e venda devem usar, quando necessário, sistemas de aquecimento ou arrefecimento para manter boa qualidade do ar, uma temperatura apropriada em compartimentos interiores nos seus estabelecimentos, e remover humidade excessiva.
+8.	Os operadores devem assegurar que os cães ou gatos são expostos à luz, e são capazes de permanecer no escuro por períodos suficientes e ininterruptos para manter um ritmo circadiano normal.
 Para efeitos do primeiro parágrafo, 'luz' significa luz natural, complementada, quando necessário, devido às condições climáticas e posição geográfica de um Estado-Membro, por luz artificial.
-7a. Os parágrafos 2(a), (b), (ba) (da) (e), 6, 6a e 7 não se aplicam a cães guardiões de gado, nem a cães de pastoreio, durante os períodos em que tais cães são utilizados para guarda ou pastoreio no contexto de transumância sazonal a pé.</t>
+9.	Os n.ºs 2(a), (b), (c), (f) e (g), 6, 7 e 8 não se aplicam a cães guardiões de gado, nem a cães de pastoreio, durante os períodos em que tais cães são utilizados para guarda ou pastoreio no contexto de transumância sazonal a pé. O n.º 2(f) não se aplica a cães guardiões de gado durante os períodos em que tais cães são utilizados para fins de treino.</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1953,11 +1958,11 @@
 d) procedimentos de higiene, higiénicos, de saúde ou reprodutivos que não sejam acasalamento;
 e) tratamento médico, incluindo tratamento cirúrgico ou reabilitação prescrita.
 3. O amarrar por mais de 1 hora é proibido, exceto durante a duração de um tratamento médico ou participação em espetáculos, exposições e competições de cães e gatos.
-3a. Os Estados-Membros podem conceder derrogações do parágrafo 3 para cães destinados a uso em serviços militares, policiais e aduaneiros que são mantidos em estabelecimentos de criação ou venda.
-4. Os operadores devem assegurar que condições estão em vigor para permitir aos cães ou gatos expressar comportamentos sociais não prejudiciais, comportamentos específicos da espécie e a possibilidade de experimentar emoções positivas.
-5. Os operadores devem assegurar que os cães ou gatos podem socializar em conformidade com o ponto 4 do Anexo I. Os operadores de estabelecimentos de criação devem documentar a sua estratégia para tal socialização.
-5a. O primeiro parágrafo não se aplica a cães guardiões de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para guarda ou treino, nem a cães de pastoreio durante transumância sazonal.
-6. Os operadores devem assegurar que enriquecimento é fornecido e acessível a todos os cães ou gatos, criando um ambiente estimulante, permitindo comportamento específico da espécie e reduzindo a sua frustração.</t>
+4.	Os Estados-Membros podem conceder derrogações do n.º 3 para cães destinados a uso em serviços militares, policiais e aduaneiros que são mantidos em estabelecimentos de criação ou venda.
+5.	Os operadores devem assegurar que condições estão em vigor para permitir aos cães ou gatos expressar comportamentos sociais não prejudiciais, comportamentos específicos da espécie e a possibilidade de experimentar emoções positivas.
+6.	Os operadores devem assegurar que os cães ou gatos podem socializar em conformidade com o ponto 4 do Anexo I. Os operadores de estabelecimentos de criação devem ter uma estratégia documentada para tal socialização.
+	A título de derrogação do primeiro parágrafo, os requisitos de socialização não se aplicam a cães guardiões de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para guarda ou treino, nem a cães de pastoreio durante transumância sazonal.
+7.	Os operadores devem assegurar que enriquecimento é fornecido e acessível a todos os cães ou gatos, criando um ambiente estimulante, permitindo comportamento específico da espécie e reduzindo a sua frustração.</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2059,18 +2064,18 @@
       <c r="D15" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores devem assegurar que mutilações, incluindo corte de orelhas, corte de cauda, remoção de garras ou amputação parcial ou completa de dígitos, e ressecção de cordas vocais ou pregas, não são realizadas a menos que por indicação médica, que pode incluir profilática, com o único propósito de preservar, melhorar a saúde de cães ou gatos ou prevenir ferimentos. Nesse caso, o procedimento deve ser realizado apenas sob anestesia e analgesia prolongada e por um médico veterinário.
-1a. A indicação médica para a mutilação e os detalhes do procedimento realizado devem ser documentados por um médico veterinário. Este documento deve ser retido pelo operador até que o cão ou gato, juntamente com este documento, seja transferido para outro estabelecimento ou proprietário. O operador do estabelecimento onde a mutilação foi realizada deve reter uma cópia do documento durante três anos após a transferência do cão ou gato.
-1b. A título de derrogação do parágrafo 1, os Estados-Membros podem permitir o corte de orelhas por entalhe ou ponta das orelhas de gatos no contexto de marcação de gatos vadios quando esterilizados sob um programa de captura-esterilização-libertação.
-2. Os operadores devem assegurar que a esterilização é realizada apenas sob anestesia e analgesia prolongada e por um médico veterinário. A título de derrogação, os Estados-Membros podem permitir que a esterilização de gatos machos seja realizada por um enfermeiro veterinário licenciado.
-3. Os operadores devem assegurar que práticas de manipulação que causam dor ou sofrimento não são realizadas, incluindo:
-a) amarrar partes do corpo a menos que por razões médicas em cujo caso a duração deve ser limitada ao período mínimo necessário;
-b) chutar, bater, arrastar, atirar, apertar cães ou gatos;
-c) aplicar corrente elétrica a cães ou gatos a menos que realizado por razões médicas;
-d) uso de focinheiras, a menos que necessário por razões médicas, segurança animal ou humana, em cujo caso a duração deve ser limitada ao período mínimo necessário e o cão ou gato deve ser supervisionado.
-(da) uso de colares de espinhos;
-(db) uso de colares de estrangulamento sem paragem de segurança;
-e) levantar cães ou gatos pelas extremidades, cabeça, orelhas, cauda ou pêlo, ou levantar cães ou gatos adultos pela pele.
-4. Os Estados-Membros podem conceder derrogações do parágrafo 3 para cães destinados a uso em serviços militares, policiais ou aduaneiros.</t>
+2.	A indicação médica para a mutilação e os detalhes do procedimento realizado devem ser documentados por um médico veterinário. Este documento deve ser retido pelo operador até que o cão ou gato, juntamente com este documento, seja transferido para outro estabelecimento ou proprietário. O operador do estabelecimento onde a mutilação foi realizada deve reter uma cópia do documento durante três anos após a transferência do cão ou gato.
+3.	A título de derrogação do parágrafo 1, os Estados-Membros podem permitir o corte de orelhas por entalhe ou ponta das orelhas de gatos no contexto de marcação de gatos vadios quando esterilizados sob um programa de captura-esterilização-libertação.
+4.	Os operadores devem assegurar que a esterilização é realizada apenas sob anestesia e analgesia prolongada e por um médico veterinário. A título de derrogação, os Estados-Membros podem permitir que a esterilização de gatos machos seja realizada por um enfermeiro veterinário licenciado.
+5.	Os operadores devem assegurar que práticas de manipulação que causam dor ou sofrimento não são realizadas, incluindo:
+a)	amarrar partes do corpo a menos que por razões médicas em cujo caso a duração deve ser limitada ao período mínimo necessário;
+b)	chutar, bater, arrastar, atirar, apertar cães ou gatos;
+c)	aplicar corrente elétrica a cães ou gatos a menos que realizado por razões médicas;
+d)	uso de focinheiras, a menos que necessário por razões médicas, segurança animal ou humana, em cujo caso a duração deve ser limitada ao período mínimo necessário e o cão ou gato deve ser supervisionado.
+e)	uso de colares de espinhos;
+f)	uso de colares de estrangulamento sem paragem de segurança;
+g)	levantar cães ou gatos pelas extremidades, cabeça, orelhas, cauda ou pêlo, ou levantar cães ou gatos adultos pela pele.
+	Os Estados-Membros podem conceder derrogações do primeiro parágrafo para cães destinados a uso em serviços militares, policiais ou aduaneiros.</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2267,18 +2272,21 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>1. Todos os cães e gatos mantidos em estabelecimentos colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com o Anexo II.
-1a. Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de 3 meses após o nascimento e, em qualquer caso, antes da data da sua colocação no mercado.
-Os operadores de estabelecimentos de venda, abrigos e os que colocam e são responsáveis por cães e gatos em famílias de acolhimento devem assegurar que os cães e gatos que entrem nos seus estabelecimentos sejam identificados individualmente no prazo de 30 dias após a chegada.
-Os donos de animais de companhia e quaisquer outras pessoas singulares ou coletivas que detenham cães ou gatos devem assegurar que os animais sejam identificados individualmente o mais tardar quando o animal atingir os 3 meses de idade ou, no caso de o animal ser colocado no mercado, antes da data da sua colocação no mercado.
-2. A implantação do transponder devem ser efetuada por um médico veterinário. Os Estados-Membros podem permitir que a implantação de transponders em gatos seja efetuada por pessoa que não seja médico veterinário, se for feita sob a responsabilidade de um médico veterinário.
-3. Cães e gatos que tenham sido identificados individualmente por meio de um transponder injetável contendo um microchip, em conformidade com legislação nacional anterior à entrada em vigor do presente Regulamento, são reconhecidos como identificados de acordo com os requisitos do presente artigo.
-4. No prazo de dois dias úteis após a sua identificação, os cães e gatos devem ser registados por um médico veterinário numa base de dados nacional.
-5. Para cães e gatos mantidos em estabelecimentos, o registo deve ser efetuado em nome do operador do estabelecimento. Para cães e gatos colocados em famílias de acolhimento, o registo deve ser efetuado em nome da pessoa responsável pela família de acolhimento. Para cães e gatos detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva, o registo deve ser efetuado em nome do dono ou da pessoa singular ou coletiva.
-Os Estados-Membros podem conceder derrogações ao primeiro parágrafo a cães militares, policiais e aduaneiros.
-6. Em caso de colocação no mercado ou cedência ocasional e irregular por pessoa singular sem publicidade em linha, os requisitos de registo não se aplicam.
-7. Em caso de morte de um cão ou gato, o operador, dono do animal ou pessoa singular ou coletiva proprietária devem informar a base de dados nacional.
-8. Em caso de transponder ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato devem assegurar que o animal é reidentificado com um novo transponder e re-registado na base de dados nacional.</t>
+          <t>1.	Todos os cães e gatos mantidos em estabelecimentos, colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva, devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com os requisitos estabelecidos no Anexo II.
+2.	Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de três meses após o nascimento e, em qualquer caso, antes da data da sua colocação no mercado.
+Os operadores de estabelecimentos de venda e abrigos, e os operadores que colocam e são responsáveis por cães e gatos em famílias de acolhimento, devem assegurar que os cães e gatos que entrem nos seus estabelecimentos ou fiquem sob a sua responsabilidade sejam identificados individualmente no prazo de 30 dias após a chegada e, em qualquer caso, antes da data da sua colocação no mercado.
+Os donos de animais de companhia e quaisquer outras pessoas singulares ou coletivas que não sejam operadores e que sejam proprietários de cães ou gatos devem assegurar que cada cão ou gato seja identificado individualmente o mais tardar quando o animal atingir a idade de três meses ou, caso o cão ou gato seja colocado no mercado, antes da data dessa colocação no mercado.
+A implantação do transponder deve ser efetuada por um médico veterinário. Os Estados-Membros podem permitir que a implantação de transponders seja efetuada por pessoas que não sejam médicos veterinários, desde que adotem regras nacionais que estabeleçam as qualificações mínimas que essas pessoas devem ter.
+Caso os cães e gatos tenham sido identificados individualmente por meio de um transponder injetável contendo um microchip em conformidade com o direito da União ou nacional antes de … [data dois anos após a data de entrada em vigor do presente Regulamento], considera-se que cumprem os requisitos do n.º 1 e do primeiro, segundo, terceiro e quarto parágrafos do presente número, desde que o microchip seja ainda legível.
+3.	No prazo de dois dias úteis após a sua identificação, os cães e gatos devem ser registados por um médico veterinário numa base de dados nacional referida no artigo 23.º. Os Estados-Membros podem permitir o registo por pessoas que não sejam médicos veterinários, desde que os Estados-Membros disponham de medidas para assegurar a exatidão das informações que essas pessoas introduzem na base de dados. No caso de cães e gatos mantidos em estabelecimentos, o registo deve ser efetuado em nome do operador do estabelecimento responsável pelo cão ou gato. No caso de cães e gatos detidos por quaisquer outras pessoas singulares ou coletivas, o registo deve ser efetuado em nome dessas pessoas.
+Os Estados-Membros podem conceder derrogações ao primeiro parágrafo do presente número relativamente a cães militares, policiais e aduaneiros.
+4.	Em caso de colocação no mercado ou cedência ocasional por pessoas singulares sem recorrer a publicidade em linha, a pessoa singular ou coletiva que transfere a propriedade ou a responsabilidade pelo cão ou gato deve assegurar que a mudança de propriedade ou de responsabilidade pelo cão ou gato é registada na base de dados referida no artigo 23.º, no prazo de duas semanas a contar da data dessa transferência, em conformidade com as condições estabelecidas pelo Estado-Membro responsável por essa base de dados.
+5.	Em caso de morte de um cão ou gato, o operador, o dono do animal de companhia ou a pessoa singular ou coletiva proprietária do cão ou gato deve assegurar que a morte é registada na base de dados referida no artigo 23.º, em conformidade com as condições estabelecidas pelo Estado-Membro responsável por essa base de dados.
+6.	Caso um transponder seja ou fique ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato deve assegurar que um novo transponder é injetado e que o registo na base de dados é atualizado com o número de identificação desse novo transponder.
+7.	Os requisitos de identificação e registo do presente artigo são aplicáveis:
+(a)	aos operadores e às pessoas singulares ou coletivas que colocam cães e gatos no mercado, a partir de … [4 anos após a entrada em vigor do presente Regulamento];
+(b)	aos donos de animais de companhia e outras pessoas singulares ou coletivas que não sejam operadores e que não coloquem cães no mercado, a partir de … [10 anos após a entrada em vigor do presente Regulamento];
+(c)	aos donos de animais de companhia e outras pessoas singulares ou coletivas que não sejam operadores e que não coloquem gatos no mercado, a partir de … [15 anos após a entrada em vigor do presente Regulamento].</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2384,23 +2392,37 @@
 -	the technical, electronic and cryptographic requirements for the system;
 -	the procedural steps to be followed, and the information to be provided,  by the natural or legal person placing the dog or cat on the market, and the steps and information required of the acquirer, in order for the online verification system to work.
 The implementing acts referred to in point (a) shall be adopted by ... [two years after the date of entry into force of this Regulation] and the implementing act referred to in points (b) and (c) shall be adopted by ... [three years from date of entry into force of this Regulation]
-Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 29.
-CHAPTER IV
-COMPETENT AUTHORITIES</t>
+Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 29.</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>1. Quando operadores anunciem online um cão ou gato com vista ao seu colocamento no mercado da União, devem assegurar a apresentação do seguinte aviso no anúncio em caracteres claramente visíveis e em negrito:
-"Um animal não é um brinquedo. Ter um é uma decisão que muda a vida. É seu dever assegurar a sua saúde e bem-estar e não o abandonar."
-2. Quando pessoas singulares ou coletivas que não sejam operadores anunciem online um cão ou gato com vista ao seu colocamento no mercado da União, devem assegurar a apresentação de um aviso sobre detenção responsável utilizando a redação referida no primeiro parágrafo ou uma redação diferente com significado equivalente.
-3. Ao colocar um cão ou gato no mercado na União, a pessoa singular ou coletiva que coloca o cão ou gato no mercado deve:
-a) Fornecer ao adquirente prova de identificação e registo do cão ou gato em conformidade com o artigo 20.º;
-b) Fornecer ao adquirente as seguintes informações sobre o cão ou gato: espécie, sexo, data e país de nascimento, e, quando relevante, raça;
-c) No caso de anúncio online, utilizar o sistema referido no parágrafo 6 para gerar um token único de verificação e disponibilizar o token e a ligação web para o sistema referido no parágrafo 6 no anúncio.
-4. Os adquirentes podem verificar a autenticidade da identificação, registo e propriedade de cães ou gatos anunciados online através do sistema referido no parágrafo 6.
-5. Os fornecedores de plataformas online devem assegurar que a sua interface online é concebida e organizada de forma a facilitar aos operadores ou outras pessoas singulares ou coletivas que colocam cães ou gatos no mercado o cumprimento das suas obrigações, e devem informar os adquirentes, de forma visível, da possibilidade de verificar a identificação e o registo do cão ou gato através de uma ligação web para o sistema referido no parágrafo 6.
-6. A Comissão garante que um sistema de verificação online que realiza controlos automatizados da autenticidade da identificação, registo e propriedade de cães ou gatos anunciados online, utilizando a base de dados referida no artigo 23.º, está disponível publicamente gratuitamente e gera o token único de verificação referido no parágrafo 3, alínea c).</t>
+          <t>1.	Quando operadores anunciem online um cão ou gato com vista ao seu colocamento no mercado da União, devem assegurar a apresentação do seguinte aviso no anúncio em caracteres claramente visíveis e em negrito:
+	"Um animal não é um brinquedo. Ter um é uma decisão que muda a vida. É seu dever assegurar a sua saúde e bem-estar e não o abandonar."
+2.	Quando pessoas singulares ou coletivas que não sejam operadores anunciem online um cão ou gato com vista ao seu colocamento no mercado da União, devem assegurar a apresentação de um aviso sobre detenção responsável utilizando a redação referida no n.º 1 ou uma redação diferente com significado equivalente.
+3.	Ao colocar um cão ou gato no mercado na União, a pessoa singular ou coletiva que coloca o cão ou gato no mercado deve fornecer ao adquirente:
+(a)	prova da identificação e do registo do cão ou gato em conformidade com o artigo 20.º;
+(b)	as seguintes informações sobre o cão ou gato:
+(i)	a sua espécie;
+(ii)	o seu sexo;
+(iii)	a sua data e país de nascimento; e
+(iv)	quando relevante, a sua raça.
+	Caso uma pessoa singular ou coletiva anuncie um cão ou gato online com vista ao seu colocamento no mercado da União, essa pessoa deve utilizar o sistema referido no n.º 5 para gerar um token único de verificação e incluir esse token no anúncio, juntamente com uma ligação web para o sistema referido no n.º 5.
+	O sistema referido no n.º 5 deve permitir aos adquirentes verificar a autenticidade da identificação, do registo e da propriedade de cães ou gatos anunciados online.
+4.	Os fornecedores de plataformas online devem assegurar que a sua interface online é concebida e organizada de forma a facilitar aos operadores ou outras pessoas singulares ou coletivas que colocam cães ou gatos no mercado o cumprimento das suas obrigações nos termos dos n.ºs 1 a 3 do presente artigo, e em conformidade com o artigo 31.º do Regulamento (UE) 2022/2065, e devem informar os adquirentes, de forma visível, da possibilidade de verificar a autenticidade da identificação, do registo e da propriedade do cão ou gato no sistema de verificação online referido no n.º 5, acessível através de uma ligação web.
+	Apenas a pessoa singular ou coletiva que coloca cães ou gatos no mercado é responsável pela exatidão das informações fornecidas através da interface da plataforma online. Nenhuma disposição do presente número pode ser interpretada como impondo uma obrigação geral de monitorização ao fornecedor da plataforma online, na aceção do artigo 8.º do Regulamento (UE) 2022/2065.
+5.	A Comissão garante que um sistema de verificação destinado a realizar controlos automatizados da autenticidade da identificação, do registo e da propriedade de cães ou gatos anunciados online, utilizando a base de dados referida no artigo 23.º, está publicamente disponível online, a título gratuito, e gera o token único de verificação referido no segundo parágrafo do n.º 3 do presente artigo. A Comissão pode confiar o desenvolvimento, a manutenção e o funcionamento deste sistema a uma entidade independente, escolhida para essa missão na sequência de um processo de seleção pública. O sistema deve assegurar:
+(a)	a verificação fiável da autenticidade da identificação, do registo e da propriedade do cão ou gato, utilizando as bases de dados nacionais referidas no artigo 23.º;
+(b)	a conformidade com a proteção de dados, em conformidade com o Regulamento (UE) 2018/1725 e o Regulamento (UE) 2016/679.
+6.	A Comissão adota atos de execução que estabelecem:
+(a)	as informações a fornecer pelas pessoas singulares e coletivas que colocam cães ou gatos no mercado como prova de identificação e registo dos cães e gatos em conformidade com o n.º 3, alínea a);
+(b)	as informações a fornecer pelas pessoas singulares e coletivas que anunciam cães ou gatos ao sistema de verificação referido no n.º 5, para efeitos de demonstração da autenticidade da identificação, do registo e da propriedade do cão ou gato anunciado;
+(c)	as seguintes características do sistema referido no n.º 5:
+-	as funções essenciais do sistema;
+-	os requisitos técnicos, eletrónicos e criptográficos do sistema;
+-	os passos procedimentais a seguir, e as informações a fornecer, pela pessoa singular ou coletiva que coloca o cão ou gato no mercado, bem como os passos e informações exigidos ao adquirente, para que o sistema de verificação online funcione.
+	Os atos de execução referidos na alínea a) devem ser adotados até … [dois anos após a data de entrada em vigor do presente Regulamento] e os atos de execução referidos nas alíneas b) e c) devem ser adotados até … [três anos a contar da data de entrada em vigor do presente Regulamento].
+	Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2598,10 +2620,18 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>1. Os Estados-Membros são responsáveis pela criação e manutenção de bases de dados para o registo de cães e gatos identificados, em conformidade com os artigos 20.º (parágrafos 1 e 2) e 21.º (parágrafo 4 e segundo parágrafo do parágrafo 4a).
-1a. Para este efeito, os Estados-Membros podem utilizar bases de dados mantidas por outro Estado-Membro, com base em acordos apropriados entre esses Estados-Membros.
-2. Os Estados-Membros asseguram que as suas bases de dados referidas no parágrafo 1 estão em conformidade com os requisitos estabelecidos pelo ato de execução referido no parágrafo 3, alínea b), de modo a assegurar a sua interoperabilidade, permitindo que a identificação de um cão ou gato possa ser autenticada e rastreada em toda a União.
-2a. A Comissão estabelece e mantém uma base de dados de índice contendo o conjunto mínimo de campos definido no parágrafo 3, alínea b). A Comissão pode confiar o desenvolvimento, manutenção e funcionamento dessa base de dados de índice a uma entidade independente, após um processo de seleção pública.</t>
+          <t>1.	Os Estados-Membros são responsáveis pela criação e manutenção de bases de dados para o registo de cães e gatos identificados, em conformidade com o artigo 20.º, n.ºs 1 e 2, e com o artigo 26.º, n.ºs 3 e 4, segundo parágrafo.
+2.	Para este efeito, os Estados-Membros podem utilizar bases de dados mantidas por outro Estado-Membro, com base em acordos apropriados entre esses Estados-Membros.
+3.	Os Estados-Membros asseguram que as suas bases de dados referidas no n.º 1 estão em conformidade com os requisitos estabelecidos pelo ato de execução referido no n.º 4, segundo parágrafo, alínea b), de modo a assegurar a sua interoperabilidade.
+4.	A Comissão estabelece e mantém uma base de dados de índice contendo o conjunto mínimo de campos estabelecido nos atos de execução referidos no segundo parágrafo, alínea b). A Comissão pode confiar o desenvolvimento, a manutenção e o funcionamento dessa base de dados de índice a uma entidade independente, na sequência de um processo de seleção pública.
+	A Comissão adota atos de execução que estabelecem regras pormenorizadas relativas a:
+(a)	o conteúdo mínimo das bases de dados referidas no n.º 1;
+(b)	a interoperabilidade entre as bases de dados dos Estados-Membros e a base de dados de índice, incluindo o conjunto mínimo de campos a transmitir à base de dados de índice e os intervalos da transmissão;
+(c)	a funcionalidade para fornecer prova de identificação e registo de um cão ou gato, tal como referido no artigo 21.º, n.º 3, alínea a);
+(d)	o registo onde os Estados-Membros declaram as suas bases de dados, e os parâmetros necessários para a conexão dessas bases de dados entre si, em conformidade com as disposições estabelecidas em aplicação da alínea b);
+(e)	a interconexão entre as bases de dados dos Estados-Membros referidas no n.º 1, a base de dados de viajantes da União com animais de estimação referida no artigo 26.º, n.º 4, e o Sistema de Gestão da Informação para os Controlos Oficiais (IMSOC), quando relevante.
+	A Comissão adota os atos de execução referidos no segundo parágrafo, alíneas a) e c), até … [data dois anos após a data de entrada em vigor do presente Regulamento]. Adota os atos de execução referidos no segundo parágrafo, alíneas b), d) e e), até … [três anos a contar da data de entrada em vigor do presente Regulamento].
+	Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2908,26 +2938,30 @@
 The Commission shall by ... [ 8 years after the date of entry into force of this Regulation] adopt implementing acts laying down detailed arrangements for the following:
 (i)	the information to be pre-notified by owners in accordance with paragraph (4) of this Article in the Union pet travellers’ database, taking into account the personal data protection requirements of Regulation (EU) 2018/1725 and Regulation (EU) 2016/679;
 (ii)	the procedure by which the risk of fraud is to be established, which is to take into account the activities carried out by the AAC network
-Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 29.
-CHAPTER VI
-PROCEDURAL PROVISIONS</t>
+Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 29.</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>1. Os cães e os gatos podem ser introduzidos na União apenas para colocação no mercado da União se estiverem satisfeitas as seguintes condições:
-a) Tenham sido criados e mantidos em conformidade com qualquer das seguintes situações:
-   i) Capítulo II do presente Regulamento;
-   ii) Condições reconhecidas pela União em conformidade com o artigo 129.º do Regulamento (UE) 2017/625 como equivalentes às estabelecidas no Capítulo II do presente Regulamento; ou
-   iii) Quando aplicável, requisitos contidos num acordo específico entre a União e o país exportador.
-b) Provenham de um país terceiro ou território e de um estabelecimento listado em conformidade com os artigos 126.º e 127.º do Regulamento (UE) 2017/625.
-2. O certificado oficial referido no artigo 126.º, parágrafo 2, alínea c), do Regulamento (UE) 2017/625 que acompanha os cães e gatos que entram na União desde países terceiros e territórios para colocação no mercado da União deve conter uma atestação certificando a conformidade com o parágrafo 1 do presente artigo.
-3. Os cães e gatos que entram na União para colocação no mercado da União devem ser identificados antes da sua entrada por um médico veterinário através de um transponder injetável contendo um microchip legível em conformidade com o Anexo II.
-4. O operador responsável pela importação de cães ou gatos que entram na União deve assegurar o registo dos cães ou gatos por um médico veterinário numa base de dados nacional referida no artigo 19.º, parágrafo 1, no prazo de 5 dias úteis após a sua entrada na União.
-4a. O movimento não-comercial de um cão ou gato desde um país terceiro ou território para a União deve ser pré-notificado pelo seu proprietário numa base de dados online de viajantes da União com animais de estimação, pelo menos 5 dias úteis antes da passagem da fronteira da União, exceto nos seguintes casos:
-— cães ou gatos que entram na União diretamente desde países terceiros ou territórios que satisfazem as condições estabelecidas no artigo 17.º, parágrafo 1, alínea a), do Regulamento Delegado (C(2026) 20); e
-— cães ou gatos registados numa base de dados de um Estado-Membro referida no artigo 19.º, parágrafo 1.
-Se o cão ou gato permanecer mais de seis meses na União, o proprietário deve assegurar o seu registo por um médico veterinário na base de dados do Estado-Membro de residência referida no artigo 19.º, parágrafo 1, no prazo de 5 dias úteis após o termo do sexto mês. Os Estados-Membros podem permitir o registo por outras pessoas que não médicos veterinários, desde que tenham medidas em vigor para assegurar a exatidão das informações inseridas na base de dados.</t>
+          <t>1.	Os cães e os gatos podem ser introduzidos na União para efeitos de colocação no mercado da União apenas se estiverem cumpridas as seguintes condições:
+(a)	tenham sido criados e mantidos em conformidade com qualquer das seguintes situações:
+(i)	os requisitos do Capítulo II do presente Regulamento;
+(ii)	requisitos reconhecidos pela União, em conformidade com o artigo 129.º do Regulamento (UE) 2017/625, como equivalentes aos estabelecidos no Capítulo II do presente Regulamento; ou
+(iii)	quando aplicável, requisitos constantes de um acordo específico entre a União e o país exportador.
+(b)	provenham de um país terceiro ou território e de um estabelecimento incluído em lista em conformidade com os artigos 126.º e 127.º do Regulamento (UE) 2017/625.
+2.	O certificado oficial referido no artigo 126.º, n.º 2, alínea c), do Regulamento (UE) 2017/625 que acompanha os cães e gatos introduzidos na União desde países terceiros e territórios para efeitos de colocação no mercado da União deve conter uma atestação certificando a conformidade com o n.º 1 do presente artigo.
+3.	Os cães e gatos introduzidos na União para efeitos de colocação no mercado da União devem ser identificados antes da sua entrada na União por um médico veterinário por meio de um transponder injetável contendo um microchip legível em conformidade com os requisitos estabelecidos no Anexo II.
+	O operador responsável pela importação dos cães ou gatos para a União deve assegurar que estes são registados por um médico veterinário numa base de dados nacional referida no artigo 23.º, n.º 1, no prazo de cinco dias úteis após a sua introdução na União. Os Estados-Membros podem permitir o registo por pessoas que não sejam médicos veterinários, desde que disponham de medidas para assegurar a exatidão das informações que essas pessoas introduzem na base de dados.
+4.	O movimento não comercial de um cão ou gato desde um país terceiro ou território para a União deve ser pré-notificado pelo seu proprietário a uma base de dados online de viajantes da União com animais de estimação, pelo menos cinco dias úteis antes de o cão ou gato atravessar a fronteira da União, exceto nos seguintes casos:
+(a)	quando o cão ou gato é introduzido na União diretamente desde países terceiros ou territórios que satisfazem as condições estabelecidas no artigo 17.º, n.º 1, alínea a), do Regulamento Delegado (UE) …/… da Comissão; e
+(b)	quando o cão ou gato está registado numa base de dados de um Estado-Membro referida no artigo 23.º, n.º 1, do presente Regulamento.
+	Caso o cão ou gato permaneça mais de seis meses na União, o proprietário deve assegurar o seu registo por um médico veterinário na base de dados do Estado-Membro de residência referida no artigo 23.º, n.º 1, no prazo de cinco dias úteis após o termo do sexto mês desde a sua entrada na União. Os Estados-Membros podem permitir o registo por pessoas que não sejam médicos veterinários, desde que disponham de medidas para assegurar a exatidão das informações que essas pessoas introduzem na base de dados.
+	A Comissão estabelece e mantém a base de dados de viajantes da União com animais de estimação referida no primeiro parágrafo. A Comissão pode confiar o desenvolvimento, a manutenção e o funcionamento dessa base de dados a uma entidade independente, na sequência de um processo de seleção pública. O acesso a essa base de dados fica restrito às autoridades competentes dos Estados-Membros e à Comissão.
+	A Comissão assegura que a base de dados aciona notificações iRASFF para os movimentos pré-notificados que apresentem um risco de fraude. O Estado-Membro que recebe a notificação toma as medidas adequadas para dar seguimento à notificação, em conformidade com o artigo 105.º, n.º 2, do Regulamento (UE) 2017/625.
+	A Comissão adota, até … [8 anos após a data de entrada em vigor do presente Regulamento], atos de execução que estabelecem regras pormenorizadas relativas a:
+(i)	as informações a pré-notificar pelos proprietários em conformidade com o n.º 4 do presente artigo na base de dados de viajantes da União com animais de estimação, tendo em conta os requisitos de proteção de dados pessoais do Regulamento (UE) 2018/1725 e do Regulamento (UE) 2016/679;
+(ii)	o procedimento pelo qual o risco de fraude deve ser determinado, tendo em conta as atividades realizadas pela rede CAA.
+	Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -3591,73 +3625,21 @@
 This Regulation shall be binding in its entirety and directly applicable in all Member States.
 Done at …,
 For the European Parliament	For the Council
-The President	The President
-Annex I
-Requirements applicable to establishments
-1.	Feeding and watering
-1.1.	Dogs and cats shall be fed at least twice per day. Puppies and kittens shall be fed more frequently.
-However, those requirements shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
-1.2.	Each puppy or kitten shall be fed with colostrum during at least the first two days of its life. Thereafter, it shall be fed with milk from its mother or a lactating bitch or queen. If that is not possible, because the mother is ill or is otherwise unable to feed her offspring or unable to provide sufficient milk, the puppy or kitten shall be fed with a milk replacer that has been designed for puppies and kittens . The frequency of such feeding shall comply with the manufacturer’s instructions or those of a veterinarian.
-1.3.	All unweaned puppies and kittens shall be fed enough milk, milk replacer or a combination of both, to allow them to gain bodyweight steadily.
-1.4.	Weaning shall be performed by the gradual introduction of solid feed over a period that is not shorter than seven days and shall not be completed before the age of six weeks for puppies and kittens alike.
-2.	Housing
-2.1.	Temperature:
-In breeding establishments, the temperature shall be maintained within a range of:
-(a)	22 to 28°C in whelping areas for the first 10 days of puppies’ lives;
-(b)	18 to 27°C in kittening areas for the first 21 days of kittens’ lives.
-2.2.	Lighting
-2.2.1.	Dogs and cats shall be exposed to light for at least 7 hours per day.
-2.2.2.	Artificial light shall be broad spectrum or full spectrum with a frequency of at least 80 Hertz.
-2.2.3.	Dogs and cats shall have the possibility to be without artificial lighting for at least 8 hours per day.
-2.3.	Space allowances
-2.3.1.	Whelping and kittening areas shall be designed to allow the mother to move away from her offspring.
-2.3.2,	In the case of breeding and selling establishments, the following minimum space allowances for dogs and cats shall apply, based on the total permanently accessible area for the dogs or cats:
-2.3.3,
-3.	Health
-3.1.	Queens shall be bred from only if their age is at least 10 months;
-3.2.	Bitches shall not be used for breeding from before their second oestrus.
-3.3.	A bitch or queen shall not produce more than three litters within a period of two years.
-3.4.	For bitches and queens that have produced 3 litters, including stillborns, within a period of two years, there shall be a recuperation  period of at least one year.
-3.5.	Any bitch or queen that has undergone two caesarean sections shall no longer be used for breeding.
-3.6.	Before any bitch aged eight years or more, or any queen aged six years or more, is used for breeding, it must be physically examined by a veterinarian who confirms in writing that, at the time of the examination, there are no medical indications that argue against the use of that bitch or queen for breeding.
-The operator shall keep the written confirmation referred to in the first subparagraph for a period of at least three years.
-4.	Behavioural needs
-4.1.	Socialisation
-4.1.1.	From three weeks of age, dogs and cats shall be gradually provided with daily opportunities for social contact with other animals of the same species and humans, and, where possible, with animals of other species.
-4.1.2.	Dogs or cats that pose a threat to each other due to aggressive behaviour, or that cause each other undue stress or discomfort shall be kept separate.
-4.2.	Enrichment
-4.2.1.	Cats shall be provided with a sufficient number of scratching posts, hiding places and shelves to ensure that each cat can climb, rest, observe and withdraw.
-4.3.	Separation
-Puppies kept in establishments shall not be permanently separated from their mothers before the age of eight weeks.
-Kittens kept in shelters and foster homes shall not be permanently separated from their mothers before the age of eight weeks. Kittens kept in breeding establishments shall not be permanently separated from their mothers before the age of 12 weeks.
-However, earlier separation from mothers shall be possible for medical reasons based on the written advice of a veterinarian. The operator shall keep a record of such advice until the last puppy or kitten of the litter concerned is placed on the market.
-Annex II
-Identification and registration of dogs and cats
-Transponders used to individually identify dogs and cats as required in Article 20 and Article 26 shall meet the following requirements:
-(a)	the microchip shall contain an individual, non-repeatable and non-reprogrammable identification number;
-(b)	the identification number shall start with the country of identification of the dog or cat identified in accordance with ISO standard 3166;
-(c)	the code structure and technical concept of the radio frequency identification shall be in compliance with ISO standards 11784 and 11785;
-(d)	compliance with ISO standards 11784 and 11785 shall be evaluated in accordance with ISO standard 24631-1.
-Annex III
-Data on animal welfare
-1.	The number of dogs and cats registered per year, as referred to in Article 20 and Article 26(3).
-2.	The number of breeding establishments, selling establishments, shelters and foster homes registered per year in accordance with Article 9.
-3.	The number of breeding establishments approved per year, as referred to in Article 10.
-4.	The number of breeding establishments approval of which has been suspended or withdrawn per year.</t>
+The President	The President</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>1 — O presente regulamento entra em vigor no vigésimo dia seguinte ao da sua publicação no Jornal Oficial da União Europeia.
-2 — O presente regulamento é aplicável a partir de [2 anos após a data de entrada em vigor do presente regulamento], salvo:
-a) O artigo 13.º que é aplicável a partir de [3 anos após a data de entrada em vigor do presente regulamento];
-b) O artigo 6a, n.º 2 que é aplicável a partir de 1 de julho de 2030;
-c) O artigo 12.º, artigo 17a (n.º 3, alíneas c, d e f), artigo 18.º (alíneas a, b e ba), artigo 19.º (n.ºs 2 e 2a) e artigo 21.º (n.ºs 1 a 4) que são aplicáveis a partir de [5 anos após a data de entrada em vigor do presente regulamento];
-d) O artigo 9.º (n.ºs 2 e 2a) que é aplicável a partir de [7 anos após a data de entrada em vigor do presente regulamento];
-e) O artigo 7a que é aplicável a partir de [8 anos após a data de entrada em vigor do presente regulamento];
-f) O artigo 21.º, n.º 4a que é aplicável a partir de [10 anos após a entrada em vigor do regulamento] e;
-g) O segundo parágrafo do artigo 17.º (n.ºs 1 e 2), artigo 17a (n.º 3) e artigo 19.º, n.º 1 que são aplicáveis a partir de [4 anos após a entrada em vigor do presente regulamento], com exceção dos proprietários de animais de estimação e outras pessoas singulares ou coletivas, que não sejam operadores, que não colocam cães ou gatos no mercado, para os quais o artigo 17.º (n.ºs 1 e 2) é aplicável a partir de [10 anos após a entrada em vigor do presente regulamento] no caso da identificação e registo de cães e [15 anos após a entrada em vigor do presente regulamento] no caso da identificação e registo de gatos.
-3 — O presente regulamento é obrigatório em todos os seus elementos e diretamente aplicável em todos os Estados-Membros.</t>
+          <t>O presente regulamento entra em vigor no vigésimo dia seguinte ao da sua publicação no Jornal Oficial da União Europeia.
+É aplicável a partir de … [dois anos após a data de entrada em vigor do presente Regulamento]. Todavia:
+(i)	o artigo 16.º é aplicável a partir de … [três anos após a data de entrada em vigor do presente Regulamento];
+(ii)	o artigo 21.º, n.º 3, e o artigo 23.º, n.º 1, são aplicáveis a partir de … [quatro anos após a entrada em vigor do presente Regulamento];
+(iii)	o artigo 8.º-A, n.º 1, é aplicável a partir de 1 de julho de 2036 e o artigo 8.º-A, n.º 2, é aplicável a partir de 1 de julho de 2030;
+(iv)	o artigo 15.º, o artigo 21.º, n.º 3, segundo parágrafo, n.ºs 4 e 5, o artigo 22.º, n.º 1, alíneas a), b) e c), o artigo 23.º, n.ºs 3 e 4, e o artigo 26.º, n.ºs 1, 2 e 3, são aplicáveis a partir de … [cinco anos após a data de entrada em vigor do presente Regulamento];
+(v)	o artigo 12.º, n.ºs 2 e 3, é aplicável a partir de … [sete anos após a data de entrada em vigor do presente Regulamento];
+(vi)	o artigo 10.º é aplicável a partir de … [oito anos após a data de entrada em vigor do presente Regulamento]; e
+(vii)	o artigo 26.º, n.º 4, é aplicável a partir de … [10 anos após a entrada em vigor do presente Regulamento].
+O presente regulamento é obrigatório em todos os seus elementos e diretamente aplicável em todos os Estados-Membros.</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -669,19 +669,19 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Art.º 5.º do Regulamento 2023/0447</t>
+          <t>Art.º 5.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>1.	A breeding establishment where no more than two litters per calendar year are produced for placing on the market shall be subject to only the obligations laid down in Article 6, Article 7(1) (2), (3) and (4). Article 8, Article 9, Article 11, Article 14(2), (3) and (4), Article 15(3), (4) and (8), Article 16(1). points (b), (c) and (d), Article 17(2), (3), (5) and (7), Article 18, Article 19(1) and points 3 and 4.3 of Annex I.
-2.	A shelter in which not more than a combined total of 15 dogs or cats are kept at any given time, or any foster home shall be subject to only the obligations laid down in Article 6, Article 7(1), (2), (3), (4), and(5), Article 9, Article 11, Article 14(2), (3) and (4), Article 15(3), (4) and (8), Article 16(1). points (a), (b), (c) and (d), Article 17(2), (3), (5) and (7), Article 18 and point 4.3 of Annex I.</t>
+          <t>A breeding establishment where no more than two litters per calendar year are produced for placing on the market shall be subject to only the obligations laid down in Article 6, Article 7(1) (2), (3) and (4). Article 8, Article 9, Article 11, Article 14(2), (3) and (4), Article 15(3), (4) and (8), Article 16(1). points (b), (c) and (d), Article 17(2), (3), (5) and (7), Article 18, Article 19(1) and points 3 and 4.3 of Annex I.
+A shelter in which not more than a combined total of 15 dogs or cats are kept at any given time, or any foster home shall be subject to only the obligations laid down in Article 6, Article 7(1), (2), (3), (4), and(5), Article 9, Article 11, Article 14(2), (3) and (4), Article 15(3), (4) and (8), Article 16(1). points (a), (b), (c) and (d), Article 17(2), (3), (5) and (7), Article 18 and point 4.3 of Annex I.</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>1 — Um estabelecimento de criação que produz no máximo duas ninhadas por ano civil para colocação no mercado fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (n.º 1, alíneas 1b, 1c e 1d), artigo 6a, artigo 7.º, artigo 8.º, artigo 11.º (n.ºs 2, 3 e 3a), artigo 12.º (n.ºs 3, 4 e 7), artigo 13.º (n.º 2, alíneas b, c e d), artigo 14.º (n.ºs 2, 3, 4 e 5a), artigo 15.º, artigo 15a (n.º 1) e ponto 3 e 4.3 do Anexo I.
-2 — Um abrigo, onde são mantidos no máximo 15 cães ou gatos em qualquer momento, ou qualquer lar de acolhimento fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (n.ºs 1, 1a, 1b, 1c e 1d), artigo 7.º, artigo 8.º, artigo 11.º (n.ºs 2, 3 e 3a), artigo 12.º (n.ºs 3, 4 e 7), artigo 13.º (n.º 2, alíneas a, b, c e d), artigo 14.º (n.ºs 2, 3, 4 e 5a), artigo 15.º e ponto 4.3 do Anexo I.</t>
+          <t>Um estabelecimento de criação que produz no máximo duas ninhadas por ano civil para colocação no mercado fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (n.º 1, alíneas 1b, 1c e 1d), artigo 6a, artigo 7.º, artigo 8.º, artigo 11.º (n.ºs 2, 3 e 3a), artigo 12.º (n.ºs 3, 4 e 7), artigo 13.º (n.º 2, alíneas b, c e d), artigo 14.º (n.ºs 2, 3, 4 e 5a), artigo 15.º, artigo 15a (n.º 1) e ponto 3 e 4.3 do Anexo I.
+Um abrigo, onde são mantidos no máximo 15 cães ou gatos em qualquer momento, ou qualquer lar de acolhimento fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (n.ºs 1, 1a, 1b, 1c e 1d), artigo 7.º, artigo 8.º, artigo 11.º (n.ºs 2, 3 e 3a), artigo 12.º (n.ºs 3, 4 e 7), artigo 13.º (n.º 2, alíneas a, b, c e d), artigo 14.º (n.ºs 2, 3, 4 e 5a), artigo 15.º e ponto 4.3 do Anexo I.</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -689,46 +689,34 @@
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr"/>
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr"/>
+      <c r="K2" s="8" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="M2" s="10" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="K2" s="8" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="L2" s="9" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="M2" s="10" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
       <c r="N2" s="11" t="inlineStr">
         <is>
           <t>Artigo de isenções do Regulamento europeu — não tem correspondência directa em legislação portuguesa.</t>
@@ -739,11 +727,7 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="P2" s="11" t="inlineStr">
-        <is>
-          <t>Artigo relativo a isenções no âmbito do Regulamento europeu.</t>
-        </is>
-      </c>
+      <c r="P2" s="11" t="inlineStr"/>
     </row>
     <row r="3" ht="120" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -753,87 +737,65 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Art.º 6.º do Regulamento 2023/0447</t>
+          <t>Art.º 6.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Operators shall apply the following general welfare principles with respect to dogs or cats bred or kept in their establishment:
-(a)	dogs and cats are provided with water and feed of a quality and quantity that affords them appropriate nutrition and hydration;
-(b)	dogs and cats are kept in a physical environment that is appropriate and regularly cleaned, that is secure and comfortable, especially in terms of space, air quality, temperature, light, protection against adverse climatic conditions and that is big enough to prevent overcrowding and to afford them ease of movement;
-(c)	dogs and cats are kept safe, clean and in good health, and diseases, injuries, and pain due, in particular, to management, handling practices and breeding practices, are prevented;
-(d)	dogs and cats are kept in an environment that enables them to exhibit species-specific and social non-harmful behaviour, and to establish a positive relationship with human beings;
+dogs and cats are provided with water and feed of a quality and quantity that affords them appropriate nutrition and hydration;
+dogs and cats are kept in a physical environment that is appropriate and regularly cleaned, that is secure and comfortable, especially in terms of space, air quality, temperature, light, protection against adverse climatic conditions and that is big enough to prevent overcrowding and to afford them ease of movement;
+dogs and cats are kept safe, clean and in good health, and diseases, injuries, and pain due, in particular, to management, handling practices and breeding practices, are prevented;
+dogs and cats are kept in an environment that enables them to exhibit species-specific and social non-harmful behaviour, and to establish a positive relationship with human beings;
 (e)	dogs and cats are kept in such a way as to optimise their mental state by preventing or reducing negative stimuli in duration and intensity, as well as by maximising opportunities for positive stimuli in duration and intensity, preventing the development of abnormal repetitive or other behaviours indicative of negative animal welfare, and taking into consideration the individual animal’s needs in the domains referred to in points (a) to (d).</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem aplicar os seguintes princípios gerais de bem-estar aos cães e gatos criados ou detidos nos seus estabelecimentos:
-(a) os cães e gatos são alimentados e abebeirados com água e ração de qualidade e quantidade adequadas a uma nutrição e hidratação apropriadas;
-(b) os cães e gatos são mantidos num ambiente físico adequado, regularmente limpo, seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, iluminação, proteção face a condições climáticas adversas e facilidade de movimentação, prevenindo a sobrelotação;
-(c) os cães e gatos são mantidos seguros, limpos e com boa saúde, prevenindo doenças, lesões e dor, nomeadamente através de práticas de maneio, manuseamento e reprodução adequadas;
-(d) os cães e gatos são mantidos num ambiente que lhes permite exibir comportamentos específicos da espécie e comportamentos sociais não nocivos, e estabelecer uma relação positiva com os seres humanos;
+Os cães e os gatos recebem água e alimentos de qualidade e numa quantidade que assegura a sua boa e adequada nutrição e hidratação;
+os cães e gatos são mantidos num ambiente físico adequado, regularmente limpo, seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, iluminação, proteção face a condições climáticas adversas e facilidade de movimentação, prevenindo a sobrelotação;
+os cães e gatos são mantidos seguros, limpos e com boa saúde, prevenindo doenças, lesões e dor, nomeadamente através de práticas de maneio, manuseamento e reprodução adequadas;
+os cães e gatos são mantidos num ambiente que lhes permite exibir comportamentos específicos da espécie e comportamentos sociais não nocivos, e estabelecer uma relação positiva com os seres humanos;
 (e) os cães e gatos são mantidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo estímulos negativos em duração e intensidade, maximizando oportunidades de estímulos positivos, prevenindo o desenvolvimento de comportamentos repetitivos anormais, tendo em conta as necessidades individuais do animal nos domínios referidos nas alíneas (a) a (d).</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>al. a) do n.º 1 do art.º 10.º do RGBEAC (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>1 — O detentor do animal de companhia deve:
-a) Assegurar o bem-estar do animal, de acordo com sua espécie, raça, idade e necessidades físicas e etológicas, proporcionando-lhe:
-— Atenção, supervisão, controlo, exercício físico e estímulo mental;
-— Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável;
-— Condições higiossanitárias que atendam, no mínimo, ao estabelecido no presente decreto-lei e na demais legislação aplicável;
-— Liberdade de movimento, sendo proibidos todos os sistemas de contenção permanentes;
-— Abrigo adequado, em termos de tamanho e qualidade, com vista a proteger de condições atmosféricas adversas, incluindo frio, chuva, sol ou calor excessivos, com cama seca, limpa e confortável;
-— Contato social adequado a cada espécie, de acordo com a sua idade e atividade.</t>
-        </is>
-      </c>
+          <t>Análise no Art.º 7</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>n.ºs 1, 2 e 3 do art.º 5.º do Código do Animal (DL n.º 214/2013)</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal.
-2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
-3 — É proibida a violência contra animais, considerando-se como tal todos os atos que, sem necessidade, infligem a morte, o sofrimento, abuso ou lesões a um animal.</t>
-        </is>
-      </c>
+          <t>Análise no Art.º 7</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr"/>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>n.º 1 do art.º 7.º e n.º 1 do art.º 9.º do DL n.º 276/2001, de 17 de outubro</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>Artigo 7.º, n.º 1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
-Artigo 9.º, n.º 1 — A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam.</t>
-        </is>
-      </c>
+          <t>Análise no Art.º 7</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr">
         <is>
-          <t>O DL n.º 276/2001 (art.ºs 7.º e 9.º) consagra os mesmos parâmetros mas desenvolve-os em artigos separados (alojamento, alimentação, ambiente) sem os denominar como domínios nem os sistematizar de forma unificada segundo o referencial OMSA.</t>
+          <t>Análise no Art.º 7</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
         <is>
-          <t>O @codigo (art.º 5.º) refere 'parâmetros de bem-estar animal' genericamente, sem adotar formalmente a nomenclatura dos 5 domínios OMSA nem a sua sistematização explícita.</t>
+          <t>Análise no Art.º 7</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac (art.º 10.º, n.º 1, al. a)) articula obrigações equivalentes ao nível do detentor de forma descritiva, sem sistematização nos 5 domínios nem referência ao quadro OMSA.</t>
+          <t>Análise no Art.º 7</t>
         </is>
       </c>
       <c r="N3" s="11" t="inlineStr">
         <is>
-          <t>Alinhamento substancial de conteúdo; sem necessidade de alteração imediata. Recomenda-se a adoção formal dos 5 domínios OMSA como referencial estruturante em futura revisão legislativa ou em normas de orientação técnica da DGAV.</t>
+          <t>Regulamento especifica novos conceitos: estabelecer uma relação positiva com os seres humanos; otimizar o seu estado mental; prevenindo o desenvolvimento de comportamentos repetitivos anormais;</t>
         </is>
       </c>
       <c r="O3" s="11" t="inlineStr">
@@ -841,73 +803,150 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="P3" s="11" t="inlineStr">
-        <is>
-          <t>(espaço para anotações da reunião)</t>
-        </is>
-      </c>
+      <c r="P3" s="11" t="inlineStr"/>
     </row>
     <row r="4" ht="120" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Bem-Estar e Detenção</t>
+          <t>Obrigações gerais de bem-estar animal</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Art.º 7.º do Regulamento 2023/0447</t>
+          <t>Art.º 7.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>1.	Operators shall be responsible for the welfare of dogs and cats kept in establishments under their responsibility and control, and shall be responsible for minimising any risks to the welfare of those animals.
-2.	In the case of foster homes, the responsibility shall lie with the operator on whose behalf dogs or cats are kept. Such operators shall not place more than a combined total of five dogs or cats or one litter with or without mother in a foster home at any given time and shall provide the foster family with adequate information on the animal welfare obligations as well as the individual needs of the dogs or cats, and shall ensure that the relevant obligations laid down in this Regulation are complied with in foster homes.
-	The Member State in which the foster home is located may allow a greater number of dogs, cats or litters to be placed in the foster home, provided that the premises of the foster home have sufficient space, including outdoor space, and that the number of animal carers in the foster home is sufficient, to ensure the welfare of the dogs or cats.
-3.	Operators shall not subject any dog or cat to cruelty, abuse or mistreatment, including by making them participate in activities likely to result in cruelty to or abuse or mistreatment of the dogs or cats bred or kept by the operator.
-4.	Operators shall not abandon the dogs or cats bred or kept by them.
-5.	Before operators cease activities at an establishment, they shall ensure that the dogs or cats kept there are rehomed, either by taking up the pet ownership themselves or by transferring the responsibility for, or the ownership of, the dogs and cats to other operators or acquirers.
-6.	Operators shall ensure that dogs and cats are handled by a number of animal carers sufficient to meet the welfare needs of dogs or cats kept in their establishments, and that those carers have the competences required under Article 12.
-7.	Operators shall ensure the welfare of the dogs or cats for which they are responsible by monitoring animal-based indicators concerning behaviour and physical appearance, and by taking actions based on the results of such monitoring.
-8.	The Commission is empowered to adopt delegated acts in accordance with Article 28 supplementing this Regulation by laying down the animal-based indicators concerning behaviour and physical appearance that operators are to use for monitoring, in accordance with paragraph 7 of this Article, and the methods by which operators are to measure them.</t>
+          <t>Operators shall be responsible for the welfare of dogs and cats kept in establishments under their responsibility and control, and shall be responsible for minimising any risks to the welfare of those animals.
+In the case of foster homes, the responsibility shall lie with the operator on whose behalf dogs or cats are kept. Such operators shall not place more than a combined total of five dogs or cats or one litter with or without mother in a foster home at any given time and shall provide the foster family with adequate information on the animal welfare obligations as well as the individual needs of the dogs or cats, and shall ensure that the relevant obligations laid down in this Regulation are complied with in foster homes.
+The Member State in which the foster home is located may allow a greater number of dogs, cats or litters to be placed in the foster home, provided that the premises of the foster home have sufficient space, including outdoor space, and that the number of animal carers in the foster home is sufficient, to ensure the welfare of the dogs or cats.
+Operators shall not subject any dog or cat to cruelty, abuse or mistreatment, including by making them participate in activities likely to result in cruelty to or abuse or mistreatment of the dogs or cats bred or kept by the operator.
+Operators shall not abandon the dogs or cats bred or kept by them.
+Before operators cease activities at an establishment, they shall ensure that the dogs or cats kept there are rehomed, either by taking up the pet ownership themselves or by transferring the responsibility for, or the ownership of, the dogs and cats to other operators or acquirers.
+Operators shall ensure that dogs and cats are handled by a number of animal carers sufficient to meet the welfare needs of dogs or cats kept in their establishments, and that those carers have the competences required under Article 12.
+Operators shall ensure the welfare of the dogs or cats for which they are responsible by monitoring animal-based indicators concerning behaviour and physical appearance, and by taking actions based on the results of such monitoring.
+The Commission is empowered to adopt delegated acts in accordance with Article 28 supplementing this Regulation by laying down the animal-based indicators concerning behaviour and physical appearance that operators are to use for monitoring, in accordance with paragraph 7 of this Article, and the methods by which operators are to measure them.</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores são responsáveis pelo bem-estar dos cães ou gatos mantidos nos estabelecimentos sob a sua responsabilidade e controlo e devem minimizar quaisquer riscos para o seu bem-estar.
-2.	No caso de famílias de acolhimento, a responsabilidade recai sobre o operador em nome de quem os cães ou gatos são mantidos. Esses operadores não devem colocar mais do que um total de cinco cães ou gatos ou uma ninhada com ou sem mãe numa família de acolhimento em qualquer momento e devem fornecer à família de acolhimento informação adequada sobre as obrigações de bem-estar animal, bem como as necessidades individuais dos animais, e devem assegurar que as obrigações relevantes estabelecidas por este Regulamento são cumpridas em famílias de acolhimento. Os Estados-Membros onde a família de acolhimento está localizada podem prever um número maior de cães, gatos ou ninhadas a serem colocadas na família de acolhimento, desde que as instalações da família de acolhimento providenciem espaço suficiente, incluindo espaço ao ar livre, e que o número de cuidadores de animais na família de acolhimento seja suficiente, para assegurar o bem-estar dos cães ou gatos.
-3.	Os operadores não devem sujeitar nenhum cão ou gato a crueldade, abuso ou maus-tratos, incluindo através de participação em atividades que possam resultar em crueldade, abuso ou maus-tratos, aos cães ou gatos criados ou mantidos pelo operador.
-4.	Os operadores não devem abandonar cães ou gatos.
-5.	Os operadores que estejam prestes a cessar as atividades do seu estabelecimento devem assegurar a reintegração dos cães ou gatos mantidos aí, quer através da assunção da posse do animal de companhia, quer através da transferência da responsabilidade ou propriedade dos cães e gatos para outros operadores ou adquirentes.
-6.	Os operadores devem assegurar que os cães ou gatos são tratados por um número adequado de cuidadores de animais e de modo a satisfazer as necessidades de bem-estar dos cães ou gatos mantidos nos seus estabelecimentos e que têm as competências exigidas no artigo 12.º.
-7.	Os operadores devem assegurar o bem-estar dos cães ou gatos sob a sua responsabilidade através da monitorização de indicadores baseados no comportamento e aparência física, e através da adoção de ações com base nos resultados de tal monitorização.
-8.	A Comissão tem competência para adotar atos delegados em conformidade com o artigo 28.º que complementem este Regulamento através do estabelecimento de indicadores baseados no bem-estar dos animais relativos ao comportamento e aparência física e dos métodos da sua medição.</t>
+          <t>Os operadores são responsáveis pelo bem-estar dos cães e gatos detidos nos estabelecimentos sob a sua responsabilidade e controlo, devendo minimizar quaisquer riscos para o bem-estar desses animais.
+No caso das famílias de acolhimento, a responsabilidade incumbe ao operador em cujo nome os cães ou gatos são detidos. Tais operadores não colocam mais do que um total combinado de cinco cães ou gatos ou uma ninhada, com ou sem a mãe, num lar de acolhimento em qualquer momento dado e fornecem à família de acolhimento informações adequadas sobre as obrigações em matéria de bem-estar dos animais, bem como sobre as necessidades individuais dos cães ou gatos, e asseguram que as obrigações relevantes previstas no presente regulamento são cumpridas nos lares de acolhimento.
+O Estado-Membro em que se situa o lar de acolhimento pode autorizar um maior número de cães, gatos ou ninhadas na família de acolhimento, desde que as instalações do lar de acolhimento disponham de espaço suficiente, incluindo espaço exterior, e que o número de cuidadores de animais no lar de acolhimento seja suficiente para garantir o bem-estar dos cães e gatos.
+Os operadores não sujeitam qualquer cão ou gato a crueldade, abusos ou maus-tratos, incluindo fazendo-os participar em atividades suscetíveis de resultar em crueldade, abusos ou maus-tratos para os cães ou gatos criados ou detidos pelo operador.
+Os operadores não abandonam os cães ou gatos criados ou detidos por eles.
+Antes de os operadores cessarem as atividades num estabelecimento, asseguram que os cães ou gatos aí detidos são realojados, seja assumindo eles próprios a propriedade de animal de companhia, seja transferindo a responsabilidade pela propriedade dos cães e gatos para outros operadores ou adquirentes.
+Os operadores asseguram que os cães e gatos são manuseados por um número suficiente de cuidadores de animais para satisfazer as necessidades de bem-estar dos cães ou gatos detidos nos seus estabelecimentos, e que esses cuidadores possuem as competências exigidas no artigo 12.º.
+Os operadores asseguram o bem-estar dos cães ou gatos pelos quais são responsáveis, monitorizando indicadores baseados nos animais relativos ao comportamento e à aparência física, e adotando ações com base nos resultados desse monitoramento.
+A Comissão fica habilitada a adotar atos delegados, nos termos do artigo 28.º, que complementem o presente regulamento, estabelecendo os indicadores baseados nos animais relativos ao comportamento e à aparência física que os operadores devem utilizar para efeitos de monitorização nos termos do n.º 7 do presente artigo, bem como os métodos pelos quais os operadores devem medi-los.</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Art.º 10.º do RGBEAC (proposta, jun. 2025)</t>
+          <t>art.º 7.º e 9 a 12.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>1 — O detentor do animal de companhia deve:
-a) Assegurar o bem-estar do animal, de acordo com a sua espécie, raça, idade e necessidades físicas e etológicas, proporcionando-lhe:
-— Atenção, supervisão, controlo, exercício físico e estímulo mental;
-— Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável;
-— Condições higiossanitárias que atendam, no mínimo, ao estabelecido no presente decreto-lei e na demais legislação aplicável;
-— Liberdade de movimento, sendo proibidos todos os sistemas de contenção permanentes.</t>
+          <t>Artigo 7.º - Princípios fundamentais para o bem-estar dos animais de companhia
+1 – Todos têm o dever de garantir condições de bem-estar aos animais de companhia, em especial que:
+a) não passem fome ou sede, nem sejam sujeitos a malnutrição;
+b) não sejam expostos a situações de desconforto físico ou térmico;
+c) não sofram dor, lesão física ou doença;
+d) possam expressar padrões normais de comportamento; e
+e) não sejam colocados em situações que lhes provoquem stresse, medo ou ansiedade injustificados.
+2 - As condições de detenção e de alojamento dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes. 
+3 - Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no presente decreto-lei ou se não se adaptar ao cativeiro
+Artigo 9.º - Obrigações gerais  
+Todos os cidadãos têm o dever de notificar às autoridades competentes os casos de suspeita de infração à legislação de proteção do bem-estar dos animais de companhia de que tenham conhecimento.  
+Em caso de lesão de um animal de companhia em acidente de viação, é obrigatória a comunicação imediata deste facto às autoridades competentes por parte do condutor, ao qual, salvaguardada a sua integridade física, compete também socorrer o animal.  
+Os animais doentes, feridos ou em perigo devem, na medida do possível, ser socorridos por quem os encontrar, sem prejuízo de notificação às autoridades competentes.  
+O alojamento no quadro de respostas sociais de pessoas em situação de vulnerabilidade, incluindo as casas de abrigo de vítimas de violência doméstica e os albergues de pessoas em situação de sem-abrigo, devem, sempre que possível, assegurar o acolhimento dos animais de companhia das pessoas que acolhem.  
+Os planos de emergência e proteção civil devem incluir medidas para a proteção e resgate de animais em situação de emergência.  
+Artigo 10.º - Obrigações especiais dos detentores de animais de companhia  
+1 – O detentor do animal de companhia deve:  
+a) Assegurar o bem-estar do animal, de acordo com sua espécie, raça, idade e necessidades físicas e etológicas, proporcionando-lhe:  
+i) Atenção, supervisão, controlo, exercício físico e estímulo mental;  
+ii) Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável;  
+iii) Condições higiossanitárias que atendam, no mínimo, ao estabelecido no presente decreto-lei e na demais legislação aplicável;  
+iv) Liberdade de movimento, sendo proibidos todos os sistemas de contenção permanentes e, no caso de animais que, pelas características da espécie ou comportamento, tenham de ser mantidos em gaiolas, aquários, terrários, canis, espaços vedados ou outros, sendo obrigatório que os mesmos disponham de espaço e enriquecimento ambiental adequados para garantir o seu bem-estar e a expressão dos seus comportamentos naturais, obedecendo aos requisitos fixados na portaria prevista no artigo 58.º do presente decreto-lei;  
+v) Abrigo adequado, em termos de tamanho e qualidade, com vista a proteger de condições atmosféricas adversas, incluindo frio, chuva, sol ou calor excessivos, com cama seca, limpa e confortável;  
+vi) Contato social adequado a cada espécie, de acordo com a sua idade e atividade.  
+b) Vigiar o animal, de modo a evitar que este cause danos a pessoas, outros animais ou coisas;  
+c) Educar o animal com recurso a métodos de reforço positivo visando a sua vinculação e integração positivas no espaço familiar e no meio ambiente;  
+d) Identificar e registar o animal, nos termos do presente decreto-lei;  
+e) Transportar o animal de forma adequada e de acordo com a legislação em vigor, garantindo a segurança rodoviária e o bem-estar e conforto do animal durante o transporte, inclusive em veículos particulares;  
+f) Proporcionar ao animal toda e qualquer intervenção sanitária declarada como obrigatória por parte autoridade sanitária nacional, bem como qualquer outro tipo de tratamento veterinário preventivo, paliativo ou curativo indispensável ao seu bem-estar;  
+g) Comunicar o desaparecimento ou morte do animal de companhia, qualquer alteração nos dados do animal de companhia ou do proprietário, nos prazos prescritos, bem como manter atualizado o SIAC e o DIAC, nos termos previstos no presente decreto-lei;  
+h) Colocar à disposição das autoridades competentes a documentação necessária e obrigatória em cada caso, colaborando para a obtenção das informações solicitadas a todo o momento e atendendo, de forma geral, a todas as recomendações que a autoridade competente emita;  
+i) Recolher os excrementos do animal de companhia de quaisquer locais de acesso público.  
+2 – É obrigatório o uso por todos os cães e gatos que circulem em espaços públicos de coleira ou peitoral, no qual deve constar a morada ou contacto telefónico do detentor.  
+3 – Em espaços públicos, os cães e gatos devem ser conduzidos à trela ou, no caso dos cães, exceto durante a participação em provas e treinos ou, tratando-se de animais utilizados na caça, durante os atos venatórios, cães-pastor enquanto guardam os rebanhos, ou cães pertencentes às Forças Armadas e às Forças de Segurança e Serviços de Segurança e cães de busca e salvamento, quando em serviço.  
+4 – As autarquias locais devem prever espaços públicos, ainda que condicionados a determinados horários, para a permanência e circulação de cães ou gatos sem a obrigatoriedade de utilização de trela ou açaimo.  
+5 – As autarquias locais estabelecem o regime aplicável à circulação e permanência de animais de companhia em “Praias de Uso Canino”: zonas de praia não classificadas como “águas balneares”, nas quais são disponibilizados equipamentos e materiais de recolha de dejetos, bem como normas a cumprir pelos respetivos titulares do animal de companhia.  
+6 – Os cães e gatos não registados como animais reprodutores em nome de criadores com alojamentos autorizados para o efeito devem ser esterilizados antes dos seis meses de idade, desde entrada em vigor deste Decreto-Lei.  
+7 – Todos os cães e gatos, com mais de 6 meses, que não se encontrem registados como animais reprodutores em nome de criadores com alojamento licenciados para o efeito, devem ser esterilizados, caso não existam contraindicações médico veterinárias, no prazo de 2 anos, desde a entrada em vigor do presente Decreto-Lei.  
+Artigo 11.º - Obrigações especiais dos detentores relativas ao alojamento  
+A determinação do número de animais permitidos em alojamento que não seja destinado ao exercício da atividade de exploração para hospedagem, nos termos do presente decreto-lei, seja em prédios urbanos, mistos ou rústicos, é competência do respetivo município e freguesia, que terão acesso à base de dados de apoio ao Sistema de Informação de Animais de Companhia, para monitorização e controlo do número de animais mantidos em cada local. O Município e a Junta de Freguesia, excecionalmente, podem autorizar a permanência de um número maior de animais em cada alojamento.  
+Qualquer norma restritiva em relação ao disposto no número anterior, estipulada em título constitutivo da propriedade horizontal, em contrato de arrendamento, em regulamento do condomínio ou outro instrumento, deve considerar-se não escrita, exceto no respeitante a alojamento em partes comuns e sem prejuízo do disposto no número seguinte.  
+Nas situações em que a permanência do animal de companhia é fonte de prejuízo para o sossego, a salubridade ou a segurança dos restantes moradores, qualquer morador pode intimar o proprietário a tomar providências ao seu alcance no sentido de as fazer cessar.
+Em caso de não cumprimento do disposto no presente artigo, as câmaras municipais, após vistoria conjunta do delegado de saúde e do médico veterinário municipal, notificam o detentor para retirar os animais para um local adequado, que poderá ser um centro de bem-estar animal, no prazo estabelecido por aquelas entidades, caso o detentor não opte por outro destino que reúna as condições estabelecidas pelo presente decreto-lei.
+Artigo 12.º- Proibições gerais
+1 – São interditas quaisquer práticas que violem o bem-estar dos animais de companhia, em especial as seguintes:
+Causar a sua morte, em violação do que está previsto no presente decreto-lei para a eutanásia ;
+Sujeitá-los a qualquer prática que lhes possa causar sofrimento, dano, stresse ou angústia, por ação ou omissão, salvo nas situações legalmente previstas;
+Sujeitá-los a abuso sexual ou práticas sexuais, bem como captar ou disseminar, por qualquer forma, imagens de contacto sexual entre pessoas e animais;
+Deter, comercializar, alojar, produzir, distribuir, importar, exportar, divulgar, exibir, ceder, disseminar ou disponibilizar, a qualquer título ou por qualquer meio, material audiovisual retratando a sua sujeição a contacto sexual ou a atos de abuso ou violência.
+Abandoná-los;
+Acorrentá-los ou mantê-los em espaços confinados, entre os quais varandas, caves, armazéns e outros, que não garantam o seu bem-estar, sendo permitido prendê-los temporariamente com trela à porta de locais que não permitam a entrada de animais ou durante atividades ao ar livre, sob supervisão humana e desde que não sejam expostos a fatores que ponham em causa o seu bem-estar.
+Mantê-los em veículos estacionados  sem ventilação e temperatura adequadas.
+Mantê-los predominantemente isolados de humanos ou de outros animais apropriados à espécie;
+Sujeitá-los a intervenções cirúrgicas, com o objetivo de modificar a sua aparência ou alcançar outros fins não curativos, ou não destinados a impedir a reprodução, em particular, corte da cauda, secção das cordas vocais, remoção de unhas ou dentes, e corte das orelhas que não seja realizada para fins de identificação de animais esterilizados conforme boas práticas internacionais;
+Doá-los como prémio, recompensa ou no âmbito de sorteios ou promoções;
+Vendê-los ou registá-los a menores de dezoito anos ou a pessoas incapazes do exercício de diretos, sem a autorização do respetivo representante legal;
+Vendê-los ou transacioná-los sem estarem registados no SIAC;
+Vendê-los através da Internet;
+Utilizá-los para atividades de venda ambulante;
+Criá-los ou vendê-los sem as autorizações e os registos legalmente previstos, bem como publicitar qualquer prestação de serviço ou venda sem o número de registo do alojamento;
+Administrar-lhes substâncias, tratamentos ou procedimentos com vista a aumentar ou diminuir o nível natural das suas capacidades fisiológicas e etológicas ou que não tenham fins médico-veterinários;
+Sujeitá-lo a amputações sem razão médica veterinária que o justifique;
+Utilizá-los ou mantê-los em estabelecimentos de ensino ou formação, sem prejuízo dos animais de experimentação científica ou de atividades educativas assistidas por animais, tais como para fins de adoção, terapêuticos ou de sensibilização para o bem-estar animal; 
+Utilizá-los em eventos, confrontos entre animais, ou outras atividades que envolvam crueldade ou tratamento humilhante, maus-tratos, sofrimento ou morte, ou coloquem em risco a sua saúde e bem-estar;
+Utilizá-los em corridas de cães, com ou sem isco, com fins competitivos ou recreativos;
+Utilizá-los em eventos que não estejam devidamente licenciados e autorizados;
+Educá-los ou treiná-los com recurso a métodos aversivos, punitivos ou violentos, suscetíveis de causar danos físicos, angústia, stresse ou medo aos animais ou que visem estimular a sua agressividade ou fazê-los trabalhar de forma a exceder as suas forças ou capacidades naturais, prejudicando a sua saúde ou bem-estar;
+Mantê-los em vitrines expostas ao público; 
+Vender cães, gatos ou furões senão por criadores comerciais em alojamentos autorizados para o efeito;
+Utilizá-los em carrosséis, atrações de feiras, circos, exposições itinerantes, números com animais e manifestações similares;  
+Levá-los amarrados a veículos motorizados em movimento;
+Utilizar, deter ou comercializar qualquer meio que tenha como propósito influenciar o comportamento do animal através de métodos aversivos, violentos ou estímulos punitivos, tais como coleiras elétricas, de choques, estranguladoras ou com bicos, açaimos fechados ou que dificultem a respiração do animal;
+z) Usá-los para a promoção ou concretização de sacrifício ritual de animais de companhia;
+aa) Consumi-los, usar ou comercializar a sua carne, pele, pelo ou qualquer parte do seu corpo, excetuando-se as utilizações autorizadas para fins experimentais ou científicos;
+bb) Utilizá-los para a prática de mendicidade, sem prejuízo do direito das pessoas sem-abrigo se fazerem acompanhar dos seus animais de companhia, salvaguardado o seu bem-estar.</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Art.º 5.º do Código do Animal (DL n.º 214/2013)</t>
+          <t>Art.º 4 e 5.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os cinco domínios do bem-estar animal (Nutrição, Ambiente, Saúde, Comportamento e Psicológico), estabelecidos pela Organização Mundial da Saúde Animal (OMSA).
-2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou as demais previstas no presente diploma.
-3 — É proibida a violência contra animais, considerando-se como tal todos os atos que, sem necessidade, infligem a morte, o sofrimento, a dor, a angústia ou ferimentos a um animal.</t>
+          <t>Artigo 4.º - Detenção responsável
+Cabe aos detentores de animais de companhia assegurar as necessidades básicas de bem-estar dos mesmos, garantir o controlo da sua reprodução, salvaguardar a sua saúde e prevenir os riscos inerentes à transmissão de doenças a pessoas e a outros animais e, ainda, a segurança das populações, garantindo a salubridade dos locais e a tranquilidade das pessoas.
+Artigo 5.º Princípios básicos para o bem-estar dos animais
+1 - As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal.
+2 - Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
+3 -É proibida a violência contra animais, considerando-se como tal todos os atos que, sem necessidade, infligem a morte, o sofrimento, abuso ou lesões a um animal, designadamente os seguintes:
+	a) Agredir animais, nomeadamente com o uso de chicotes, estimulantes elétricos ou objetos contundentes ou perfurantes, ou com murros, bofetadas ou pontapés;
+	b) Restringir a liberdade de movimentos dos animais de tal forma que lhes seja impedido levantar-se, deitar-se ou virar-se sobre si próprios;
+	c) Usar equipamentos de maneio, contenção ou treino, que causem sofrimento desnecessário ou lesões aos animais;
+	d) Incitar, realizar ou promover lutas entre animais de companhia, quando destas possa resultar sofrimento, lesões ou morte dos animais.
+	e) Criar cães e gatos para consumo, utilização ou comércio da sua carne, pele, pelo ou qualquer parte destes animais, excetuando-se as utilizações autorizadas para fins experimentais ou científicos;
+	f) Promover ou concretizar o sacrifício ritual de animais de companhia.
+4 - É proibido utilizar animais para fins didáticos e lúdicos, de treino, filmagens, exibições, publicidade ou atividades semelhantes, sempre que daí resultem para aqueles dor ou sofrimentos consideráveis, salvo experiência científica de comprovada necessidade e justificada nos termos da lei.
+Art. 75.º, n.º 8 - Em caso de abandono de animais ou em caso de incumprimento do dever de vigilância que tenha dado origem a uma agressão, os cães e gatos são devolvidos ao seu detentor após esterilização cirúrgica definitiva executada no centro de recolha a suas expensas.</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
@@ -919,27 +958,40 @@
         <is>
           <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
 2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
-3 — São proibidas todas as violências contra animais, considerando-se como tais os atos consistentes em, sem necessidade, se infligir a morte, o sofrimento ou lesões a um animal.</t>
+3 — São proibidas todas as violências contra animais, considerando-se como tais os atos consistentes em, sem necessidade, se infligir a morte, o sofrimento ou lesões a um animal.
+Lei n.º 92/95, de 12 de Setembro - PROTECÇÃO AOS ANIMAIS
+Artigo 1.º - Medidas gerais de protecção
+1 - São proibidas todas as violências injustificadas contra animais, considerando-se como tais os actos consistentes em, sem necessidade, se infligir a morte, o sofrimento cruel e prolongado ou graves lesões a um animal.
+2 - Os animais doentes, feridos ou em perigo devem, na medida do possível, ser socorridos.
+3 - São também proibidos os actos consistentes em:
+a) Exigir a um animal, em casos que não sejam de emergência, esforços ou actuações que, em virtude da sua condição, ele seja obviamente incapaz de realizar ou que estejam obviamente para além das suas possibilidades;
+b) Utilizar chicotes com nós, aguilhões com mais de 5 mm, ou outros instrumentos perfurantes, na condução de animais, com excepção dos usados na arte equestre e nas touradas autorizadas por lei;
+c) Adquirir ou dispor de um animal enfraquecido, doente, gasto ou idoso, que tenha vivido num ambiente doméstico, numa instalação comercial ou industrial ou outra, sob protecção e cuidados humanos, para qualquer fim que não seja o do seu tratamento e recuperação ou, no caso disso, a administração de uma morte imediata e condigna;
+d) Abandonar intencionalmente na via pública animais que tenham sido mantidos sob cuidado e protecção humanas, num ambiente doméstico ou numa instalação comercial ou industrial;
+e) Utilizar animais para fins didácticos, de treino, filmagens, exibições, publicidade ou actividades semelhantes, na medida em que daí resultem para eles dor ou sofrimentos consideráveis, salvo experiência científica de comprovada necessidade;
+f) Utilizar animais em treinos particularmente difíceis ou em experiências ou divertimentos consistentes em confrontar mortalmente animais uns contra os outros, salvo na prática da caça.
+g) Utilizar pombos como alvo na prática desportiva do tiro ao voo, incluindo treinos e provas.
+4 - As espécies de animais em perigo de extinção serão objecto de medidas de protecção, nomeadamente para preservação dos ecossistemas em que se enquadram.</t>
         </is>
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>O DL n.º 276/2001 (art.º 7.º) centra a responsabilidade no detentor em geral, sem distinguir o contexto de acolhimento temporário nem fixar limites numéricos de animais por família. O conceito de família de acolhimento é inexistente na legislação vigente.</t>
+          <t>O conceito de família de acolhimento é inexistente na legislação vigente.</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">
         <is>
-          <t>O @codigo não prevê o conceito de família de acolhimento nem qualquer limite numérico de animais por unidade. A responsabilidade do operador como figura distinta do detentor particular também não é contemplada.</t>
+          <t>O @codigo não prevê o conceito de família de acolhimento nem qualquer limite numérico de animais por unidade.</t>
         </is>
       </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac menciona famílias de acolhimento temporário mas não fixa o limite de 5 animais por família de acolhimento nem especifica que a responsabilidade jurídica recai sobre o operador e não sobre a família.</t>
+          <t>O @rgbeac menciona famílias de acolhimento temporário, mas não fixa o limite de 5 animais por família de acolhimento nem especifica que a responsabilidade jurídica recai sobre o operador e não sobre a família.</t>
         </is>
       </c>
       <c r="N4" s="11" t="inlineStr">
         <is>
-          <t>Lacuna transversal a toda a legislação nacional. Necessidade de: (1) criar o conceito de 'família de acolhimento' como extensão da atividade do operador; (2) fixar limite numérico de animais por família (máximo 5, ou 1 ninhada com mãe); (3) atribuir responsabilidade jurídica ao operador, não à família de acolhimento.</t>
+          <t>Necessidade de: (1) criar o conceito de 'família de acolhimento' como extensão da atividade do operador; (2) fixar limite numérico de animais por família (máximo 5, ou 1 ninhada com mãe); (3) atribuir responsabilidade jurídica ao operador, não à família de acolhimento.</t>
         </is>
       </c>
       <c r="O4" s="11" t="inlineStr">
@@ -947,104 +999,161 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="P4" s="11" t="inlineStr">
-        <is>
-          <t>(espaço para anotações da reunião)</t>
-        </is>
-      </c>
+      <c r="P4" s="11" t="inlineStr"/>
     </row>
     <row r="5" ht="120" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Estratégias de Criação — Conformação e Consanguinidade</t>
+          <t>Obrigações relativas às estratégias de reprodução</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Art.º 8.º-A do Regulamento 2023/0447</t>
+          <t>Art.º 8.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>1.	Operators of breeding establishments shall ensure that their breeding strategies minimise the risk of producing dogs or cats with genotypes associated with effects detrimental to the health and welfare of those animals.
-2.	Operators of breeding establishments shall not use for reproduction dogs or cats that have excessive conformational traits leading to a high risk of detrimental effects on the welfare of such dogs or cats, or of their offspring. Before selecting a dog or cat that might have an excessive conformational trait for breeding, the operator shall consult a veterinarian or an independent qualified person acting under the responsibility of a veterinarian. That veterinarian or independent qualified person shall assess whether the dog or cat has an excessive conformational trait.
-3.	The Commission is empowered to adopt delegated acts in accordance with Article 28 supplementing this Regulation by:
-(a)	defining characteristics of the genotypes referred to in paragraph 1 that are to be excluded from reproduction, and the methods for their assessment and the record keeping requirements;
-(b)	defining excessive conformational traits referred to in paragraph 2 of this Article that are to be excluded from reproduction, the methods for their assessment and the record keeping requirements.
-	When adopting those delegated acts, the Commission shall take into account the scientific opinion of the European Food Safety Authority (EFSA), as well as any social and economic impacts of those delegated acts.
-	The delegated acts concerning the excessive conformational traits shall be adopted by 1 July 2030. The delegated acts concerning the genotypes shall be adopted by 1 July 2036.
-4.	The following shall be prohibited when managing the reproduction of dogs and cats:
-(a)	breeding between parents and offspring, between siblings, between half-siblings or between grandparents and grandchildren, unless approved by the competent authority based on a specific need to preserve local breeds with a limited genetic pool;
-(b)	breeding for the purpose of producing hybrids.</t>
+          <t>Operators of breeding establishments shall ensure that their breeding strategies minimise the risk of producing dogs or cats with genotypes associated with effects detrimental to the health and welfare of those animals.
+Operators of breeding establishments shall not use for reproduction dogs or cats that have excessive conformational traits leading to a high risk of detrimental effects on the welfare of such dogs or cats, or of their offspring. Before selecting a dog or cat that might have an excessive conformational trait for breeding, the operator shall consult a veterinarian or an independent qualified person acting under the responsibility of a veterinarian. That veterinarian or independent qualified person shall assess whether the dog or cat has an excessive conformational trait.
+The Commission is empowered to adopt delegated acts in accordance with Article 28 supplementing this Regulation by:
+defining characteristics of the genotypes referred to in paragraph 1 that are to be excluded from reproduction, and the methods for their assessment and the record keeping requirements;
+defining excessive conformational traits referred to in paragraph 2 of this Article that are to be excluded from reproduction, the methods for their assessment and the record keeping requirements.
+When adopting those delegated acts, the Commission shall take into account the scientific opinion of the European Food Safety Authority (EFSA), as well as any social and economic impacts of those delegated acts.
+The delegated acts concerning the excessive conformational traits shall be adopted by 1 July 2030. The delegated acts concerning the genotypes shall be adopted by 1 July 2036.
+The following shall be prohibited when managing the reproduction of dogs and cats:
+breeding between parents and offspring, between siblings, between half-siblings or between grandparents and grandchildren, unless approved by the competent authority based on a specific need to preserve local breeds with a limited genetic pool;
+breeding for the purpose of producing hybrids.
+@regulamento — Health  ·  ANEXO I, Ponto 3 do Regulamento 2023/0447  |  EN
+Health
+Queens shall only be bred if their age is at least 10 months.
+Bitches shall only be bred as of their second oestrus.
+A bitch or queen shall not deliver more than 3 litters within a period of 2 years.
+For bitches and queens that have delivered 3 litters, including stillborns within a period of 2 years, there shall be a recuperation period of at least 1 year.
+Any bitch or queen that underwent two cesarean sections shall not be used for breeding.
+Before any bitch aged 8 years or more and any queen aged 6 years or more, is used for breeding, it must have been physically examined by a veterinarian who confirms in writing that, at the time of the examination, there are no counter-indications to pregnancy. 
+The operator shall keep the written confirmation referred to in point 3.4.b for a period of at least 3 years</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>1.	Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
-2.	Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem traços conformacionais excessivos que conduzam a um risco elevado de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por traço conformacional excessivo, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem um traço conformacional excessivo.
-3.	A Comissão tem competência para adotar atos delegados em conformidade com o artigo 28.º que complementem este Regulamento, definindo:
-(a)	características dos genótipos a que se refere o n.º 1 que devem ser excluídos da reprodução, e os métodos para a sua avaliação e requisitos de manutenção de registos;
-(b)	traços conformacionais excessivos a que se refere o n.º 2 do presente artigo que devem ser excluídos da reprodução, os métodos para a sua avaliação e requisitos de manutenção de registos.
-	Ao adotar esses atos delegados, a Comissão tem em conta os pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos (EFSA), bem como os impactos sociais e económicos desses atos delegados.
-	Os atos delegados relativos aos traços conformacionais excessivos devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
-4.	São proibidos na gestão da reprodução de cães e gatos:
-(a)	o cruzamento entre progenitores e descendentes, entre irmãos, entre meios-irmãos ou entre avós e netos, exceto com aprovação da autoridade competente por razão de necessidade específica de preservação de raças locais com reserva genética limitada;
-(b)	o cruzamento para produção de híbridos.</t>
+          <t>Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
+Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem características de conformação excessivas que acarretem um elevado risco de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por características de conformação excessivas, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem uma característica de conformação excessiva.
+A Comissão tem competência para adotar atos delegados em conformidade com o artigo 28.º que complementem este Regulamento, definindo:
+características dos genótipos a que se refere o n.º 1 que devem ser excluídos da reprodução, e os métodos para a sua avaliação e requisitos de manutenção de registos;
+características de conformação excessivas a que se refere o n.º 2 do presente artigo que devem ser excluídos da reprodução, os métodos para a sua avaliação e requisitos de manutenção de registos.
+Ao adotar esses atos delegados, a Comissão tem em conta os pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos (EFSA), bem como os impactos sociais e económicos desses atos delegados.
+Os atos delegados relativos aos traços conformacionais excessivos devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
+São proibidos na gestão da reprodução de cães e gatos:
+o cruzamento entre progenitores e descendentes, entre irmãos, entre meios-irmãos ou entre avós e netos, exceto com aprovação da autoridade competente por razão de necessidade específica de preservação de raças locais com reserva genética limitada;
+o cruzamento para produção de híbridos.
+@regulamento — Tradução PT-PT · ANEXO I, Ponto 3 do Regulamento 2023/0447
+As gatas só devem ser utilizadas para reprodução se tiverem, pelo menos, 10 meses de idade.
+As cadelas só devem ser utilizadas para reprodução a partir do seu segundo estro.
+Uma cadela ou gata não deve ter mais de 3 ninhadas num período de 2 anos.
+No caso de cadelas e gatas que tenham tido 3 ninhadas num período de 2 anos, incluindo nado-mortos, deve ser respeitado um período de recuperação de, pelo menos, 1 ano.
+Qualquer cadela ou gata que tenha sido submetida a duas cesarianas não pode ser utilizada para reprodução.
+Antes de qualquer cadela com 8 ou mais anos de idade e de qualquer gata com 6 ou mais anos de idade serem utilizadas para reprodução, devem ser submetidas a um exame físico por um médico veterinário que confirme, por escrito, que, à data do exame, não existem contraindicações para a gestação.
+O operador deve conservar a confirmação escrita referida no ponto 3.4.b por um período de, pelo menos, 3 anos.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>n.ºs 1 e 2 do art.º 34.º do RGBEAC (proposta, jun. 2025)</t>
+          <t>Art.º 70.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>1 — As intervenções cirúrgicas com o objetivo da modificação da aparência ou com fins não curativos ou não destinados a impedir a reprodução dos animais são proibidas, nos termos do disposto na alínea i) do n.º 1 do artigo 12.º.
-2 — O detentor de animal sujeito a intervenção curativa que modifique a sua aparência deve possuir documento comprovativo da necessidade da mesma, passado pelo médico veterinário que a ela procedeu, sob a forma de atestado do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura, ou, no caso de animais importados, documento comprovativo da necessidade dessa intervenção, emitida pelo médico veterinário que a ela procedeu, legalizado pela autoridade competente do respetivo país.</t>
+          <t>As condições de reprodução e criação de animais de companhia devem ser o mais análogas possível às de um ambiente doméstico, onde se espera que venham a viver após a sua transmissão.
+As cadelas podem reproduzir entre os dezoito meses e os seis anos de idade, até ao limite de quatro ninhadas com um intervalo mínimo de doze meses entre cada ninhada.
+As gatas podem reproduzir entre os doze meses e os seis anos de idade, até ao limite de quatro ninhadas com um intervalo mínimo de doze meses entre cada ninhada.
+Os cães e os gatos machos podem reproduzir entre os doze meses e os sete anos de idade.
+As crias não podem ser separadas da progenitora antes da décima semana de idade, no caso dos cães, e antes da décima segunda semana de idade, no caso dos gatos, salvaguardado um período de desmame gradual.
+Os animais reprodutores são inscritos como tal no SIAC e devem ter um temperamento amistoso e confiante relativamente a pessoas e outros animais, não devendo ser utilizados para reprodução animais perigosos ou que demonstrem comportamento agressivo ou excessivamente tímido.
+Os cães e gatos reprodutores são sujeitos aos testes genéticos, rastreios de saúde, coeficiente de consanguinidade e limite aplicável ao número de descendentes permitidos por macho reprodutor específicos para a raça em questão, conforme definidos em portaria do membro do Governo responsável pela Direção geral de alimentação e Veterinária 
+Os cães e gatos só podem ser usados para reprodução se, após parecer do médico veterinário assistente, não seja de esperar que a sua reprodução, com base no seu genótipo, fenótipo ou estado de saúde, tenha um efeito prejudicial para a sua saúde e bem-estar, ou para a saúde e bem-estar dos seus descendentes.
+Com base nos critérios referidos no número anterior, a reprodução de determinados animais ou determinadas raças de cães e gatos pode ser limitada por portaria referida no n.º 7. 
+As fêmeas que tenham sido sujeitas a uma cesariana apenas podem voltar a reproduzir mediante atestado do médico veterinário assistente, que ateste não ser de esperar que a sua reprodução tenha um efeito prejudicial à sua saúde ou bem-estar.
+Ambos os progenitores devem ser capazes de acasalar naturalmente, sendo a inseminação artificial restrita a situações excecionais previstas na portaria referida no n.º 7. 
+São vedadas a reprodução de fêmeas que tenham sido já sujeitas a duas cesarianas e a colheita de sémen por eletroejaculação.
+O detentor de animal reprodutor que deixe de poder ser usado para reprodução, nos termos do presente artigo, é obrigado a esterilizá-lo e a garantir o seu bem-estar e uma detenção responsável até ao final da sua vida, diretamente ou cedendo-o a terceiros nos termos do disposto nos artigos 42.º ou 91.º.</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>n.º 2, als. a), b) e c) do art.º 8.º do Código do Animal (DL n.º 214/2013)</t>
+          <t>Art.º 8.º do Código do Animal (DL n.º 214/2013)  -Reprodução e criação</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>2 — A reprodução de animais obedece ao seguinte:
-a) Os animais só devem ser utilizados na reprodução depois de atingida a maturidade reprodutiva para a espécie e raça devendo, no caso dos cães e gatos, seguir os parâmetros referidos no anexo I ao presente diploma, do qual faz parte integrante, não sendo autorizado, no caso das fêmeas, o acasalamento em cios sucessivos;
-b) Deve ser respeitada a regra do porte semelhante dos progenitores, para prevenir a possibilidade de distócia;
-c) Devem ser excluídos da reprodução, os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia da anca nos cães e rim poliquístico nos gatos, ou alterações comportamentais.</t>
+          <t>A reprodução de animais deve ser realizada de forma planeada.	
+A reprodução de animais obedece ao seguinte: 
+Os animais só devem ser utilizados na reprodução depois de atingida a maturidade reprodutiva para a espécie e raça devendo, no caso dos cães e gatos, seguir os parâmetros referidos no anexo I ao presente diploma, do qual faz parte integrante, não sendo autorizado, no caso das fêmeas, o acasalamento em cios sucessivos; 
+Deve ser respeitada a regra do porte semelhante dos progenitores, para prevenir a possibilidade de distócia; 
+Devem ser excluídos da reprodução, os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia da anca nos cães e rim poliquístico nos gatos, ou alterações comportamentais. 
+É proibida a atividade de criação resultante do cruzamento de espécies e raças diferentes, com exceção dos cruzamentos devidamente autorizados, com finalidade de melhoramento da raça ou investigação experimental e os cruzamentos de raças, em particular caninas, que tenham ocorrido acidentalmente e não tenham fins comerciais. 
+Anexo I – Normas mínimas de proteção animal para a reprodução (alínea a) do n.º 2 do artigo 53.º
+Parâmetros reprodutivos
+Canídeos - Machos
+Idade mínima para reprodução:
+Raças de pequeno e médio porte – 1,5 anos
+Raças de grande porte – 2 anos
+Idade máxima para reprodução: 12 anos ou mais, se o estatuto sanitário o permitir
+Reprodução no 1.º ciclo: Não definido
+Número de ninhadas por ano: Não definido
+Número de ninhadas durante a vida reprodutiva: Não definido 
+Intervalo mínimo entre parto e nova gestação: Não definido
+Canídeos - Fêmeas
+Idade mínima para reprodução:
+Raças de pequeno e médio porte – 3.º cio
+Raças de grande porte – 2 anos
+Idade máxima para reprodução: 8 anos, ou 5 anos se for a 1.ª gestação
+Reprodução no 1.º ciclo: Não
+Número de ninhadas por ano: 1
+Número de ninhadas durante a vida reprodutiva: 4–6
+Intervalo mínimo entre parto e nova gestação: 1 ciclo reprodutivo
+Felídeos - Machos
+Idade mínima para reprodução: 1 ano
+Idade máxima para reprodução: 12 anos
+Reprodução no 1.º ciclo: Não definido
+Número de ninhadas por ano: Não definido
+Número de ninhadas durante a vida reprodutiva: Não definido
+Intervalo mínimo entre parto e nova gestação: Não definido
+Felídeos - Fêmeas
+Idade mínima para reprodução: 1 ano
+Idade máxima para reprodução: 12 anos
+Reprodução no 1.º ciclo: Não
+Número de ninhadas por ano: 1 (ver abaixo)
+Número de ninhadas durante a vida reprodutiva: 8–10
+Intervalo mínimo entre parto e nova gestação: 3–6 meses
+N. B. As cadelas não devem ter mais de 2 ninhadas num período de 2 anos e as gatas não devem ultrapassar as 3 ninhadas no período de 2 anos, a menos que haja uma declaração de aprovação emitida pelo veterinário assistente</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>art.º 17.º e n.º 1 do art.º 18.º do DL n.º 276/2001, de 17 de outubro</t>
+          <t>Não há correspondência</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>Artigo 17.º — As intervenções cirúrgicas, nomeadamente as destinadas ao corte de caudas nos canídeos, têm de ser executadas por um médico veterinário.
-Artigo 18.º, n.º 1 — Os detentores de animais de companhia que os apresentem com quaisquer amputações que modifiquem a aparência dos animais ou com fins não curativos devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa amputação, nomeadamente discriminando que as mesmas foram feitas por razões médico-veterinárias ou no interesse particular do animal ou para impedir a reprodução.</t>
+          <t>n.º 3 do art. 8.º - As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar.</t>
         </is>
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>O DL n.º 276/2001 (art.ºs 17.º e 18.º) exige intervenção veterinária em cirurgias e documentação para amputações, mas não prevê qualquer restrição à reprodução por traços conformacionais excessivos nem proibição de consanguinidade próxima ou hibridação.</t>
+          <t>Breve referência. Sem equivalência</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>O @codigo (art.º 8.º, n.º 2) exclui da reprodução animais com defeitos genéticos e malformações (displasia, rim poliquístico) e proíbe cios sucessivos, mas não prevê o conceito de traços conformacionais excessivos nem a proibição de consanguinidade.</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>O @rgbeac (art.º 34.º) proíbe intervenções cirúrgicas de modificação da aparência, mas não contém qualquer norma sobre estratégia genética de criação, conformação excessiva ou consanguinidade.</t>
-        </is>
-      </c>
+          <t>O @codigo (art.º 8.º, n.º 2) exclui da reprodução animais com defeitos genéticos e malformações (monorquidia, displasia, rim poliquístico e alterações comportamentais) e proíbe cios sucessivos, mas não prevê o conceito de traços conformacionais excessivos nem a proibição de consanguinidade.</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr"/>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>Lacuna normativa transversal. Necessidade de criar norma específica que: (1) defina traços conformacionais excessivos (a regular por ato delegado europeu até 2030); (2) proíba consanguinidade próxima (pais/filhos, irmãos, avós/netos); (3) proíba a produção de híbridos; (4) imponha consulta veterinária prévia ao acasalamento de animais potencialmente afetados.</t>
+          <t>Introduzir conceito de características conformacionais excessivas (a regular por ato delegado europeu até 2030); (2) proibir consanguinidade próxima (pais/filhos, irmãos, avós/netos); (3) proibir a produção de híbridos; (4) impor consulta veterinária prévia ao acasalamento de animais potencialmente afetados. 
+ANNEX I, Ponto 3 estabelece requisitos técnicos obrigatórios de saúde reprodutiva. Recomenda-se: (i) incorporar idade mínima 10 meses (gatas) e 2º estro (cadelas); (ii) estabelecer máximo imperativo de 3 ninhadas em 2 anos (sem exceções veterinárias); (iii) exigir período de recuperação 1 ano após atingir limite; (iv) proibir uso após 2 cesarianas; (v) exigir avaliação veterinária escrita para cadelas ≥8 anos e gatas ≥6 anos.</t>
         </is>
       </c>
       <c r="O5" s="11" t="inlineStr">
@@ -1052,89 +1161,197 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="P5" s="11" t="inlineStr">
-        <is>
-          <t>(espaço para anotações da reunião)</t>
-        </is>
-      </c>
+      <c r="P5" s="11" t="inlineStr"/>
     </row>
     <row r="6" ht="120" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Reprodução e Criação</t>
+          <t>Notificação e registo dos estabelecimentos</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Art.º 9.º do Regulamento 2023/0447</t>
+          <t>Art.º 9.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>1.	Operators shall notify the competent authorities of their activity, providing at least the following information for each of their establishments:
-(a)	the name, address and contact details of the operator;
-(b)	the location of the establishment;
-(c)	the type of establishment: breeding establishment, selling establishment, shelter or foster home;
-(d)	the species and, for breeding establishments, the breeds of the dogs or cats kept in the establishment;
-(e)	the capacity of the establishment, expressed as the maximum number of dogs and cats which can be kept in the establishment;
-(f)	for breeding establishments, the estimated number of litters to be placed on the market per year.
-2.	Operators shall notify the competent authority of:
-(a)	any changes concerning the information referred to in paragraph 1;
-(b)	where applicable, the planned date of a cessation of their activities, at the latest five working days before that date.
-3.	Member States shall use the information provided in accordance with Article 84 of Regulation (EU) 2016/429. Operators shall not be required to notify the information already submitted in accordance with Article 84 of Regulation (EU) 2016/429 again.
-4.	The competent authority shall maintain a register of establishments. The competent authority may use for that purpose the register provided for in Article 101(1), point (a), of Regulation (EU) 2016/429.</t>
+          <t>Operators shall notify the competent authorities of their activity, providing at least the following information for each of their establishments:
+the name, address and contact details of the operator;
+the location of the establishment;
+the type of establishment: breeding establishment, selling establishment, shelter or foster home;
+the species and, for breeding establishments, the breeds of the dogs or cats kept in the establishment;
+the capacity of the establishment, expressed as the maximum number of dogs and cats which can be kept in the establishment;
+for breeding establishments, the estimated number of litters to be placed on the market per year.
+Operators shall notify the competent authority of:
+any changes concerning the information referred to in paragraph 1;
+where applicable, the planned date of a cessation of their activities, at the latest five working days before that date.
+Member States shall use the information provided in accordance with Article 84 of Regulation (EU) 2016/429. Operators shall not be required to notify the information already submitted in accordance with Article 84 of Regulation (EU) 2016/429 again. 
+The competent authority shall maintain a register of establishments. The competent authority may use for that purpose the register provided for in Article 101(1), point (a), of Regulation (EU) 2016/429.</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>1.	Os operadores devem notificar as autoridades competentes da sua atividade, fornecendo pelo menos as seguintes informações para cada um dos seus estabelecimentos:
-(a)	o nome, morada e contactos do operador;
-(b)	a localização do estabelecimento;
-(c)	o tipo de estabelecimento: estabelecimento de criação, estabelecimento de venda, abrigo ou família de acolhimento;
-(d)	as espécies e, para os estabelecimentos de criação, as raças dos cães ou gatos mantidos no estabelecimento;
-(e)	a capacidade do estabelecimento, expressa no número máximo de cães e gatos que podem ser alojados no estabelecimento;
-(f)	para os estabelecimentos de criação, o número estimado de ninhadas a colocar no mercado por ano.
-2.	Os operadores devem notificar a autoridade competente de:
-(a)	quaisquer alterações relativas às informações referidas no n.º 1;
-(b)	quando aplicável, a data prevista de cessação das suas atividades, o mais tardar cinco dias úteis antes dessa data.
+          <t>Os operadores devem notificar as autoridades competentes da sua atividade, fornecendo pelo menos as seguintes informações para cada um dos seus estabelecimentos:
+o nome, morada e contactos do operador;
+a localização do estabelecimento;
+o tipo de estabelecimento: estabelecimento de criação, estabelecimento de venda, abrigo ou família de acolhimento;
+as espécies e, para os estabelecimentos de criação, as raças dos cães ou gatos mantidos no estabelecimento;
+a capacidade do estabelecimento, expressa no número máximo de cães e gatos que podem ser alojados no estabelecimento;
+para os estabelecimentos de criação, o número estimado de ninhadas a colocar no mercado por ano.
+Os operadores devem notificar a autoridade competente de:
+quaisquer alterações relativas às informações referidas no n.º 1;
+quando aplicável, a data prevista de cessação das suas atividades, o mais tardar cinco dias úteis antes dessa data.
 3.	Os Estados-Membros devem utilizar as informações fornecidas em conformidade com o artigo 84.º do Regulamento (UE) 2016/429. Os operadores não são obrigados a notificar novamente as informações já apresentadas em conformidade com o artigo 84.º do Regulamento (UE) 2016/429.
 4.	A autoridade competente deve manter um registo dos estabelecimentos. A autoridade competente pode utilizar para esse efeito o registo previsto no artigo 101.º, n.º 1, alínea a), do Regulamento (UE) 2016/429.</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Art.º 43.º do RGBEAC (proposta, jun. 2025)</t>
+          <t>Artigo 60.º - Comunicação prévia com prazo</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>1 — Os centros de bem-estar animal procedem à esterilização dos animais recolhidos que se presuma terem sido abandonados, nos termos do artigo 41.º.
-2 — As câmaras municipais devem, sempre que necessário e sob a responsabilidade do médico veterinário municipal, incentivar e promover programas de esterilização de animais de companhia, nomeadamente os cães e gatos, em complementaridade com os centros de bem-estar animal.
-3 — Os requisitos mínimos das instalações adequadas à realização de esterilizações nos centros de bem-estar animal são estabelecidos em portaria do membro do Governo responsável pela área da agricultura.</t>
+          <t>1 - O exercício da atividade de exploração de alojamentos para hospedagem, incluindo os centros de bem-estar animal, com exceção dos alojamentos destinados exclusivamente à venda, depende de comunicação prévia com prazo.
+2 - A comunicação prévia com prazo dá lugar a um número de identificação do alojamento.
+3 - O disposto nos números anteriores não prejudica as obrigações devidas junto da Autoridade Tributária e Aduaneira.
+Artigo 61.º - Requisitos da comunicação prévia com prazo
+1 - A comunicação prévia com prazo a que se refere o n.º 1 do artigo anterior é dirigida pelo titular do alojamento à DGAV., e deve conter os seguintes elementos, quando aplicáveis:
+a) O nome ou a denominação social do interessado;
+b) A localização do alojamento e a sua designação comercial;
+c) O número de identificação fiscal ou de pessoa coletiva do interessado;
+d) Municípios integrantes, no caso dos centros de bem-estar animal intermunicipais;
+e) Caracterização das atividades a exercer;
+f) Identificação do médico veterinário responsável pelo alojamento;
+g) O número de celas de quarentena para isolamento de animais por suspeita de raiva, no caso dos centros de bem-estar animal;
+h) A capacidade máxima de animais a alojar e respetivas espécies;
+i) O número de animais detidos, espécies e raças;
+j) Parecer do médico veterinário responsável pelo alojamento, relativo à verificação das condições higiossanitárias e de bem-estar animal exigidas no presente decreto-lei
+k) Declaração de responsabilidade, subscrita pelo interessado, relativa ao cumprimento do presente decreto-lei e demais legislação aplicável aos animais de companhia.
+2 – O cumprimento dos requisitos referidos no número anterior pode ser objeto de verificação através da realização de vistoria pelo ICNF, I.P. (leia-se DGAV)  ou por entidade por este mandatada para o efeito.
+3 - A comunicação prévia com prazo é efetuada por via eletrónica, através do balcão único eletrónico de serviços a que se refere o artigo 6.º do Decreto-Lei n.º 92/2010, de 26 de julho.
+4 - Quando, por motivo de indisponibilidade das plataformas eletrónicas, não for possível o cumprimento do disposto no número anterior, a comunicação prévia pode ser efetuada por qualquer outro meio previsto na lei.
+5 - A comunicação prévia prazo produz efeitos trinta dias após o seu registo no balcão único eletrónico, com a exceção prevista no número seguinte.
+6 - Até trinta dias contados da data do registo da comunicação prévia no balcão único eletrónico, a DGAVpode, fundamentadamente, emitir ato administrativo de indeferimento, total ou parcial, da produção dos efeitos legais pretendidos pelo interessado.
+Artigo 62.º - Divulgação dos alojamentos (TRATADO NOUTRO TEMA)
+Artigo 63.º Alteração de funcionamento dos alojamentos
+ 1 - A alteração de funcionamento do alojamento, designadamente a modificação de qualquer dos elementos previstos no n.º 1 do art.º 61.º, é comunicada à DGAV pelo titular da exploração do mesmo, por via eletrónica, através do balcão único eletrónico dos serviços a que se refere o artigo 6.º do Decreto-Lei n.º 92/2010, de 26 de julho, no prazo de 15 dias contados da sua ocorrência.
+ 2 - A comunicação de obras de modificação estrutural nos alojamentos é acompanhada das respetivas plantas.
+3 - Compete à DGAV ICNF, I.P., atualizar as informações obtidas através das comunicações referidas nos números anteriores.
+4 - Quando, por motivo de indisponibilidade das plataformas eletrónicas, não for possível o cumprimento do disposto no n.º 1, as comunicações aí referidas podem ser efetuadas por qualquer outro meio previsto na lei.
+Artigo 64.º - Suspensão de atividade e encerramento dos alojamentos
+1 – A DGAV pode determinar a suspensão da atividade ou o encerramento do alojamento, designadamente quando se verifique uma das seguintes situações:
+a) Existência de riscos higiossanitários que ponham em causa a saúde das pessoas ou dos animais;
+b) Maus-tratos aos animais;
+c) Existência de graves problemas de saúde ou de bem-estar dos animais;
+d) Falta de condições de segurança e de tranquilidade para as pessoas ou para os animais, bem como de proteção do meio ambiente.
+2 – As situações referidas no número anterior são comprovadas em processo instruído pela DGAV, que elabora relatório com proposta de decisão a proferir pelo diretor-geral.
+3 – A decisão é de suspensão sempre que seja possível suprir, num curto prazo, a situação que a determinou.
+4 – A deliberação que determina a suspensão da atividade do alojamento fixa um prazo, não superior a 180 dias, durante o qual o titular deve proceder às alterações necessárias, sob pena de ser determinado o encerramento definitivo do alojamento.
+5 – A deliberação que determine o encerramento do alojamento é notificada ao respetivo titular, devendo o alojamento cessar a sua atividade no prazo fixado pela DGAV, o qual não deve exceder dez dias úteis, sob pena de ser solicitado às autoridades administrativas e policiais competentes o encerramento compulsivo.
+6 – Compete às câmaras municipais executar as medidas necessárias ao cumprimento da decisão a que se referem os números 3 e 5, procedendo os centros de bem-estar animal, quando necessário, à recolha dos animais.
+Artigo 65.º - Permissão de reabertura após suspensão da atividade
+1 – Após o decurso do prazo fixado nos termos do n.º 4 do artigo anterior, a DGAV realiza visita de controlo no prazo de 20 dias, a fim de verificar se se encontram reunidas condições para o levantamento da suspensão, mediante decisão de permissão de reabertura a proferir pelo diretor-geral.
+2 – Na falta de decisão do diretor-geral a que se refere o número anterior, no prazo de 30 dias contados do termo do prazo fixado nos termos do n.º 4 do artigo anterior, ou no prazo de 10 dias após a realização da visita de controlo, no caso de esta ser realizada, não há lugar a deferimento tácito, podendo o interessado obter a tutela adequada junto dos tribunais administrativos.
+3 – A permissão de reabertura é publicitada pelos meios utilizados para a divulgação da suspensão da atividade.
+Artigo 66.º - Divulgação da suspensão de atividade, do encerramento e da reabertura de alojamento
+As medidas previstas nos artigos 64.º e 65.º são publicitadas através do balcão único eletrónico dos serviços, a que se refere o artigo 6.º do Decreto-Lei n.º 92/2010, de 26 de julho, e no sítio na Internet da DGAV.
+Artigo 67.º - Reconhecimento mútuo
+1 - Não pode haver duplicação entre as condições exigíveis para o cumprimento dos procedimentos previstos no presente decreto-lei e os requisitos e os controlos equivalentes ou comparáveis, quanto à finalidade, a que o interessado já tenha sido submetido noutro Estado membro da União Europeia ou do Espaço Económico Europeu. 
+2 - O disposto no número anterior não é aplicável ao cumprimento das condições diretamente referentes às instalações físicas localizadas em território nacional, nem aos respetivos controlos por autoridade competente. 
+3 – O disposto no presente artigo não prejudica a legislação aplicável ao reconhecimento mútuo de requisitos relativos a qualificações.</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Art.º 8.º do Código do Animal (DL n.º 214/2013)</t>
+          <t>Artigo 31.º - Procedimento para o exercício da atividade de exploração de alojamentos</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>1 — A reprodução de animais deve ser realizada de forma planeada.
-2 — A reprodução de animais obedece ao seguinte:
-a) Os animais só devem ser utilizados na reprodução depois de atingida a maturidade reprodutiva para a espécie e raça devendo, no caso de cães e gatos, as fêmeas ter pelo menos dois anos de idade no momento da primeira cobertura;
-b) Deve ser respeitada a regra do porte semelhante dos progenitores, para prevenir a possibilidade de distócia;
-c) Devem ser excluídos da reprodução os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia.</t>
+          <t>Procedimento para o exercício da atividade de exploração de alojamentos Sem prejuízo do disposto no Decreto-Lei n.º 48/2011, de 1 de abril, alterado pelo Decreto-Lei n.º 141/2012, de 11 de julho, quanto aos estabelecimentos de comércio a retalho de animais de companhia, o exercício da atividade de exploração de alojamentos depende de:
+a) Mera comunicação prévia, no caso dos centros de recolha, alojamentos para hospedagem, com ou sem fins lucrativos, com exceção dos destinados exclusivamente à venda, sem prejuízo do disposto na alínea seguinte;
+b) Permissão administrativa, no caso dos alojamentos para hospedagem com fins lucrativos destinados à reprodução e criação de animais potencialmente perigosos, nomeadamente de cães das raças consideradas como potencialmente perigosas.
+Art. 32.º - MV responsável (tratado noutro tema)
+Artigo 33.º - Mera comunicação prévia
+A mera comunicação prévia a que se refere a alínea a) do artigo 31.º é dirigida à DGAV e deve conter os seguintes elementos, quando aplicáveis:
+a) O nome ou a denominação social do interessado;
+b) A localização do alojamento e a sua designação comercial;
+c) O número de identificação fiscal ou de pessoa coletiva do interessado;
+d) A identificação dos municípios integrantes, no caso dos centros de recolha intermunicipais;
+e) A caracterização das atividades a exercer;
+f) A indicação do médico veterinário responsável pelo alojamento;
+g) O número de celas de quarentena para isolamento de animais por suspeita de raiva, no caso dos centros de recolha;
+h) A capacidade máxima de animais e respetivas espécies a alojar;
+i) O número de animais detidos, espécies e raças;
+j) Declaração de responsabilidade, subscrita pelo interessado, relativa ao cumprimento de toda a legislação aplicável aos animais de companhia, nomeadamente em matéria de instalações, equipamentos, higiene, saúde e bem-estar dos animais.
+Artigo 34.º Pedido de permissão administrativa
+1 - O pedido de permissão administrativa a que se refere a alínea b) do n.º 1 do artigo 31.º é apresentado à DGAV e deve conter os seguintes elementos, quando aplicáveis:
+a) O nome ou a denominação social do interessado;
+b) A localização do alojamento e a sua designação comercial;
+c) O número de identificação fiscal ou de pessoa coletiva do interessado;
+d) A finalidade do alojamento;
+e) O número de animais a deter, respetivas espécies, raças e sexos;
+f) A identificação do médico veterinário responsável pelo alojamento.
+2 - O pedido de permissão administrativa é acompanhado dos seguintes documentos:
+a) Cópia dos documentos de identificação civil e fiscal do interessado ou, se aplicável, extrato em forma simples do teor das inscrições em vigor no registo comercial ou a indicação do código de certidão permanente de registo comercial;
+b) Declaração de responsabilidade, subscrita pelo interessado, relativa ao cumprimento da legislação aplicável aos animais de companhia, incluindo a legislação relativa a animais perigosos e potencialmente perigosos, nomeadamente em matéria de instalações, equipamentos, higiene, saúde e bem-estar;
+c) Descrição sumária dos alojamentos, com indicação do número de celas destinadas a animais, a respetiva função e indicação de outras instalações existentes, bem como das medidas de segurança adotadas.
+3 - O pedido de permissão administrativa é apresentado por via eletrónica, através do balcão único eletrónico de serviços a que se refere o artigo 6.º do Decreto-Lei n.º 92/2010, de 26 de julho.
+4 - Quando, por motivo de indisponibilidade das plataformas eletrónicas, não for possível o cumprimento do disposto no número anterior, o pedido de permissão administrativa pode ser apresentado por qualquer outro meio previsto na lei.
+Artigo 35.º Instrução do processo de permissão administrativa
+1 - Compete à direção de serviços veterinários da região de localização do alojamento a instrução do processo de permissão administrativa.
+2 - Para os efeitos previstos no número anterior, o serviço instrutor pode solicitar ao requerente, por uma vez, todos os esclarecimentos adicionais que considere essenciais para a apreciação do processo, fixando um prazo não superior a 10 dias para a resposta.
+3 - Em caso de fundadas dúvidas sobre os dados apresentados pelo requerente, o serviço instrutor pode requerer a exibição de documentos comprovativos dos referidos dados, fixando um prazo não superior a 10 dias para a resposta.
+4 - O cumprimento dos requisitos necessários para a atribuição de permissão administrativa é verificado através de visita de controlo a efetuar pela direção de serviços veterinários da respetiva região, no prazo de 30 dias a contar da data de receção do respetivo pedido ou dos elementos referidos nos n.os 2 e 3, quando solicitados.
+5 - No prazo de 15 dias a contar da data da visita de controlo, a direção de serviços veterinários da região conclui a instrução, elabora um relatório final com proposta de decisão e remete o processo, com os elementos dele constantes, ao diretor-geral de Alimentação e Veterinária, para decisão.
+Artigo 36.º Decisão
+1 - O diretor-geral de Alimentação e Veterinária profere decisão no prazo de 15 dias a contar da remessa do processo a que se refere o n.º 5 do artigo anterior.
+2 - Caso não seja proferida a decisão referida no número anterior no prazo de 60 dias contados da data de receção do pedido de permissão administrativa devidamente instruído, independentemente da realização de visita de controlo, não há lugar a deferimento tácito, podendo o interessado obter a tutela adequada junto dos tribunais administrativos.
+Artigo 37.º - Divulgação dos alojamentos (TRATADO NOUTRO TEMA)
+Artigo 38.º - Alteração de funcionamento dos alojamentos 
+1	— A alteração de funcionamento dos alojamentos, designadamente a modificação estrutural nos alojamentos, a transferência de titularidade, a cessão de exploração, a cessação da atividade e a alteração do médico responsável pelo alojamento, é comunicada à DGAV no prazo de 15 dias contados da sua ocorrência. 
+2	— A comunicação de obras de modificação estrutural nos alojamentos é acompanhada das respetivas plantas. 
+3	— Compete à DGAV atualizar as informações obtidas através das comunicações referidas nos números anteriores. 
+Artigo 39.º - Suspensão de atividade e encerramento dos alojamentos
+1 – O diretor-geral de Alimentação e Veterinária pode, mediante despacho, determinar a suspensão da atividade ou o encerramento do alojamento, designadamente quando se verifique uma das seguintes situações:
+a) Existência de riscos higiossanitários que ponham em causa a saúde das pessoas e/ou dos animais;
+b) Maus-tratos aos animais;
+c) Existência de graves problemas de saúde e de bem-estar dos animais;
+d) Falta de condições de segurança e de tranquilidade para as pessoas ou para os animais, bem como de proteção do meio ambiente.
+2 – As situações referidas no número anterior são comprovadas em processo instruído pela direção de serviços de alimentação e veterinária da região onde se localiza o alojamento, que elabora relatório com proposta de decisão a proferir pelo diretor-geral da Alimentação e Veterinária.
+3 – A decisão é de suspensão sempre que seja possível suprir, num curto prazo, a situação que a determinou.
+4 – O despacho que determina a suspensão da atividade do alojamento fixa um prazo, não superior a 180 dias, durante o qual o titular da exploração do alojamento deve proceder às alterações necessárias, sob pena de ser determinado o encerramento definitivo do alojamento.
+5 – O despacho que determine o encerramento do alojamento é notificado ao titular da exploração do alojamento, devendo o alojamento cessar a sua atividade no prazo fixado pela DGAV, o qual não deve exceder cinco dias úteis, sob pena de ser solicitado às autoridades administrativas e policiais competentes o encerramento compulsivo.
+6 – Compete às câmaras municipais executar as medidas necessárias ao cumprimento da decisão a que se referem os números 3 e 4, nomeadamente proceder, quando necessário, à recolha dos animais.
+Artigo 40.º - Permissão de reabertura após suspensão da atividade
+1 – Após o decurso do prazo fixado nos termos do n.º 4 do artigo anterior, a direção de serviços veterinários de alimentação e veterinária da região onde se localiza o alojamento realiza visita de controlo no prazo de 20 dias, a fim de verificar se se encontram reunidas as condições para o levantamento da suspensão, mediante decisão de permissão de reabertura a proferir pelo diretor-geral da Alimentação e Veterinária.
+2 – Na falta de decisão do diretor-geral de Alimentação e Veterinária a que se refere o número anterior, no prazo de 30 dias contados do termo do prazo fixado nos termos do n.º 4 do artigo anterior, ou no prazo de 10 dias após a realização da visita de controlo, no caso de esta ser realizada, não há lugar a deferimento tácito, podendo o interessado obter a tutela adequada junto dos tribunais administrativos.
+3 – A permissão de reabertura é publicitada pelos meios utilizados para a divulgação da suspensão da permissão.
+Artigo 41.° - Divulgação da suspensão de atividade, do encerramento e da reabertura de alojamento 
+As medidas previstas nos artigos 39.º e 40.º são publicitadas através do balcão único electrónico de serviços, a que se refere o artigo 6.º do Decreto-Lei n.º 92/2010, de 26 de julho, e no sítio na Internet da DGAV. 
+Artigo 42.º - Reconhecimento mútuo  
+1	- Não pode haver duplicação entre as condições exigíveis para o cumprimento dos procedimentos previstos no presente diploma e os requisitos e os controlos equivalentes ou comparáveis, quanto à finalidade, a que o interessado já tenha sido submetido noutro Estado membro da União Europeia ou do Espaço Económico Europeu. 
+2	- O disposto no número anterior não é aplicável ao cumprimento das condições diretamente referentes às instalações físicas localizadas em território nacional, nem aos respetivos controlos por autoridade competente.</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>n.º 1 do art.º 3.º-A do DL n.º 276/2001, de 17 de outubro</t>
+          <t>Artigo 3.º</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>1 — A mera comunicação prévia a que se refere a alínea a) do n.º 1 do artigo anterior é dirigida à DGAV e deve conter os seguintes elementos, quando aplicáveis:
+          <t>Procedimento para o exercício da atividade de exploração de alojamentos e criação comercial de animais de companhia
+1 - Sem prejuízo do disposto no Decreto-Lei n.º 10/2015, de 16 de janeiro, quanto aos estabelecimentos de comércio a retalho de animais de companhia, o exercício da atividade de exploração de alojamentos, bem como a atividade de criação comercial de animais de companhia depende de:
+a) Mera comunicação prévia, no caso dos centros de recolha, alojamentos para hospedagem, com ou sem fins lucrativos, criação comercial de animais de companhia, em qualquer caso com exceção dos destinados exclusivamente à venda, sem prejuízo do disposto na alínea seguinte;
+b) Permissão administrativa, no caso dos alojamentos para hospedagem com fins lucrativos destinados à reprodução e criação de animais potencialmente perigosos, nomeadamente de cães das raças consideradas como potencialmente perigosas.
+11 - A comunicação prévia ou a permissão administrativa dão lugar a um número de identificação, o qual é pessoal e intransmissível.
+12 - A DGAV publicita, no seu sítio de Internet, os nomes dos criadores comerciais de animais de companhia e respetivo município de atividade e número de identificação.
+13 - O disposto nos números anteriores não prejudica as obrigações devidas junto da Autoridade Tributária e Aduaneira."
+N.º 1 do Art.º 3.º-A  - Mera comunicação prévia
+A mera comunicação prévia a que se refere a alínea a) do n.º 1 do artigo anterior é dirigida à DGAV e deve conter os seguintes elementos, quando aplicáveis:
 a) O nome ou a denominação social do interessado;
 b) A localização do alojamento e a sua designação comercial;
 c) O número de identificação fiscal ou de pessoa coletiva do interessado;
@@ -1144,27 +1361,76 @@
 g) O número de celas de quarentena para isolamento de animais por suspeita de raiva, no caso dos centros de recolha;
 h) A capacidade máxima de animais e respetivas espécies a alojar;
 i) O número de animais detidos, espécies e raças;
-j) Declaração de responsabilidade, subscrita pelo interessado, relativa ao cumprimento da legislação aplicável aos animais de companhia, nomeadamente em matéria de instalações, equipamentos, higiene, saúde e bem-estar dos animais.</t>
+j) Declaração de responsabilidade, subscrita pelo interessado, relativa ao cumprimento da legislação aplicável aos animais de companhia, nomeadamente em matéria de instalações, equipamentos, higiene, saúde e bem-estar dos animais.
+Artigo 3.º-B Permissão administrativa
+1 - O pedido de permissão administrativa a que se refere a alínea b) do n.º 1 do artigo 3.º é apresentado à DGAV e deve conter os seguintes elementos, quando aplicáveis:
+a) O nome ou a denominação social do interessado;
+b) A localização do alojamento e a sua designação comercial;
+c) O número de identificação fiscal ou de pessoa coletiva do interessado;
+d) A finalidade do alojamento;
+e) O número de animais a deter, respetivas espécies, raças e sexos;
+f) A identificação do médico veterinário responsável pelo alojamento.
+2 - O pedido de permissão administrativa é acompanhado dos seguintes documentos:
+a) Cópia dos documentos de identificação civil e fiscal do interessado ou, se aplicável, extrato em forma simples do teor das inscrições em vigor no registo comercial ou a indicação do código de certidão permanente de registo comercial;
+b) Declaração de responsabilidade, subscrita pelo interessado, relativa ao cumprimento da legislação aplicável aos animais de companhia, incluindo a legislação relativa a animais perigosos e potencialmente perigosos, nomeadamente em matéria de instalações, equipamentos, higiene, saúde e bem-estar;
+c) Descrição sumária dos alojamentos, com indicação do número de celas destinadas a animais, a respetiva função e indicação de outras instalações existentes, bem como das medidas de segurança adotadas.
+3 - O pedido de permissão administrativa é apresentado por via eletrónica, através do balcão único eletrónico de serviços a que se refere o artigo 6.º do Decreto-Lei n.º 92/2010, de 26 de julho.
+4 - Quando, por motivo de indisponibilidade das plataformas eletrónicas, não for possível o cumprimento do disposto no número anterior, o pedido de permissão administrativa pode ser apresentado por qualquer outro meio previsto na lei.
+Artigo 3.º-C Instrução do processo de permissão administrativa
+1 - Compete à direção de serviços veterinários da região de localização do alojamento a instrução do processo de permissão administrativa.
+2 - Para os efeitos previstos no número anterior, o serviço instrutor pode solicitar ao requerente, por uma vez, todos os esclarecimentos adicionais que considere essenciais para a apreciação do processo, fixando um prazo não superior a 10 dias para a resposta.
+3 - Em caso de fundadas dúvidas sobre os dados apresentados pelo requerente, o serviço instrutor pode requerer a exibição de documentos comprovativos dos referidos dados, fixando um prazo não superior a 10 dias para a resposta.
+4 - O cumprimento dos requisitos necessários para a atribuição de permissão administrativa é verificado através de visita de controlo a efetuar pela direção de serviços veterinários da respetiva região, no prazo de 30 dias a contar da data de receção do respetivo pedido ou dos elementos referidos nos n.os 2 e 3, quando solicitados.
+5 - No prazo de 15 dias a contar da data da visita de controlo, a direção de serviços veterinários da região conclui a instrução, elabora um relatório final com proposta de decisão e remete o processo, com os elementos dele constantes, ao diretor-geral de Alimentação e Veterinária, para decisão.
+Artigo 3.º-D Decisão
+1 - O diretor-geral de Alimentação e Veterinária profere decisão no prazo de 15 dias a contar da remessa do processo a que se refere o n.º 5 do artigo anterior.
+2 - Caso não seja proferida a decisão referida no número anterior no prazo de 60 dias contados da data de receção do pedido de permissão administrativa devidamente instruído, independentemente da realização de visita de controlo, não há lugar a deferimento tácito, podendo o interessado obter a tutela adequada junto dos tribunais administrativos.
+Artigo 3.º-E Divulgação (tratado abaixo)
+  Artigo 3.º-F Alteração de funcionamento dos alojamentos
+1 - A alteração de funcionamento dos alojamentos, designadamente a modificação estrutural nos alojamentos, a transferência de titularidade, a cessão de exploração, a cessação da atividade e a alteração do médico veterinário responsável pelo alojamento, é comunicada à DGAV por via eletrónica, através do balcão único eletrónico dos serviços a que se refere o artigo 6.º do Decreto-Lei n.º 92/2010, de 26 de julho, no prazo de 15 dias contados da sua ocorrência.
+2 - A comunicação de obras de modificação estrutural nos alojamentos é acompanhada das respetivas plantas.
+3 - Compete à DGAV atualizar as informações obtidas através das comunicações referidas nos números anteriores.
+4 - Quando, por motivo de indisponibilidade das plataformas eletrónicas, não for possível o cumprimento do disposto no n.º 1, as comunicações aí referidas podem ser efetuadas por qualquer outro meio previsto na lei."
+Artigo 3.º-G
+Suspensão de atividade e encerramento dos alojamentos
+1 - O diretor-geral de Alimentação e Veterinária pode, mediante despacho, determinar a suspensão da atividade ou o encerramento do alojamento, designadamente quando se verifique uma das seguintes situações:
+a) Existência de riscos higiossanitários que ponham em causa a saúde das pessoas e ou dos animais;
+b) Maus tratos aos animais;
+c) Existência de graves problemas de saúde e bem-estar dos animais;
+d) Falta de condições de segurança e de tranquilidade para as pessoas ou animais, bem como de proteção do meio ambiente.
+2 - As situações referidas no número anterior são comprovadas em processo instruído pela direção de serviços veterinários da região onde se localiza o alojamento, que elabora relatório com proposta de decisão a proferir pelo diretor-geral da Alimentação e Veterinária.
+3 - A decisão é de suspensão sempre que seja possível suprir, num curto prazo, a situação que a determinou.
+4 - O despacho que determina a suspensão da atividade do alojamento fixa um prazo, não superior a 180 dias, durante o qual o titular da exploração do alojamento deve proceder às alterações necessárias, sob pena de ser determinado o encerramento definitivo do alojamento.
+5 - O despacho que determine o encerramento do alojamento é notificado ao titular da exploração do alojamento, devendo o alojamento cessar a sua atividade no prazo fixado pela DGAV, o qual não deve exceder cinco dias úteis, sob pena de ser solicitado às autoridades administrativas e policiais competentes o encerramento compulsivo.
+6 - Compete às câmaras municipais executar as medidas necessárias ao cumprimento da decisão a que se referem os n.os 3 e 4, nomeadamente proceder, quando necessário, à recolha dos animais.
+Artigo 3.º-H Permissão de reabertura após suspensão da actividade
+1 - Após o decurso do prazo fixado nos termos do n.º 4 do artigo anterior, a direção de serviços veterinários da região onde se localiza o alojamento realiza visita de controlo no prazo de 20 dias, a fim de verificar se se encontram reunidas condições para o levantamento da suspensão, mediante decisão de permissão de reabertura a proferir pelo diretor-geral de Alimentação e Veterinária.
+2 - Na falta da decisão do diretor-geral de Alimentação e Veterinária a que se refere o número anterior no prazo de 30 dias contados do termo do prazo fixado nos termos do n.º 4 do artigo anterior, ou no prazo de 10 dias após a realização de visita de controlo, no caso de esta ser realizada, não há lugar a deferimento tácito, podendo o interessado obter a tutela adequada junto dos tribunais administrativos.
+3 - A permissão de reabertura é publicitada pelos meios utilizados para a divulgação da suspensão da permissão.
+  Artigo 3.º-I Divulgação da suspensão de atividade, do encerramento e da reabertura de alojamento
+As medidas previstas nos artigos 3.º-G e 3.º-H são publicitadas através do balcão único eletrónico dos serviços, a que se refere o artigo 6.º do Decreto-Lei n.º 92/2010, de 26 de julho, e no sítio na Internet da DGAV.</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>O DL n.º 276/2001 (art.º 3.º-A) prevê comunicação prévia à DGAV com elementos parcialmente equivalentes (capacidade máxima, espécies, raças). Não exige a estimativa anual de ninhadas a colocar no mercado (al. ea) do @regulamento), constituindo lacuna parcial. É o diploma mais próximo do @regulamento neste eixo.</t>
+          <t>Não exige a estimativa anual de ninhadas a colocar no mercado (al. ea) do @regulamento), constituindo lacuna parcial.</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>O @codigo regula condições de reprodução (art.º 8.º) mas não prevê qualquer sistema de notificação ou registo de estabelecimentos criadores junto da autoridade competente.</t>
+          <t>Alterações de funcionamento
+Comunicação à DGAV, sem referência a via eletrónica, balcão único</t>
         </is>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac trata da esterilização de errantes e CED, mas não contém norma sobre notificação de criadores ou registo de estabelecimentos com fins de reprodução comercial.</t>
+          <t>O RGBEAC substitui a mera comunicação prévia por um modelo que abre lugar à fiscalização preventiva quando se aparente justificar, e permite à DGAV travar o início da atividade antes da produção de efeitos ao fim de 30 dias.
+O artigo 63.º, abre o leque, não nomeia as alterações, remete para qualquer “modificação de qualquer dos elementos previstos no n.º 1 do artigo 61.º</t>
         </is>
       </c>
       <c r="N6" s="11" t="inlineStr">
         <is>
-          <t>A @legislacao vigente é o diploma base adequado para a transposição. Necessidade de ajuste: acrescentar a obrigação de estimativa anual de ninhadas a colocar no mercado e alinhar os restantes elementos informativos com a lista exaustiva do art.º 7.º do @regulamento.</t>
+          <t>Necessidade de ajuste: acrescentar a obrigação de estimativa anual de ninhadas a colocar no mercado e alinhar os restantes elementos informativos com a lista exaustiva do art.º 7.º do @regulamento.</t>
         </is>
       </c>
       <c r="O6" s="11" t="inlineStr">
@@ -1172,11 +1438,7 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="P6" s="11" t="inlineStr">
-        <is>
-          <t>(espaço para anotações da reunião)</t>
-        </is>
-      </c>
+      <c r="P6" s="11" t="inlineStr"/>
     </row>
     <row r="7" ht="120" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -1186,61 +1448,64 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Art.º 10.º do Regulamento 2023/0447</t>
+          <t>Art.º 10.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>1.	Operators of breeding establishments that either produce or intend to produce more than five litters per calendar year or that keep more than a combined total of five bitches or queens at any given time shall place dogs or cats on the market only after their establishment has been approved by the competent authority.
-2.	The competent authority shall perform on-site inspections to verify that the establishment meets the requirements of this Regulation. Member States may allow such inspections to be carried out remotely, provided that the means of distance communication used provides sufficient evidence for the competent authority to perform reliable inspections. The competent authority shall grant certificates of approval only to breeding establishments that meet the requirements of this Regulation.
-3.	The competent authority shall maintain a publicly available list including the following information for each approved establishment:
-(a)	the name, contact details and, where available, the URL of the website of the establishment;
-(b)	the address of the establishment;
-(c)	the name of the operator;
-(d)	the species and, if relevant, the breeds related to the establishment activities approved;
-(e)	the unique approval number assigned to the establishment by the competent authority and the date of the approval and cessation of activities.</t>
+          <t>Operators of breeding establishments that either produce or intend to produce more than five litters per calendar year or that keep more than a combined total of five bitches or queens at any given time shall place dogs or cats on the market only after their establishment has been approved by the competent authority.
+The competent authority shall perform on-site inspections to verify that the establishment meets the requirements of this Regulation. Member States may allow such inspections to be carried out remotely, provided that the means of distance communication used provides sufficient evidence for the competent authority to perform reliable inspections. The competent authority shall grant certificates of approval only to breeding establishments that meet the requirements of this Regulation.
+The competent authority shall maintain a publicly available list including the following information for each approved establishment:
+the name, contact details and, where available, the URL of the website of the establishment;
+the address of the establishment;
+the name of the operator;
+the species and, if relevant, the breeds related to the establishment activities approved;
+the unique approval number assigned to the establishment by the competent authority and the date of the approval and cessation of activities.</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1.	Os operadores de estabelecimentos de criação que produzem ou pretendem produzir mais de cinco ninhadas por ano civil ou que mantêm mais do que um total combinado de cinco cadelas ou gatas em qualquer momento podem colocar cães ou gatos no mercado apenas após a aprovação do seu estabelecimento pela autoridade competente.
-2.	A autoridade competente deve realizar inspeções no local para verificar que o estabelecimento atende aos requisitos do presente Regulamento. Os Estados-Membros podem permitir que tais inspeções sejam realizadas remotamente, desde que o meio de comunicação à distância utilizado forneça provas suficientes para a autoridade competente realizar inspeções fiáveis. A autoridade competente deve conceder certificados de aprovação apenas aos estabelecimentos de criação que cumprem os requisitos do presente Regulamento.
-3.	A autoridade competente deve manter uma lista disponível ao público incluindo as seguintes informações para cada estabelecimento aprovado:
-(a)	o nome, dados de contacto e, se disponível, o URL do site do estabelecimento;
-(b)	a morada do estabelecimento;
-(c)	o nome do operador;
-(d)	a(s) espécie(s) e, se relevante, a(s) raça(s) relacionada(s) com as atividades do estabelecimento aprovadas;
-(e)	o número de aprovação único atribuído ao estabelecimento pela autoridade competente e a data da aprovação e cessação de atividades.</t>
+          <t>Os operadores de estabelecimentos de criação que produzem ou pretendem produzir mais de cinco ninhadas por ano civil ou que mantêm mais do que um total combinado de cinco cadelas ou gatas em qualquer momento podem colocar cães ou gatos no mercado apenas após a aprovação do seu estabelecimento pela autoridade competente.
+A autoridade competente deve realizar inspeções no local para verificar que o estabelecimento atende aos requisitos do presente Regulamento. Os Estados-Membros podem permitir que tais inspeções sejam realizadas remotamente, desde que o meio de comunicação à distância utilizado forneça provas suficientes para a autoridade competente realizar inspeções fiáveis. A autoridade competente deve conceder certificados de aprovação apenas aos estabelecimentos de criação que cumprem os requisitos do presente Regulamento.
+A autoridade competente deve manter uma lista disponível ao público incluindo as seguintes informações para cada estabelecimento aprovado:
+o nome, dados de contacto e, se disponível, o URL do site do estabelecimento;
+a morada do estabelecimento;
+o nome do operador;
+a(s) espécie(s) e, se relevante, a(s) raça(s) relacionada(s) com as atividades do estabelecimento aprovadas;
+o número de aprovação único atribuído ao estabelecimento pela autoridade competente e a data da aprovação e cessação de atividades.</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Artigo 62.º - Divulgação dos alojamentos</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>A DGAV publicita no balcão único eletrónico de serviços, a que se refere o artigo 6.º do Decreto-Lei n.º 92/2010, de 26 de julho, e no seu sítio na Internet a lista dos centros de bem-estar animal, bem como de todos os alojamentos para hospedagem de animais de companhia, em relação aos quais tenha recebido comunicação prévia com prazo, nos termos do presente decreto-lei, incluindo os criadores de animais de companhia, respetivo município de atividade e número de identificação.</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Artigo 37.º - Divulgação dos alojamentos</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>A DGAV publicita no balcão único electrónico de serviços, a que se refere o artigo 6.º do Decreto-Lei n.º 92/2010, de 26 de julho e no seu sítio na Internet, a lista dos centros de recolha, bem como de todos os alojamentos de hospedagem, com ou sem fins lucrativos, que haja permitido ou em relação aos quais tenha recebido mera comunicação prévia, nos termos do presente diploma.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Havia a Permissão Administrativa apenas no caso de criação/reprodução de cães PP, conforme art. 3.º-B</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Art.º 3.º, n.º 12
+A DGAV publicita, no seu sítio de Internet, os nomes dos criadores comerciais de animais de companhia e respetivo município de atividade e número de identificação.
+Art.º3.º E - Divulgação dos alojamentos
+DGAV publicita no balcão único eletrónico de serviços, a que se refere o artigo 6.º do Decreto-Lei n.º 92/2010, de 26 de julho, e no seu sítio na Internet a lista dos centros de recolha oficiais, bem como de todos os centros de hospedagem, com ou sem fins lucrativos, que haja permitido ou em relação aos quais tenha recebido mera comunicação prévia, nos termos do presente diploma.</t>
         </is>
       </c>
       <c r="K7" s="8" t="inlineStr">
@@ -1248,19 +1513,12 @@
           <t>Conceito novo de ‘aprovação’ com limiar (&gt;5 ninhadas/ano ou &gt;5 cadelas/gatas)</t>
         </is>
       </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>Não implementado</t>
-        </is>
-      </c>
-      <c r="M7" s="10" t="inlineStr">
-        <is>
-          <t>Não implementado</t>
-        </is>
-      </c>
+      <c r="L7" s="9" t="inlineStr"/>
+      <c r="M7" s="10" t="inlineStr"/>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>Artigo completamente novo no Regulamento. Introduz aprovação formal de criadores com limiar numérico.</t>
+          <t>Artigo novo no Regulamento, introduz aprovação formal de criadores com limiar numérico para ninhadas ou fêmeas no local.
+A publicitação prevista pelo @regulamento inclui mais informação do que a legislação vigente ou em proposta.</t>
         </is>
       </c>
       <c r="O7" s="11" t="inlineStr">
@@ -1268,38 +1526,34 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="P7" s="11" t="inlineStr">
-        <is>
-          <t>Análise e correspondência nacional pendente de complementação.</t>
-        </is>
-      </c>
+      <c r="P7" s="11" t="inlineStr"/>
     </row>
     <row r="8" ht="120" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Detenção Responsável e Informação</t>
+          <t>Obrigação de informação de detenção responsável</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Art.º 11.º do Regulamento 2023/0447</t>
+          <t>Art.º 11.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>1.	Operators shall provide to the acquirer of a dog or cat written information necessary to enable the acquirer to ensure the animal’s welfare, including information on responsible ownership and on the specific needs of the animal in terms of feeding, care, health and housing, as well as information on its behavioural needs and health history.
-2.	The written information on the dog or cat’s health history referred to in the first paragraph shall include at least:
-(a)	the animal’s vaccination status;
-(b)	any medical conditions or predispositions to diseases, including allergies, that are known to the operator, and any diagnostic test results for the dog or cat that are available to the operator.
+          <t>Operators shall provide the acquirer of a dog or cat written information necessary to enable the acquirer to ensure the animal’s welfare, including information on responsible ownership and on the specific needs of the animal in terms of feeding, care, health and housing, as well as information on its behavioural needs and health history.
+The written information on the dog or cat’s health history referred to in the first paragraph shall include at least:
+the animal’s vaccination status;
+any medical conditions or predispositions to diseases, including allergies, that are known to the operator, and any diagnostic test results for the dog or cat that are available to the operator.
 Where the information on the animal’s health history is set out in a document required under Regulation (EU) 2016/429, the operator shall transmit that document to the acquirer.</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>1.	Os operadores devem fornecer ao adquirente de um cão ou gato informação escrita necessária para lhe permitir assegurar o bem-estar do cão ou gato, incluindo informação sobre detenção responsável e sobre as necessidades específicas do cão ou gato em termos de alimentação, cuidados, saúde e alojamento, bem como informação sobre as suas necessidades comportamentais e historial de saúde.
-2.	A informação escrita sobre o historial de saúde do cão ou gato referida no n.º 1 deve incluir pelo menos:
-(a)	o estado de vacinação do cão ou gato;
-(b)	quaisquer condições médicas ou predisposições a doenças, incluindo alergias, conhecidas pelo operador, e quaisquer resultados de testes de diagnóstico para o cão ou gato que estejam disponíveis para o operador.
+          <t>Os operadores devem fornecer ao adquirente de um cão ou gato informação escrita necessária para lhe permitir assegurar o bem-estar do cão ou gato, incluindo informação sobre detenção responsável e sobre as necessidades específicas do cão ou gato em termos de alimentação, cuidados, saúde e alojamento, bem como informação sobre as suas necessidades comportamentais e historial de saúde.
+A informação escrita sobre o historial de saúde do cão ou gato referida no n.º 1 deve incluir pelo menos:
+o estado de vacinação do cão ou gato;
+quaisquer condições médicas ou predisposições a doenças, incluindo alergias, conhecidas pelo operador, e quaisquer resultados de testes de diagnóstico para o cão ou gato que estejam disponíveis para o operador.
 Caso a informação sobre o historial de saúde do cão ou gato esteja prevista num documento exigido nos termos do Regulamento (UE) 2016/429, o operador deve transmitir esse documento ao adquirente.</t>
         </is>
       </c>
@@ -1321,45 +1575,41 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>1 — O detentor do animal deve ter acesso a informação sobre:
-a) As obrigações inerentes à sua detenção, direitos e responsabilidades;
-b) As normas de bem-estar, cuidados de saúde e comportamento esperado;
-c) As necessidades específicas da espécie ou raça;
-d) A duração de vida esperada;
-e) Os custos de manutenção;
-f) A proibição de abandono.
-2 — Os criadores e comerciantes devem fornecer informação escrita completa ao adquirente antes da transferência do animal, incluindo dados de identificação e cuidados de saúde.</t>
+          <t>O detentor do animal deve ter acesso à informação sobre:
+As obrigações inerentes à sua detenção, direitos e responsabilidades;
+As normas de bem-estar, cuidados de saúde e comportamento esperado;
+As necessidades específicas da espécie ou raça;
+A duração de vida esperada;
+Os custos de manutenção;
+A proibição de abandono.
+Os criadores e comerciantes devem fornecer informação escrita completa ao adquirente antes da transferência do animal, incluindo dados de identificação e cuidados de saúde.</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>Art.º 20.º do DL n.º 276/2001, de 17 de outubro</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>1 — O proprietário ou detentor de animal de companhia deve ter acesso a informação adequada sobre as suas obrigações relativas ao bem-estar do animal.
-2 — Os detentores de animais de companhia que os comercializem devem fornecer informação ao adquirente sobre o estado de saúde do animal e vacinas efetuadas.</t>
-        </is>
-      </c>
+          <t>Sem equivalência</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr"/>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>O DL n.º 276/2001 (art.º 20.º) é genérico e não especifica a forma escrita nem detalhes de conteúdo. O @regulamento exige informação escrita sobre necessidades específicas de bem-estar (alimentação, cuidados, saúde, alojamento, comportamento) e condiciona a transferência à transmissão dessa informação.</t>
+          <t>Sem equivalência</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>O @codigo (art.º 57.º) exige informação escrita mas com âmbito mais amplo (duração de vida, custos) do que o @regulamento, que se foca especificamente em bem-estar e saúde.</t>
+          <t>Faltam alguns elementos</t>
         </is>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac (art.º 8.º) aproxima-se do conteúdo do @regulamento, exigindo informação escrita antes da transferência, incluindo dados de saúde e vacinação, mas ainda sem o enfoque específico em bem-estar comportamental.</t>
+          <t>Recupera todos os elementos do @código
+Faltam alguns elementos em relação ao @regulamento</t>
         </is>
       </c>
       <c r="N8" s="11" t="inlineStr">
         <is>
-          <t>Necessidade de alteração: (1) formalizar requisito de informação escrita como condição de transferência de animal; (2) especificar conteúdo obrigatório sobre bem-estar, saúde e necessidades comportamentais; (3) harmonizar entre @codigo e @rgbeac quanto a âmbito e forma.</t>
+          <t>Necessidade de alteração: introduzir quaisquer condições médicas ou predisposições a doenças, incluindo alergias, conhecidas pelo operador, e quaisquer resultados de testes de diagnóstico para o cão ou gato que estejam disponíveis para o operador.</t>
         </is>
       </c>
       <c r="O8" s="11" t="inlineStr">
@@ -1367,11 +1617,7 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="P8" s="11" t="inlineStr">
-        <is>
-          <t>(espaço para anotações da reunião)</t>
-        </is>
-      </c>
+      <c r="P8" s="11" t="inlineStr"/>
     </row>
     <row r="9" ht="120" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -1381,33 +1627,35 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Art.º 12.º do Regulamento 2023/0447</t>
+          <t>Art.º 12.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>1.	Animal carers, other than volunteers in shelters and interns who are acting under the responsibility of a competent animal carer, shall have the following competences as regards the dogs and cats they are handling:
-(a)	an understanding of the animals’ biological behaviour and their physiological and ethological needs;
-(b)	the ability to recognise the animals’ expressions, including any sign of suffering, and to identify and to take the appropriate mitigating measures  in such cases;
-(c)	the ability to apply good animal management practices, including operant conditioning and positive reinforcement, to use and maintain the equipment used for the dogs or cats under their care and to minimise any risks to the welfare of those dogs or cats, preventing them from suffering;
-(d)	knowledge of the carers’ obligations under this Regulation.
-2.	The competences referred to in paragraph 1 may be acquired through education, training or professional experience. Only documented education, training or professional experience shall be taken into account when determining whether an animal carer has the competences referred to in paragraph 1.
-3.	Operators shall ensure that at least one animal carer, other than a volunteer or intern, at the establishment has completed the training courses referred to in Article 22. Operators shall ensure that that animal carer transfers his or her knowledge to the other animal carers of the establishment.
-4.	The Commission shall adopt implementing acts, laying down minimum requirements concerning the formal education, training or professional experience referred to in paragraph 2 of this Article necessary to determine whether an animal carer has the competences referred to in paragraph 1 and for the training courses referred to in paragraph 3.
+          <t>Animal carers, other than volunteers in shelters and interns who are acting under the responsibility of a competent animal carer, shall have the following competences as regards the dogs and cats they are handling:
+an understanding of the animals’ biological behaviour and their physiological and ethological needs;
+the ability to recognise the animals’ expressions, including any sign of suffering, and to identify and to take the appropriate mitigating measures  in such cases;
+the ability to apply good animal management practices, including operant conditioning and positive reinforcement, to use and maintain the equipment used for the dogs or cats under their care and to minimise any risks to the welfare of those dogs or cats, preventing them from suffering;
+knowledge of the carers’ obligations under this Regulation.
+The competences referred to in paragraph 1 may be acquired through education, training or professional experience. Only documented education, training or professional experience shall be taken into account when determining whether an animal carer has the competences referred to in paragraph 1.
+Operators shall ensure that at least one animal carer, other than a volunteer or intern, at the establishment has completed the training courses referred to in Article 22. Operators shall ensure that that animal carer transfers his or her knowledge to the other animal carers of the establishment.
+The Commission shall adopt implementing acts, laying down minimum requirements concerning the formal education, training or professional experience referred to in paragraph 2 of this Article necessary to determine whether an animal carer has the competences referred to in paragraph 1 and for the training courses referred to in paragraph 3.
 The implementing act concerning the training courses referred to in paragraph 3 shall be adopted by ... [3 years from the date of entry into force of this Regulation].
 Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 29.</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>1. Os cuidadores de animais, com exceção de voluntários em abrigos e estagiários sob a responsabilidade de um cuidador competente, devem ter as seguintes competências no que diz respeito aos cães e gatos que manuseiam:
-(a) compreensão do seu comportamento biológico e das suas necessidades fisiológicas e etológicas;
-(b) capacidade de reconhecer as suas expressões, incluindo qualquer sinal de sofrimento, e de identificar e adotar as medidas mitigantes apropriadas nesses casos;
-(c) capacidade de aplicar boas práticas de maneio de animais, incluindo condicionamento operante e reforço positivo, utilizar e manter o equipamento utilizado para os cães ou gatos sob os seus cuidados e minimizar quaisquer riscos para o bem-estar dos cães ou gatos, prevenindo sofrimento;
-(d) conhecimento das suas obrigações sob este Regulamento.
-2. As competências referidas no parágrafo 1 podem ser adquiridas através de educação, formação ou experiência profissional. A educação, formação ou experiência profissional devem ser documentadas.
-3.	Os operadores devem assegurar que pelo menos um cuidador de animais, que não seja um voluntário ou estagiário, no estabelecimento tenha completado os cursos de formação referidos no artigo 22.º e que o cuidador transfira os conhecimentos aos outros cuidadores de animais do estabelecimento.
-4.	A Comissão estabelecerá, por meio de atos de execução, os requisitos mínimos relativos à educação formal, formação ou experiência profissional para adquirir as competências referidas no parágrafo 2 e para os cursos de formação referidos no n.º 3. Esses atos de execução serão adotados de acordo com o procedimento de exame referido no artigo 29.º. O ato de execução relativo aos cursos de formação referidos no n.º 3 deve ser adotado por [3 anos da data de entrada em vigor do Regulamento].</t>
+          <t>Os cuidadores de animais, com exceção dos voluntários em abrigos e dos estagiários que atuem sob a responsabilidade de um cuidador de animais competente, devem possuir as seguintes competências no que diz respeito aos cães e gatos que manuseiam:
+(a) compreensão do comportamento biológico dos animais e das respetivas necessidades fisiológicas e etológicas;​
+(b) capacidade para reconhecer as expressões dos animais, incluindo qualquer sinal de sofrimento, e para identificar e adotar as medidas de atenuação adequadas nesses casos;
+(c) capacidade para aplicar boas práticas de gestão animal, incluindo o condicionamento operante e o reforço positivo, para utilizar e manter o equipamento utilizado para os cães ou gatos sob o seu cuidado e para minimizar quaisquer riscos para o bem-estar desses cães ou gatos, prevenindo o seu sofrimento;
+(d) conhecimento das obrigações que lhes incumbem por força do presente regulamento.​
+As competências referidas no n.º 1 podem ser adquiridas através de ensino, formação ou experiência profissional. Só o ensino, a formação ou a experiência profissional documentada são tidos em conta para determinar se um cuidador de animais possui as competências referidas no n.º 1.​
+Os operadores asseguram que, em cada estabelecimento, pelo menos um cuidador de animais, que não seja voluntário nem estagiário, tenha concluído os cursos de formação a que se refere o artigo 22.º. Os operadores asseguram que esse cuidador de animais transmita os seus conhecimentos aos restantes cuidadores de animais do estabelecimento.
+A Comissão adota atos de execução que estabelecem requisitos mínimos relativos ao ensino formal, à formação ou à experiência profissional referidos no n.º 2 do presente artigo, necessários para determinar se um cuidador de animais possui as competências referidas no n.º 1, bem como relativos aos cursos de formação a que se refere o n.º 3.​
+O ato de execução relativo aos cursos de formação referidos no n.º 3 é adotado até … [3 anos a contar da data de entrada em vigor do presente regulamento].​
+Os referidos atos de execução são adotados pelo procedimento de exame a que se refere o artigo 29.º</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1417,7 +1665,9 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Artigo 69.º — Formação
+          <t>Artigo 52.º - Maneio
+1 - A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico que possua formação teórica e prática específica ministrada ou certificada pela DGAV e em número adequado à quantidade e espécies animais que alojam
+Artigo 69.º — Formação
 A reprodução, criação, manutenção, venda ou treino de animais de companhia depende de aprovação em formação sobre detenção responsável de animais de companhia, bem como sobre as necessidades fisiológicas e etológicas específicas da espécie animal em causa, ministrada pelo ICNF, I.P. ou entidades por este certificadas.
 Artigo 84.º — Pessoal
 O pessoal responsável pelas tarefas referidas no artigo 82.º deve possuir os conhecimentos e a experiência adequados para as executar.
@@ -1433,7 +1683,12 @@
       <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Artigo 19.º — Pessoal auxiliar
-Os alojamentos devem dispor de pessoal auxiliar que possua os conhecimentos e a aptidão necessária para assegurar os cuidados adequados aos animais, o qual fica sob a orientação do médico veterinário responsável.</t>
+Os alojamentos devem dispor de pessoal auxiliar que possua os conhecimentos e a aptidão necessária para assegurar os cuidados adequados aos animais, o qual fica sob a orientação do médico veterinário responsável.
+Art.º 47º - Maneio
+1 - Nos alojamentos de hospedagem de animais, nos centros de recolha e nas hospedagens com fins médico-veterinários, a observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal com aptidão para o efeito e em número adequado à quantidade e espécies animais que alojam.
+2 - O maneio deve ser feito por pessoal que possua experiência ou formação adequada e sob a orientação de um médico veterinário ou pessoa com competência para o efeito.
+Art. 49º - Cuidados de Saúde
+1 - Sem prejuízo de quaisquer medidas determinadas pela DGAV, nos locais de criação, manutenção e venda, bem como nos centros de recolha e alojamentos de hospedagem, deve existir um programa de profilaxia médica e sanitária, elaborado e supervisionado pelo médico veterinário responsável e executado por profissionais habilitados para o efeito.</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
@@ -1443,10 +1698,10 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>Artigo 13.º — Maneio
-1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
-2 — O maneio deve ser feito por pessoal que possua formação teórica e prática específica ou sob a supervisão de uma pessoa competente para o efeito.
-3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados.</t>
+          <t>Artigo 13.º - Maneio
+A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
+O maneio deve ser feito por pessoal que possua formação teórica e prática específica ou sob a supervisão de uma pessoa competente para o efeito.
+Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados.</t>
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr">
@@ -1456,17 +1711,21 @@
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>O @codigo (art.º 19.º) é genérico: exige apenas 'conhecimentos e aptidão necessária' sob orientação do médico veterinário responsável. Não detalha competências concretas nem exigências de formação formal.</t>
+          <t>O @codigo (art.º 19.º) é mais genérico: exige apenas 'conhecimentos e aptidão necessária' sob orientação do médico veterinário responsável. Não detalha competências concretas nem exigências de formação formal.</t>
         </is>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac (art.ºs 69.º, 84.º, 90.º) aproxima-se mais do @regulamento: exige 'conhecimentos e experiência adequados', menciona 'necessidades fisiológicas e etológicas', exige formação certificada pelo ICNF. Lacuna: não detalha as 4 competências específicas do @regulamento (reconhecimento de sofrimento, condicionamento operante, etc.).</t>
+          <t>O @rgbeac (art.ºs 52.º, 69.º, 84.º, 90.º) aproxima-se mais do @regulamento: menciona 'necessidades fisiológicas e etológicas', exige formação certificada. Lacuna: não detalha as 4 competências específicas do @regulamento (reconhecimento de sofrimento, condicionamento operante, etc.).</t>
         </is>
       </c>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>Alinhamento parcial do @rgbeac com @regulamento. Para @codigo e @legislacao, necessidade de: (1) detalhar as 4 competências específicas (comportamento, reconhecimento de sofrimento, maneio positivo, conhecimento de obrigações); (2) exigir documentação formal de educação/formação/experiência; (3) requerer que operador designe formador responsável que transfira conhecimento; (4) implementar requisitos mínimos de formação via regulamento delegado.</t>
+          <t>Necessidade de: 
+(1) detalhar as 4 competências específicas (comportamento, reconhecimento de sofrimento, maneio positivo, conhecimento de obrigações); 
+(2) exigir documentação formal de educação/formação/experiência;
+(3) requerer que operador designe formador responsável que transfira conhecimento;
+(4) implementar requisitos mínimos de formação via regulamento delegado.</t>
         </is>
       </c>
       <c r="O9" s="11" t="inlineStr">
@@ -1474,37 +1733,33 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="P9" s="11" t="inlineStr">
-        <is>
-          <t>(espaço para anotações da reunião)</t>
-        </is>
-      </c>
+      <c r="P9" s="11" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Avaliação e Supervisão de Bem-Estar</t>
+          <t>Supervisão de Bem-Estar</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Art.º 13.º do Regulamento 2023/0447</t>
+          <t>Art.º 13.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1.	Operators shall:
+          <t>1. Operators shall:
 (a)	ensure that the establishments for which they are responsible receive a visit by a veterinarian for the purpose of identifying and assessing any risk factor for the welfare of the dogs or cats and advising the operator on measures to address those risks initially by ... [date three years after the date of entry into force of this Regulation] or one year following the notification of the new establishment, and thereafter when appropriate, based on a risk analysis by the competent authorities, or on an annual basis if Member States so provide in their national law;
 (b)	keep the records of the findings of the veterinarian’s visit referred to in point (a) and of their follow up actions for at least four years, from the day of the visit, and shall make those records available to the competent authorities upon request as well as to the veterinarians that perform subsequent advisory visits.
-2.	By ... [date 24 months from the date of entry into force of this Regulation], the Commission shall adopt delegated acts in accordance with Article 28 supplementing this Article by laying down the minimum criteria to be assessed by the veterinarian during the advisory welfare visit.</t>
+2. By ... [date 24 months from the date of entry into force of this Regulation], the Commission shall adopt delegated acts in accordance with Article 28 supplementing this Article by laying down the minimum criteria to be assessed by the veterinarian during the advisory welfare visit.</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Os operadores devem:
+          <t>1. Os operadores devem:
 (a) assegurar que os estabelecimentos sob a sua responsabilidade recebem uma visita de um médico veterinário no prazo de um ano a partir da data de aplicação do presente Regulamento ou no prazo de um ano após notificação de novo estabelecimento, com o objetivo de identificar e avaliar quaisquer fatores de risco para o bem-estar dos cães ou gatos e aconselhar o operador sobre medidas para resolver esses riscos; depois, as visitas do médico veterinário devem ocorrer quando apropriado, com base numa análise de risco pelas autoridades competentes; os Estados-Membros podem estabelecer que as visitas de aconselhamento de bem-estar sejam anuais;
 (b) manter registos dos resultados da visita do médico veterinário referida na alínea (a) e das ações de acompanhamento por um período mínimo de 4 anos, a partir da data da visita, e disponibilizá-los às autoridades competentes a pedido e ao médico veterinário que realiza visitas de aconselhamento subsequentes.
-Dentro de 24 meses a partir da data de entrada em vigor do presente Regulamento, a Comissão deve adotar atos delegados em conformidade com o artigo 28.º que complementem o presente artigo de forma a estabelecer critérios mínimos a serem avaliados durante a visita de aconselhamento de bem-estar.</t>
+2. Dentro de 24 meses a partir da data de entrada em vigor do presente Regulamento, a Comissão deve adotar atos delegados em conformidade com o artigo 28.º que complementem o presente artigo de forma a estabelecer critérios mínimos a serem avaliados durante a visita de aconselhamento de bem-estar.</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1555,22 +1810,26 @@
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>O DL n.º 276/2001 (art.º 4.º) estabelece a obrigação de ter médico veterinário responsável que execute 'programas e ações' para saúde e bem-estar, mas não especifica que essa avaliação deve ocorrer em prazo determinado (ex.: 1 ano) ou que os registos devem ser mantidos por período específico (4 anos). O @regulamento é mais prescritivo neste aspecto.</t>
+          <t>Estabelece a obrigação de ter médico veterinário responsável que execute 'programas e ações' para saúde e bem-estar, 
+Não fixa prazos para avaliações de bem-estar nem obrigações de manutenção de registos estruturados, conforme @regulamento</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>O @codigo (art.º 32.º) replica quase verbatim o art.º 4.º do DL n.º 276/2001, mantendo as mesmas lacunas: não fixa prazos para avaliações de bem-estar nem obrigações de manutenção de registos estruturados.</t>
+          <t>Replica quase verbatim o art.º 4.º do DL n.º 276/2001, mas exclui «ações»
+Não fixa prazos para avaliações de bem-estar nem obrigações de manutenção de registos estruturados, conforme @regulamento</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac (art.º 56.º) reforça a obrigação com 'parecer relativo à verificação das condições higiossanitárias e de bem-estar', mas igualmente sem prazos específicos para avaliações ou duração de retenção de registos. Ambos focam-se em 'programas' interno, não em 'visitas periódicas externas'.</t>
+          <t>Recupera as «ações»
+Reforça a obrigação com 'parecer relativo à verificação das condições higiossanitárias e de bem-estar'
+Não fixa prazos para avaliações de bem-estar nem obrigações de manutenção de registos estruturados, conforme @regulamento</t>
         </is>
       </c>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>Lacuna estrutural em toda a legislação nacional: enquanto o @regulamento exige 'visita de um veterinário' num prazo específico (1 ano) com manutenção de registos por 4 anos e transmissão entre veterinários, a legislação nacional concentra-se em ter um 'médico veterinário responsável' no estabelecimento. Necessidade de alteração: (1) formalizar obrigação de 'visita de avaliação' por veterinário dentro de 1 ano após notificação; (2) exigir avaliações periódicas conforme risco; (3) obrigatória manutenção de registos por 4 anos; (4) garantir transmissão de informações ao próximo veterinário avaliador; (5) estabelecer critérios mínimos de avaliação (bem-estar comportamental, alojamento, saúde, etc.).</t>
+          <t>O @regulamento exige 'visita de um veterinário' num prazo específico (1 ano) após entrada em funcionamento com manutenção de registos por 4 anos e transmissão entre veterinários. Necessidade de alteração: (1) formalizar obrigação de 'visita de avaliação' por veterinário dentro de 1 ano após implementação do regulamento/notificação; (2) exigir avaliações periódicas conforme risco; (3) obrigatória manutenção de registos por 4 anos;</t>
         </is>
       </c>
       <c r="O10" s="11" t="inlineStr">
@@ -1578,16 +1837,12 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="P10" s="11" t="inlineStr">
-        <is>
-          <t>(espaço para anotações da reunião)</t>
-        </is>
-      </c>
+      <c r="P10" s="11" t="inlineStr"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Alimentação e Hidratação</t>
+          <t>Alimentação e Abeberamento</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1597,29 +1852,29 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>1.	Operators  shall ensure that dogs and cats are fed in accordance with the requirements laid down in point 1 of Annex I  .
-2.	In addition, operators  shall ensure that dogs and cats are adequately fed and hydrated by supplying:
-(a)	clean and fresh water, ad libitum;
-(b)	feed of sufficient quantity and quality to meet the physiological, nutritional and metabolic needs  of the dogs and cats, as part of a diet adapted to the age, breed, category, activity level,  health and reproductive status of the dogs or cats, with the overall objective of achieving and maintaining their good health;
-(c)	feed free of substances which could cause suffering;
-(d)	feed in such a way as to avoid abrupt changes and ensure a well-functioning gastro-intestinal system, in particular during the weaning phase.
-3.	Operators  shall ensure that feeding and watering facilities are kept clean and are constructed and installed in such a way as to:
-(a)	provide equal access to adequate amounts of feed and water for all dogs or cats and minimise competition between them;
-(b)	minimise spillage and prevent the contamination of feed and water with harmful physical, chemical or biological contaminants;
-(c)	prevent injury, drowning or other harm to the dogs or cats;
-(d)	be easily cleaned and disinfected to prevent the spread of diseases.
-4.	Where advised in writing by a veterinarian to do so, the operators may adjust the feeding and watering frequencies for an individual dog or cat. The operators shall keep a record of that written advice for the entire duration of those arrangements.</t>
+          <t>Operators shall ensure that dogs and cats are fed in accordance with the requirements laid down in point 1 of Annex I.
+In addition, operators shall ensure that dogs and cats are adequately fed and hydrated by supplying:
+clean and fresh water, ad libitum;
+feed of sufficient quantity and quality to meet the physiological, nutritional and metabolic needs of the dogs and cats, as part of a diet adapted to the age, breed, category, activity level, health and reproductive status of the dogs or cats, with the overall objective of achieving and maintaining their good health;
+feed free of substances which could cause suffering;
+feed in such a way as to avoid abrupt changes and ensure a well-functioning gastro-intestinal system, in particular during the weaning phase.
+Operators shall ensure that feeding and watering facilities are kept clean and are constructed and installed in such a way as to:
+provide equal access to adequate amounts of feed and water for all dogs or cats and minimise competition between them;
+minimise spillage and prevent the contamination of feed and water with harmful physical, chemical or biological contaminants;
+prevent injury, drowning or other harm to the dogs or cats;
+be easily cleaned and disinfected to prevent the spread of diseases.
+Where advised in writing by a veterinarian to do so, the operators may adjust the feeding and watering frequencies for an individual dog or cat. The operators shall keep a record of that written advice for the entire duration of those arrangements.</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores devem assegurar que os cães ou gatos são alimentados em conformidade com os requisitos estabelecidos no ponto 1 do Anexo I.
-2. Os operadores devem assegurar que os cães ou gatos são adequadamente alimentados e hidratados através do fornecimento de:
+2. Os operadores devem assegurar que os cães ou gatos sejam alimentados e hidratados de forma adequada, fornecendo-lhes:
 a) água limpa e fresca, ad libitum;
-b) alimento em quantidade e qualidade suficientes para satisfazer as necessidades fisiológicas, nutricionais e metabólicas dos cães e gatos, como parte de uma dieta adaptada à idade, raça, categoria, nível de atividade, saúde e estado reprodutivo dos cães ou gatos, com o objetivo geral de atingir e manter boa saúde;
+b) Alimentos para animais em quantidade e qualidade suficientes para satisfazer as necessidades fisiológicas, nutricionais e metabólicas dos cães e gatos, no âmbito de uma dieta adaptada à idade, raça, categoria, nível de atividade e estado reprodutivo dos cães ou gatos, com o objetivo global de alcançar manter um bom estado saúde;
 c) alimento livre de substâncias que possam causar sofrimento;
-d) alimento de forma a evitar mudanças abruptas e assegurar um sistema gastrointestinal bem funcionante, em particular durante a fase de desmame.
-3. Os operadores devem assegurar que as instalações de alimentação e hidratação são mantidas limpas e são construídas e instaladas de forma a:
+d) alimento de forma a evitar mudanças abruptas e assegurar um sistema gastrointestinal em bom funcionamento, em particular durante a fase de desmame.
+3. Os operadores devem assegurar que as instalações de alimentação e abeberamento sejam mantidas limpas e sejam construídas e instaladas de forma a:
 a) proporcionar acesso igualitário a quantidades adequadas de alimento e água para todos os cães ou gatos e minimizar a competição entre eles;
 b) minimizar derramamentos e evitar a contaminação do alimento e da água com contaminantes físicos, químicos ou biológicos prejudiciais;
 c) evitar ferimentos, afogamento ou outro dano aos cães ou gatos;
@@ -1629,13 +1884,21 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Arts. 7.º (n.º 1, al. a) e 10.º (n.º 1, al. a) do RGBEAC (proposta, jun. 2025)</t>
+          <t>Art. 51.º do RGBEAC (proposta, jun 2025)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Artigo 7.º - Princípios fundamentais: Não passem fome ou sede, nem sejam sujeitos a malnutrição.
-Artigo 10.º - Obrigações especiais dos detentores: Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável. Ênfase em necessidades nutricionais adequadas ao estado de saúde.</t>
+          <t>1 - Deve existir um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies e dos indivíduos de acordo com a fase de evolução fisiológica em que se encontram, nomeadamente idade, sexo, fêmeas prenhes ou em fase de lactação.
+2 - As refeições devem ainda ser distribuídas segundo a rotina que mais se adequar à espécie e de forma a manter aspetos do seu comportamento alimentar natural, incluindo comedouros interativos e outros dispositivos adequados à espécie.
+3 - O número, formato e distribuição de comedouros e bebedouros deve ser tal que permita aos animais satisfazerem as suas necessidades sem que haja competição dentro do grupo.
+4 - Os alimentos devem ser preparados e armazenados de acordo com padrões estritos de higiene, em locais secos, limpos, livres de agentes patogénicos e de produtos tóxicos e, no caso dos alimentos compostos, devem, ainda, ser armazenados sobre estrados ou prateleiras.
+5 – Sempre que se justifique, devem existir aparelhos de frio para uma eficiente conservação dos alimentos.
+6 - Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.
+Art. 7.º (n.º 1, al. a) - Princípios fundamentais: 
+Não passem fome ou sede, nem sejam sujeitos a malnutrição.
+Art. 10.º (n.º 1, al. a) - Obrigações especiais dos detentores:
+Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável.</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -1645,14 +1908,18 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Alimentação e abeberamento:
-A alimentação dos animais de companhia, nos locais de criação, manutenção e venda bem como nos centros de recolha e instalações de hospedagem, deve obedecer a um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies.
-Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.</t>
+          <t>1 - A alimentação dos animais de companhia, nos locais de criação, manutenção e venda bem como nos centros de recolha e instalações de hospedagem, deve obedecer a um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies e dos indivíduos, de acordo com a fase de evolução fisiológica em que se encontram, nomeadamente idade, sexo, fêmeas prenhes ou em fase de lactação.
+2 - As refeições devem ainda ser variadas, sendo distribuídas segundo a rotina que mais se adequar à espécie e de forma a manter, tanto quanto possível, aspetos do seu comportamento alimentar natural.
+3 - O número, formato e distribuição de comedouros e bebedouros deve ser tal que permita aos animais satisfazerem as suas necessidades sem que haja competição excessiva dentro do grupo.
+4 - Os alimentos devem ser preparados e armazenados de acordo com padrões estritos de higiene, em locais secos, limpos, livres de agentes patogénicos e de produtos tóxicos e, no caso dos alimentos compostos devem, ainda, ser armazenados sobre estrados de madeira ou prateleiras.
+5 - Devem existir aparelhos de frio para uma eficiente conservação dos alimentos.
+6 - Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.
+7 - É proibido alimentar animais com restos de comida, produtos de pastelaria e desperdícios da indústria alimentar e de restauração.</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Decreto-Lei n.º 276/2001 - Artigo 12.º</t>
+          <t>Artigo 12.º Decreto-Lei n.º 276/2001</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
@@ -1665,24 +1932,24 @@
 6 — Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t>NÃO APLICÁVEL - Diploma não específico nesta matéria</t>
-        </is>
-      </c>
+      <c r="K11" s="8" t="inlineStr"/>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>SIM - COBERTURA COMPLETA (Art. 46.º implementa integralmente)</t>
+          <t>Parece restringir as obrigações aos estabelecimentos.
+Apenas @código proíbe restos, pastelaria e desperdícios.</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
-          <t>SIM - COBERTURA COMPLETA (linguagem modernizada)</t>
+          <t>Introduz comedouros interativos e outros dispositivos adequados à espécie – pode ir ao encontro do conceito de categoria?
+Obriga a que não haja competição – mais restritivo que o @regulamento
+Retira a obrigatoriedade de aparelhos de frio</t>
         </is>
       </c>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>COBERTURA COMPLETA. Código do Animal (Art. 46.º) implementa todos os requisitos do Artigo 11.º. RGBEAC alinha melhor com linguagem e especificidades do Regulamento europeu. Sem divergências substanciais.</t>
+          <t>Regulamento introduz mais «categorias» - raça, categoria, nível de atividade e estado reprodutivo.
+Nenhum aborda transições alimentares graduais, cuidados específicos com desmame, segurança estrutural das instalações.</t>
         </is>
       </c>
       <c r="O11" s="11" t="inlineStr">
@@ -1692,7 +1959,7 @@
       </c>
       <c r="P11" s="11" t="inlineStr">
         <is>
-          <t>Correspondências completas - RGBEAC alinha melhor com Regulamento EU</t>
+          <t>Nutrição e hidratação são também princípios básicos de bem-estar previstos pelo Artigo 5 – parágrafo 1 – alínea a) do @regulamento</t>
         </is>
       </c>
     </row>
@@ -1704,188 +1971,237 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Art.º 15.º do Regulamento 2023/0447</t>
+          <t>Art.º 15.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>1.	The operators of breeding and selling establishments shall ensure that dogs and cats are housed in accordance with point 2 of Annex I. The operators of shelters shall ensure that dogs and cats are housed in accordance with point 2.2 of Annex I.
-2.	Operators  shall ensure that:
-(a)	the establishments where dogs or cats are kept and the equipment used therein are suitable for the types and the number of dogs or cats, and make possible the necessary access to, and the thorough inspection of, all dogs or cats;
-(b)	all building components of the establishment, including the flooring and roof,  and space divisions, as well as the equipment used for dogs or cats, are constructed and maintained properly,  to ensure that they do not pose any risks to the welfare of the dogs or cats;
-(c)	all building components of the establishment, including the flooring, and space divisions, as well as the equipment used for dogs or cats, are kept clean to ensure that they do not pose any risks to the welfare of the dogs or cats;
-(d)	 in breeding and selling establishments where dogs or cats are kept indoors, the dust levels, the temperature, and the relative air humidity and gas concentrations are  not harmful to dogs or cats and that ventilation is sufficient to avoid overheating  ;
-(e)	dogs or cats have enough space to be able to move around freely and to express species-specific behaviour according to their needs with the possibility to withdraw and rest;
-(f)	dogs or cats have clean, comfortable and dry resting places that are sufficiently large and numerous to ensure that all of them can lie down and rest in a natural position at the same time;
-(g)	appropriate structures and measures are in place for dogs or cats that are kept outdoors in order to protect them from adverse weather conditions, including to prevent thermal stress, sunburn and frostbite.
-3.	Operators shall not keep dogs or cats in containers
+          <t>The operators of breeding and selling establishments shall ensure that dogs and cats are housed in accordance with point 2 of Annex I. The operators of shelters shall ensure that dogs and cats are housed in accordance with point 2.2 of Annex I.
+Operators shall ensure that:
+the establishments where dogs or cats are kept and the equipment used therein are suitable for the types and the number of dogs or cats, and make possible the necessary access to, and the thorough inspection of, all dogs or cats;
+all building components of the establishment, including the flooring and roof, and space divisions, as well as the equipment used for dogs or cats, are constructed and maintained properly, to ensure that they do not pose any risks to the welfare of the dogs or cats;
+all building components of the establishment, including the flooring, and space divisions, as well as the equipment used for dogs or cats, are kept clean to ensure that they do not pose any risks to the welfare of the dogs or cats;
+in breeding and selling establishments where dogs or cats are kept indoors, the dust levels, the temperature, and the relative air humidity and gas concentrations are not harmful to dogs or cats and that ventilation is sufficient to avoid overheating  ;
+dogs or cats have enough space to be able to move around freely and to express species-specific behaviour according to their needs with the possibility to withdraw and rest;
+dogs or cats have clean, comfortable and dry resting places that are sufficiently large and numerous to ensure that all of them can lie down and rest in a natural position at the same time;
+appropriate structures and measures are in place for dogs or cats that are kept outdoors in order to protect them from adverse weather conditions, including to prevent thermal stress, sunburn and frostbite.
+Operators shall not keep dogs or cats in containers
 However, containers may be used for transportation, for the short term isolation of individual dogs or cats and for participation in shows, exhibitions and competitions, for puppies or kittens with reduced thermoregulation capacity or for puppies or kittens together with their mothers, provided that, for the dogs or cats concerned, stress is minimised and suffering is avoided, and they are able to stand, turn around and lie down in a natural position.
-4.	Operators shall not keep dogs older than 8 weeks exclusively indoors. Such dogs shall have daily access to an outdoor area, or be walked daily,  to allow exercise, exploration and socialisation. The minimum combined duration of such daily access or walk shall be one hour in total. The operator may only deviate from these requirements based on the written advice of a veterinarian.
-5.	When cats are kept in catteries, operators shall design and construct individual enclosures to allow cats to move around freely and to exhibit their natural behaviour.
-6.	Operators of breeding and selling establishments shall ensure that  in indoor areas where dogs and cats are kept, an appropriate thermoneutral zone is maintained that takes into account their coat type, age, size, breed, and health.
-7.	Operators of breeding and selling establishments shall, where necessary, use heating or cooling systems in the indoor enclosures at their establishments to maintain good air quality and an appropriate temperature and to remove excessive moisture.
-8.	Operators shall ensure that dogs or cats are exposed to light, and are able to stay in the dark for sufficient and uninterrupted periods in order to maintain a normal circadian rhythm.
+Operators shall not keep dogs older than 8 weeks exclusively indoors. Such dogs shall have daily access to an outdoor area, or be walked daily, to allow exercise, exploration and socialisation. The minimum combined duration of such daily access or walk shall be one hour in total. The operator may only deviate from these requirements based on the written advice of a veterinarian.
+When cats are kept in catteries, operators shall design and construct individual enclosures to allow cats to move around freely and to exhibit their natural behaviour.
+Operators of breeding and selling establishments shall ensure that in indoor areas where dogs and cats are kept, an appropriate thermoneutral zone is maintained that takes into account their coat type, age, size, breed, and health.
+Operators of breeding and selling establishments shall, where necessary, use heating or cooling systems in the indoor enclosures at their establishments to maintain good air quality and an appropriate temperature and to remove excessive moisture.
+Operators shall ensure that dogs or cats are exposed to light, and are able to stay in the dark for sufficient and uninterrupted periods in order to maintain a normal circadian rhythm.
 For the purposes of the first subparagraph, ‘light’ means natural light, complemented, where necessary due to the climatic conditions and geographic position of a Member State, by artificial light.
-9.	Paragraph 2, points (a), (b), (c) (f) and (g), and paragraphs 6, 7 and 8 shall apply neither to livestock guardian dogs, nor to herding dogs, during the periods where such dogs are used for guarding or herding in the context of seasonal transhumance on foot. Paragraph 2(f) shall not apply to livestock guardian dogs during the periods when such dogs are used for training purposes.</t>
+Paragraph 2, points (a), (b), (c) (f) and (g), and paragraphs 6, 7 and 8 shall apply neither to livestock guardian dogs, nor to herding dogs, during the periods where such dogs are used for guarding or herding in the context of seasonal transhumance on foot. Paragraph 2(f) shall not apply to livestock guardian dogs during the periods when such dogs are used for training purposes.</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores de estabelecimentos de criação e venda devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2 do Anexo I. Os operadores de abrigos devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2.2 do Anexo I.
-2. Os operadores devem assegurar que:
-a) os estabelecimentos onde os cães ou gatos são mantidos e o equipamento utilizado são adequados aos tipos e número de cães ou gatos, e permitem o acesso necessário e inspeção minuciosa de todos os cães ou gatos;
-b) todos os componentes de construção do estabelecimento, incluindo o pavimento, telhado e divisões de espaço, bem como o equipamento utilizado para cães ou gatos, são construídos e mantidos adequadamente, para assegurar que não apresentam riscos ao bem-estar dos cães ou gatos.
-c)	todos os componentes de construção do estabelecimento, incluindo o pavimento e divisões de espaço, bem como o equipamento utilizado para cães ou gatos, são mantidos limpos para assegurar que não apresentam riscos ao bem-estar dos cães ou gatos;
-d)	em estabelecimentos de criação e venda onde os cães ou gatos são mantidos no interior, pó, temperatura, humidade relativa do ar e concentrações de gases não são prejudiciais aos cães ou gatos e a ventilação é suficiente para evitar sobreaquecimento;
-e)	os cães e gatos têm espaço suficiente para se moverem livremente e expressar comportamento específico da espécie de acordo com as suas necessidades com possibilidade de se retirarem e descansarem;
-f)	os cães ou gatos têm lugares de repouso limpos, confortáveis e secos, suficientemente grandes e numerosos para assegurar que todos podem deitar-se e descansar ao mesmo tempo numa posição natural;
-g)	estrututras e medidas apropriadas estão em vigor para cães ou gatos mantidos no exterior para os proteger de condições climáticas adversas, incluindo para evitar stress térmico, queimaduras solares e frieiras.
-3. Os operadores não devem manter cães ou gatos em contentores.
-A título de derrogação, contentores podem ser usados apenas para transporte, isolamento a curto prazo de cães ou gatos individuais e durante participação em espetáculos, exposições e competições, para cachorros ou gatinhos com capacidade termorreguladora reduzida ou cachorros ou gatinhos juntamente com as suas mães, desde que o stress seja minimizado e o sofrimento seja evitado e os cães e gatos sejam capazes de se manter em pé e deitar-se numa posição natural.
-4. Os operadores não devem manter cães com mais de 8 semanas exclusivamente no interior. Tais cães devem ter acesso diário a uma área ao ar livre, ou ser passeados diariamente, para permitir exercício, exploração e socialização. A duração do acesso diário a uma área ao ar livre ou passeio deve ser mínimo uma hora no total. O operador pode apenas derrogar destes requisitos com base em aconselhamento escrito de um médico veterinário.
-5. Quando gatos são mantidos em gatarias, os operadores devem desenhar e construir compartimentos individuais para permitir aos gatos mover-se livremente e expressar o seu comportamento natural.
-6. Os operadores de estabelecimentos de criação e venda devem assegurar que em áreas interiores onde os cães ou gatos são mantidos, uma zona termoneural apropriada é mantida levando em conta o seu tipo de pelagem, idade, tamanho, raça e saúde.
-7.	Os operadores de estabelecimentos de criação e venda devem usar, quando necessário, sistemas de aquecimento ou arrefecimento para manter boa qualidade do ar, uma temperatura apropriada em compartimentos interiores nos seus estabelecimentos, e remover humidade excessiva.
-8.	Os operadores devem assegurar que os cães ou gatos são expostos à luz, e são capazes de permanecer no escuro por períodos suficientes e ininterruptos para manter um ritmo circadiano normal.
+          <t>Os operadores de estabelecimentos de criação e venda devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2 do Anexo I. Os operadores de abrigos devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2.2 do Anexo I.
+Os operadores devem assegurar que:
+os estabelecimentos onde os cães ou gatos são detidos e o equipamento neles utilizado sejam adequados aos tipos e ao número de cães ou gatos, e permitam o acesso necessário e a inspeção exaustiva de todos os cães ou gatos;​
+todos os componentes do edifício do estabelecimento, incluindo o pavimento e o telhado, e as divisões de espaço, bem como o equipamento utilizado para cães ou gatos, sejam construídos e mantidos adequadamente, de modo a garantir que não representem quaisquer riscos para o bem-estar dos cães ou gatos;​
+todos os componentes do edifício do estabelecimento, incluindo o pavimento e as divisões de espaço, bem como o equipamento utilizado para cães ou gatos, sejam mantidos limpos, de modo a garantir que não representem quaisquer riscos para o bem-estar dos cães ou gatos;​
+nos estabelecimentos de criação e venda onde os cães ou gatos são detidos em espaços interiores, os níveis de poeira, a temperatura, a humidade relativa do ar e as concentrações de gases não sejam prejudiciais para os cães ou gatos e a ventilação seja suficiente para evitar o sobreaquecimento;​
+os cães ou gatos disponham de espaço suficiente para circular livremente e exprimir comportamentos específicos da espécie de acordo com as suas necessidades, com a possibilidade de se retirarem e descansarem;​
+os cães ou gatos disponham de locais de repouso limpos, confortáveis e secos, suficientemente amplos e numerosos para garantir que todos eles possam deitar-se e descansar em posição natural ao mesmo tempo;​
+existam estruturas e medidas adequadas para os cães ou gatos detidos ao ar livre, de modo a protegê-los de condições climáticas adversas, incluindo para prevenir stress térmico, queimaduras solares e queimaduras pelo frio.
+Os operadores não devem manter cães ou gatos em contentores.
+Contudo, contentores podem ser utilizados para o transporte, o isolamento de curto prazo de cães ou gatos individuais e durante a participação em espetáculos, exposições e concursos, para cachorros ou gatinhos com capacidade de termorregulação reduzida ou cachorros ou gatinhos acompanhados das respetivas mães, desde que seja minimizado o stress e evitado o sofrimento e os cães e gatos possam estar de pé e deitar-se numa posição natural. 
+Os operadores não devem manter cães com mais de 8 semanas exclusivamente no interior. Tais cães devem ter acesso diário a uma área ao ar livre, ou ser passeados diariamente, para permitir exercício, exploração e socialização. A duração do acesso diário a uma área ao ar livre ou passeio deve ser mínimo uma hora no total. O operador só pode desviar-se destes requisitos com base no parecer escrito de um veterinário.
+Quando gatos são mantidos em gatis, os operadores devem desenhar e construir compartimentos individuais para permitir aos gatos mover-se livremente e expressar o seu comportamento natural.
+Os operadores dos estabelecimentos de criação e venda devem garantir que, nas áreas interiores onde os cães e gatos são detidos, seja mantida uma zona termicamente neutra adequada que tenha em conta o tipo de pelagem, a idade, o tamanho, a raça e a saúde deles.
+Os operadores dos estabelecimentos de criação e venda devem, quando necessário, utilizar sistemas de aquecimento ou arrefecimento nos recintos interiores dos seus estabelecimentos para manter uma boa qualidade do ar, uma temperatura adequada e eliminar a humidade excessiva.
+Os operadores devem garantir que os cães ou gatos sejam expostos à luz e possam permanecer no escuro durante períodos suficientes e ininterruptos, a fim de manter um ritmo circadiano normal.
 Para efeitos do primeiro parágrafo, 'luz' significa luz natural, complementada, quando necessário, devido às condições climáticas e posição geográfica de um Estado-Membro, por luz artificial.
-9.	Os n.ºs 2(a), (b), (c), (f) e (g), 6, 7 e 8 não se aplicam a cães guardiões de gado, nem a cães de pastoreio, durante os períodos em que tais cães são utilizados para guarda ou pastoreio no contexto de transumância sazonal a pé. O n.º 2(f) não se aplica a cães guardiões de gado durante os períodos em que tais cães são utilizados para fins de treino.</t>
+Os n.ºs 2 (a), (b), (c), (f) e (g), 6, 7 e 8 não se aplicam nem aos cães de guarda de gado, nem aos cães de pastoreio, durante os períodos em que tais cães são utilizados para guarda ou pastoreio no contexto da transumância sazonal a pé. A alínea (f) do ponto 2 não se aplica aos cães de guarda de gado durante os períodos em que tais cães são utilizados para fins de formação.</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Arts. 7.º, 10.º, 11.º, 47-57 do RGBEAC (proposta, jun. 2025)</t>
+          <t>Artigos 47-57 - Regulação detalhada de alojamentos para hospedagem (estruturas, proteção, maneio, responsabilidades veterinárias).</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Artigo 7.º - Princípios: Condições de detenção e alojamento salvaguardam bem-estar animal.
-Artigo 10.º - Obrigações especiais: Liberdade de movimento, proibição de contenção permanente, espaço adequado, enriquecimento ambiental e abrigo protetor.
-Artigo 11.º - Obrigações especiais relativas ao alojamento doméstico.
-Artigos 47-57 - Regulação detalhada de alojamentos para hospedagem (estruturas, proteção, maneio, responsabilidades veterinárias).</t>
+          <t>Artigo 47.º- Condições dos alojamentos
+1 - Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir: 
+a) A prática de exercício físico adequado; 
+b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
+2 - Os animais devem dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem. 
+3 - As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar. 
+4 - As instalações devem providenciar um enriquecimento ambiental complexo e estimulante de acordo com as necessidades específicas dos animais que albergam, incluindo materiais e equipamento que estimulem a expressão do repertório de comportamentos naturais, nomeadamente materiais para substrato, cama ou ninhos, ramos, buracos, locais para banhos, brinquedos e outros adequados ao fim em vista.
+5 - As estruturas físicas das instalações, todo o equipamento nelas introduzido e a vegetação não podem representar ameaça ao bem-estar dos animais, designadamente não podem conter objetos ou equipamentos perigosos para os animais.
+6 – Os cães devem ter acesso diário a uma área de exercício fora do seu alojamento habitual, pelo menos duas vezes por dia, durante 30 minutos.
+7 – As áreas de exercício referidas no artigo anterior devem incluir equipamento de enriquecimento ambiental e agilidade, incluindo piscinas, plataformas elevadas e outros adequados ao fim em vista. 
+Artigo 48.º- Fatores ambientais
+1 - A temperatura, ventilação, luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do bem-estar e conforto das espécies que albergam. 
+2 - Os fatores ambientais referidos no número anterior devem ser adequados às necessidades específicas de animais quando em fase reprodutiva, recém-nascidos ou doentes. 
+3 - A luz deve preferencialmente natural, mas quando a luz artificial for imprescindível, esta deve ser o mais próxima possível do espectro da luz solar e deve respeitar o fotoperíodo natural do local onde o animal está instalado. 
+4 - As instalações devem permitir a adequada inspeção dos animais, devendo ainda existir equipamento alternativo, nomeadamente focos de luz, para o caso de falência do equipamento central. 
+5 - Os tanques ou aquários devem possuir água de qualidade adequada aos animais que a utilizem, nomeadamente tratada por produtos ou substâncias que não prejudiquem a sua saúde. 
+6 - As instalações devem dispor de abrigos para que os animais se protejam de condições climáticas adversas.
+7 – Deve ser evitado o ruído excessivo ou contínuo.
+Artigo 49.º-Carga e descarga de animais
+Os alojamentos devem dispor de estruturas e equipamentos adequados à carga ou à descarga dos animais dos meios de transporte, assegurando-se que os mesmos não sejam maltratados ou derrubados durante aquelas operações, e evitando-se as situações que lhes possam provocar medo ou excitação desnecessários.
+Artigo 50.º- Sistemas de proteção
+Os alojamentos devem assegurar as medidas de proteção contra incêndios previstas pela Autoridade Nacional de Emergência e Proteção Civil para o efeito.</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Arts. 3.º, 14.º, 18.º, 28.º do Código do Animal (DL 214/2013)</t>
+          <t>Artigo 13.º - Condições dos alojamentos</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Artigo 3.º - Define 'Alojamento' como qualquer instalação, edifício ou local onde animais se encontram mantidos.
-Artigo 14.º - A temperatura, ventilação, luminosidade e obscuridade devem ser adequadas ao conforto e bem-estar.
-Artigo 18.º - Alojamentos devem possuir instalações para armazenagem, lavagem, quarentena, enfermaria e higienização.
-Artigo 28.º - Define separação por espécie e requisitos de estrutura para hospedagem.</t>
+          <t>- Os animais devem dispor de um espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir: 
+A prática de exercício físico adequado; 
+A fuga e refúgio de animais sujeitos a agressão por parte de outros. 
+- Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem. 
+- As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar. 
+- As estruturas físicas das instalações, todo o equipamento nelas introduzido e a vegetação, não podem representar nenhum tipo de ameaça ao bem-estar dos animais, designadamente não podem possuir objetos ou equipamentos perigosos para os animais. 
+- As instalações devem ser equipadas de acordo com as necessidades específicas dos animais que albergam, com materiais e equipamento que estimulem a expressão dos comportamentos naturais, nomeadamente material para substrato, cama ou ninhos, ramos, buracos, locais para banhos e outros quaisquer adequados ao fim em vista. 
+Artigo 14.º - Fatores ambientais 
+- A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam. 
+- Os fatores ambientais referidos no número anterior devem ser adequados às necessidades específicas de animais quando em fase reprodutiva, recém-nascidos ou doentes. 
+- A luz deve ser preferencialmente natural, mas quando a luz artificial for imprescindível, esta deve ser o mais próxima possível do espectro da luz solar e deve respeitar o fotoperíodo natural do local onde o animal está instalado. 
+- As instalações devem permitir uma adequada inspeção dos animais, devendo ainda existir equipamento alternativo, nomeadamente focos de luz, para o caso de falência do equipamento central. 
+- Os tanques ou aquários devem possuir água de qualidade adequada aos animais que a utilizem, nomeadamente tratada por produtos ou substâncias que não prejudiquem a sua saúde. 
+Artigo 15.o - Sistemas de proteção 
+As instalações dos alojamentos de animais devem dispor de um sistema de proteção contra incêndios, alarme para aviso de avarias deste sistema e, ainda, dos equipamentos referidos no artigo anterior, quando se tratar de alojamentos em edifícios fechados e ainda, de outros equipamentos em função das espécies, sempre que da sua falta possa resultar prejuízo para o bem-estar dos animais, ou a sua morte. 
+Artigo 16.º - Carga e descarga de animais 
+As instalações dos alojamentos devem dispor, sempre que necessário, de estruturas e equipamentos adequados à carga ou à descarga dos animais dos meios de transporte, assegurando-se sempre que os mesmos não sejam maltratados ou derrubados durante aquelas operações e procurando-se minorar as situações que lhes possam provocar medo ou excitação desnecessários.	
+Artigo 17.º - Segurança de pessoas, animais e bens 
+Os alojamentos devem assegurar que as espécies animais neles mantidas não possam causar quaisquer riscos para a saúde e para a segurança de pessoas, outros animais e bens</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>Decreto-Lei n.º 276/2001 - Artigos 8.º e 15.º</t>
+          <t>Art.º 8.º, Art.º 9.º, Art.º 15.º do DL n.º 276/2001</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>Artigo 8.º — 1 — Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir: a) A prática de exercício físico adequado; b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
-2 — Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.
-3 — As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar.
-4 — As estruturas físicas das instalações, todo o equipamento nelas introduzido e a vegetação não podem representar nenhum tipo de ameaça ao bem-estar dos animais.
+          <t>Artigo 8.º - Condições dos alojamentos
+1 - Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
+a) A prática de exercício físico adequado;
+b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
+2 - Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.
+3 - As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar.
+4 - As estruturas físicas das instalações, todo o equipamento nelas introduzido e a vegetação não podem representar nenhum tipo de ameaça ao bem-estar dos animais, designadamente não podem possuir objetos ou equipamentos perigosos para os animais.
+5 - As instalações devem ser equipadas de acordo com as necessidades específicas dos animais que albergam, com materiais e equipamento que estimulem a expressão do repertório de comportamentos naturais, nomeadamente material para substrato, cama ou ninhos, ramos, buracos, locais para banhos e outros quaisquer adequados ao fim em vista.
+Artigo 9.º - Fatores ambientais
+1 - A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam.
+2 - Os fatores ambientais referidos no número anterior devem ser adequados às necessidades específicas de animais quando em fase reprodutiva, recém-nascidos ou doentes.
+3 - A luz deve ser de preferência natural, mas quando a luz artificial for imprescindível esta deve ser o mais próxima possível do espetro da luz solar e deve respeitar o fotoperíodo natural do local onde o animal está instalado.
+4 - As instalações devem permitir uma adequada inspeção dos animais, devendo ainda existir equipamento alternativo, nomeadamente focos de luz, para o caso de falência do equipamento central.
+5 - Os tanques ou aquários devem possuir água de qualidade adequada aos animais que a utilizem, nomeadamente tratada por produtos ou substâncias que não prejudiquem a sua saúde.
+6 - As instalações devem dispor de abrigos para que os animais se protejam de condições climáticas adversas
 Artigo 15.º — Os alojamentos devem assegurar que as espécies animais neles mantidas não possam causar quaisquer riscos para a saúde e para a segurança de pessoas, outros animais e bens.</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t>PARCIAL - Não específico para condições técnicas de alojamento</t>
-        </is>
-      </c>
-      <c r="L12" s="9" t="inlineStr">
-        <is>
-          <t>SIM - COBERTURA COMPLETA (Arts. 3, 14, 18, 28)</t>
-        </is>
-      </c>
+      <c r="K12" s="8" t="inlineStr"/>
+      <c r="L12" s="9" t="inlineStr"/>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>SIM - COBERTURA EXPANDIDA (especifica detalhes técnicos)</t>
+          <t>@rgbeac prevê acesso diário a área de exercício exterior 2x/dia durante 30 minutos (= 1h total),</t>
         </is>
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>COBERTURA COMPLETA. Código do Animal e RGBEAC implementam requisitos do Artigo 12.º. Faltam especificações técnicas detalhadas (temperatura, ventilação, iluminação) — recomenda-se Portaria complementar.</t>
+          <t>N.º 2, Proibição expressa de manter cães ou gatos em contentores : não coberto, nenhum dos três diplomas contém esta proibição explícita. 
+N.º 3 – Exceções ao uso de contentores (transporte, isolamento curto prazo, espetáculos, neonatos com termorregulação reduzida ou acompanhados da mãe) Não coberto
+N.º 4 – Proibição de manter cães &gt;8 semanas exclusivamente no interior; acesso diário ao exterior mínimo 1h total (ou passeio); desvio apenas por parecer veterinário escrito - Parcialmente coberto no n.º 6, art.º 47.º @rgbeac prevê acesso diário a área de exercício exterior 2x/dia durante 30 minutos (= 1h total), mas não contém a proibição explícita de manutenção exclusiva no interior nem o mecanismo de desvio por parecer veterinário escrito. Ausente no @codigo e @legislacao. 
+Prever exceções para cães de guarda de rebanho</t>
         </is>
       </c>
       <c r="O12" s="11" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P12" s="11" t="inlineStr">
-        <is>
-          <t>Princípios cobertos; faltam normas técnicas pormenorizadas</t>
-        </is>
-      </c>
+          <t>Sim - Portaria complementar com especificações técnicas</t>
+        </is>
+      </c>
+      <c r="P12" s="11" t="inlineStr"/>
     </row>
     <row r="13" ht="120" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Saúde e Monitorização Sanitária</t>
+          <t>Saúde</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Art.º 16.º do Regulamento 2023/0447 (PE/Conselho)</t>
+          <t>Art.º 16.º do Regulamento 2023/0447 (PE/Conselho)  |  EN</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>1.	Operators  shall ensure that:
-(a)	dogs or cats for which they are responsible are inspected by animal carers at least once a day and that vulnerable dogs and cats, such as newborns, ill or injured dogs and cats, and peri-partum bitches and queens, are inspected more frequently;
-(b)	dogs or cats with  compromised welfare are, where necessary, transferred  without undue delay to a separate area and, where necessary, receive appropriate treatment;
-(c)	where the recovery of a dog or a cat whose welfare is compromised is not achievable and the dog or cat experiences severe pain or suffering, a veterinarian is consulted without undue delay to decide whether the dog or cat is to be euthanised to end its suffering, and, if that is the case, to perform the euthanasia using anaesthesia and analgesia.
-(d)	measures  are taken to prevent and control external and internal parasites, and vaccinations are carried out to prevent common diseases to which dogs or cats are likely to be exposed.
-(e)	enrichments  that are used do not present a significant risk to dogs and cats of injury or biological or chemical contamination or any other health risk.
+          <t>Operators shall ensure that:
+dogs or cats for which they are responsible are inspected by animal carers at least once a day and that vulnerable dogs and cats, such as newborns, ill or injured dogs and cats, and peri-partum bitches and queens, are inspected more frequently.
+dogs or cats with compromised welfare are, where necessary, transferred without undue delay to a separate area and, where necessary, receive appropriate treatment;
+where the recovery of a dog or a cat whose welfare is compromised is not achievable and the dog or cat experiences severe pain or suffering, a veterinarian is consulted without undue delay to decide whether the dog or cat is to be euthanised to end its suffering, and, if that is the case, to perform the euthanasia using anaesthesia and analgesia.
+measures are taken to prevent and control external and internal parasites, and vaccinations are carried out to prevent common diseases to which dogs or cats are likely to be exposed.
+enrichments that are used do not present a significant risk to dogs and cats of injury or biological or chemical contamination or any other health risk.
 Point (a) shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
 Member States may grant exemptions from point (c) in cases of emergency, where no veterinarian can be reached without undue delay, provided that national rules are put in place to ensure that:
-(i)	any immediate action ending the life of the dog or cat with minimum pain and suffering using a method inducing instant death is undertaken by a trained competent person;
-(ii)	for the purposes of the official control under Regulation (EU) 2017/625, the operator keeps a record of the use of the exemption.
-2.	Operators of breeding establishments shall ensure that:
-(a)	measures are taken to safeguard the health of dogs or cats in accordance with point 3 of Annex I;
-(b)	bitches or queens are bred only if they have reached a minimum age and skeletal maturity in accordance with point 3 of Annex I  , and only if they have no diagnosed disease, clinical sign of diseases or physical conditions which could negatively impact their pregnancy and welfare;
-(c)	the litter-giving pregnancies of bitches or queens follows a maximum frequency in accordance with point 3 of Annex I;
-(d)	lactating queens are not mated or inseminated;
-(e)	 dogs and cats which are no longer used for reproduction, including as a result of the provisions of this Regulation, are either kept or sold, donated or rehomed, and not killed or abandoned.</t>
+any immediate action ending the life of the dog or cat with minimum pain and suffering using a method inducing instant death is undertaken by a trained competent person;
+for the purposes of the official control under Regulation (EU) 2017/625, the operator keeps a record of the use of the exemption.
+Operators of breeding establishments shall ensure that:
+measures are taken to safeguard the health of dogs or cats in accordance with point 3 of Annex I;
+bitches or queens are bred only if they have reached a minimum age and skeletal maturity in accordance with point 3 of Annex I , and only if they have no diagnosed disease, clinical sign of diseases or physical conditions which could negatively impact their pregnancy and welfare;
+the litter-giving pregnancies of bitches or queens follows a maximum frequency in accordance with point 3 of Annex I;
+lactating queens are not mated or inseminated;
+dogs and cats which are no longer used for reproduction, including as a result of the provisions of this Regulation, are either kept or sold, donated or rehomed, and not killed or abandoned.</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>1 — Os operadores devem assegurar que:
-(a) os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados e fêmeas em período peri-parto, são inspecionados com maior frequência;
-(b) os cães e gatos com bem-estar comprometido são, quando necessário, transferidos sem demora injustificada para uma área separada e, se necessário, recebem tratamento adequado;
-(c) quando a recuperação de um cão ou gato com bem-estar comprometido não seja alcançável e o animal experiencie dor ou sofrimento severo, um médico veterinário é consultado sem demora injustificada para decidir se o animal deve ser objeto de eutanásia para pôr termo ao seu sofrimento e, em caso afirmativo, para realizar a eutanásia com recurso a anestesia e analgesia;
-(d) são implementadas medidas de prevenção e controlo de parasitas externos e internos, bem como vacinações para prevenção de doenças comuns às quais os cães ou gatos são suscetíveis de estar expostos;
-(e) os enriquecimentos não apresentam risco significativo de lesões ou de contaminação biológica ou química, nem qualquer outro risco para a saúde.
+          <t>Os operadores devem assegurar que:
+os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados e fêmeas em período peri-parto, são inspecionados com maior frequência;
+os cães e gatos com bem-estar comprometido são, quando necessário, transferidos sem demora injustificada para uma área separada e, se necessário, recebem tratamento adequado;
+quando a recuperação de um cão ou gato com bem-estar comprometido não seja alcançável e o animal experiencie dor ou sofrimento severo, um médico veterinário é consultado sem demora injustificada para decidir se o animal deve ser objeto de eutanásia para pôr termo ao seu sofrimento e, em caso afirmativo, para realizar a eutanásia com recurso a anestesia e analgesia;
+são implementadas medidas de prevenção e controlo de parasitas externos e internos, bem como vacinações para prevenção de doenças comuns às quais os cães ou gatos são suscetíveis de estar expostos;
+os enriquecimentos não apresentam risco significativo de lesões ou de contaminação biológica ou química, nem qualquer outro risco para a saúde.
 A alínea (a) não se aplica aos cães de guarda de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para fins de guarda ou treino.
 Os Estados-Membros podem conceder derrogações relativamente à alínea (c) em casos de emergência, quando não seja possível contactar um médico veterinário sem demora injustificada, desde que sejam estabelecidas regras nacionais que assegurem que:
-(i) é tomada imediatamente uma ação que ponha fim à vida do cão ou gato com o mínimo de dor e sofrimento, utilizando um método que induza a morte instantânea, por uma pessoa competente e devidamente habilitada;
-(ii) o operador mantém um registo da utilização da derrogação para efeitos de controlo oficial.
-2 — Os operadores de estabelecimentos de criação devem adicionalmente assegurar que:
-(-a) são tomadas medidas para salvaguardar a saúde dos cães ou gatos em conformidade com o ponto 3 do Anexo I;
-(-b) as cadelas ou gatas só são reproduzidas se tiverem atingido a idade mínima e a maturidade esquelética em conformidade com o ponto 3 do Anexo I, e não apresentem doença diagnosticada, sinais clínicos de doença ou condições físicas que possam impactar negativamente a gestação e o seu bem-estar;
-(-c) a frequência de gestações com ninhadas de cadelas ou gatas respeita a frequência máxima fixada no ponto 3 do Anexo I;
-(-d) as gatas a lactar não são acasaladas nem inseminadas;
-(-e) os cães e gatos que deixem de ser utilizados para reprodução, nomeadamente em resultado das disposições do presente Regulamento, são mantidos ou vendidos, doados ou realojados, não sendo mortos nem abandonados.</t>
+é tomada imediatamente uma ação que ponha fim à vida do cão ou gato com o mínimo de dor e sofrimento, utilizando um método que induza a morte instantânea, por uma pessoa competente e devidamente habilitada;
+o operador mantém um registo da utilização da derrogação para efeitos de controlo oficial.
+Os operadores de estabelecimentos de criação devem assegurar que:
+ são tomadas medidas para salvaguardar a saúde dos cães ou gatos em conformidade com o ponto 3 do Anexo I;
+as cadelas ou gatas só se reproduzem se tiverem atingido a idade mínima e a maturidade esquelética em conformidade com o ponto 3 do Anexo I, e não apresentem doença diagnosticada, sinais clínicos de doença ou condições físicas que possam impactar negativamente a gestação e o seu bem-estar;
+ As gravidezes das cadelas e gatas que resultem numa ninhada respeitem uma frequência máxima fixada no ponto 3 do Anexo I;
+ as gatas em lactação não sejam acasaladas nem inseminadas;
+ os cães e gatos que deixem de ser utilizados para reprodução, nomeadamente em resultado das disposições do presente Regulamento, são mantidos ou vendidos, doados ou realojados, não sendo mortos nem abandonados.</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Art.º 33.º do RGBEAC — Regime Geral do Bem-Estar dos Animais de Companhia (proposta, jun. 2025)</t>
+          <t>Arts.º 33.º e 55.º do RGBEAC — Regime Geral do Bem-Estar dos Animais de Companhia (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Artigo 33.º — Cuidados de saúde
-1 — Os detentores dos animais de companhia devem assegurar-lhes os cuidados de saúde adequados, nomeadamente seguindo as orientações da DGAV em matéria de vacinação e tratamentos obrigatórios, bem como consultas regulares junto de médico veterinário.
-2 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
-3 — Os médicos veterinários e os centros de atendimento médico-veterinário (CAMV) devem manter um arquivo com os dados clínicos de cada animal, pelo período mínimo de cinco anos, que ficará à disposição das autoridades competentes.
-[dim]4 — Os CAMV, enquanto estabelecimentos de saúde, colaborarão na vigilância epidemiológica das doenças de notificação obrigatória que detetem e no seu controlo.
-[dim]5 — Os médicos veterinários denunciam, junto da DGAV ou demais entidades com competência de fiscalização do cumprimento das normas constantes do presente decreto-lei, sempre que, no exercício de sua profissão, suspeitem de maus-tratos a animais de companhia.</t>
+          <t>Artigo 33.º — Cuidados de saúde (geral)
+Os detentores dos animais de companhia devem assegurar-lhes os cuidados de saúde adequados, nomeadamente seguindo as orientações da DGAV em matéria de vacinação e tratamentos obrigatórios, bem como consultas regulares junto de médico veterinário.
+Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
+Os médicos veterinários e os centros de atendimento médico-veterinário (CAMV) devem manter um arquivo com os dados clínicos de cada animal, pelo período mínimo de cinco anos, que ficará à disposição das autoridades competentes.
+Os CAMV, enquanto estabelecimentos de saúde, colaborarão na vigilância epidemiológica das doenças de notificação obrigatória que detetem e no seu controlo.
+Os médicos veterinários denunciam, junto da DGAV ou demais entidades com competência de fiscalização do cumprimento das normas constantes do presente decreto-lei, sempre que, no exercício de sua profissão, suspeitem de maus-tratos a animais de companhia.
+Artigo 52.º - Maneio
+A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico que possua formação teórica e prática específica ministrada ou certificada pela DGAV e em número adequado à quantidade e espécies animais que alojam. 
+Todos os animais devem ser alvo de inspeção no início e final do dia de trabalho e a cada quatro horas, sendo de imediato prestados os primeiros cuidados aos que tiverem sinais que levem a suspeitar estarem doentes, lesionados ou com alterações comportamentais. 
+O maneio dos animais deve ser feito de forma a não lhes causar quaisquer dores, sofrimento ou distúrbios desnecessários, salvaguardando o seu bem-estar. 
+As interações do pessoal técnico com os animais devem ser positivas, regulares, previsíveis, e não forçadas. 
+Quando houver necessidade de recorrer a meios de contenção, não devem estes causar ferimentos, dores ou angústia desnecessária aos animais.
+Todos os alojamentos para hospedagem de cães e gatos, à exceção dos alojamentos com fins higiénicos, devem dispor de um plano de socialização e enriquecimento ambiental
+Artigo 55.º — Cuidados de saúde animal (Capítulo dos Alojamentos)
+Os animais devem ser sujeitos a exames médico-veterinários de rotina, vacinações e desparasitações sempre que aconselhável.
+Sem prejuízo de quaisquer medidas determinadas pela DGAV, deve existir um programa de profilaxia médica e sanitária elaborado e supervisionado pelo médico veterinário responsável.
+Aos animais feridos ou doentes devem ser de imediato assegurados os cuidados médico-veterinários adequados.
+Os animais doentes ou lesionados devem ser isolados em instalações adequadas e equipadas, se adequado à espécie, com cama seca e confortável, salvaguardando o seu bem-estar.
+Os medicamentos, produtos ou substâncias de prescrição médico-veterinária devem ser armazenados em locais secos e com acesso restrito.
+A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior deve ser feita sob orientação do médico veterinário responsável.</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -1896,7 +2212,20 @@
       <c r="H13" s="6" t="inlineStr">
         <is>
           <t>Artigo 6.º — Cuidados médico-veterinários
-O detentor do animal deve assegurar ao animal ferido ou doente os cuidados médico-veterinários adequados, designadamente retirando o mesmo do alojamento sempre que este seja um local de venda.</t>
+O detentor do animal deve assegurar ao animal ferido ou doente os cuidados médico-veterinários adequados, designadamente retirando o mesmo do alojamento sempre que este seja um local de venda.
+Artigo 47.º - Maneio 
+- Nos alojamentos de hospedagem de animais, nos centros de recolha e nas hospedagens com fins médico-veterinários, a observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal com aptidão para o efeito e em número adequado à quantidade e espécies animais que alojam. 
+- O maneio deve ser feito por pessoal que possua experiência ou formação adequada e sob a orientação de um médico veterinário ou pessoa com competência para o efeito. 
+- Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados aos que tiverem sinais que levem a suspeitar estarem doentes, lesionados ou com alterações comportamentais. 
+- O manuseamento dos animais deve ser feito de forma a não lhes causar quaisquer dores, sofrimento ou distúrbios desnecessários. 
+- Quando houver necessidade de recorrer a meios de contenção, não devem estes causar ferimentos, dores ou angústia desnecessários aos animais. 
+Artigo 49.º - Cuidados de saúde animal
+Sem prejuízo de quaisquer medidas determinadas pela DGAV, nos locais de criação, manutenção e venda, bem como nos centros de recolha e alojamentos de hospedagem, deve existir um programa de profilaxia médica e sanitária, elaborado e supervisionado pelo médico veterinário responsável e executado por profissionais habilitados para o efeito.
+No âmbito do número anterior, os animais devem ser sujeitos a exames médico-veterinários de rotina, vacinações e desparasitações sempre que aconselhável.
+Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
+Sempre que se justifique, os animais doentes ou lesionados devem ser isolados em instalações adequadas e equipadas, se for caso disso, com cama seca e confortável.
+Os medicamentos, produtos ou substâncias de prescrição médico-veterinária devem ser armazenados em locais secos e com acesso restrito.
+A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior, deve ser feita sob orientação do médico veterinário responsável.</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -1908,37 +2237,38 @@
         <is>
           <t>Artigo 13.º — Maneio
 1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
-[dim]2 — O maneio deve ser feito por pessoal que possua formação teórica e prática específica ou sob a supervisão de uma pessoa competente para o efeito.
+2 — O maneio deve ser feito por pessoal que possua formação teórica e prática específica ou sob a supervisão de uma pessoa competente para o efeito.
 3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados aos que tiverem sinais que levem a suspeitar estarem doentes, lesionados ou com alterações comportamentais.
-[dim]4 — O manuseamento dos animais deve ser feito de forma a não lhes causar quaisquer dores, sofrimento ou distúrbios desnecessários.
-[dim]5 — Quando houver necessidade de recorrer a meios de contenção, não devem estes causar ferimentos, dores ou angústia desnecessários aos animais.
+4 — O manuseamento dos animais deve ser feito de forma a não lhes causar quaisquer dores, sofrimento ou distúrbios desnecessários.
+5 — Quando houver necessidade de recorrer a meios de contenção, não devem estes causar ferimentos, dores ou angústia desnecessários aos animais.
 Artigo 16.º — Cuidados de saúde animal
 1 — Sem prejuízo de quaisquer medidas determinadas pela DGAV, deve existir um programa de profilaxia médica e sanitária devidamente elaborado e supervisionado pelo médico veterinário responsável e executado por profissionais competentes.
 2 — No âmbito do número anterior, os animais devem ser sujeitos a exames médico-veterinários de rotina, vacinações e desparasitações sempre que aconselhável.
 3 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
 4 — Sempre que se justifique, os animais doentes ou lesionados devem ser isolados em instalações adequadas e equipadas, se for caso disso, com cama seca e confortável.
-[dim]5 — Os medicamentos, produtos ou substâncias de prescrição médico-veterinária devem ser armazenados em locais secos e com acesso restrito.
-[dim]6 — A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior deve ser feita sob orientação do médico veterinário responsável.</t>
+5 — Os medicamentos, produtos ou substâncias de prescrição médico-veterinária devem ser armazenados em locais secos e com acesso restrito.
+6 — A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior deve ser feita sob orientação do médico veterinário responsável.</t>
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>O DL n.º 276/2001 prevê inspeção diária (n.º 3 do art.º 13.º) e programa de profilaxia supervisionado por veterinário (n.º 1 do art.º 16.º) — alinhamento parcial com as als. (a) e (d) do n.º 1 do art.º 13.º do @regulamento. Lacunas: (1) não distingue animais vulneráveis com maior frequência de inspeção; (2) não prevê isolamento em área separada com tratamento (al. (b)); (3) não exige consulta veterinária para decisão de eutanásia com anestesia/analgesia (al. (c)); (4) nenhuma das obrigações sanitárias para criadores previstas no n.º 2 está contemplada: sem idade mínima de reprodução, sem frequência máxima de partos, sem proibição de cobrição de fêmeas a lactar, sem regime de rehoming.</t>
+          <t>Em análise</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>O @codigo limita os cuidados médico-veterinários ao animal ferido ou doente (art.º 6.º) — sem qualquer obrigação de inspeção diária, programa de profilaxia ou isolamento. É o diploma com maior divergência face ao n.º 1 do art.º 13.º do @regulamento, omitindo igualmente todas as obrigações sanitárias específicas para criadores previstas no n.º 2.</t>
+          <t>Em análise</t>
         </is>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac (art.º 33.º) centra os cuidados de saúde no detentor em geral (n.ºs 1 a 3), sem distinguir obrigações reforçadas para operadores de criação. Não prevê: inspeção diária sistemática por cuidadores; isolamento imediato de animais com bem-estar comprometido; nem qualquer dos requisitos sanitários para criadores do n.º 2 do art.º 13.º do @regulamento. Os n.ºs 4 e 5 (CAMV e denúncia de maus-tratos) não têm correspondência direta no @regulamento.</t>
+          <t>O @rgbeac (art.º 33.º) centra os cuidados de saúde no detentor em geral (n.ºs 1 a 3), sem distinguir obrigações reforçadas para operadores de criação. Os n.ºs 4 e 5 (CAMV e denúncia de maus-tratos) não têm correspondência direta no @regulamento.</t>
         </is>
       </c>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>A @legislacao vigente (DL n.º 276/2001) tem o maior alinhamento, mas insuficiente. Necessidade de alteração dos três diplomas: (1) introduzir inspeção diária diferenciada para animais vulneráveis (al. (a) do n.º 1 do art.º 13.º do @regulamento); (2) criar obrigação de isolamento e tratamento imediato (al. (b)); (3) regular o processo de eutanásia com supervisão veterinária e anestesia/analgesia (al. (c)); (4) para criadores (n.º 2): fixar idade mínima e maturidade esquelética das fêmeas reprodutoras, frequência máxima de partos conforme Anexo I, proibição de cobrição de fêmeas a lactar, e regime de rehoming dos animais retirados da reprodução.</t>
+          <t>Necessidade de alteração dos três diplomas: (1) introduzir inspeção diária diferenciada para animais vulneráveis (al. (a) do n.º 1 do art.º 13.º do @regulamento); (2) para criadores (n.º 2): fixar idade mínima e maturidade esquelética das fêmeas reprodutoras, frequência máxima de partos conforme Anexo I, proibição de cobrição de fêmeas a lactar, e regime de rehoming dos animais retirados da reprodução.
+Ver ainda análise do art.º 8.º do @regulamento, que tem as disposições sobre estratégias e saúde reprodutiva</t>
         </is>
       </c>
       <c r="O13" s="11" t="inlineStr">
@@ -1946,11 +2276,7 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="P13" s="11" t="inlineStr">
-        <is>
-          <t>(espaço para anotações da reunião)</t>
-        </is>
-      </c>
+      <c r="P13" s="11" t="inlineStr"/>
     </row>
     <row r="14" ht="120" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1960,55 +2286,58 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Art.º 17.º do Regulamento 2023/0447</t>
+          <t>Art.º 17.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>1.	Operators  shall ensure that measures are taken to meet the behavioural needs of  dogs and cats in accordance with point 4 of Annex I.
-2.	In addition, operators shall not keep dogs or cats in areas which limit their natural movements  , except in cases where Article 15(3), second subparagraph, applies or where the following procedures or treatments are performed:
-(a)	physical examinations ;
-(b)	the individual identification of dogs or cats, or reading such identification information;
-(c)	the collection of samples and vaccinations;
-(d)	procedures for grooming, hygienic, health or reproductive purposes other than mating;
-(e)	medical treatments, including surgical treatments or prescribed rehabilitation.
-3.	Tethering  for more than 1 hour shall be prohibited, except for the duration of a medical treatment or for participation in shows, exhibitions and competitions of dogs or cats.
-4.	Member States may grant exemptions from paragraph 3 for dogs intended for use in military, police and customs services that are kept in breeding or selling establishments.
-5.	Operators  shall ensure that dogs or cats are kept in conditions that allow them to exhibit non-harmful social behaviours and species-specific behaviours and to experience positive emotions.
-6.	Operators shall ensure that dogs or cats can socialise in accordance with point 4 of Annex I. Operators of breeding establishments shall have a documented strategy for such socialisation.
+          <t>Operators shall ensure that measures are taken to meet the behavioural needs of dogs and cats in accordance with point 4 of Annex I.
+In addition, operators shall not keep dogs or cats in areas which limit their natural movements, except in cases where Article 15(3), second subparagraph, applies or where the following procedures or treatments are performed:
+physical examinations;
+the individual identification of dogs or cats, or reading such identification information;
+the collection of samples and vaccinations;
+procedures for grooming, hygienic, health or reproductive purposes other than mating;
+medical treatments, including surgical treatments or prescribed rehabilitation.
+Tethering for more than 1 hour shall be prohibited, except for the duration of a medical treatment or for participation in shows, exhibitions and competitions of dogs or cats.
+Member States may grant exemptions from paragraph 3 for dogs intended for use in military, police and customs services that are kept in breeding or selling establishments.
+Operators shall ensure that dogs or cats are kept in conditions that allow them to exhibit non-harmful social behaviours and species-specific behaviours and to experience positive emotions.
+Operators shall ensure that dogs or cats can socialise in accordance with point 4 of Annex I. Operators of breeding establishments shall have a documented strategy for such socialisation.
 By way of derogation from the first subparagraph, socialisation requirements shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes, or to herding dogs during seasonal transhumance.
-7.	Operators shall ensure that enrichments  are provided and accessible to all dogs or cats, creating a stimulating environment for them, enabling them to develop and exhibit species-specific behaviour and reducing their frustration.</t>
+7.	Operators shall ensure that enrichments are provided and accessible to all dogs or cats, creating a stimulating environment for them, enabling them to develop and exhibit species-specific behaviour and reducing their frustration.</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores devem assegurar que medidas são tomadas para satisfazer as necessidades comportamentais de cães ou gatos em conformidade com o ponto 4 do Anexo I.
-2. Os operadores não devem manter cães ou gatos em áreas que restringem os seus movimentos naturais, exceto no caso do artigo 15.º (parágrafo 3), segundo parágrafo, ou para realizar os seguintes procedimentos ou tratamentos:
-a) exames físicos;
-b) identificação individual de cães ou gatos e leitura da informação de identificação;
-c) recolha de amostras e vacinações;
-d) procedimentos de higiene, higiénicos, de saúde ou reprodutivos que não sejam acasalamento;
-e) tratamento médico, incluindo tratamento cirúrgico ou reabilitação prescrita.
-3. O amarrar por mais de 1 hora é proibido, exceto durante a duração de um tratamento médico ou participação em espetáculos, exposições e competições de cães e gatos.
-4.	Os Estados-Membros podem conceder derrogações do n.º 3 para cães destinados a uso em serviços militares, policiais e aduaneiros que são mantidos em estabelecimentos de criação ou venda.
-5.	Os operadores devem assegurar que condições estão em vigor para permitir aos cães ou gatos expressar comportamentos sociais não prejudiciais, comportamentos específicos da espécie e a possibilidade de experimentar emoções positivas.
-6.	Os operadores devem assegurar que os cães ou gatos podem socializar em conformidade com o ponto 4 do Anexo I. Os operadores de estabelecimentos de criação devem ter uma estratégia documentada para tal socialização.
-	A título de derrogação do primeiro parágrafo, os requisitos de socialização não se aplicam a cães guardiões de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para guarda ou treino, nem a cães de pastoreio durante transumância sazonal.
-7.	Os operadores devem assegurar que enriquecimento é fornecido e acessível a todos os cães ou gatos, criando um ambiente estimulante, permitindo comportamento específico da espécie e reduzindo a sua frustração.</t>
+          <t>Os operadores devem assegurar que medidas são tomadas para satisfazer as necessidades comportamentais de cães ou gatos em conformidade com o ponto 4 do Anexo I.
+Os operadores não devem manter cães ou gatos em áreas que restringem os seus movimentos naturais, exceto no caso do artigo 15.º (parágrafo 3), segundo parágrafo, ou para realizar os seguintes procedimentos ou tratamentos:
+exames físicos;
+identificação individual de cães ou gatos e leitura da informação de identificação;
+recolha de amostras e vacinações;
+procedimentos de higiene, higiénicos, de saúde ou reprodutivos que não sejam acasalamento;
+tratamento médico, incluindo tratamento cirúrgico ou reabilitação prescrita.
+O acorrentamento por mais de 1 hora é proibido, exceto durante a duração de um tratamento médico ou participação em espetáculos, exposições e competições de cães e gatos.
+Os Estados-Membros podem conceder isenções ao disposto no n.º 3 para os cães destinados a ser utilizados nos serviços militares, policiais e aduaneiros que sejam mantidos em estabelecimentos de criação ou de venda.
+ Os operadores devem assegurar que os cães ou gatos sejam mantidos em condições que lhes permitam exibir comportamentos sociais não prejudiciais e comportamentos específicos da espécie, bem como vivenciar emoções positivas.
+Os operadores devem assegurar que os cães ou gatos possam socializar em conformidade com o ponto 4 do anexo I. Os operadores de estabelecimentos de criação devem dispor de uma estratégia documentada para essa socialização. 
+Em derrogação do primeiro parágrafo, os requisitos de socialização não se aplicam aos cães de proteção de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães sejam utilizados para fins de guarda ou de treino, nem aos cães de pastoreio durante a transumância sazonal.
+Os operadores devem assegurar que o enriquecimento seja facultado e esteja acessível a todos os cães ou gatos, criando-lhes um ambiente estimulante que lhes permita desenvolver e exibir comportamentos específicos da espécie e reduza a sua frustração.</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>RGBEAC (proposta, jun. 2025) - Artigos 10, 12, 13, 14, 15</t>
+          <t>RGBEAC (proposta, jun. 2025) - Artigos 7 a 12 e 52º</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Especificação clara: 'exercício físico e estímulo mental'.
-'Contato social adequado'.
+          <t>Analisado no Art.º 8.º do Reg.
+Especificação clara: 'exercício físico e estímulo mental', 'Contato social adequado'. (Art.º 10.º).
 Métodos de 'reforço positivo' (OBRIGATÓRIO).
 Proibição explícita de 'métodos aversivos, punitivos ou violentos'.
-Documentação obrigatória de estratégia de socialização (criadores).</t>
+n.º 7, do art.º 52.º 
+Todos os alojamentos para hospedagem de cães e gatos, à exceção dos alojamentos com fins higiénicos, devem dispor de um plano de socialização e enriquecimento ambiental.
+(Documentação obrigatória de estratégia de socialização - criadores).
+Fatores de socialização também previstos no treino dos perigosos e PP.</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -2020,7 +2349,7 @@
         <is>
           <t>Artigo 5.º - Princípios que proíbem violência e maus-tratos, garantem bem-estar.
 Artigo 13.º - Espaço para exercício físico e expressão de comportamentos naturais.
-Cobertura GENÉRICA: não especifica enriquecimento, socialização ou método de treino baseado em reforço positivo.</t>
+Analisado no art.º 8.º do Reg.</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -2030,40 +2359,28 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>Artigo 8.º — 1 — Os animais devem dispor de um espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir: a) A prática de exercício físico adequado; b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
+          <t>1 — Os animais devem dispor de um espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir: a) A prática de exercício físico adequado; b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
 2 — Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.</t>
         </is>
       </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t>PARCIAL - Legislação vigente oferece cobertura genérica</t>
-        </is>
-      </c>
+      <c r="K14" s="8" t="inlineStr"/>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>PARCIAL - Genérico, sem especificações sobre socialização e enriquecimento</t>
+          <t>Sem especificações sobre socialização e enriquecimento</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>SIM - COBERTURA SIGNIFICATIVAMENTE EXPANDIDA</t>
-        </is>
-      </c>
-      <c r="N14" s="11" t="inlineStr">
-        <is>
-          <t>Legislação portuguesa oferece cobertura genérica. RGBEAC (2025) oferece avanço substancial com obrigatoriedade de reforço positivo e documentação de estratégia de socialização. Falta ainda regulamentação pormenorizada.</t>
-        </is>
-      </c>
+          <t>Cobertura mais significtiva</t>
+        </is>
+      </c>
+      <c r="N14" s="11" t="inlineStr"/>
       <c r="O14" s="11" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P14" s="11" t="inlineStr">
-        <is>
-          <t>RGBEAC alinha melhor; implementação de reforço positivo obrigatório recomendada</t>
-        </is>
-      </c>
+          <t>Em análise. RGBEAC alinha melhor; implementação de reforço positivo obrigatório recomendada</t>
+        </is>
+      </c>
+      <c r="P14" s="11" t="inlineStr"/>
     </row>
     <row r="15" ht="120" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -2073,41 +2390,41 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Art.º 18.º do Regulamento 2023/0447</t>
+          <t>Art.º 18.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>1.	Operators shall ensure that mutilations, including ear cropping, tail docking, claw removal or other partial or complete digit amputation, and resection of vocal cords or folds,  are not performed unless justified by medical indications, including where the procedure is prophylactic, with the sole purpose of maintaining or improving the health of dogs or cats or preventing their injury. In such cases, the procedure shall be performed  only under anaesthesia and prolonged analgesia and only by a veterinarian.
-2.	The medical indications justifying the mutilation, and the details of procedure carried out, shall be documented by a veterinarian. That document shall be retained by the operator and shall accompany the dog or cat when it is transferred to another establishment or owner. The operator of the establishment where the mutilation was performed shall retain a copy of the document for the first three years after that transfer.
-3.	By way of derogation from paragraph 1, Member States may allow ear cropping by notching or tipping cat ears in the context of marking stray cats when neutered under a ‘trap-neuter-return’ programme.
-4.	Operators shall ensure that neutering is performed  only under anaesthesia and prolonged analgesia and only by a veterinarian. However, Member States may allow the neutering of male cats to be performed by a licensed veterinary nurse.
-5.	Operators shall ensure that handling practices that cause pain or suffering are not performed, including:
-(a)	tying up body parts, unless required for medical reasons and limited to the minimum period necessary;
-(b)	the kicking, hitting, dragging, throwing or squeezing of dogs or cats;
-(c)	applying electric current to dogs or cats, unless performed for medical reasons;
-(d)	using  muzzles, unless required for medical reasons or animal or human safety reasons, limited to the minimum period necessary and where the dog or cat is supervised.
-(e)	using prong collars;
-(f)	using choke collars without a safety stop;
-(g)	lifting dogs or cats by the limbs,  head, ears, tail or hair, or lifting adult dogs or cats by the skin.
+          <t>Operators shall ensure that mutilations, including ear cropping, tail docking, claw removal or other partial or complete digit amputation, and resection of vocal cords or folds,  are not performed unless justified by medical indications, including where the procedure is prophylactic, with the sole purpose of maintaining or improving the health of dogs or cats or preventing their injury. In such cases, the procedure shall be performed  only under anaesthesia and prolonged analgesia and only by a veterinarian.
+The medical indications justifying the mutilation, and the details of procedure carried out, shall be documented by a veterinarian. That document shall be retained by the operator and shall accompany the dog or cat when it is transferred to another establishment or owner. The operator of the establishment where the mutilation was performed shall retain a copy of the document for the first three years after that transfer.
+By way of derogation from paragraph 1, Member States may allow ear cropping by notching or tipping cat ears in the context of marking stray cats when neutered under a ‘trap-neuter-return’ programme.
+Operators shall ensure that neutering is performed  only under anaesthesia and prolonged analgesia and only by a veterinarian. However, Member States may allow the neutering of male cats to be performed by a licensed veterinary nurse.
+Operators shall ensure that handling practices that cause pain or suffering are not performed, including:
+tying up body parts, unless required for medical reasons and limited to the minimum period necessary;
+the kicking, hitting, dragging, throwing or squeezing of dogs or cats;
+applying electric current to dogs or cats, unless performed for medical reasons;
+using  muzzles, unless required for medical reasons or animal or human safety reasons, limited to the minimum period necessary and where the dog or cat is supervised.
+using prong collars;
+using choke collars without a safety stop;
+lifting dogs or cats by the limbs,  head, ears, tail or hair, or lifting adult dogs or cats by the skin.
 Member States may grant exemptions from the first subparagraph for dogs intended for use in military, police or customs services.</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores devem assegurar que mutilações, incluindo corte de orelhas, corte de cauda, remoção de garras ou amputação parcial ou completa de dígitos, e ressecção de cordas vocais ou pregas, não são realizadas a menos que por indicação médica, que pode incluir profilática, com o único propósito de preservar, melhorar a saúde de cães ou gatos ou prevenir ferimentos. Nesse caso, o procedimento deve ser realizado apenas sob anestesia e analgesia prolongada e por um médico veterinário.
-2.	A indicação médica para a mutilação e os detalhes do procedimento realizado devem ser documentados por um médico veterinário. Este documento deve ser retido pelo operador até que o cão ou gato, juntamente com este documento, seja transferido para outro estabelecimento ou proprietário. O operador do estabelecimento onde a mutilação foi realizada deve reter uma cópia do documento durante três anos após a transferência do cão ou gato.
-3.	A título de derrogação do parágrafo 1, os Estados-Membros podem permitir o corte de orelhas por entalhe ou ponta das orelhas de gatos no contexto de marcação de gatos vadios quando esterilizados sob um programa de captura-esterilização-libertação.
-4.	Os operadores devem assegurar que a esterilização é realizada apenas sob anestesia e analgesia prolongada e por um médico veterinário. A título de derrogação, os Estados-Membros podem permitir que a esterilização de gatos machos seja realizada por um enfermeiro veterinário licenciado.
-5.	Os operadores devem assegurar que práticas de manipulação que causam dor ou sofrimento não são realizadas, incluindo:
+2. A indicação médica para a mutilação e os detalhes do procedimento realizado devem ser documentados por um médico veterinário. Este documento deve ser retido pelo operador até que o cão ou gato, juntamente com este documento, seja transferido para outro estabelecimento ou proprietário. O operador do estabelecimento onde a mutilação foi realizada deve reter uma cópia do documento durante três anos após a transferência do cão ou gato.
+3. A título de derrogação do parágrafo 1, os Estados-Membros podem permitir o corte de orelhas por entalhe ou ponta das orelhas de gatos no contexto de marcação de gatos errantes quando esterilizados sob um programa de captura-esterilização-libertação.
+4. Os operadores devem assegurar que a esterilização é realizada apenas sob anestesia e analgesia prolongada e por um médico veterinário. A título de derrogação, os Estados-Membros podem permitir que a esterilização de gatos machos seja realizada por um enfermeiro veterinário licenciado.
+5. Os operadores devem assegurar que práticas de manipulação que causam dor ou sofrimento não são realizadas, incluindo:
 a)	amarrar partes do corpo a menos que por razões médicas em cujo caso a duração deve ser limitada ao período mínimo necessário;
 b)	chutar, bater, arrastar, atirar, apertar cães ou gatos;
 c)	aplicar corrente elétrica a cães ou gatos a menos que realizado por razões médicas;
-d)	uso de focinheiras, a menos que necessário por razões médicas, segurança animal ou humana, em cujo caso a duração deve ser limitada ao período mínimo necessário e o cão ou gato deve ser supervisionado.
+d)	uso de açaimos, a menos que necessário por razões médicas, segurança animal ou humana, em cujo caso a duração deve ser limitada ao período mínimo necessário e o cão ou gato deve ser supervisionado.
 e)	uso de colares de espinhos;
 f)	uso de colares de estrangulamento sem paragem de segurança;
 g)	levantar cães ou gatos pelas extremidades, cabeça, orelhas, cauda ou pêlo, ou levantar cães ou gatos adultos pela pele.
-	Os Estados-Membros podem conceder derrogações do primeiro parágrafo para cães destinados a uso em serviços militares, policiais ou aduaneiros.</t>
+Os Estados-Membros podem conceder derrogações do primeiro parágrafo para cães destinados a uso em serviços militares, policiais ou aduaneiros.</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2117,11 +2434,16 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Lista idêntica de mutilações proibidas ao Código.
-Referência a 'boas práticas internacionais' (alinhamento com Reg. 2023/0447).
-Alargamento: 'qualquer amputação sem razão médica veterinária'.
-Ênfase em anestesia e analgesia prolongada.
-Documentação obrigatória de indicação médica.</t>
+          <t>Art. 12.º
+i)	Sujeitá-los a intervenções cirúrgicas, com o objetivo de modificar a sua aparência ou alcançar outros fins não curativos, ou não destinados a impedir a reprodução, em particular, corte da cauda, secção das cordas vocais, remoção de unhas ou dentes, e corte das orelhas que não seja realizada para fins de identificação de animais esterilizados conforme boas práticas internacionais
+(…)
+Administrar-lhes substâncias, tratamentos ou procedimentos com vista a aumentar ou diminuir o nível natural das suas capacidades fisiológicas e etológicas ou que não tenham fins médico-veterinários;
+Sujeitá-lo a amputações sem razão médica veterinária que o justifique;
+Artigo 34.º- Intervenções cirúrgicas
+1 – As intervenções cirúrgicas com o objetivo da modificação da aparência ou com fins não curativos ou não destinados a impedir a reprodução dos animais são proibidas, nos termos do disposto na alínea i) do n.º 1 do artigo 12.º.
+2 – O detentor de animal sujeito a intervenção curativa que modifique a sua aparência deve possuir documento comprovativo da necessidade da mesma, passado pelo médico veterinário que a ela procedeu, sob a forma de atestado do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura, ou, no caso de animais importados, documento comprovativo da necessidade dessa intervenção, emitida pelo médico veterinário que a ela procedeu, legalizado pela autoridade competente do respetivo país..
+Artigo 22.º - Controlo da reprodução pelo detentor
+O detentor de um animal de companhia que pretenda controlar a reprodução do mesmo deve fazê-lo de acordo com as orientações de um médico veterinário, salvaguardando sempre o mínimo sofrimento do animal"</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -2131,13 +2453,15 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Artigo 51.º - Intervenções cirúrgicas exclusivamente por médico veterinário.
-Artigo 52.º - Proibição específica de mutilações:
-- Corte de orelhas (exceto fins medicinais)
-- Corte de cauda (revogado em 2015)
-- Ressecção de cordas vocais
-- Remoção de unhas/dentes
-- Exceções: reprodução e interesse do animal (com documentação)</t>
+          <t>Artigo 51.o Intervenções cirúrgicas 
+As intervenções cirúrgicas têm de ser executadas por um médico veterinário. 
+Artigo 52.o - Mutilações 
+- São proibidas as mutilações que modifiquem a aparência dos animais ou que sejam realizadas com objetivos não curativos, designadamente o corte de orelhas ou de cordas vocais e a excisão de garras ou unhas, de dentes ou presas.  
+- Excetuam-se do disposto no número anterior as intervenções cirúrgicas feitas com vista a impedir a reprodução, por razões médico-veterinárias, ou no interesse particular do animal. 
+- O corte de caudas é proibido para todos os cães nascidos a partir de 1 de Janeiro de 2015.  
+- Os detentores de animais de companhia que os apresentem com quaisquer mutilações que modifiquem a aparência dos animais, devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa mutilação, nomeadamente discriminando que as mesmas foram feitas por razões médico-veterinárias ou no interesse particular do animal ou ainda, como nos casos previstos no DL n.º 315/2009, de 29 outubro,alterado pelo Decreto-Lei n.º 260/2012, de 12 de dezembro, para impedir a reprodução. 	
+- O documento referido no número anterior deve ter a forma de um atestado, do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura, bem como a causa da mutilação. 
+- Os detentores de animais importados que apresentem quaisquer das amputações referidas no n.º 1 devem possuir documento comprovativo da necessidade dessa mutilação, passada pelo médico veterinário que a ela procedeu, legalizado pela autoridade competente do respetivo país.</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
@@ -2147,28 +2471,24 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>Artigo 18.º — 1 — Os detentores de animais de companhia que os apresentem com quaisquer amputações que modifiquem a aparência dos animais ou com fins não curativos devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa amputação.
+          <t>Artigo 17.º 
+As intervenções cirúrgicas, nomeadamente as destinadas ao corte de caudas nos canídeos, têm de ser executadas por um médico veterinário.
+Artigo 18.º 
+ 1 — Os detentores de animais de companhia que os apresentem com quaisquer amputações que modifiquem a aparência dos animais ou com fins não curativos devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa amputação.
 2 — O documento referido no número anterior deve ter a forma de um atestado, do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura.</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
-        <is>
-          <t>SIM - DL 276/2001 cobre amputações documentadas</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>SIM - COBERTURA COMPLETA (Arts. 51-52)</t>
-        </is>
-      </c>
+      <c r="K15" s="8" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr"/>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>SIM - COBERTURA COMPLETA + EXPANSÃO</t>
+          <t>@rgbeac ressalva expressamente o corte das orelhas que não seja realizada para fins de identificação de animais esterilizados conforme boas práticas internacionais", o que cobre o essencial desta derrogação.</t>
         </is>
       </c>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>COBERTURA COMPLETA. Código do Animal (Arts. 51-52) implementa integralmente Art. 15.º. RGBEAC alinha substancialmente com Regulamento europeu. Sem divergências substanciais.</t>
+          <t>exige expressamente anestesia e analgesia prolongada como condição do procedimento.
+Rever proibições na análise do art.7.º</t>
         </is>
       </c>
       <c r="O15" s="11" t="inlineStr">
@@ -2176,11 +2496,7 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="P15" s="11" t="inlineStr">
-        <is>
-          <t>Correspondências completas - Cobertura legislativa adequada</t>
-        </is>
-      </c>
+      <c r="P15" s="11" t="inlineStr"/>
     </row>
     <row r="16" ht="120" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -2190,15 +2506,13 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Art.º 19.º do Regulamento 2023/0447</t>
+          <t>Art.º 19.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>1.	In aesthetic shows, exhibitions and competitions of dogs and cats, operators of breeding and selling establishments shall not use dogs or cats with excessive conformational traits, or dogs or cats which have been mutilated in a way that alters their physical characteristics.
-2.	When organising aesthetic shows, exhibitions and competitions of dogs and cats, organisers shall exclude dogs and cats which have excessive conformational traits or dogs or cats which have been mutilated in a way that alters their physical characteristics.
-CHAPTER III
-IDENTIFICATION AND REGISTRATION OF DOGS AND CATS</t>
+          <t>In aesthetic shows, exhibitions and competitions of dogs and cats, operators of breeding and selling establishments shall not use dogs or cats with excessive conformational traits, or dogs or cats which have been mutilated in a way that alters their physical characteristics.
+When organising aesthetic shows, exhibitions and competitions of dogs and cats, organisers shall exclude dogs and cats which have excessive conformational traits or dogs or cats which have been mutilated in a way that alters their physical characteristics.</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -2215,8 +2529,33 @@
       <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Artigo 39.º - Participação em eventos
-1 – A participação de animais de companhia em concursos, exposições, espetáculos, manifestações culturais, divertimentos públicos, atividades performativas, cinematográficas e audiovisuais, campanhas publicitárias, ou outros eventos onde participem animais de companhia carece de autorização do diretor geral da DGAV a área da realização da mesma, após parecer da respetiva câmara municipal.
-3 - Só serão admitidos no evento os animais de companhia que: a) Estejam registados no SIAC; b) Quando aplicável, possuam prova de vacinação antirrábica; c) Possuam vacinações contra as principais doenças infectocontagiosas; d) Não tenham sido submetidos a intervenções cirúrgicas em infração.</t>
+A participação de animais de companhia em concursos, exposições, espetáculos, manifestações culturais, divertimentos públicos, atividades performativas, cinematográficas e audiovisuais, campanhas publicitárias ou outros eventos onde participem animais de companhia carece de autorização do diretor-geral da DGAV da área da realização da mesma, após parecer da respetiva câmara municipal.
+A autorização prévia a que se refere o número anterior deve ser solicitada pela organização do evento com a antecedência mínima de 15 dias, mediante requerimento dirigido ao diretor-geral da DGAV, acompanhado dos seguintes documentos:
+a) Planta do local de realização do evento e parecer da respetiva câmara municipal, incluindo em relação ao ruído e recinto, se aplicável;
+b) Duração da participação dos animais no evento;
+c) Identificação do(s) médico(s) veterinário(s) responsável(eis);
+d) Regulamento sanitário e de bem-estar animal do evento, onde deve estar especificado o modo como se prevê dar cumprimento ao disposto nos números seguintes.
+Só serão admitidos no evento os animais de companhia que:
+a) Estejam registados no SIAC ou, no caso de animais provenientes de outros países, através do PAC que permita uma identificação rigorosa do animal;
+b) Quando aplicável, possuam prova de vacinação antirrábica dentro do prazo de validade, conforme determinado anualmente por despacho do diretor-geral da DGAV, nos termos da legislação e regulamentação em vigor;
+c) Possuam, dentro dos prazos de validade e efetuadas há mais de oito dias, as vacinações contra as principais doenças infectocontagiosas da espécie;
+d) Não tenham sido submetidos a intervenções cirúrgicas em infração ao disposto na alínea i) do n.º 1 do artigo 12.º e no artigo 34.º.
+Compete à organização do evento:
+a) Assegurar a presença do número de médicos veterinários necessários ao cumprimento do disposto neste decreto-lei;
+b) Assegurar que o local onde o evento decorre reúne as condições que permitam salvaguardar o disposto no presente decreto-lei;
+c) Salvaguardar os aspetos de segurança, no caso de animais potencialmente perigosos, que deverão estar convenientemente açaimados ou protegidos do contacto com o público quando fora do evento;
+d) Disponibilizar os meios que os médicos veterinários considerem necessários ao bom desempenho das suas funções;
+e) Assegurar que a exposição, incluindo os expositores, possui todas as licenças e autorizações necessárias à sua realização.
+Compete aos médicos veterinários responsáveis:
+a) Verificar o cumprimento do registo obrigatório no SIAC;
+b) Proceder ao exame clínico dos animais que se apresentam para participar no evento;
+c) Examinar a documentação sanitária dos animais;
+d) Prestar a assistência médico-veterinária que se revelar necessária à salvaguarda do bem-estar animal durante o evento;
+e) Proceder às observações que entenderem necessárias para a defesa sanitária do evento.
+A DGAV pode, sempre que entender necessário, determinar a realização de quaisquer exames médico-veterinários, laboratoriais ou outros, para verificar se foi administrada a um animal de companhia qualquer substância, tratamento ou procedimento com vista a aumentar ou diminuir o nível natural das capacidades fisiológicas e etológicas desse animal.
+Os eventos sem fins lucrativos que visem a adoção de animais de companhia, os passeios de animais organizados por centros de bem-estar animal ou associações zoófilas, ou outros eventos de socialização, são objeto de comunicação prévia à câmara municipal e à DGAV.
+A comunicação prévia a que se refere o número anterior é isenta de taxas.
+É proibida a participação de animais de companhia em eventos onde seja utilizada pirotecnia.</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -2227,50 +2566,90 @@
       <c r="H16" s="6" t="inlineStr">
         <is>
           <t>Artigo 79.º - Concursos e exposições
-1 - A realização de concursos e exposições com animais de companhia carece de autorização prévia da câmara municipal, ficando esta dependente do parecer vinculativo do MVM.
-3 - Só são admitidos a concurso os cães e gatos que: a) Estejam identificados eletronicamente; b) Sejam portadores de boletim sanitário e prova de vacinação antirrábica; c) Possuam vacinações contra principais doenças infecto-contagiosas.</t>
+- A realização de concursos e exposições com animais de companhia carece de autorização prévia da câmara municipal, ficando esta dependente do parecer vinculativo do MVM. 
+- A autorização prévia a que se refere o número anterior deve ser solicitada, pela organização da exposição, com a antecedência mínima de 15 dias, à câmara municipal da área da realização da exposição, mediante requerimento acompanhado dos seguintes documentos: 
+Descrição das condições de alojamento e manutenção dos animais; 
+A identificação do(s) médico(s) veterinário(s) responsável(eis) pela exposição ou concurso; 
+Regulamento sanitário do concurso ou exposição, onde deve estar especificado o modo como se prevê dar cumprimento ao disposto nos números seguintes. 
+- Só são admitidos a concurso os cães e gatos que: 
+Estejam identificados eletronicamente nos termos do disposto no presente diploma, no caso dos concorrentes nacionais ou, no caso de animais provenientes de outros países, de acordo com as disposições da legislação específica sobre a matéria; 
+Sejam portadores de boletim sanitário de cães e gatos ou passaporte de animal de companhia e possuam prova de vacinação antirrábica dentro do prazo de validade, no caso dos animais com idade superior a três meses; 
+Possuam dentro dos prazos de validade e efetuadas há mais de oito dias as vacinações contra as principais doenças infecto-contagiosas da espécie, comprovadas pelas vinhetas de vacinação respetiva, apostas no boletim sanitário de cães e gatos, devidamente autenticadas por um médico veterinário. 
+4 - Compete à organização da exposição: 
+Assegurar a presença do número de médicos veterinários necessário ao cumprimento do disposto no presente diploma; 
+Assegurar que o local onde a exposição decorre reúne as condições que permitam salvaguardar o disposto nas normas do presente diploma, em especial no que se refere à saúde e ao bem-estar dos animais exibidos; 
+Salvaguardar os aspetos de segurança, em particular no caso de animais potencialmente perigosos, que deverão estar convenientemente açaimados ou protegidos do contacto com o público, quando fora do concurso ou quando não estejam a competir; 
+Disponibilizar os meios que os médicos veterinários considerem necessários ao bom desempenho das suas funções, designadamente as seguintes: 
+Verificar a identificação electrónica dos animais sempre que obrigatória e a sua correspondência com o constante do boletim sanitário de cães e gatos; 
+Proceder ao exame clínico dos animais que se apresentam para participar na exposição ou concurso e impedir a participação de animais doentes ou feridos;
+Examinar a documentação sanitária dos animais; 
+Prestar a assistência médico-veterinária que se revelar necessária durante o evento; 
+Proceder às observações que entenderem necessárias para a defesa sanitária da exposição ou concurso. 
+5 - A exposição de animais para adoção, promovida por associações de proteção animal ou por particulares, que não nos alojamentos para hospedagem registados no âmbito do presente diploma, depende de autorização prévia do município, sob parecer vinculativo do MVM.</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>Lei n.º 27/2016 e DL n.º 82/2019 (Normas de eventos)</t>
+          <t>DL 314/2003 de 17 dezembro</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>A legislação portuguesa estabelece que a participação de animais em espetáculos e competições requer: - Autorização prévia de autoridades competentes; - Identificação e registo no SIAC; - Vacinações obrigatórias; - Supervisão veterinária durante o evento; - Condições de bem-estar animal garantidas.</t>
+          <t>Artigo 4.º - Exposições
+A participação de cães e gatos em concursos e exposições está sujeita às normas sanitárias emitidas pela DGV.
+A realização de concursos e exposições carece de autorização da DRA da área da realização da mesma, após parecer da respectiva câmara municipal.
+A autorização prévia a que se refere o número anterior deve ser solicitada pela organização da exposição com a antecedência mínima de 15 dias na câmara municipal da área da realização da exposição, mediante requerimento dirigido ao director regional de agricultura respectivo para efeitos do disposto no número anterior, acompanhado dos seguintes documentos:
+a) Planta do local de realização do concurso ou exposição;
+b) A identificação do(s) médico(s) veterinário(s) responsável(eis) pela exposição ou concurso;
+c) Regulamento sanitário do concurso ou exposição, onde deve estar especificado o modo como se prevê dar cumprimento ao disposto nos números seguintes.
+4 - Só serão admitidos a concurso os animais que:
+a) Estejam identificados electronicamente nos termos do Sistema de Identificação de Caninos e Felinos (SICAFE), no caso dos concorrentes nacionais ou, no caso de animais provenientes de outros países, de sistema de identificação em vigor no país de origem e que permita uma identificação rigorosa e eficaz do animal;
+b) Sejam portadores de boletim sanitário de cães e gatos e possuam prova de vacinação anti-rábica dentro do prazo de validade conforme determinado anualmente por despacho do director-geral de Veterinária, nos termos do n.º 2 do artigo 1.º da Portaria n.º 81/2002, de 24 de Janeiro, no caso dos animais com idade superior a 3 meses;
+c) Possuam dentro dos prazos de validade e efectuadas há mais de oito dias as vacinações contra as principais doenças infecto-contagiosas da espécie, comprovadas pelas vinhetas de vacinação respectivas apostas no boletim sanitário de cães e gatos, devidamente autenticadas por um médico veterinário.
+5 - Compete à organização da exposição:
+a) Assegurar a presença do número de médicos veterinários necessários ao cumprimento do disposto neste diploma;
+b) Assegurar que o local onde a exposição decorre reúne as condições que permitam salvaguardar o disposto no capítulo VII do Decreto-Lei n.º 276/2001, de 17 de Outubro;
+c) Salvaguardar os aspectos de segurança, no caso de animais potencialmente perigosos, que deverão estar convenientemente açaimados ou protegidos do contacto com o público, quando fora do concurso;
+d) Disponibilizar os meios que os médicos veterinários considerem necessários ao bom desempenho das suas funções.
+6 - Compete aos médicos veterinários responsáveis pela exposição ou concurso:
+a) Verificar a identificação electrónica dos animais e a sua correspondência com o constante do boletim;
+b) Proceder ao exame clínico dos animais que se apresentam para participar na exposição ou concurso;
+c) Examinar a documentação sanitária dos animais;
+d) Prestar a assistência médico-veterinária que se revelar necessária durante o evento;
+e) Proceder às observações que entenderem necessárias para a defesa sanitária da exposição ou concurso.</t>
         </is>
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>SIM - Cobertura COMPLETA (autorização, identificação, vacinação, supervisão veterinária)</t>
+          <t>Cães/gatos em concursos/exposições</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>SIM - Cobertura COMPLETA (concursos e exposições com requisitos específicos)</t>
+          <t>Cães/gatos em concursos/exposições e acrescenta adoções
+Parecer MVM vinculativo</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
-          <t>SIM - Cobertura COMPLETA (participação em eventos com normas de bem-estar)</t>
+          <t>Todos animais de companhia em múltiplos eventos (concursos, campanhas, cinema, etc.)
+Câmara Municipal (consultivo)
+Comunicação prévia isenta de taxa para sem fins lucrativos
+Possibilidade de exames de dopagem
+Proibida pirotecnia</t>
         </is>
       </c>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>A legislação portuguesa cobre completamente os requisitos do Artigo 15a. Implementa autorizações prévias, exigências de identificação, vacinação obrigatória e supervisão veterinária. O RGBEAC (Art. 39.º) e Código do Animal (Art. 79.º) estabelecem normas detalhadas sobre espetáculos, exposições e competições estéticas.</t>
+          <t>Prever a exclusão de animais com características conformacionais excessivas</t>
         </is>
       </c>
       <c r="O16" s="11" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="P16" s="11" t="inlineStr">
-        <is>
-          <t>Correspondências completas encontradas - Cobertura legislativa adequada</t>
-        </is>
-      </c>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P16" s="11" t="inlineStr"/>
     </row>
     <row r="17" ht="120" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -2280,23 +2659,24 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Art.º 20.º do Regulamento 2023/0447</t>
+          <t>Art.º 20.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>1.	All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip that complies with the requirements set out in Annex II.
-2.	Operators shall ensure that dogs and cats born in their establishments are individually identified within three months after their birth, and in any event before the date that they are placed on the market.
+          <t>All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip that complies with the requirements set out in Annex II.
+Operators shall ensure that dogs and cats born in their establishments are individually identified within three months after their birth, and in any event before the date that they are placed on the market.
 Operators of selling establishments and shelters, and operators who place and are responsible for dogs and cats in foster homes shall ensure that dogs and cats that enter their establishments or come under their responsibility are individually identified within 30 days of arrival and in any event before the date of their placing on the market.
 Pet owners and any other natural or legal persons other than operators who own dogs or cats, shall ensure that every dog or cat is individually identified at the latest when it reaches the age of three months or, if the dog or cat is placed on the market, before the date of that placing on the market.
 The implantation of the transponder shall be performed by a veterinarian. Member States may allow the implantation of transponders by persons other than veterinarians provided that they adopt national rules laying down  the minimum qualifications that such persons are required to have.
 Where dogs and cats have been individually identified by means of an injectable transponder containing a microchip in accordance with Union or national law before … [date two years after the date of entry into force of this Regulation] they shall be considered to be compliant with the requirements in paragraph 1 and the first, second, third and fourth subparagraphs of this paragraph, provided that the microchip is still readable.
-3.	Within two working days after their identification, the dogs and cats  shall be registered by a veterinarian  in a national database referred to in Article 23. Member States may allow registration by persons other than veterinarians, provided that the Member States have measures in place to ensure the accuracy of information that those persons enter in the database. For dogs and cats kept in  establishments, the registration shall be made in the name of the operator of the  establishment responsible for the dog or the cat. For dogs and cats owned by any other natural and legal persons  , the registration shall be made in the name of those persons.
+Within two working days after their identification, the dogs and cats shall be registered by a veterinarian in a national database referred to in Article 23. 
+Member States may allow registration by persons other than veterinarians, provided that the Member States have measures in place to ensure the accuracy of information that those persons enter in the database. For dogs and cats kept in establishments, the registration shall be made in the name of the operator of the establishment responsible for the dog or the cat. For dogs and cats owned by any other natural and legal persons, the registration shall be made in the name of those persons.
 Member States may grant exemptions from the first subparagraph of this paragraph in respect of military, police and customs dogs.
-4.	Where dogs or cats are placed on the market or are donated in an occasional manner by natural persons without using online advertising, the natural or legal person transferring the ownership of, or responsibility for, the dog or cat shall ensure that the change of ownership of, or responsibility for, the dog or cat is recorded in the database referred to in Article 23, within two weeks from the date of that transfer, in accordance with the conditions laid down by the Member State responsible for that database.
-5.	In the case of the death of a dog or a cat, the operator, pet owner or natural or legal person owning the dog or cat shall ensure that the death is recorded in the database referred to in Article 23, in accordance with the conditions laid down by the Member State responsible for that database.
-6.	Where a transponder is or becomes unreadable, the operator or the natural or legal person responsible for the dog or cat shall ensure that a new transponder is injected and that the registration in the database is updated with the identification number of that new transponder.
-7.	The identification and registration requirements of this Article shall apply as follows:
+Where dogs or cats are placed on the market or are donated in an occasional manner by natural persons without using online advertising, the natural or legal person transferring the ownership of, or responsibility for, the dog or cat shall ensure that the change of ownership of, or responsibility for, the dog or cat is recorded in the database referred to in Article 23, within two weeks from the date of that transfer, in accordance with the conditions laid down by the Member State responsible for that database.
+In the case of the death of a dog or a cat, the operator, pet owner or natural or legal person owning the dog or cat shall ensure that the death is recorded in the database referred to in Article 23, in accordance with the conditions laid down by the Member State responsible for that database.
+Where a transponder is or becomes unreadable, the operator or the natural or legal person responsible for the dog or cat shall ensure that a new transponder is injected and that the registration in the database is updated with the identification number of that new transponder.
+The identification and registration requirements of this Article shall apply as follows:
 (a) 	for operators and natural or legal persons placing dogs and cats on the market from ... [4 years from the entry into force of this Regulation];
 (b)	for pet owners and other natural or legal persons other than operators, who do not place dogs on the market: from … [10 years from entry into force of this Regulation];
 (c)	 for pet owners and other natural or legal persons other than operators, who do not place cats on the market: from … [15 years from entry into force of this Regulation.</t>
@@ -2331,7 +2711,8 @@
           <t>1 — A identificação dos animais de companhia, pela sua marcação, quando aplicável, e registo no SIAC, deve ser realizada:
 a) Relativamente aos cães, gatos e furões nascidos em alojamentos, até aos três meses de idade ou, em qualquer caso, antes da sua colocação no mercado;
 b) Relativamente aos cães, gatos e furões que entrem em alojamentos, nos termos dos artigos 12.º a 15.º, até trinta dias após a sua chegada ao alojamento ou, em qualquer caso, antes da data de colocação no mercado;
-c) Relativamente aos cães, gatos e furões detidos por pessoas singulares, exceto nos casos previstos nas alíneas anteriores, até aos três meses de idade ou, no caso de colocação no mercado, antes da data de colocação no mercado.</t>
+c) Relativamente aos cães, gatos e furões detidos por pessoas singulares, exceto nos casos previstos nas alíneas anteriores, até aos três meses de idade ou, no caso de colocação no mercado, antes da data de colocação no mercado.
+(…)</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -2344,19 +2725,21 @@
           <t>1 — Todos os cães devem ser identificados e registados, entre os três e os seis meses de idade.
 2 — Os gatos em exposição, para fins comerciais ou lucrativos, em estabelecimentos de venda, locais de criação, feiras ou concursos, provas funcionais, publicidade ou fins similares, devem ser identificados e registados entre os três e os seis meses de idade.
 4 — Os cães e gatos são identificados através de método electrónico e registados na base de dados nacional.
-5 — A identificação electrónica é efetuada através da aplicação subcutânea de um microchip no centro da face lateral esquerda do pescoço.</t>
+— A identificação electrónica é efetuada através da aplicação subcutânea de um microchip no centro da face lateral esquerda do pescoço.
+(…)</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>n.ºs 1, 2 e 3 do art.º 5.º do DL n.º 82/2019, de 27 de junho</t>
+          <t>DL n.º 82/2019, de 27 de junho</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
           <t>1 — A identificação dos animais de companhia, pela sua marcação e registo no SIAC, deve ser realizada até 120 dias após o seu nascimento.
 2 — Na impossibilidade de determinar a data de nascimento exata, para efeitos de contagem do prazo referido no número anterior, a identificação deve ser efetuada até à perda dos dentes incisivos de leite.
-3 — Sem prejuízo dos números anteriores, e relativamente aos cães, gatos e furões que sejam cedidos e ou comercializados a partir de um criador ou de um estabelecimento autorizado para a detenção de animais de companhia, nomeadamente os centros de hospedagem com ou sem fins lucrativos e os centros de recolha oficiais, deve ser assegurada a sua marcação e registo no SIAC antes de abandonarem a instalação de nascimento ou de alojamento, independentemente da sua idade.</t>
+— Sem prejuízo dos números anteriores, e relativamente aos cães, gatos e furões que sejam cedidos e ou comercializados a partir de um criador ou de um estabelecimento autorizado para a detenção de animais de companhia, nomeadamente os centros de hospedagem com ou sem fins lucrativos e os centros de recolha oficiais, deve ser assegurada a sua marcação e registo no SIAC antes de abandonarem a instalação de nascimento ou de alojamento, independentemente da sua idade.
+(…)</t>
         </is>
       </c>
       <c r="K17" s="8" t="inlineStr">
@@ -2366,17 +2749,18 @@
       </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
-          <t>O @codigo fixa prazo de identificação entre 3 e 6 meses, igualmente sem distinção entre nascimentos e entrada em estabelecimentos, ficando aquém da precisão exigida pelo @regulamento.</t>
+          <t>O @codigo fixa prazo de identificação entre 3 e 6 meses, sem distinção entre nascimentos e entrada em estabelecimentos, como previsto pelo @regulamento</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac aproxima-se dos prazos do @regulamento mas aplica-se apenas a cães, gatos e furões. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
+          <t>O @rgbeac aproxima-se dos prazos do @regulamento: identificação até aos três meses e prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>Necessidade de alteração: (1) reduzir prazo máximo de identificação de nascimentos para 3 meses; (2) criar prazo diferenciado de 30 dias para animais admitidos em estabelecimentos; (3) harmonizar prazos entre todos os diplomas nacionais.</t>
+          <t>Necessidade de alteração: (1) reduzir prazo máximo de identificação de nascimentos para 3 meses; (2) criar prazo diferenciado de 30 dias para animais admitidos em estabelecimentos; (3) harmonizar prazos entre todos os diplomas nacionais.
+Necessário análise mais aprofundada</t>
         </is>
       </c>
       <c r="O17" s="11" t="inlineStr">
@@ -2384,11 +2768,7 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="P17" s="11" t="inlineStr">
-        <is>
-          <t>(espaço para anotações da reunião)</t>
-        </is>
-      </c>
+      <c r="P17" s="11" t="inlineStr"/>
     </row>
     <row r="18" ht="120" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -2398,7 +2778,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Art.º 21.º do Regulamento 2023/0447</t>
+          <t>Art.º 21.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -2434,7 +2814,7 @@
       <c r="D18" s="4" t="inlineStr">
         <is>
           <t>1.	Quando operadores anunciem online um cão ou gato com vista ao seu colocamento no mercado da União, devem assegurar a apresentação do seguinte aviso no anúncio em caracteres claramente visíveis e em negrito:
-	"Um animal não é um brinquedo. Ter um é uma decisão que muda a vida. É seu dever assegurar a sua saúde e bem-estar e não o abandonar."
+"Um animal não é um brinquedo. Ter um é uma decisão que muda a vida. É seu dever assegurar a sua saúde e bem-estar e não o abandonar."
 2.	Quando pessoas singulares ou coletivas que não sejam operadores anunciem online um cão ou gato com vista ao seu colocamento no mercado da União, devem assegurar a apresentação de um aviso sobre detenção responsável utilizando a redação referida no n.º 1 ou uma redação diferente com significado equivalente.
 3.	Ao colocar um cão ou gato no mercado na União, a pessoa singular ou coletiva que coloca o cão ou gato no mercado deve fornecer ao adquirente:
 (a)	prova da identificação e do registo do cão ou gato em conformidade com o artigo 20.º;
@@ -2443,10 +2823,10 @@
 (ii)	o seu sexo;
 (iii)	a sua data e país de nascimento; e
 (iv)	quando relevante, a sua raça.
-	Caso uma pessoa singular ou coletiva anuncie um cão ou gato online com vista ao seu colocamento no mercado da União, essa pessoa deve utilizar o sistema referido no n.º 5 para gerar um token único de verificação e incluir esse token no anúncio, juntamente com uma ligação web para o sistema referido no n.º 5.
-	O sistema referido no n.º 5 deve permitir aos adquirentes verificar a autenticidade da identificação, do registo e da propriedade de cães ou gatos anunciados online.
+Caso uma pessoa singular ou coletiva anuncie um cão ou gato online com vista ao seu colocamento no mercado da União, essa pessoa deve utilizar o sistema referido no n.º 5 para gerar um token único de verificação e incluir esse token no anúncio, juntamente com uma ligação web para o sistema referido no n.º 5.
+O sistema referido no n.º 5 deve permitir aos adquirentes verificar a autenticidade da identificação, do registo e da propriedade de cães ou gatos anunciados online.
 4.	Os fornecedores de plataformas online devem assegurar que a sua interface online é concebida e organizada de forma a facilitar aos operadores ou outras pessoas singulares ou coletivas que colocam cães ou gatos no mercado o cumprimento das suas obrigações nos termos dos n.ºs 1 a 3 do presente artigo, e em conformidade com o artigo 31.º do Regulamento (UE) 2022/2065, e devem informar os adquirentes, de forma visível, da possibilidade de verificar a autenticidade da identificação, do registo e da propriedade do cão ou gato no sistema de verificação online referido no n.º 5, acessível através de uma ligação web.
-	Apenas a pessoa singular ou coletiva que coloca cães ou gatos no mercado é responsável pela exatidão das informações fornecidas através da interface da plataforma online. Nenhuma disposição do presente número pode ser interpretada como impondo uma obrigação geral de monitorização ao fornecedor da plataforma online, na aceção do artigo 8.º do Regulamento (UE) 2022/2065.
+Apenas a pessoa singular ou coletiva que coloca cães ou gatos no mercado é responsável pela exatidão das informações fornecidas através da interface da plataforma online. Nenhuma disposição do presente número pode ser interpretada como impondo uma obrigação geral de monitorização ao fornecedor da plataforma online, na aceção do artigo 8.º do Regulamento (UE) 2022/2065.
 5.	A Comissão garante que um sistema de verificação destinado a realizar controlos automatizados da autenticidade da identificação, do registo e da propriedade de cães ou gatos anunciados online, utilizando a base de dados referida no artigo 23.º, está publicamente disponível online, a título gratuito, e gera o token único de verificação referido no segundo parágrafo do n.º 3 do presente artigo. A Comissão pode confiar o desenvolvimento, a manutenção e o funcionamento deste sistema a uma entidade independente, escolhida para essa missão na sequência de um processo de seleção pública. O sistema deve assegurar:
 (a)	a verificação fiável da autenticidade da identificação, do registo e da propriedade do cão ou gato, utilizando as bases de dados nacionais referidas no artigo 23.º;
 (b)	a conformidade com a proteção de dados, em conformidade com o Regulamento (UE) 2018/1725 e o Regulamento (UE) 2016/679.
@@ -2457,21 +2837,57 @@
 -	as funções essenciais do sistema;
 -	os requisitos técnicos, eletrónicos e criptográficos do sistema;
 -	os passos procedimentais a seguir, e as informações a fornecer, pela pessoa singular ou coletiva que coloca o cão ou gato no mercado, bem como os passos e informações exigidos ao adquirente, para que o sistema de verificação online funcione.
-	Os atos de execução referidos na alínea a) devem ser adotados até … [dois anos após a data de entrada em vigor do presente Regulamento] e os atos de execução referidos nas alíneas b) e c) devem ser adotados até … [três anos a contar da data de entrada em vigor do presente Regulamento].
-	Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
+Os atos de execução referidos na alínea a) devem ser adotados até … [dois anos após a data de entrada em vigor do presente Regulamento] e os atos de execução referidos nas alíneas b) e c) devem ser adotados até … [três anos a contar da data de entrada em vigor do presente Regulamento].
+Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Art.º 95.º + Art.º 115.º n.º 3 do RGBEAC (proposta, jun. 2025)</t>
+          <t>Art.º 91 a 95.º + Art.º 115.º n.º 3 do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Artigo 95.º - Local de venda dos animais
+          <t>Artigo 91.º- Procedimento de venda
+1 – A venda de animais só pode ser exercida nos alojamentos referidos no artigo 68.º e a pessoas maiores de idade e plenamente capazes do exercício de direitos, mediante contrato de compra e venda reduzido a escrito.
+2 – O  vendedor deve procurar aferir se o animal em questão se adequa ao estilo de vida, condições de alojamento e preferências do comprador e que o mesmo está consciente do dever de cuidar e assegurar o bem-estar do animal até ao fim da sua vida.
+3 – O contrato de compra e venda deve integrar informação relativamente às obrigações legais do detentor, às necessidades de bem-estar específicas da espécie e do animal em concreto, bem como a todo o historial clínico do animal, incluindo rastreios genéticos e despistes de doenças realizados, bem como doenças congénitas comuns da raça ou hereditárias a considerar pelo comprador.
+5 – O dever de informação referido no número anterior inclui, também, o regime alimentar do animal, aconselhamento sobre a adaptação ao novo lar, controlo reprodutivo, socialização e métodos de educação e treino baseados no reforço positivo, bem como os dados de contacto do vendedor.
+6 - No caso dos cães e gatos, o contrato de compra e venda deve prever também a indemnização do comprador no caso de doença congénita ou viral imputada à criação, autorização de reprodução no caso de criadores com alojamento devidamente licenciado para o efeito, ou compromisso de não reprodução com obrigatoriedade de esterilização até aos seis meses de idade.
+7 - O contrato de compra e venda de animais de companhia identifica os meios de contacto entre o comprador e o vendedor, ficando este obrigado a prestar apoio na eventualidade de falta de adaptação e integração do animal, incluindo o auxílio na busca de um novo detentor para o mesmo. 
+Artigo 92.º - Requisitos de validade do anúncio de transmissão de animal de companhia
+1 - Qualquer anúncio de transmissão, gratuita ou onerosa, de animais de companhia deve conter as seguintes informações:
+a) A data de nascimento do animal, ou data de nascimento aproximada, no caso de anúncios de cedência gratuita em que não seja conhecida a data exata do nascimento;
+b) O país de origem do animal;
+c) Fotografia atual do animal;
+d) Número de identificação eletrónica;
+e) Tratando-se de cão ou gato, a indicação se é animal de raça pura ou indeterminada, sendo que, tratando-se de animal de raça pura, deve obrigatoriamente ser referido o número de registo no livro de origens português;
+f) Prova da legalidade dos animais de companhia.
+2 - Sem prejuízo do disposto no número anterior, qualquer anúncio de transmissão de animal, a título oneroso, deve conter também as seguintes informações:
+a) O respetivo preço;
+b) Número de identificação eletrónica da cria e da fêmea reprodutora;
+c) Número de registo de alojamento nos termos do disposto no artigo 60.º;
+d) Número de animais da ninhada.
+3 - Qualquer publicação de uma oferta de transmissão de animal a título gratuito deve mencionar de forma explícita e inequívoca a sua gratuitidade.
+4 - Os cães e gatos só podem ser considerados de raça pura se estiverem inscritos no livro de origens português, caso contrário são identificados como cão ou gato de raça indeterminada.
+5 - No caso de anúncios de animais de raça indeterminada é proibida qualquer referência a raças no texto do anúncio.
+Artigo 93.º - Plataformas de Internet para anunciar a transmissão de animais
+- As plataformas de Internet disponíveis para anunciar a transmissão, gratuita ou onerosa, de animais de companhia, apenas podem publicitar os anúncios que cumpram os requisitos dispostos no artigo anterior.
+- As plataformas de Internet têm o dever de implementar e manter um sistema de controlo e de validação destinado à verificação da veracidade dos dados introduzidos pelo anunciante.
+Artigo 94.º - Requisitos de validade da transmissão de propriedade de animal de companhia
+1 - Qualquer transmissão de propriedade, gratuita ou onerosa, de animal de companhia deve ser acompanhada, no momento da transmissão, dos seguintes documentos entregues ao adquirente: 
+a) Contrato de adoção ou de compra e venda do animal e respetiva fatura, nos termos do disposto no artigo 42.º, referente ao procedimento de adoção, e no artigo 91.º, referente ao procedimento de venda.
+ b) Documento de identificação do animal, nos termos do disposto no n.º 6 do artigo 26.º.
+c) Declaração médico-veterinária, com prazo de pelo menos 15 dias, que ateste que o animal se encontra de boa saúde; 
+d) Informação completa sobre o historial clínico do animal, sem prejuízo das informações que deverão constar no DIAC.
+e) Apresentação da licença de detenção prevista no artigo 102.º, no caso de animais potencialmente perigosos;
+f) Prova da legalidade dos animais de companhia.
+2 – Previamente à transmissão da propriedade do animal, é obrigatória a consulta ao registo de infratores, nos termos do disposto no artigo 144.º, com vista a determinar a vigência de sanções que obstem à venda ou à adoção naquela data.
+Artigo 95.º - Local de venda dos animais
 1 - Os animais de companhia não podem ser vendidos por entidade transportadora ou através da Internet, designadamente através de quaisquer portais ou plataformas.
 2 - Os animais de companhia não podem ser publicitados na Internet, mas a compra e venda dos mesmos apenas é admitida no local de criação ou em estabelecimentos devidamente licenciados.
-Artigo 115.º n.º 3 - É proibida a publicidade e comercialização de animais perigosos ou que demonstrem comportamento agressivo.</t>
+Artigo 115.º 
+n.º 3 - É proibida a publicidade e comercialização de animais perigosos ou que demonstrem comportamento agressivo.</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
@@ -2481,7 +2897,23 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>A legislação proíbe a venda de animais de companhia sem documentação adequada e restringe a comercialização de animais com comportamentos perigosos. As disposições cobrem identificação obrigatória e informações sobre o animal antes da venda.</t>
+          <t>Artigo 80.º - Comércio de animais de companhia
+1 - O comércio de animais de companhia, em particular de cães e de gatos, apenas é permitido quando os mesmos sejam provenientes de alojamentos para hospedagem devidamente autorizados.
+2 - É proibida a venda ou cedência de:
+a) Animais de companhia fora dos locais de criação ou de quaisquer outros locais autorizados pela autoridade competente, para o efeito, designadamente na via pública;
+b) Animais que apresentem sintomas evidentes de doença, de animais cuja detenção ou introdução no território nacional é proibida, de animais errantes, perdidos ou abandonados, ou de animais que tenham sofrido mutilações não autorizadas.
+3 - A proibição referida no n.º 2 não inclui a transferência de propriedade de animais entre particulares, sem fins lucrativos, ou a cedência a novos detentores, por centros de recolha e centros de hospedagem pertença de associações de proteção animal.
+4 - É interdita a venda de animais a menores de 16 anos, sem autorização expressa dos seus pais ou tutores.
+5 - Os cães e os gatos que se encontrem em estabelecimentos destinados exclusivamente ao seu comércio devem estar acompanhados dos seguintes documentos:
+a) Boletim sanitário de cães e gatos ou passaporte, onde deve estar aposta a etiqueta autocolante comprovativa da identificação eletrónica, bem como o comprovativo da realização das ações de profilaxia médica e sanitária obrigatórias, ou consideradas adequadas à saúde e idade dos animais pelo médico veterinário;
+b) Documento de Registo ou Ficha de Registo, em nome do criador, servindo o documento comprovativo da venda, onde está especificado o número de microchip, como documento de transferência de propriedade.
+6 - Após a realização da venda de animais, os documentos referidos nas alíneas anteriores são entregues ao comprador.
+7 - Os cães e gatos com idade superior a três meses de idade devem possuir comprovativo das ações de profilaxia consideradas obrigatórias para a espécie.
+8 - Os animais de companhia de espécie diferente de cão ou gato devem ser acompanhados de documento que ateste a origem, emitido pelo criador, e dos certificados das ações profiláticas que possam ser exigidos para a espécie.
+9 - Os responsáveis pela venda de animais de companhia devem disponibilizar informação escrita, relativa à espécie animal a comercializar, que inclua cuidados gerais, alojamento, maneio, dieta adequada, bem como indicações relativas a obrigações legais do detentor, nomeadamente as que se referem à vacinação, esterilização, registo, licença ou treino, quando aplicável.
+10 - A venda de animais da espécie felina ou canina deve ser acompanhada de uma garantia de reembolso ou de substituição do animal doente ou falecido, em caso de aparecimento de doenças infeto-contagiosas próprias da espécie, nos oito dias subsequentes à venda, bem como de doenças congénitas próprias da espécie e raça, até um ano após a venda, desde que confirmadas por escrito por um médico veterinário.
+11 - A pessoa responsável pela comercialização dos animais não pode fornecer falsas informações, designadamente no que respeita à raça, idade, origem ou espécie de um determinado animal, com vista a promover a sua venda.
+12 - É proibida a colocação para venda e a publicidade dos animais cuja detenção é proibida por legislação específica</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -2491,17 +2923,22 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>A legislação portuguesa estabelece controlos sobre a comercialização de cães e gatos, com requisitos de identificação e documentação sanitária. DL 82/2019 reforça as normas de rastreabilidade através do SIAC.</t>
-        </is>
-      </c>
-      <c r="K18" s="8" t="inlineStr">
-        <is>
-          <t>PARCIAL - Proíbe venda online mas sem sistema de verificação online específico</t>
-        </is>
-      </c>
+          <t>Artigo 53.º - Requisitos de validade do anúncio de venda de animal de companhia
+1 - Qualquer anúncio de transmissão, a título oneroso, de animais de companhia deve conter as seguintes informações:
+a) A idade dos animais;
+b) Tratando-se de cão ou gato, a indicação se é animal de raça pura ou indeterminada, sendo que, tratando-se de animal de raça pura, deve obrigatoriamente ser referido o número de registo no livro de origens português;
+c) Número de identificação eletrónica da cria e da fêmea reprodutora;
+d) Número de inscrição de criador nos termos do artigo 3.º do presente diploma;
+e) Número de animais da ninhada.
+2 - Qualquer publicação de uma oferta de transmissão de animal a título gratuito deve mencionar explicitamente a sua gratuitidade.
+3 - Os cães e gatos só podem ser considerados de raça pura se estiverem inscritos no livro de origens português, caso contrário são identificados como cão ou gato de raça indeterminada.
+4 - No caso de anúncios de animais de raça indeterminada é proibida qualquer referência a raças no texto do anúncio.</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr"/>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>PARCIAL - Cobre restrições comerciais mas não implementa sistema de token de verificação</t>
+          <t>Apenas proíbe a venda de animais de companhia sem documentação adequada e restringe a comercialização de animais com comportamentos perigosos. As disposições cobrem identificação obrigatória e informações sobre o animal antes da venda.</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr">
@@ -2511,19 +2948,15 @@
       </c>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>A legislação portuguesa PROÍBE a publicidade e venda de animais de companhia na Internet (Art. 95.º RGBEAC). Falta apenas a implementação do sistema de verificação online com token único conforme Art. 17a.6 do Regulamento. A proibição é mais restritiva que o Regulamento que permite venda online com verificação.</t>
+          <t>@rgbeac tem concordâncias extensas mas falta a implementação do sistema de verificação online com token único conforme Art. 17a.6 do Regulamento. A proibição é mais restritiva que o Regulamento que permite venda online com verificação.</t>
         </is>
       </c>
       <c r="O18" s="11" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P18" s="11" t="inlineStr">
-        <is>
-          <t>Legislação portuguesa mais restritiva - proíbe venda online; Reg. EU permite com verificação</t>
-        </is>
-      </c>
+          <t>Sim - Sistema de verificação online com token único</t>
+        </is>
+      </c>
+      <c r="P18" s="11" t="inlineStr"/>
     </row>
     <row r="19" ht="120" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -2533,17 +2966,17 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Art.º 22.º do Regulamento 2023/0447</t>
+          <t>Art.º 22.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>1.	For the purposes of Article 12, the competent authorities shall be responsible for:
+          <t>1. For the purposes of Article 12, the competent authorities shall be responsible for:
 (a)	ensuring that training courses are available for animal carers;
 (b)	approving the content of the training courses referred to in point (a), in accordance with the minimum requirements laid down by the implementing acts referred to in Article 12(4);
 (c)	certifying animal carers who have successfully completed the training courses referred to in point (a).
 The competent authorities may delegate the task referred to in point (c) to providers of training courses.
-2.	A European Union Reference Centre for Animal Welfare designated in accordance with Article 95 of Regulation (EU) 2017/625 may develop models of training materials and recommendations for the competent authorities or other providers of training courses.</t>
+2. A European Union Reference Centre for Animal Welfare designated in accordance with Article 95 of Regulation (EU) 2017/625 may develop models of training materials and recommendations for the competent authorities or other providers of training courses.</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -2551,69 +2984,99 @@
           <t>1. Para efeitos do artigo 12.º, as autoridades competentes são responsáveis por:
 a) Assegurar que existem cursos de formação disponíveis para cuidadores de animais;
 b) Aprovar o conteúdo dos cursos de formação referidos na alínea a), tendo em conta os requisitos mínimos estabelecidos pelos atos de execução referidos no artigo 12.º, parágrafo 3;
-ba) Certificar os cuidadores de animais que completaram com sucesso os cursos de formação referidos na alínea a).
-2. As autoridades competentes podem delegar a tarefa referida na alínea ba).
+c) Certificar os cuidadores de animais que completaram com sucesso os cursos de formação referidos na alínea a).
+2. As autoridades competentes podem delegar a tarefa referida na alínea (c) 
 3. O Centro de Referência da União Europeia para o Bem-Estar Animal designado em conformidade com o artigo 95.º do Regulamento (UE) 2017/625 pode desenvolver modelos de materiais de formação e recomendações para os fornecedores dos cursos de formação referidos no parágrafo 1.</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Arts. 118.º, 119.º, 120.º do RGBEAC (proposta, jun. 2025)</t>
+          <t>Arts. 118.º, 119.º, 120.º, Secção I, do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Artigo 118.º - Reserva de atividade de treinadores de cães
-O treino de cães para qualquer fim só pode ser ministrado por treinador possuidor do respetivo título profissional.
-Artigo 119.º - Título profissional de treinador de cães
-1 - O acesso e exercício da atividade de treinador de cães depende da obtenção do respetivo título profissional, emitido pela DGAV.
-2 - O requerente deve: ter habilitação mínima 12.º ano; apresentar certificado criminal; ser detentor do certificado de qualificações.
+          <t>Artigo 118.º - Reserva de atividade de treinadores de cães 
+O treino de cães para qualquer fim, incluindo o treino básico de socialização e de obediência, de cães de assistência ou intervenções e terapias assistidas por animais, de cães para competição e para atividades desportivas, recreativas e para fins económicos, só pode ser ministrado por treinador possuidor do respetivo título profissional, emitido nos termos do artigo seguinte.
+Artigo 119.º - Título profissional de treinador de cães 
+ 1 - O acesso e exercício da atividade de treinador de cães depende da obtenção do respetivo título profissional, emitido pela DGAV 
+2 - Sem prejuízo do disposto nos n.ºs 5 e 6, o requerente de título profissional deve reunir, cumulativamente, os seguintes requisitos: 
+a) Ser maior de idade e não estar interdito ou inabilitado, por decisão judicial, para gerir a sua pessoa e os seus bens; 
+b) Ter como habilitação mínima o 12.º ano de escolaridade ou equivalente; 
+c) Apresentar certificado do registo criminal do qual resulte não ter sido o candidato à certificação de treinadores condenado, por sentença transitada em julgado, há menos de cinco anos, por qualquer dos crimes previstos no presente decreto-lei, por crime de homicídio por negligência, por crime doloso contra a vida, a integridade física, a liberdade pessoal, a liberdade e autodeterminação sexual, a saúde pública ou a paz pública, tráfico de estupefacientes e substâncias psicotrópicas, tráfico de pessoas, tráfico de armas, crimes contra animais de companhia, ou por outro crime doloso cometido com uso de violência; 
+d) Ser detentor do certificado de qualificações referido no artigo seguinte. 
+3 - Para efeito da obtenção do título profissional de treinador de cães, o requerente de título profissional deve apresentar ao ICNF, I.P., um documento de identificação civil e o certificado do registo criminal. 
+4 - O ICNF, I.P., dispõe do prazo de 20 dias para decidir o requerimento referido no número anterior, após o que, na ausência de decisão, não há lugar a deferimento tácito, podendo o interessado obter a tutela adequada junto dos tribunais administrativos. 
+5 - O treinador de cães nacional de Estado-membro da União Europeia ou do Espaço Económico Europeu cujas qualificações tenham sido obtidas fora de Portugal e pretenda estabelecer-se em território nacional requer a emissão do seu título profissional ao ICNF, I.P., nos termos do artigo 47.º da Lei n.º 9/2009, de 4 de março, alterada pela Lei n.º 31/2021, de 24 de maio, comprovando adicionalmente os requisitos referidos nas alíneas a) e c) do n.º 2. 
+6 - Os profissionais provenientes de outro Estado membro da União Europeia ou do Espaço Económico Europeu que pretendam exercer a atividade de treino de cães em território nacional em regime de livre prestação de serviços ficam sujeitos à verificação prévia de qualificações constante do artigo 6.º da Lei n.º 9/2009, de 4 de março, alterada pela Lei n.º 31/2021, de 24 de maio. 
 Artigo 120.º - Certificado de qualificações
-1 - Emitido por entidade certificadora após aprovação em provas teóricas e práticas, demonstrando habilitação técnica com base em métodos de reforço positivo.
-2 - Provas incidem sobre comportamento animal, metodologia de treino, aprendizagem e extinção de comportamentos.</t>
+ 1 - O certificado de qualificações de treinador de cães, referido na alínea d) do n.º 2 do artigo anterior, é emitido por entidade certificadora, após aprovação em provas teóricas e práticas através das quais o candidato demonstre a sua habilitação técnica para influenciar e adaptar o carácter do canídeo, com base em métodos de reforço positivo, de forma a garantir uma detenção responsável, bem como a vinculação e integração positiva com o detentor e o meio ambiente, promovendo o bem-estar animal e a segurança de pessoas, outros animais e bens, devendo ser dado conhecimento do certificado ao ICNF, I.P, no prazo máximo de 10 dias. 
+2 - As provas teóricas referidas no número anterior devem incidir sobre comportamento animal, metodologia de treino, aprendizagem e extinção de comportamentos, devendo a avaliação prática fazer-se com a presença de animal próprio ou de terceiros, sempre devidamente identificado, para que cada cão só possa realizar a prova com um candidato. 
+3 - A certificação das entidades certificadoras, o modelo de provas e a avaliação dos candidatos são definidos por portaria do membro do Governo responsável pela área da conservação da natureza.
+Artigo 121.º - Lista de treinadores de cães 
+ 1 - A emissão do título profissional, nos termos do disposto no artigo 119.º, determina a inscrição automática na lista de treinadores disponível no sítio na Internet do ICNF, I.P.. 
+2 – O ICNF, I.P., mantém atualizada a lista referida no número anterior, cuja base de dados deve respeitar o disposto no Regulamento Geral de Proteção de Dados.
+Artigo 122.º - Obrigações dos treinadores
+ 1 - Os treinadores de cães devem manter, pelo prazo mínimo de 10 anos, e disponibilizar às entidades fiscalizadoras, sempre que solicitado, um registo contendo: 
+a) A identificação dos animais submetidos a treino, com a indicação do motivo, das datas de início e conclusão do treino e respetivos resultados; 
+b) A identificação dos seus detentores, com indicação dos nomes e moradas; 
+c) A identificação dos animais submetidos a treinos de manutenção. 
+2 - A cada animal treinado é emitido um documento que ateste a realização do treino, quando este tenha sido concluído com aproveitamento. 
+3 - O treinador é obrigado a publicitar, em local visível ao público, o seu título profissional. 
+4 - Sempre que um treinador certificado estabelecido em território nacional cesse a sua atividade neste território, deve comunicar este facto à DGAV
+Artigo 123.º - Suspensão ou cassação do título profissional
+A violação do disposto no presente decreto-lei, incluindo a violência ou agressividade contra os animais ou seus detentores, podem determinar a suspensão ou o cancelamento do título profissional. 
+A condenação do treinador, por sentença transitada em julgado, aquando da posse de título profissional como treinador de cães, por crimes dolosos contra bens jurídicos pessoais puníveis com pena de prisão igual ou superior a 3 anos, por crimes contra a paz pública ou por qualquer crime previsto no presente decreto-lei ou crime contra animais de companhia, determina a suspensão ou o cancelamento do título profissional. 
+Com o cancelamento ou suspensão do título profissional, deve o profissional entregar de imediato o respetivo título ao ICNF, I.P, pelo período de aplicação da sanção em causa, sob pena de o mesmo ser cassado.
+Secção II - Treino e utilização de cães para fins específicos
+Artigo 124.º - Obrigações especiais para treino e utilização de cães para fins específicos
+O treino e a utilização de cães para fins de assistência, intervenções e terapias assistidas por animais, competição e atividades desportivas, recreativas e de trabalho, deve garantir a todo o tempo a salvaguarda do bem-estar do animal.
+Para efeitos do disposto no número anterior, deve ser considerada a existência de um plano de profilaxia médico-veterinária, que a duração e frequência das sessões ou atividades respeitam os períodos de descanso e recuperação do animal, que as interações humano-animal são positivas, que o animal tem a possibilidade de se retirar da atividade quando se mostra relutante em participar nela ou demonstre sinais de cansaço fadiga, que a condição física e temperamento do animal são adequados à atividade a realizar, que o animal apresenta motivação para a tarefa, que o detentor reconhece e atende aos sinais de stresse ou desconforto por parte do detentor, e que são proporcionados ao animal oportunidades para momentos lúdicos e de relaxamento.</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Arts. 51.º, 52.º do Código do Animal (DL 214/2013)</t>
+          <t>Art. 7.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Artigo 51.º - Exercício de profissões relacionadas com cães
-O exercício de certas profissões (adestrador, criador) requer documentação específica e conformidade com normas de bem-estar animal.
-Artigo 52.º - Documentação necessária
-Requerimentos de certificação e qualificação profissional para operadores.</t>
+          <t>Os detentores de cães devem promover o treino dos mesmos, com vista à sua socialização e obediência.
+O treino dos cães é realizado de acordo com as boas práticas em uso no exercício da atividade.</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>DL 82/2019 - Normas de profissionalismo</t>
+          <t>Decreto-Lei n.º 315/2009, de 29 de outubro,</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Legislação portuguesa estabelece normas de profissionalismo e qualificação para operadores em bem-estar animal, com requisitos de formação e certificação conforme disposições de Decreto-Lei específico.</t>
+          <t>Treino/Treinadores de cães potencialmente perigosos e perigosos
+Decreto-Lei n.º 74/2007, de 27 de março
+ Treino em Cães de Assistência</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>SIM - Cobertura COMPLETA (certificação profissional, provas teóricas e práticas, métodos positivos)</t>
+          <t>Cães de assistência e perigosos ou potencialmente perigosos a rever no contexto próprio, não abrangido pelo @regulamento</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>SIM - Cobertura COMPLETA (profissionalismo, qualificações obrigatórias)</t>
+          <t>Necessita ir ao encontro da certificação</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
-          <t>SIM - Cobertura COMPLETA (Arts. 118-120 implementam sistema profissional com certificação)</t>
+          <t>Cobertura completa, implementam sistema profissional com certificação pela Autoridade como requerido)
+Vai mais além e regula toda as facetas de treino, incluindo excetuando os perigos e potencialmente perigosos previstos na secção anterior</t>
         </is>
       </c>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>A legislação portuguesa implementa COMPLETAMENTE os requisitos do Artigo 18. O RGBEAC (Arts. 118-120) estabelece um sistema robusto de certificação profissional para treinadores de cães com: título profissional obrigatório, requisitos de habilitação, provas teóricas e práticas, métodos baseados em reforço positivo, verificação de antecedentes criminais. Sistema já em vigor conforme Decreto-Lei.</t>
+          <t>O RGBEAC cumpre os critérios ao prever um sistema robusto de certificação profissional para treinadores de cães com: título profissional obrigatório, requisitos de habilitação, provas teóricas e práticas, métodos baseados em reforço positivo, verificação de antecedentes criminais. 
+Na legislação vigente só se encontra referências ao treino no Decreto-Lei n.º 315/2009, de 29 de Outubro, (regime dos cães perigosos e potencialmente perigosos), e no Decreto-Lei n.º 74/2007, de 27 de março, relativo ao treino em Cães de Assistência</t>
         </is>
       </c>
       <c r="O19" s="11" t="inlineStr">
@@ -2621,11 +3084,7 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="P19" s="11" t="inlineStr">
-        <is>
-          <t>Sistema profissional português já implementado - cobertura completa e adequada</t>
-        </is>
-      </c>
+      <c r="P19" s="11" t="inlineStr"/>
     </row>
     <row r="20" ht="120" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -2635,39 +3094,39 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Art.º 23.º do Regulamento 2023/0447</t>
+          <t>Art.º 23.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>1.	Member States shall be responsible for establishing and maintaining databases for the registration of identified dogs and cats in accordance with Article 20(1) and (2) and Article 26(3) and Article 26(4), second subparagraph.
-2.	For that purpose, the Member States may use databases maintained by another Member State, on the basis of appropriate arrangements between those Member States.
-3.	 Member States shall ensure that their databases, as referred to in paragraph 1, comply with the requirements laid down by the implementing act referred to in paragraph 4, second subparagraph, point (b), to ensure their interoperability.
-4.	The Commission shall establish and maintain an index database containing the minimum set of fields laid down in the implementing acts referred to in subparagraph 2, point (b). The Commission may entrust the development, maintenance and operation of that index database to an independent entity, following a public selection process pursuant to the relevant provisions of Title VII of the Regulation (EU, Euratom) 2024/2509.
+          <t>Member States shall be responsible for establishing and maintaining databases for the registration of identified dogs and cats in accordance with Article 20(1) and (2) and Article 26(3) and Article 26(4), second subparagraph.
+For that purpose, the Member States may use databases maintained by another Member State, on the basis of appropriate arrangements between those Member States.
+Member States shall ensure that their databases, as referred to in paragraph 1, comply with the requirements laid down by the implementing act referred to in paragraph 4, second subparagraph, point (b), to ensure their interoperability.
+The Commission shall establish and maintain an index database containing the minimum set of fields laid down in the implementing acts referred to in subparagraph 2, point (b). The Commission may entrust the development, maintenance and operation of that index database to an independent entity, following a public selection process pursuant to the relevant provisions of Title VII of the Regulation (EU, Euratom) 2024/2509.
 The Commission shall adopt implementing acts laying down detailed arrangements concerning:
-(a)	the minimum content of the databases referred to in paragraph 1;
-(b)	the interoperability between Member States’ databases and the index database, including the minimum set of fields to be transmitted to the index database and the intervals of the transmission;
-(c)	the functionality for providing proof of the identification and registration of a dog or a cat, as referred to in Article 21 (3) point (a).
-(d)	the registry where Member States will declare their databases, and the necessary parameters for connecting those databases with one another in accordance with the provisions established pursuant to point (b);
-(e)	the interconnection between the Member States’ databases referred to in paragraph 1, the pet travellers' database referred to in Article 26, paragraph 4, and the Information Management System for Official Controls (IMSOC), where relevant.
+the minimum content of the databases referred to in paragraph 1;
+the interoperability between Member States’ databases and the index database, including the minimum set of fields to be transmitted to the index database and the intervals of the transmission;
+the functionality for providing proof of the identification and registration of a dog or a cat, as referred to in Article 21 (3) point (a).
+the registry where Member States will declare their databases, and the necessary parameters for connecting those databases with one another in accordance with the provisions established pursuant to point (b);
+the interconnection between the Member States’ databases referred to in paragraph 1, the pet travellers' database referred to in Article 26, paragraph 4, and the Information Management System for Official Controls (IMSOC), where relevant.
 The Commission shall adopt the implementing acts referred to in the second subparagraph, points (a) and (c) by ... [date two years after the date of entry into force of this Regulation]. It shall adopt the implementing acts referred to in the second subparagraph, points (b), (d) and (e) by ...[three years from the date of entry into force of this Regulation].
 Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 29.</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>1.	Os Estados-Membros são responsáveis pela criação e manutenção de bases de dados para o registo de cães e gatos identificados, em conformidade com o artigo 20.º, n.ºs 1 e 2, e com o artigo 26.º, n.ºs 3 e 4, segundo parágrafo.
-2.	Para este efeito, os Estados-Membros podem utilizar bases de dados mantidas por outro Estado-Membro, com base em acordos apropriados entre esses Estados-Membros.
-3.	Os Estados-Membros asseguram que as suas bases de dados referidas no n.º 1 estão em conformidade com os requisitos estabelecidos pelo ato de execução referido no n.º 4, segundo parágrafo, alínea b), de modo a assegurar a sua interoperabilidade.
-4.	A Comissão estabelece e mantém uma base de dados de índice contendo o conjunto mínimo de campos estabelecido nos atos de execução referidos no segundo parágrafo, alínea b). A Comissão pode confiar o desenvolvimento, a manutenção e o funcionamento dessa base de dados de índice a uma entidade independente, na sequência de um processo de seleção pública.
-	A Comissão adota atos de execução que estabelecem regras pormenorizadas relativas a:
-(a)	o conteúdo mínimo das bases de dados referidas no n.º 1;
-(b)	a interoperabilidade entre as bases de dados dos Estados-Membros e a base de dados de índice, incluindo o conjunto mínimo de campos a transmitir à base de dados de índice e os intervalos da transmissão;
-(c)	a funcionalidade para fornecer prova de identificação e registo de um cão ou gato, tal como referido no artigo 21.º, n.º 3, alínea a);
-(d)	o registo onde os Estados-Membros declaram as suas bases de dados, e os parâmetros necessários para a conexão dessas bases de dados entre si, em conformidade com as disposições estabelecidas em aplicação da alínea b);
-(e)	a interconexão entre as bases de dados dos Estados-Membros referidas no n.º 1, a base de dados de viajantes da União com animais de estimação referida no artigo 26.º, n.º 4, e o Sistema de Gestão da Informação para os Controlos Oficiais (IMSOC), quando relevante.
-	A Comissão adota os atos de execução referidos no segundo parágrafo, alíneas a) e c), até … [data dois anos após a data de entrada em vigor do presente Regulamento]. Adota os atos de execução referidos no segundo parágrafo, alíneas b), d) e e), até … [três anos a contar da data de entrada em vigor do presente Regulamento].
-	Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
+          <t>Os Estados-Membros são responsáveis pela criação e manutenção de bases de dados para o registo de cães e gatos identificados, em conformidade com o artigo 20.º, n.ºs 1 e 2, e com o artigo 26.º, n.ºs 3 e 4, segundo parágrafo.
+Para este efeito, os Estados-Membros podem utilizar bases de dados mantidas por outro Estado-Membro, com base em acordos apropriados entre esses Estados-Membros.
+Os Estados-Membros asseguram que as suas bases de dados referidas no n.º 1 estão em conformidade com os requisitos estabelecidos pelo ato de execução referido no n.º 4, segundo parágrafo, alínea b), de modo a assegurar a sua interoperabilidade.
+A Comissão estabelece e mantém uma base de dados de índice contendo o conjunto mínimo de campos estabelecido nos atos de execução referidos no segundo parágrafo, alínea b). A Comissão pode confiar o desenvolvimento, a manutenção e o funcionamento dessa base de dados de índice a uma entidade independente, na sequência de um processo de seleção pública.
+A Comissão adota atos de execução que estabelecem regras pormenorizadas relativas a:
+o conteúdo mínimo das bases de dados referidas no n.º 1;
+a interoperabilidade entre as bases de dados dos Estados-Membros e a base de dados de índice, incluindo o conjunto mínimo de campos a transmitir à base de dados de índice e os intervalos da transmissão;
+a funcionalidade para fornecer prova de identificação e registo de um cão ou gato, tal como referido no artigo 21.º, n.º 3, alínea a);
+o registo onde os Estados-Membros declaram as suas bases de dados, e os parâmetros necessários para a conexão dessas bases de dados entre si, em conformidade com as disposições estabelecidas em aplicação da alínea b);
+a interconexão entre as bases de dados dos Estados-Membros referidas no n.º 1, a base de dados de viajantes da União com animais de estimação referida no artigo 26.º, n.º 4, e o Sistema de Gestão da Informação para os Controlos Oficiais (IMSOC), quando relevante.
+A Comissão adota os atos de execução referidos no segundo parágrafo, alíneas a) e c), até … [data dois anos após a data de entrada em vigor do presente Regulamento]. Adota os atos de execução referidos no segundo parágrafo, alíneas b), d) e e), até … [três anos a contar da data de entrada em vigor do presente Regulamento].
+Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2678,10 +3137,10 @@
       <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Artigo 20.º - Sistema de Informação de Animais de Companhia (SIAC)
-1 - O SIAC reúne a informação relativa à rastreabilidade dos dispositivos de identificação, à identificação dos animais de companhia, à sua titularidade ou detenção e à informação relacionada com a defesa da saúde pública, saúde animal e bem-estar animal.
-2 – A DGAV é a entidade responsável pelo SIAC, competindo-lhe assegurar o seu funcionamento e o tratamento seguro da informação.
-3 – A DGAV pode atribuir a gestão do SIAC a outras entidades, mediante a celebração de protocolo e parecer prévio da Comissão Nacional de Proteção de Dados.
-4 - As normas e procedimentos relativos ao funcionamento do SIAC constam de um Manual de Procedimentos SIAC, aprovado pelo diretor-geral de alimentação e veterinária.</t>
+O SIAC reúne a informação relativa à rastreabilidade dos dispositivos de identificação, à identificação dos animais de companhia, à sua titularidade ou detenção e à informação relacionada com a defesa da saúde pública, saúde animal e bem-estar animal.
+A DGAV é a entidade responsável pelo SIAC, competindo-lhe assegurar o seu funcionamento e o tratamento seguro da informação.
+A DGAV pode atribuir a gestão do SIAC a outras entidades, mediante a celebração de protocolo e parecer prévio da Comissão Nacional de Proteção de Dados.
+As normas e procedimentos relativos ao funcionamento do SIAC constam de um Manual de Procedimentos SIAC, aprovado pelo diretor-geral de alimentação e veterinária.</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -2708,27 +3167,23 @@
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>DL 82/2019 estabelece o SIAC com extensas disposições cobrindo: criação da base de dados, procedimentos de registo e controlos de acesso, gestão por DGAV, identificação eletrónica via transponder, segurança de dados e autorização de acesso, integração de registos de identificação de animais, gestão da distribuição de dispositivos de identificação, procedimentos de registo e atualização. O sistema é totalmente operacional desde 2019.</t>
-        </is>
-      </c>
-      <c r="K20" s="8" t="inlineStr">
-        <is>
-          <t>NÃO - SIAC em funcionamento desde 2019 cumpre todos os requisitos</t>
-        </is>
-      </c>
+          <t>DL 82/2019 estabelece o SIAC com extensas disposições cobrindo: criação da base de dados, procedimentos de registo e controlos de acesso, gestão por DGAV, identificação eletrónica via transponder, segurança de dados e autorização de acesso, integração de registos de identificação de animais, gestão da distribuição de dispositivos de identificação, procedimentos de registo e atualização. O sistema é operacional desde 2019.</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr"/>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>NÃO - Código do Animal estabelece estrutura completa com classificações</t>
+          <t>Código do Animal estabelece estrutura completa com classificações</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
-          <t>NÃO - RGBEAC (Art. 20.º) reafirma e fortalece o sistema SIAC</t>
+          <t>Reafirma e fortalece o sistema SIAC</t>
         </is>
       </c>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>A legislação portuguesa CUMPRE COMPLETAMENTE os requisitos do Artigo 19. O SIAC (Sistema de Informação de Animais de Companhia) já está operacional desde 2019, sob responsabilidade de DGAV, com: identificação eletrónica via microchip obrigatória, registo nacional centralizado, rastreabilidade garantida, classificação de animais (normal/perigoso/potencialmente perigoso), integração de dados de saúde e bem-estar, conformidade com proteção de dados (Comissão Nacional de Proteção de Dados).</t>
+          <t>A legislação portuguesa cumpre os requisitos do Artigo 19. O SIAC está operacional desde 2019, sob responsabilidade de DGAV, com: identificação eletrónica via microchip obrigatória, registo nacional centralizado, rastreabilidade, classificação de animais (normal/perigoso/potencialmente perigoso), integração de dados de saúde e bem-estar, conformidade com proteção de dados (Comissão Nacional de Proteção de Dados).</t>
         </is>
       </c>
       <c r="O20" s="11" t="inlineStr">
@@ -2736,11 +3191,7 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="P20" s="11" t="inlineStr">
-        <is>
-          <t>SIAC totalmente operacional e conforme - Interoperabilidade EU pendente de implementação</t>
-        </is>
-      </c>
+      <c r="P20" s="11" t="inlineStr"/>
     </row>
     <row r="21" ht="120" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -2750,85 +3201,63 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Art.º 24.º do Regulamento 2023/0447</t>
+          <t>Art.º 24.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>1.	The competent authorities shall collect, analyse and publish the data on animal welfare set out in Annex III:
-2.	The competent authorities shall draw up and transmit to the Commission a report in electronic form, on the data on animal welfare, set out in Annex III, by 31 August at three-yearly intervals. The first such report shall be drawn up and transmitted to the Commission by ... [date 6 years from the date of entry into force of this Regulation]. Each report shall contain a summary of the data gathered during the previous three years.
-3.	The Commission may adopt implementing acts, establishing a harmonised methodology for collecting the data on animal welfare set out in Annex III and establishing a template for the report referred to in paragraph 2 of this Article. Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 29.</t>
+          <t>The competent authorities shall collect, analyse and publish the data on animal welfare set out in Annex III:
+The competent authorities shall draw up and transmit to the Commission a report in electronic form, on the data on animal welfare, set out in Annex III, by 31 August at three-yearly intervals. The first such report shall be drawn up and transmitted to the Commission by ... [date 6 years from the date of entry into force of this Regulation]. Each report shall contain a summary of the data gathered during the previous three years.
+The Commission may adopt implementing acts, establishing a harmonized methodology for collecting the data on animal welfare set out in Annex III and establishing a template for the report referred to in paragraph 2 of this Article. Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 29.</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>1.	As autoridades competentes devem recolher, analisar e publicar os dados sobre bem-estar animal estabelecidos no Anexo III.
-2.	As autoridades competentes devem elaborar e transmitir à Comissão um relatório em formato eletrónico, sobre os dados relativos ao bem-estar animal estabelecidos no Anexo III, até 31 de agosto, com periodicidade trienal. O primeiro relatório deve ser elaborado e transmitido à Comissão até ... [data 6 anos após a data de entrada em vigor do presente regulamento]. Cada relatório deve conter um resumo dos dados recolhidos durante os três anos anteriores.
-3.	A Comissão pode adotar atos de execução que estabeleçam uma metodologia harmonizada para a recolha dos dados sobre bem-estar animal estabelecidos no Anexo III e que definam um modelo para o relatório referido no n.º 2 do presente artigo. Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
+          <t>As autoridades competentes devem recolher, analisar e publicar os dados sobre bem-estar animal estabelecidos no Anexo III.
+As autoridades competentes devem elaborar e transmitir à Comissão um relatório em formato eletrónico, sobre os dados relativos ao bem-estar animal estabelecidos no Anexo III, até 31 de agosto, com periodicidade trienal. O primeiro relatório deve ser elaborado e transmitido à Comissão até ... [data 6 anos após a data de entrada em vigor do presente regulamento]. Cada relatório deve conter um resumo dos dados recolhidos durante os três anos anteriores.
+A Comissão pode adotar atos de execução que estabeleçam uma metodologia harmonizada para a recolha dos dados sobre bem-estar animal estabelecidos no Anexo III e que definam um modelo para o relatório referido no n.º 2 do presente artigo. Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Art.º 46.º do RGBEAC (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Artigo 46.º - Relatório Nacional Anual
-1 - Os centros de bem-estar animal e alojamentos remetem à DGAV no primeiro mês de cada ano civil, os relatórios de gestão do ano anterior, com números de animais recolhidos, restituídos, eutanasiados, cedidos, adotados, devolvidos após adoção, vacinados, esterilizados e intervencionados em programas CED.
-2 – A DGVA consolida a informação a nível nacional sobre bem-estar animal em cada ano, incluindo: acompanhamento da política internacional, prestação de apoios públicos, atividade do SIAC, resultados de planos de controlo, processos contraordenacionais, coimas aplicadas, atividade de centros de bem-estar, programas de interesse nacional, ações informativas e educativas, para efeitos de elaboração do Relatório Anual sobre a situação do Bem-Estar Animal.</t>
-        </is>
-      </c>
+          <t>Análise no Anexo III</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr"/>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Arts. 141.º-145.º do Código do Animal (DL 214/2013)</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>Código do Animal estabelece estrutura de monitorização e relatórios sobre bem-estar animal, incluindo: recolha de dados de infrações, aplicação de sanções, atividades de centros de recolha, estatísticas de animais processados. Sistema de contraordenações com documentação e coimas registadas.</t>
-        </is>
-      </c>
+          <t>Análise no Anexo III</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr"/>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>Decreto-Regulamentar n.º 3/2021 + DL 82/2019</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>Decreto-Regulamentar 3/2021 (Art. 3.º) requer Relatório Anual sobre situação do Bem-Estar Animal. DL 82/2019 estabelece procedimentos de recolha de dados, monitorização, registo de atividades médico-veterinárias e compilação de informação de bem-estar animal para fins de relatório anual e transmissão a autoridades europeias.</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>SIM - Cobertura COMPLETA (relatórios anuais, recolha de dados, consolidação nacional)</t>
-        </is>
-      </c>
+          <t>Análise no Anexo III</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr"/>
+      <c r="K21" s="8" t="inlineStr"/>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>SIM - Cobertura COMPLETA (monitorização, infrações, sanções, estatísticas)</t>
+          <t>Análise no Anexo III</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
-          <t>SIM - Cobertura COMPLETA (Art. 46.º estabelece sistema de relatórios nacionais)</t>
+          <t>Análise no Anexo III</t>
         </is>
       </c>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>A legislação portuguesa implementa COMPLETAMENTE o Artigo 20. Sistema já estabelecido com: recolha anual de dados de centros de bem-estar animal, consolidação de informação de bem-estar a nível nacional, inclusão de estatísticas de SIAC, registos de contraordenações e sanções, relatórios sobre atividades de proteção animal, conformidade com requisitos de Decreto-Regulamentar 3/2021. Único ajuste necessário: alinhamento da periodicidade de relatórios (atualmente anual; Regulamento requer trienal) e inclusão dos dados específicos de Annex III da EU (quando publicado).</t>
+          <t>necessário: alinhamento da periodicidade de relatórios (atualmente anual; Regulamento requer trienal) e inclusão dos dados específicos de Annex III da EU (quando publicado).</t>
         </is>
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P21" s="11" t="inlineStr">
-        <is>
-          <t>Sistema de relatórios já operacional - apenas alinhamento com padrões EU necessário</t>
-        </is>
-      </c>
+          <t>Sim - Ajuste de periodicidade e conformidade com Annex III EU</t>
+        </is>
+      </c>
+      <c r="P21" s="11" t="inlineStr"/>
     </row>
     <row r="22" ht="120" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -2838,38 +3267,36 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Art.º 25.º do Regulamento 2023/0447</t>
+          <t>Art.º 25.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>1.	The competent authorities of the Member States shall be controllers within the meaning of Regulation (EU) 2016/679 in relation to the processing of personal data collected under Articles 9 and 10 of this Regulation, as well as under Article 23(1) of this Regulation when used for the purposes of official control.
+          <t>The competent authorities of the Member States shall be controllers within the meaning of Regulation (EU) 2016/679 in relation to the processing of personal data collected under Articles 9 and 10 of this Regulation, as well as under Article 23(1) of this Regulation when used for the purposes of official control.
 The Commission shall be a controller within the meaning of Regulation (EU) 2018/1725 in relation to the processing of personal data collected under Article 21(5), Article 23(4), and Article 26(4), third subparagraph, , as well as under Article 23(1) of this Regulation when that data is used for the purposes of compliance with Article 108 of Regulation (EU) 2017/625 and the reporting obligations under this Regulation.
 It shall be prohibited for any person with access to the personal data referred to in the first and second subparagraphs to divulge any personal data the knowledge of which was acquired in the exercise of his or her duties or otherwise incidentally to such exercise. Member States and the Commission shall take all appropriate measures to enforce that prohibition.
 The personal data collected under the first and second subparagraphs shall not be used for purposes other than:
-(a)	official controls by Member States’ competent authorities of compliance with the welfare and traceability requirements of this Regulation and of compliance with Regulation (EU) 2016/429, including the detection of fraudulent practices; and
-(b)	compliance by the Commission with its obligations under Article 108 of Regulation (EU) 2017/625 and with the Commission’s reporting obligations under this Regulation.
-2.	The personal data referred to in paragraph 1 of this Article shall be retained for the following periods:
-(a)	in the case of Articles 9 and 10, 10 years after the date of cessation of the activity of the establishment;
-(b)	in the case of Article 21(5), 18 months after the generation of the token referred to in Article 21(3), second subparagraph;
-(c)	in the case of Articles 23(1) and 23(4), 25 years after the first registration of the dog or cat in the database referred to in that Article or five years after the recording of the death of the dog or cat in that database;
-(d)	in the case of Article 26(4), third subparagraph, 5 years after the date of pre-notification.
-CHAPTER V
-ENTRY OF DOGS AND CATS INTO THE UNION</t>
+official controls by Member States’ competent authorities of compliance with the welfare and traceability requirements of this Regulation and of compliance with Regulation (EU) 2016/429, including the detection of fraudulent practices; and
+compliance by the Commission with its obligations under Article 108 of Regulation (EU) 2017/625 and with the Commission’s reporting obligations under this Regulation.
+The personal data referred to in paragraph 1 of this Article shall be retained for the following periods:
+in the case of Articles 9 and 10, 10 years after the date of cessation of the activity of the establishment;
+in the case of Article 21(5), 18 months after the generation of the token referred to in Article 21(3), second subparagraph;
+in the case of Articles 23(1) and 23(4), 25 years after the first registration of the dog or cat in the database referred to in that Article or five years after the recording of the death of the dog or cat in that database;
+in the case of Article 26(4), third subparagraph, 5 years after the date of pre-notification.</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>1.	As autoridades competentes dos Estados-Membros devem ser controladoras na aceção do Regulamento (UE) 2016/679 no que respeita ao tratamento de dados pessoais recolhidos nos termos dos artigos 9.º e 10.º do presente Regulamento, bem como no âmbito do artigo 23.º, n.º 1, do presente Regulamento quando utilizados para efeitos de controlo oficial.
-	A Comissão deve ser controladora na aceção do Regulamento (UE) 2018/1725 no que respeita ao tratamento de dados pessoais recolhidos nos termos do artigo 21.º, n.º 5, do artigo 23.º, n.º 4, e do terceiro parágrafo do artigo 26.º, n.º 4, do presente Regulamento, bem como no âmbito do artigo 23.º, n.º 1, do presente Regulamento quando esses dados são utilizados para efeitos de conformidade com o artigo 108.º do Regulamento (UE) 2017/625 e de obrigações de comunicação de informações previstas no presente Regulamento.
-	É proibido a qualquer pessoa com acesso aos dados pessoais referidos nos primeiro e segundo parágrafos divulgar quaisquer dados pessoais cujo conhecimento tenha sido adquirido no exercício das suas funções ou a título acessório do exercício dessas funções. Os Estados-Membros e a Comissão devem adotar todas as medidas adequadas para fazer respeitar essa proibição.
-	Os dados pessoais recolhidos nos termos do primeiro e segundo parágrafos não podem ser utilizados para outros fins que não:
-(a)	controlos oficiais pelas autoridades competentes dos Estados-Membros da conformidade com os requisitos de bem-estar e de rastreabilidade do presente Regulamento e da conformidade com o Regulamento (UE) 2016/429, incluindo a deteção de práticas fraudulentas; e
-(b)	o cumprimento pela Comissão das suas obrigações nos termos do artigo 108.º do Regulamento (UE) 2017/625 e das obrigações de comunicação de informações da Comissão previstas no presente Regulamento.
-2.	Os dados pessoais referidos no n.º 1 do presente artigo são conservados pelos seguintes períodos:
-(a)	no caso dos artigos 9.º e 10.º, 10 anos após a data de cessação da atividade do estabelecimento;
-(b)	no caso do artigo 21.º, n.º 5, 18 meses após a geração do token referido no artigo 21.º, n.º 3, segundo parágrafo;
-(c)	no caso dos artigos 23.º, n.ºs 1 e 4, 25 anos após o primeiro registo do cão ou gato na base de dados referida nesse artigo ou cinco anos após o registo da morte do cão ou gato nessa base de dados;
+          <t>As autoridades competentes dos Estados-Membros devem ser controladoras na aceção do Regulamento (UE) 2016/679 no que respeita ao tratamento de dados pessoais recolhidos nos termos dos artigos 9.º e 10.º do presente Regulamento, bem como no âmbito do artigo 23.º, n.º 1, do presente Regulamento quando utilizados para efeitos de controlo oficial.
+A Comissão deve ser controladora na aceção do Regulamento (UE) 2018/1725 no que respeita ao tratamento de dados pessoais recolhidos nos termos do artigo 21.º, n.º 5, do artigo 23.º, n.º 4, e do terceiro parágrafo do artigo 26.º, n.º 4, do presente Regulamento, bem como no âmbito do artigo 23.º, n.º 1, do presente Regulamento quando esses dados são utilizados para efeitos de conformidade com o artigo 108.º do Regulamento (UE) 2017/625 e de obrigações de comunicação de informações previstas no presente Regulamento.
+É proibido a qualquer pessoa com acesso aos dados pessoais referidos nos primeiro e segundo parágrafos divulgar quaisquer dados pessoais cujo conhecimento tenha sido adquirido no exercício das suas funções ou a título acessório do exercício dessas funções. Os Estados-Membros e a Comissão devem adotar todas as medidas adequadas para fazer respeitar essa proibição.
+Os dados pessoais recolhidos nos termos do primeiro e segundo parágrafos não podem ser utilizados para outros fins que não:
+controlos oficiais pelas autoridades competentes dos Estados-Membros da conformidade com os requisitos de bem-estar e de rastreabilidade do presente Regulamento e da conformidade com o Regulamento (UE) 2016/429, incluindo a deteção de práticas fraudulentas; e
+o cumprimento pela Comissão das suas obrigações nos termos do artigo 108.º do Regulamento (UE) 2017/625 e das obrigações de comunicação de informações da Comissão previstas no presente Regulamento.
+Os dados pessoais referidos no n.º 1 do presente artigo são conservados pelos seguintes períodos:
+no caso dos artigos 9.º e 10.º, 10 anos após a data de cessação da atividade do estabelecimento;
+no caso do artigo 21.º, n.º 5, 18 meses após a geração do token referido no artigo 21.º, n.º 3, segundo parágrafo;
+no caso dos artigos 23.º, n.ºs 1 e 4, 25 anos após o primeiro registo do cão ou gato na base de dados referida nesse artigo ou cinco anos após o registo da morte do cão ou gato nessa base de dados;
 (d)	no caso do artigo 26.º, n.º 4, terceiro parágrafo, 5 anos após a data da pré-notificação.</t>
         </is>
       </c>
@@ -2912,24 +3339,20 @@
 1 - Os animais de companhia abrangidos pela obrigação de identificação devem ser registados pelo médico veterinário no SIAC, imediatamente após a sua marcação com o transponder, em nome do respetivo titular.</t>
         </is>
       </c>
-      <c r="K22" s="8" t="inlineStr">
-        <is>
-          <t>NÃO - Legislação portuguesa cobre completamente com incorporação de GDPR</t>
-        </is>
-      </c>
+      <c r="K22" s="8" t="inlineStr"/>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>NÃO - Cobertura expressa em Art. 55.º</t>
+          <t>Cobertura expressa em Art. 55.º</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
-          <t>NÃO - Implementação completa em Arts. 20.º</t>
+          <t>Implementação completa em Arts. 20.º</t>
         </is>
       </c>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>A legislação portuguesa implementa completamente os requisitos de proteção de dados do Artigo 20a. O SIAC é configurado como sistema compliant com GDPR (EU 2016/679) e com regulamentações de proteção de dados. Não há necessidade de alterações legislativas.</t>
+          <t>A legislação portuguesa implementa completamente os requisitos de proteção de dados. O SIAC é configurado como sistema compliant com GDPR (EU 2016/679) e com regulamentações de proteção de dados.</t>
         </is>
       </c>
       <c r="O22" s="11" t="inlineStr">
@@ -2937,11 +3360,7 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="P22" s="11" t="inlineStr">
-        <is>
-          <t>Correspondências confirmadas por agente de pesquisa em 2026-03-02</t>
-        </is>
-      </c>
+      <c r="P22" s="11" t="inlineStr"/>
     </row>
     <row r="23" ht="120" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -2951,7 +3370,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Art.º 26.º do Regulamento 2023/0447</t>
+          <t>Art.º 26.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2987,17 +3406,17 @@
 (b)	provenham de um país terceiro ou território e de um estabelecimento incluído em lista em conformidade com os artigos 126.º e 127.º do Regulamento (UE) 2017/625.
 2.	O certificado oficial referido no artigo 126.º, n.º 2, alínea c), do Regulamento (UE) 2017/625 que acompanha os cães e gatos introduzidos na União desde países terceiros e territórios para efeitos de colocação no mercado da União deve conter uma atestação certificando a conformidade com o n.º 1 do presente artigo.
 3.	Os cães e gatos introduzidos na União para efeitos de colocação no mercado da União devem ser identificados antes da sua entrada na União por um médico veterinário por meio de um transponder injetável contendo um microchip legível em conformidade com os requisitos estabelecidos no Anexo II.
-	O operador responsável pela importação dos cães ou gatos para a União deve assegurar que estes são registados por um médico veterinário numa base de dados nacional referida no artigo 23.º, n.º 1, no prazo de cinco dias úteis após a sua introdução na União. Os Estados-Membros podem permitir o registo por pessoas que não sejam médicos veterinários, desde que disponham de medidas para assegurar a exatidão das informações que essas pessoas introduzem na base de dados.
+O operador responsável pela importação dos cães ou gatos para a União deve assegurar que estes são registados por um médico veterinário numa base de dados nacional referida no artigo 23.º, n.º 1, no prazo de cinco dias úteis após a sua introdução na União. Os Estados-Membros podem permitir o registo por pessoas que não sejam médicos veterinários, desde que disponham de medidas para assegurar a exatidão das informações que essas pessoas introduzem na base de dados.
 4.	O movimento não comercial de um cão ou gato desde um país terceiro ou território para a União deve ser pré-notificado pelo seu proprietário a uma base de dados online de viajantes da União com animais de estimação, pelo menos cinco dias úteis antes de o cão ou gato atravessar a fronteira da União, exceto nos seguintes casos:
 (a)	quando o cão ou gato é introduzido na União diretamente desde países terceiros ou territórios que satisfazem as condições estabelecidas no artigo 17.º, n.º 1, alínea a), do Regulamento Delegado (UE) …/… da Comissão; e
 (b)	quando o cão ou gato está registado numa base de dados de um Estado-Membro referida no artigo 23.º, n.º 1, do presente Regulamento.
-	Caso o cão ou gato permaneça mais de seis meses na União, o proprietário deve assegurar o seu registo por um médico veterinário na base de dados do Estado-Membro de residência referida no artigo 23.º, n.º 1, no prazo de cinco dias úteis após o termo do sexto mês desde a sua entrada na União. Os Estados-Membros podem permitir o registo por pessoas que não sejam médicos veterinários, desde que disponham de medidas para assegurar a exatidão das informações que essas pessoas introduzem na base de dados.
-	A Comissão estabelece e mantém a base de dados de viajantes da União com animais de estimação referida no primeiro parágrafo. A Comissão pode confiar o desenvolvimento, a manutenção e o funcionamento dessa base de dados a uma entidade independente, na sequência de um processo de seleção pública. O acesso a essa base de dados fica restrito às autoridades competentes dos Estados-Membros e à Comissão.
-	A Comissão assegura que a base de dados aciona notificações iRASFF para os movimentos pré-notificados que apresentem um risco de fraude. O Estado-Membro que recebe a notificação toma as medidas adequadas para dar seguimento à notificação, em conformidade com o artigo 105.º, n.º 2, do Regulamento (UE) 2017/625.
-	A Comissão adota, até … [8 anos após a data de entrada em vigor do presente Regulamento], atos de execução que estabelecem regras pormenorizadas relativas a:
+Caso o cão ou gato permaneça mais de seis meses na União, o proprietário deve assegurar o seu registo por um médico veterinário na base de dados do Estado-Membro de residência referida no artigo 23.º, n.º 1, no prazo de cinco dias úteis após o termo do sexto mês desde a sua entrada na União. Os Estados-Membros podem permitir o registo por pessoas que não sejam médicos veterinários, desde que disponham de medidas para assegurar a exatidão das informações que essas pessoas introduzem na base de dados.
+A Comissão estabelece e mantém a base de dados de viajantes da União com animais de estimação referida no primeiro parágrafo. A Comissão pode confiar o desenvolvimento, a manutenção e o funcionamento dessa base de dados a uma entidade independente, na sequência de um processo de seleção pública. O acesso a essa base de dados fica restrito às autoridades competentes dos Estados-Membros e à Comissão.
+A Comissão assegura que a base de dados aciona notificações iRASFF para os movimentos pré-notificados que apresentem um risco de fraude. O Estado-Membro que recebe a notificação toma as medidas adequadas para dar seguimento à notificação, em conformidade com o artigo 105.º, n.º 2, do Regulamento (UE) 2017/625.
+A Comissão adota, até … [8 anos após a data de entrada em vigor do presente Regulamento], atos de execução que estabelecem regras pormenorizadas relativas a:
 (i)	as informações a pré-notificar pelos proprietários em conformidade com o n.º 4 do presente artigo na base de dados de viajantes da União com animais de estimação, tendo em conta os requisitos de proteção de dados pessoais do Regulamento (UE) 2018/1725 e do Regulamento (UE) 2016/679;
 (ii)	o procedimento pelo qual o risco de fraude deve ser determinado, tendo em conta as atividades realizadas pela rede CAA.
-	Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
+Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -3035,23 +3454,23 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>Artigo 2.º - Âmbito de Aplicação
-O presente decreto-lei aplica-se à identificação de animais de companhia das espécies referidas no anexo I do Regulamento (UE) n.º 576/2013, do Parlamento Europeu e do Conselho, de 12 de junho de 2013, e no anexo I do Regulamento (UE) n.º 2016/429, do Parlamento Europeu e do Conselho, de 9 de março de 2016, nascidos ou presentes no território nacional.</t>
+          <t>Vários artigos
+(…)</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>PARCIAL - Cobre entrada/importação mas sem database online de viajantes pré-notificação</t>
+          <t>Sem database online de viajantes pré-notificação</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>SIM - Implementa controlos sanitários e requisitos de identificação</t>
+          <t>Implementa controlos sanitários e requisitos de identificação</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
-          <t>PARCIAL - Cobre entrada no território nacional com condições, não cobre movimento não-comercial pré-notificação</t>
+          <t>Cobre entrada no território nacional com condições, não cobre movimento não-comercial pré-notificação</t>
         </is>
       </c>
       <c r="N23" s="11" t="inlineStr">
@@ -3064,11 +3483,7 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="P23" s="11" t="inlineStr">
-        <is>
-          <t>Parcialmente coberto. Complementação necessária para movimento não-comercial e sistema iRASFF.</t>
-        </is>
-      </c>
+      <c r="P23" s="11" t="inlineStr"/>
     </row>
     <row r="24" ht="120" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -3078,121 +3493,89 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Art.º 27.º do Regulamento 2023/0447</t>
+          <t>Art.º 27.º do Regulamento 2023/0447 |  EN</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
           <t>The Commission is empowered to adopt delegated acts in accordance with Article 28 to amend the Annexes to this Regulation to take account of scientific and technical progress, including, where relevant, the scientific opinions of EFSA, as regards:
-(a)	a suitable number of animal carers in breeding and selling establishments;
-(b)	watering and feeding requirements and weaning process;
-(c)	temperature ranges;
-(d)	lighting requirements;
-(e)	ammonia and carbon monoxide levels;
-(f)	kennel and cattery designs;
-(g)	group housing;
-(h)	space allowances for various categories of dogs and cats;
-(i)	the frequency of pregnancies;
-(j)	the minimum and maximum age of bitches and queens for  breeding;
-(k)	socialisation, the provision of enrichments and other measures for meeting the behavioural needs of dogs and cats;
-(l)	the requirements for the transponders used to identify dogs and cats individually;
-(m)	the data to be collected for policy monitoring and evaluation.
+a suitable number of animal carers in breeding and selling establishments;
+watering and feeding requirements and weaning process;
+temperature ranges;
+lighting requirements;
+ammonia and carbon monoxide levels;
+kennel and cattery designs;
+group housing;
+space allowances for various categories of dogs and cats;
+the frequency of pregnancies;
+the minimum and maximum age of bitches and queens for  breeding;
+socialisation, the provision of enrichments and other measures for meeting the behavioural needs of dogs and cats;
+the requirements for the transponders used to identify dogs and cats individually;
+the data to be collected for policy monitoring and evaluation.
 Any additions of requirements in the Annexes shall be based on updated scientific or technical evidence, in particular such evidence regarding the specific conditions needed to ensure the welfare of the dogs and cats covered by the scope of this Regulation. Where relevant, those delegated acts shall take into account social, economic and environmental impacts and shall provide for sufficient transition periods to allow the operators concerned to adapt to the new requirements.</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>1. A Comissão fica habilitada a adotar atos delegados em conformidade com o artigo 28.º que alterem os anexos do presente Regulamento para ter em conta o progresso científico e técnico, incluindo, quando relevante, pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, nos seguintes aspetos:
-a) Um número adequado de cuidadores de animais em estabelecimentos de criação e venda;
-b) Requisitos de abastecimento de água e alimentação e processo de desmame;
-c) Gamas de temperatura;
-d) Requisitos de iluminação;
-e) Níveis de amoníaco e monóxido de carbono;
-f) Conceção de canis e gateis;
-g) Alojamento em grupo;
-h) Espaços permitidos para diferentes categorias de cães e gatos;
-i) Frequência de gestações;
-j) Idade mínima e máxima de cadelas e gatas para reprodução;
-k) Socialização, enriquecimento e outras medidas para satisfazer as necessidades comportamentais de cães e gatos;
-l) Requisitos para transponders utilizados na identificação individual de cães e gatos;
-m) Dados a recolher para avaliação e monitorização de políticas.
-2. Qualquer complemento de requisitos nos Anexos deve ser baseado em evidência científica ou técnica atualizada, em particular no que diz respeito às condições específicas necessárias para assegurar o bem-estar dos cães e gatos abrangidos pelo âmbito do presente Regulamento. Quando relevante, esses atos delegados devem levar em conta impactos sociais, económicos e ambientais e prever períodos de transição suficientes para permitir aos operadores envolvidos a adaptação aos novos requisitos.</t>
+          <t>A Comissão fica habilitada a adotar atos delegados em conformidade com o artigo 28.º que alterem os anexos do presente Regulamento para ter em conta o progresso científico e técnico, incluindo, quando relevante, pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, nos seguintes aspetos:
+Um número adequado de cuidadores de animais em estabelecimentos de criação e venda;
+Requisitos de abastecimento de água e alimentação e processo de desmame;
+Gamas de temperatura;
+Requisitos de iluminação;
+Níveis de amoníaco e monóxido de carbono;
+Conceção de canis e gatis;
+Alojamento em grupo;
+Espaços permitidos para diferentes categorias de cães e gatos;
+Frequência de gestações;
+Idade mínima e máxima de cadelas e gatas para reprodução;
+Socialização, enriquecimento e outras medidas para satisfazer as necessidades comportamentais de cães e gatos;
+Requisitos para transponders utilizados na identificação individual de cães e gatos;
+Dados a recolher para avaliação e monitorização de políticas.
+Qualquer complemento de requisitos nos Anexos deve ser baseado em evidência científica ou técnica atualizada, em particular no que diz respeito às condições específicas necessárias para assegurar o bem-estar dos cães e gatos abrangidos pelo âmbito do presente Regulamento. Quando relevante, esses atos delegados devem levar em conta impactos sociais, económicos e ambientais e prever períodos de transição suficientes para permitir aos operadores envolvidos a adaptação aos novos requisitos.</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Arts. 3-8 e ANEXO do RGBEAC (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>Artigos 3.º a 8.º do Decreto-Lei que aprova o RGBEAC estabelecem mecanismo legislativo para alteração de diplomas anteriores. O RGBEAC contém um ANEXO estruturado com:
-- TÍTULO I: Disposições gerais
-- TÍTULO II: Obrigações e proibições (Lista Nacional de Animais, identificação, registo)
-- TÍTULO III: Fiscalização, contraordenações, crimes e sanções
-- TÍTULO V: Disposições finais
-O ANEXO contém todas as disposições técnicas relativas a bem-estar, espaço disponível, temperatura, frequência de alimentação, e outros parâmetros correspondentes aos Anexos I-V do Regulamento EU 2023/0447.
-NOTA: O mecanismo atual é legislativo padrão (alteração de Decreto-Lei por novo Decreto-Lei). NÃO existe autoridade delegada expressa para alteração por atos de execução, conforme previsto no Art. 22-24 do Regulamento EU 2023/0447.</t>
-        </is>
-      </c>
+          <t>Sem equivalência</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr"/>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Art.º 23.º e ANEXO II do Código do Animal (DL 214/2013)</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>Artigo 23.º - Condições Particulares para a Manutenção de Cães e Gatos
-1 - O alojamento de cães e gatos deve obedecer às dimensões mínimas indicadas no anexo II ao presente diploma.
-ANEXO II - Parâmetros Técnicos de Alojamento
-Contém requisitos para:
-- Dimensões mínimas de gaiolas e recintos
-- Superfícies de exercício
-- Estruturas para enriquecimento ambiental (gatos: tabuleiros, superfícies de repouso, estruturas para afiar garras)
-- Pavimentos (proibição de grades)
-- Condições de higiene e bem-estar
-Corresponde materialmente aos requisitos de espaço, temperatura e frequência referidos no Art. 22 do Regulamento.</t>
-        </is>
-      </c>
+          <t>Sem equivalência.</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr"/>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>DL n.º 82/2019 - Referências a Anexos de Regulamentos EU</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>DL n.º 82/2019 incorpora por referência os Anexos I dos Regulamentos EU n.º 576/2013 e n.º 2016/429, estabelecendo que os requisitos de identificação de animais de companhia aplicáveis em Portugal são os das espécies referidas nesses anexos.
-NOTA: DL 82/2019 não implementa mecanismo de delegação de autoridade para alteração de anexos como previsto no Art. 22-24 do Regulamento EU 2023/0447.</t>
-        </is>
-      </c>
+          <t>Sem equivalência.</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr"/>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>PARCIAL - Anexos existem; falta delegação de autoridade para alteração dinâmica</t>
+          <t>Sem equivalência.</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>PARCIAL - Estrutura de anexos com parâmetros técnicos; falta delegação</t>
+          <t>Sem equivalência.</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>PARCIAL - ANEXO estruturado; falta mecanismo de atos delegados/execução</t>
-        </is>
-      </c>
-      <c r="N24" s="11" t="inlineStr">
-        <is>
-          <t>A legislação portuguesa possui estrutura de anexos contendo parâmetros técnicos equivalentes aos do Regulamento. Falta implementar: Mecanismo de delegação de autoridade à Comissão Europeia para adoção de atos delegados/execução, conforme Arts. 22-24 do Regulamento 2023/0447. Atualmente, qualquer alteração de anexos requer procedimento legislativo nacional (novo Decreto-Lei), não havendo procedimento expedito de atos delegados.</t>
-        </is>
-      </c>
+          <t>Sem equivalência.</t>
+        </is>
+      </c>
+      <c r="N24" s="11" t="inlineStr"/>
       <c r="O24" s="11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>sem equivalência</t>
         </is>
       </c>
       <c r="P24" s="11" t="inlineStr">
         <is>
-          <t>Estrutura de anexos presente mas sem mecanismo de delegação de autoridade para atos delegados/execução conforme Reg. EU.</t>
+          <t>.</t>
         </is>
       </c>
     </row>
@@ -3204,27 +3587,27 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Art.º 28.º do Regulamento 2023/0447</t>
+          <t>Art.º 28.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>1.	The power to adopt delegated acts is conferred on the Commission subject to the conditions laid down in this Article.
-2.	The power to adopt delegated acts referred to in Article 7(8), Article 8(3), Article 13(2) and Article 27 shall be conferred on the Commission for an indeterminate period of time from … [the date of entry into force of this Regulation].
-3.	The delegation of power referred to in Article 7(8), Article 8(3), Article 13(2) and Article 27may be revoked at any time by the European Parliament or by the Council. A decision to revoke shall put an end to the delegation of the power specified in that decision. It shall take effect the day following the publication of the decision in the Official Journal of the European Union or at a later date specified therein. It shall not affect the validity of any delegated acts already in force.
-4.	Before adopting a delegated act, the Commission shall consult experts designated by each Member State in accordance with the principles laid down in the Interinstitutional Agreement of 13 April 2016 on Better Law-Making.
-5.	As soon as it adopts a delegated act, the Commission shall notify it simultaneously to the European Parliament and to the Council.
-6.	A delegated act adopted pursuant to Article 7(8), Article 8(3), Article 13(2) or Article 27 shall enter into force only if no objection has been expressed either by the European Parliament or by the Council within a period of two months of notification of that act to the European Parliament and the Council or if, before the expiry of that period, the European Parliament and the Council have both informed the Commission that they will not object. That period shall be extended by two months at the initiative of the European Parliament or of the Council</t>
+          <t>The power to adopt delegated acts is conferred on the Commission subject to the conditions laid down in this Article.
+The power to adopt delegated acts referred to in Article 7(8), Article 8(3), Article 13(2) and Article 27 shall be conferred on the Commission for an indeterminate period of time from … [the date of entry into force of this Regulation].
+The delegation of power referred to in Article 7(8), Article 8(3), Article 13(2) and Article 27may be revoked at any time by the European Parliament or by the Council. A decision to revoke shall put an end to the delegation of the power specified in that decision. It shall take effect the day following the publication of the decision in the Official Journal of the European Union or at a later date specified therein. It shall not affect the validity of any delegated acts already in force.
+Before adopting a delegated act, the Commission shall consult experts designated by each Member State in accordance with the principles laid down in the Interinstitutional Agreement of 13 April 2016 on Better Law-Making.
+As soon as it adopts a delegated act, the Commission shall notify it simultaneously to the European Parliament and to the Council.
+A delegated act adopted pursuant to Article 7(8), Article 8(3), Article 13(2) or Article 27 shall enter into force only if no objection has been expressed either by the European Parliament or by the Council within a period of two months of notification of that act to the European Parliament and the Council or if, before the expiry of that period, the European Parliament and the Council have both informed the Commission that they will not object. That period shall be extended by two months at the initiative of the European Parliament or of the Council</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1 — O poder de adotar atos delegados é conferido à Comissão nas condições estabelecidas no presente artigo.
-2 — O poder de adotar atos delegados referido no artigo 7.º, n.º 8, no artigo 8.º-A, n.º 3, no artigo 13.º, n.º 2, e no artigo 27.º é conferido à Comissão por tempo indeterminado a partir de [data de entrada em vigor do presente regulamento].
-3 — A delegação de poderes referida no artigo 7.º, n.º 8, no artigo 8.º-A, n.º 3, no artigo 13.º, n.º 2, e no artigo 27.º pode ser revogada em qualquer momento pelo Parlamento Europeu ou pelo Conselho. A decisão de revogação põe termo à delegação dos poderes nela especificados. A decisão de revogação produz efeitos a partir do dia seguinte ao da sua publicação no Jornal Oficial da União Europeia ou de uma data posterior nela especificada. A decisão de revogação não afeta os atos delegados já em vigor.
-4 — Antes de adotar um ato delegado, a Comissão consulta os peritos designados por cada Estado-Membro de acordo com os princípios estabelecidos no Acordo Interinstitucional, de 13 de abril de 2016, sobre legislar melhor.
-5 — Assim que adotar um ato delegado, a Comissão notifica-o simultaneamente ao Parlamento Europeu e ao Conselho.
-6 — Os atos delegados adotados nos termos do artigo 7.º, n.º 8, do artigo 8.º-A, n.º 3, do artigo 13.º, n.º 2, ou do artigo 27.º só entram em vigor se não tiverem sido formuladas objeções pelo Parlamento Europeu ou pelo Conselho no prazo de dois meses a contar da notificação desse ato ao Parlamento Europeu e ao Conselho, ou se, antes do termo desse prazo, o Parlamento Europeu e o Conselho tiverem informado a Comissão de que não têm objeções a formular. O referido prazo é prorrogado por dois meses por iniciativa do Parlamento Europeu ou do Conselho.</t>
+          <t>O poder de adotar atos delegados é conferido à Comissão nas condições estabelecidas no presente artigo.
+O poder de adotar atos delegados referido no artigo 7.º, n.º 8, no artigo 8.º-A, n.º 3, no artigo 13.º, n.º 2, e no artigo 27.º é conferido à Comissão por tempo indeterminado a partir de [data de entrada em vigor do presente regulamento].
+A delegação de poderes referida no artigo 7.º, n.º 8, no artigo 8.º-A, n.º 3, no artigo 13.º, n.º 2, e no artigo 27.º pode ser revogada em qualquer momento pelo Parlamento Europeu ou pelo Conselho. A decisão de revogação põe termo à delegação dos poderes nela especificados. A decisão de revogação produz efeitos a partir do dia seguinte ao da sua publicação no Jornal Oficial da União Europeia ou de uma data posterior nela especificada. A decisão de revogação não afeta os atos delegados já em vigor.
+Antes de adotar um ato delegado, a Comissão consulta os peritos designados por cada Estado-Membro de acordo com os princípios estabelecidos no Acordo Interinstitucional, de 13 de abril de 2016, sobre legislar melhor.
+Assim que adotar um ato delegado, a Comissão notifica-o simultaneamente ao Parlamento Europeu e ao Conselho.
+Os atos delegados adotados nos termos do artigo 7.º, n.º 8, do artigo 8.º-A, n.º 3, do artigo 13.º, n.º 2, ou do artigo 27.º só entram em vigor se não tiverem sido formuladas objeções pelo Parlamento Europeu ou pelo Conselho no prazo de dois meses a contar da notificação desse ato ao Parlamento Europeu e ao Conselho, ou se, antes do termo desse prazo, o Parlamento Europeu e o Conselho tiverem informado a Comissão de que não têm objeções a formular. O referido prazo é prorrogado por dois meses por iniciativa do Parlamento Europeu ou do Conselho.</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -3232,49 +3615,38 @@
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="H25" s="6" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr"/>
+      <c r="K25" s="8" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="L25" s="9" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr">
+      <c r="M25" s="10" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="K25" s="8" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="L25" s="9" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="M25" s="10" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>Artigo processual do Regulamento europeu — sem correspondência em legislação portuguesa.</t>
+          <t>Artigo processual do Regulamento europeu — sem correspondência em legislação portuguesa.
+O regulamento principal fixa as regras de base, mas deixa alguns aspetos mais técnicos ou de pormenor para a Comissão completar mais tarde através de atos delegados</t>
         </is>
       </c>
       <c r="O25" s="11" t="inlineStr">
@@ -3282,11 +3654,7 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="P25" s="11" t="inlineStr">
-        <is>
-          <t>Artigo sobre procedimento de delegação de atos à Comissão Europeia.</t>
-        </is>
-      </c>
+      <c r="P25" s="11" t="inlineStr"/>
     </row>
     <row r="26" ht="120" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -3296,16 +3664,14 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Art.º 29.º do Regulamento 2023/0447</t>
+          <t>Art.º 29.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
           <t>1.	The Commission shall be assisted by the Standing Committee on Plants, Animals, Food and Feed established by Article 58(1) of Regulation (EC) No 178/2002. That Committee shall be a committee within the meaning of Regulation (EU) No 182/2011.
 2.	Where reference is made to this paragraph, Article 5 of Regulation (EU) No 182/2011 shall apply.
-Where the Committee delivers no opinion, the Commission shall not adopt the draft implementing act, and Article 5(4), third subparagraph, of Regulation (EU) No 182/2011 shall apply.
-CHAPTER VII
-STRICTER NATIONAL RULES AND FINAL PROVISIONS</t>
+Where the Committee delivers no opinion, the Commission shall not adopt the draft implementing act, and Article 5(4), third subparagraph, of Regulation (EU) No 182/2011 shall apply.</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -3320,85 +3686,65 @@
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="H26" s="6" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr"/>
+      <c r="K26" s="8" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="L26" s="9" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="J26" s="7" t="inlineStr">
+      <c r="M26" s="10" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="L26" s="9" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="M26" s="10" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="N26" s="11" t="inlineStr">
-        <is>
-          <t>Artigo processual do Regulamento europeu — sem correspondência em legislação portuguesa.</t>
-        </is>
-      </c>
+      <c r="N26" s="11" t="inlineStr"/>
       <c r="O26" s="11" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="P26" s="11" t="inlineStr">
-        <is>
-          <t>Artigo sobre procedimento de comité — assistência à Comissão Europeia.</t>
-        </is>
-      </c>
+          <t>Não - Artigo processual sobre procedimento de comité — assistência à Comissão Europeia.</t>
+        </is>
+      </c>
+      <c r="P26" s="11" t="inlineStr"/>
     </row>
     <row r="27" ht="120" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Medidas Nacionais Mais Rigorosas</t>
+          <t>Medidas Nacionais Mais Restritivas</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Art.º 30.º do Regulamento 2023/0447</t>
+          <t>Art.º 30.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>1.	This Regulation shall not prevent Member States from maintaining or adopting stricter national rules aimed at providing more extensive protection of the welfare of dogs and cats kept in establishments, and a greater traceability of dogs and cats, provided that those rules are not inconsistent with this Regulation and do not interfere with the proper functioning of the internal market.
-2.	Member States shall, by ... [two years after the date of entry into force of this Regulation], inform the Commission about any existing stricter national rules that they intend to maintain in accordance with paragraph 1. Thereafter, Member States shall inform the Commission about stricter national rules before their adoption, unless the Member States have already notified the draft national rules as a draft technical regulation under Article 5 of Directive (EU) 2015/1535 of the European Parliament and of the Council. The Commission shall bring them to the attention of the other Member States.
-3.	A Member State that has stricter national rules referred to in paragraph 1 shall not prohibit or impede the placing on the market within its territory of dogs and cats kept in another Member State on the grounds that the dogs and cats concerned have not been kept in accordance with its stricter national rules  .</t>
+          <t>This Regulation shall not prevent Member States from maintaining or adopting stricter national rules aimed at providing more extensive protection of the welfare of dogs and cats kept in establishments, and a greater traceability of dogs and cats, provided that those rules are not inconsistent with this Regulation and do not interfere with the proper functioning of the internal market.
+Member States shall, by ... [two years after the date of entry into force of this Regulation], inform the Commission about any existing stricter national rules that they intend to maintain in accordance with paragraph 1. Thereafter, Member States shall inform the Commission about stricter national rules before their adoption, unless the Member States have already notified the draft national rules as a draft technical regulation under Article 5 of Directive (EU) 2015/1535 of the European Parliament and of the Council. The Commission shall bring them to the attention of the other Member States.
+A Member State that has stricter national rules referred to in paragraph 1 shall not prohibit or impede the placing on the market within its territory of dogs and cats kept in another Member State on the grounds that the dogs and cats concerned have not been kept in accordance with its stricter national rules.</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1 — O presente regulamento não obsta a que os Estados-Membros mantenham disposições nacionais mais rigorosas que visem uma proteção mais ampla do bem-estar dos cães e gatos detidos em estabelecimentos e a rastreabilidade dos cães e gatos, desde que essas disposições não sejam incompatíveis com o presente regulamento e não interfiram com o bom funcionamento do mercado interno.
-1a — Os Estados-Membros devem informar a Comissão acerca de tais disposições nacionais existentes até [data de aplicação do presente regulamento] e devem informar a Comissão acerca de tais disposições nacionais novas antes da sua adoção, salvo se os Estados-Membros tiverem notificado os projetos de disposições nacionais em conformidade com a Diretiva (UE) 2015/1535. A Comissão transmite essas informações aos outros Estados-Membros.
-2 — Um Estado-Membro que tenha disposições nacionais mais rigorosas referidas no n.º 1 não pode proibir ou impedir a colocação no mercado, no seu território, de cães e gatos detidos noutro Estado-Membro com o fundamento de que os cães e gatos em causa não estiveram detidos em conformidade com as suas disposições nacionais mais rigorosas.</t>
+          <t>O presente regulamento não obsta a que os Estados-Membros mantenham disposições nacionais mais restritivas que visem uma proteção mais ampla do bem-estar dos cães e gatos detidos em estabelecimentos e a rastreabilidade dos cães e gatos, desde que essas disposições não sejam incompatíveis com o presente regulamento e não interfiram com o bom funcionamento do mercado interno.
+Os Estados-Membros devem informar a Comissão acerca de tais disposições nacionais existentes até [data de aplicação do presente regulamento] e devem informar a Comissão acerca de tais disposições nacionais novas antes da sua adoção, salvo se os Estados-Membros tiverem notificado os projetos de disposições nacionais em conformidade com a Diretiva (UE) 2015/1535. A Comissão transmite essas informações aos outros Estados-Membros.
+Um Estado-Membro que tenha disposições nacionais mais restritivas referidas no n.º 1 não pode proibir ou impedir a colocação no mercado, no seu território, de cães e gatos detidos noutro Estado-Membro com o fundamento de que os cães e gatos em causa não estiveram detidos em conformidade com as suas disposições nacionais mais rigorosas.</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -3406,61 +3752,41 @@
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr"/>
+      <c r="K27" s="8" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="L27" s="9" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="M27" s="10" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="K27" s="8" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="L27" s="9" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="M27" s="10" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="N27" s="11" t="inlineStr">
-        <is>
-          <t>Artigo sobre direitos dos Estados-Membros de manter ou adoptar medidas mais rigorosas.</t>
-        </is>
-      </c>
+      <c r="N27" s="11" t="inlineStr"/>
       <c r="O27" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P27" s="11" t="inlineStr">
-        <is>
-          <t>Artigo sobre liberdade de Estados-Membros para legislação mais rigorosa.</t>
-        </is>
-      </c>
+      <c r="P27" s="11" t="inlineStr"/>
     </row>
     <row r="28" ht="120" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -3470,75 +3796,63 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Art.º 31.º do Regulamento 2023/0447</t>
+          <t>Art.º 31.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
           <t>1.	On the basis of the reports received in accordance with Article 24 and any additional relevant information, the Commission shall publish, by ... [7 years from the date of entry into force of this Regulation] and thereafter at three-yearly intervals, a monitoring report on the welfare of dogs and cats placed on the market in the Union.
-2.	By … [14 years from the date of entry into force of this Regulation ] , the Commission shall carry out an evaluation of this Regulation  and present a report on the main findings to the European Parliament, the Council, the European Economic and Social Committee, and the Committee of the Regions. In that evaluation and report the Commission shall assess, in particular:
-(a)	the extent to which this Regulation has contributed to ensuring a high level of welfare for dogs and cats, improving their traceability, and reducing the illegal trade in them;
-(b)	the impact that this Regulation has had on operators of breeding and selling establishments and shelters, and of operators who place dogs and cats in foster homes, taking into account inter alia the administrative burden and compliance costs.
+2.	By … [14 years from the date of entry into force of this Regulation, the Commission shall carry out an evaluation of this Regulation and present a report on the main findings to the European Parliament, the Council, the European Economic and Social Committee, and the Committee of the Regions. In that evaluation and report the Commission shall assess, in particular:
+the extent to which this Regulation has contributed to ensuring a high level of welfare for dogs and cats, improving their traceability, and reducing the illegal trade in them;
+the impact that this Regulation has had on operators of breeding and selling establishments and shelters, and of operators who place dogs and cats in foster homes, taking into account inter alia the administrative burden and compliance costs.
 3.	For the purposes of the reporting referred to in paragraph 2, Member States shall provide the Commission with the information necessary for the preparation of its report.</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>1 — Com base nos relatórios recebidos em conformidade com o artigo 24.º e em informações adicionais pertinentes, a Comissão publica, até [7 anos após a data de entrada em vigor do presente regulamento] e, posteriormente, de três em três anos, um relatório de monitorização sobre o bem-estar dos cães e gatos colocados no mercado da União.
-2 — Até [14 anos a contar da data de entrada em vigor do presente regulamento], a Comissão procede a uma avaliação do presente regulamento e apresenta um relatório sobre as principais conclusões ao Parlamento Europeu, ao Conselho, ao Comité Económico e Social Europeu e ao Comité das Regiões. Em particular, a Comissão avalia:
-a) O grau em que o presente regulamento contribuiu para assegurar um elevado nível de bem-estar dos cães e gatos, melhorando a rastreabilidade, reduzindo o comércio ilegal;
-b) O impacto do presente regulamento nos operadores de estabelecimentos de criação e venda e de abrigos, e nos operadores que colocam cães e gatos em lares de acolhimento, incluindo o encargo administrativo e os custos de conformidade.
-3 — Para efeitos dos relatórios referidos no n.º 2, os Estados-Membros devem fornecer à Comissão as informações necessárias para a elaboração dos mesmos.</t>
+          <t>Com base nos relatórios recebidos em conformidade com o artigo 24.º e em informações adicionais pertinentes, a Comissão publica, até [7 anos após a data de entrada em vigor do presente regulamento] e, posteriormente, de três em três anos, um relatório de monitorização sobre o bem-estar dos cães e gatos colocados no mercado da União.
+Até [14 anos a contar da data de entrada em vigor do presente regulamento], a Comissão procede a uma avaliação do presente regulamento e apresenta um relatório sobre as principais conclusões ao Parlamento Europeu, ao Conselho, ao Comité Económico e Social Europeu e ao Comité das Regiões. Em particular, a Comissão avalia:
+O grau em que o presente regulamento contribuiu para assegurar um elevado nível de bem-estar dos cães e gatos, melhorando a rastreabilidade, reduzindo o comércio ilegal;
+O impacto do presente regulamento nos operadores de estabelecimentos de criação e venda e de abrigos, e nos operadores que colocam cães e gatos em lares de acolhimento, incluindo o encargo administrativo e os custos de conformidade.
+Para efeitos dos relatórios referidos no n.º 2, os Estados-Membros devem fornecer à Comissão as informações necessárias para a elaboração dos mesmos.</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
+          <t>Sem equivalência</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr"/>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
+          <t>Sem equivalência</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr"/>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
+          <t>Sem equivalência</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr"/>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Sem equivalência</t>
         </is>
       </c>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Sem equivalência</t>
         </is>
       </c>
       <c r="M28" s="10" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Sem equivalência</t>
         </is>
       </c>
       <c r="N28" s="11" t="inlineStr">
         <is>
-          <t>Artigo sobre obrigações de relatório e avaliação pela Comissão Europeia.</t>
+          <t>Artigo sobre obrigações de relatório e avaliação pela Comissão Europeia. Impõe que Estados-Membros contribuam para o relatório a produzir 14 anos após a entrada em vigor.</t>
         </is>
       </c>
       <c r="O28" s="11" t="inlineStr">
@@ -3546,11 +3860,7 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="P28" s="11" t="inlineStr">
-        <is>
-          <t>Artigo sobre relatórios de monitorização e avaliação do Regulamento.</t>
-        </is>
-      </c>
+      <c r="P28" s="11" t="inlineStr"/>
     </row>
     <row r="29" ht="120" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -3560,7 +3870,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Art.º 32.º do Regulamento 2023/0447</t>
+          <t>Art.º 32.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -3571,8 +3881,8 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1 — Os Estados-Membros estabelecem as regras relativas às sanções aplicáveis em caso de violação do disposto no presente regulamento, incluindo as resultantes do abandono de cães e gatos por parte de operadores, e tomam todas as medidas necessárias para garantir a sua aplicação. As sanções previstas devem ser efetivas, proporcionadas e dissuasivas.
-2 — Os Estados-Membros notificam a Comissão dessas regras e dessas medidas e também, sem demora, de qualquer alteração ulterior das mesmas.</t>
+          <t>Os Estados-Membros estabelecem as regras relativas às sanções aplicáveis em caso de violação do disposto no presente regulamento, incluindo as resultantes do abandono de cães e gatos por parte de operadores, e tomam todas as medidas necessárias para garantir a sua aplicação. As sanções previstas devem ser efetivas, proporcionadas e dissuasivas.
+Os Estados-Membros notificam a Comissão dessas regras e dessas medidas e também, sem demora, de qualquer alteração ulterior das mesmas.</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -3580,61 +3890,41 @@
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="H29" s="6" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="H29" s="6" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr"/>
+      <c r="K29" s="8" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="L29" s="9" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="M29" s="10" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="K29" s="8" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="L29" s="9" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="M29" s="10" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="N29" s="11" t="inlineStr">
-        <is>
-          <t>Artigo sobre responsabilidade dos Estados-Membros em estabelecer sanções por infração.</t>
-        </is>
-      </c>
+      <c r="N29" s="11" t="inlineStr"/>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="P29" s="11" t="inlineStr">
-        <is>
-          <t>Artigo sobre regime sancionatório a ser definido pelos Estados-Membros.</t>
-        </is>
-      </c>
+          <t>Responsabilidade dos Estados-Membros em estabelecer sanções e notificar a Comissão destas, e de qualquer alteração ulterior das mesmas.</t>
+        </is>
+      </c>
+      <c r="P29" s="11" t="inlineStr"/>
     </row>
     <row r="30" ht="120" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -3644,37 +3934,34 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Art.º 33.º do Regulamento 2023/0447</t>
+          <t>Art.º 33.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
           <t>This Regulation shall enter into force on the twentieth day following that of its publication in the Official Journal of the European Union.
 It shall apply from ... [two years from the date of entry into force of this Regulation]. However,
-(i)	Article 16 shall apply from … [three years from the date of entry into force of this Regulation];
-(ii)	 Article 21(3) and Article 23(1) shall apply from … [four years from entry into force of this Regulation];
-(iii)	Article 8(1) shall apply from 1 July 2036 and Article 8(2) shall apply from 1 July 2030;
-(iv)	Article 15, Article 21(3), second subparagraph, (4) and (5), Article 22(1), points (a),(b) and (c), Article 23(3) and (4), and Article 26(1), (2) and (3) shall apply from … [five years from the date of entry into force of this Regulation];
-(v)	Article 12(2) and (3) shall apply from … [seven years from the date of entry into force of this Regulation];
-(vi)	Article 10 shall apply from … [eight years from the date of entry into force of this Regulation]; and
-(vii)	Article 26(4) shall apply from … [10 years from the entry into force of the Regulation].
-This Regulation shall be binding in its entirety and directly applicable in all Member States.
-Done at …,
-For the European Parliament	For the Council
-The President	The President</t>
+Article 16 shall apply from … [three years from the date of entry into force of this Regulation];
+Article 21(3) and Article 23(1) shall apply from … [four years from entry into force of this Regulation];
+Article 8(1) shall apply from 1 July 2036 and Article 8(2) shall apply from 1 July 2030;
+Article 15, Article 21(3), second subparagraph, (4) and (5), Article 22(1), points (a),(b) and (c), Article 23(3) and (4), and Article 26(1), (2) and (3) shall apply from … [five years from the date of entry into force of this Regulation];
+Article 12(2) and (3) shall apply from … [seven years from the date of entry into force of this Regulation];
+Article 10 shall apply from … [eight years from the date of entry into force of this Regulation]; and
+Article 26(4) shall apply from … [10 years from the entry into force of the Regulation].
+This Regulation shall be binding in its entirety and directly applicable in all Member States.</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
           <t>O presente regulamento entra em vigor no vigésimo dia seguinte ao da sua publicação no Jornal Oficial da União Europeia.
 É aplicável a partir de … [dois anos após a data de entrada em vigor do presente Regulamento]. Todavia:
-(i)	o artigo 16.º é aplicável a partir de … [três anos após a data de entrada em vigor do presente Regulamento];
-(ii)	o artigo 21.º, n.º 3, e o artigo 23.º, n.º 1, são aplicáveis a partir de … [quatro anos após a entrada em vigor do presente Regulamento];
-(iii)	o artigo 8.º-A, n.º 1, é aplicável a partir de 1 de julho de 2036 e o artigo 8.º-A, n.º 2, é aplicável a partir de 1 de julho de 2030;
-(iv)	o artigo 15.º, o artigo 21.º, n.º 3, segundo parágrafo, n.ºs 4 e 5, o artigo 22.º, n.º 1, alíneas a), b) e c), o artigo 23.º, n.ºs 3 e 4, e o artigo 26.º, n.ºs 1, 2 e 3, são aplicáveis a partir de … [cinco anos após a data de entrada em vigor do presente Regulamento];
-(v)	o artigo 12.º, n.ºs 2 e 3, é aplicável a partir de … [sete anos após a data de entrada em vigor do presente Regulamento];
-(vi)	o artigo 10.º é aplicável a partir de … [oito anos após a data de entrada em vigor do presente Regulamento]; e
-(vii)	o artigo 26.º, n.º 4, é aplicável a partir de … [10 anos após a entrada em vigor do presente Regulamento].
+o artigo 16.º é aplicável a partir de … [três anos após a data de entrada em vigor do presente Regulamento];
+o artigo 21.º, n.º 3, e o artigo 23.º, n.º 1, são aplicáveis a partir de … [quatro anos após a entrada em vigor do presente Regulamento];
+o artigo 8.º-A, n.º 1, é aplicável a partir de 1 de julho de 2036 e o artigo 8.º-A, n.º 2, é aplicável a partir de 1 de julho de 2030;
+o artigo 15.º, o artigo 21.º, n.º 3, segundo parágrafo, n.ºs 4 e 5, o artigo 22.º, n.º 1, alíneas a), b) e c), o artigo 23.º, n.ºs 3 e 4, e o artigo 26.º, n.ºs 1, 2 e 3, são aplicáveis a partir de … [cinco anos após a data de entrada em vigor do presente Regulamento];
+o artigo 12.º, n.ºs 2 e 3, é aplicável a partir de … [sete anos após a data de entrada em vigor do presente Regulamento];
+o artigo 10.º é aplicável a partir de … [oito anos após a data de entrada em vigor do presente Regulamento]; e
+o artigo 26.º, n.º 4, é aplicável a partir de … [10 anos após a entrada em vigor do presente Regulamento].
 O presente regulamento é obrigatório em todos os seus elementos e diretamente aplicável em todos os Estados-Membros.</t>
         </is>
       </c>
@@ -3683,49 +3970,37 @@
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="H30" s="6" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr"/>
+      <c r="K30" s="8" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="L30" s="9" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="J30" s="7" t="inlineStr">
+      <c r="M30" s="10" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="K30" s="8" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="L30" s="9" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="M30" s="10" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
       <c r="N30" s="11" t="inlineStr">
         <is>
-          <t>Artigo sobre entrada em vigor e aplicação do Regulamento.</t>
+          <t>Entrada em vigor, períodos de aplicação escalonados e obrigatoriedade do Regulamento.</t>
         </is>
       </c>
       <c r="O30" s="11" t="inlineStr">
@@ -3733,11 +4008,7 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="P30" s="11" t="inlineStr">
-        <is>
-          <t>Artigo sobre entrada em vigor, períodos de aplicação escalonados e obrigatoriedade do Regulamento.</t>
-        </is>
-      </c>
+      <c r="P30" s="11" t="inlineStr"/>
     </row>
     <row r="31" ht="120" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
@@ -3747,27 +4018,28 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>ANEXO I, Ponto 1 do Regulamento 2023/0447</t>
+          <t>Annex I, Ponto 1 do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>1. Feeding and watering
-1.1 Dogs and cats shall be fed at least twice per day. Puppies and kittens shall be fed more frequently.
-1.2 These requirements shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
-1.3 Each puppy or kitten shall be fed with colostrum during at least the first two days of its life and thereafter with milk from its mother or a lactating bitch or queen. If this is not possible, because she is ill or is otherwise unable to feed her offspring or not sufficient, the puppy or kitten shall be fed with a milk replacer designed for puppies and kittens with such feeding frequency as instructed by the producer of the replacer or by a veterinarian.
-1.4 All unweaned puppies and kittens shall be fed enough milk, milk replacer or a combination thereof to steadily gain bodyweight.
-1.5 Weaning shall be performed with gradual introduction of firm feed, in a process not shorter than 7 days and shall not be completed before 6 weeks of age for puppies and kittens alike.</t>
+          <t>Requirements applicable to establishments
+Feeding and watering
+Dogs and cats shall be fed at least twice per day. Puppies and kittens shall be fed more frequently.
+However, those requirements shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
+Each puppy or kitten shall be fed with colostrum during at least the first two days of its life. Thereafter, it shall be fed with milk from its mother or a lactating bitch or queen. If that is not possible, because the mother is ill or is otherwise unable to feed her offspring or unable to provide sufficient milk, the puppy or kitten shall be fed with a milk replacer that has been designed for puppies and kittens. The frequency of such feeding shall comply with the manufacturer’s instructions or those of a veterinarian.
+All unweaned puppies and kittens shall be fed enough milk, milk replacer or a combination of both, to allow them to gain bodyweight steadily.
+Weaning shall be performed by the gradual introduction of solid feed over a period that is not shorter than seven days and shall not be completed before the age of six weeks for puppies and kittens alike.</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>1. Alimentação e abeberamento
-1.1 Os cães e gatos devem ser alimentados pelo menos duas vezes por dia. Os filhotes de cão e gato devem ser alimentados com maior frequência.
-1.2 Estes requisitos não se aplicam aos cães pastores de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para guarda ou treino.
-1.3 Cada filhote de cão ou gato deve ser alimentado com colostro durante pelo menos os primeiros dois dias de vida e depois com leite da mãe ou de uma cadela ou gata lactante. Se tal não for possível, porque está doente ou incapaz de alimentar a ninhada ou se o leite for insuficiente, o filhote deve ser alimentado com um substituto de leite concebido para filhotes, com a frequência de alimentação instruída pelo produtor do substituto ou por um veterinário.
-1.4 Todos os filhotes de cão e gato ainda em aleitamento devem ser alimentados com leite, substituto de leite ou uma combinação dos dois, em quantidade suficiente para ganhar peso corporal de forma constante.
-1.5 O desmame deve ser realizado com introdução gradual de alimentos sólidos, num processo que não seja inferior a 7 dias e não deve ser concluído antes dos 6 semanas de idade para filhotes de cão e gato.</t>
+          <t>Alimentação e abeberamento
+Os cães e gatos devem ser alimentados, pelo menos, duas vezes por dia. Os cachorros e gatinhos devem ser alimentados com maior frequência. 
+No entanto, estes requisitos não se aplicam aos cães de proteção de gado mantidos em estabelecimentos de criação durante os períodos em que esses cães sejam utilizados para fins de guarda ou de treino.
+Cada cachorro ou gatinho deve ser alimentado com colostro, pelo menos, durante os dois primeiros dias de vida. Posteriormente, deve ser alimentado com leite da progenitora ou de uma cadela ou gata lactante. Se tal não for possível, por a progenitora estar doente ou estar de outro modo impossibilitada de alimentar a sua ninhada ou de fornecer leite em quantidade suficiente, o cachorro ou gatinho deve ser alimentado com um sucedâneo de leite concebido para cachorros e gatinhos. A frequência dessa alimentação deve respeitar as instruções do fabricante ou de um médico veterinário.
+Todos os cachorros e gatinhos não desmamados devem receber leite, sucedâneo de leite ou uma combinação de ambos em quantidade suficiente para lhes permitir aumentar de peso de forma constante
+O desmame deve ser efetuado através da introdução gradual de alimentos sólidos durante um período não inferior a sete dias e não deve estar concluído antes das seis semanas de idade, tanto para os cachorros como para os gatinhos.</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -3778,12 +4050,14 @@
       <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Artigo 33.º - Alimentação
-1 - Deve existir um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades fisiológicas, nutricionais e metabólicas dos cães e gatos, consoante a edad, raça, categoria, nível de atividade e estado de saúde.
-2 - Os animais devem receber alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável.
-3 - As refeições devem ser variadas, sendo distribuídas segundo a rotina que mais se adequar à espécie.
-4 - Os alimentos devem ser preparados e armazenados de acordo com padrões estritos de higiene, em locais secos, limpos, livres de agentes patogénicos e de produtos tóxicos.
-5 – Sempre que se justifique, devem existir aparelhos de frio para uma eficiente conservação dos alimentos.
-6 - Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.</t>
+Deve existir um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades fisiológicas, nutricionais e metabólicas dos cães e gatos, consoante a idade, raça, categoria, nível de atividade e estado de saúde.
+Os animais devem receber alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável.
+As refeições devem ser variadas, sendo distribuídas segundo a rotina que mais se adequar à espécie.
+Os alimentos devem ser preparados e armazenados de acordo com padrões estritos de higiene, em locais secos, limpos, livres de agentes patogénicos e de produtos tóxicos.
+Sempre que se justifique, devem existir aparelhos de frio para uma eficiente conservação dos alimentos.
+Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.
+Art.º 70.º - Reprodução de cães e gatos
+5 - As crias não podem ser separadas da progenitora antes da décima semana de idade, no caso dos cães, e antes da décima segunda semana de idade, no caso dos gatos, salvaguardado um período de desmame gradual.</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
@@ -3793,21 +4067,19 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Artigo 18.º - Instalações
-n.º 1 - Os alojamentos que se destinem à reprodução, criação, manutenção ou venda de animais de companhia, devem possuir instalações individualizadas destinadas à armazenagem de alimentos e equipamento limpo e à lavagem e recolha de material.
-Artigo 46.º - Alimentação e abeberamento
-n.º 1 - A alimentação dos animais de companhia, nos locais de criação, manutenção e venda bem como nos centros de recolha e instalações de hospedagem, deve obedecer a um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies e dos indivíduos, de acordo com a fase de evolução fisiológica em que se encontram, nomeadamente idade, sexo, fêmeas prenhes ou em fase de lactação.
-n.º 2 - As refeições devem ainda ser variadas, sendo distribuídas segundo a rotina que mais se adequar à espécie.
-n.º 3 - O número, formato e distribuição de comedouros e bebedouros deve ser tal que permita aos animais satisfazerem as suas necessidades sem que haja competição excessiva dentro do grupo.
-n.º 4 - Os alimentos devem ser preparados e armazenados de acordo com padrões estritos de higiene, em locais secos, limpos, livres de agentes patogénicos e de produtos tóxicos e, no caso dos alimentos compostos devem, ainda, ser armazenados sobre estrados de madeira ou prateleiras.
-n.º 5 - Devem existir aparelhos de frio para uma eficiente conservação dos alimentos.
-n.º 6 - Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.
-n.º 7 - É proibido alimentar animais com restos de comida, produtos de pastelaria e desperdícios da indústria alimentar e de restauração.</t>
+          <t>Artigo 46.º - Alimentação e abeberamento
+A alimentação dos animais de companhia, nos locais de criação, manutenção e venda bem como nos centros de recolha e instalações de hospedagem, deve obedecer a um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies e dos indivíduos, de acordo com a fase de evolução fisiológica em que se encontram, nomeadamente idade, sexo, fêmeas prenhes ou em fase de lactação.
+As refeições devem ainda ser variadas, sendo distribuídas segundo a rotina que mais se adequar à espécie.
+O número, formato e distribuição de comedouros e bebedouros deve ser tal que permita aos animais satisfazerem as suas necessidades sem que haja competição excessiva dentro do grupo.
+Os alimentos devem ser preparados e armazenados de acordo com padrões estritos de higiene, em locais secos, limpos, livres de agentes patogénicos e de produtos tóxicos e, no caso dos alimentos compostos devem, ainda, ser armazenados sobre estrados de madeira ou prateleiras.
+Devem existir aparelhos de frio para uma eficiente conservação dos alimentos.
+Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.
+É proibido alimentar animais com restos de comida, produtos de pastelaria e desperdícios da indústria alimentar e de restauração.</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>Art.º 12.º, Art.º 49.º do DL n.º 276-2001, de 17 de outubro; Art.º 5.º, n.º 5 da Portaria n.º 146/2017</t>
+          <t>Art.º 12.º, Art.º 49.º do DL n.º 276-2001, de 17 de outubro;</t>
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr">
@@ -3819,35 +4091,25 @@
 4 - Os alimentos devem ser preparados e armazenados de acordo com padrões estritos de higiene, em locais secos, limpos, livres de agentes patogénicos e de produtos tóxicos e, no caso dos alimentos compostos, devem, ainda, ser armazenados sobre estrados de madeira ou prateleiras.
 5 - Devem existir aparelhos de frio para uma eficiente conservação dos alimentos.
 6 - Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.
-[dim]
-Artigo 49.º — Alimentação e abeberamento
-Deve ser mantida comida suficiente e de boa qualidade e água potável, a administrar de acordo com a prescrição do médico veterinário.
-[/dim]</t>
-        </is>
-      </c>
-      <c r="K31" s="8" t="inlineStr">
-        <is>
-          <t>PARCIAL CONVERGÊNCIA
-DL 276/2001 (Art. 12.º) cobre: programa alimentar, padrões de higiene, água potável, variação de refeições, equipamentos (comedouros, bebedouros, frio).
-FALTAM especificidades do Regulamento: frequência mínima (2x/dia para cães e gatos), colostro (mínimo 2 dias), leite materno, desmame gradual (mínimo 7 dias, não antes 6 semanas), disposições específicas para filhotes.</t>
-        </is>
-      </c>
+Normas para a hospedagem com fins médico-veterinários – Artigo 49.º — Alimentação e abeberamento
+Deve ser mantida comida suficiente e de boa qualidade e água potável, a administrar de acordo com a prescrição do médico veterinário.</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="inlineStr"/>
       <c r="L31" s="9" t="inlineStr">
         <is>
-          <t>PARCIAL CONVERGÊNCIA
-O Código do Animal (DL 214/2013, Art. 46) cobre: programa alimentar, padrões de higiene, água potável, proibições de restos.
-FALTAM especificidades do Regulamento: frequência mínima (2x/dia), colostro (mínimo 2 dias), leite materno, desmame gradual (mínimo 7 dias, não antes 6 semanas).</t>
+          <t>Sem detalhes de armazenamento ou alojamento</t>
         </is>
       </c>
       <c r="M31" s="10" t="inlineStr">
         <is>
-          <t>CONVERGÊNCIA COMPLETA
-RGBEAC (Art. 33) espelha integralmente os requisitos do Regulamento: programa definido, frequências, padrões de higiene, água potável, refrigeração, alimentos saudáveis e adequados.</t>
+          <t>Frequências, padrões de higiene, água potável, refrigeração, alimentos saudáveis e adequados.</t>
         </is>
       </c>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>ANNEX I, Ponto 1 do Regulamento especifica requisitos técnicos mínimos: frequência 2x/dia, colostro (2 dias), leite materno, desmame gradual (7 dias). DL 276/2001 (Art. 12.º) cobre aspetos gerais (programa, higiene, água, equipamentos) mas não detalha frequências, colostro, desmame. Código do Animal (Art. 46) é convergente com DL 276/2001. RGBEAC já incorpora todas as especificidades. Recomenda-se alteração do DL 276/2001 e/ou Código do Animal para integrar especificidades técnicas do Regulamento (frequências, colostro, desmame).</t>
+          <t>FALTAM especificidades do Regulamento: frequência mínima (2x/dia para cães e gatos), colostro (mínimo 2 dias), leite materno, desmame gradual (mínimo 7 dias, não antes 6 semanas), disposições específicas para filhotes.
+Cão de guarda de gado = «Cão de proteção de gado contra ataques de lobo» na nossa legislação, conforme al. c) do n.º 2 do art.º 2.º do Decreto-Lei n.º 54/2016, de 25 de Agosto (desenvolvimento dos princípios da proteção e conservação do lobo-ibérico).</t>
         </is>
       </c>
       <c r="O31" s="11" t="inlineStr">
@@ -3855,11 +4117,7 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="P31" s="11" t="inlineStr">
-        <is>
-          <t>ANNEX I, Ponto 1 estabelece requisitos técnicos de alimentação. DL 276/2001 (Art. 12.º) e Código do Animal (Art. 46) cobrem aspetos gerais. RGBEAC já implementa integralmente as especificidades do Regulamento. Recomenda-se harmonização definitiva através de alteração legislativa para integrar: (i) frequência mínima 2x/dia; (ii) colostro (mínimo 2 dias); (iii) desmame gradual (mínimo 7 dias, não antes 6 semanas).</t>
-        </is>
-      </c>
+      <c r="P31" s="11" t="inlineStr"/>
     </row>
     <row r="32" ht="120" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -3869,23 +4127,36 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>ANEXO I, Ponto 2 do Regulamento 2023/0447</t>
+          <t>ANEXO I, Ponto 2 do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>2. Housing
+          <t>2.Housing
 2.1 Temperature
 In breeding establishments the temperature shall be maintained within a range of:
-— 22 to 28°C in whelping areas for the first 10 days of puppies' lives;
-— 18 to 27°C in kittening areas for the first 21 days of kittens' lives.
+22 to 28°C in whelping areas for the first 10 days of puppies' lives;
+18 to 27°C in kittening areas for the first 21 days of kittens' lives.
 2.2 Lighting
 Dogs and cats shall be exposed to light for at least 7 hours per day. Artificial light shall be broad spectrum or full spectrum with a frequency of at least 80 Hertz.
 Dogs and cats shall have the possibility to be without artificial lights for at least 8 hours per day.
 2.3 Space allowances
-2.3.1 [Details on minimum space by dog/cat size and age]
-2.3.2 Whelping and kittening areas shall be designed to permit the mother to move away from her offspring.
-2.3.3a In case of breeding and selling establishments, the following minimum space allowances for dogs and cats shall apply, which shall be calculated based on the total permanently accessible area for the dogs or cats.</t>
+2.3.1 Whelping and kittening areas shall be designed to permit the mother to move away from her offspring.
+2.3.2 In case of breeding and selling establishments, the following minimum space allowances for dogs and cats shall apply, which shall be calculated based on the total permanently accessible area for the dogs or cats.
+2.3.3 
+Espaço para cães com ou sem crias
+Altura do var (cm): 
+&lt; 30 → Área mínima: 4 m², Altura: 200 cm
+30-40 → 5 m², 200 cm
+40-60 → 8 m², 200 cm
+60-70 → 10 m², 200 cm
+&gt;70 → 10 m², 200 cm
+Cada cão adicional: 3/3.5/4/5/6 m² respetivamente.
+Espaço para gatos com ou sem crias
+Um gato: 3 m² solo, 200 cm altura
+Cada adicional: 2 m².
+* No caso de cães de raça pura, as alturas do var podem ser calculadas com base no cercado individual; mantêm-se apenas as colunas para área de superfície mínima para a altura. 
+** A superfície com enriquecimento para gatos não é incluída na área mínima do solo.</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -3899,9 +4170,22 @@
 Cães e gatos devem ser expostos a luz durante pelo menos 7 horas por dia. A luz artificial deve ser de espectro amplo ou espectro completo com uma frequência de pelo menos 80 Hz.
 Cães e gatos devem ter a possibilidade de estar sem luzes artificiais durante pelo menos 8 horas por dia.
 2.3 Espaço adequado
-2.3.1 [Detalhes sobre espaço mínimo por tamanho e idade de cão/gato]
-2.3.2 As áreas de parto de cães e gatos devem ser projetadas para permitir que a mãe se afaste da sua prole.
-2.3.3a No caso de estabelecimentos de criação e venda, as seguintes alocações mínimas de espaço para cães e gatos devem ser aplicadas, que devem ser calculadas com base na área total permanentemente acessível para os cães ou gatos.</t>
+2.3.1 As áreas de parto devem ser concebidas de modo a permitir que a progenitora se afaste da sua prole.
+2.3.2 No caso dos estabelecimentos de criação e de venda, aplicam-se as seguintes superfícies mínimas para cães e gatos, as quais devem ser calculadas com base na área total permanentemente acessível aos cães ou gatos.
+2.3.3 
+Espaço para cães com ou sem crias
+Altura do var (cm): 
+&lt; 30 → Área mínima: 4 m², Altura: 200 cm
+30-40 → 5 m², 200 cm
+40-60 → 8 m², 200 cm
+60-70 → 10 m², 200 cm
+&gt;70 → 10 m², 200 cm
+Cada cão adicional: 3/3.5/4/5/6 m² respetivamente.
+Espaço para gatos com ou sem crias
+Um gato: 3 m² solo, 200 cm altura
+Cada adicional: 2 m².
+* No caso de cães de raça pura, as alturas do var podem ser calculadas com base no cercado individual; mantêm-se apenas as colunas para área de superfície mínima para a altura. 
+** A superfície com enriquecimento para gatos não é incluída na área mínima do solo.</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -3909,81 +4193,33 @@
           <t>Sem equivalência específica</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>Sem equivalência identificada no @RGBEAC para os requisitos técnicos específicos de temperatura, iluminação e espaço do ANNEX I, Ponto 2 do Regulamento.</t>
-        </is>
-      </c>
+      <c r="F32" s="5" t="inlineStr"/>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Art.º 8.º, Art.º 9.º do Código do Animal (DL 214/2013)</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>Artigo 8.º - Condições dos alojamentos
-1 - Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
-a) A prática de exercício físico adequado;
-b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
-2 - Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.
-3 - As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar.
-4 - As estruturas físicas das instalações, todo o equipamento nelas introduzido e a vegetação não podem representar nenhum tipo de ameaça ao bem-estar dos animais, designadamente não podem possuir objetos ou equipamentos perigosos para os animais.
-5 - As instalações devem ser equipadas de acordo com as necessidades específicas dos animais que albergam, com materiais e equipamento que estimulem a expressão do repertório de comportamentos naturais, nomeadamente material para substrato, cama ou ninhos, ramos, buracos, locais para banhos e outros quaisquer adequados ao fim em vista.
-Artigo 9.º - Fatores ambientais
-1 - A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam.
-2 - Os fatores ambientais referidos no número anterior devem ser adequados às necessidades específicas de animais quando em fase reprodutiva, recém-nascidos ou doentes.
-3 - A luz deve ser de preferência natural, mas quando a luz artificial for imprescindível esta deve ser o mais próxima possível do espetro da luz solar e deve respeitar o fotoperíodo natural do local onde o animal está instalado.
-4 - As instalações devem permitir uma adequada inspeção dos animais, devendo ainda existir equipamento alternativo, nomeadamente focos de luz, para o caso de falência do equipamento central.
-5 - Os tanques ou aquários devem possuir água de qualidade adequada aos animais que a utilizem, nomeadamente tratada por produtos ou substâncias que não prejudiquem a sua saúde.
-6 - As instalações devem dispor de abrigos para que os animais se protejam de condições climáticas adversas.</t>
-        </is>
-      </c>
+          <t>Verificar Anexo</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr"/>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>Art.º 8.º, Art.º 9.º do DL n.º 276-2001; Art.º 10.º do DL n.º 276-2001 (transporte)</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>Artigo 8.º - Condições dos alojamentos
-1 - Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
-a) A prática de exercício físico adequado;
-b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
-2 - Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.
-3 - As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar.
-4 - As estruturas físicas das instalações, todo o equipamento nelas introduzido e a vegetação não podem representar nenhum tipo de ameaça ao bem-estar dos animais, designadamente não podem possuir objetos ou equipamentos perigosos para os animais.
-5 - As instalações devem ser equipadas de acordo com as necessidades específicas dos animais que albergam, com materiais e equipamento que estimulem a expressão do repertório de comportamentos naturais, nomeadamente material para substrato, cama ou ninhos, ramos, buracos, locais para banhos e outros quaisquer adequados ao fim em vista.
-Artigo 9.º - Fatores ambientais
-1 - A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam.
-2 - Os fatores ambientais referidos no número anterior devem ser adequados às necessidades específicas de animais quando em fase reprodutiva, recém-nascidos ou doentes.
-3 - A luz deve ser de preferência natural, mas quando a luz artificial for imprescindível esta deve ser o mais próxima possível do espetro da luz solar e deve respeitar o fotoperíodo natural do local onde o animal está instalado.
-4 - As instalações devem permitir uma adequada inspeção dos animais, devendo ainda existir equipamento alternativo, nomeadamente focos de luz, para o caso de falência do equipamento central.
-5 - Os tanques ou aquários devem possuir água de qualidade adequada aos animais que a utilizem, nomeadamente tratada por produtos ou substâncias que não prejudiquem a sua saúde.
-6 - As instalações devem dispor de abrigos para que os animais se protejam de condições climáticas adversas.</t>
-        </is>
-      </c>
+          <t>Anexo ao DL n.º 260/2012</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr"/>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>PARCIAL CONVERGÊNCIA
-DL 276/2001 (Arts. 8.º e 9.º) cobrem: espaço adequado, estruturas seguras, fatores ambientais (temperatura, ventilação, luz), abrigos para condições adversas.
-FALTAM especificidades do Regulamento: temperatura exata (22-28°C para parto de cães; 18-27°C para parto de gatos), iluminação mínima (7 horas luz, 8 horas sem luz, espectro 80 Hz), espaço mínimo quantificado, áreas de parto separadas.</t>
+          <t>FALTAM especificidades do Regulamento: temperatura exata (22-28°C para parto de cães; 18-27°C para parto de gatos), iluminação mínima (7 horas luz, 8 horas sem luz, espectro 80 Hz), espaço mínimo quantificado, áreas de parto separadas.</t>
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr">
         <is>
-          <t>PARCIAL CONVERGÊNCIA
-Código do Animal (Arts. 8.º e 9.º) equivalentes ao DL 276/2001 mas também faltam: temperatura específica, iluminação quantificada (7h luz/80Hz, 8h sem luz), espaço mínimo por tamanho/idade.</t>
-        </is>
-      </c>
-      <c r="M32" s="10" t="inlineStr">
-        <is>
-          <t>SEM EQUIVALÊNCIA ESPECÍFICA
-Não foi identificada correspondência específica no @RGBEAC para os requisitos técnicos detalhados de temperatura, iluminação e espaço do ANNEX I, Ponto 2 do Regulamento.</t>
-        </is>
-      </c>
+          <t>Faltam: temperatura específica, iluminação quantificada (7h luz/80Hz, 8h sem luz), espaço mínimo por tamanho/idade.</t>
+        </is>
+      </c>
+      <c r="M32" s="10" t="inlineStr"/>
       <c r="N32" s="11" t="inlineStr">
         <is>
-          <t>ANNEX I, Ponto 2 do Regulamento especifica requisitos técnicos detalhados: temperatura por fase (parto de cães 22-28°C; gatos 18-27°C), iluminação (7h luz + 80Hz, 8h sem luz), espaço mínimo quantificado, áreas de parto separadas. DL 276/2001 cobre conceitos gerais mas não detalha temperaturas, frequências de luz ou espaço mínimo. Recomenda-se alteração do DL 276/2001 para integrar parâmetros técnicos específicos do Regulamento.</t>
+          <t>ANNEX I, Ponto 2 do Regulamento especifica requisitos técnicos detalhados: temperatura por fase (parto de cães 22-28°C; gatos 18-27°C), iluminação (7h luz + 80Hz, 8h sem luz), espaço mínimo quantificado, áreas de parto separadas.</t>
         </is>
       </c>
       <c r="O32" s="11" t="inlineStr">
@@ -3991,11 +4227,7 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="P32" s="11" t="inlineStr">
-        <is>
-          <t>ANNEX I, Ponto 2 estabelece requisitos técnicos de alojamento. DL 276/2001 (Arts. 8.º e 9.º) cobrem aspetos gerais. RGBEAC já implementa integralmente as especificidades do Regulamento. Recomenda-se harmonização definitiva através de alteração legislativa para integrar: (i) temperatura exata (22-28°C parto cães; 18-27°C parto gatos); (ii) iluminação mínima (7h luz + 80Hz, 8h sem luz); (iii) espaço mínimo quantificado por tamanho/idade.</t>
-        </is>
-      </c>
+      <c r="P32" s="11" t="inlineStr"/>
     </row>
     <row r="33" ht="120" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
@@ -4005,105 +4237,73 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>ANEXO I, Ponto 3 do Regulamento 2023/0447</t>
+          <t>ANEXO I, Ponto 3 do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>3. Health
-3.1 Queens shall only be bred if their age is at least 10 months.
-3.2 Bitches shall only be bred as of their second oestrus.
-3.3 A bitch or queen shall not deliver more than 3 litters within a period of 2 years.
-3.4 For bitches and queens that have delivered 3 litters, including stillborns within a period of 2 years, there shall be a recuperation period of at least 1 year.
-3.4a Any bitch or queen that underwent two cesarean sections shall not be used for breeding.
-3.4b Before any bitch aged 8 years or more and any queen aged 6 years or more, is used for breeding, it must have been physically examined by a veterinarian who confirms in writing that, at the time of the examination, there are no counter-indications to pregnancy. The operator shall keep the written confirmation referred to in point 3.4.b for a period of at least 3 years.</t>
+          <t>Health
+Queens shall only be bred if their age is at least 10 months.
+Bitches shall only be bred as of their second oestrus.
+A bitch or queen shall not deliver more than 3 litters within a period of 2 years.
+For bitches and queens that have delivered 3 litters, including stillborns within a period of 2 years, there shall be a recuperation period of at least 1 year.
+Any bitch or queen that underwent two cesarean sections shall not be used for breeding.
+Before any bitch aged 8 years or more and any queen aged 6 years or more, is used for breeding, it must have been physically examined by a veterinarian who confirms in writing that, at the time of the examination, there are no counter-indications to pregnancy. 
+The operator shall keep the written confirmation referred to in point 3.4.b for a period of at least 3 years.</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3. Saúde Reprodutiva
-3.1 As gatas só podem reproduzir se tiverem uma idade mínima de 10 meses.
-3.2 As cadelas só podem reproduzir a partir do segundo ciclo estral.
-3.3 Uma cadela ou gata não deve ter mais de 3 ninhadas num período de 2 anos.
-3.4 Para cadelas e gatas que tenham tido 3 ninhadas, incluindo natimortos, num período de 2 anos, deve haver um período de recuperação de pelo menos 1 ano.
-3.4a Qualquer cadela ou gata que tenha sido submetida a duas cesarianas não deve ser usada para reprodução.
-3.4b Antes de qualquer cadela com 8 ou mais anos e qualquer gata com 6 ou mais anos ser usada para reprodução, deve ter sido submetida a exame físico por médico veterinário que confirme por escrito que, na altura do exame, não existem contraindicações para a gravidez. O operador deve manter a confirmação escrita referida no ponto 3.4.b por um período de pelo menos 3 anos.</t>
+          <t>Saúde
+As gatas só devem ser utilizadas para reprodução se tiverem, pelo menos, 10 meses de idade.
+As cadelas só devem ser utilizadas para reprodução a partir do seu segundo estro.
+Uma cadela ou gata não deve ter mais de 3 ninhadas num período de 2 anos.
+No caso de cadelas e gatas que tenham tido 3 ninhadas num período de 2 anos, incluindo nascimortos, deve ser respeitado um período de recuperação de, pelo menos, 1 ano.
+Qualquer cadela ou gata que tenha sido submetida a duas cesarianas não pode ser utilizada para reprodução.
+Antes de qualquer cadela com 8 ou mais anos de idade e de qualquer gata com 6 ou mais anos de idade serem utilizadas para reprodução, devem ser submetidas a um exame físico por um médico veterinário que confirme, por escrito, que, à data do exame, não existem contraindicações para a gestação.
+O operador deve conservar a confirmação escrita referida no ponto 3.4.b por um período de, pelo menos, 3 anos.</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Arts. 70.º-73.º do RGBEAC (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Artigo 70.º - Reprodução de cães e gatos
-1 - Os cães reprodutores devem cumprir as seguintes exigências: [...]
-2 - As cadelas podem reproduzir entre os dezoito meses e os seis anos de idade, até ao limite de quatro ninhadas com um intervalo mínimo de doze meses entre cada ninhada.
-3 - As gatas podem reproduzir entre os doze meses e os seis anos de idade, até ao limite de quatro ninhadas com um intervalo mínimo de doze meses entre cada ninhada.
-10 - As cadelas submetidas a duas cesarianas não podem ser utilizadas para reprodução.
-12 - As gatas submetidas a duas cesarianas não podem ser utilizadas para reprodução.
-[Ver artigos 71.º-73.º para disposições complementares sobre avaliação de saúde, testes genéticos e destino de reprodutores]</t>
-        </is>
-      </c>
+          <t>Ver análise do art.º 8º do @regulamento</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr"/>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Art.º 8.º do Código do Animal (DL 214/2013) + Anexo I</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>Artigo 8.º - Reprodução
-1 - Os operadores devem assegurar que:
-[...]
-2 - Os animais só devem ser utilizados na reprodução depois de atingida a maturidade reprodutiva para a espécie e raça devendo, no caso dos cães e gatos, seguir os parâmetros referidos no anexo I ao presente diploma, do qual faz parte integrante, não sendo autorizado, no caso das fêmeas, o acasalamento em cios sucessivos.
-[ANEXO I] Raças pequeno e médio porte – 3.º cio; Raças grande porte – 2 anos. Ninhadas: Cadelas não mais de 2 ninhadas em 2 anos; Gatas não mais de 3 ninhadas em 2 anos (recomendação, com exceção veterinária).</t>
-        </is>
-      </c>
+          <t>Ver análise do art.º 8º do @regulamento</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr"/>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>Art.º 8.º e Anexo do DL n.º 276-2001</t>
-        </is>
-      </c>
-      <c r="J33" s="7" t="inlineStr">
-        <is>
-          <t>[DL 276/2001 não contém artigos específicos sobre idade mínima para reprodução, frequência máxima de ninhadas, período de recuperação, proibição de cesarianas ou avaliação veterinária de reprodutores idosos]
-Nota: O DL 276/2001 menciona genericamente a necessidade de cumprir 'condições de saúde' e 'bem-estar', mas não detalha requisitos específicos de reprodução como o faz o Regulamento.</t>
-        </is>
-      </c>
+          <t>Ver análise do art.º 8º do @regulamento</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr"/>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>DIVERGÊNCIA TOTAL/PARCIAL
-DL 276/2001 não contém disposições específicas sobre: (i) idade mínima para reprodução (cadelas/gatas); (ii) número máximo de ninhadas por período; (iii) período obrigatório de recuperação; (iv) proibição de 2 cesarianas; (v) avaliação veterinária obrigatória para reprodutores idosos. Legislação é omissa em matéria de Health reprodutivo.</t>
+          <t>Ver análise do art.º 8º do @regulamento</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
-          <t>PARCIAL CONVERGÊNCIA
-Código do Animal estabelece idades mínimas (3º cio pequenas/médias; 2 anos grandes) e frequência máxima de ninhadas, mas: (i) critérios fisiológicos diferem (cio vs. estro); (ii) sem período de recuperação obrigatório após limite; (iii) sem proibição expressa de 2 cesarianas; (iv) sem avaliação veterinária obrigatória para reprodutores idosos. Mais restritivo que Regulamento em idades mínimas, menos em frequência.</t>
+          <t>Ver análise do art.º 8º do @regulamento</t>
         </is>
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
-          <t>PARCIAL CONVERGÊNCIA COM DIVERGÊNCIAS
-RGBEAC implementa a maioria dos requisitos mas com diferenças críticas: (i) idade mínima cadelas 18 meses (vs. 2º estro); (ii) idade máxima 6 anos (vs. sem máximo no Regulamento); (iii) frequência máxima 4 ninhadas/4 anos (vs. 3 ninhadas/2 anos); (iv) sem período de recuperação obrigatório; (v) proíbe 2 cesarianas (alinhado); (vi) sem avaliação veterinária para &gt;8 anos (RGBEAC proíbe a partir dos 6 anos). Mais restritivo em idades máximas, menos em frequência temporal.</t>
-        </is>
-      </c>
-      <c r="N33" s="11" t="inlineStr">
-        <is>
-          <t>ANNEX I, Ponto 3 (Health) estabelece cinco requisitos essenciais: (i) idade mínima (rainhas 10 meses, cadelas 2º estro); (ii) máximo 3 ninhadas em 2 anos; (iii) período de recuperação 1 ano após limite; (iv) proibição de 2 cesarianas; (v) avaliação veterinária ≥8 anos (cadelas) / ≥6 anos (gatas). Legislação nacional carece de disposições específicas ou é significativamente divergente. Recomenda-se alteração fundamental para integrar todos os cinco requisitos, com atenção especial à frequência de ninhadas e período de recuperação, inexistentes na legislação atual.</t>
-        </is>
-      </c>
+          <t>Ver análise do art.º 8º do @regulamento</t>
+        </is>
+      </c>
+      <c r="N33" s="11" t="inlineStr"/>
       <c r="O33" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P33" s="11" t="inlineStr">
-        <is>
-          <t>ANNEX I, Ponto 3 estabelece requisitos técnicos obrigatórios de saúde reprodutiva. Legislação portuguesa (DL 276/2001, Código, RGBEAC) carece de ou diverge significativamente nesta matéria. Recomenda-se: (i) incorporar idade mínima 10 meses (gatas) e 2º estro (cadelas); (ii) estabelecer máximo imperativo de 3 ninhadas em 2 anos (sem exceções veterinárias); (iii) exigir período de recuperação 1 ano após atingir limite; (iv) proibir uso após 2 cesarianas; (v) exigir avaliação veterinária escrita para cadelas ≥8 anos e gatas ≥6 anos. Estas alterações são críticas para garantir a conformidade com o Regulamento.</t>
-        </is>
-      </c>
+      <c r="P33" s="11" t="inlineStr"/>
     </row>
     <row r="34" ht="120" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -4113,18 +4313,18 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>ANEXO I, Ponto 4 do Regulamento 2023/0447</t>
+          <t>ANEXO I, Ponto 4 do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>4. Behavioural needs
-4.1 Socialisation
+          <t>Behavioural needs
+Socialisation
 From three weeks of age, dogs and cats shall be gradually provided with daily opportunities for social contact with their conspecifics and humans, and, where possible, with other animal species.
 Dogs and cats that pose a threat to each other due to aggressive behaviour or cause each other undue stress or discomfort shall be kept separate.
-4.2 Enrichment
+Enrichment
 Where cats are kept, there shall be a sufficient number of scratching posts, hiding places and shelves to ensure that each cat can climb, rest, observe and withdraw.
-4.3 Separation
+Separation
 Puppies kept in establishments shall not be permanently separated from their mothers before the age of 8 weeks.
 Kittens kept in shelters and foster homes shall not be permanently separated from their mothers before the age of 8 weeks. Kittens kept in breeding establishments shall not be permanently separated from their mothers before the age of 12 weeks.
 By way of derogation, earlier separation shall be possible due to medical reasons based on written advice of a veterinarian. The operator shall keep a record of the advice until the last puppy or kitten of the litter concerned is placed on the market.</t>
@@ -4132,15 +4332,15 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>4. Bem-Estar Comportamental
-4.1 Socialização
+          <t>Bem-Estar Comportamental
+Socialização
 A partir das três semanas de idade, cães e gatos devem ser gradualmente fornecidos com oportunidades diárias de contato social com seus congêneres e humanos, e, sempre que possível, com outras espécies animais.
 Cães e gatos que representam uma ameaça um ao outro devido a comportamento agressivo ou causam um ao outro stress excessivo ou desconforto devem ser mantidos separados.
-4.2 Enriquecimento
+Enriquecimento
 Onde gatos são mantidos, deve haver um número suficiente de postes de arranhadura, locais de abrigo e prateleiras para garantir que cada gato pode subir, descansar, observar e retirar-se.
-4.3 Separação
-Cachorros mantidos em estabelecimentos não devem ser permanentemente separados das suas mães antes dos 8 semanas de idade.
-Gatinhos mantidos em abrigos e casas de acolhimento não devem ser permanentemente separados das suas mães antes dos 8 semanas de idade. Gatinhos mantidos em estabelecimentos de criação não devem ser permanentemente separados das suas mães antes dos 12 semanas de idade.
+Separação
+Cachorros mantidos em estabelecimentos não devem ser permanentemente separados das suas mães antes das 8 semanas de idade.
+Gatinhos mantidos em abrigos e casas de acolhimento não devem ser permanentemente separados das suas mães antes das 8 semanas de idade. Gatinhos mantidos em estabelecimentos de criação não devem ser permanentemente separados das suas mães antes das 12 semanas de idade.
 Por derrogação, separação anterior é possível por razões médicas com base em parecer escrito de um veterinário. O operador deve conservar o parecer até o último cachorro ou gatinho da ninhada em questão ser colocado no mercado.</t>
         </is>
       </c>
@@ -4209,82 +4409,93 @@
       <c r="L34" s="9" t="inlineStr">
         <is>
           <t>4.1 SOCIALIZAÇÃO: DIVERGÊNCIA SIGNIFICATIVA — Código menciona contato social mas sem detalhe (idade, frequência, documentação)
-4.2 ENRIQUECIMENTO: PARCIAL — menciona prateleiras/poleiros mas omite 'postes de arranhadura' (essencial para gatos)
+4.2 ENRIQUECIMENTO: PARCIAL — menciona prateleiras/poleiros mas omite 'postes de arranhadura'
 4.3 SEPARAÇÃO: DIVERGÊNCIA SIGNIFICATIVA — Código exige 8 semanas (Arts. 23.º, 82.º) para EXPOSIÇÃO em venda; Regulamento exige 8 semanas (puppies, kittens abrigos) e 12 semanas (kittens breeding) para SEPARAÇÃO de mãe — conceitos distintos</t>
         </is>
       </c>
       <c r="M34" s="10" t="inlineStr">
         <is>
           <t>4.1 SOCIALIZAÇÃO: CONVERGÊNCIA PARCIAL — exige 'plano de socialização' (Art. 52.7) mas sem especificação de: idade 3 semanas, frequência diária, tipos de contato, separação de animais agressivos
-4.2 ENRIQUECIMENTO: CONVERGÊNCIA SIGNIFICATIVA — menciona enriquecimento 'complexo', inclui 'brinquedos', mas omite 'postes de arranhadura' (essencial para gatos)
-4.3 SEPARAÇÃO: CONVERGÊNCIA SIGNIFICATIVA — @RGBEAC (Art. 70.5) exige 10 semanas (cães) / 12 semanas (gatos) com desmame gradual (MAIS RESTRITIVO que Regulamento 8-12 semanas)</t>
+4.2 ENRIQUECIMENTO: menciona enriquecimento 'complexo', inclui 'brinquedos', mas omite 'postes de arranhadura'
+4.3 SEPARAÇÃO: @RGBEAC (Art. 70.5) exige 10 semanas (cães) / 12 semanas (gatos) com desmame gradual (mais restritivo que Regulamento 8-12 semanas)</t>
         </is>
       </c>
       <c r="N34" s="11" t="inlineStr">
         <is>
-          <t>ANNEX I, Ponto 4 (Behavioural Needs) tem três subsecções: (i) 4.1 Socialização — contato social diário desde 3 semanas (NOVO); (ii) 4.2 Enriquecimento — postes de arranhadura, abrigos, prateleiras para gatos (PARCIAL na legislação); (iii) 4.3 Separação — 8 semanas (puppies, kittens abrigos), 12 semanas (kittens breeding). DL 276/2001 é omisso em 4.1 e 4.3, parcial em 4.2. Código implementa 8 semanas para exposição (4.3) mas não separação maternal. @RGBEAC é mais restritivo (10-12 semanas separação) e cobre 4.1 (plano) e 4.2 (enriquecimento) com gaps específicos.</t>
+          <t>ANNEX I, Ponto 4 (Behavioural Needs) tem três subsecções: (i) 4.1 Socialização — contato social diário desde 3 semanas (NOVO); (ii) 4.2 Enriquecimento — postes de arranhadura, abrigos, prateleiras para gatos (PARCIAL na legislação); (iii) 4.3 Separação — 8 semanas (puppies, kittens abrigos), 12 semanas (kittens breeding). 
+DL 276/2001 é omisso em 4.1 e 4.3, parcial em 4.2. 
+@Código implementa 8 semanas para exposição (4.3) mas não separação maternal. 
+@RGBEAC é mais restritivo (10-12 semanas separação) e cobre 4.1 (plano) e 4.2 (enriquecimento) com gaps específicos.</t>
         </is>
       </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P34" s="11" t="inlineStr">
-        <is>
-          <t>ANNEX I, Ponto 4 contém 3 subsecções críticas de bem-estar comportamental. 4.1 SOCIALIZAÇÃO: COMPLETAMENTE NOVO — DL 276/2001 omisso. @RGBEAC menciona 'plano' (Art. 52.7) mas sem detalhe do Regulamento (3 semanas, frequência diária, tipos contato, documentação). IMPLEMENTAR: idade, frequência, contatos, registos, separação agressivos. 4.2 ENRIQUECIMENTO: CRÍTICO PARA GATOS — DL 276/2001 genérico, omite 'postes de arranhadura'. Código do Animal menciona 'prateleiras, poleiros' mas não especifica 'postes de arranhadura'. @RGBEAC omite completamente. IMPLEMENTAR: 'número suficiente de postes de arranhadura' (essencial bem-estar felino). 4.3 SEPARAÇÃO: DIVERGÊNCIA CONCEITUAL — Regulamento estabelece idade separação de MÃE (8-12 semanas); Código do Animal refere EXPOSIÇÃO em venda (8 semanas); @RGBEAC mais restritivo (10-12 semanas separação com desmame gradual). CLARIFICAR: 4.3 refere separação maternal, não comercialização.</t>
-        </is>
-      </c>
+          <t>Sim - Harmonização fundamental (4.1) + clarificação (4.2 postes arranhadura) + ajuste (4.3 separação vs. exposição)</t>
+        </is>
+      </c>
+      <c r="P34" s="11" t="inlineStr"/>
     </row>
     <row r="35" ht="120" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Requisitos Técnicos — Identificação e Registo de Cães e Gatos (Identification and Registration)</t>
+          <t>Identificação e Registo de Cães e Gatos - Requisitos Técnicos</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>ANEXO II do Regulamento 2023/0447 (conforme Articles 20 e 26)</t>
+          <t>ANEXO II do Regulamento 2023/0447 (conforme Articles 20 e 26)  |  EN</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Transponders used to individually identify dogs and cats as required in Article 17 and Article 21 shall meet the following requirements:
-— the microchip shall contain an individual, non-repeatable and non-reprogrammable identification number;
-— the identification number shall start with the country of identification of the dog or cat identified in accordance with ISO standard 3166;
-— code structure and technical concept of radio frequency identification shall be in compliance with ISO standards 11784 and 11785;
-— compliance with ISO standards 11784 and 11785 shall be evaluated according to ISO standard 24631-1.</t>
+          <t>Identification and registration of dogs and cats
+Transponders used to individually identify dogs and cats as required in Article 20 and Article 26 shall meet the following requirements:
+the microchip shall contain an individual, non-repeatable and non-reprogrammable identification number;
+the identification number shall start with the country of identification of the dog or cat identified in accordance with ISO standard 3166;
+the code structure and technical concept of the radio frequency identification shall be in compliance with ISO standards 11784 and 11785;
+compliance with ISO standards 11784 and 11785 shall be evaluated in accordance with ISO standard 24631-1.</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Os transponders usados para identificar individualmente cães e gatos conforme exigido nos artigos 17 e 21 devem cumprir os seguintes requisitos:
-— o microchip deve conter um número de identificação individual, não repetível e não reprogramável;
-— o número de identificação deve começar com o país de identificação do cão ou gato identificado de acordo com a norma ISO 3166;
-— a estrutura de código e o conceito técnico da identificação por radiofrequência devem estar em conformidade com as normas ISO 11784 e 11785;
-— a conformidade com as normas ISO 11784 e 11785 deve ser avaliada de acordo com a norma ISO 24631-1.</t>
+          <t>Identificação e registo de cães e gatos
+Os transponders utilizados para identificar individualmente cães e gatos, tal como exigido nos artigos 20.º e 26.º, devem cumprir os seguintes requisitos:
+O microchip deve conter um número de identificação individual, não repetível e não reprogramável;
+O número de identificação deve começar pelo país de identificação do cão ou gato, identificado em conformidade com a norma ISO 3166;
+A estrutura do código e o conceito técnico da identificação por radiofrequência devem estar em conformidade com as normas ISO 11784 e 11785;
+a conformidade com as normas ISO 11784 e 11785 deve ser avaliada de acordo com a norma ISO 24631-1</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Capítulo II — Sistema de Informação de Animais de Companhia (SIAC) do RGBEAC (proposta, jun. 2025)</t>
+          <t>Arts. 18.º e 19.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>O RGBEAC prevê a Lista Nacional de Animais de Companhia como instrumento de proteção, integrando o Sistema de Informação de Animais de Companhia (SIAC), anteriormente previsto no DL n.º 82/2019, de 27 de junho. O registo passa a ser obrigatório para TODOS os animais de companhia como medida de valorização, prevenção do abandono e melhoria do acompanhamento e proteção. [Detalhe técnico sobre ISO standards pendente de análise do texto completo do Capítulo II do RGBEAC]</t>
+          <t>Artigo 18.º- Métodos de marcação
+1 – Os métodos de marcação devem atender às melhoras práticas internacionais vigentes e salvaguardar o bem-estar animal.
+2 – Os cães, gatos e furões devem ser marcados por implantação de um transponder, que assegure os requisitos estabelecidos no anexo II do Regulamento (UE) n.º 576/2013, do Parlamento Europeu e do Conselho, de 12 de junho de 2013. 
+3 - Os demais animais de companhia devem ser marcados através do método determinado para cada espécie por deliberação da DGAV, publicitado no respetivo sítio na Internet.
+4 - A implantação do transponder referido no n.º 2 deve ser efetuada por médico veterinário, no centro da face lateral esquerda do pescoço, após verificação de que o animal não se encontra já marcado por outro dispositivo de identificação.
+5 - Se não for possível, por motivo justificado, aplicar o transponder no local referido no número anterior, deve o mesmo ser aplicado num local alternativo, devendo o médico veterinário inserir essa informação no documento de identificação do animal e no SIAC.
+6 – Caso a marcação não seja tecnicamente possível ou exista alguma contraindicação que por motivos de saúde temporariamente não permita a sua marcação, o registo deve ser realizado no SIAC pelo médico veterinário, com a emissão de uma declaração, conforme modelo aprovado pela DGAV, publicitado no respetivo sítio na Internet.
+7 – A emissão de declaração prevista no número anterior é igualmente aplicável aos casos em que não exista ainda a deliberação prevista no n.º 3 do presente artigo.
+Artigo 19º- Dispositivos de identificação 
+1 - A colocação no mercado nacional de transponders e outros dispositivos de identificação individual invioláveis depende de acreditação prévia para efeitos do seu registo e autorização da sua comercialização, de acordo com os procedimentos estabelecidos pela DGAV.
+2 - Às entidades autorizadas a comercializar transponders e outros dispositivos de identificação individual invioláveis para animais de companhia é atribuído um acesso único ao SIAC, para que estas registem todos os dispositivos que tenham comercializado para cada médico veterinário ou entidade autorizada perante o SIAC a deter meios de identificação, de acordo com procedimento a determinar pela DGAV 
+3 - Para a marcação só pode ser utilizado um transponder ou outro dispositivo de identificação individual que tenha sido previamente registado no SIAC pela empresa comercializadora, e atribuído ao médico veterinário ou a uma entidade autorizada a identificar animais de companhia.</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Arts. 53.º a 59.º do Código do Animal (DL 214/2013)</t>
+          <t>Arts. 53.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
           <t>Artigo 53.º — Identificação e registo na base de dados
-1 - Todos os cães devem ser identificados e registados, entre os três e os seis meses de idade.
-4 - Os cães e gatos são identificados através de método electrónico e registados na base de dados nacional.
+(…)
 5 - A identificação electrónica é efetuada através da aplicação subcutânea de um microchip no centro da face lateral esquerda do pescoço.
 6 - Para efeito de registo na base de dados, só podem ser aplicados os microchips que estejam em conformidade com as normas ISO 11784.
 7 - A aplicação do microchip apenas pode ser efetuada por médico veterinário, enfermeiro ou outro técnico habilitado.
@@ -4298,53 +4509,17 @@
           <t>DL n.º 82/2019, de 27 de junho (LEGISLAÇÃO VIGENTE) + DL n.º 276-2001</t>
         </is>
       </c>
-      <c r="J35" s="7" t="inlineStr">
-        <is>
-          <t>[DL n.º 82/2019, de 27 de junho — LEGISLAÇÃO VIGENTE RELEVANTE]
-Este diploma contém o regime atual de identificação e registo de animais de companhia, incluindo Sistema de Informação de Animais de Companhia (SIAC). REMETE PARA: Análise detalhada online de DL 82/2019 consolidado (dre.pt ou eur-lex) — CRÍTICO para comparação com ANNEX II do Regulamento.
-[DL 276/2001 — legislação anterior, sem disposições operacionais específicas sobre identificação eletrónica]</t>
-        </is>
-      </c>
-      <c r="K35" s="8" t="inlineStr">
-        <is>
-          <t>REVOGAÇÃO TOTAL
-DL 276/2001 foi revogado pelo Código do Animal (DL 214/2013). Sem disposições sobre ISO standards ou requisitos técnicos de microchip.</t>
-        </is>
-      </c>
-      <c r="L35" s="9" t="inlineStr">
-        <is>
-          <t>CONVERGÊNCIA SIGNIFICATIVA
-✅ Código exige conformidade ISO 11784 (Art. 53.6)
-✅ Identificação eletrónica por microchip (Art. 53.5)
-✅ Registo em base de dados nacional (Arts. 55-59)
-⚠️ Código refere ISO 11784; Regulamento exige ISO 11784/11785 + 24631-1 (mais restritivo)
-⚠️ Prazos diferentes: Código 3-6 meses; Regulamento 3 meses (proprietários), 30 dias (operadores)</t>
-        </is>
-      </c>
-      <c r="M35" s="10" t="inlineStr">
-        <is>
-          <t>CONVERGÊNCIA PARCIAL
-✅ Integra Sistema de Informação de Animais de Companhia (SIAC) — mais robusto que Código
-✅ Registo obrigatório para TODOS os animais de companhia (não apenas cães e gatos comerciais)
-⚠️ CRÍTICO: Requisitos técnicos ISO standards NÃO MENCIONADOS explicitamente no resumo disponível
-⚠️ Prazos: A confirmar em texto completo do Capítulo II</t>
-        </is>
-      </c>
-      <c r="N35" s="11" t="inlineStr">
-        <is>
-          <t>ANNEX II (Identification and Registration) estabelece quatro requisitos técnicos de transponders: (i) número individual não-repetível; (ii) ISO 3166 (país); (iii) ISO 11784/11785 (radiofrequência); (iv) ISO 24631-1 (avaliação). Código do Animal implementa ISO 11784 mas não ISO 11785 ou 24631-1 (menos restritivo). @RGBEAC promove SIAC (mais robusto) mas não especifica ISO standards. Recomenda-se: validar conformidade portuguesa com ISO 11785 e 24631-1 (inovações do Regulamento).</t>
-        </is>
-      </c>
+      <c r="J35" s="7" t="inlineStr"/>
+      <c r="K35" s="8" t="inlineStr"/>
+      <c r="L35" s="9" t="inlineStr"/>
+      <c r="M35" s="10" t="inlineStr"/>
+      <c r="N35" s="11" t="inlineStr"/>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P35" s="11" t="inlineStr">
-        <is>
-          <t>ANNEX II especifica requisitos TÉCNICOS de transponders/microchips (não procedimentos administrativos). IMPORTANTE DIVERGÊNCIA: Código do Animal exige ISO 11784; Regulamento exige ISO 11784/11785 + 24631-1. ISO 11785: estabelece padrão de radiofrequência para microchips. ISO 24631-1: metodologia de avaliação de conformidade. Ambas são NOVIDADES do Regulamento não presentes na legislação portuguesa anterior. @RGBEAC menciona SIAC (Sistema de Informação) mas não detalha requisitos técnicos ISO. Recomenda-se: (i) validar conformidade microchips portugueses com ISO 11785 e 24631-1; (ii) atualizar requisitos de aprovação/certificação de equipamentos; (iii) harmonizar prazos de identificação (3 meses vs. 30 dias por tipo operador).</t>
-        </is>
-      </c>
+          <t>ANNEX II (Identification and Registration) estabelece quatro requisitos técnicos de transponders: (i) número individual não-repetível; (ii) ISO 3166 (país); (iii) ISO 11784/11785 (radiofrequência); (iv) ISO 24631-1 (avaliação).</t>
+        </is>
+      </c>
+      <c r="P35" s="11" t="inlineStr"/>
     </row>
     <row r="36" ht="120" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -4354,23 +4529,23 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>ANEXO III do Regulamento 2023/0447 (conforme Article 24)</t>
+          <t>ANEXO III do Regulamento 2023/0447 (conforme Article 24)  |  EN</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>1. Number of dogs and cats registered per year, as referred to in Article 17 and Article 21(4).
-1a. Number of breeding establishments, selling establishments, shelters, and foster homes registered per year in accordance with Article 7.
-2. Number of breeding establishments approved per year, as referred to in Article 7a.
-2a. Number of breeding establishments whose approval has been suspended or withdrawn per year.</t>
+          <t>The number of dogs and cats registered per year, as referred to in Article 20 and Article 26(3).
+The number of breeding establishments, selling establishments, shelters and foster homes registered per year in accordance with Article 9.
+The number of breeding establishments approved per year, as referred to in Article 10.
+The number of breeding establishments approval of which has been suspended or withdrawn per year.</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1. Número de cães e gatos registados por ano, conforme referido nos artigos 17.º e 21.º, n.º 4.
-1a. Número de estabelecimentos de criação, estabelecimentos de venda, abrigos e famílias de acolhimento registados por ano, em conformidade com o artigo 7.º.
-2. Número de estabelecimentos de criação aprovados por ano, conforme referido no artigo 7a.º.
-2a. Número de estabelecimentos de criação cuja aprovação foi suspensa ou revogada por ano.</t>
+          <t>O número de cães e gatos registados por ano, conforme referido no artigo 20.º e no artigo 26.º, n.º 3.
+ O número de estabelecimentos de criação, estabelecimentos de venda, abrigos e famílias de acolhimento registados por ano em conformidade com o artigo 9.º.
+O número de estabelecimentos de criação aprovados por ano, conforme referido no artigo 10.º. 
+O número de estabelecimentos de criação cuja aprovação tenha sido suspensa ou retirada por ano.</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -4381,18 +4556,18 @@
       <c r="F36" s="5" t="inlineStr">
         <is>
           <t>Artigo 20.º — Sistema de Informação de Animais de Companhia (SIAC)
-1 - O SIAC reúne informação relativa à: a) Rastreabilidade de dispositivos de identificação; b) Identificação dos animais de companhia; c) Sua titularidade ou detenção; d) Informação de saúde pública, saúde animal e bem-estar animal.
-2 – A DGAV é a entidade responsável pelo SIAC, assegurando seu funcionamento e tratamento seguro de informação.
-3 – A DGAV pode atribuir gestão do SIAC a outras entidades, mediante protocolo e parecer da Comissão Nacional de Proteção de Dados.
-4 - Normas e procedimentos constam de Manual de Procedimentos SIAC, aprovado pelo diretor-geral de alimentação e veterinária.
+O SIAC reúne informação relativa à: a) Rastreabilidade de dispositivos de identificação; b) Identificação dos animais de companhia; c) Sua titularidade ou detenção; d) Informação de saúde pública, saúde animal e bem-estar animal.
+A DGAV é a entidade responsável pelo SIAC, assegurando seu funcionamento e tratamento seguro de informação.
+A DGAV pode atribuir gestão do SIAC a outras entidades, mediante protocolo e parecer da Comissão Nacional de Proteção de Dados.
+Normas e procedimentos constam de Manual de Procedimentos SIAC, aprovado pelo diretor-geral de alimentação e veterinária.
 Artigo 46.º — Relatório Nacional Anual
-1 - Centros de bem-estar animal e alojamentos com fins de promoção remetem à DGAV no primeiro mês de cada ano, relatórios de gestão do ano anterior.
-2 – A DGAV consolida informação a nível nacional sobre bem-estar animal em cada ano, incluindo: a) Acompanhamento da política internacional; b) Prestação de apoios públicos; c) Atividade do SIAC; d) Resultados de planos de controlo; e) Processos contraordenacionais; f) Coimas e sanções; g) Atividade de centros de bem-estar animal; h) Programas de interesse nacional.</t>
+Para efeitos de monitorização, os centros de bem-estar animal e alojamentos com fins de promoção do bem-estar animal remetem à DGAV no primeiro mês de cada ano civil, os relatórios de gestão do ano anterior, com os números de animais de companhia recolhidos, restituídos aos detentores, eutanasiados, cedidos a associações zoófilas, adotados, devolvidos após adoção, vacinados, esterilizados e intervencionados no âmbito de programas CED.
+A DGVA consolida a informação a nível nacional sobre bem-estar animal em cada ano, incluindo o acompanhamento da política internacional do Estado Português na área do bem-estar dos animais de companhia, a prestação dos apoios públicos, a atividade do SIAC, os resultados dos planos de controlo, os processos contraordenacionais instaurados e coimas e sanções acessórias aplicadas, a atividade dos centros de bem-estar animal e dos alojamentos com fins de promoção de bem-estar animal, bem como os programas e ações de interesse nacional em matéria do bem-estar dos animais de companhia, incluindo ações informativas, formativas, educativas e estudos desenvolvidos, para efeitos de elaboração do Relatório Anual sobre a situação do Bem-Estar Animal previsto na alínea i) do n.º 1 do artigo 3.º do Decreto-Regulamentar n.º 3/2021, de 25 de junho;</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Código do Animal (DL 214/2013) — Arts. 55.º, 56.º, 141.º-145.º</t>
+          <t>Código do Animal (DL 214/2013) — Arts. 55.º, 141.º-145.º</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -4400,97 +4575,49 @@
           <t>Artigo 55.º — Base de dados
 1 - Toda informação de registo coligida numa aplicação informática nacional.
 2 - A DGAV detém, define e coordena acesso à BD, podendo autorizar gestão em outras entidades mediante protocolos e parecer da Comissão Nacional de Proteção de Dados.
-3 - Só entidades autorizadas pela DGAV têm acesso.
-Artigo 56.º — Classificação dos animais
-Categorias para registo na BD: a) Cão (designado A); b) Cão Potencialmente Perigoso (designado G); c) Cão Perigoso (designado H); d) Gato (designado I).
-Artigos 141.º-145.º — Monitorização e Relatórios
-Código do Animal estabelece estrutura de: a) Monitorização de bem-estar animal; b) Recolha de dados de infrações; c) Aplicação de sanções; d) Atividades de centros de recolha; e) Estatísticas de animais processados; f) Sistema de contraordenações.</t>
+3 - Só entidades autorizadas pela DGAV têm acesso.</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>DL 82/2019 (Arts. 2.º-7.º), Lei 27/2016 (Arts. 1.º-9.º)</t>
+          <t>Decreto-Regulamentar n.º 3/2021 e Lei 27/2016</t>
         </is>
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>Decreto-Lei n.º 82/2019 de 27 de junho — Bem-Estar de Animais de Companhia
-Artigo 2.º — Âmbito de aplicação — Aplicável a cães, gatos e furões detidos para fins não comerciais.
-Artigo 3.º — Obrigações de registo — Proprietários de cães e gatos devem proceder ao registo no SIAC com identificação eletrónica obrigatória.
-Artigo 4.º — Identificação eletrónica — Via aplicação subcutânea de microchip (ISO 11784 e 11785).
-Artigo 5.º — Procedimentos de registo — Procedimentos de registo, atualização e consulta do SIAC estabelecidos em regulação complementar.
-Artigo 6.º — Controlos de acesso — Segurança de dados e autorização de acesso ao SIAC sob responsabilidade DGAV.
-Artigo 7.º — Rastreabilidade — Sistema garante rastreabilidade de dispositivos de identificação e proprietários.
-[dim]Lei n.º 27/2016 de 23 de agosto — Rede de Centros de Recolha e Proibição do Abate
-Artigo 1.º — Objeto — Aprova medidas para criação de rede de centros de recolha oficial de animais errantes.
-Artigo 2.º — Definições — Centros de recolha, abrigos, famílias de acolhimento — conceitos e categorias.
-Artigos 3.º-9.º — Estrutura e Funcionamento — Procedimentos de registo, aprovação, funcionamento e supervisão.</t>
+          <t>Decreto-Regulamentar 3/2021 (Art. 3.º) requer Relatório Anual sobre situação do Bem-Estar Animal. 
+nº 9 e 10, artigo 3.º da Lei nº 27/2016, de 23 de agosto
+9 - Para efeitos de monitorização, todos os centros de recolha oficial de animais publicitam, no primeiro mês de cada ano civil, os relatórios de gestão do ano anterior, com os números de recolhas, abates ou occisões, eutanásias, adoções, vacinações e esterilizações efetuadas.
+10 - Com base nos relatórios referidos no número anterior, a Direção-Geral de Alimentação e Veterinária elabora e publicita um relatório anual sobre a situação ao nível nacional, até ao fim do primeiro trimestre de cada ano civil.</t>
         </is>
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>ANÁLISE POR PONTO:
-PONTO 1 (Cães/gatos registados): ✅ CONFORMIDADE COMPLETA
-SIAC operacional desde 2019 (DL 82/2019) — registo obrigatório e eletrónico. Dados disponíveis anualmente.
-PONTO 1a (Estabelecimentos registados): ⚠️ CONFORMIDADE PARCIAL
-Lei 27/2016 e DL 82/2019 cobrem criação, venda, abrigos. LACUNA: conceito "famílias de acolhimento" não explicitamente codificado em legislação vigente.
-PONTO 2 (Estabelecimentos aprovados): ❌ LACUNA CRÍTICA
-Legislação vigente menciona REGISTO de estabelecimentos de criação. FALTA: sistema específico de "aprovação" formal (vs. apenas registo). Portarias específicas de aprovação existem para outros setores (científico) — NÃO claramente para criadores de animais de companhia.
-PONTO 2a (Suspensão/revogação): ❌ LACUNA CRÍTICA
-DL 82/2019 e Lei 27/2016 NÃO mencionam procedimentos de suspensão ou revogação de aprovação de estabelecimentos.</t>
+          <t>Sem equivalência</t>
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>ANÁLISE POR PONTO:
-PONTO 1: ✅ CONFORMIDADE COMPLETA
-Arts. 55.º-56.º estabelecem base de dados nacional com classificação detalhada de animais. Sistema estruturado.
-PONTO 1a: ❌ NÃO IMPLEMENTADO
-Código do Animal não estabelece sistema específico de registo de estabelecimentos de criação, venda, abrigos, famílias de acolhimento.
-PONTO 2: ❌ NÃO IMPLEMENTADO
-Código do Animal não estabelece sistema de aprovação de criadores.
-PONTO 2a: ❌ NÃO IMPLEMENTADO
-Código do Animal não menciona suspensão/revogação de aprovação.</t>
+          <t>Sem equivalência</t>
         </is>
       </c>
       <c r="M36" s="10" t="inlineStr">
         <is>
-          <t>ANÁLISE POR PONTO:
-PONTO 1: ✅ CONFORMIDADE COMPLETA
-Art. 20.º (SIAC) — registo obrigatório e operacional. Relatório nacional anual possível (Art. 46.º).
-PONTO 1a: ⚠️ CONFORMIDADE PARCIAL
-Art. 20.º implicitamente cobre estabelecimentos através de rastreabilidade de dispositivos. REQUER complementação: codificação explícita de registo de "famílias de acolhimento".
-PONTO 2: ❌ NÃO IMPLEMENTADO
-RGBEAC não menciona sistema de aprovação de criadores.
-PONTO 2a: ❌ NÃO IMPLEMENTADO
-RGBEAC não menciona suspensão/revogação de aprovação.</t>
+          <t>Sem equivalência</t>
         </is>
       </c>
       <c r="N36" s="11" t="inlineStr">
         <is>
-          <t>CONCLUSÃO GERAL:
-Legislação portuguesa implementa PARCIALMENTE os 4 pontos de Annex III (dados para relatório trienal à Comissão UE):
-✅ PONTO 1 — COBERTURA COMPLETA: SIAC operacional desde 2019. Dados de cães/gatos registados disponíveis anualmente.
-⚠️ PONTO 1a — COBERTURA PARCIAL: Sistema de registo de estabelecimentos existe (Lei 27/2016); conceito "famílias de acolhimento" requer codificação explícita.
-❌ PONTO 2 — LACUNA ESTRUTURAL: Falta sistema formal de "aprovação" de criadores. Existe apenas registo administrativo. Necessário: distinguir registo (mera inscrição) de aprovação (avaliação de conformidade com requisitos técnicos).
-❌ PONTO 2a — LACUNA ESTRUTURAL: Falta procedimentos formais de suspensão/revogação de aprovação. Necessário: mecanismo administrativo com critérios de suspensão e revogação.
-RECOMENDAÇÕES:
-1. Complementar Lei 27/2016 com definição e registo de "famílias de acolhimento" (ponto 1a).
-2. Criar sistema de aprovação prévia de estabelecimentos de criação, com avaliação de conformidade (ponto 2).
-3. Estabelecer procedimentos formais de suspensão/revogação com critérios administrativos (ponto 2a).
-4. Integrar dados coletados em relatório trienal da Comissão UE (conforme Art. 20 do Regulamento).</t>
+          <t>ANNEX III define dados obrigatórios para relatório trienal à Comissão UE (Art. 20 do Regulamento). SIAC português fornece dados para ponto 1 (cães/gatos registados) — sistema operacional desde 2019. Pontos 2 e 2a requerem regulação complementar: aprovação formal de criadores (vs. apenas registo) + procedimentos de suspensão/revogação. Ponto 1a (estabelecimentos) — codificação explícita de "famílias de acolhimento" como categoria administrativa.
+Integrar dados coletados em relatório trienal da Comissão UE (conforme Art. 20 do Regulamento).</t>
         </is>
       </c>
       <c r="O36" s="11" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P36" s="11" t="inlineStr">
-        <is>
-          <t>ANNEX III define dados OBRIGATÓRIOS para relatório trienal à Comissão UE (Art. 20 do Regulamento). SIAC português fornece dados para ponto 1 (cães/gatos registados) — sistema operacional desde 2019. Pontos 2 e 2a requerem regulação complementar urgente: aprovação formal de criadores (vs. apenas registo) + procedimentos de suspensão/revogação. Ponto 1a (estabelecimentos) — codificação explícita de "famílias de acolhimento" como categoria administrativa. Recomenda-se: Lei complementar ou Portaria reguladora para implementação completa dos 4 pontos antes do próximo período de reporte (trienal).</t>
-        </is>
-      </c>
+          <t>Sim — Estabelecer sistema de aprovação, suspensão e revogação de estabelecimentos de criação + codificar famílias de acolhimento</t>
+        </is>
+      </c>
+      <c r="P36" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -704,27 +704,27 @@
       <c r="J2" s="7" t="inlineStr"/>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Não se aplica — a legislação nacional não utiliza o modelo de limiares de isenção adoptado pelo Regulamento (≤2 ninhadas/ano; ≤15 animais em abrigo). A Portaria n.º 148/2016 regula o registo de cães que integrem matilhas de caça maior junto do ICNF, I. P., mas não fixa limiares de isenção de obrigações de bem-estar.</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Não se aplica — artigo processual de isenções sem correspondência nas propostas nacionais.</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Não se aplica — artigo processual de isenções sem correspondência nas propostas nacionais.</t>
         </is>
       </c>
       <c r="N2" s="11" t="inlineStr">
         <is>
-          <t>Artigo de isenções do Regulamento europeu — não tem correspondência directa em legislação portuguesa.</t>
+          <t>O n.º 1 do Art.º 5.º define um limiar de 2 ninhadas por ano civil que libera os pequenos criadores das obrigações de bem-estar mais exigentes do Capítulo II. Este limiar pode capturar proprietários de matilhas de caça em Portugal (especialmente caça maior) sem actividade comercial, que regularmente produzem ninhadas de cães de trabalho. No debate legislativo europeu (EP A10-0104/2025), as federações de caçadores (FACE, Federación Española de Caza) argumentaram que o limiar de 2 ninhadas deveria isentar a criação não comercial de cães de caça, enquanto as ONG de bem-estar animal (AnimaNaturalis, Eurogroup for Animals) exigiram a aplicação universal do Regulamento sem excepções. O texto final não criou uma derrogação explícita para cães de caça. A aplicação prática deste limiar a proprietários de matilhas portuguesas (que podem deter 20–120 cães) terá de ser avaliada pela autoridade competente.</t>
         </is>
       </c>
       <c r="O2" s="11" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Não — artigo de isenções de aplicação directa; o limiar é fixado pelo Regulamento e não carece de transposição. Pode carecer de orientação administrativa para aplicação a matilhas de caça.</t>
         </is>
       </c>
       <c r="P2" s="11" t="inlineStr"/>
@@ -2363,21 +2363,29 @@
 2 — Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.</t>
         </is>
       </c>
-      <c r="K14" s="8" t="inlineStr"/>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 (art.º 8.º) prevê genericamente que os animais devem 'dispor de um espaço adequado às suas necessidades fisiológicas e etológicas' e de 'esconderijos', mas sem requisitos de socialização, enriquecimento documentado ou estratégia formal. A Portaria n.º 148/2016 regula o registo de cães em matilhas de caça maior (junto do ICNF, I. P.) mas não fixa normas de bem-estar comportamental para esses cães. O @rgbeac (art.º 10.º, n.º 3) isenta expressamente os cães utilizados na caça durante os atos venatórios da obrigação de trela — o que representa uma derrogação análoga (embora com âmbito e fundamento distintos) à derrogação do n.º 4 do Art.º 17.º do Regulamento para cães militares/policiais/aduaneiros. Não existe, no entanto, na legislação nacional, qualquer equivalente à isenção de socialização para cães de proteção de gado ou de pastoreio em transumância.</t>
+        </is>
+      </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>Sem especificações sobre socialização e enriquecimento</t>
+          <t>O @codigo (DL 214/2013) não contém especificações sobre socialização, enriquecimento ambiental ou estratégia documentada de socialização por parte dos criadores. O art.º 13.º prevê genericamente 'espaço para exercício físico e expressão de comportamentos naturais', mas sem os requisitos quantitativos ou processuais do Regulamento. Não inclui as derrogações para cães funcionais.</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>Cobertura mais significtiva</t>
-        </is>
-      </c>
-      <c r="N14" s="11" t="inlineStr"/>
+          <t>O @rgbeac cobre parcialmente: prevê 'exercício físico e estímulo mental' (art.º 10.º, n.º 1, al. a), i)), 'métodos de reforço positivo' como obrigação (art.º 10.º, n.º 1, al. c)) e proíbe 'métodos aversivos, punitivos ou violentos' (art.º 12.º, al. v)). Prevê ainda obrigação de 'plano de socialização e enriquecimento ambiental' (art.º 52.º, n.º 7) para alojamentos. No entanto, o @rgbeac não contempla as derrogações específicas do Regulamento: (1) isenção dos cães de proteção de gado («livestock guardian dogs») dos requisitos de socialização durante períodos de guarda ou treino; (2) isenção dos cães de pastoreio durante a transumância sazonal; (3) isenção de cães militares, policiais e aduaneiros da proibição de acorrentamento superior a 1 hora. Também não inclui a obrigação de 'estratégia documentada de socialização' para criadores.</t>
+        </is>
+      </c>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>O Regulamento introduz obrigações novas sem equivalente nacional: (1) proibição de acorrentamento superior a 1 hora (com isenção para cães militares, policiais e aduaneiros); (2) obrigação de estratégia documentada de socialização por parte dos criadores; (3) isenção explícita de socialização para cães de proteção de gado ("livestock guardian dogs") durante guarda/treino e para cães de pastoreio em transumância sazonal. Em Portugal, a realidade dos cães de caça (matilhas) é relevante: a Portaria n.º 148/2016 exige registo mas não impõe normas de bem-estar comportamental. O Regulamento não inclui derrogação explícita para cães de caça — estes estão abrangidos pelas obrigações gerais do Art.º 17.º enquanto permanecerem em estabelecimentos de criação ou venda.</t>
+        </is>
+      </c>
       <c r="O14" s="11" t="inlineStr">
         <is>
-          <t>Em análise. RGBEAC alinha melhor; implementação de reforço positivo obrigatório recomendada</t>
+          <t>Sim — necessidade de: (1) criar regime de proibição de acorrentamento superior a 1 hora com as isenções previstas; (2) impor estratégia documentada de socialização aos criadores; (3) clarificar o estatuto dos cães de caça e matilhas face às obrigações comportamentais.</t>
         </is>
       </c>
       <c r="P14" s="11" t="inlineStr"/>
@@ -2478,22 +2486,29 @@
 2 — O documento referido no número anterior deve ter a forma de um atestado, do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura.</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr"/>
-      <c r="L15" s="9" t="inlineStr"/>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 (arts. 17.º e 18.º) exige que as intervenções cirúrgicas (incluindo corte de caudas) sejam realizadas por médico veterinário e que as amputações estejam documentadas por atestado. Não existe proibição expressa de corte de cauda anterior a 2013. O @rgbeac e o @codigo já proíbem o corte de cauda desde 2015 (art.º 52.º, n.º 3 do @codigo), o que excede o regime do Regulamento no que respeita a cães de caça (o Regulamento admite a excepção profilática que poderia ser invocada para justificar o corte de cauda em cães de caça). A derrogação do n.º 5 do Art.º 18.º para cães militares, policiais e aduaneiros não tem equivalente na legislação nacional. A proibição de coleiras de espinhos e de estrangulamento sem paragem de segurança não consta expressamente da legislação nacional vigente (embora o uso de 'aguilhões' e instrumentos perfurantes na condução de animais seja proibido pela Lei n.º 92/95).</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>O @codigo (DL 214/2013) proíbe mutilações com fins não curativos (art.º 52.º, n.º 1), incluindo corte de orelhas, cordas vocais, garras ou unhas, dentes ou presas. O art.º 52.º, n.º 3 proíbe o corte de cauda para todos os cães nascidos a partir de 1 de Janeiro de 2015 — regime mais restritivo que o Regulamento, que admite corte de cauda por razões profiláticas (incluindo potencialmente para cães de caça). O @codigo exige atestado veterinário (n.º 4) alinhado com o n.º 2 do Art.º 18.º. Não cobre explicitamente a proibição de coleiras de espinhos (prong collars) nem de coleiras de estrangulamento sem paragem de segurança prevista no n.º 5, als. (e) e (f) do Regulamento.</t>
+        </is>
+      </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>@rgbeac ressalva expressamente o corte das orelhas que não seja realizada para fins de identificação de animais esterilizados conforme boas práticas internacionais", o que cobre o essencial desta derrogação.</t>
+          <t>O @rgbeac (art.º 12.º, al. i)) proíbe intervenções cirúrgicas com objectivo de modificar a aparência, incluindo 'corte da cauda, secção das cordas vocais, remoção de unhas ou dentes, e corte das orelhas que não seja realizada para fins de identificação de animais esterilizados conforme boas práticas internacionais'. O art.º 34.º do @rgbeac exige atestado veterinário para qualquer intervenção curativa que modifique a aparência, alinhando com o n.º 2 do Art.º 18.º do Regulamento. O @rgbeac também proíbe coleiras elétricas, de choques, estranguladores e açaimos fechados (art.º 12.º, al. aa)), convergindo com o n.º 5 do Art.º 18.º. A derrogação do Art.º 18.º, n.º 3, sobre corte de orelha de gatos em programas TNR está coberta pela ressalva do @rgbeac ('fins de identificação de animais esterilizados conforme boas práticas internacionais').</t>
         </is>
       </c>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>exige expressamente anestesia e analgesia prolongada como condição do procedimento.
-Rever proibições na análise do art.7.º</t>
+          <t>Portugal está em grande medida alinhado com o Regulamento no que respeita à proibição de mutilações: o corte de cauda já é proibido desde 2015 (mais restritivo do que o Regulamento, que admite excepção profilática para cães de caça). Os principais gaps são: (1) ausência de proibição expressa de coleiras de espinhos (prong collars) e de estrangulamento sem paragem de segurança; (2) ausência de derrogação específica para cães militares, policiais e aduaneiros; (3) necessidade de clarificar que a excepção profilática do Art.º 18.º, n.º 1 não se aplica ao corte de cauda de cães de caça em Portugal (o @codigo e @rgbeac são mais restritivos). Exige anestesia e analgesia prolongada como condição obrigatória para qualquer procedimento justificado — requisito que a legislação nacional não especifica explicitamente.</t>
         </is>
       </c>
       <c r="O15" s="11" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim — necessidade de: (1) proibir expressamente coleiras de espinhos e de estrangulamento sem paragem de segurança; (2) clarificar o âmbito da excepção profilática face ao regime mais restritivo nacional; (3) confirmar conformidade do regime de atestado veterinário com os requisitos documentais do Art.º 18.º, n.º 2.</t>
         </is>
       </c>
       <c r="P15" s="11" t="inlineStr"/>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -704,27 +704,27 @@
       <c r="J2" s="7" t="inlineStr"/>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Não se aplica — a legislação nacional não utiliza o modelo de limiares de isenção adoptado pelo Regulamento (≤2 ninhadas/ano; ≤15 animais em abrigo). A Portaria n.º 148/2016 regula o registo de cães que integrem matilhas de caça maior junto do ICNF, I. P., mas não fixa limiares de isenção de obrigações de bem-estar.</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Não se aplica — artigo processual de isenções sem correspondência nas propostas nacionais.</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Não se aplica — artigo processual de isenções sem correspondência nas propostas nacionais.</t>
         </is>
       </c>
       <c r="N2" s="11" t="inlineStr">
         <is>
-          <t>Artigo de isenções do Regulamento europeu — não tem correspondência directa em legislação portuguesa.</t>
+          <t>O n.º 1 do Art.º 5.º define um limiar de 2 ninhadas por ano civil que libera os pequenos criadores das obrigações de bem-estar mais exigentes do Capítulo II. Este limiar pode capturar proprietários de matilhas de caça em Portugal (especialmente caça maior) sem actividade comercial, que regularmente produzem ninhadas de cães de trabalho. No debate legislativo europeu (EP A10-0104/2025), as federações de caçadores (FACE, Federación Española de Caza) argumentaram que o limiar de 2 ninhadas deveria isentar a criação não comercial de cães de caça, enquanto as ONG de bem-estar animal (AnimaNaturalis, Eurogroup for Animals) exigiram a aplicação universal do Regulamento sem excepções. O texto final não criou uma derrogação explícita para cães de caça. A aplicação prática deste limiar a proprietários de matilhas portuguesas (que podem deter 20–120 cães) terá de ser avaliada pela autoridade competente.</t>
         </is>
       </c>
       <c r="O2" s="11" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Não — artigo de isenções de aplicação directa; o limiar é fixado pelo Regulamento e não carece de transposição. Pode carecer de orientação administrativa para aplicação a matilhas de caça.</t>
         </is>
       </c>
       <c r="P2" s="11" t="inlineStr"/>
@@ -762,45 +762,77 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Análise no Art.º 7</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr"/>
+          <t>Art.º 7.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1 – Todos têm o dever de garantir condições de bem-estar aos animais de companhia, em especial que:
+a) não passem fome ou sede, nem sejam sujeitos a malnutrição;
+b) não sejam expostos a situações de desconforto físico ou térmico;
+c) não sofram dor, lesão física ou doença;
+d) possam expressar padrões normais de comportamento; e
+e) não sejam colocados em situações que lhes provoquem stresse, medo ou ansiedade injustificados.
+2 - As condições de detenção e de alojamento dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
+3 - Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no presente decreto-lei ou se não se adaptar ao cativeiro.</t>
+        </is>
+      </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Análise no Art.º 7</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr"/>
+          <t>Arts. 4.º e 5.º do Código do Animal (DL n.º 214/2013)</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 4.º — Detenção responsável
+Cabe aos detentores de animais de companhia assegurar as necessidades básicas de bem-estar dos mesmos, garantir o controlo da sua reprodução, salvaguardar a sua saúde e prevenir os riscos inerentes à transmissão de doenças a pessoas e a outros animais e, ainda, a segurança das populações, garantindo a salubridade dos locais e a tranquilidade das pessoas.
+Artigo 5.º — Princípios básicos para o bem-estar dos animais
+1 - As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal.
+2 - Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
+3 - É proibida a violência contra animais, considerando-se como tal todos os atos que, sem necessidade, infligem a morte, o sofrimento, abuso ou lesões a um animal, designadamente os seguintes:
+a) Agredir animais, nomeadamente com o uso de chicotes, estimulantes elétricos ou objetos contundentes ou perfurantes, ou com murros, bofetadas ou pontapés;
+b) Restringir a liberdade de movimentos dos animais de tal forma que lhes seja impedido levantar-se, deitar-se ou virar-se sobre si próprios;
+c) Usar equipamentos de maneio, contenção ou treino, que causem sofrimento desnecessário ou lesões aos animais;
+d) Incitar, realizar ou promover lutas entre animais de companhia, quando destas possa resultar sofrimento, lesões ou morte dos animais.
+4 - É proibido utilizar animais para fins didáticos e lúdicos, de treino, filmagens, exibições, publicidade ou atividades semelhantes, sempre que daí resultem para aqueles dor ou sofrimentos consideráveis, salvo experiência científica de comprovada necessidade e justificada nos termos da lei.</t>
+        </is>
+      </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>Análise no Art.º 7</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr"/>
+          <t>n.ºs 1, 2, 3 e 4 do art.º 7.º do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
+2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
+3 — São proibidas todas as violências contra animais, considerando-se como tais os atos consistentes em, sem necessidade, se infligir a morte, o sofrimento ou lesões a um animal.
+4 — É proibido utilizar animais para fins didáticos e lúdicos, de treino, filmagens, exibições, publicidade ou atividades semelhantes, na medida em que daí resultem para eles dor ou sofrimentos consideráveis, salvo experiência científica de comprovada necessidade e justificada nos termos da lei.</t>
+        </is>
+      </c>
       <c r="K3" s="8" t="inlineStr">
         <is>
-          <t>Análise no Art.º 7</t>
+          <t>O DL 276/2001 (Art.º 7.º) enuncia princípios gerais de bem-estar sem estrutura de cinco domínios. Os princípios (d) e (e) do Regulamento não têm correspondência. As obrigações específicas estão desenvolvidas nos arts. 8.º a 16.º do DL 276/2001.</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
         <is>
-          <t>Análise no Art.º 7</t>
+          <t>O @codigo (Arts. 4.º e 5.º) estabelece princípios gerais equivalentes mas sem a estrutura de cinco domínios explícitos do Regulamento. Os princípios (d) — relação positiva com os seres humanos — e (e) — otimização do estado mental e prevenção de comportamentos repetitivos anormais — não têm correspondência no @codigo. As obrigações específicas estão desenvolvidas nos arts. 13.º a 16.º e 46.º a 48.º do @codigo.</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
-          <t>Análise no Art.º 7</t>
+          <t>O @rgbeac (Art.º 7.º, n.º 1) enuncia cinco domínios de bem-estar em alíneas a) a e) análogas às do Regulamento — correspondência estrutural directa. Divergência: o Regulamento dirige-se exclusivamente aos operadores de estabelecimentos; o @rgbeac dirige-se a todos os cidadãos. O princípio (e) do Regulamento — otimização do estado mental e prevenção de comportamentos repetitivos anormais — não tem correspondência literal no @rgbeac: a alínea e) do @rgbeac refere apenas a proibição de stresse/medo/ansiedade. O domínio (d) do Regulamento — 'relação positiva com os seres humanos' — não consta do @rgbeac. As obrigações específicas para operadores são desenvolvidas nos arts. 9.º a 12.º e 47.º a 55.º do @rgbeac.</t>
         </is>
       </c>
       <c r="N3" s="11" t="inlineStr">
         <is>
-          <t>Regulamento especifica novos conceitos: estabelecer uma relação positiva com os seres humanos; otimizar o seu estado mental; prevenindo o desenvolvimento de comportamentos repetitivos anormais;</t>
+          <t>O Art.º 6.º do Regulamento codifica os 'Five Domains' de bem-estar animal como obrigação jurídica para operadores. Os diplomas nacionais reconhecem os primeiros três domínios (nutrição, ambiente físico, saúde) mas não desenvolvem explicitamente os domínios comportamental e mental tal como formulados no Regulamento. As obrigações específicas de cada princípio são desenvolvidas nos Arts. 14.º a 17.º do Regulamento, com correspondências nacionais detalhadas em cada artigo.</t>
         </is>
       </c>
       <c r="O3" s="11" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="P3" s="11" t="inlineStr"/>
@@ -1141,15 +1173,19 @@
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>Breve referência. Sem equivalência</t>
+          <t>O DL n.º 276/2001 não contém disposições específicas sobre estratégia de reprodução, limites etários para criadores, restrições de consanguinidade ou proibição de traços conformacionais excessivos. As normas de reprodução estão essencialmente remetidas para os artigos de alojamento (arts. 21.º a 26.º). Sem equivalência material ao Art.º 8.º do Regulamento.</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>O @codigo (art.º 8.º, n.º 2) exclui da reprodução animais com defeitos genéticos e malformações (monorquidia, displasia, rim poliquístico e alterações comportamentais) e proíbe cios sucessivos, mas não prevê o conceito de traços conformacionais excessivos nem a proibição de consanguinidade.</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="inlineStr"/>
+          <t>O @codigo (art.º 8.º, n.º 2) exclui da reprodução animais com defeitos genéticos e malformações (monorquidia, displasia, rim poliquístico e alterações comportamentais) e proíbe cios sucessivos, mas não prevê o conceito de traços conformacionais excessivos nem a proibição de consanguinidade próxima (pais/filhos, irmãos, avós/netos). Não proíbe a produção de híbridos. Não exige avaliação veterinária prévia ao acasalamento nem limita o número de descendentes por macho reprodutor.</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac (Art.º 70.º) prevê limites de idade para reprodução (cadelas 18 meses a 6 anos; gatas 12 meses a 6 anos; machos 12 meses a 7 anos), máximo de 4 ninhadas com intervalo mínimo de 12 meses, testes genéticos e de saúde e proibição de reprodução após 2 cesarianas — vários destes requisitos são mais detalhados que o Regulamento. O Art.º 70.º, n.º 7 remete para portaria a definição de coeficiente de consanguinidade e limite de descendentes por macho, sem proibição expressa de cruzamentos entre pais/filhos, irmãos ou avós/netos como o Regulamento. O conceito de 'características conformacionais excessivas' não está explicitado no @rgbeac, embora o n.º 8 proíba genericamente a reprodução quando se espere efeito prejudicial na saúde com base no fenótipo. A proibição de híbridos (espécies distintas) não consta do @rgbeac.</t>
+        </is>
+      </c>
       <c r="N5" s="11" t="inlineStr">
         <is>
           <t>Introduzir conceito de características conformacionais excessivas (a regular por ato delegado europeu até 2030); (2) proibir consanguinidade próxima (pais/filhos, irmãos, avós/netos); (3) proibir a produção de híbridos; (4) impor consulta veterinária prévia ao acasalamento de animais potencialmente afetados.
@@ -1510,11 +1546,19 @@
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>Conceito novo de ‘aprovação’ com limiar (&gt;5 ninhadas/ano ou &gt;5 cadelas/gatas)</t>
-        </is>
-      </c>
-      <c r="L7" s="9" t="inlineStr"/>
-      <c r="M7" s="10" t="inlineStr"/>
+          <t>Conceito de ‘aprovação’ específica de estabelecimentos de criação com limiar numérico (&gt;5 ninhadas/ano ou &gt;5 fêmeas) é novo no Regulamento, sem equivalente na legislação vigente. O DL n.º 276/2001 exige licença/autorização para alojamentos de hospedagem mas sem distinguir criadores por volume de atividade.</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>O @codigo (Art.º 37.º) publicita a lista de alojamentos de hospedagem, mas não prevê aprovação específica de estabelecimentos de criação com limiar numérico, nem revisão da aprovação por alteração das condições. O @codigo trata o licenciamento de criadores como parte do regime geral de alojamentos, sem o limiar específico do Regulamento.</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac (Art.º 62.º) divulga a lista de alojamentos autorizados através do balcão único eletrónico e do sítio da DGAV, mas não distingue ‘aprovação de estabelecimento de criação’ como procedimento específico com limiar numérico (&gt;5 ninhadas/ano ou &gt;5 fêmeas reprodutoras). O @rgbeac não exige revisão da aprovação por alteração das condições, nem prevê o mecanismo de consulta de aprovação por autoridades de outros Estados-Membros.</t>
+        </is>
+      </c>
       <c r="N7" s="11" t="inlineStr">
         <is>
           <t>Artigo novo no Regulamento, introduz aprovação formal de criadores com limiar numérico para ninhadas ou fêmeas no local.
@@ -1932,11 +1976,14 @@
 6 — Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr"/>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 (Art.º 12.º) tem disposições de nutrição substancialmente equivalentes às do @codigo (Art.º 46.º) e ao @rgbeac (Art.º 51.º): programa de alimentação bem definido, valor nutritivo adequado, refeições variadas, comedouros/bebedouros adequados, água potável ad libitum, higiene e refrigeração. Divergências face ao Regulamento: (1) não especifica dieta adaptada a raça, nível de atividade ou categoria do animal; (2) não exige transições alimentares graduais nem cuidados específicos de desmame; (3) não prevê obrigação de instalações de alimentação que previnam ferimentos, afogamento ou outros danos físicos; (4) não regula ajuste de frequência alimentar por conselho veterinário escrito.</t>
+        </is>
+      </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>Parece restringir as obrigações aos estabelecimentos.
-Apenas @código proíbe restos, pastelaria e desperdícios.</t>
+          <t>O @codigo (Art.º 46.º) restringe a aplicação das obrigações de nutrição aos estabelecimentos de criação, manutenção, venda, centros de recolha e instalações de hospedagem — não se aplica à detenção doméstica individual. O Regulamento dirige-se aos operadores em geral. O n.º 7 do Art.º 46.º do @codigo proíbe alimentar com restos de comida, pastelaria e desperdícios da indústria alimentar — requisito mais restritivo que o Regulamento, que apenas proíbe substâncias causadoras de sofrimento. O @codigo não prevê dieta adaptada a nível de atividade, categoria ou transições alimentares graduais (desmame), nem registro de ajuste de frequência por conselho veterinário escrito.</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr">
@@ -1948,8 +1995,7 @@
       </c>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>Regulamento introduz mais «categorias» - raça, categoria, nível de atividade e estado reprodutivo.
-Nenhum aborda transições alimentares graduais, cuidados específicos com desmame, segurança estrutural das instalações.</t>
+          <t>Regulamento introduz mais «categorias» de adaptação da dieta — raça, categoria, nível de atividade e estado reprodutivo — que os diplomas nacionais não contemplam. Nenhum dos diplomas nacionais aborda transições alimentares graduais, cuidados específicos com desmame, prevenção de ferimentos por instalações de alimentação, ou registo de ajuste de frequência por conselho veterinário. O @codigo é mais restritivo que o Regulamento na proibição de restos de comida e desperdícios.</t>
         </is>
       </c>
       <c r="O11" s="11" t="inlineStr">
@@ -2102,19 +2148,27 @@
 Artigo 15.º — Os alojamentos devem assegurar que as espécies animais neles mantidas não possam causar quaisquer riscos para a saúde e para a segurança de pessoas, outros animais e bens.</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr"/>
-      <c r="L12" s="9" t="inlineStr"/>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 (Arts. 8.º e 9.º) prevê espaço adequado às necessidades fisiológicas e etológicas, esconderijos, enriquecimento ambiental e fatores ambientais (temperatura, ventilação, luz). Não proíbe a manutenção permanente em contentores, não impõe acesso mínimo ao exterior nem contém o mecanismo de desvio por parecer veterinário escrito do Regulamento n.4. As dimensões mínimas das instalações para cada espécie e categoria constam de legislação complementar (portarias).</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>O @codigo (Arts. 13.º e 14.º) estabelece que os animais devem dispor de 'espaço adequado às necessidades fisiológicas e etológicas', possibilidade de exercício físico, esconderijos e enriquecimento ambiental. Não proíbe expressamente a manutenção permanente em contentores (Regulamento n.2) nem impõe acesso mínimo ao exterior (Regulamento n.4). Não regula dimensões mínimas das instalações nem a proibição de manutenção exclusiva no interior por mais de 8 semanas. O Art.º 14.º do @codigo prevê exigências de temperatura, ventilação, luz e obscuridade mas sem parâmetros quantitativos específicos.</t>
+        </is>
+      </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>@rgbeac prevê acesso diário a área de exercício exterior 2x/dia durante 30 minutos (= 1h total),</t>
+          <t>O @rgbeac (Art.º 47.º, n.º 6) prevê acesso diário a área de exercício exterior, pelo menos 2 vezes por dia, durante 30 minutos — mais específico que o Regulamento (mínimo 1h total). O @rgbeac não contém a proibição explícita de manutenção de cães &gt;8 semanas exclusivamente no interior (Regulamento n.4, primeira parte), nem o mecanismo de desvio desta proibição por parecer veterinário escrito. O @rgbeac não proíbe expressamente a manutenção permanente em contentores (Regulamento n.2), embora a exigência de espaço adequado às necessidades etológicas (Art.º 47.º, n.º 1) produza efeito equivalente.</t>
         </is>
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>N.º 2, Proibição expressa de manter cães ou gatos em contentores : não coberto, nenhum dos três diplomas contém esta proibição explícita.
-N.º 3 – Exceções ao uso de contentores (transporte, isolamento curto prazo, espetáculos, neonatos com termorregulação reduzida ou acompanhados da mãe) Não coberto
-N.º 4 – Proibição de manter cães &gt;8 semanas exclusivamente no interior; acesso diário ao exterior mínimo 1h total (ou passeio); desvio apenas por parecer veterinário escrito - Parcialmente coberto no n.º 6, art.º 47.º @rgbeac prevê acesso diário a área de exercício exterior 2x/dia durante 30 minutos (= 1h total), mas não contém a proibição explícita de manutenção exclusiva no interior nem o mecanismo de desvio por parecer veterinário escrito. Ausente no @codigo e @legislacao.
-Prever exceções para cães de guarda de rebanho</t>
+          <t>N.º 2 — Proibição expressa de manter cães ou gatos em contentores: não coberta por nenhum dos três diplomas de forma explícita.
+N.º 3 — Exceções ao uso de contentores (transporte, isolamento curto prazo, espetáculos, neonatos com termorregulação reduzida ou acompanhados da mãe): não coberta.
+N.º 4 — Proibição de manter cães &gt;8 semanas exclusivamente no interior; acesso diário ao exterior mínimo 1h total (ou passeio); desvio apenas por parecer veterinário escrito: parcialmente coberto pelo @rgbeac (art.º 47.º, n.º 6) mas ausente no @codigo e @legislacao.
+Necessidade de portaria complementar com especificações técnicas de alojamento por espécie/categoria.</t>
         </is>
       </c>
       <c r="O12" s="11" t="inlineStr">
@@ -2325,59 +2379,81 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>RGBEAC (proposta, jun. 2025) - Artigos 7 a 12 e 52º</t>
+          <t>Arts. 47.º e 52.º (n.º 7) do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Analisado no Art.º 8.º do Reg.
-Especificação clara: 'exercício físico e estímulo mental', 'Contato social adequado'. (Art.º 10.º).
-Métodos de 'reforço positivo' (OBRIGATÓRIO).
-Proibição explícita de 'métodos aversivos, punitivos ou violentos'.
-n.º 7, do art.º 52.º
-Todos os alojamentos para hospedagem de cães e gatos, à exceção dos alojamentos com fins higiénicos, devem dispor de um plano de socialização e enriquecimento ambiental.
-(Documentação obrigatória de estratégia de socialização - criadores).
-Fatores de socialização também previstos no treino dos perigosos e PP.</t>
+          <t>Artigo 47.º — Condições dos alojamentos
+1 - Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
+a) A prática de exercício físico adequado;
+b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
+2 - Os animais devem dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.
+3 - [dim]As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar.[/dim]
+4 - As instalações devem providenciar um enriquecimento ambiental complexo e estimulante de acordo com as necessidades específicas dos animais que albergam, incluindo materiais e equipamento que estimulem a expressão do repertório de comportamentos naturais, nomeadamente materiais para substrato, cama ou ninhos, ramos, buracos, locais para banhos, brinquedos e outros adequados ao fim em vista.
+5 - [dim]As estruturas físicas das instalações, todo o equipamento nelas introduzido e a vegetação não podem representar ameaça ao bem-estar dos animais, designadamente não podem conter objetos ou equipamentos perigosos para os animais.[/dim]
+6 – Os cães devem ter acesso diário a uma área de exercício fora do seu alojamento habitual, pelo menos duas vezes por dia, durante 30 minutos.
+7 – As áreas de exercício referidas no número anterior devem incluir equipamento de enriquecimento ambiental e agilidade, incluindo piscinas, plataformas elevadas e outros adequados ao fim em vista.
+Artigo 52.º — Maneio (excerto)
+7 – Todos os alojamentos para hospedagem de cães e gatos, à exceção dos alojamentos com fins higiénicos, devem dispor de um plano de socialização e enriquecimento ambiental.</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Arts. 5.º e 13.º do Código do Animal (DL 214/2013)</t>
+          <t>Art.º 13.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Artigo 5.º - Princípios que proíbem violência e maus-tratos, garantem bem-estar.
-Artigo 13.º - Espaço para exercício físico e expressão de comportamentos naturais.
-Analisado no art.º 8.º do Reg.</t>
+          <t>Artigo 13.º — Condições dos alojamentos
+1 - Os animais devem dispor de um espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
+a) A prática de exercício físico adequado;
+b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
+2 - Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.
+3 - [dim]As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar.[/dim]
+4 - [dim]As estruturas físicas das instalações, todo o equipamento nelas introduzido e a vegetação, não podem representar nenhum tipo de ameaça ao bem-estar dos animais, designadamente não podem possuir objetos ou equipamentos perigosos para os animais.[/dim]
+5 - As instalações devem ser equipadas de acordo com as necessidades específicas dos animais que albergam, com materiais e equipamento que estimulem a expressão dos comportamentos naturais, nomeadamente material para substrato, cama ou ninhos, ramos, buracos, locais para banhos e outros quaisquer adequados ao fim em vista.</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>Decreto-Lei n.º 276/2001 - Artigo 8.º</t>
+          <t>art.º 8.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>1 — Os animais devem dispor de um espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir: a) A prática de exercício físico adequado; b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
-2 — Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.</t>
-        </is>
-      </c>
-      <c r="K14" s="8" t="inlineStr"/>
+          <t>1 — Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
+a) A prática de exercício físico adequado;
+b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
+2 — Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.
+3 — [dim]As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar.[/dim]
+4 — [dim]As estruturas físicas das instalações, todo o equipamento nelas introduzido e a vegetação não podem representar nenhum tipo de ameaça ao bem-estar dos animais, designadamente não podem possuir objetos ou equipamentos perigosos para os animais.[/dim]
+5 — As instalações devem ser equipadas de acordo com as necessidades específicas dos animais que albergam, com materiais e equipamento que estimulem a expressão do repertório de comportamentos naturais, nomeadamente material para substrato, cama ou ninhos, ramos, buracos, locais para banhos e outros quaisquer adequados ao fim em vista.</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 (art.º 8.º) prevê genericamente que os animais devem 'dispor de um espaço adequado às suas necessidades fisiológicas e etológicas' e de 'esconderijos', mas sem requisitos de socialização, enriquecimento documentado ou estratégia formal. A Portaria n.º 148/2016 regula o registo de cães em matilhas de caça maior (junto do ICNF, I. P.) mas não fixa normas de bem-estar comportamental para esses cães. O @rgbeac (art.º 10.º, n.º 3) isenta expressamente os cães utilizados na caça durante os atos venatórios da obrigação de trela — o que representa uma derrogação análoga (embora com âmbito e fundamento distintos) à derrogação do n.º 4 do Art.º 17.º do Regulamento para cães militares/policiais/aduaneiros. Não existe, no entanto, na legislação nacional, qualquer equivalente à isenção de socialização para cães de proteção de gado ou de pastoreio em transumância.</t>
+        </is>
+      </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>Sem especificações sobre socialização e enriquecimento</t>
+          <t>O @codigo (DL 214/2013) não contém especificações sobre socialização, enriquecimento ambiental ou estratégia documentada de socialização por parte dos criadores. O art.º 13.º prevê genericamente 'espaço para exercício físico e expressão de comportamentos naturais', mas sem os requisitos quantitativos ou processuais do Regulamento. Não inclui as derrogações para cães funcionais.</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>Cobertura mais significtiva</t>
-        </is>
-      </c>
-      <c r="N14" s="11" t="inlineStr"/>
+          <t>O @rgbeac (Art.º 47.º, n.º 4) prevê 'enriquecimento ambiental complexo e estimulante' e o Art.º 47.º, n.º 6 impõe acesso diário a área de exercício, pelo menos 2 vezes por dia durante 30 minutos — obrigação mais específica que o Regulamento. O n.º 7 do Art.º 52.º do @rgbeac impõe 'plano de socialização e enriquecimento ambiental' a todos os alojamentos de hospedagem, mas não especifica 'estratégia documentada de socialização' exclusiva para criadores. Derrogações não contempladas: (1) isenção dos cães de proteção de gado («livestock guardian dogs») dos requisitos de socialização durante períodos de guarda/treino; (2) isenção dos cães de pastoreio durante transumância sazonal; (3) isenção de cães militares/policiais/aduaneiros da proibição de acorrentamento superior a 1 hora.</t>
+        </is>
+      </c>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>O Regulamento introduz obrigações novas sem equivalente nacional: (1) proibição de acorrentamento superior a 1 hora (com isenção para cães militares, policiais e aduaneiros); (2) obrigação de estratégia documentada de socialização por parte dos criadores; (3) isenção explícita de socialização para cães de proteção de gado ("livestock guardian dogs") durante guarda/treino e para cães de pastoreio em transumância sazonal. Em Portugal, a realidade dos cães de caça (matilhas) é relevante: a Portaria n.º 148/2016 exige registo mas não impõe normas de bem-estar comportamental. O Regulamento não inclui derrogação explícita para cães de caça — estes estão abrangidos pelas obrigações gerais do Art.º 17.º enquanto permanecerem em estabelecimentos de criação ou venda.</t>
+        </is>
+      </c>
       <c r="O14" s="11" t="inlineStr">
         <is>
-          <t>Em análise. RGBEAC alinha melhor; implementação de reforço positivo obrigatório recomendada</t>
+          <t>Sim — necessidade de: (1) criar regime de proibição de acorrentamento superior a 1 hora com as isenções previstas; (2) impor estratégia documentada de socialização aos criadores; (3) clarificar o estatuto dos cães de caça e matilhas face às obrigações comportamentais.</t>
         </is>
       </c>
       <c r="P14" s="11" t="inlineStr"/>
@@ -2478,22 +2554,29 @@
 2 — O documento referido no número anterior deve ter a forma de um atestado, do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura.</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr"/>
-      <c r="L15" s="9" t="inlineStr"/>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 (arts. 17.º e 18.º) exige que as intervenções cirúrgicas (incluindo corte de caudas) sejam realizadas por médico veterinário e que as amputações estejam documentadas por atestado. Não existe proibição expressa de corte de cauda anterior a 2013. O @rgbeac e o @codigo já proíbem o corte de cauda desde 2015 (art.º 52.º, n.º 3 do @codigo), o que excede o regime do Regulamento no que respeita a cães de caça (o Regulamento admite a excepção profilática que poderia ser invocada para justificar o corte de cauda em cães de caça). A derrogação do n.º 5 do Art.º 18.º para cães militares, policiais e aduaneiros não tem equivalente na legislação nacional. A proibição de coleiras de espinhos e de estrangulamento sem paragem de segurança não consta expressamente da legislação nacional vigente (embora o uso de 'aguilhões' e instrumentos perfurantes na condução de animais seja proibido pela Lei n.º 92/95).</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>O @codigo (DL 214/2013) proíbe mutilações com fins não curativos (art.º 52.º, n.º 1), incluindo corte de orelhas, cordas vocais, garras ou unhas, dentes ou presas. O art.º 52.º, n.º 3 proíbe o corte de cauda para todos os cães nascidos a partir de 1 de Janeiro de 2015 — regime mais restritivo que o Regulamento, que admite corte de cauda por razões profiláticas (incluindo potencialmente para cães de caça). O @codigo exige atestado veterinário (n.º 4) alinhado com o n.º 2 do Art.º 18.º. Não cobre explicitamente a proibição de coleiras de espinhos (prong collars) nem de coleiras de estrangulamento sem paragem de segurança prevista no n.º 5, als. (e) e (f) do Regulamento.</t>
+        </is>
+      </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>@rgbeac ressalva expressamente o corte das orelhas que não seja realizada para fins de identificação de animais esterilizados conforme boas práticas internacionais", o que cobre o essencial desta derrogação.</t>
+          <t>O @rgbeac (art.º 12.º, al. i)) proíbe intervenções cirúrgicas com objectivo de modificar a aparência, incluindo 'corte da cauda, secção das cordas vocais, remoção de unhas ou dentes, e corte das orelhas que não seja realizada para fins de identificação de animais esterilizados conforme boas práticas internacionais'. O art.º 34.º do @rgbeac exige atestado veterinário para qualquer intervenção curativa que modifique a aparência, alinhando com o n.º 2 do Art.º 18.º do Regulamento. O @rgbeac também proíbe coleiras elétricas, de choques, estranguladores e açaimos fechados (art.º 12.º, al. aa)), convergindo com o n.º 5 do Art.º 18.º. A derrogação do Art.º 18.º, n.º 3, sobre corte de orelha de gatos em programas TNR está coberta pela ressalva do @rgbeac ('fins de identificação de animais esterilizados conforme boas práticas internacionais').</t>
         </is>
       </c>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>exige expressamente anestesia e analgesia prolongada como condição do procedimento.
-Rever proibições na análise do art.7.º</t>
+          <t>Portugal está em grande medida alinhado com o Regulamento no que respeita à proibição de mutilações: o corte de cauda já é proibido desde 2015 (mais restritivo do que o Regulamento, que admite excepção profilática para cães de caça). Os principais gaps são: (1) ausência de proibição expressa de coleiras de espinhos (prong collars) e de estrangulamento sem paragem de segurança; (2) ausência de derrogação específica para cães militares, policiais e aduaneiros; (3) necessidade de clarificar que a excepção profilática do Art.º 18.º, n.º 1 não se aplica ao corte de cauda de cães de caça em Portugal (o @codigo e @rgbeac são mais restritivos). Exige anestesia e analgesia prolongada como condição obrigatória para qualquer procedimento justificado — requisito que a legislação nacional não especifica explicitamente.</t>
         </is>
       </c>
       <c r="O15" s="11" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim — necessidade de: (1) proibir expressamente coleiras de espinhos e de estrangulamento sem paragem de segurança; (2) clarificar o âmbito da excepção profilática face ao regime mais restritivo nacional; (3) confirmar conformidade do regime de atestado veterinário com os requisitos documentais do Art.º 18.º, n.º 2.</t>
         </is>
       </c>
       <c r="P15" s="11" t="inlineStr"/>
@@ -2935,15 +3018,19 @@
 4 - No caso de anúncios de animais de raça indeterminada é proibida qualquer referência a raças no texto do anúncio.</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr"/>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 (Art.º 57.º) permite publicitar animais de companhia na Internet mas proíbe a venda em linha — apenas em local de criação ou estabelecimentos licenciados. O DL n.º 82/2019 (Art.º 53.º) estabelece requisitos para anúncios de transmissão (identificação, raça, informação sanitária) mas sem a especificidade dos requisitos do Regulamento para plataformas digitais.</t>
+        </is>
+      </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>Apenas proíbe a venda de animais de companhia sem documentação adequada e restringe a comercialização de animais com comportamentos perigosos. As disposições cobrem identificação obrigatória e informações sobre o animal antes da venda.</t>
+          <t>O @codigo (Art.º 80.º) proíbe a venda pela Internet e exige documentação adequada. Cobre a identificação obrigatória e informações sobre o animal antes da venda. Não inclui os requisitos de informação específica exigidos pelo Regulamento para anúncios em linha (número de registo do operador, informação sobre saúde, socialização e comportamento).</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>SIM - Proibição clara de publicidade e venda online, com requisitos de local licenciado</t>
+          <t>O @rgbeac (Art.º 91.º) proíbe a venda de cães, gatos e furões através da Internet e exige que a transmissão decorra presencialmente em alojamentos autorizados, convergindo com o Regulamento na proibição da venda em linha. No entanto, os requisitos específicos do Regulamento sobre informação obrigatória em anúncios (número de registo, informação de bem-estar, rastreabilidade) vão além do que o @rgbeac prevê explicitamente.</t>
         </is>
       </c>
       <c r="N18" s="11" t="inlineStr">
@@ -3170,15 +3257,19 @@
           <t>DL 82/2019 estabelece o SIAC com extensas disposições cobrindo: criação da base de dados, procedimentos de registo e controlos de acesso, gestão por DGAV, identificação eletrónica via transponder, segurança de dados e autorização de acesso, integração de registos de identificação de animais, gestão da distribuição de dispositivos de identificação, procedimentos de registo e atualização. O sistema é operacional desde 2019.</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr"/>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 82/2019 operacionalizou o SIAC como sistema nacional de identificação e registo de animais de companhia (cães, gatos e furões), com registo centralizado sob responsabilidade da DGAV, identificação por microchip e dados sanitários. O SIAC cobre os requisitos fundamentais do Art.º 23.º do Regulamento. Lacuna: ausência de disposição sobre interoperabilidade com bases de dados de outros Estados-Membros da UE.</t>
+        </is>
+      </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>Código do Animal estabelece estrutura completa com classificações</t>
+          <t>O @codigo (Art.º 53.º) estabelece estrutura completa de identificação e registo com classificações (normal/perigoso/potencialmente perigoso), integra dados de saúde. Alinhado com os requisitos de base de dados do Regulamento. Sem disposições sobre interoperabilidade entre Estados-Membros.</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
-          <t>Reafirma e fortalece o sistema SIAC</t>
+          <t>O @rgbeac (Art.º 20.º) reafirma e fortalece o sistema SIAC, alargando o âmbito de dados registados (comportamento, bem-estar, histórico sanitário). Alinhado com os requisitos de base de dados do Regulamento. O @rgbeac não especifica mecanismos de interoperabilidade com bases de dados de outros Estados-Membros, que o Regulamento exige.</t>
         </is>
       </c>
       <c r="N20" s="11" t="inlineStr">
@@ -3236,20 +3327,24 @@
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr"/>
-      <c r="K21" s="8" t="inlineStr"/>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 82/2019 prevê recolha de dados no SIAC (identificação, saúde, registos) mas não estabelece obrigação de reporte periódico à Comissão Europeia sobre indicadores de bem-estar animal. A legislação vigente não prevê o mecanismo trienal de relatório ao nível nacional nem a consolidação de dados por categorias de operadores.</t>
+        </is>
+      </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>Análise no Anexo III</t>
+          <t>O @codigo não prevê mecanismo de recolha de dados sobre bem-estar animal para fins de reporte à Comissão Europeia. Os dados de identificação e registo são recolhidos pelo SIAC mas não consolidados para os indicadores do Regulamento.</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
-          <t>Análise no Anexo III</t>
+          <t>O @rgbeac (Art.º 46.º) prevê relatório anual de gestão dos centros de bem-estar animal, mas não tem equivalente ao mecanismo de recolha de dados e relatório trienal à Comissão Europeia exigido pelo Regulamento. Não há disposição sobre indicadores de bem-estar animal baseados em animais para reporte à UE.</t>
         </is>
       </c>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>necessário: alinhamento da periodicidade de relatórios (atualmente anual; Regulamento requer trienal) e inclusão dos dados específicos de Annex III da EU (quando publicado).</t>
+          <t>Necessário: alinhamento da periodicidade de relatórios (atualmente anual para centros de recolha; Regulamento requer trienal à Comissão) e inclusão dos dados específicos de Annex III da EU (quando publicado).</t>
         </is>
       </c>
       <c r="O21" s="11" t="inlineStr">
@@ -3339,15 +3434,19 @@
 1 - Os animais de companhia abrangidos pela obrigação de identificação devem ser registados pelo médico veterinário no SIAC, imediatamente após a sua marcação com o transponder, em nome do respetivo titular.</t>
         </is>
       </c>
-      <c r="K22" s="8" t="inlineStr"/>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 82/2019 (Art.º 20.º) estabelece que o SIAC é operado em conformidade com a legislação de proteção de dados (Regulamento (UE) 2016/679 — RGPD). A legislação vigente implementa os requisitos do Art.º 25.º do Regulamento. Sem lacunas identificadas.</t>
+        </is>
+      </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>Cobertura expressa em Art. 55.º</t>
+          <t>O @codigo (Art.º 55.º) prevê cobertura expressa de proteção de dados em conformidade com legislação aplicável. Alinhado com os requisitos do Regulamento.</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
-          <t>Implementação completa em Arts. 20.º</t>
+          <t>O @rgbeac (Art.º 20.º, n.º 8) prevê que o tratamento de dados pessoais no âmbito do SIAC observa o regime geral de proteção de dados — implementação completa dos requisitos do Regulamento.</t>
         </is>
       </c>
       <c r="N22" s="11" t="inlineStr">
@@ -3554,23 +3653,27 @@
       <c r="J24" s="7" t="inlineStr"/>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>Sem equivalência.</t>
+          <t>Sem equivalência — artigo de habilitação delegada da Comissão Europeia, sem correspondência em legislação nacional.</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>Sem equivalência.</t>
+          <t>Sem equivalência — artigo de habilitação delegada da Comissão Europeia, sem correspondência em proposta nacional.</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>Sem equivalência.</t>
-        </is>
-      </c>
-      <c r="N24" s="11" t="inlineStr"/>
+          <t>Sem equivalência — artigo de habilitação delegada da Comissão Europeia, sem correspondência em proposta nacional.</t>
+        </is>
+      </c>
+      <c r="N24" s="11" t="inlineStr">
+        <is>
+          <t>Artigo de habilitação delegada — confere poderes à Comissão para actualizar os Anexos com base em evidência científica. Implica que os requisitos técnicos dos Anexos (espaço por animal, temperatura, iluminação, etc.) poderão ser actualizados sem necessidade de co-decisão do Parlamento/Conselho. Para Portugal, implica monitorização contínua das actualizações dos Anexos e adaptação da legislação complementar (portarias) sempre que os Anexos forem alterados.</t>
+        </is>
+      </c>
       <c r="O24" s="11" t="inlineStr">
         <is>
-          <t>sem equivalência</t>
+          <t>Sem necessidade de alteração directa — obrigação de acompanhamento e transposição das actualizações dos Anexos.</t>
         </is>
       </c>
       <c r="P24" s="11" t="inlineStr">
@@ -3701,23 +3804,27 @@
       <c r="J26" s="7" t="inlineStr"/>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Não se aplica — artigo de procedimento institucional europeu.</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Não se aplica — artigo de procedimento institucional europeu.</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="N26" s="11" t="inlineStr"/>
+          <t>Não se aplica — artigo de procedimento institucional europeu.</t>
+        </is>
+      </c>
+      <c r="N26" s="11" t="inlineStr">
+        <is>
+          <t>Artigo processual sobre procedimento de comité — designa o Comité Permanente dos Vegetais, Animais e dos Alimentos para Consumo Humano e Animal como comité assistente da Comissão para atos de execução do Regulamento. Sem impacto directo na legislação nacional.</t>
+        </is>
+      </c>
       <c r="O26" s="11" t="inlineStr">
         <is>
-          <t>Não - Artigo processual sobre procedimento de comité — assistência à Comissão Europeia.</t>
+          <t>Não — artigo processual sobre procedimento de comité europeu.</t>
         </is>
       </c>
       <c r="P26" s="11" t="inlineStr"/>
@@ -3767,23 +3874,27 @@
       <c r="J27" s="7" t="inlineStr"/>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Relevante: o DL n.º 276/2001 (Art.º 57.º) permite publicitar animais na Internet mas proíbe a venda online — medida mais restritiva que o Regulamento. Portugal deverá notificar a Comissão desta disposição nacional mais restritiva ao abrigo do n.º 2 do Art.º 30.º do Regulamento.</t>
         </is>
       </c>
       <c r="L27" s="9" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Relevante: o @codigo (Art.º 80.º) proíbe a venda de animais de companhia pela Internet — medida mais restritiva que o Regulamento. Portugal poderá manter esta proibição ao abrigo do n.º 1.</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="N27" s="11" t="inlineStr"/>
+          <t>Relevante: o @rgbeac (Art.º 12.º, als. m) a r)) proíbe a venda online de cães, gatos e furões — medida mais restritiva que o Regulamento, que apenas exige requisitos de informação para venda em linha. Portugal poderá manter esta proibição ao abrigo do n.º 1.</t>
+        </is>
+      </c>
+      <c r="N27" s="11" t="inlineStr">
+        <is>
+          <t>Portugal detém várias disposições nacionais mais restritivas que o Regulamento — nomeadamente a proibição de venda online de cães, gatos e furões (DL 276/2001, Art.º 57.º; @codigo Art.º 80.º; @rgbeac Art.º 12.º). Estas disposições são compatíveis com o Regulamento ao abrigo do n.º 1. Obrigação de notificação à Comissão Europeia nos termos do n.º 2: Portugal deve comunicar as medidas mais restritivas que pretenda manter no prazo de dois anos após a entrada em vigor do Regulamento.</t>
+        </is>
+      </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Não — mas obrigação de notificação das medidas nacionais mais restritivas à Comissão nos termos do n.º 2.</t>
         </is>
       </c>
       <c r="P27" s="11" t="inlineStr"/>
@@ -3905,23 +4016,27 @@
       <c r="J29" s="7" t="inlineStr"/>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>O DL n.º 276/2001 (Arts. 66.º a 72.º) estabelece o regime de contraordenações e coimas para infracções. Portugal já dispõe de regime sancionatório aplicável — necessidade de verificar se as sanções existentes são suficientemente efetivas, proporcionadas e dissuasivas para as infracções ao Regulamento, e de notificar a Comissão.</t>
         </is>
       </c>
       <c r="L29" s="9" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>O @codigo (Arts. 88.º a 97.º) estabelece o regime de contraordenações e sanções para infracções à legislação de bem-estar animal. O Regulamento não fixa os montantes — remete para os Estados-Membros.</t>
         </is>
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="N29" s="11" t="inlineStr"/>
+          <t>Artigo de habilitação nacional — o @rgbeac (Arts. 138.º a 160.º) contém o regime sancionatório nacional. O Regulamento não fixa sanções — remete para os Estados-Membros a obrigação de estabelecerem sanções efetivas, proporcionadas e dissuasivas.</t>
+        </is>
+      </c>
+      <c r="N29" s="11" t="inlineStr">
+        <is>
+          <t>Artigo de habilitação nacional para sanções. Portugal dispõe de regime sancionatório no DL 276/2001 (Arts. 66.º-72.º), @codigo (Arts. 88.º-97.º) e @rgbeac (Arts. 138.º-160.º). Obrigação de: (1) verificar se as sanções existentes cobrem todas as infracções ao Regulamento, em particular o abandono por operadores; (2) garantir proporcionalidade e carácter dissuasivo; (3) notificar a Comissão das regras de sanções e de qualquer alteração ulterior.</t>
+        </is>
+      </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>Responsabilidade dos Estados-Membros em estabelecer sanções e notificar a Comissão destas, e de qualquer alteração ulterior das mesmas.</t>
+          <t>Verificar cobertura completa e notificar a Comissão das sanções nacionais aplicáveis.</t>
         </is>
       </c>
       <c r="P29" s="11" t="inlineStr"/>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -762,22 +762,54 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Análise no Art.º 7</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr"/>
+          <t>Art.º 7.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1 – Todos têm o dever de garantir condições de bem-estar aos animais de companhia, em especial que:
+a) não passem fome ou sede, nem sejam sujeitos a malnutrição;
+b) não sejam expostos a situações de desconforto físico ou térmico;
+c) não sofram dor, lesão física ou doença;
+d) possam expressar padrões normais de comportamento; e
+e) não sejam colocados em situações que lhes provoquem stresse, medo ou ansiedade injustificados.
+2 - As condições de detenção e de alojamento dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
+3 - Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no presente decreto-lei ou se não se adaptar ao cativeiro.</t>
+        </is>
+      </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Análise no Art.º 7</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr"/>
+          <t>Arts. 4.º e 5.º do Código do Animal (DL n.º 214/2013)</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 4.º — Detenção responsável
+Cabe aos detentores de animais de companhia assegurar as necessidades básicas de bem-estar dos mesmos, garantir o controlo da sua reprodução, salvaguardar a sua saúde e prevenir os riscos inerentes à transmissão de doenças a pessoas e a outros animais e, ainda, a segurança das populações, garantindo a salubridade dos locais e a tranquilidade das pessoas.
+Artigo 5.º — Princípios básicos para o bem-estar dos animais
+1 - As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal.
+2 - Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
+3 - É proibida a violência contra animais, considerando-se como tal todos os atos que, sem necessidade, infligem a morte, o sofrimento, abuso ou lesões a um animal, designadamente os seguintes:
+a) Agredir animais, nomeadamente com o uso de chicotes, estimulantes elétricos ou objetos contundentes ou perfurantes, ou com murros, bofetadas ou pontapés;
+b) Restringir a liberdade de movimentos dos animais de tal forma que lhes seja impedido levantar-se, deitar-se ou virar-se sobre si próprios;
+c) Usar equipamentos de maneio, contenção ou treino, que causem sofrimento desnecessário ou lesões aos animais;
+d) Incitar, realizar ou promover lutas entre animais de companhia, quando destas possa resultar sofrimento, lesões ou morte dos animais.
+4 - É proibido utilizar animais para fins didáticos e lúdicos, de treino, filmagens, exibições, publicidade ou atividades semelhantes, sempre que daí resultem para aqueles dor ou sofrimentos consideráveis, salvo experiência científica de comprovada necessidade e justificada nos termos da lei.</t>
+        </is>
+      </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>Análise no Art.º 7</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr"/>
+          <t>n.ºs 1, 2, 3 e 4 do art.º 7.º do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
+2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
+3 — São proibidas todas as violências contra animais, considerando-se como tais os atos consistentes em, sem necessidade, se infligir a morte, o sofrimento ou lesões a um animal.
+4 — É proibido utilizar animais para fins didáticos e lúdicos, de treino, filmagens, exibições, publicidade ou atividades semelhantes, na medida em que daí resultem para eles dor ou sofrimentos consideráveis, salvo experiência científica de comprovada necessidade e justificada nos termos da lei.</t>
+        </is>
+      </c>
       <c r="K3" s="8" t="inlineStr">
         <is>
           <t>Análise no Art.º 7</t>
@@ -1152,7 +1184,7 @@
       <c r="M5" s="10" t="inlineStr"/>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>Introduzir conceito de características conformacionais excessivas (a regular por ato delegado europeu até 2030); (2) proibir consanguinidade próxima (pais/filhos, irmãos, avós/netos); (3) proibir a produção de híbridos; (4) impor consulta veterinária prévia ao acasalamento de animais potencialmente afetados.
+          <t>Introduzir conceito de características conformacionais excessivas (a regular por ato delegado europeu até 2030); (2) proibir consanguinidade próxima (pais/filhos, irmãos, avós/netos); (3) proibir a produção de híbridos; (4) impor consulta veterinária prévia ao acasalamento de animais potencialmente afetados. 
 ANNEX I, Ponto 3 estabelece requisitos técnicos obrigatórios de saúde reprodutiva. Recomenda-se: (i) incorporar idade mínima 10 meses (gatas) e 2º estro (cadelas); (ii) estabelecer máximo imperativo de 3 ninhadas em 2 anos (sem exceções veterinárias); (iii) exigir período de recuperação 1 ano após atingir limite; (iv) proibir uso após 2 cesarianas; (v) exigir avaliação veterinária escrita para cadelas ≥8 anos e gatas ≥6 anos.</t>
         </is>
       </c>
@@ -1810,7 +1842,7 @@
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>Estabelece a obrigação de ter médico veterinário responsável que execute 'programas e ações' para saúde e bem-estar,
+          <t>Estabelece a obrigação de ter médico veterinário responsável que execute 'programas e ações' para saúde e bem-estar, 
 Não fixa prazos para avaliações de bem-estar nem obrigações de manutenção de registos estruturados, conforme @regulamento</t>
         </is>
       </c>
@@ -2111,9 +2143,9 @@
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>N.º 2, Proibição expressa de manter cães ou gatos em contentores : não coberto, nenhum dos três diplomas contém esta proibição explícita.
+          <t>N.º 2, Proibição expressa de manter cães ou gatos em contentores : não coberto, nenhum dos três diplomas contém esta proibição explícita. 
 N.º 3 – Exceções ao uso de contentores (transporte, isolamento curto prazo, espetáculos, neonatos com termorregulação reduzida ou acompanhados da mãe) Não coberto
-N.º 4 – Proibição de manter cães &gt;8 semanas exclusivamente no interior; acesso diário ao exterior mínimo 1h total (ou passeio); desvio apenas por parecer veterinário escrito - Parcialmente coberto no n.º 6, art.º 47.º @rgbeac prevê acesso diário a área de exercício exterior 2x/dia durante 30 minutos (= 1h total), mas não contém a proibição explícita de manutenção exclusiva no interior nem o mecanismo de desvio por parecer veterinário escrito. Ausente no @codigo e @legislacao.
+N.º 4 – Proibição de manter cães &gt;8 semanas exclusivamente no interior; acesso diário ao exterior mínimo 1h total (ou passeio); desvio apenas por parecer veterinário escrito - Parcialmente coberto no n.º 6, art.º 47.º @rgbeac prevê acesso diário a área de exercício exterior 2x/dia durante 30 minutos (= 1h total), mas não contém a proibição explícita de manutenção exclusiva no interior nem o mecanismo de desvio por parecer veterinário escrito. Ausente no @codigo e @legislacao. 
 Prever exceções para cães de guarda de rebanho</t>
         </is>
       </c>
@@ -2325,42 +2357,56 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>RGBEAC (proposta, jun. 2025) - Artigos 7 a 12 e 52º</t>
+          <t>Arts. 47.º e 52.º (n.º 7) do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Analisado no Art.º 8.º do Reg.
-Especificação clara: 'exercício físico e estímulo mental', 'Contato social adequado'. (Art.º 10.º).
-Métodos de 'reforço positivo' (OBRIGATÓRIO).
-Proibição explícita de 'métodos aversivos, punitivos ou violentos'.
-n.º 7, do art.º 52.º
-Todos os alojamentos para hospedagem de cães e gatos, à exceção dos alojamentos com fins higiénicos, devem dispor de um plano de socialização e enriquecimento ambiental.
-(Documentação obrigatória de estratégia de socialização - criadores).
-Fatores de socialização também previstos no treino dos perigosos e PP.</t>
+          <t>Artigo 47.º — Condições dos alojamentos
+1 - Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
+a) A prática de exercício físico adequado;
+b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
+2 - Os animais devem dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.
+3 - [dim]As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar.[/dim]
+4 - As instalações devem providenciar um enriquecimento ambiental complexo e estimulante de acordo com as necessidades específicas dos animais que albergam, incluindo materiais e equipamento que estimulem a expressão do repertório de comportamentos naturais, nomeadamente materiais para substrato, cama ou ninhos, ramos, buracos, locais para banhos, brinquedos e outros adequados ao fim em vista.
+5 - [dim]As estruturas físicas das instalações, todo o equipamento nelas introduzido e a vegetação não podem representar ameaça ao bem-estar dos animais, designadamente não podem conter objetos ou equipamentos perigosos para os animais.[/dim]
+6 – Os cães devem ter acesso diário a uma área de exercício fora do seu alojamento habitual, pelo menos duas vezes por dia, durante 30 minutos.
+7 – As áreas de exercício referidas no número anterior devem incluir equipamento de enriquecimento ambiental e agilidade, incluindo piscinas, plataformas elevadas e outros adequados ao fim em vista.
+Artigo 52.º — Maneio (excerto)
+7 – Todos os alojamentos para hospedagem de cães e gatos, à exceção dos alojamentos com fins higiénicos, devem dispor de um plano de socialização e enriquecimento ambiental.</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Arts. 5.º e 13.º do Código do Animal (DL 214/2013)</t>
+          <t>Art.º 13.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Artigo 5.º - Princípios que proíbem violência e maus-tratos, garantem bem-estar.
-Artigo 13.º - Espaço para exercício físico e expressão de comportamentos naturais.
-Analisado no art.º 8.º do Reg.</t>
+          <t>Artigo 13.º — Condições dos alojamentos
+1 - Os animais devem dispor de um espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
+a) A prática de exercício físico adequado;
+b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
+2 - Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.
+3 - [dim]As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar.[/dim]
+4 - [dim]As estruturas físicas das instalações, todo o equipamento nelas introduzido e a vegetação, não podem representar nenhum tipo de ameaça ao bem-estar dos animais, designadamente não podem possuir objetos ou equipamentos perigosos para os animais.[/dim]
+5 - As instalações devem ser equipadas de acordo com as necessidades específicas dos animais que albergam, com materiais e equipamento que estimulem a expressão dos comportamentos naturais, nomeadamente material para substrato, cama ou ninhos, ramos, buracos, locais para banhos e outros quaisquer adequados ao fim em vista.</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>Decreto-Lei n.º 276/2001 - Artigo 8.º</t>
+          <t>art.º 8.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>1 — Os animais devem dispor de um espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir: a) A prática de exercício físico adequado; b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
-2 — Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.</t>
+          <t>1 — Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
+a) A prática de exercício físico adequado;
+b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
+2 — Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.
+3 — [dim]As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar.[/dim]
+4 — [dim]As estruturas físicas das instalações, todo o equipamento nelas introduzido e a vegetação não podem representar nenhum tipo de ameaça ao bem-estar dos animais, designadamente não podem possuir objetos ou equipamentos perigosos para os animais.[/dim]
+5 — As instalações devem ser equipadas de acordo com as necessidades específicas dos animais que albergam, com materiais e equipamento que estimulem a expressão do repertório de comportamentos naturais, nomeadamente material para substrato, cama ou ninhos, ramos, buracos, locais para banhos e outros quaisquer adequados ao fim em vista.</t>
         </is>
       </c>
       <c r="K14" s="8" t="inlineStr"/>
@@ -2621,22 +2667,22 @@
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>— Cães/gatos em concursos/exposições</t>
+          <t>Cães/gatos em concursos/exposições</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>— Cães/gatos em concursos/exposições e acrescenta adoções
-— Parecer MVM vinculativo</t>
+          <t>Cães/gatos em concursos/exposições e acrescenta adoções
+Parecer MVM vinculativo</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
-          <t>— Todos animais de companhia em múltiplos eventos (concursos, campanhas, cinema, etc.)
-— Câmara Municipal (consultivo)
-— Comunicação prévia isenta de taxa para sem fins lucrativos
-— Possibilidade de exames de dopagem
-— Proibida pirotecnia</t>
+          <t>Todos animais de companhia em múltiplos eventos (concursos, campanhas, cinema, etc.)
+Câmara Municipal (consultivo)
+Comunicação prévia isenta de taxa para sem fins lucrativos
+Possibilidade de exames de dopagem
+Proibida pirotecnia</t>
         </is>
       </c>
       <c r="N16" s="11" t="inlineStr">
@@ -3075,7 +3121,7 @@
       </c>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>O RGBEAC cumpre os critérios ao prever um sistema robusto de certificação profissional para treinadores de cães com: título profissional obrigatório, requisitos de habilitação, provas teóricas e práticas, métodos baseados em reforço positivo, verificação de antecedentes criminais.
+          <t>O RGBEAC cumpre os critérios ao prever um sistema robusto de certificação profissional para treinadores de cães com: título profissional obrigatório, requisitos de habilitação, provas teóricas e práticas, métodos baseados em reforço positivo, verificação de antecedentes criminais. 
 Na legislação vigente só se encontra referências ao treino no Decreto-Lei n.º 315/2009, de 29 de Outubro, (regime dos cães perigosos e potencialmente perigosos), e no Decreto-Lei n.º 74/2007, de 27 de março, relativo ao treino em Cães de Assistência</t>
         </is>
       </c>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -1023,7 +1023,29 @@
       </c>
       <c r="N4" s="11" t="inlineStr">
         <is>
-          <t>Necessidade de: (1) criar o conceito de 'família de acolhimento' como extensão da atividade do operador; (2) fixar limite numérico de animais por família (máximo 5, ou 1 ninhada com mãe); (3) atribuir responsabilidade jurídica ao operador, não à família de acolhimento.</t>
+          <t>Necessidade de: (1) criar o conceito de 'família de acolhimento' como extensão da atividade do operador; (2) fixar limite numérico de animais por família (máximo 5, ou 1 ninhada com mãe); (3) atribuir responsabilidade jurídica ao operador, não à família de acolhimento.
+Critério / Determinação do Regulamento | Regulamento (UE) 2023/0447(texto PT-PT) | @rgbeac(proposta jun. 2025) | @codigo(proposta DL n.º 214/2013) | Proposta
+al. (a) — Água e alimentaçãoFornecimento adequado de água e alimentos(nutrição e hidratação) | Os cães e gatos recebem água e alimentos de qualidade e numa quantidade que assegura a sua boa e adequada nutrição e hidratação.(al. (a) do art.º 6.º) | Art.º 7.º, n.º 1, al. a) — proibição de fome, sede ou malnutrição.Art.º 10.º, n.º 1, al. a), ii) — alimentos saudáveis, adequados e convenientes; acesso permanente a água potável.Art.º 51.º, n.º 1 — programa de alimentação bem definido, de valor nutritivo adequado, em quantidade suficiente para as necessidades das espécies e dos indivíduos.Art.º 51.º, n.º 6 — acesso a água potável sem restrição (salvo razões médico-veterinárias).Coberto. | Art.º 4.º — dever de assegurar as necessidades básicas de bem-estar.Art.º 46.º, n.º 1 — programa de alimentação bem definido, de valor nutritivo adequado, em quantidade suficiente para as necessidades das espécies e dos indivíduos (nos locais de criação, manutenção, venda, centros de recolha e hospedagem).Art.º 46.º, n.º 6 — acesso a água potável sem restrição (salvo razões médico-veterinárias).Coberto no âmbito de estabelecimentos (art.º 46.º não se aplica à detenção doméstica individual). | Rgbeac ou código, ampliado à detenção
+al. (b) — Ambiente físico (1/2)Limpo, seguro e confortável(espaço, ar, temperatura, luz, clima) | Os cães e gatos são mantidos num ambiente físico adequado, regularmente limpo, seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, iluminação e proteção face a condições climáticas adversas.(al. (b) do art.º 6.º) | Art.º 7.º, n.º 1, al. b) — proibição de desconforto físico ou térmico.Art.º 10.º, n.º 1, al. a), v) — abrigo adequado com proteção de condições atmosféricas adversas (frio, chuva, sol ou calor excessivos); cama seca, limpa e confortável.Art.º 48.º, n.º 1 — temperatura, ventilação, luminosidade e obscuridade adequadas à manutenção do bem-estar e conforto das espécies.Art.º 48.º, n.º 3 — luz preferencialmente natural; luz artificial o mais próxima do espectro solar.Parcialmente coberto (sem referência explícita a qualidade do ar como parâmetro distinto da ventilação). | Art.º 5.º, n.º 1 — condições de detenção devem salvaguardar bem-estar.Art.º 14.º, n.º 1 — temperatura, ventilação, luminosidade e obscuridade das instalações adequadas ao bem-estar das espécies.Art.º 14.º, n.º 3 — luz preferencialmente natural; artificial o mais próxima do espectro solar.Parcialmente coberto (sem referência explícita a qualidade do ar como parâmetro distinto da ventilação). | Referir qualidade do ar?
+al. (b) — Ambiente físico (2/2)Espaço anti-sobrelotação;liberdade de movimentos | Os cães e gatos são mantidos num espaço suficientemente grande para prevenir a sobrelotação e garantir a facilidade de movimentação.(al. (b) do art.º 6.º) | Art.º 10.º, n.º 1, al. a), iv) — liberdade de movimento; proibição de contenção permanente; espaço e enriquecimento ambiental adequados. Art.º 47.º, n.º 1 — espaço adequado às necessidades fisiológicas e etológicas; prática de exercício físico; fuga de animais agressores. Portaria prevista no art.º 58.º fixará requisitos específicos. Parcialmente coberto (sobrelotação não referenciada de forma autónoma). | Art.º 5.º, n.º 3, al. b) — proibição de restringir a liberdade de movimentos de forma a impedir levantar-se, deitar-se ou virar-se sobre si próprios. Art.º 13.º, n.º 1, als. a) e b) — espaço adequado às necessidades fisiológicas e etológicas; prática de exercício físico; fuga de animais agressores. Parcialmente coberto (sobrelotação não referenciada de forma autónoma). | Rgbeac com referência à sobrelotação
+al. (c) — Saúde e higiene (1/2)Segurança, limpeza, boa saúde;prevenção de doenças, lesões e dor | Os cães e gatos são mantidos seguros, limpos e com boa saúde, prevenindo doenças, lesões e dor.(al. (c) do art.º 6.º) | Art.º 7.º, n.º 1, al. c) — proibição de dor, lesão física ou doença.Art.º 10.º, n.º 1, al. a), iii) — condições higiossanitárias.Art.º 10.º, n.º 1, al. f) — tratamento veterinário preventivo, paliativo ou curativo.Art.º 52.º, n.º 2 — todos os animais alvo de inspeção no início e final do dia e a cada quatro horas; primeiros cuidados imediatos a animais doentes ou lesionados. | Art.º 4.º — dever de salvaguardar a saúde.Art.º 6.º — dever de assegurar cuidados médico-veterinários ao animal ferido ou doente.Art.º 47.º, n.º 3 — inspeção diária de todos os animais; primeiros cuidados imediatos a animais doentes, lesionados ou com alterações comportamentais.Coberto em termos gerais (inspeção diária; sem diferenciação de frequência para animais vulneráveis). | 
+al. (c) — Saúde e higiene (2/2)Prevenção via maneio, manuseamentoe reprodução adequados | Prevenção de doenças, lesões e dor, nomeadamente através de práticas de maneio, manuseamento e reprodução adequadas.(al. (c) do art.º 6.º) | Art.º 12.º, n.º 1, al. b) — proibição de práticas que causem sofrimento, dano, stresse ou angústia.Art.º 52.º, n.ºs 3 e 5 — maneio feito de forma a não causar dores, sofrimento ou distúrbios desnecessários; meios de contenção não devem causar ferimentos, dores ou angústia.Art.º 70.º (normas reprodutivas) — limitações à reprodução para proteção da saúde.Coberto. | Art.º 5.º, n.º 3, al. c) — proibição de usar equipamentos de maneio, contenção ou treino que causem sofrimento desnecessário ou lesões.Art.º 47.º, n.ºs 4 e 5 — manuseamento feito de forma a não causar dores, sofrimento ou distúrbios desnecessários; meios de contenção não devem causar ferimentos, dores ou angústia.Art.º 8.º, n.º 1 e 2 — reprodução planeada e parâmetros reprodutivos.Coberto. | 
+al. (d) — Comportamento (1/2)Expressão de comportamentos da espéciee sociais não nocivos | Os cães e gatos são mantidos num ambiente que lhes permite exibir comportamentos específicos da espécie e comportamentos sociais não nocivos.(al. (d) do art.º 6.º) | Art.º 7.º, n.º 1, al. d) — direito de expressar padrões normais de comportamento.Art.º 10.º, n.º 1, al. a), iv) — espaço e enriquecimento ambiental adequados para a expressão dos comportamentos naturais.Art.º 10.º, n.º 1, al. a), vi) — contato social adequado à espécie, de acordo com a idade e atividade.Art.º 47.º, n.º 4 — enriquecimento ambiental complexo e estimulante com materiais e equipamento que estimulem a expressão do repertório de comportamentos naturais.Coberto. | Art.º 5.º, n.º 1 — condições de detenção que salvaguardem parâmetros de bem-estar.Art.º 13.º, n.º 5 — instalações equipadas com materiais e equipamento que estimulem a expressão dos comportamentos naturais (substrato, cama, ninhos, ramos, buracos, locais para banhos).Parcialmente coberto (enriquecimento ambiental para comportamentos naturais; sem referência explícita a comportamentos sociais não nocivos). | 
+al. (d) — Comportamento (2/2)Relação positiva com os seres humanos | Os cães e gatos são mantidos num ambiente que lhes permite estabelecer uma relação positiva com os seres humanos.(al. (d) do art.º 6.º) | Art.º 10.º, n.º 1, al. c) — dever de educar o animal com recurso a métodos de reforço positivo visando a sua vinculação e integração positivas no espaço familiar e no meio ambiente.Art.º 52.º, n.º 4 — interações do pessoal técnico com os animais devem ser positivas, regulares, previsíveis e não forçadas.Coberto. | Art.º 7.º, n.º 1 — dever de promover o treino dos cães com vista à socialização e obediência.Art.º 7.º, n.º 2 — treino de acordo com boas práticas.Parcialmente coberto (apenas cães; sem referência explícita a relação positiva com os seres humanos como fim autónomo). | 
+al. (e) — Estado mental (1/4)Prevenir/reduzir estímulos negativos(duração e intensidade) | Os cães e gatos são mantidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo estímulos negativos em duração e intensidade.(al. (e) do art.º 6.º) | Art.º 7.º, n.º 1, al. e) — proibição de situações que provoquem stresse, medo ou ansiedade injustificados.Art.º 12.º, n.º 1, al. b) — proibição de práticas que causem sofrimento, dano, stresse ou angústia.Parcialmente coberto (abordagem proibitiva; não preventiva). | Art.º 5.º, n.º 3 — proibição de violência e sofrimento.Sem referência explícita à gestão ativa de estímulos negativos. | 
+al. (e) — Estado mental (2/4)Maximizar estímulos positivos(duração e intensidade) | Os cães e gatos são mantidos de forma a maximizar oportunidades para estímulos positivos em duração e intensidade.(al. (e) do art.º 6.º) | Art.º 10.º, n.º 1, al. a), i) — dever de proporcionar atenção, supervisão, controlo, exercício físico e estímulo mental.Art.º 47.º, n.ºs 6 e 7 — acesso diário a área de exercício (mínimo 2×30 min); equipamento de enriquecimento ambiental e agilidade.Parcialmente coberto. | Art.º 13.º, n.º 5 — materiais e equipamento que estimulem a expressão dos comportamentos naturais.Sem norma positiva explícita sobre maximização de estímulos positivos. | 
+al. (e) — Estado mental (3/4)Prevenir comportamentos repetitivos anormaisou indicativos de bem-estar negativo | Os cães e gatos são mantidos de forma a prevenir o desenvolvimento de comportamentos repetitivos anormais ou outros comportamentos indicativos de bem-estar negativo.(al. (e) do art.º 6.º) | Não regulado explicitamente como norma autónoma.(O art.º 7.º, n.º 1, al. d) e e) e o art.º 47.º do @rgbeac indiretamente impõem condições que previnem o seu aparecimento.) | Não regulado explicitamente. | 
+al. (e) — Estado mental (4/4)Necessidades individuais do animal(als. (a) a (d)) | Os cães e gatos são mantidos tendo em conta as necessidades individuais do animal nos domínios referidos nas alíneas (a) a (d).(al. (e) do art.º 6.º) | Art.º 10.º, n.º 1, al. a) — bem-estar assegurado "de acordo com a sua espécie, raça, idade e necessidades físicas e etológicas".Art.º 48.º, n.º 2 — fatores ambientais adequados às necessidades específicas de animais em fase reprodutiva, recém-nascidos ou doentes.Parcialmente coberto (necessidades da espécie/raça/idade/fase fisiológica; não explicitamente individuais). | Art.º 4.º — necessidades básicas de bem-estar (sem referência à individualidade do animal).Art.º 14.º, n.º 2 — fatores ambientais adequados às necessidades específicas de animais em fase reprodutiva, recém-nascidos ou doentes.Parcialmente coberto. | 
+Critério / Determinação do Regulamento | Regulamento (UE) 2023/0447(texto PT-PT) | @rgbeac(proposta jun. 2025) | @codigo(proposta DL n.º 214/2013) | 
+n.º 1 — Responsabilidade geralBem-estar dos animais;minimizar riscos | Os operadores são responsáveis pelo bem-estar dos cães e gatos detidos nos estabelecimentos sob a sua responsabilidade e controlo, devendo minimizar quaisquer riscos para o bem-estar desses animais.(n.º 1 do art.º 7.º) | Art.º 9.º, n.º 1 — dever geral de todos os cidadãos de notificar infrações.Art.º 10.º, n.º 1 — obrigações especiais dos detentores: assegurar bem-estar.Sem distinção entre detentor doméstico e operador de estabelecimento comercial.Parcialmente coberto. | Art.º 4.º — detenção responsável: cabe aos detentores assegurar as necessidades básicas de bem-estar e salvaguardar a saúde.Sem atribuição explícita de responsabilidade ao "operador" como sujeito autónomo de estabelecimento.Parcialmente coberto. | 
+n.º 2 — Famílias de acolhimento (1/2)Responsabilidade do operador;informação sobre bem-estar e necessidades individuais | No caso das famílias de acolhimento, a responsabilidade incumbe ao operador em cujo nome os cães ou gatos são detidos. O operador presta à família informações adequadas sobre as obrigações de bem-estar e as necessidades individuais dos animais.(n.º 2 do art.º 7.º) | Art.º 4.º — define "Família de acolhimento temporário" como detentor transitório (45 dias, extensível).Art.º 101.º, n.ºs 3 e 4 — contrato escrito entre titular e família; registo no SIAC.Art.º 101.º, n.º 5 — destino do animal é da responsabilidade do titular.Parcialmente coberto (responsabilidade no titular; mas não se fixa o dever de informação ao acolhedor sobre bem-estar e necessidades individuais). | Art.º 9.º — define abandono; não prevê o conceito de família de acolhimento.Não coberto. | 
+n.º 2 — Famílias de acolhimento (2/2)Máx. 5 animais ou 1 ninhada(com/sem mãe) por família | Os operadores não colocam mais do que um total combinado de cinco cães ou gatos ou uma ninhada, com ou sem a mãe, numa família de acolhimento em qualquer momento.(n.º 2 do art.º 7.º) | Art.º 101.º — acolhimento temporário: sem fixação de limite numérico de animais por família.Não coberto. | Não regulado. | 
+n.º 3 — Derrogação (Estados-Membros)Maior número autorizadose espaço e cuidadores suficientes | O Estado-Membro pode autorizar maior número de cães, gatos ou ninhadas na família de acolhimento, desde que as instalações disponham de espaço suficiente (incluindo exterior) e o número de cuidadores seja suficiente.(n.º 3 do art.º 7.º) | Não regulado. | Não regulado. | 
+n.º 4 — Proibição de crueldade e maus-tratosInclui participaçãoem atividades de crueldade | Os operadores não sujeitam qualquer cão ou gato a crueldade, abusos ou maus-tratos, incluindo fazendo-os participar em atividades suscetíveis de resultar em crueldade, abusos ou maus-tratos.(n.º 4 do art.º 7.º) | Art.º 12.º, n.º 1, al. a) — proibição de causar a morte em violação das normas.Art.º 12.º, n.º 1, al. b) — proibição de práticas que causem sofrimento, dano, stresse ou angústia.Art.º 12.º, n.º 1, al. t) — proibição de utilização em eventos que envolvam crueldade, maus-tratos, sofrimento ou morte.Coberto. | Art.º 5.º, n.º 3 — proibição de violência: atos que infligem, sem necessidade, morte, sofrimento, abuso ou lesões a um animal.Art.º 5.º, n.º 4 — proibição de fins didáticos e lúdicos com dor ou sofrimentos consideráveis.Coberto. | 
+n.º 5 — Proibição de abandono | Os operadores não abandonam os cães ou gatos criados ou detidos por eles.(n.º 5 do art.º 7.º) | Art.º 12.º, n.º 1, al. e) — proibição expressa de abandono.Art.º 9.º, n.º 1 — dever de notificação de infrações (inclui abandono).Coberto. | Art.º 9.º — define abandono; não estabelece proibição autónoma expressa (proibição implícita pela definição).Parcialmente coberto. | 
+n.º 6 — Realojamento ao cessar atividadeAdoção ou transferênciapara outros operadores/adquirentes | Antes de os operadores cessarem as atividades num estabelecimento, asseguram que os cães ou gatos aí detidos são realojados, seja assumindo eles próprios a propriedade de animal de companhia, seja transferindo a responsabilidade para outros operadores ou adquirentes.(n.º 6 do art.º 7.º) | Art.º 101.º, n.º 5 — destino do animal é da responsabilidade do titular; mas esta norma aplica-se ao acolhimento temporário, não ao encerramento de estabelecimento.Não coberto (para encerramento de estabelecimento comercial). | Não regulado. | 
+n.º 7 — Cuidadores suficientes e competentes(competências do art.º 12.º) | Os operadores asseguram que os cães e gatos são manuseados por um número suficiente de cuidadores de animais para satisfazer as necessidades de bem-estar, e que esses cuidadores possuem as competências exigidas no artigo 12.º.(n.º 7 do art.º 7.º) | Art.º 52.º, n.º 1 — observação diária dos animais e maneio assegurados por pessoal técnico com formação teórica e prática específica certificada pela DGAV e em número adequado à quantidade e espécies animais alojados.Parcialmente coberto (número adequado e formação exigidos; sem remissão para catálogo de competências específico equivalente ao art.º 12.º do Regulamento). | Art.º 47.º, n.º 1 — observação diária dos animais e maneio assegurados por pessoal com aptidão para o efeito e em número adequado à quantidade e espécies animais.Art.º 47.º, n.º 2 — maneio por pessoal com experiência ou formação adequada, sob orientação de médico veterinário.Parcialmente coberto (número adequado e formação exigidos; sem catálogo de competências específico equivalente ao art.º 12.º do Regulamento). | 
+n.º 8 — Monitorização de indicadoresComportamento e aparência física;ações baseadas em resultados | Os operadores asseguram o bem-estar dos cães ou gatos monitorizando indicadores baseados nos animais relativos ao comportamento e à aparência física, e adotando ações com base nos resultados desse monitoramento.A Comissão adotará atos delegados que estabelecerão os indicadores e os métodos de medição.(n.ºs 8 e 9 do art.º 7.º) | Art.º 10.º, n.º 1, al. b) — dever de vigiar o animal de modo a evitar que cause danos (obrigação de vigilância; não equivale a monitorização de indicadores de bem-estar).Art.º 52.º, n.º 2 — inspeção dos animais no início e final do dia e a cada quatro horas; primeiros cuidados imediatos.Parcialmente coberto (periodicidade de inspeção regulada; sem sistema formal de indicadores baseados nos animais nem obrigação de ação estruturada com base nos resultados). | Art.º 47.º, n.º 3 — inspeção diária de todos os animais; primeiros cuidados imediatos a doentes, lesionados ou com alterações comportamentais.Parcialmente coberto (inspeção diária; sem sistema formal de indicadores de bem-estar nem atos delegados equivalentes). |</t>
         </is>
       </c>
       <c r="O4" s="11" t="inlineStr">

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -664,62 +664,64 @@
     <row r="2" ht="120" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Isenções de Obrigações</t>
+          <t>Objeto</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Art.º 5.º do Regulamento 2023/0447  |  EN</t>
+          <t>Art.º 1.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>1. A breeding establishment where no more than two litters per calendar year are produced for placing on the market shall be subject to only the obligations laid down in Article 6, Article 7(1) (2), (3) and (4). Article 8, Article 9, Article 11, Article 14(2), (3) and (4), Article 15(3), (4) and (8), Article 16(1). points (b), (c) and (d), Article 17(2), (3), (5) and (7), Article 18, Article 19(1) and points 3 and 4.3 of Annex I.
-2. A shelter in which not more than a combined total of 15 dogs or cats are kept at any given time, or any foster home shall be subject to only the obligations laid down in Article 6, Article 7(1), (2), (3), (4), and(5), Article 9, Article 11, Article 14(2), (3) and (4), Article 15(3), (4) and (8), Article 16(1). points (a), (b), (c) and (d), Article 17(2), (3), (5) and (7), Article 18 and point 4.3 of Annex I.</t>
+          <t>This Regulation lays down:
+(a) minimum requirements for the welfare of dogs and cats bred or kept in establishments or placed on the market of the Union; and
+(b) rules on the traceability of dogs and cats ▌.</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>1. Um estabelecimento de criação que produz no máximo duas ninhadas por ano civil para colocação no mercado fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (n.º 1, alíneas 1b, 1c e 1d), artigo 6a, artigo 7.º, artigo 8.º, artigo 11.º (n.ºs 2, 3 e 3a), artigo 12.º (n.ºs 3, 4 e 7), artigo 13.º (n.º 2, alíneas b, c e d), artigo 14.º (n.ºs 2, 3, 4 e 5a), artigo 15.º, artigo 15a (n.º 1) e ponto 3 e 4.3 do Anexo I.
-2. Um abrigo, onde são mantidos no máximo 15 cães ou gatos em qualquer momento, ou qualquer lar de acolhimento fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (n.ºs 1, 1a, 1b, 1c e 1d), artigo 7.º, artigo 8.º, artigo 11.º (n.ºs 2, 3 e 3a), artigo 12.º (n.ºs 3, 4 e 7), artigo 13.º (n.º 2, alíneas a, b, c e d), artigo 14.º (n.ºs 2, 3, 4 e 5a), artigo 15.º e ponto 4.3 do Anexo I.</t>
+          <t>O presente regulamento define:
+a) Os requisitos mínimos para o bem-estar dos cães e gatos criados ou detidos em estabelecimentos ou colocados no mercado da União;
+b) A rastreabilidade dos cães e gatos.</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Sem correspondência</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr"/>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Sem correspondência</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr"/>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Sem correspondência</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr"/>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Sem correspondência</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Sem correspondência</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Sem correspondência</t>
         </is>
       </c>
       <c r="N2" s="11" t="inlineStr">
         <is>
-          <t>Artigo de isenções do Regulamento europeu — não tem correspondência directa em legislação portuguesa.</t>
+          <t>Artigo introdutório do Regulamento europeu — define o objeto geral do regulamento.</t>
         </is>
       </c>
       <c r="O2" s="11" t="inlineStr">
@@ -732,15 +734,301 @@
     <row r="3" ht="120" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>Âmbito de Aplicação Material</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 2.º do Regulamento 2023/0447  |  EN</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>1. This Regulation applies to the breeding, keeping, tracing, placing on the market and entry into the Union of dogs and cats ▌.
+2. This Regulation does not apply to the breeding, keeping or placing on the market or entry into the Union of dogs or cats intended or used for scientific purposes or for clinical trials required for the marketing authorisation of veterinary medicinal products.
+▌</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>1. O presente regulamento aplica-se à criação, à detenção, ao rastreio, à colocação no mercado e à entrada na União de cães e gatos.
+2. O presente regulamento não se aplica à criação, detenção ou colocação no mercado ou à entrada na União de cães ou gatos destinados ou utilizados para fins científicos ou para ensaios clínicos exigidos para a autorização de comercialização de medicamentos veterinários.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Sem correspondência</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Sem correspondência</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr"/>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Sem correspondência</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>Sem correspondência</t>
+        </is>
+      </c>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>Sem correspondência</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>Sem correspondência</t>
+        </is>
+      </c>
+      <c r="N3" s="11" t="inlineStr">
+        <is>
+          <t>Define o âmbito material do Regulamento — aplica-se à criação, detenção, rastreio e colocação no mercado de cães e gatos.</t>
+        </is>
+      </c>
+      <c r="O3" s="11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P3" s="11" t="inlineStr"/>
+    </row>
+    <row r="4" ht="120" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Âmbito de Aplicação Pessoal</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 3.º do Regulamento 2023/0447  |  EN</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>1. Chapter II of this Regulation applies to all operators.
+2. Chapter III of this Regulation applies to all natural and legal persons owning dogs or cats in the Union.
+3. Chapter IV applies to all natural and legal persons who bring dogs or cats into the Union.
+4. This Regulation does not apply to farmers offering refuge on their holding to free-roaming stray cats that are useful for pest control, where those farmers are not operators and do not place those cats on the market.</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>1. O capítulo II do presente regulamento aplica-se a todos os operadores.
+2. O capítulo III do presente regulamento aplica-se a todas as pessoas singulares e coletivas proprietárias de cães e gatos na União.
+3. O capítulo IV aplica-se a todas as pessoas singulares e coletivas que introduzam cães ou gatos na União.
+4. O presente regulamento não aplica-se a agricultores que, na sua exploração, ofereçam refúgio a gatos vadios em liberdade que sejam úteis para controlo de pragas, desde que esses agricultores não sejam operadores e não coloquem esses gatos no mercado.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Sem correspondência</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Sem correspondência</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Sem correspondência</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>Sem correspondência</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>Sem correspondência</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>Sem correspondência</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="inlineStr">
+        <is>
+          <t>Define o âmbito pessoal — quem está obrigado pelo Regulamento (operadores, proprietários, importadores).</t>
+        </is>
+      </c>
+      <c r="O4" s="11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P4" s="11" t="inlineStr"/>
+    </row>
+    <row r="5" ht="120" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Definições</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 4.º do Regulamento 2023/0447  |  EN</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>For the purposes of this Regulation, the following definitions apply:
+1. 'dog' means an animal of the species Canis lupus familiaris;
+▌
+2. 'cat' means an animal of the species Felis silvestris catus;
+3. 'welfare of dogs and cats' means the physical and mental state of a dog or a cat, which receives appropriate nutrition, is kept in an appropriate environment, is in good health, displays appropriate behaviour, and has an overall a positive mental experience of life;
+4. 'hybrid' means any offspring of the first to the fourth generation following a cross-breeding event between a wild species and the domestic species of dog or cat;
+5. 'breeding' means the activity of keeping dogs or cats in breeding establishments for the purposes of reproduction;</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Para efeitos do presente regulamento, entende-se por:
+1. «Cão», um animal da espécie Canis lupus familiaris;
+2. «Gato», um animal da espécie Felis silvestris catus;
+3. «Bem-estar dos cães e gatos», o estado físico e mental de um cão ou de um gato que recebe nutrição adequada, é mantido num ambiente apropriado, está em bom estado de saúde, exibe comportamento apropriado e tem uma experiência mental geral positiva da vida;
+4. «Híbrido», qualquer descendência da primeira à quarta geração após o cruzamento entre uma espécie selvagem e a espécie doméstica de cão ou gato;
+5. «Criação», a atividade de detenção de cães ou gatos em estabelecimentos de criação para efeitos de reprodução;</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Sem correspondência</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Sem correspondência</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Sem correspondência</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>Sem correspondência</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>Sem correspondência</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>Sem correspondência</t>
+        </is>
+      </c>
+      <c r="N5" s="11" t="inlineStr">
+        <is>
+          <t>Define conceitos-chave usados ao longo do Regulamento (cão, gato, bem-estar, criação, etc.).</t>
+        </is>
+      </c>
+      <c r="O5" s="11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P5" s="11" t="inlineStr"/>
+    </row>
+    <row r="6" ht="120" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Isenções de Obrigações</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 5.º do Regulamento 2023/0447  |  EN</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>1. A breeding establishment where no more than two litters per calendar year are produced for placing on the market shall be subject to only the obligations laid down in Article 6, Article 7(1) (2), (3) and (4). Article 8, Article 9, Article 11, Article 14(2), (3) and (4), Article 15(3), (4) and (8), Article 16(1). points (b), (c) and (d), Article 17(2), (3), (5) and (7), Article 18, Article 19(1) and points 3 and 4.3 of Annex I.
+2. A shelter in which not more than a combined total of 15 dogs or cats are kept at any given time, or any foster home shall be subject to only the obligations laid down in Article 6, Article 7(1), (2), (3), (4), and(5), Article 9, Article 11, Article 14(2), (3) and (4), Article 15(3), (4) and (8), Article 16(1). points (a), (b), (c) and (d), Article 17(2), (3), (5) and (7), Article 18 and point 4.3 of Annex I.</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>1. Um estabelecimento de criação que produz no máximo duas ninhadas por ano civil para colocação no mercado fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (n.º 1, alíneas 1b, 1c e 1d), artigo 6a, artigo 7.º, artigo 8.º, artigo 11.º (n.ºs 2, 3 e 3a), artigo 12.º (n.ºs 3, 4 e 7), artigo 13.º (n.º 2, alíneas b, c e d), artigo 14.º (n.ºs 2, 3, 4 e 5a), artigo 15.º, artigo 15a (n.º 1) e ponto 3 e 4.3 do Anexo I.
+2. Um abrigo, onde são mantidos no máximo 15 cães ou gatos em qualquer momento, ou qualquer lar de acolhimento fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (n.ºs 1, 1a, 1b, 1c e 1d), artigo 7.º, artigo 8.º, artigo 11.º (n.ºs 2, 3 e 3a), artigo 12.º (n.ºs 3, 4 e 7), artigo 13.º (n.º 2, alíneas a, b, c e d), artigo 14.º (n.ºs 2, 3, 4 e 5a), artigo 15.º e ponto 4.3 do Anexo I.</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr"/>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>Artigo de isenções do Regulamento europeu — não tem correspondência directa em legislação portuguesa.</t>
+        </is>
+      </c>
+      <c r="O6" s="11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P6" s="11" t="inlineStr"/>
+    </row>
+    <row r="7" ht="120" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>Princípios Gerais de Bem-Estar</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Art.º 6.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Operators shall apply the following general welfare principles with respect to dogs or cats bred or kept in their establishment:
 (a) dogs and cats are provided with water and feed of a quality and quantity that affords them appropriate nutrition and hydration;
@@ -750,7 +1038,7 @@
 (e)	dogs and cats are kept in such a way as to optimise their mental state by preventing or reducing negative stimuli in duration and intensity, as well as by maximising opportunities for positive stimuli in duration and intensity, preventing the development of abnormal repetitive or other behaviours indicative of negative animal welfare, and taking into consideration the individual animal’s needs in the domains referred to in points (a) to (d).</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem aplicar os seguintes princípios gerais de bem-estar aos cães e gatos criados ou detidos nos seus estabelecimentos:
 (a) Os cães e os gatos recebem água e alimentos de qualidade e numa quantidade que assegura a sua boa e adequada nutrição e hidratação;
@@ -760,12 +1048,12 @@
 (e) (e) os cães e gatos são mantidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo estímulos negativos em duração e intensidade, maximizando oportunidades de estímulos positivos, prevenindo o desenvolvimento de comportamentos repetitivos anormais, tendo em conta as necessidades individuais do animal nos domínios referidos nas alíneas (a) a (d).</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Art.º 7.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>1 – Todos têm o dever de garantir condições de bem-estar aos animais de companhia, em especial que:
 a) não passem fome ou sede, nem sejam sujeitos a malnutrição;
@@ -777,12 +1065,12 @@
 3 - Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no presente decreto-lei ou se não se adaptar ao cativeiro.</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Arts. 4.º e 5.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Artigo 4.º — Detenção responsável
 Cabe aos detentores de animais de companhia assegurar as necessidades básicas de bem-estar dos mesmos, garantir o controlo da sua reprodução, salvaguardar a sua saúde e prevenir os riscos inerentes à transmissão de doenças a pessoas e a outros animais e, ainda, a segurança das populações, garantindo a salubridade dos locais e a tranquilidade das pessoas.
@@ -797,12 +1085,12 @@
 4 - É proibido utilizar animais para fins didáticos e lúdicos, de treino, filmagens, exibições, publicidade ou atividades semelhantes, sempre que daí resultem para aqueles dor ou sofrimentos consideráveis, salvo experiência científica de comprovada necessidade e justificada nos termos da lei.</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>n.ºs 1, 2, 3 e 4 do art.º 7.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
 2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
@@ -810,45 +1098,45 @@
 4 — É proibido utilizar animais para fins didáticos e lúdicos, de treino, filmagens, exibições, publicidade ou atividades semelhantes, na medida em que daí resultem para eles dor ou sofrimentos consideráveis, salvo experiência científica de comprovada necessidade e justificada nos termos da lei.</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>Análise no Art.º 7</t>
         </is>
       </c>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>Análise no Art.º 7</t>
         </is>
       </c>
-      <c r="M3" s="10" t="inlineStr">
+      <c r="M7" s="10" t="inlineStr">
         <is>
           <t>Análise no Art.º 7</t>
         </is>
       </c>
-      <c r="N3" s="11" t="inlineStr">
+      <c r="N7" s="11" t="inlineStr">
         <is>
           <t>Regulamento especifica novos conceitos: estabelecer uma relação positiva com os seres humanos; otimizar o seu estado mental; prevenindo o desenvolvimento de comportamentos repetitivos anormais;</t>
         </is>
       </c>
-      <c r="O3" s="11" t="inlineStr">
+      <c r="O7" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P3" s="11" t="inlineStr"/>
+      <c r="P7" s="11" t="inlineStr"/>
     </row>
-    <row r="4" ht="120" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Obrigações gerais de bem-estar animal</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Art.º 7.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall be responsible for the welfare of dogs and cats kept in establishments under their responsibility and control, and shall be responsible for minimising any risks to the welfare of those animals.
 2. In the case of foster homes, the responsibility shall lie with the operator on whose behalf dogs or cats are kept. Such operators shall not place more than a combined total of five dogs or cats or one litter with or without mother in a foster home at any given time and shall provide the foster family with adequate information on the animal welfare obligations as well as the individual needs of the dogs or cats, and shall ensure that the relevant obligations laid down in this Regulation are complied with in foster homes.
@@ -861,7 +1149,7 @@
 8. The Commission is empowered to adopt delegated acts in accordance with Article 28 supplementing this Regulation by laying down the animal-based indicators concerning behaviour and physical appearance that operators are to use for monitoring, in accordance with paragraph 7 of this Article, and the methods by which operators are to measure them.</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores são responsáveis pelo bem-estar dos cães e gatos detidos nos estabelecimentos sob a sua responsabilidade e controlo, devendo minimizar quaisquer riscos para o bem-estar desses animais.
 2. No caso das famílias de acolhimento, a responsabilidade incumbe ao operador em cujo nome os cães ou gatos são detidos. Tais operadores não colocam mais do que um total combinado de cinco cães ou gatos ou uma ninhada, com ou sem a mãe, num lar de acolhimento em qualquer momento dado e fornecem à família de acolhimento informações adequadas sobre as obrigações em matéria de bem-estar dos animais, bem como sobre as necessidades individuais dos cães ou gatos, e asseguram que as obrigações relevantes previstas no presente regulamento são cumpridas nos lares de acolhimento.
@@ -874,12 +1162,12 @@
 8. A Comissão fica habilitada a adotar atos delegados, nos termos do artigo 28.º, que complementem o presente regulamento, estabelecendo os indicadores baseados nos animais relativos ao comportamento e à aparência física que os operadores devem utilizar para efeitos de monitorização nos termos do n.º 7 do presente artigo, bem como os métodos pelos quais os operadores devem medi-los.</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>art.º 7.º e 9 a 12.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Artigo 7.º - Princípios fundamentais para o bem-estar dos animais de companhia
 1 – Todos têm o dever de garantir condições de bem-estar aos animais de companhia, em especial que:
@@ -958,12 +1246,12 @@
 bb) Utilizá-los para a prática de mendicidade, sem prejuízo do direito das pessoas sem-abrigo se fazerem acompanhar dos seus animais de companhia, salvaguardado o seu bem-estar.</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Art.º 4 e 5.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Artigo 4.º - Detenção responsável
 Cabe aos detentores de animais de companhia assegurar as necessidades básicas de bem-estar dos mesmos, garantir o controlo da sua reprodução, salvaguardar a sua saúde e prevenir os riscos inerentes à transmissão de doenças a pessoas e a outros animais e, ainda, a segurança das populações, garantindo a salubridade dos locais e a tranquilidade das pessoas.
@@ -981,12 +1269,12 @@
 Art. 75.º, n.º 8 - Em caso de abandono de animais ou em caso de incumprimento do dever de vigilância que tenha dado origem a uma agressão, os cães e gatos são devolvidos ao seu detentor após esterilização cirúrgica definitiva executada no centro de recolha a suas expensas.</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>n.ºs 1, 2 e 3 do art.º 7.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
 2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
@@ -1006,22 +1294,22 @@
 4 - As espécies de animais em perigo de extinção serão objecto de medidas de protecção, nomeadamente para preservação dos ecossistemas em que se enquadram.</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>O conceito de família de acolhimento é inexistente na legislação vigente.</t>
         </is>
       </c>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="L8" s="9" t="inlineStr">
         <is>
           <t>O @codigo não prevê o conceito de família de acolhimento nem qualquer limite numérico de animais por unidade.</t>
         </is>
       </c>
-      <c r="M4" s="10" t="inlineStr">
+      <c r="M8" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac menciona famílias de acolhimento temporário, mas não fixa o limite de 5 animais por família de acolhimento nem especifica que a responsabilidade jurídica recai sobre o operador e não sobre a família.</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="N8" s="11" t="inlineStr">
         <is>
           <t>Necessidade de: (1) criar o conceito de 'família de acolhimento' como extensão da atividade do operador; (2) fixar limite numérico de animais por família (máximo 5, ou 1 ninhada com mãe); (3) atribuir responsabilidade jurídica ao operador, não à família de acolhimento.
 Critério / Determinação do Regulamento | Regulamento (UE) 2023/0447(texto PT-PT) | @rgbeac(proposta jun. 2025) | @codigo(proposta DL n.º 214/2013) | Proposta
@@ -1048,25 +1336,25 @@
 n.º 8 — Monitorização de indicadoresComportamento e aparência física;ações baseadas em resultados | Os operadores asseguram o bem-estar dos cães ou gatos monitorizando indicadores baseados nos animais relativos ao comportamento e à aparência física, e adotando ações com base nos resultados desse monitoramento.A Comissão adotará atos delegados que estabelecerão os indicadores e os métodos de medição.(n.ºs 8 e 9 do art.º 7.º) | Art.º 10.º, n.º 1, al. b) — dever de vigiar o animal de modo a evitar que cause danos (obrigação de vigilância; não equivale a monitorização de indicadores de bem-estar).Art.º 52.º, n.º 2 — inspeção dos animais no início e final do dia e a cada quatro horas; primeiros cuidados imediatos.Parcialmente coberto (periodicidade de inspeção regulada; sem sistema formal de indicadores baseados nos animais nem obrigação de ação estruturada com base nos resultados). | Art.º 47.º, n.º 3 — inspeção diária de todos os animais; primeiros cuidados imediatos a doentes, lesionados ou com alterações comportamentais.Parcialmente coberto (inspeção diária; sem sistema formal de indicadores de bem-estar nem atos delegados equivalentes). |</t>
         </is>
       </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="O8" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P4" s="11" t="inlineStr"/>
+      <c r="P8" s="11" t="inlineStr"/>
     </row>
-    <row r="5" ht="120" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Obrigações relativas às estratégias de reprodução</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Art.º 8.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>1. Operators of breeding establishments shall ensure that their breeding strategies minimise the risk of producing dogs or cats with genotypes associated with effects detrimental to the health and welfare of those animals.
 2. Operators of breeding establishments shall not use for reproduction dogs or cats that have excessive conformational traits leading to a high risk of detrimental effects on the welfare of such dogs or cats, or of their offspring. Before selecting a dog or cat that might have an excessive conformational trait for breeding, the operator shall consult a veterinarian or an independent qualified person acting under the responsibility of a veterinarian. That veterinarian or independent qualified person shall assess whether the dog or cat has an excessive conformational trait.
@@ -1089,7 +1377,7 @@
 The operator shall keep the written confirmation referred to in point 3.4.b for a period of at least 3 years</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
 2. Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem características de conformação excessivas que acarretem um elevado risco de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por características de conformação excessivas, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem uma característica de conformação excessiva.
@@ -1111,12 +1399,12 @@
 O operador deve conservar a confirmação escrita referida no ponto 3.4.b por um período de, pelo menos, 3 anos.</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Art.º 70.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>1. As condições de reprodução e criação de animais de companhia devem ser o mais análogas possível às de um ambiente doméstico, onde se espera que venham a viver após a sua transmissão.
 2. As cadelas podem reproduzir entre os dezoito meses e os seis anos de idade, até ao limite de quatro ninhadas com um intervalo mínimo de doze meses entre cada ninhada.
@@ -1133,12 +1421,12 @@
 13. O detentor de animal reprodutor que deixe de poder ser usado para reprodução, nos termos do presente artigo, é obrigado a esterilizá-lo e a garantir o seu bem-estar e uma detenção responsável até ao final da sua vida, diretamente ou cedendo-o a terceiros nos termos do disposto nos artigos 42.º ou 91.º.</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Art.º 8.º do Código do Animal (DL n.º 214/2013)  -Reprodução e criação</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>1. A reprodução de animais deve ser realizada de forma planeada.
 2. A reprodução de animais obedece ao seguinte:
@@ -1183,29 +1471,29 @@
 N. B. As cadelas não devem ter mais de 2 ninhadas num período de 2 anos e as gatas não devem ultrapassar as 3 ninhadas no período de 2 anos, a menos que haja uma declaração de aprovação emitida pelo veterinário assistente</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Não há correspondência</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>n.º 3 do art. 8.º - As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar.</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr">
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>Breve referência. Sem equivalência</t>
         </is>
       </c>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>Exclui da reprodução animais com defeitos genéticos e malformações, mas especifica monorquidia, displasia, rim poliquístico e alterações comportamentais. 
 Proíbe cios sucessivos
 Não prevê o conceito de conformações extremas nem a proibição de consanguinidade.</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr">
+      <c r="M9" s="10" t="inlineStr">
         <is>
           <t>Prevê limites de idade para reprodução (cadelas 18 meses a 6 anos; gatas 12 meses a 6 anos; machos 12 meses a 7 anos), máximo de 4 ninhadas com intervalo mínimo de 12 meses, testes genéticos e de saúde e proibição de reprodução após 2 cesarianas — vários destes requisitos são mais detalhados que o Regulamento. 
 O Art.º 70.º, n.º 7 remete para portaria a definição de coeficiente de consanguinidade e limite de descendentes por macho, sem proibição expressa de cruzamentos entre pais/filhos, irmãos ou avós/netos como o Regulamento.
@@ -1213,7 +1501,7 @@
 A proibição de híbridos não consta.</t>
         </is>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="N9" s="11" t="inlineStr">
         <is>
           <t>1. Idades mínimas de reprodução
 2. Idades máximas de reprodução
@@ -1284,25 +1572,25 @@
 Separação comportamento agressivo | Animais que representem ameaça ou causem stress excessivo devem ser mantidos separados(Anexo I, n.º 1.1) | Não regulado especificamente. As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar.(Art. 13.º, n.º 3) Artigo 83.º - As fêmeas prenhes, bem como as ninhadas em período de aleitamento, não podem ser mantidas nos locais de venda.   | Não regulado especificamente. 3 - As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar (Art.º 47.º, n.º 3) Artigo 76.º- As fêmeas prenhes, bem como as ninhadas em período de aleitamento, não podem ser mantidas nos locais de venda. | Regulamento + qq um</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="O9" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P5" s="11" t="inlineStr"/>
+      <c r="P9" s="11" t="inlineStr"/>
     </row>
-    <row r="6" ht="120" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Notificação e registo dos estabelecimentos</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Art.º 9.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall notify the competent authorities of their activity, providing at least the following information for each of their establishments:
 (a) the name, address and contact details of the operator;
@@ -1318,7 +1606,7 @@
 4. The competent authority shall maintain a register of establishments. The competent authority may use for that purpose the register provided for in Article 101(1), point (a), of Regulation (EU) 2016/429.</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores devem notificar as autoridades competentes da sua atividade, fornecendo pelo menos as seguintes informações para cada um dos seus estabelecimentos:
 (a) o nome, morada e contactos do operador;
@@ -1334,12 +1622,12 @@
 4.	A autoridade competente deve manter um registo dos estabelecimentos. A autoridade competente pode utilizar para esse efeito o registo previsto no artigo 101.º, n.º 1, alínea a), do Regulamento (UE) 2016/429.</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Artigo 60.º - Comunicação prévia com prazo</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>1 - O exercício da atividade de exploração de alojamentos para hospedagem, incluindo os centros de bem-estar animal, com exceção dos alojamentos destinados exclusivamente à venda, depende de comunicação prévia com prazo.
 2 - A comunicação prévia com prazo dá lugar a um número de identificação do alojamento.
@@ -1391,12 +1679,12 @@
 3 – O disposto no presente artigo não prejudica a legislação aplicável ao reconhecimento mútuo de requisitos relativos a qualificações.</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>Artigo 31.º - Procedimento para o exercício da atividade de exploração de alojamentos</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>Procedimento para o exercício da atividade de exploração de alojamentos Sem prejuízo do disposto no Decreto-Lei n.º 48/2011, de 1 de abril, alterado pelo Decreto-Lei n.º 141/2012, de 11 de julho, quanto aos estabelecimentos de comércio a retalho de animais de companhia, o exercício da atividade de exploração de alojamentos depende de:
 a) Mera comunicação prévia, no caso dos centros de recolha, alojamentos para hospedagem, com ou sem fins lucrativos, com exceção dos destinados exclusivamente à venda, sem prejuízo do disposto na alínea seguinte;
@@ -1464,12 +1752,12 @@
 2	- O disposto no número anterior não é aplicável ao cumprimento das condições diretamente referentes às instalações físicas localizadas em território nacional, nem aos respetivos controlos por autoridade competente.</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Artigo 3.º</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>Procedimento para o exercício da atividade de exploração de alojamentos e criação comercial de animais de companhia
 1 - Sem prejuízo do disposto no Decreto-Lei n.º 10/2015, de 16 de janeiro, quanto aos estabelecimentos de comércio a retalho de animais de companhia, o exercício da atividade de exploração de alojamentos, bem como a atividade de criação comercial de animais de companhia depende de:
@@ -1539,47 +1827,47 @@
 As medidas previstas nos artigos 3.º-G e 3.º-H são publicitadas através do balcão único eletrónico dos serviços, a que se refere o artigo 6.º do Decreto-Lei n.º 92/2010, de 26 de julho, e no sítio na Internet da DGAV.</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>Não exige a estimativa anual de ninhadas a colocar no mercado (al. ea) do @regulamento), constituindo lacuna parcial.</t>
         </is>
       </c>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="L10" s="9" t="inlineStr">
         <is>
           <t>Alterações de funcionamento
 Comunicação à DGAV, sem referência a via eletrónica, balcão único</t>
         </is>
       </c>
-      <c r="M6" s="10" t="inlineStr">
+      <c r="M10" s="10" t="inlineStr">
         <is>
           <t>O RGBEAC substitui a mera comunicação prévia por um modelo que abre lugar à fiscalização preventiva quando se aparente justificar, e permite à DGAV travar o início da atividade antes da produção de efeitos ao fim de 30 dias.
 O artigo 63.º, abre o leque, não nomeia as alterações, remete para qualquer “modificação de qualquer dos elementos previstos no n.º 1 do artigo 61.º</t>
         </is>
       </c>
-      <c r="N6" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>Necessidade de ajuste: acrescentar a obrigação de estimativa anual de ninhadas a colocar no mercado e alinhar os restantes elementos informativos com a lista exaustiva do art.º 7.º do @regulamento.</t>
         </is>
       </c>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P6" s="11" t="inlineStr"/>
+      <c r="P10" s="11" t="inlineStr"/>
     </row>
-    <row r="7" ht="120" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="11" ht="120" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Aprovação de Estabelecimentos de Criação</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Art.º 10.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>1. Operators of breeding establishments that either produce or intend to produce more than five litters per calendar year or that keep more than a combined total of five bitches or queens at any given time shall place dogs or cats on the market only after their establishment has been approved by the competent authority.
 2. The competent authority shall perform on-site inspections to verify that the establishment meets the requirements of this Regulation. Member States may allow such inspections to be carried out remotely, provided that the means of distance communication used provides sufficient evidence for the competent authority to perform reliable inspections. The competent authority shall grant certificates of approval only to breeding establishments that meet the requirements of this Regulation.
@@ -1591,7 +1879,7 @@
 (e) the unique approval number assigned to the establishment by the competent authority and the date of the approval and cessation of activities.</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores de estabelecimentos de criação que produzem ou pretendem produzir mais de cinco ninhadas por ano civil ou que mantêm mais do que um total combinado de cinco cadelas ou gatas em qualquer momento podem colocar cães ou gatos no mercado apenas após a aprovação do seu estabelecimento pela autoridade competente.
 2. A autoridade competente deve realizar inspeções no local para verificar que o estabelecimento atende aos requisitos do presente Regulamento. Os Estados-Membros podem permitir que tais inspeções sejam realizadas remotamente, desde que o meio de comunicação à distância utilizado forneça provas suficientes para a autoridade competente realizar inspeções fiáveis. A autoridade competente deve conceder certificados de aprovação apenas aos estabelecimentos de criação que cumprem os requisitos do presente Regulamento.
@@ -1603,32 +1891,32 @@
 (e) o número de aprovação único atribuído ao estabelecimento pela autoridade competente e a data da aprovação e cessação de atividades.</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Artigo 62.º - Divulgação dos alojamentos</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>A DGAV publicita no balcão único eletrónico de serviços, a que se refere o artigo 6.º do Decreto-Lei n.º 92/2010, de 26 de julho, e no seu sítio na Internet a lista dos centros de bem-estar animal, bem como de todos os alojamentos para hospedagem de animais de companhia, em relação aos quais tenha recebido comunicação prévia com prazo, nos termos do presente decreto-lei, incluindo os criadores de animais de companhia, respetivo município de atividade e número de identificação.</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Artigo 37.º - Divulgação dos alojamentos</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>A DGAV publicita no balcão único electrónico de serviços, a que se refere o artigo 6.º do Decreto-Lei n.º 92/2010, de 26 de julho e no seu sítio na Internet, a lista dos centros de recolha, bem como de todos os alojamentos de hospedagem, com ou sem fins lucrativos, que haja permitido ou em relação aos quais tenha recebido mera comunicação prévia, nos termos do presente diploma.</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Havia a Permissão Administrativa apenas no caso de criação/reprodução de cães PP, conforme art. 3.º-B</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Art.º 3.º, n.º 12
 A DGAV publicita, no seu sítio de Internet, os nomes dos criadores comerciais de animais de companhia e respetivo município de atividade e número de identificação.
@@ -1636,38 +1924,38 @@
 DGAV publicita no balcão único eletrónico de serviços, a que se refere o artigo 6.º do Decreto-Lei n.º 92/2010, de 26 de julho, e no seu sítio na Internet a lista dos centros de recolha oficiais, bem como de todos os centros de hospedagem, com ou sem fins lucrativos, que haja permitido ou em relação aos quais tenha recebido mera comunicação prévia, nos termos do presente diploma.</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="K11" s="8" t="inlineStr">
         <is>
           <t>Conceito novo de ‘aprovação’ com limiar (&gt;5 ninhadas/ano ou &gt;5 cadelas/gatas)</t>
         </is>
       </c>
-      <c r="L7" s="9" t="inlineStr"/>
-      <c r="M7" s="10" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr">
+      <c r="L11" s="9" t="inlineStr"/>
+      <c r="M11" s="10" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
         <is>
           <t>Artigo novo no Regulamento, introduz aprovação formal de criadores com limiar numérico para ninhadas ou fêmeas no local.
 A publicitação prevista pelo @regulamento inclui mais informação do que a legislação vigente ou em proposta.</t>
         </is>
       </c>
-      <c r="O7" s="11" t="inlineStr">
+      <c r="O11" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P7" s="11" t="inlineStr"/>
+      <c r="P11" s="11" t="inlineStr"/>
     </row>
-    <row r="8" ht="120" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="12" ht="120" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Obrigação de informação de detenção responsável</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Art.º 11.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall provide the acquirer of a dog or cat written information necessary to enable the acquirer to ensure the animal’s welfare, including information on responsible ownership and on the specific needs of the animal in terms of feeding, care, health and housing, as well as information on its behavioural needs and health history.
 2. The written information on the dog or cat’s health history referred to in the first paragraph shall include at least:
@@ -1676,7 +1964,7 @@
 Where the information on the animal’s health history is set out in a document required under Regulation (EU) 2016/429, the operator shall transmit that document to the acquirer.</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores devem fornecer ao adquirente de um cão ou gato informação escrita necessária para lhe permitir assegurar o bem-estar do cão ou gato, incluindo informação sobre detenção responsável e sobre as necessidades específicas do cão ou gato em termos de alimentação, cuidados, saúde e alojamento, bem como informação sobre as suas necessidades comportamentais e historial de saúde.
 2. A informação escrita sobre o historial de saúde do cão ou gato referida no n.º 1 deve incluir pelo menos:
@@ -1685,23 +1973,23 @@
 Caso a informação sobre o historial de saúde do cão ou gato esteja prevista num documento exigido nos termos do Regulamento (UE) 2016/429, o operador deve transmitir esse documento ao adquirente.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Art.º 8.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>1 — O detentor do animal de companhia deve possuir informação sobre as obrigações inerentes à sua detenção, incluindo direitos e responsabilidades, normas de bem-estar, cuidados de saúde, comportamento, necessidades específicas da espécie/raça, duração de vida esperada, custos de manutenção, e proibição de abandono.
 2 — Os comerciantes devem fornecer por escrito ao adquirente informação completa antes da transferência do animal, incluindo identidade e dados de contacto do comerciante, dados de identificação do animal, cuidados de saúde e estado de vacinação, e certificado de origem ou de compatibilidade quando aplicável.</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Art.º 57.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>1. O detentor do animal deve ter acesso à informação sobre:
 a) As obrigações inerentes à sua detenção, direitos e responsabilidades;
@@ -1713,52 +2001,52 @@
 2. Os criadores e comerciantes devem fornecer informação escrita completa ao adquirente antes da transferência do animal, incluindo dados de identificação e cuidados de saúde.</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Sem equivalência</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr"/>
-      <c r="K8" s="8" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr"/>
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>Sem equivalência</t>
         </is>
       </c>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="L12" s="9" t="inlineStr">
         <is>
           <t>Faltam alguns elementos</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="M12" s="10" t="inlineStr">
         <is>
           <t>Recupera todos os elementos do @código
 Faltam alguns elementos em relação ao @regulamento</t>
         </is>
       </c>
-      <c r="N8" s="11" t="inlineStr">
+      <c r="N12" s="11" t="inlineStr">
         <is>
           <t>Necessidade de alteração: introduzir quaisquer condições médicas ou predisposições a doenças, incluindo alergias, conhecidas pelo operador, e quaisquer resultados de testes de diagnóstico para o cão ou gato que estejam disponíveis para o operador.</t>
         </is>
       </c>
-      <c r="O8" s="11" t="inlineStr">
+      <c r="O12" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P8" s="11" t="inlineStr"/>
+      <c r="P12" s="11" t="inlineStr"/>
     </row>
-    <row r="9" ht="120" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Competências de Cuidadores e Bem-Estar Animal</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Art.º 12.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>1. Animal carers, other than volunteers in shelters and interns who are acting under the responsibility of a competent animal carer, shall have the following competences as regards the dogs and cats they are handling:
 (a) an understanding of the animals’ biological behaviour and their physiological and ethological needs;
@@ -1772,7 +2060,7 @@
 Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 29.</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>1. Os cuidadores de animais, com exceção dos voluntários em abrigos e dos estagiários que atuem sob a responsabilidade de um cuidador de animais competente, devem possuir as seguintes competências no que diz respeito aos cães e gatos que manuseiam:
 (a) compreensão do comportamento biológico dos animais e das respetivas necessidades fisiológicas e etológicas;​
@@ -1786,12 +2074,12 @@
 Os referidos atos de execução são adotados pelo procedimento de exame a que se refere o artigo 29.º</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Art.ºs 69.º, 84.º e 90.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Artigo 52.º - Maneio
 1 - A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico que possua formação teórica e prática específica ministrada ou certificada pela DGAV e em número adequado à quantidade e espécies animais que alojam
@@ -1803,12 +2091,12 @@
 O pessoal auxiliar deve possuir os conhecimentos e a experiência adequada, o qual fica, contudo, sob a orientação do médico veterinário responsável.</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Art.º 19.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>Artigo 19.º — Pessoal auxiliar
 Os alojamentos devem dispor de pessoal auxiliar que possua os conhecimentos e a aptidão necessária para assegurar os cuidados adequados aos animais, o qual fica sob a orientação do médico veterinário responsável.
@@ -1819,12 +2107,12 @@
 1 - Sem prejuízo de quaisquer medidas determinadas pela DGAV, nos locais de criação, manutenção e venda, bem como nos centros de recolha e alojamentos de hospedagem, deve existir um programa de profilaxia médica e sanitária, elaborado e supervisionado pelo médico veterinário responsável e executado por profissionais habilitados para o efeito.</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>Art.º 13.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Artigo 13.º - Maneio
 1. A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
@@ -1832,22 +2120,22 @@
 3. Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados.</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 13.º) exige pessoal 'técnico competente' com 'formação teórica e prática específica' e 'inspeção diária', mas não detalha competências concretas. O @regulamento especifica 4 competências estruturadas (comportamento biológico, reconhecimento de sofrimento, maneio e bem-estar, conhecimento de obrigações) e exige documentação de educação/formação/experiência.</t>
         </is>
       </c>
-      <c r="L9" s="9" t="inlineStr">
+      <c r="L13" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 19.º) é mais genérico: exige apenas 'conhecimentos e aptidão necessária' sob orientação do médico veterinário responsável. Não detalha competências concretas nem exigências de formação formal.</t>
         </is>
       </c>
-      <c r="M9" s="10" t="inlineStr">
+      <c r="M13" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.ºs 52.º, 69.º, 84.º, 90.º) aproxima-se mais do @regulamento: menciona 'necessidades fisiológicas e etológicas', exige formação certificada. Lacuna: não detalha as 4 competências específicas do @regulamento (reconhecimento de sofrimento, condicionamento operante, etc.).</t>
         </is>
       </c>
-      <c r="N9" s="11" t="inlineStr">
+      <c r="N13" s="11" t="inlineStr">
         <is>
           <t>Necessidade de: 
 (1) detalhar as 4 competências específicas (comportamento, reconhecimento de sofrimento, maneio positivo, conhecimento de obrigações); 
@@ -1856,25 +2144,25 @@
 (4) implementar requisitos mínimos de formação via regulamento delegado.</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O13" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P9" s="11" t="inlineStr"/>
+      <c r="P13" s="11" t="inlineStr"/>
     </row>
-    <row r="10" ht="120" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Supervisão de Bem-Estar</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Art.º 13.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall:
 (a)	ensure that the establishments for which they are responsible receive a visit by a veterinarian for the purpose of identifying and assessing any risk factor for the welfare of the dogs or cats and advising the operator on measures to address those risks initially by ... [date three years after the date of entry into force of this Regulation] or one year following the notification of the new establishment, and thereafter when appropriate, based on a risk analysis by the competent authorities, or on an annual basis if Member States so provide in their national law;
@@ -1882,7 +2170,7 @@
 2. By ... [date 24 months from the date of entry into force of this Regulation], the Commission shall adopt delegated acts in accordance with Article 28 supplementing this Article by laying down the minimum criteria to be assessed by the veterinarian during the advisory welfare visit.</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores devem:
 (a) assegurar que os estabelecimentos sob a sua responsabilidade recebem uma visita de um médico veterinário no prazo de um ano a partir da data de aplicação do presente Regulamento ou no prazo de um ano após notificação de novo estabelecimento, com o objetivo de identificar e avaliar quaisquer fatores de risco para o bem-estar dos cães ou gatos e aconselhar o operador sobre medidas para resolver esses riscos; depois, as visitas do médico veterinário devem ocorrer quando apropriado, com base numa análise de risco pelas autoridades competentes; os Estados-Membros podem estabelecer que as visitas de aconselhamento de bem-estar sejam anuais;
@@ -1890,12 +2178,12 @@
 2. Dentro de 24 meses a partir da data de entrada em vigor do presente Regulamento, a Comissão deve adotar atos delegados em conformidade com o artigo 28.º que complementem o presente artigo de forma a estabelecer critérios mínimos a serem avaliados durante a visita de aconselhamento de bem-estar.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Art.º 56.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Artigo 56.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem, com exceção dos alojamentos para hospedagem com fins higiénicos, devem ter ao seu serviço um médico veterinário responsável pelo alojamento.
@@ -1906,12 +2194,12 @@
 d) A colaboração com as autoridades competentes em todas as ações que estas determinem.</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>Art.º 32.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Artigo 32.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem sem fins lucrativos e com fins lucrativos de animais, com exceção dos com fins higiénicos, necessitam de ter ao seu serviço um médico veterinário que seja responsável pelo alojamento.
@@ -1921,12 +2209,12 @@
 c) A colaboração com as autoridades competentes em todas as ações que estas determinarem.</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>Art.º 4.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>Artigo 4.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem sem fins lucrativos e com fins lucrativos de animais, com exceção dos alojamentos para hospedagem com fins higiénicos, devem ter ao seu serviço um médico veterinário que seja responsável pelo alojamento.
@@ -1936,49 +2224,49 @@
 c) A colaboração com as autoridades competentes em todas as ações que estas determinarem.</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>Estabelece a obrigação de ter médico veterinário responsável que execute 'programas e ações' para saúde e bem-estar, 
 Não fixa prazos para avaliações de bem-estar nem obrigações de manutenção de registos estruturados, conforme @regulamento</t>
         </is>
       </c>
-      <c r="L10" s="9" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>Replica quase verbatim o art.º 4.º do DL n.º 276/2001, mas exclui «ações»
 Não fixa prazos para avaliações de bem-estar nem obrigações de manutenção de registos estruturados, conforme @regulamento</t>
         </is>
       </c>
-      <c r="M10" s="10" t="inlineStr">
+      <c r="M14" s="10" t="inlineStr">
         <is>
           <t>Recupera as «ações»
 Reforça a obrigação com 'parecer relativo à verificação das condições higiossanitárias e de bem-estar'
 Não fixa prazos para avaliações de bem-estar nem obrigações de manutenção de registos estruturados, conforme @regulamento</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="N14" s="11" t="inlineStr">
         <is>
           <t>O @regulamento exige 'visita de um veterinário' num prazo específico (1 ano) após entrada em funcionamento com manutenção de registos por 4 anos e transmissão entre veterinários. Necessidade de alteração: (1) formalizar obrigação de 'visita de avaliação' por veterinário dentro de 1 ano após implementação do regulamento/notificação; (2) exigir avaliações periódicas conforme risco; (3) obrigatória manutenção de registos por 4 anos;</t>
         </is>
       </c>
-      <c r="O10" s="11" t="inlineStr">
+      <c r="O14" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P10" s="11" t="inlineStr"/>
+      <c r="P14" s="11" t="inlineStr"/>
     </row>
-    <row r="11" ht="120" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="15" ht="120" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Alimentação e Abeberamento</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Art.º 14.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that dogs and cats are fed in accordance with the requirements laid down in point 1 of Annex I.
 2. In addition, operators shall ensure that dogs and cats are adequately fed and hydrated by supplying:
@@ -1994,7 +2282,7 @@
 4. Where advised in writing by a veterinarian to do so, the operators may adjust the feeding and watering frequencies for an individual dog or cat. The operators shall keep a record of that written advice for the entire duration of those arrangements.</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores devem assegurar que os cães ou gatos são alimentados em conformidade com os requisitos estabelecidos no ponto 1 do Anexo I.
 2. Os operadores devem assegurar que os cães ou gatos sejam alimentados e hidratados de forma adequada, fornecendo-lhes:
@@ -2010,12 +2298,12 @@
 4.	Quando aconselhado por escrito por um médico veterinário, os operadores podem ajustar as frequências de alimentação e hidratação para um cão ou gato individual. Os operadores devem manter um registo do conselho durante toda a sua duração, conforme aconselhado pelo médico veterinário.</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Art. 51.º do RGBEAC (proposta, jun 2025)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>1 - Deve existir um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies e dos indivíduos de acordo com a fase de evolução fisiológica em que se encontram, nomeadamente idade, sexo, fêmeas prenhes ou em fase de lactação.
 2 - As refeições devem ainda ser distribuídas segundo a rotina que mais se adequar à espécie e de forma a manter aspetos do seu comportamento alimentar natural, incluindo comedouros interativos e outros dispositivos adequados à espécie.
@@ -2029,12 +2317,12 @@
 Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável.</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Art.º 46.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>1 - A alimentação dos animais de companhia, nos locais de criação, manutenção e venda bem como nos centros de recolha e instalações de hospedagem, deve obedecer a um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies e dos indivíduos, de acordo com a fase de evolução fisiológica em que se encontram, nomeadamente idade, sexo, fêmeas prenhes ou em fase de lactação.
 2 - As refeições devem ainda ser variadas, sendo distribuídas segundo a rotina que mais se adequar à espécie e de forma a manter, tanto quanto possível, aspetos do seu comportamento alimentar natural.
@@ -2045,12 +2333,12 @@
 7 - É proibido alimentar animais com restos de comida, produtos de pastelaria e desperdícios da indústria alimentar e de restauração.</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>Artigo 12.º Decreto-Lei n.º 276/2001</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>1 — Deve existir um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies e dos indivíduos de acordo com a fase de evolução fisiológica em que se encontram, nomeadamente idade, sexo, fêmeas prenhes ou em fase de lactação.
 2 — As refeições devem ainda ser variadas, sendo distribuídas segundo a rotina que mais se adequar à espécie e de forma a manter, tanto quanto possível, aspetos do seu comportamento alimentar natural.
@@ -2060,49 +2348,49 @@
 6 — Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr"/>
-      <c r="L11" s="9" t="inlineStr">
+      <c r="K15" s="8" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>Parece restringir as obrigações aos estabelecimentos.
 Apenas @código proíbe restos, pastelaria e desperdícios.</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>Introduz comedouros interativos e outros dispositivos adequados à espécie – pode ir ao encontro do conceito de categoria?
 Obriga a que não haja competição – mais restritivo que o @regulamento
 Retira a obrigatoriedade de aparelhos de frio</t>
         </is>
       </c>
-      <c r="N11" s="11" t="inlineStr">
+      <c r="N15" s="11" t="inlineStr">
         <is>
           <t>Regulamento introduz mais «categorias» - raça, categoria, nível de atividade e estado reprodutivo.
 Nenhum aborda transições alimentares graduais, cuidados específicos com desmame, segurança estrutural das instalações.</t>
         </is>
       </c>
-      <c r="O11" s="11" t="inlineStr">
+      <c r="O15" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P11" s="11" t="inlineStr">
+      <c r="P15" s="11" t="inlineStr">
         <is>
           <t>Nutrição e hidratação são também princípios básicos de bem-estar previstos pelo Artigo 5 – parágrafo 1 – alínea a) do @regulamento</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="120" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="16" ht="120" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Alojamento (Housing)</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Art.º 15.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>1. The operators of breeding and selling establishments shall ensure that dogs and cats are housed in accordance with point 2 of Annex I. The operators of shelters shall ensure that dogs and cats are housed in accordance with point 2.2 of Annex I.
 2. Operators shall ensure that:
@@ -2124,7 +2412,7 @@
 9. Paragraph 2, points (a), (b), (c) (f) and (g), and paragraphs 6, 7 and 8 shall apply neither to livestock guardian dogs, nor to herding dogs, during the periods where such dogs are used for guarding or herding in the context of seasonal transhumance on foot. Paragraph 2(f) shall not apply to livestock guardian dogs during the periods when such dogs are used for training purposes.</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores de estabelecimentos de criação e venda devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2 do Anexo I. Os operadores de abrigos devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2.2 do Anexo I.
 2. Os operadores devem assegurar que:
@@ -2146,12 +2434,12 @@
 9. Os n.ºs 2 (a), (b), (c), (f) e (g), 6, 7 e 8 não se aplicam nem aos cães de guarda de gado, nem aos cães de pastoreio, durante os períodos em que tais cães são utilizados para guarda ou pastoreio no contexto da transumância sazonal a pé. A alínea (f) do ponto 2 não se aplica aos cães de guarda de gado durante os períodos em que tais cães são utilizados para fins de formação.</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Artigos 47-57 - Regulação detalhada de alojamentos para hospedagem (estruturas, proteção, maneio, responsabilidades veterinárias).</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Artigo 47.º- Condições dos alojamentos
 1 - Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
@@ -2177,12 +2465,12 @@
 Os alojamentos devem assegurar as medidas de proteção contra incêndios previstas pela Autoridade Nacional de Emergência e Proteção Civil para o efeito.</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>Artigo 13.º - Condições dos alojamentos</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>1. - Os animais devem dispor de um espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
 a. A prática de exercício físico adequado;
@@ -2205,12 +2493,12 @@
 Os alojamentos devem assegurar que as espécies animais neles mantidas não possam causar quaisquer riscos para a saúde e para a segurança de pessoas, outros animais e bens</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>Art.º 8.º, Art.º 9.º, Art.º 15.º do DL n.º 276/2001</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>Artigo 8.º - Condições dos alojamentos
 1 - Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
@@ -2230,14 +2518,14 @@
 Artigo 15.º — Os alojamentos devem assegurar que as espécies animais neles mantidas não possam causar quaisquer riscos para a saúde e para a segurança de pessoas, outros animais e bens.</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr"/>
-      <c r="L12" s="9" t="inlineStr"/>
-      <c r="M12" s="10" t="inlineStr">
+      <c r="K16" s="8" t="inlineStr"/>
+      <c r="L16" s="9" t="inlineStr"/>
+      <c r="M16" s="10" t="inlineStr">
         <is>
           <t>@rgbeac prevê acesso diário a área de exercício exterior 2x/dia durante 30 minutos (= 1h total),</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr">
+      <c r="N16" s="11" t="inlineStr">
         <is>
           <t>N.º 2, Proibição expressa de manter cães ou gatos em contentores : não coberto, nenhum dos três diplomas contém esta proibição explícita. 
 N.º 3 – Exceções ao uso de contentores (transporte, isolamento curto prazo, espetáculos, neonatos com termorregulação reduzida ou acompanhados da mãe) Não coberto
@@ -2245,25 +2533,25 @@
 Prever exceções para cães de guarda de rebanho</t>
         </is>
       </c>
-      <c r="O12" s="11" t="inlineStr">
+      <c r="O16" s="11" t="inlineStr">
         <is>
           <t>Sim - Portaria complementar com especificações técnicas</t>
         </is>
       </c>
-      <c r="P12" s="11" t="inlineStr"/>
+      <c r="P16" s="11" t="inlineStr"/>
     </row>
-    <row r="13" ht="120" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="17" ht="120" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Saúde</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Art.º 16.º do Regulamento 2023/0447 (PE/Conselho)  |  EN</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that:
 (a) dogs or cats for which they are responsible are inspected by animal carers at least once a day and that vulnerable dogs and cats, such as newborns, ill or injured dogs and cats, and peri-partum bitches and queens, are inspected more frequently.
@@ -2283,7 +2571,7 @@
 (e) dogs and cats which are no longer used for reproduction, including as a result of the provisions of this Regulation, are either kept or sold, donated or rehomed, and not killed or abandoned.</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores devem assegurar que:
 (a) os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados e fêmeas em período peri-parto, são inspecionados com maior frequência;
@@ -2303,12 +2591,12 @@
 (e)  os cães e gatos que deixem de ser utilizados para reprodução, nomeadamente em resultado das disposições do presente Regulamento, são mantidos ou vendidos, doados ou realojados, não sendo mortos nem abandonados.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Arts.º 33.º e 55.º do RGBEAC — Regime Geral do Bem-Estar dos Animais de Companhia (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Artigo 33.º — Cuidados de saúde (geral)
 1. Os detentores dos animais de companhia devem assegurar-lhes os cuidados de saúde adequados, nomeadamente seguindo as orientações da DGAV em matéria de vacinação e tratamentos obrigatórios, bem como consultas regulares junto de médico veterinário.
@@ -2332,12 +2620,12 @@
 6. A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior deve ser feita sob orientação do médico veterinário responsável.</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>Art.º 6.º (Cuidados médico-veterinários) do Código do Animal — DL n.º 214/2013</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>Artigo 6.º — Cuidados médico-veterinários
 O detentor do animal deve assegurar ao animal ferido ou doente os cuidados médico-veterinários adequados, designadamente retirando o mesmo do alojamento sempre que este seja um local de venda.
@@ -2356,12 +2644,12 @@
 6. A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior, deve ser feita sob orientação do médico veterinário responsável.</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>Art.º 13.º (Maneio) e art.º 16.º (Cuidados de saúde animal) do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>Artigo 13.º — Maneio
 1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
@@ -2378,46 +2666,46 @@
 6 — A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior deve ser feita sob orientação do médico veterinário responsável.</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="K17" s="8" t="inlineStr">
         <is>
           <t>Em análise</t>
         </is>
       </c>
-      <c r="L13" s="9" t="inlineStr">
+      <c r="L17" s="9" t="inlineStr">
         <is>
           <t>Em análise</t>
         </is>
       </c>
-      <c r="M13" s="10" t="inlineStr">
+      <c r="M17" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.º 33.º) centra os cuidados de saúde no detentor em geral (n.ºs 1 a 3), sem distinguir obrigações reforçadas para operadores de criação. Os n.ºs 4 e 5 (CAMV e denúncia de maus-tratos) não têm correspondência direta no @regulamento.</t>
         </is>
       </c>
-      <c r="N13" s="11" t="inlineStr">
+      <c r="N17" s="11" t="inlineStr">
         <is>
           <t>Necessidade de alteração dos três diplomas: (1) introduzir inspeção diária diferenciada para animais vulneráveis (al. (a) do n.º 1 do art.º 13.º do @regulamento); (2) para criadores (n.º 2): fixar idade mínima e maturidade esquelética das fêmeas reprodutoras, frequência máxima de partos conforme Anexo I, proibição de cobrição de fêmeas a lactar, e regime de rehoming dos animais retirados da reprodução.
 Ver ainda análise do art.º 8.º do @regulamento, que tem as disposições sobre estratégias e saúde reprodutiva</t>
         </is>
       </c>
-      <c r="O13" s="11" t="inlineStr">
+      <c r="O17" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P13" s="11" t="inlineStr"/>
+      <c r="P17" s="11" t="inlineStr"/>
     </row>
-    <row r="14" ht="120" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="18" ht="120" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Necessidades Comportamentais (Behavioural needs)</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Art.º 17.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that measures are taken to meet the behavioural needs of dogs and cats in accordance with point 4 of Annex I.
 2. In addition, operators shall not keep dogs or cats in areas which limit their natural movements, except in cases where Article 15(3), second subparagraph, applies or where the following procedures or treatments are performed:
@@ -2434,7 +2722,7 @@
 7.	Operators shall ensure that enrichments are provided and accessible to all dogs or cats, creating a stimulating environment for them, enabling them to develop and exhibit species-specific behaviour and reducing their frustration.</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores devem assegurar que medidas são tomadas para satisfazer as necessidades comportamentais de cães ou gatos em conformidade com o ponto 4 do Anexo I.
 2. Os operadores não devem manter cães ou gatos em áreas que restringem os seus movimentos naturais, exceto no caso do artigo 15.º (parágrafo 3), segundo parágrafo, ou para realizar os seguintes procedimentos ou tratamentos:
@@ -2451,12 +2739,12 @@
 7. Os operadores devem assegurar que o enriquecimento seja facultado e esteja acessível a todos os cães ou gatos, criando-lhes um ambiente estimulante que lhes permita desenvolver e exibir comportamentos específicos da espécie e reduza a sua frustração.</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Arts. 47.º e 52.º (n.º 7) do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Artigo 47.º — Condições dos alojamentos
 1 - Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
@@ -2472,12 +2760,12 @@
 7 – Todos os alojamentos para hospedagem de cães e gatos, à exceção dos alojamentos com fins higiénicos, devem dispor de um plano de socialização e enriquecimento ambiental.</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>Art.º 13.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>Artigo 13.º — Condições dos alojamentos
 1 - Os animais devem dispor de um espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
@@ -2489,12 +2777,12 @@
 5 - As instalações devem ser equipadas de acordo com as necessidades específicas dos animais que albergam, com materiais e equipamento que estimulem a expressão dos comportamentos naturais, nomeadamente material para substrato, cama ou ninhos, ramos, buracos, locais para banhos e outros quaisquer adequados ao fim em vista.</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>art.º 8.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>1 — Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
 a) A prática de exercício físico adequado;
@@ -2505,37 +2793,37 @@
 5 — As instalações devem ser equipadas de acordo com as necessidades específicas dos animais que albergam, com materiais e equipamento que estimulem a expressão do repertório de comportamentos naturais, nomeadamente material para substrato, cama ou ninhos, ramos, buracos, locais para banhos e outros quaisquer adequados ao fim em vista.</t>
         </is>
       </c>
-      <c r="K14" s="8" t="inlineStr"/>
-      <c r="L14" s="9" t="inlineStr">
+      <c r="K18" s="8" t="inlineStr"/>
+      <c r="L18" s="9" t="inlineStr">
         <is>
           <t>Sem especificações sobre socialização e enriquecimento</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M18" s="10" t="inlineStr">
         <is>
           <t>Cobertura mais significtiva</t>
         </is>
       </c>
-      <c r="N14" s="11" t="inlineStr"/>
-      <c r="O14" s="11" t="inlineStr">
+      <c r="N18" s="11" t="inlineStr"/>
+      <c r="O18" s="11" t="inlineStr">
         <is>
           <t>Em análise. RGBEAC alinha melhor; implementação de reforço positivo obrigatório recomendada</t>
         </is>
       </c>
-      <c r="P14" s="11" t="inlineStr"/>
+      <c r="P18" s="11" t="inlineStr"/>
     </row>
-    <row r="15" ht="120" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="19" ht="120" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Práticas Dolorosas (Painful practices)</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Art.º 18.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that mutilations, including ear cropping, tail docking, claw removal or other partial or complete digit amputation, and resection of vocal cords or folds,  are not performed unless justified by medical indications, including where the procedure is prophylactic, with the sole purpose of maintaining or improving the health of dogs or cats or preventing their injury. In such cases, the procedure shall be performed  only under anaesthesia and prolonged analgesia and only by a veterinarian.
 2. The medical indications justifying the mutilation, and the details of procedure carried out, shall be documented by a veterinarian. That document shall be retained by the operator and shall accompany the dog or cat when it is transferred to another establishment or owner. The operator of the establishment where the mutilation was performed shall retain a copy of the document for the first three years after that transfer.
@@ -2552,7 +2840,7 @@
 Member States may grant exemptions from the first subparagraph for dogs intended for use in military, police or customs services.</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores devem assegurar que mutilações, incluindo corte de orelhas, corte de cauda, remoção de garras ou amputação parcial ou completa de dígitos, e ressecção de cordas vocais ou pregas, não são realizadas a menos que por indicação médica, que pode incluir profilática, com o único propósito de preservar, melhorar a saúde de cães ou gatos ou prevenir ferimentos. Nesse caso, o procedimento deve ser realizado apenas sob anestesia e analgesia prolongada e por um médico veterinário.
 2. A indicação médica para a mutilação e os detalhes do procedimento realizado devem ser documentados por um médico veterinário. Este documento deve ser retido pelo operador até que o cão ou gato, juntamente com este documento, seja transferido para outro estabelecimento ou proprietário. O operador do estabelecimento onde a mutilação foi realizada deve reter uma cópia do documento durante três anos após a transferência do cão ou gato.
@@ -2569,12 +2857,12 @@
 Os Estados-Membros podem conceder derrogações do primeiro parágrafo para cães destinados a uso em serviços militares, policiais ou aduaneiros.</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>RGBEAC (proposta, jun. 2025) - Artigo 12.º</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Art. 12.º
 i)	Sujeitá-los a intervenções cirúrgicas, com o objetivo de modificar a sua aparência ou alcançar outros fins não curativos, ou não destinados a impedir a reprodução, em particular, corte da cauda, secção das cordas vocais, remoção de unhas ou dentes, e corte das orelhas que não seja realizada para fins de identificação de animais esterilizados conforme boas práticas internacionais
@@ -2588,12 +2876,12 @@
 O detentor de um animal de companhia que pretenda controlar a reprodução do mesmo deve fazê-lo de acordo com as orientações de um médico veterinário, salvaguardando sempre o mínimo sofrimento do animal"</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>Arts. 51.º e 52.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>Artigo 51.o Intervenções cirúrgicas
 As intervenções cirúrgicas têm de ser executadas por um médico veterinário.
@@ -2606,12 +2894,12 @@
 6 - Os detentores de animais importados que apresentem quaisquer das amputações referidas no n.º 1 devem possuir documento comprovativo da necessidade dessa mutilação, passada pelo médico veterinário que a ela procedeu, legalizado pela autoridade competente do respetivo país.</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Decreto-Lei n.º 276/2001 - Artigo 18.º</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>Artigo 17.º
 As intervenções cirúrgicas, nomeadamente as destinadas ao corte de caudas nos canídeos, têm de ser executadas por um médico veterinário.
@@ -2620,55 +2908,55 @@
 2 — O documento referido no número anterior deve ter a forma de um atestado, do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura.</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr"/>
-      <c r="L15" s="9" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr">
+      <c r="K19" s="8" t="inlineStr"/>
+      <c r="L19" s="9" t="inlineStr"/>
+      <c r="M19" s="10" t="inlineStr">
         <is>
           <t>@rgbeac ressalva expressamente o corte das orelhas que não seja realizada para fins de identificação de animais esterilizados conforme boas práticas internacionais", o que cobre o essencial desta derrogação.</t>
         </is>
       </c>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="N19" s="11" t="inlineStr">
         <is>
           <t>exige expressamente anestesia e analgesia prolongada como condição do procedimento.
 Rever proibições na análise do art.7.º</t>
         </is>
       </c>
-      <c r="O15" s="11" t="inlineStr">
+      <c r="O19" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P15" s="11" t="inlineStr"/>
+      <c r="P19" s="11" t="inlineStr"/>
     </row>
-    <row r="16" ht="120" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="20" ht="120" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Espetáculos e Competições Estéticas</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Art.º 19.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>1. In aesthetic shows, exhibitions and competitions of dogs and cats, operators of breeding and selling establishments shall not use dogs or cats with excessive conformational traits, or dogs or cats which have been mutilated in a way that alters their physical characteristics.
 2. When organising aesthetic shows, exhibitions and competitions of dogs and cats, organisers shall exclude dogs and cats which have excessive conformational traits or dogs or cats which have been mutilated in a way that alters their physical characteristics.</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores de estabelecimentos de criação e venda não devem utilizar em espetáculos, exposições e competições estéticas de cães e gatos, cães ou gatos com características conformacionais excessivas ou cães ou gatos que tenham sido mutilados de tal forma que resulte numa alteração de características físicas.
 2. Os organizadores de espetáculos, exposições e competições estéticas de cães e gatos devem excluir de tais espetáculos, exposições e competições cães e gatos que tenham características conformacionais excessivas ou cães ou gatos que tenham sido mutilados de tal forma que resulte numa alteração de características físicas.</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Art.º 39.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Artigo 39.º - Participação em eventos
 1. A participação de animais de companhia em concursos, exposições, espetáculos, manifestações culturais, divertimentos públicos, atividades performativas, cinematográficas e audiovisuais, campanhas publicitárias ou outros eventos onde participem animais de companhia carece de autorização do diretor-geral da DGAV da área da realização da mesma, após parecer da respetiva câmara municipal.
@@ -2700,12 +2988,12 @@
 9. É proibida a participação de animais de companhia em eventos onde seja utilizada pirotecnia.</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>Art.º 79.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>Artigo 79.º - Concursos e exposições
 1 - A realização de concursos e exposições com animais de companhia carece de autorização prévia da câmara municipal, ficando esta dependente do parecer vinculativo do MVM.
@@ -2730,12 +3018,12 @@
 5 - A exposição de animais para adoção, promovida por associações de proteção animal ou por particulares, que não nos alojamentos para hospedagem registados no âmbito do presente diploma, depende de autorização prévia do município, sob parecer vinculativo do MVM.</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>DL 314/2003 de 17 dezembro</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>Artigo 4.º - Exposições
 1. A participação de cães e gatos em concursos e exposições está sujeita às normas sanitárias emitidas pela DGV.
@@ -2761,18 +3049,18 @@
 e) Proceder às observações que entenderem necessárias para a defesa sanitária da exposição ou concurso.</t>
         </is>
       </c>
-      <c r="K16" s="8" t="inlineStr">
+      <c r="K20" s="8" t="inlineStr">
         <is>
           <t>Cães/gatos em concursos/exposições</t>
         </is>
       </c>
-      <c r="L16" s="9" t="inlineStr">
+      <c r="L20" s="9" t="inlineStr">
         <is>
           <t>Cães/gatos em concursos/exposições e acrescenta adoções
 Parecer MVM vinculativo</t>
         </is>
       </c>
-      <c r="M16" s="10" t="inlineStr">
+      <c r="M20" s="10" t="inlineStr">
         <is>
           <t>Todos animais de companhia em múltiplos eventos (concursos, campanhas, cinema, etc.)
 Câmara Municipal (consultivo)
@@ -2781,30 +3069,30 @@
 Proibida pirotecnia</t>
         </is>
       </c>
-      <c r="N16" s="11" t="inlineStr">
+      <c r="N20" s="11" t="inlineStr">
         <is>
           <t>Prever a exclusão de animais com características conformacionais excessivas</t>
         </is>
       </c>
-      <c r="O16" s="11" t="inlineStr">
+      <c r="O20" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P16" s="11" t="inlineStr"/>
+      <c r="P20" s="11" t="inlineStr"/>
     </row>
-    <row r="17" ht="120" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="21" ht="120" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Identificação e Registo</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Art.º 20.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>1. All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip that complies with the requirements set out in Annex II.
 2. Operators shall ensure that dogs and cats born in their establishments are individually identified within three months after their birth, and in any event before the date that they are placed on the market.
@@ -2824,7 +3112,7 @@
 (c)	 for pet owners and other natural or legal persons other than operators, who do not place cats on the market: from … [15 years from entry into force of this Regulation.</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>1.	Todos os cães e gatos mantidos em estabelecimentos, colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva, devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com os requisitos estabelecidos no Anexo II.
 2.	Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de três meses após o nascimento e, em qualquer caso, antes da data da sua colocação no mercado.
@@ -2843,12 +3131,12 @@
 (c)	aos donos de animais de companhia e outras pessoas singulares ou coletivas que não sejam operadores e que não coloquem gatos no mercado, a partir de … [15 anos após a entrada em vigor do presente Regulamento].</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Art.º 17.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>1 — A identificação dos animais de companhia, pela sua marcação, quando aplicável, e registo no SIAC, deve ser realizada:
 a) Relativamente aos cães, gatos e furões nascidos em alojamentos, até aos três meses de idade ou, em qualquer caso, antes da sua colocação no mercado;
@@ -2857,12 +3145,12 @@
 (…)</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>Art.º 53.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>1 — Todos os cães devem ser identificados e registados, entre os três e os seis meses de idade.
 2 — Os gatos em exposição, para fins comerciais ou lucrativos, em estabelecimentos de venda, locais de criação, feiras ou concursos, provas funcionais, publicidade ou fins similares, devem ser identificados e registados entre os três e os seis meses de idade.
@@ -2871,12 +3159,12 @@
 (…)</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>DL n.º 82/2019, de 27 de junho</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>1 — A identificação dos animais de companhia, pela sua marcação e registo no SIAC, deve ser realizada até 120 dias após o seu nascimento.
 2 — Na impossibilidade de determinar a data de nascimento exata, para efeitos de contagem do prazo referido no número anterior, a identificação deve ser efetuada até à perda dos dentes incisivos de leite.
@@ -2884,46 +3172,46 @@
 (…)</t>
         </is>
       </c>
-      <c r="K17" s="8" t="inlineStr">
+      <c r="K21" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 82/2019 (art.º 5.º) prevê prazo geral de 120 dias após o nascimento, sem distinguir o contexto de estabelecimento — prazo superior ao máximo de 3 meses do @regulamento, que exigirá redução. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
-      <c r="L17" s="9" t="inlineStr">
+      <c r="L21" s="9" t="inlineStr">
         <is>
           <t>O @codigo fixa prazo de identificação entre 3 e 6 meses, sem distinção entre nascimentos e entrada em estabelecimentos, como previsto pelo @regulamento</t>
         </is>
       </c>
-      <c r="M17" s="10" t="inlineStr">
+      <c r="M21" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac aproxima-se dos prazos do @regulamento: identificação até aos três meses e prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
-      <c r="N17" s="11" t="inlineStr">
+      <c r="N21" s="11" t="inlineStr">
         <is>
           <t>Necessidade de alteração: (1) reduzir prazo máximo de identificação de nascimentos para 3 meses; (2) criar prazo diferenciado de 30 dias para animais admitidos em estabelecimentos; (3) harmonizar prazos entre todos os diplomas nacionais.
 Necessário análise mais aprofundada</t>
         </is>
       </c>
-      <c r="O17" s="11" t="inlineStr">
+      <c r="O21" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P17" s="11" t="inlineStr"/>
+      <c r="P21" s="11" t="inlineStr"/>
     </row>
-    <row r="18" ht="120" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="22" ht="120" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Requisitos de Publicidade em Linha e Colocação no Mercado</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Art.º 21.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>1.	When operators advertise a dog or a cat online with a view to placing it on the Union market, they shall ensure that the following warning is included in the advertisement in clearly visible and bold characters:
 “An animal is not a toy. Getting one is a life-changing decision. It is your duty to ensure the animal’s health and welfare and not to abandon it.”.
@@ -2953,7 +3241,7 @@
 Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 29.</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>1.	Quando operadores anunciem online um cão ou gato com vista ao seu colocamento no mercado da União, devem assegurar a apresentação do seguinte aviso no anúncio em caracteres claramente visíveis e em negrito:
 "Um animal não é um brinquedo. Ter um é uma decisão que muda a vida. É seu dever assegurar a sua saúde e bem-estar e não o abandonar."
@@ -2983,12 +3271,12 @@
 Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Art.º 91 a 95.º + Art.º 115.º n.º 3 do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Artigo 91.º- Procedimento de venda
 1 – A venda de animais só pode ser exercida nos alojamentos referidos no artigo 68.º e a pessoas maiores de idade e plenamente capazes do exercício de direitos, mediante contrato de compra e venda reduzido a escrito.
@@ -3032,12 +3320,12 @@
 n.º 3 - É proibida a publicidade e comercialização de animais perigosos ou que demonstrem comportamento agressivo.</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>Art.º 24.º e Art.º 62.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>Artigo 80.º - Comércio de animais de companhia
 1 - O comércio de animais de companhia, em particular de cães e de gatos, apenas é permitido quando os mesmos sejam provenientes de alojamentos para hospedagem devidamente autorizados.
@@ -3058,12 +3346,12 @@
 12 - É proibida a colocação para venda e a publicidade dos animais cuja detenção é proibida por legislação específica</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>DL 276/2001, DL 82/2019 - Normas de comercialização</t>
         </is>
       </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Artigo 53.º - Requisitos de validade do anúncio de venda de animal de companhia
 1 - Qualquer anúncio de transmissão, a título oneroso, de animais de companhia deve conter as seguintes informações:
@@ -3077,41 +3365,41 @@
 4 - No caso de anúncios de animais de raça indeterminada é proibida qualquer referência a raças no texto do anúncio.</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr"/>
-      <c r="L18" s="9" t="inlineStr">
+      <c r="K22" s="8" t="inlineStr"/>
+      <c r="L22" s="9" t="inlineStr">
         <is>
           <t>Apenas proíbe a venda de animais de companhia sem documentação adequada e restringe a comercialização de animais com comportamentos perigosos. As disposições cobrem identificação obrigatória e informações sobre o animal antes da venda.</t>
         </is>
       </c>
-      <c r="M18" s="10" t="inlineStr">
+      <c r="M22" s="10" t="inlineStr">
         <is>
           <t>SIM - Proibição clara de publicidade e venda online, com requisitos de local licenciado</t>
         </is>
       </c>
-      <c r="N18" s="11" t="inlineStr">
+      <c r="N22" s="11" t="inlineStr">
         <is>
           <t>@rgbeac tem concordâncias extensas mas falta a implementação do sistema de verificação online com token único conforme Art. 17a.6 do Regulamento. A proibição é mais restritiva que o Regulamento que permite venda online com verificação.</t>
         </is>
       </c>
-      <c r="O18" s="11" t="inlineStr">
+      <c r="O22" s="11" t="inlineStr">
         <is>
           <t>Sim - Sistema de verificação online com token único</t>
         </is>
       </c>
-      <c r="P18" s="11" t="inlineStr"/>
+      <c r="P22" s="11" t="inlineStr"/>
     </row>
-    <row r="19" ht="120" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="23" ht="120" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Treino de Cuidadores de Animais</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Art.º 22.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>1. For the purposes of Article 12, the competent authorities shall be responsible for:
 (a)	ensuring that training courses are available for animal carers;
@@ -3121,7 +3409,7 @@
 2. A European Union Reference Centre for Animal Welfare designated in accordance with Article 95 of Regulation (EU) 2017/625 may develop models of training materials and recommendations for the competent authorities or other providers of training courses.</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>1. Para efeitos do artigo 12.º, as autoridades competentes são responsáveis por:
 a) Assegurar que existem cursos de formação disponíveis para cuidadores de animais;
@@ -3131,12 +3419,12 @@
 3. O Centro de Referência da União Europeia para o Bem-Estar Animal designado em conformidade com o artigo 95.º do Regulamento (UE) 2017/625 pode desenvolver modelos de materiais de formação e recomendações para os fornecedores dos cursos de formação referidos no parágrafo 1.</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Arts. 118.º, 119.º, 120.º, Secção I, do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Artigo 118.º - Reserva de atividade de treinadores de cães
 O treino de cães para qualquer fim, incluindo o treino básico de socialização e de obediência, de cães de assistência ou intervenções e terapias assistidas por animais, de cães para competição e para atividades desportivas, recreativas e para fins económicos, só pode ser ministrado por treinador possuidor do respetivo título profissional, emitido nos termos do artigo seguinte.
@@ -3176,70 +3464,70 @@
 2. Para efeitos do disposto no número anterior, deve ser considerada a existência de um plano de profilaxia médico-veterinária, que a duração e frequência das sessões ou atividades respeitam os períodos de descanso e recuperação do animal, que as interações humano-animal são positivas, que o animal tem a possibilidade de se retirar da atividade quando se mostra relutante em participar nela ou demonstre sinais de cansaço fadiga, que a condição física e temperamento do animal são adequados à atividade a realizar, que o animal apresenta motivação para a tarefa, que o detentor reconhece e atende aos sinais de stresse ou desconforto por parte do detentor, e que são proporcionados ao animal oportunidades para momentos lúdicos e de relaxamento.</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>Art. 7.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>1. Os detentores de cães devem promover o treino dos mesmos, com vista à sua socialização e obediência.
 2. O treino dos cães é realizado de acordo com as boas práticas em uso no exercício da atividade.</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>Decreto-Lei n.º 315/2009, de 29 de outubro,</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>Treino/Treinadores de cães potencialmente perigosos e perigosos
 Decreto-Lei n.º 74/2007, de 27 de março
  Treino em Cães de Assistência</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="K23" s="8" t="inlineStr">
         <is>
           <t>Cães de assistência e perigosos ou potencialmente perigosos a rever no contexto próprio, não abrangido pelo @regulamento</t>
         </is>
       </c>
-      <c r="L19" s="9" t="inlineStr">
+      <c r="L23" s="9" t="inlineStr">
         <is>
           <t>Necessita ir ao encontro da certificação</t>
         </is>
       </c>
-      <c r="M19" s="10" t="inlineStr">
+      <c r="M23" s="10" t="inlineStr">
         <is>
           <t>Cobertura completa, implementam sistema profissional com certificação pela Autoridade como requerido)
 Vai mais além e regula toda as facetas de treino, incluindo excetuando os perigos e potencialmente perigosos previstos na secção anterior</t>
         </is>
       </c>
-      <c r="N19" s="11" t="inlineStr">
+      <c r="N23" s="11" t="inlineStr">
         <is>
           <t>O RGBEAC cumpre os critérios ao prever um sistema robusto de certificação profissional para treinadores de cães com: título profissional obrigatório, requisitos de habilitação, provas teóricas e práticas, métodos baseados em reforço positivo, verificação de antecedentes criminais. 
 Na legislação vigente só se encontra referências ao treino no Decreto-Lei n.º 315/2009, de 29 de Outubro, (regime dos cães perigosos e potencialmente perigosos), e no Decreto-Lei n.º 74/2007, de 27 de março, relativo ao treino em Cães de Assistência</t>
         </is>
       </c>
-      <c r="O19" s="11" t="inlineStr">
+      <c r="O23" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P19" s="11" t="inlineStr"/>
+      <c r="P23" s="11" t="inlineStr"/>
     </row>
-    <row r="20" ht="120" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="24" ht="120" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Base de Dados de Cães e Gatos</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Art.º 23.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>1. Member States shall be responsible for establishing and maintaining databases for the registration of identified dogs and cats in accordance with Article 20(1) and (2) and Article 26(3) and Article 26(4), second subparagraph.
 2. For that purpose, the Member States may use databases maintained by another Member State, on the basis of appropriate arrangements between those Member States.
@@ -3255,7 +3543,7 @@
 Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 29.</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>1. Os Estados-Membros são responsáveis pela criação e manutenção de bases de dados para o registo de cães e gatos identificados, em conformidade com o artigo 20.º, n.ºs 1 e 2, e com o artigo 26.º, n.ºs 3 e 4, segundo parágrafo.
 2. Para este efeito, os Estados-Membros podem utilizar bases de dados mantidas por outro Estado-Membro, com base em acordos apropriados entre esses Estados-Membros.
@@ -3271,12 +3559,12 @@
 Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Art.º 20.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Artigo 20.º - Sistema de Informação de Animais de Companhia (SIAC)
 1. O SIAC reúne a informação relativa à rastreabilidade dos dispositivos de identificação, à identificação dos animais de companhia, à sua titularidade ou detenção e à informação relacionada com a defesa da saúde pública, saúde animal e bem-estar animal.
@@ -3285,12 +3573,12 @@
 4. As normas e procedimentos relativos ao funcionamento do SIAC constam de um Manual de Procedimentos SIAC, aprovado pelo diretor-geral de alimentação e veterinária.</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>Arts. 53.º, 55.º, 56.º, 57.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>Artigo 53.º - Identificação e registo na base de dados
 1 - Todos os cães devem ser identificados e registados entre os três e seis meses de idade.
@@ -3302,117 +3590,117 @@
 Artigo 56.º - Classificação dos animais (Cão, Cão Potencialmente Perigoso, Cão Perigoso, Gato)</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>DL n.º 82/2019, Art.º 2.º (Estabelece SIAC)</t>
         </is>
       </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>DL 82/2019 estabelece o SIAC com extensas disposições cobrindo: criação da base de dados, procedimentos de registo e controlos de acesso, gestão por DGAV, identificação eletrónica via transponder, segurança de dados e autorização de acesso, integração de registos de identificação de animais, gestão da distribuição de dispositivos de identificação, procedimentos de registo e atualização. O sistema é operacional desde 2019.</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr"/>
-      <c r="L20" s="9" t="inlineStr">
+      <c r="K24" s="8" t="inlineStr"/>
+      <c r="L24" s="9" t="inlineStr">
         <is>
           <t>Código do Animal estabelece estrutura completa com classificações</t>
         </is>
       </c>
-      <c r="M20" s="10" t="inlineStr">
+      <c r="M24" s="10" t="inlineStr">
         <is>
           <t>Reafirma e fortalece o sistema SIAC</t>
         </is>
       </c>
-      <c r="N20" s="11" t="inlineStr">
+      <c r="N24" s="11" t="inlineStr">
         <is>
           <t>A legislação portuguesa cumpre os requisitos do Artigo 19. O SIAC está operacional desde 2019, sob responsabilidade de DGAV, com: identificação eletrónica via microchip obrigatória, registo nacional centralizado, rastreabilidade, classificação de animais (normal/perigoso/potencialmente perigoso), integração de dados de saúde e bem-estar, conformidade com proteção de dados (Comissão Nacional de Proteção de Dados).</t>
         </is>
       </c>
-      <c r="O20" s="11" t="inlineStr">
+      <c r="O24" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P20" s="11" t="inlineStr"/>
+      <c r="P24" s="11" t="inlineStr"/>
     </row>
-    <row r="21" ht="120" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="25" ht="120" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Recolha de Dados sobre Bem-Estar Animal e Relatório</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Art.º 24.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>1. The competent authorities shall collect, analyse and publish the data on animal welfare set out in Annex III:
 2. The competent authorities shall draw up and transmit to the Commission a report in electronic form, on the data on animal welfare, set out in Annex III, by 31 August at three-yearly intervals. The first such report shall be drawn up and transmitted to the Commission by ... [date 6 years from the date of entry into force of this Regulation]. Each report shall contain a summary of the data gathered during the previous three years.
 3. The Commission may adopt implementing acts, establishing a harmonized methodology for collecting the data on animal welfare set out in Annex III and establishing a template for the report referred to in paragraph 2 of this Article. Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 29.</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>1. As autoridades competentes devem recolher, analisar e publicar os dados sobre bem-estar animal estabelecidos no Anexo III.
 2. As autoridades competentes devem elaborar e transmitir à Comissão um relatório em formato eletrónico, sobre os dados relativos ao bem-estar animal estabelecidos no Anexo III, até 31 de agosto, com periodicidade trienal. O primeiro relatório deve ser elaborado e transmitido à Comissão até ... [data 6 anos após a data de entrada em vigor do presente regulamento]. Cada relatório deve conter um resumo dos dados recolhidos durante os três anos anteriores.
 3. A Comissão pode adotar atos de execução que estabeleçam uma metodologia harmonizada para a recolha dos dados sobre bem-estar animal estabelecidos no Anexo III e que definam um modelo para o relatório referido no n.º 2 do presente artigo. Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Análise no Anexo III</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>Análise no Anexo III</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="H25" s="6" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Análise no Anexo III</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr"/>
-      <c r="K21" s="8" t="inlineStr"/>
-      <c r="L21" s="9" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr"/>
+      <c r="K25" s="8" t="inlineStr"/>
+      <c r="L25" s="9" t="inlineStr">
         <is>
           <t>Análise no Anexo III</t>
         </is>
       </c>
-      <c r="M21" s="10" t="inlineStr">
+      <c r="M25" s="10" t="inlineStr">
         <is>
           <t>Análise no Anexo III</t>
         </is>
       </c>
-      <c r="N21" s="11" t="inlineStr">
+      <c r="N25" s="11" t="inlineStr">
         <is>
           <t>necessário: alinhamento da periodicidade de relatórios (atualmente anual; Regulamento requer trienal) e inclusão dos dados específicos de Annex III da EU (quando publicado).</t>
         </is>
       </c>
-      <c r="O21" s="11" t="inlineStr">
+      <c r="O25" s="11" t="inlineStr">
         <is>
           <t>Sim - Ajuste de periodicidade e conformidade com Annex III EU</t>
         </is>
       </c>
-      <c r="P21" s="11" t="inlineStr"/>
+      <c r="P25" s="11" t="inlineStr"/>
     </row>
-    <row r="22" ht="120" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="26" ht="120" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Proteção de Dados</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Art.º 25.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>1. The competent authorities of the Member States shall be controllers within the meaning of Regulation (EU) 2016/679 in relation to the processing of personal data collected under Articles 9 and 10 of this Regulation, as well as under Article 23(1) of this Regulation when used for the purposes of official control.
 The Commission shall be a controller within the meaning of Regulation (EU) 2018/1725 in relation to the processing of personal data collected under Article 21(5), Article 23(4), and Article 26(4), third subparagraph, , as well as under Article 23(1) of this Regulation when that data is used for the purposes of compliance with Article 108 of Regulation (EU) 2017/625 and the reporting obligations under this Regulation.
@@ -3427,7 +3715,7 @@
 (d) in the case of Article 26(4), third subparagraph, 5 years after the date of pre-notification.</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>1. As autoridades competentes dos Estados-Membros devem ser controladoras na aceção do Regulamento (UE) 2016/679 no que respeita ao tratamento de dados pessoais recolhidos nos termos dos artigos 9.º e 10.º do presente Regulamento, bem como no âmbito do artigo 23.º, n.º 1, do presente Regulamento quando utilizados para efeitos de controlo oficial.
 A Comissão deve ser controladora na aceção do Regulamento (UE) 2018/1725 no que respeita ao tratamento de dados pessoais recolhidos nos termos do artigo 21.º, n.º 5, do artigo 23.º, n.º 4, e do terceiro parágrafo do artigo 26.º, n.º 4, do presente Regulamento, bem como no âmbito do artigo 23.º, n.º 1, do presente Regulamento quando esses dados são utilizados para efeitos de conformidade com o artigo 108.º do Regulamento (UE) 2017/625 e de obrigações de comunicação de informações previstas no presente Regulamento.
@@ -3442,12 +3730,12 @@
 (d) (d)	no caso do artigo 26.º, n.º 4, terceiro parágrafo, 5 anos após a data da pré-notificação.</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>Art.º 20.º, nn. 3, 6, 8 do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>Artigo 20.º, n.º 8 - SIAC e Proteção de Dados:
 Ao tratamento, segurança, conservação, acesso e proteção dos dados pessoais constantes do SIAC é diretamente aplicável o disposto na legislação e regulamentação relativa à proteção de dados pessoais, nomeadamente o Regulamento (UE) 2016/679 do Parlamento Europeu e do Conselho, de 27 de abril de 2016, relativo à proteção das pessoas singulares no que diz respeito ao tratamento de dados pessoais e à livre circulação desses dados.
@@ -3457,12 +3745,12 @@
 A DGAV, pode atribuir a gestão do SIAC a outras entidades, mediante a celebração de protocolo e sob sua supervisão, observado o regime de subcontratação de tratamento de dados pessoais.</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>Art.º 55.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>Artigo 55.º - Base de Dados
 1 - Toda a informação resultante do registo do animal é coligida numa aplicação informática nacional.
@@ -3470,52 +3758,52 @@
 3 - Só têm acesso à base de dados as entidades que se encontrem autorizadas, para o efeito, pela DGAV.</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>DL n.º 82/2019, Art.º 9.º</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>Artigo 9.º - Registo no Sistema de Informação de Animais de Companhia
 1 - Os animais de companhia abrangidos pela obrigação de identificação devem ser registados pelo médico veterinário no SIAC, imediatamente após a sua marcação com o transponder, em nome do respetivo titular.</t>
         </is>
       </c>
-      <c r="K22" s="8" t="inlineStr"/>
-      <c r="L22" s="9" t="inlineStr">
+      <c r="K26" s="8" t="inlineStr"/>
+      <c r="L26" s="9" t="inlineStr">
         <is>
           <t>Cobertura expressa em Art. 55.º</t>
         </is>
       </c>
-      <c r="M22" s="10" t="inlineStr">
+      <c r="M26" s="10" t="inlineStr">
         <is>
           <t>Implementação completa em Arts. 20.º</t>
         </is>
       </c>
-      <c r="N22" s="11" t="inlineStr">
+      <c r="N26" s="11" t="inlineStr">
         <is>
           <t>A legislação portuguesa implementa completamente os requisitos de proteção de dados. O SIAC é configurado como sistema compliant com GDPR (EU 2016/679) e com regulamentações de proteção de dados.</t>
         </is>
       </c>
-      <c r="O22" s="11" t="inlineStr">
+      <c r="O26" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P22" s="11" t="inlineStr"/>
+      <c r="P26" s="11" t="inlineStr"/>
     </row>
-    <row r="23" ht="120" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="27" ht="120" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Entrada de Cães e Gatos na União</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Art.º 26.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>1.	Dogs and cats may be brought into the Union for the purpose of being placed on the Union market  only if the following conditions are met:
 (a)	they have been bred and kept in compliance with any of the following requirements:
@@ -3538,7 +3826,7 @@
 Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 29.</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>1.	Os cães e os gatos podem ser introduzidos na União para efeitos de colocação no mercado da União apenas se estiverem cumpridas as seguintes condições:
 (a)	tenham sido criados e mantidos em conformidade com qualquer das seguintes situações:
@@ -3561,12 +3849,12 @@
 Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Art.º 114.º e Art.º 96.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Artigo 114.º - Entrada no Território Nacional
 1 - A entrada no território nacional, por compra, cedência ou troca direta, de cães classificados como potencialmente perigosos pode ser condicionada.
@@ -3576,12 +3864,12 @@
 A importação de animais que constem da lista nacional de animais de companhia provenientes de outros Estados é admitida desde que sejam cumpridas as regras sanitárias e de bem-estar animal portuguesas e comunitárias.</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>Art.º 62.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>Artigo 62.º - Entrada de Animais de Companhia Suscetíveis à Raiva em Território Nacional
 1 - A entrada em território nacional de animais de companhia suscetíveis à raiva destinados ao comércio, provenientes de outros Estados-membros ou de países terceiros, depende do cumprimento das condições fixadas no Decreto-Lei n.º 79/2001, de 20 de junho, alterado pelo Decreto-Lei n.º 260/2012, de 12 de dezembro, e noutras normas de polícia sanitária que regem o comércio e as importações de animais vivos na comunidade.
@@ -3589,56 +3877,56 @@
 3 - A entrada em território nacional de furões destinados ao comércio ou sem carácter comercial, para além do cumprimento do disposto nos números anteriores, depende de autorização prévia do ICNF, I.P.</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>DL n.º 82/2019, Art.º 2.º</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>Vários artigos
 (…)</t>
         </is>
       </c>
-      <c r="K23" s="8" t="inlineStr">
+      <c r="K27" s="8" t="inlineStr">
         <is>
           <t>Sem database online de viajantes pré-notificação</t>
         </is>
       </c>
-      <c r="L23" s="9" t="inlineStr">
+      <c r="L27" s="9" t="inlineStr">
         <is>
           <t>Implementa controlos sanitários e requisitos de identificação</t>
         </is>
       </c>
-      <c r="M23" s="10" t="inlineStr">
+      <c r="M27" s="10" t="inlineStr">
         <is>
           <t>Cobre entrada no território nacional com condições, não cobre movimento não-comercial pré-notificação</t>
         </is>
       </c>
-      <c r="N23" s="11" t="inlineStr">
+      <c r="N27" s="11" t="inlineStr">
         <is>
           <t>A legislação portuguesa implementa os requisitos essenciais de entrada e identificação pré-entrada, referenciando os Regulamentos EU 576/2013 e 2016/429. Faltam: (1) Sistema de base de dados online de viajantes com pré-notificação obrigatória para movimento não-comercial; (2) Sistema iRASFF integrado para notificações de risco de fraude.</t>
         </is>
       </c>
-      <c r="O23" s="11" t="inlineStr">
+      <c r="O27" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P23" s="11" t="inlineStr"/>
+      <c r="P27" s="11" t="inlineStr"/>
     </row>
-    <row r="24" ht="120" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="28" ht="120" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Alteração dos Anexos</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Art.º 27.º do Regulamento 2023/0447 |  EN</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>The Commission is empowered to adopt delegated acts in accordance with Article 28 to amend the Annexes to this Regulation to take account of scientific and technical progress, including, where relevant, the scientific opinions of EFSA, as regards:
 (a) a suitable number of animal carers in breeding and selling establishments;
@@ -3657,7 +3945,7 @@
 Any additions of requirements in the Annexes shall be based on updated scientific or technical evidence, in particular such evidence regarding the specific conditions needed to ensure the welfare of the dogs and cats covered by the scope of this Regulation. Where relevant, those delegated acts shall take into account social, economic and environmental impacts and shall provide for sufficient transition periods to allow the operators concerned to adapt to the new requirements.</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>A Comissão fica habilitada a adotar atos delegados em conformidade com o artigo 28.º que alterem os anexos do presente Regulamento para ter em conta o progresso científico e técnico, incluindo, quando relevante, pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, nos seguintes aspetos:
 (a) Um número adequado de cuidadores de animais em estabelecimentos de criação e venda;
@@ -3676,63 +3964,63 @@
 Qualquer complemento de requisitos nos Anexos deve ser baseado em evidência científica ou técnica atualizada, em particular no que diz respeito às condições específicas necessárias para assegurar o bem-estar dos cães e gatos abrangidos pelo âmbito do presente Regulamento. Quando relevante, esses atos delegados devem levar em conta impactos sociais, económicos e ambientais e prever períodos de transição suficientes para permitir aos operadores envolvidos a adaptação aos novos requisitos.</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Sem equivalência</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>Sem equivalência.</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr"/>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="H28" s="6" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>Sem equivalência.</t>
         </is>
       </c>
-      <c r="J24" s="7" t="inlineStr"/>
-      <c r="K24" s="8" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr"/>
+      <c r="K28" s="8" t="inlineStr">
         <is>
           <t>Sem equivalência.</t>
         </is>
       </c>
-      <c r="L24" s="9" t="inlineStr">
+      <c r="L28" s="9" t="inlineStr">
         <is>
           <t>Sem equivalência.</t>
         </is>
       </c>
-      <c r="M24" s="10" t="inlineStr">
+      <c r="M28" s="10" t="inlineStr">
         <is>
           <t>Sem equivalência.</t>
         </is>
       </c>
-      <c r="N24" s="11" t="inlineStr"/>
-      <c r="O24" s="11" t="inlineStr">
+      <c r="N28" s="11" t="inlineStr"/>
+      <c r="O28" s="11" t="inlineStr">
         <is>
           <t>sem equivalência</t>
         </is>
       </c>
-      <c r="P24" s="11" t="inlineStr">
+      <c r="P28" s="11" t="inlineStr">
         <is>
           <t>.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="120" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="29" ht="120" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Exercício da Delegação</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Art.º 28.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>1. The power to adopt delegated acts is conferred on the Commission subject to the conditions laid down in this Article.
 2. The power to adopt delegated acts referred to in Article 7(8), Article 8(3), Article 13(2) and Article 27 shall be conferred on the Commission for an indeterminate period of time from … [the date of entry into force of this Regulation].
@@ -3742,7 +4030,7 @@
 6. A delegated act adopted pursuant to Article 7(8), Article 8(3), Article 13(2) or Article 27 shall enter into force only if no objection has been expressed either by the European Parliament or by the Council within a period of two months of notification of that act to the European Parliament and the Council or if, before the expiry of that period, the European Parliament and the Council have both informed the Commission that they will not object. That period shall be extended by two months at the initiative of the European Parliament or of the Council</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>1. O poder de adotar atos delegados é conferido à Comissão nas condições estabelecidas no presente artigo.
 2. O poder de adotar atos delegados referido no artigo 7.º, n.º 8, no artigo 8.º-A, n.º 3, no artigo 13.º, n.º 2, e no artigo 27.º é conferido à Comissão por tempo indeterminado a partir de [data de entrada em vigor do presente regulamento].
@@ -3752,196 +4040,196 @@
 6. Os atos delegados adotados nos termos do artigo 7.º, n.º 8, do artigo 8.º-A, n.º 3, do artigo 13.º, n.º 2, ou do artigo 27.º só entram em vigor se não tiverem sido formuladas objeções pelo Parlamento Europeu ou pelo Conselho no prazo de dois meses a contar da notificação desse ato ao Parlamento Europeu e ao Conselho, ou se, antes do termo desse prazo, o Parlamento Europeu e o Conselho tiverem informado a Comissão de que não têm objeções a formular. O referido prazo é prorrogado por dois meses por iniciativa do Parlamento Europeu ou do Conselho.</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="H29" s="6" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr"/>
-      <c r="K25" s="8" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr"/>
+      <c r="K29" s="8" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="L25" s="9" t="inlineStr">
+      <c r="L29" s="9" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="M25" s="10" t="inlineStr">
+      <c r="M29" s="10" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="N25" s="11" t="inlineStr">
+      <c r="N29" s="11" t="inlineStr">
         <is>
           <t>Artigo processual do Regulamento europeu — sem correspondência em legislação portuguesa.
 O regulamento principal fixa as regras de base, mas deixa alguns aspetos mais técnicos ou de pormenor para a Comissão completar mais tarde através de atos delegados</t>
         </is>
       </c>
-      <c r="O25" s="11" t="inlineStr">
+      <c r="O29" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P25" s="11" t="inlineStr"/>
+      <c r="P29" s="11" t="inlineStr"/>
     </row>
-    <row r="26" ht="120" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="30" ht="120" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Procedimento de Comité</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Art.º 29.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>1.	The Commission shall be assisted by the Standing Committee on Plants, Animals, Food and Feed established by Article 58(1) of Regulation (EC) No 178/2002. That Committee shall be a committee within the meaning of Regulation (EU) No 182/2011.
 2.	Where reference is made to this paragraph, Article 5 of Regulation (EU) No 182/2011 shall apply.
 Where the Committee delivers no opinion, the Commission shall not adopt the draft implementing act, and Article 5(4), third subparagraph, of Regulation (EU) No 182/2011 shall apply.</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>1 — A Comissão é assistida pelo Comité Permanente dos Vegetais, Animais e dos Alimentos para Consumo Humano e Animal criado pelo artigo 58.º, n.º 1, do Regulamento (CE) n.º 178/2002. Este comité deve ser entendido como comité na aceção do Regulamento (UE) n.º 182/2011.
 2 — Caso se faça referência ao presente número, aplica-se o artigo 5.º do Regulamento (UE) n.º 182/2011.
 3 — Na falta de parecer do comité, a Comissão não adota o projeto de ato de execução, aplicando-se o artigo 5.º, n.º 4, terceiro parágrafo, do Regulamento (UE) n.º 182/2011.</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="H30" s="6" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="J26" s="7" t="inlineStr"/>
-      <c r="K26" s="8" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr"/>
+      <c r="K30" s="8" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="L26" s="9" t="inlineStr">
+      <c r="L30" s="9" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="M26" s="10" t="inlineStr">
+      <c r="M30" s="10" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="N26" s="11" t="inlineStr"/>
-      <c r="O26" s="11" t="inlineStr">
+      <c r="N30" s="11" t="inlineStr"/>
+      <c r="O30" s="11" t="inlineStr">
         <is>
           <t>Não - Artigo processual sobre procedimento de comité — assistência à Comissão Europeia.</t>
         </is>
       </c>
-      <c r="P26" s="11" t="inlineStr"/>
+      <c r="P30" s="11" t="inlineStr"/>
     </row>
-    <row r="27" ht="120" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="31" ht="120" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Medidas Nacionais Mais Restritivas</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Art.º 30.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>1. This Regulation shall not prevent Member States from maintaining or adopting stricter national rules aimed at providing more extensive protection of the welfare of dogs and cats kept in establishments, and a greater traceability of dogs and cats, provided that those rules are not inconsistent with this Regulation and do not interfere with the proper functioning of the internal market.
 2. Member States shall, by ... [two years after the date of entry into force of this Regulation], inform the Commission about any existing stricter national rules that they intend to maintain in accordance with paragraph 1. Thereafter, Member States shall inform the Commission about stricter national rules before their adoption, unless the Member States have already notified the draft national rules as a draft technical regulation under Article 5 of Directive (EU) 2015/1535 of the European Parliament and of the Council. The Commission shall bring them to the attention of the other Member States.
 3. A Member State that has stricter national rules referred to in paragraph 1 shall not prohibit or impede the placing on the market within its territory of dogs and cats kept in another Member State on the grounds that the dogs and cats concerned have not been kept in accordance with its stricter national rules.</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>1. O presente regulamento não obsta a que os Estados-Membros mantenham disposições nacionais mais restritivas que visem uma proteção mais ampla do bem-estar dos cães e gatos detidos em estabelecimentos e a rastreabilidade dos cães e gatos, desde que essas disposições não sejam incompatíveis com o presente regulamento e não interfiram com o bom funcionamento do mercado interno.
 2. Os Estados-Membros devem informar a Comissão acerca de tais disposições nacionais existentes até [data de aplicação do presente regulamento] e devem informar a Comissão acerca de tais disposições nacionais novas antes da sua adoção, salvo se os Estados-Membros tiverem notificado os projetos de disposições nacionais em conformidade com a Diretiva (UE) 2015/1535. A Comissão transmite essas informações aos outros Estados-Membros.
 3. Um Estado-Membro que tenha disposições nacionais mais restritivas referidas no n.º 1 não pode proibir ou impedir a colocação no mercado, no seu território, de cães e gatos detidos noutro Estado-Membro com o fundamento de que os cães e gatos em causa não estiveram detidos em conformidade com as suas disposições nacionais mais rigorosas.</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="H31" s="6" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr"/>
-      <c r="K27" s="8" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr"/>
+      <c r="K31" s="8" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="L27" s="9" t="inlineStr">
+      <c r="L31" s="9" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="M27" s="10" t="inlineStr">
+      <c r="M31" s="10" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="N27" s="11" t="inlineStr"/>
-      <c r="O27" s="11" t="inlineStr">
+      <c r="N31" s="11" t="inlineStr"/>
+      <c r="O31" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P27" s="11" t="inlineStr"/>
+      <c r="P31" s="11" t="inlineStr"/>
     </row>
-    <row r="28" ht="120" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="32" ht="120" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Relatórios e Avaliação</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Art.º 31.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>1.	On the basis of the reports received in accordance with Article 24 and any additional relevant information, the Commission shall publish, by ... [7 years from the date of entry into force of this Regulation] and thereafter at three-yearly intervals, a monitoring report on the welfare of dogs and cats placed on the market in the Union.
 2.	By … [14 years from the date of entry into force of this Regulation, the Commission shall carry out an evaluation of this Regulation and present a report on the main findings to the European Parliament, the Council, the European Economic and Social Committee, and the Committee of the Regions. In that evaluation and report the Commission shall assess, in particular:
@@ -3950,7 +4238,7 @@
 3.	For the purposes of the reporting referred to in paragraph 2, Member States shall provide the Commission with the information necessary for the preparation of its report.</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>1. Com base nos relatórios recebidos em conformidade com o artigo 24.º e em informações adicionais pertinentes, a Comissão publica, até [7 anos após a data de entrada em vigor do presente regulamento] e, posteriormente, de três em três anos, um relatório de monitorização sobre o bem-estar dos cães e gatos colocados no mercado da União.
 2. Até [14 anos a contar da data de entrada em vigor do presente regulamento], a Comissão procede a uma avaliação do presente regulamento e apresenta um relatório sobre as principais conclusões ao Parlamento Europeu, ao Conselho, ao Comité Económico e Social Europeu e ao Comité das Regiões. Em particular, a Comissão avalia:
@@ -3959,127 +4247,127 @@
 3. Para efeitos dos relatórios referidos no n.º 2, os Estados-Membros devem fornecer à Comissão as informações necessárias para a elaboração dos mesmos.</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Sem equivalência</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>Sem equivalência</t>
         </is>
       </c>
-      <c r="H28" s="6" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="H32" s="6" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>Sem equivalência</t>
         </is>
       </c>
-      <c r="J28" s="7" t="inlineStr"/>
-      <c r="K28" s="8" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr"/>
+      <c r="K32" s="8" t="inlineStr">
         <is>
           <t>Sem equivalência</t>
         </is>
       </c>
-      <c r="L28" s="9" t="inlineStr">
+      <c r="L32" s="9" t="inlineStr">
         <is>
           <t>Sem equivalência</t>
         </is>
       </c>
-      <c r="M28" s="10" t="inlineStr">
+      <c r="M32" s="10" t="inlineStr">
         <is>
           <t>Sem equivalência</t>
         </is>
       </c>
-      <c r="N28" s="11" t="inlineStr">
+      <c r="N32" s="11" t="inlineStr">
         <is>
           <t>Artigo sobre obrigações de relatório e avaliação pela Comissão Europeia. Impõe que Estados-Membros contribuam para o relatório a produzir 14 anos após a entrada em vigor.</t>
         </is>
       </c>
-      <c r="O28" s="11" t="inlineStr">
+      <c r="O32" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P28" s="11" t="inlineStr"/>
+      <c r="P32" s="11" t="inlineStr"/>
     </row>
-    <row r="29" ht="120" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="33" ht="120" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Sanções</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Art.º 32.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Member States shall lay down the rules on penalties applicable to infringements of this Regulation, including those resulting from the abandonment by operators of dogs and cats, and shall take all measures necessary to ensure that they are implemented. The penalties provided for shall be effective, proportionate and dissuasive.
 Member States shall notify the Commission of those rules and of those measures and shall notify it, without delay, of any subsequent amendments affecting them.</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>Os Estados-Membros estabelecem as regras relativas às sanções aplicáveis em caso de violação do disposto no presente regulamento, incluindo as resultantes do abandono de cães e gatos por parte de operadores, e tomam todas as medidas necessárias para garantir a sua aplicação. As sanções previstas devem ser efetivas, proporcionadas e dissuasivas.
 Os Estados-Membros notificam a Comissão dessas regras e dessas medidas e também, sem demora, de qualquer alteração ulterior das mesmas.</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="H29" s="6" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="H33" s="6" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr"/>
-      <c r="K29" s="8" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr"/>
+      <c r="K33" s="8" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="L29" s="9" t="inlineStr">
+      <c r="L33" s="9" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="M29" s="10" t="inlineStr">
+      <c r="M33" s="10" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="N29" s="11" t="inlineStr"/>
-      <c r="O29" s="11" t="inlineStr">
+      <c r="N33" s="11" t="inlineStr"/>
+      <c r="O33" s="11" t="inlineStr">
         <is>
           <t>Responsabilidade dos Estados-Membros em estabelecer sanções e notificar a Comissão destas, e de qualquer alteração ulterior das mesmas.</t>
         </is>
       </c>
-      <c r="P29" s="11" t="inlineStr"/>
+      <c r="P33" s="11" t="inlineStr"/>
     </row>
-    <row r="30" ht="120" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="34" ht="120" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Entrada em Vigor e Aplicação</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Art.º 33.º do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>This Regulation shall enter into force on the twentieth day following that of its publication in the Official Journal of the European Union.
 It shall apply from ... [two years from the date of entry into force of this Regulation]. However,
@@ -4093,7 +4381,7 @@
 This Regulation shall be binding in its entirety and directly applicable in all Member States.</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>O presente regulamento entra em vigor no vigésimo dia seguinte ao da sua publicação no Jornal Oficial da União Europeia.
 É aplicável a partir de … [dois anos após a data de entrada em vigor do presente Regulamento]. Todavia:
@@ -4107,63 +4395,63 @@
 O presente regulamento é obrigatório em todos os seus elementos e diretamente aplicável em todos os Estados-Membros.</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr"/>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="H34" s="6" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="J30" s="7" t="inlineStr"/>
-      <c r="K30" s="8" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr"/>
+      <c r="K34" s="8" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="L30" s="9" t="inlineStr">
+      <c r="L34" s="9" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="M30" s="10" t="inlineStr">
+      <c r="M34" s="10" t="inlineStr">
         <is>
           <t>Não se aplica</t>
         </is>
       </c>
-      <c r="N30" s="11" t="inlineStr">
+      <c r="N34" s="11" t="inlineStr">
         <is>
           <t>Entrada em vigor, períodos de aplicação escalonados e obrigatoriedade do Regulamento.</t>
         </is>
       </c>
-      <c r="O30" s="11" t="inlineStr">
+      <c r="O34" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P30" s="11" t="inlineStr"/>
+      <c r="P34" s="11" t="inlineStr"/>
     </row>
-    <row r="31" ht="120" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="35" ht="120" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Requisitos Técnicos — Alimentação e Abeberamento</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Annex I, Ponto 1 do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>Requirements applicable to establishments
 1. Feeding and watering
@@ -4174,7 +4462,7 @@
 4.4 Weaning shall be performed by the gradual introduction of solid feed over a period that is not shorter than seven days and shall not be completed before the age of six weeks for puppies and kittens alike.</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>1. Alimentação e abeberamento
 1.1 Os cães e gatos devem ser alimentados, pelo menos, duas vezes por dia. Os cachorros e gatinhos devem ser alimentados com maior frequência.
@@ -4184,12 +4472,12 @@
 4.4 O desmame deve ser efetuado através da introdução gradual de alimentos sólidos durante um período não inferior a sete dias e não deve estar concluído antes das seis semanas de idade, tanto para os cachorros como para os gatinhos.</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Art.º 33.º, Arts. 38-40 do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Artigo 33.º - Alimentação
 1. Deve existir um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades fisiológicas, nutricionais e metabólicas dos cães e gatos, consoante a idade, raça, categoria, nível de atividade e estado de saúde.
@@ -4202,12 +4490,12 @@
 5 - As crias não podem ser separadas da progenitora antes da décima semana de idade, no caso dos cães, e antes da décima segunda semana de idade, no caso dos gatos, salvaguardado um período de desmame gradual.</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>Art.º 18.º (n.º 1), Art.º 46.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>Artigo 46.º - Alimentação e abeberamento
 1. A alimentação dos animais de companhia, nos locais de criação, manutenção e venda bem como nos centros de recolha e instalações de hospedagem, deve obedecer a um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies e dos indivíduos, de acordo com a fase de evolução fisiológica em que se encontram, nomeadamente idade, sexo, fêmeas prenhes ou em fase de lactação.
@@ -4219,12 +4507,12 @@
 7. É proibido alimentar animais com restos de comida, produtos de pastelaria e desperdícios da indústria alimentar e de restauração.</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>Art.º 12.º, Art.º 49.º do DL n.º 276-2001, de 17 de outubro;</t>
         </is>
       </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>Artigo 12.º — Alimentação e abeberamento
 1 - Deve existir um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies e dos indivíduos de acordo com a fase de evolução fisiológica em que se encontram, nomeadamente idade, sexo, fêmeas prenhes ou em fase de lactação.
@@ -4237,42 +4525,42 @@
 Deve ser mantida comida suficiente e de boa qualidade e água potável, a administrar de acordo com a prescrição do médico veterinário.</t>
         </is>
       </c>
-      <c r="K31" s="8" t="inlineStr"/>
-      <c r="L31" s="9" t="inlineStr">
+      <c r="K35" s="8" t="inlineStr"/>
+      <c r="L35" s="9" t="inlineStr">
         <is>
           <t>Sem detalhes de armazenamento ou alojamento</t>
         </is>
       </c>
-      <c r="M31" s="10" t="inlineStr">
+      <c r="M35" s="10" t="inlineStr">
         <is>
           <t>Frequências, padrões de higiene, água potável, refrigeração, alimentos saudáveis e adequados.</t>
         </is>
       </c>
-      <c r="N31" s="11" t="inlineStr">
+      <c r="N35" s="11" t="inlineStr">
         <is>
           <t>FALTAM especificidades do Regulamento: frequência mínima (2x/dia para cães e gatos), colostro (mínimo 2 dias), leite materno, desmame gradual (mínimo 7 dias, não antes 6 semanas), disposições específicas para filhotes.
 Cão de guarda de gado = «Cão de proteção de gado contra ataques de lobo» na nossa legislação, conforme al. c) do n.º 2 do art.º 2.º do Decreto-Lei n.º 54/2016, de 25 de Agosto (desenvolvimento dos princípios da proteção e conservação do lobo-ibérico).</t>
         </is>
       </c>
-      <c r="O31" s="11" t="inlineStr">
+      <c r="O35" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P31" s="11" t="inlineStr"/>
+      <c r="P35" s="11" t="inlineStr"/>
     </row>
-    <row r="32" ht="120" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="36" ht="120" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Requisitos Técnicos — Alojamento (Housing)</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>ANEXO I, Ponto 2 do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>2.Housing
 2.1 Temperature
@@ -4301,7 +4589,7 @@
 ** A superfície com enriquecimento para gatos não é incluída na área mínima do solo.</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>2. Alojamento
 2.1 Temperatura
@@ -4330,59 +4618,59 @@
 ** A superfície com enriquecimento para gatos não é incluída na área mínima do solo.</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>Sem equivalência específica</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>Verificar Anexo</t>
         </is>
       </c>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="H36" s="6" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>Anexo ao DL n.º 260/2012</t>
         </is>
       </c>
-      <c r="J32" s="7" t="inlineStr"/>
-      <c r="K32" s="8" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr"/>
+      <c r="K36" s="8" t="inlineStr">
         <is>
           <t>FALTAM especificidades do Regulamento: temperatura exata (22-28°C para parto de cães; 18-27°C para parto de gatos), iluminação mínima (7 horas luz, 8 horas sem luz, espectro 80 Hz), espaço mínimo quantificado, áreas de parto separadas.</t>
         </is>
       </c>
-      <c r="L32" s="9" t="inlineStr">
+      <c r="L36" s="9" t="inlineStr">
         <is>
           <t>Faltam: temperatura específica, iluminação quantificada (7h luz/80Hz, 8h sem luz), espaço mínimo por tamanho/idade.</t>
         </is>
       </c>
-      <c r="M32" s="10" t="inlineStr"/>
-      <c r="N32" s="11" t="inlineStr">
+      <c r="M36" s="10" t="inlineStr"/>
+      <c r="N36" s="11" t="inlineStr">
         <is>
           <t>ANNEX I, Ponto 2 do Regulamento especifica requisitos técnicos detalhados: temperatura por fase (parto de cães 22-28°C; gatos 18-27°C), iluminação (7h luz + 80Hz, 8h sem luz), espaço mínimo quantificado, áreas de parto separadas.</t>
         </is>
       </c>
-      <c r="O32" s="11" t="inlineStr">
+      <c r="O36" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P32" s="11" t="inlineStr"/>
+      <c r="P36" s="11" t="inlineStr"/>
     </row>
-    <row r="33" ht="120" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="37" ht="120" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Requisitos Técnicos — Reprodução (Health)</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>ANEXO I, Ponto 3 do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>3. Health
 1.1 Queens shall only be bred if their age is at least 10 months.
@@ -4394,7 +4682,7 @@
 The operator shall keep the written confirmation referred to in point 3.4.b for a period of at least 3 years.</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>3. Saúde
 1.1 As gatas só devem ser utilizadas para reprodução se tiverem, pelo menos, 10 meses de idade.
@@ -4406,59 +4694,59 @@
 O operador deve conservar a confirmação escrita referida no ponto 3.4.b por um período de, pelo menos, 3 anos.</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>Ver análise do art.º 8º do @regulamento</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr"/>
+      <c r="G37" s="6" t="inlineStr">
         <is>
           <t>Ver análise do art.º 8º do @regulamento</t>
         </is>
       </c>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="H37" s="6" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>Ver análise do art.º 8º do @regulamento</t>
         </is>
       </c>
-      <c r="J33" s="7" t="inlineStr"/>
-      <c r="K33" s="8" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr"/>
+      <c r="K37" s="8" t="inlineStr">
         <is>
           <t>Ver análise do art.º 8º do @regulamento</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr">
+      <c r="L37" s="9" t="inlineStr">
         <is>
           <t>Ver análise do art.º 8º do @regulamento</t>
         </is>
       </c>
-      <c r="M33" s="10" t="inlineStr">
+      <c r="M37" s="10" t="inlineStr">
         <is>
           <t>Ver análise do art.º 8º do @regulamento</t>
         </is>
       </c>
-      <c r="N33" s="11" t="inlineStr"/>
-      <c r="O33" s="11" t="inlineStr">
+      <c r="N37" s="11" t="inlineStr"/>
+      <c r="O37" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P33" s="11" t="inlineStr"/>
+      <c r="P37" s="11" t="inlineStr"/>
     </row>
-    <row r="34" ht="120" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="38" ht="120" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Requisitos Técnicos — Bem-Estar Comportamental (Behavioural Needs)</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>ANEXO I, Ponto 4 do Regulamento 2023/0447  |  EN</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>3. Behavioural needs
 1.1 Socialisation
@@ -4472,7 +4760,7 @@
 By way of derogation, earlier separation shall be possible due to medical reasons based on written advice of a veterinarian. The operator shall keep a record of the advice until the last puppy or kitten of the litter concerned is placed on the market.</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>Bem-Estar Comportamental
 1.1 Socialização
@@ -4486,12 +4774,12 @@
 Por derrogação, separação anterior é possível por razões médicas com base em parecer escrito de um veterinário. O operador deve conservar o parecer até o último cachorro ou gatinho da ninhada em questão ser colocado no mercado.</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>Arts. 10.º, 12.º, 47.º, 52.º, 68.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>SUBSECÇÃO 4.1 (SOCIALIZAÇÃO):
 Artigo 52.º — Maneio
@@ -4504,12 +4792,12 @@
 5 — As crias não podem ser separadas da progenitora antes da décima semana de idade, no caso dos cães, e antes da décima segunda semana de idade, no caso dos gatos, salvaguardado um período de desmame gradual.</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>Arts. 13.º, 18.º, e outros do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H34" s="6" t="inlineStr">
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>SUBSECÇÃO 4.1 (SOCIALIZAÇÃO):
 [Código do Animal não contém disposições específicas sobre socialização]
@@ -4525,12 +4813,12 @@
 2 — [...] devendo os animais: [...] Ter idade superior a oito semanas.</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>Art.º 8.º do DL n.º 276-2001</t>
         </is>
       </c>
-      <c r="J34" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>SUBSECÇÃO 4.1 (SOCIALIZAÇÃO):
 [DL 276/2001 não contém disposições específicas sobre socialização]
@@ -4541,28 +4829,28 @@
 [DL 276/2001 não contém disposições específicas sobre idade mínima de separação de mãe ou exposição em locais de venda]</t>
         </is>
       </c>
-      <c r="K34" s="8" t="inlineStr">
+      <c r="K38" s="8" t="inlineStr">
         <is>
           <t>4.1 SOCIALIZAÇÃO: DIVERGÊNCIA TOTAL — DL 276/2001 omisso completamente
 4.2 ENRIQUECIMENTO: PARCIAL — cobre genérico (substrato, ninhos, buracos) mas omite 'postes de arranhadura' (crítico para gatos)
 4.3 SEPARAÇÃO: DIVERGÊNCIA TOTAL — DL 276/2001 omisso; Regulamento exige mínimo 8-12 semanas, DL não especifica</t>
         </is>
       </c>
-      <c r="L34" s="9" t="inlineStr">
+      <c r="L38" s="9" t="inlineStr">
         <is>
           <t>4.1 SOCIALIZAÇÃO: DIVERGÊNCIA SIGNIFICATIVA — Código menciona contato social mas sem detalhe (idade, frequência, documentação)
 4.2 ENRIQUECIMENTO: PARCIAL — menciona prateleiras/poleiros mas omite 'postes de arranhadura'
 4.3 SEPARAÇÃO: DIVERGÊNCIA SIGNIFICATIVA — Código exige 8 semanas (Arts. 23.º, 82.º) para EXPOSIÇÃO em venda; Regulamento exige 8 semanas (puppies, kittens abrigos) e 12 semanas (kittens breeding) para SEPARAÇÃO de mãe — conceitos distintos</t>
         </is>
       </c>
-      <c r="M34" s="10" t="inlineStr">
+      <c r="M38" s="10" t="inlineStr">
         <is>
           <t>4.1 SOCIALIZAÇÃO: CONVERGÊNCIA PARCIAL — exige 'plano de socialização' (Art. 52.7) mas sem especificação de: idade 3 semanas, frequência diária, tipos de contato, separação de animais agressivos
 4.2 ENRIQUECIMENTO: menciona enriquecimento 'complexo', inclui 'brinquedos', mas omite 'postes de arranhadura'
 4.3 SEPARAÇÃO: @RGBEAC (Art. 70.5) exige 10 semanas (cães) / 12 semanas (gatos) com desmame gradual (mais restritivo que Regulamento 8-12 semanas)</t>
         </is>
       </c>
-      <c r="N34" s="11" t="inlineStr">
+      <c r="N38" s="11" t="inlineStr">
         <is>
           <t>ANNEX I, Ponto 4 (Behavioural Needs) tem três subsecções: (i) 4.1 Socialização — contato social diário desde 3 semanas (NOVO); (ii) 4.2 Enriquecimento — postes de arranhadura, abrigos, prateleiras para gatos (PARCIAL na legislação); (iii) 4.3 Separação — 8 semanas (puppies, kittens abrigos), 12 semanas (kittens breeding).
 DL 276/2001 é omisso em 4.1 e 4.3, parcial em 4.2.
@@ -4570,25 +4858,25 @@
 @RGBEAC é mais restritivo (10-12 semanas separação) e cobre 4.1 (plano) e 4.2 (enriquecimento) com gaps específicos.</t>
         </is>
       </c>
-      <c r="O34" s="11" t="inlineStr">
+      <c r="O38" s="11" t="inlineStr">
         <is>
           <t>Sim - Harmonização fundamental (4.1) + clarificação (4.2 postes arranhadura) + ajuste (4.3 separação vs. exposição)</t>
         </is>
       </c>
-      <c r="P34" s="11" t="inlineStr"/>
+      <c r="P38" s="11" t="inlineStr"/>
     </row>
-    <row r="35" ht="120" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="39" ht="120" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Identificação e Registo de Cães e Gatos - Requisitos Técnicos</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>ANEXO II do Regulamento 2023/0447 (conforme Articles 20 e 26)  |  EN</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>Identification and registration of dogs and cats
 Transponders used to individually identify dogs and cats as required in Article 20 and Article 26 shall meet the following requirements:
@@ -4598,7 +4886,7 @@
 (d) compliance with ISO standards 11784 and 11785 shall be evaluated in accordance with ISO standard 24631-1.</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>Identificação e registo de cães e gatos
 Os transponders utilizados para identificar individualmente cães e gatos, tal como exigido nos artigos 20.º e 26.º, devem cumprir os seguintes requisitos:
@@ -4608,12 +4896,12 @@
 (d) a conformidade com as normas ISO 11784 e 11785 deve ser avaliada de acordo com a norma ISO 24631-1</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>Arts. 18.º e 19.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>Artigo 18.º- Métodos de marcação
 1 – Os métodos de marcação devem atender às melhoras práticas internacionais vigentes e salvaguardar o bem-estar animal.
@@ -4629,12 +4917,12 @@
 3 - Para a marcação só pode ser utilizado um transponder ou outro dispositivo de identificação individual que tenha sido previamente registado no SIAC pela empresa comercializadora, e atribuído ao médico veterinário ou a uma entidade autorizada a identificar animais de companhia.</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>Arts. 53.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H35" s="6" t="inlineStr">
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>Artigo 53.º — Identificação e registo na base de dados
 (…)
@@ -4646,35 +4934,35 @@
 2 - A DGAV detém, define e coordena o acesso à base de dados.</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>DL n.º 82/2019, de 27 de junho (LEGISLAÇÃO VIGENTE) + DL n.º 276-2001</t>
         </is>
       </c>
-      <c r="J35" s="7" t="inlineStr"/>
-      <c r="K35" s="8" t="inlineStr"/>
-      <c r="L35" s="9" t="inlineStr"/>
-      <c r="M35" s="10" t="inlineStr"/>
-      <c r="N35" s="11" t="inlineStr"/>
-      <c r="O35" s="11" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr"/>
+      <c r="K39" s="8" t="inlineStr"/>
+      <c r="L39" s="9" t="inlineStr"/>
+      <c r="M39" s="10" t="inlineStr"/>
+      <c r="N39" s="11" t="inlineStr"/>
+      <c r="O39" s="11" t="inlineStr">
         <is>
           <t>ANNEX II (Identification and Registration) estabelece quatro requisitos técnicos de transponders: (i) número individual não-repetível; (ii) ISO 3166 (país); (iii) ISO 11784/11785 (radiofrequência); (iv) ISO 24631-1 (avaliação).</t>
         </is>
       </c>
-      <c r="P35" s="11" t="inlineStr"/>
+      <c r="P39" s="11" t="inlineStr"/>
     </row>
-    <row r="36" ht="120" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="40" ht="120" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Recolha de Dados sobre Bem-Estar Animal — Relatório Trienal à Comissão UE</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>ANEXO III do Regulamento 2023/0447 (conforme Article 24)  |  EN</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>1. The number of dogs and cats registered per year, as referred to in Article 20 and Article 26(3).
 2. The number of breeding establishments, selling establishments, shelters and foster homes registered per year in accordance with Article 9.
@@ -4682,7 +4970,7 @@
 4. The number of breeding establishments approval of which has been suspended or withdrawn per year.</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>1. O número de cães e gatos registados por ano, conforme referido no artigo 20.º e no artigo 26.º, n.º 3.
 2.  O número de estabelecimentos de criação, estabelecimentos de venda, abrigos e famílias de acolhimento registados por ano em conformidade com o artigo 9.º.
@@ -4690,12 +4978,12 @@
 4. O número de estabelecimentos de criação cuja aprovação tenha sido suspensa ou retirada por ano.</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>RGBEAC (Regime Geral do Bem-Estar dos Animais de Companhia, proposta jun. 2025) — Arts. 20.º, 46.º</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>Artigo 20.º — Sistema de Informação de Animais de Companhia (SIAC)
 1. O SIAC reúne informação relativa à: a) Rastreabilidade de dispositivos de identificação; b) Identificação dos animais de companhia; c) Sua titularidade ou detenção; d) Informação de saúde pública, saúde animal e bem-estar animal.
@@ -4707,12 +4995,12 @@
 2. A DGVA consolida a informação a nível nacional sobre bem-estar animal em cada ano, incluindo o acompanhamento da política internacional do Estado Português na área do bem-estar dos animais de companhia, a prestação dos apoios públicos, a atividade do SIAC, os resultados dos planos de controlo, os processos contraordenacionais instaurados e coimas e sanções acessórias aplicadas, a atividade dos centros de bem-estar animal e dos alojamentos com fins de promoção de bem-estar animal, bem como os programas e ações de interesse nacional em matéria do bem-estar dos animais de companhia, incluindo ações informativas, formativas, educativas e estudos desenvolvidos, para efeitos de elaboração do Relatório Anual sobre a situação do Bem-Estar Animal previsto na alínea i) do n.º 1 do artigo 3.º do Decreto-Regulamentar n.º 3/2021, de 25 de junho;</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>Código do Animal (DL 214/2013) — Arts. 55.º, 141.º-145.º</t>
         </is>
       </c>
-      <c r="H36" s="6" t="inlineStr">
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>Artigo 55.º — Base de dados
 1 - Toda informação de registo coligida numa aplicação informática nacional.
@@ -4720,12 +5008,12 @@
 3 - Só entidades autorizadas pela DGAV têm acesso.</t>
         </is>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>Decreto-Regulamentar n.º 3/2021 e Lei 27/2016</t>
         </is>
       </c>
-      <c r="J36" s="7" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>Decreto-Regulamentar 3/2021 (Art. 3.º) requer Relatório Anual sobre situação do Bem-Estar Animal.
 nº 9 e 10, artigo 3.º da Lei nº 27/2016, de 23 de agosto
@@ -4733,33 +5021,33 @@
 10 - Com base nos relatórios referidos no número anterior, a Direção-Geral de Alimentação e Veterinária elabora e publicita um relatório anual sobre a situação ao nível nacional, até ao fim do primeiro trimestre de cada ano civil.</t>
         </is>
       </c>
-      <c r="K36" s="8" t="inlineStr">
+      <c r="K40" s="8" t="inlineStr">
         <is>
           <t>Sem equivalência</t>
         </is>
       </c>
-      <c r="L36" s="9" t="inlineStr">
+      <c r="L40" s="9" t="inlineStr">
         <is>
           <t>Sem equivalência</t>
         </is>
       </c>
-      <c r="M36" s="10" t="inlineStr">
+      <c r="M40" s="10" t="inlineStr">
         <is>
           <t>Sem equivalência</t>
         </is>
       </c>
-      <c r="N36" s="11" t="inlineStr">
+      <c r="N40" s="11" t="inlineStr">
         <is>
           <t>ANNEX III define dados obrigatórios para relatório trienal à Comissão UE (Art. 20 do Regulamento). SIAC português fornece dados para ponto 1 (cães/gatos registados) — sistema operacional desde 2019. Pontos 2 e 2a requerem regulação complementar: aprovação formal de criadores (vs. apenas registo) + procedimentos de suspensão/revogação. Ponto 1a (estabelecimentos) — codificação explícita de "famílias de acolhimento" como categoria administrativa.
 Integrar dados coletados em relatório trienal da Comissão UE (conforme Art. 20 do Regulamento).</t>
         </is>
       </c>
-      <c r="O36" s="11" t="inlineStr">
+      <c r="O40" s="11" t="inlineStr">
         <is>
           <t>Sim — Estabelecer sistema de aprovação, suspensão e revogação de estabelecimentos de criação + codificar famílias de acolhimento</t>
         </is>
       </c>
-      <c r="P36" s="11" t="inlineStr"/>
+      <c r="P40" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -676,7 +676,7 @@
         <is>
           <t>This Regulation lays down:
 (a) minimum requirements for the welfare of dogs and cats bred or kept in establishments or placed on the market of the Union; and
-(b) rules on the traceability of dogs and cats ▌.</t>
+(b) rules on the traceability of dogs and cats.</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -744,9 +744,8 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>1. This Regulation applies to the breeding, keeping, tracing, placing on the market and entry into the Union of dogs and cats ▌.
-2. This Regulation does not apply to the breeding, keeping or placing on the market or entry into the Union of dogs or cats intended or used for scientific purposes or for clinical trials required for the marketing authorisation of veterinary medicinal products.
-▌</t>
+          <t>1. This Regulation applies to the breeding, keeping, tracing, placing on the market and entry into the Union of dogs and cats.
+2. This Regulation does not apply to the breeding, keeping or placing on the market or entry into the Union of dogs or cats intended or used for scientific purposes or for clinical trials required for the marketing authorisation of veterinary medicinal products.</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -887,11 +886,44 @@
         <is>
           <t>For the purposes of this Regulation, the following definitions apply:
 1. 'dog' means an animal of the species Canis lupus familiaris;
-▌
 2. 'cat' means an animal of the species Felis silvestris catus;
 3. 'welfare of dogs and cats' means the physical and mental state of a dog or a cat, which receives appropriate nutrition, is kept in an appropriate environment, is in good health, displays appropriate behaviour, and has an overall a positive mental experience of life;
 4. 'hybrid' means any offspring of the first to the fourth generation following a cross-breeding event between a wild species and the domestic species of dog or cat;
-5. 'breeding' means the activity of keeping dogs or cats in breeding establishments for the purposes of reproduction;</t>
+5. 'breeding' means the activity of keeping dogs or cats in breeding establishments for the purposes of reproduction;
+6. 'keeping' means any activity during which dogs or cats are held, accommodated or handled, whether in an establishment or otherwise;
+7. 'placing on the market' means the sale, offering for sale, distribution or any other form of transfer, whether for profit or free of charge, of dogs or cats;
+8. 'advertising' means any form of communication to the public, or to part of the public, which has the direct or indirect effect of promoting the placing on the market of dogs or cats;
+9. 'online platform' means an online platform within the meaning of Article 3(i) of Regulation (EU) 2022/2065;
+10. 'female dog' means a female dog from its first mating or insemination until the weaning of its last litter;
+11. 'female cat' means a female cat from its first mating or insemination until the weaning of its last litter;
+12. 'livestock guardian dog' means a dog held or trained mainly to protect livestock from predators in an agricultural context;
+13. 'herding dog' means a dog held or trained mainly to guide, move or manage livestock in an agricultural context;
+14. 'establishment' means a breeding establishment, a selling establishment, a shelter or a foster home;
+15. 'breeding establishment' means any facility or structure, including private homes, where dogs or cats are kept for the purposes of reproduction;
+16. 'farmer' means a farmer within the meaning of Article 3, point 1, of Regulation (EU) 2021/2115;
+17. 'selling establishment' means any facility or structure where dogs or cats are held for sale but have not been born and bred there;
+18. 'shelter' means any facility or structure, including private homes, where dogs or cats are held not for commercial purposes;
+19. 'foster home' means a private home where dogs or cats are held on behalf of an operator responsible for dogs or cats;
+20. 'operator' means any natural or legal person placing dogs or cats on the market and responsible for an establishment;
+21. 'competent authorities' means the competent authorities within the meaning of Article 3, point 3, of Regulation (EU) 2017/625;
+22. 'breeding strategy' means a set of systematic actions, including registration, selection, breeding and interbreeding of dogs or cats;
+23. 'euthanasia' means the act of inducing death by a method that causes rapid and irreversible loss of consciousness and death;
+24. 'mutilation' means an intervention, including a surgical intervention, carried out for reasons other than therapeutic or prophylactic purposes;
+25. 'neutering' means the process by which dogs or cats are prevented from reproducing by means of surgery and/or a pharmaceutical substance;
+26. 'suffering' means an unpleasant and unwanted physical or mental state resulting from the exposure of a dog or cat to aversive stimuli;
+27. 'accommodation' means buildings or delimited outdoor space in establishments where dogs or cats are held on a temporary or permanent basis;
+28. 'kennel' means a physical structure containing one or more compartments for housing dogs;
+29. 'cattery' means a physical structure containing one or more compartments for housing cats;
+30. 'animal carer' means a person who looks after dogs or cats bred or held in an establishment, including volunteers and interns;
+31. 'enrichment' means any materials or structures present in the environment of a dog or cat with properties that encourage positive activity;
+32. 'tethering' means the act of fastening a dog or cat to a fixed point or object to confine it to a desired area;
+33. 'container' means any box, cage, receptacle or other mobile structure used to confine dogs or cats;
+34. 'responsible ownership' means the set of behaviours of an owner or prospective owner of a dog or cat complying with the requirements;
+35. 'pet owner' means a natural or legal person that is the owner of a dog or cat as a pet;
+36. 'pet' means a dog or cat held for personal enjoyment or to provide companionship to humans;
+37. 'Rapid Alert System' (iRASFF) means the electronic system applying the rapid alert system described in Article 50 of Regulation (EU) 2017/625;
+38. 'AAC Network' means the network set up by the Commission and the liaison bodies designated by Member States in accordance with Article 36 of Regulation (EU) 2017/625;
+39. 'non-commercial movement' means non-commercial movement as defined in Article 4, point 14, of Regulation (EU) 2016/429.</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -900,8 +932,42 @@
 1. «Cão», um animal da espécie Canis lupus familiaris;
 2. «Gato», um animal da espécie Felis silvestris catus;
 3. «Bem-estar dos cães e gatos», o estado físico e mental de um cão ou de um gato que recebe nutrição adequada, é mantido num ambiente apropriado, está em bom estado de saúde, exibe comportamento apropriado e tem uma experiência mental geral positiva da vida;
-4. «Híbrido», qualquer descendência da primeira à quarta geração após o cruzamento entre uma espécie selvagem e a espécie doméstica de cão ou gato;
-5. «Criação», a atividade de detenção de cães ou gatos em estabelecimentos de criação para efeitos de reprodução;</t>
+4. «Híbrido», qualquer descendência da primeira à quarta geração após o cruzamento entre uma espécie selvagem e um cão ou gato doméstico;
+5. «Criação», a atividade de detenção de cães ou gatos em estabelecimentos de criação para efeitos de reprodução;
+6. «Detenção», qualquer atividade durante a qual cães e gatos sejam mantidos, alojados ou manuseados, quer num estabelecimento quer noutro local;
+7. «Colocação no mercado», a venda, oferta para fins de venda, distribuição ou qualquer outra forma de transferência de propriedade ou responsabilidade, quer mediante compensação financeira quer a título gratuito, de cães ou gatos;
+8. «Publicidade», qualquer forma de comunicação com o público, ou com uma parte deste, que tenha o efeito direto ou indireto de promover a colocação de cães ou gatos no mercado;
+9. «Plataforma em linha», uma plataforma em linha na aceção do artigo 3.º, alínea i), do Regulamento (UE) 2022/2065;
+10. «Cadela», a fêmea do cão, desde o primeiro acasalamento ou inseminação até ao desmame da sua última ninhada;
+11. «Gata», a fêmea do gato, desde o primeiro acasalamento ou inseminação até ao desmame da sua última ninhada;
+12. «Cão de guarda de gado», um cão detido ou treinado principalmente para proteger o gado de predadores em contextos agrícolas;
+13. «Cão de pastoreio», um cão detido ou treinado principalmente para guiar, movimentar ou gerir gado em contextos agrícolas;
+14. «Estabelecimento», um estabelecimento de criação, um estabelecimento de venda, um abrigo ou uma casa de acolhimento;
+15. «Estabelecimento de criação», qualquer instalação ou estrutura, incluindo casas particulares, onde são mantidos cães ou gatos para efeitos de reprodução;
+16. «Agricultor», um agricultor na aceção do artigo 3.º, ponto 1, do Regulamento (UE) 2021/2115;
+17. «Estabelecimento de venda», qualquer instalação ou estrutura onde cães ou gatos são detidos para venda sem aí terem nascido nem sido criados;
+18. «Abrigo», qualquer instalação ou estrutura, incluindo as casas particulares, onde são detidos cães ou gatos não para fins comerciais;
+19. «Casa de acolhimento», uma casa particular onde cães ou gatos são detidos em nome de um operador responsável por cães ou gatos;
+20. «Operador», qualquer pessoa singular ou coletiva que coloca cães ou gatos no mercado e é responsável por um estabelecimento;
+21. «Autoridades competentes», as autoridades competentes na aceção do artigo 3.º, ponto 3, do Regulamento (UE) 2017/625;
+22. «Estratégia de reprodução», um conjunto de ações sistemáticas, incluindo o registo, a seleção, a reprodução e o cruzamento de cães ou gatos;
+23. «Eutanásia», o ato de induzir a morte através de um método que provoca uma perda de consciência rápida e irreversível e morte;
+24. «Mutilação», uma intervenção, incluindo uma intervenção cirúrgica, realizada por razões que não sejam terapêuticas ou profiláticas;
+25. «Esterilização», o processo através do qual cães ou gatos são impedidos de se reproduzirem com recurso a cirurgia e/ou a uma substância farmacêutica;
+26. «Sofrimento», um estado físico ou mental desagradável e indesejado, resultante da exposição de um cão ou gato a estímulos aversivos;
+27. «Alojamento», edifícios ou espaço exterior delimitado em estabelecimentos onde são detidos cães ou gatos de forma temporária ou permanente;
+28. «Canil», uma estrutura física que contém um ou mais compartimentos para alojar cães;
+29. «Gatil», uma estrutura física que contém um ou mais compartimentos para alojar gatos;
+30. «Cuidador de animais», uma pessoa que cuida dos cães ou gatos criados ou detidos num estabelecimento, incluindo voluntários e estagiários;
+31. «Enriquecimentos», quaisquer materiais ou estruturas presentes no ambiente de um cão ou de um gato, com propriedades que promovem atividade positiva;
+32. «Acorrentamento», ato de prender um cão ou gato a um ponto de fixação ou a um objeto para o manter numa zona desejada;
+33. «Contentor», qualquer caixa, jaula, recetáculo ou outra estrutura móvel utilizada para confinar cães ou gatos;
+34. «Propriedade responsável», conjunto de comportamentos de um proprietário ou futuro proprietário de um cão ou gato em conformidade com os requisitos;
+35. «Proprietário de um animal de companhia», uma pessoa singular ou coletiva que é proprietária de um cão ou gato como animal de companhia;
+36. «Animal de companhia», um cão ou gato detido para entretenimento pessoal ou para fazer companhia a humanos;
+37. «Sistema de Alerta Rápido» (iRASFF), o sistema eletrónico que aplica o sistema de alerta rápido descrito no artigo 50.º do Regulamento (UE) 2017/625;
+38. «Rede AAC», a rede constituída pela Comissão e pelos organismos de ligação designados pelos Estados-Membros em conformidade com o artigo 36.º do Regulamento (UE) 2017/625;
+39. «Circulação sem caráter comercial», a circulação sem caráter comercial definida no artigo 4.º, ponto 14, do Regulamento (UE) 2016/429.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -939,7 +1005,7 @@
       </c>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>Define conceitos-chave usados ao longo do Regulamento (cão, gato, bem-estar, criação, etc.).</t>
+          <t>Define os 39 conceitos-chave usados ao longo do Regulamento (cão, gato, bem-estar, criação, operador, estabelecimento, etc.).</t>
         </is>
       </c>
       <c r="O5" s="11" t="inlineStr">

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -931,43 +931,43 @@
           <t>Para efeitos do presente regulamento, entende-se por:
 1. «Cão», um animal da espécie Canis lupus familiaris;
 2. «Gato», um animal da espécie Felis silvestris catus;
-3. «Bem-estar dos cães e gatos», o estado físico e mental de um cão ou de um gato que recebe nutrição adequada, é mantido num ambiente apropriado, está em bom estado de saúde, exibe comportamento apropriado e tem uma experiência mental geral positiva da vida;
-4. «Híbrido», qualquer descendência da primeira à quarta geração após o cruzamento entre uma espécie selvagem e um cão ou gato doméstico;
-5. «Criação», a atividade de detenção de cães ou gatos em estabelecimentos de criação para efeitos de reprodução;
-6. «Detenção», qualquer atividade durante a qual cães e gatos sejam mantidos, alojados ou manuseados, quer num estabelecimento quer noutro local;
-7. «Colocação no mercado», a venda, oferta para fins de venda, distribuição ou qualquer outra forma de transferência de propriedade ou responsabilidade, quer mediante compensação financeira quer a título gratuito, de cães ou gatos;
-8. «Publicidade», qualquer forma de comunicação com o público, ou com uma parte deste, que tenha o efeito direto ou indireto de promover a colocação de cães ou gatos no mercado;
-9. «Plataforma em linha», uma plataforma em linha na aceção do artigo 3.º, alínea i), do Regulamento (UE) 2022/2065;
+3. «Bem‑estar dos cães e gatos», o estado físico e mental de um cão ou de um gato que recebe alimentação adequada, é detido num ambiente adequado, está em boa saúde, um comportamento adequado e, no geral, tem uma experiência mental positiva da vida;
+4. «Híbrido», qualquer descendência da primeira à quarta geração após o cruzamento entre uma espécie selvagem e um cão ou gato doméstico, ou entre um híbrido e uma espécie selvagem, um cão ou gato doméstico ou outros híbridos;
+5. «Criação», a detenção de cães ou gatos em estabelecimentos de criação para efeitos de reprodução;
+6. «Detenção», qualquer atividade durante a qual cães e gatos sejam mantidos, alojados ou manuseados, quer num estabelecimento quer sob a responsabilidade de um operador, ou ambos;
+7. «Colocação no mercado», a venda, oferta para fins de venda, distribuição ou qualquer outra forma de transferência de propriedade ou responsabilidade relativa a cães e gatos, quer a título oneroso quer a título gratuito, assim como a publicidade de cães e gatos para esses fins, com exceção das doações ocasionais por pessoas singulares que não sejam operadores sem publicidade em linha;
+8. «Publicidade», qualquer forma de comunicação com o público, ou com uma parte deste, que tenha o efeito direto ou indireto de promover um cão ou um gato, uma ou mais das suas características físicas, ou uma raça, com o intuito de despertar interesse, de provocar o contacto ou de atrair vendas;
+9. «Plataforma em linha», uma plataforma em linha na aceção do artigo 3.º, alínea i), do Regulamento (UE) 2022/2065, do Parlamento Europeu e do Conselho, que intermedeia a colocação no mercado de cães ou gatos;
 10. «Cadela», a fêmea do cão, desde o primeiro acasalamento ou inseminação até ao desmame da sua última ninhada;
 11. «Gata», a fêmea do gato, desde o primeiro acasalamento ou inseminação até ao desmame da sua última ninhada;
-12. «Cão de guarda de gado», um cão detido ou treinado principalmente para proteger o gado de predadores em contextos agrícolas;
-13. «Cão de pastoreio», um cão detido ou treinado principalmente para guiar, movimentar ou gerir gado em contextos agrícolas;
-14. «Estabelecimento», um estabelecimento de criação, um estabelecimento de venda, um abrigo ou uma casa de acolhimento;
-15. «Estabelecimento de criação», qualquer instalação ou estrutura, incluindo casas particulares, onde são mantidos cães ou gatos para efeitos de reprodução;
-16. «Agricultor», um agricultor na aceção do artigo 3.º, ponto 1, do Regulamento (UE) 2021/2115;
-17. «Estabelecimento de venda», qualquer instalação ou estrutura onde cães ou gatos são detidos para venda sem aí terem nascido nem sido criados;
-18. «Abrigo», qualquer instalação ou estrutura, incluindo as casas particulares, onde são detidos cães ou gatos não para fins comerciais;
-19. «Casa de acolhimento», uma casa particular onde cães ou gatos são detidos em nome de um operador responsável por cães ou gatos;
-20. «Operador», qualquer pessoa singular ou coletiva que coloca cães ou gatos no mercado e é responsável por um estabelecimento;
-21. «Autoridades competentes», as autoridades competentes na aceção do artigo 3.º, ponto 3, do Regulamento (UE) 2017/625;
-22. «Estratégia de reprodução», um conjunto de ações sistemáticas, incluindo o registo, a seleção, a reprodução e o cruzamento de cães ou gatos;
-23. «Eutanásia», o ato de induzir a morte através de um método que provoca uma perda de consciência rápida e irreversível e morte;
-24. «Mutilação», uma intervenção, incluindo uma intervenção cirúrgica, realizada por razões que não sejam terapêuticas ou profiláticas;
-25. «Esterilização», o processo através do qual cães ou gatos são impedidos de se reproduzirem com recurso a cirurgia e/ou a uma substância farmacêutica;
-26. «Sofrimento», um estado físico ou mental desagradável e indesejado, resultante da exposição de um cão ou gato a estímulos aversivos;
+12. «Cão de guarda de gado», um cão detido ou treinado principalmente para proteger o gado de predadores em contextos agrícolas ou pastoris;
+13. «Cão de pastoreio», um cão detido ou treinado principalmente para guiar, movimentar ou gado em contextos agrícolas ou pastoris, incluindo explorações agrícolas, zonas de pastoreio ou durante a transumância;
+14. «Estabelecimento», um estabelecimento de criação, um estabelecimento de venda, um abrigo ou um lar de acolhimento;
+15. «Estabelecimento de criação», qualquer instalação ou estrutura, incluindo casas particulares, onde são mantidos cães ou gatos para fins de reprodução com vista à colocação da sua descendência no mercado;
+16. «Agricultor», um agricultor na aceção do artigo 3.º, ponto 1, do Regulamento (UE) 2021/2115 do Parlamento Europeu e do Conselho;
+17. «Estabelecimento de venda», qualquer instalação ou estrutura onde cães ou gatos são detidos para venda sem aí terem nascido, incluindo lojas de animais de companhia ou casas particulares, bem como quaisquer instalações ou estruturas destinadas a operações de agrupamento nas quais sejam agrupados cães ou gatos a partir de mais do que um estabelecimento;
+18. «Abrigo», qualquer instalação ou estrutura, incluindo as casas particulares, onde são detidos cães ou gatos não desejados, abandonados, perdidos, confiscados ou anteriormente errantes, para efeitos de colocação no mercado;
+19. «Lar de acolhimento», uma casa particular onde cães ou gatos são detidos em nome de um operador responsável por cães ou gatos não desejados, abandonados, perdidos, confiscados ou anteriormente errantes;
+20. «Operador», qualquer pessoa singular ou coletiva que coloca cães ou gatos no mercado e é responsável por um estabelecimento de criação, por um estabelecimento de venda ou por um abrigo e pelos cães ou gatos aí detidos, ou que coloca cães e gatos num lar de acolhimento e é responsável pelos cães ou gatos aí detidos;
+21. «Autoridades competentes», as autoridades competentes na aceção do artigo 3.º, ponto 3, do Regulamento (UE) 2017/625 do Parlamento Europeu e do Conselho;
+22. «Estratégia de reprodução», um conjunto de ações sistemáticas, incluindo o registo, a seleção, a reprodução e o intercâmbio de cães ou gatos reprodutores e dos respetivos produtos germinais, concebidas e aplicadas com vista a preservar ou reforçar as características fenotípicas ou genotípicas pretendidas da população reprodutora alvo;
+23. «Eutanásia», o ato de induzir a morte através de um método que provoca uma perda de consciência rápida e irreversível com um mínimo de dor e angústia e que põe termo à vida do cão ou do gato;
+24. «Mutilação», uma intervenção, incluindo uma intervenção cirúrgica, realizada por razões que não sejam terapêuticas ou de diagnóstico, exceto a esterilização ou a implantação de um transpondedor, que provoca danos ou perda de uma parte sensível do corpo, ou a alteração da estrutura óssea, de um cão ou de um gato;
+25. «Esterilização», o processo através do qual cães ou gatos são impedidos de se reproduzirem com recurso a cirurgia e de forma irreversível;
+26. «Sofrimento», um estado físico ou mental desagradável e indesejado, resultante da exposição de um cão ou gato a estímulos nocivos ou da ausência continuada de estímulos positivos importantes;
 27. «Alojamento», edifícios ou espaço exterior delimitado em estabelecimentos onde são detidos cães ou gatos de forma temporária ou permanente;
 28. «Canil», uma estrutura física que contém um ou mais compartimentos para alojar cães;
 29. «Gatil», uma estrutura física que contém um ou mais compartimentos para alojar gatos;
-30. «Cuidador de animais», uma pessoa que cuida dos cães ou gatos criados ou detidos num estabelecimento, incluindo voluntários e estagiários;
-31. «Enriquecimentos», quaisquer materiais ou estruturas presentes no ambiente de um cão ou de um gato, com propriedades que promovem atividade positiva;
-32. «Acorrentamento», ato de prender um cão ou gato a um ponto de fixação ou a um objeto para o manter numa zona desejada;
-33. «Contentor», qualquer caixa, jaula, recetáculo ou outra estrutura móvel utilizada para confinar cães ou gatos;
-34. «Propriedade responsável», conjunto de comportamentos de um proprietário ou futuro proprietário de um cão ou gato em conformidade com os requisitos;
+30. «Tratador de animais», uma pessoa que trata dos cães ou gatos criados ou detidos num estabelecimento, incluindo voluntários, estagiários e trabalhadores a tempo parcial, sob a responsabilidade de um operador;
+31. «Enriquecimentos», quaisquer materiais ou estruturas presentes no ambiente de um cão ou de um gato, com propriedades ocupacionais ou nutricionais capazes de provocar e satisfazer a curiosidade ou o comportamento apetitivo de um cão ou de um gato, ou de o motivar fisicamente;
+32. «Amarração», ato de prender um cão ou gato a um ponto de fixação ou a um objeto para o manter numa zona desejada ou para restringir o seu movimento;
+33. «Contentor», qualquer grade, jaula, caixa ou recetáculo ou outra estrutura móvel utilizada para confinar cães ou gatos;
+34. «Propriedade responsável», conjunto de comportamentos de um proprietário ou futuro proprietário de um cão ou gato coerentes com um compromisso de desempenhar várias funções centradas na satisfação das necessidades de saúde, comportamentais, ambientais e físicas do cão ou do gato e de minimizar os riscos que o cão ou gato pode representar para a comunidade, para outros animais ou para o ambiente;
 35. «Proprietário de um animal de companhia», uma pessoa singular ou coletiva que é proprietária de um cão ou gato como animal de companhia;
-36. «Animal de companhia», um cão ou gato detido para entretenimento pessoal ou para fazer companhia a humanos;
-37. «Sistema de Alerta Rápido» (iRASFF), o sistema eletrónico que aplica o sistema de alerta rápido descrito no artigo 50.º do Regulamento (UE) 2017/625;
-38. «Rede AAC», a rede constituída pela Comissão e pelos organismos de ligação designados pelos Estados-Membros em conformidade com o artigo 36.º do Regulamento (UE) 2017/625;
-39. «Circulação sem caráter comercial», a circulação sem caráter comercial definida no artigo 4.º, ponto 14, do Regulamento (UE) 2016/429.</t>
+36. «Animal de companhia», um cão ou um gato detido para entretenimento pessoal ou para fazer companhia a humanos;
+37. «Sistema de Alerta Rápido» (iRASFF), o sistema eletrónico que aplica o sistema de alerta rápido descrito no artigo 50.º do Regulamento (CE) n.º 178/2002 do Parlamento Europeu e do Conselho e os procedimentos de assistência e de cooperação administrativas entre Estados-Membros descritos nos artigos 102.º a 108.º do Regulamento (UE) 2017/625, respetivamente;
+38. «Rede AAC», a rede constituída pela Comissão e pelos organismos de ligação designados pelos Estados-Membros em conformidade com o artigo 103.º, n.º 1, do Regulamento (UE) 2017/625 com o objetivo de facilitar a comunicação entre as autoridades competentes;
+39. «Circulação sem caráter comercial», a circulação sem caráter comercial na aceção do artigo 4.º, ponto 14, do Regulamento (UE) 2016/429 do Parlamento Europeu e do Conselho, quando o animal de companhia em causa for um cão ou um gato.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>Define os 39 conceitos-chave usados ao longo do Regulamento (cão, gato, bem-estar, criação, operador, estabelecimento, etc.).</t>
+          <t>Define os 39 conceitos-chave usados ao longo do Regulamento (cão, gato, bem-estar, criação, operador, estabelecimento, lar de acolhimento, amarração, etc.).</t>
         </is>
       </c>
       <c r="O5" s="11" t="inlineStr">

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -681,9 +681,9 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>O presente regulamento define:
-a) Os requisitos mínimos para o bem-estar dos cães e gatos criados ou detidos em estabelecimentos ou colocados no mercado da União;
-b) A rastreabilidade dos cães e gatos.</t>
+          <t>O presente regulamento define os requisitos mínimos para:
+a)	O bem-estar dos cães e gatos criados ou detidos em estabelecimentos ou colocados no mercado da União;
+b)	A rastreabilidade dos cães e gatos ▌.</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -750,8 +750,9 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>1. O presente regulamento aplica-se à criação, à detenção, ao rastreio, à colocação no mercado e à entrada na União de cães e gatos.
-2. O presente regulamento não se aplica à criação, detenção ou colocação no mercado ou à entrada na União de cães ou gatos destinados ou utilizados para fins científicos ou para ensaios clínicos exigidos para a autorização de comercialização de medicamentos veterinários.</t>
+          <t>1.	O presente regulamento é aplicável à criação, à detenção, à rastreabilidade, à colocação no mercado e à entrada na União de cães e gatos ▌.
+2.	O presente regulamento não é aplicável à criação, à detenção, à colocação no mercado ou à entrada na União de cães ou gatos destinados ou usados para fins científicos ou para ensaios clínicos exigidos para efeitos da autorização de introdução no mercado de medicamentos veterinários.
+▌</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -820,10 +821,10 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>1. O capítulo II do presente regulamento aplica-se a todos os operadores.
-2. O capítulo III do presente regulamento aplica-se a todas as pessoas singulares e coletivas proprietárias de cães e gatos na União.
-3. O capítulo IV aplica-se a todas as pessoas singulares e coletivas que introduzam cães ou gatos na União.
-4. O presente regulamento não aplica-se a agricultores que, na sua exploração, ofereçam refúgio a gatos vadios em liberdade que sejam úteis para controlo de pragas, desde que esses agricultores não sejam operadores e não coloquem esses gatos no mercado.</t>
+          <t>1.	O capítulo II é aplicável a todos os operadores.
+2.	O capítulo III é aplicável a todas as pessoas singulares e coletivas proprietárias de cães ou gatos na União.
+3.	O capítulo V é aplicável a todas as pessoas singulares e coletivas que introduzam cães ou gatos na União.
+4.	O presente regulamento não é aplicável a agricultores que, na sua exploração, ofereçam refúgio a gatos errantes que sejam úteis para o controlo de pragas, desde que tais agricultores não sejam operadores e não coloquem esses gatos no mercado.</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -929,45 +930,52 @@
       <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Para efeitos do presente regulamento, entende-se por:
-1. «Cão», um animal da espécie Canis lupus familiaris;
-2. «Gato», um animal da espécie Felis silvestris catus;
-3. «Bem‑estar dos cães e gatos», o estado físico e mental de um cão ou de um gato que recebe alimentação adequada, é detido num ambiente adequado, está em boa saúde, um comportamento adequado e, no geral, tem uma experiência mental positiva da vida;
-4. «Híbrido», qualquer descendência da primeira à quarta geração após o cruzamento entre uma espécie selvagem e um cão ou gato doméstico, ou entre um híbrido e uma espécie selvagem, um cão ou gato doméstico ou outros híbridos;
-5. «Criação», a detenção de cães ou gatos em estabelecimentos de criação para efeitos de reprodução;
-6. «Detenção», qualquer atividade durante a qual cães e gatos sejam mantidos, alojados ou manuseados, quer num estabelecimento quer sob a responsabilidade de um operador, ou ambos;
-7. «Colocação no mercado», a venda, oferta para fins de venda, distribuição ou qualquer outra forma de transferência de propriedade ou responsabilidade relativa a cães e gatos, quer a título oneroso quer a título gratuito, assim como a publicidade de cães e gatos para esses fins, com exceção das doações ocasionais por pessoas singulares que não sejam operadores sem publicidade em linha;
-8. «Publicidade», qualquer forma de comunicação com o público, ou com uma parte deste, que tenha o efeito direto ou indireto de promover um cão ou um gato, uma ou mais das suas características físicas, ou uma raça, com o intuito de despertar interesse, de provocar o contacto ou de atrair vendas;
-9. «Plataforma em linha», uma plataforma em linha na aceção do artigo 3.º, alínea i), do Regulamento (UE) 2022/2065, do Parlamento Europeu e do Conselho, que intermedeia a colocação no mercado de cães ou gatos;
-10. «Cadela», a fêmea do cão, desde o primeiro acasalamento ou inseminação até ao desmame da sua última ninhada;
-11. «Gata», a fêmea do gato, desde o primeiro acasalamento ou inseminação até ao desmame da sua última ninhada;
-12. «Cão de guarda de gado», um cão detido ou treinado principalmente para proteger o gado de predadores em contextos agrícolas ou pastoris;
-13. «Cão de pastoreio», um cão detido ou treinado principalmente para guiar, movimentar ou gado em contextos agrícolas ou pastoris, incluindo explorações agrícolas, zonas de pastoreio ou durante a transumância;
-14. «Estabelecimento», um estabelecimento de criação, um estabelecimento de venda, um abrigo ou um lar de acolhimento;
-15. «Estabelecimento de criação», qualquer instalação ou estrutura, incluindo casas particulares, onde são mantidos cães ou gatos para fins de reprodução com vista à colocação da sua descendência no mercado;
-16. «Agricultor», um agricultor na aceção do artigo 3.º, ponto 1, do Regulamento (UE) 2021/2115 do Parlamento Europeu e do Conselho;
-17. «Estabelecimento de venda», qualquer instalação ou estrutura onde cães ou gatos são detidos para venda sem aí terem nascido, incluindo lojas de animais de companhia ou casas particulares, bem como quaisquer instalações ou estruturas destinadas a operações de agrupamento nas quais sejam agrupados cães ou gatos a partir de mais do que um estabelecimento;
-18. «Abrigo», qualquer instalação ou estrutura, incluindo as casas particulares, onde são detidos cães ou gatos não desejados, abandonados, perdidos, confiscados ou anteriormente errantes, para efeitos de colocação no mercado;
-19. «Lar de acolhimento», uma casa particular onde cães ou gatos são detidos em nome de um operador responsável por cães ou gatos não desejados, abandonados, perdidos, confiscados ou anteriormente errantes;
-20. «Operador», qualquer pessoa singular ou coletiva que coloca cães ou gatos no mercado e é responsável por um estabelecimento de criação, por um estabelecimento de venda ou por um abrigo e pelos cães ou gatos aí detidos, ou que coloca cães e gatos num lar de acolhimento e é responsável pelos cães ou gatos aí detidos;
-21. «Autoridades competentes», as autoridades competentes na aceção do artigo 3.º, ponto 3, do Regulamento (UE) 2017/625 do Parlamento Europeu e do Conselho;
-22. «Estratégia de reprodução», um conjunto de ações sistemáticas, incluindo o registo, a seleção, a reprodução e o intercâmbio de cães ou gatos reprodutores e dos respetivos produtos germinais, concebidas e aplicadas com vista a preservar ou reforçar as características fenotípicas ou genotípicas pretendidas da população reprodutora alvo;
-23. «Eutanásia», o ato de induzir a morte através de um método que provoca uma perda de consciência rápida e irreversível com um mínimo de dor e angústia e que põe termo à vida do cão ou do gato;
-24. «Mutilação», uma intervenção, incluindo uma intervenção cirúrgica, realizada por razões que não sejam terapêuticas ou de diagnóstico, exceto a esterilização ou a implantação de um transpondedor, que provoca danos ou perda de uma parte sensível do corpo, ou a alteração da estrutura óssea, de um cão ou de um gato;
-25. «Esterilização», o processo através do qual cães ou gatos são impedidos de se reproduzirem com recurso a cirurgia e de forma irreversível;
-26. «Sofrimento», um estado físico ou mental desagradável e indesejado, resultante da exposição de um cão ou gato a estímulos nocivos ou da ausência continuada de estímulos positivos importantes;
-27. «Alojamento», edifícios ou espaço exterior delimitado em estabelecimentos onde são detidos cães ou gatos de forma temporária ou permanente;
-28. «Canil», uma estrutura física que contém um ou mais compartimentos para alojar cães;
-29. «Gatil», uma estrutura física que contém um ou mais compartimentos para alojar gatos;
-30. «Tratador de animais», uma pessoa que trata dos cães ou gatos criados ou detidos num estabelecimento, incluindo voluntários, estagiários e trabalhadores a tempo parcial, sob a responsabilidade de um operador;
-31. «Enriquecimentos», quaisquer materiais ou estruturas presentes no ambiente de um cão ou de um gato, com propriedades ocupacionais ou nutricionais capazes de provocar e satisfazer a curiosidade ou o comportamento apetitivo de um cão ou de um gato, ou de o motivar fisicamente;
-32. «Amarração», ato de prender um cão ou gato a um ponto de fixação ou a um objeto para o manter numa zona desejada ou para restringir o seu movimento;
-33. «Contentor», qualquer grade, jaula, caixa ou recetáculo ou outra estrutura móvel utilizada para confinar cães ou gatos;
-34. «Propriedade responsável», conjunto de comportamentos de um proprietário ou futuro proprietário de um cão ou gato coerentes com um compromisso de desempenhar várias funções centradas na satisfação das necessidades de saúde, comportamentais, ambientais e físicas do cão ou do gato e de minimizar os riscos que o cão ou gato pode representar para a comunidade, para outros animais ou para o ambiente;
-35. «Proprietário de um animal de companhia», uma pessoa singular ou coletiva que é proprietária de um cão ou gato como animal de companhia;
-36. «Animal de companhia», um cão ou um gato detido para entretenimento pessoal ou para fazer companhia a humanos;
-37. «Sistema de Alerta Rápido» (iRASFF), o sistema eletrónico que aplica o sistema de alerta rápido descrito no artigo 50.º do Regulamento (CE) n.º 178/2002 do Parlamento Europeu e do Conselho e os procedimentos de assistência e de cooperação administrativas entre Estados-Membros descritos nos artigos 102.º a 108.º do Regulamento (UE) 2017/625, respetivamente;
-38. «Rede AAC», a rede constituída pela Comissão e pelos organismos de ligação designados pelos Estados-Membros em conformidade com o artigo 103.º, n.º 1, do Regulamento (UE) 2017/625 com o objetivo de facilitar a comunicação entre as autoridades competentes;
-39. «Circulação sem caráter comercial», a circulação sem caráter comercial na aceção do artigo 4.º, ponto 14, do Regulamento (UE) 2016/429 do Parlamento Europeu e do Conselho, quando o animal de companhia em causa for um cão ou um gato.</t>
+1)	«Cão», um animal da espécie Canis lupus familiaris;
+▌
+2)	«Gato», um animal da espécie Felis silvestris catus;
+3)	«Bem‑estar dos cães e gatos», o estado físico e mental de um cão ou de um gato que recebe alimentação adequada, é detido num ambiente adequado, é mantido em boa saúde, exibe um comportamento adequado e, no geral, tem uma experiência mental positiva da vida;
+4)	«Híbrido», qualquer descendência da primeira à quarta geração após o cruzamento entre uma espécie selvagem e um cão ou gato doméstico, ou entre um híbrido e uma espécie selvagem, um cão ou gato doméstico ou outros híbridos;
+5)	«Criação», a detenção de cães ou gatos em estabelecimentos de criação para efeitos de reprodução;
+6)	«Detenção», qualquer atividade durante a qual cães e gatos sejam mantidos, alojados ou manuseados, quer num estabelecimento quer sob a responsabilidade de um operador, ou ambos;
+7)	«Colocação no mercado», a ▌venda, oferta para fins de venda, distribuição ou qualquer outra forma de transferência de propriedade ou responsabilidade relativa a cães e gatos, quer a título oneroso quer a título gratuito, assim como a publicidade de cães e gatos para esses fins, com exceção das doações ocasionais a intervalos irregulares por pessoas singulares que não sejam operadores sem publicidade em linha;
+8)	«Publicidade», qualquer forma de comunicação com o público, ou com uma parte deste, que tenha o efeito direto ou indireto de promover um cão ou um gato, uma ou mais das suas características físicas, ou uma raça, com o intuito de despertar interesse, de provocar o contacto ou de atrair vendas;
+9)	«Plataforma em linha», uma plataforma em linha na aceção do artigo 3.º, alínea i), do Regulamento (UE) 2022/2065, do Parlamento Europeu e do Conselho, que intermedeia a colocação no mercado ▌de cães ou gatos;
+▌
+10)	«Cadela», a fêmea do cão, desde o primeiro acasalamento ou inseminação até ao desmame da sua última ninhada;
+11)	«Gata», a fêmea do gato, desde o primeiro acasalamento ou inseminação até ao desmame da sua última ninhada;
+12)	«Cão de guarda de gado», um cão detido ou treinado principalmente para proteger o gado de predadores em contextos agrícolas ou pastoris;
+13)	«Cão de pastoreio», um cão detido ou treinado principalmente para guiar, movimentar ou, de outro modo, controlar gado em contextos agrícolas ou pastoris, incluindo explorações agrícolas, zonas de pastoreio ou durante a transumância;
+14)	«Estabelecimento», um estabelecimento de criação, um estabelecimento de venda, um abrigo ou um lar de acolhimento;
+15)	«Estabelecimento de criação», qualquer instalação ou estrutura, incluindo casas particulares, onde são mantidos cães ou gatos para fins de reprodução com vista à colocação da sua descendência no mercado;
+16)	«Agricultor», um agricultor na aceção do artigo 3.º, ponto 1, do Regulamento (UE) 2021/2115 do Parlamento Europeu e do Conselho;
+17)	«Estabelecimento de venda», qualquer instalação ou estrutura onde cães ou gatos são detidos para venda ▌sem aí terem nascido, incluindo lojas de animais de companhia ou casas particulares, bem como quaisquer instalações ou estruturas destinadas a operações de agrupamento nas quais sejam agrupados cães ou gatos a partir de mais do que um estabelecimento;
+18)	«Abrigo», qualquer instalação ou estrutura, incluindo as casas particulares ▌, onde são detidos cães ou gatos não desejados, abandonados, perdidos, confiscados ou anteriormente errantes, para efeitos de colocação no mercado;
+19)	«Lar de acolhimento», uma casa particular onde cães ou gatos são detidos em nome de um operador responsável por cães ou gatos não desejados, abandonados, perdidos, confiscados ou anteriormente errantes;
+20)	«Operador», qualquer pessoa singular ou coletiva que coloca cães ou gatos no mercado e é responsável por um estabelecimento de criação, por um estabelecimento de venda ou por um abrigo e pelos cães ou gatos aí detidos, ou que coloca cães e gatos num lar de acolhimento e é responsável pelos cães ou gatos aí detidos;
+▌
+21)	«Autoridades competentes», as autoridades competentes na aceção do artigo 3.º, ponto 3, do Regulamento (UE) 2017/625 do Parlamento Europeu e do Conselho;
+22)	«Estratégia de reprodução», um conjunto de ações sistemáticas, incluindo o registo, a seleção, a reprodução e o intercâmbio de cães ou gatos reprodutores e dos respetivos produtos germinais, concebidas e aplicadas com vista a preservar ou reforçar as características fenotípicas ou genotípicas pretendidas da população reprodutora alvo;
+23)	«Eutanásia», o ato de induzir a morte através de um método que provoca uma perda de consciência rápida e irreversível com um mínimo de dor e angústia e que põe termo à vida do cão ou do gato;
+24)	«Mutilação», uma intervenção, incluindo uma intervenção cirúrgica, realizada por razões que não sejam terapêuticas ou de diagnóstico, exceto a esterilização ou a implantação de um transponder, que provoca danos ou perda de uma parte sensível do corpo, ou a alteração da estrutura óssea, de um cão ou de um gato;
+25)	«Esterilização», o processo através do qual cães ou gatos são impedidos de se reproduzirem com recurso a cirurgia e de forma irreversível;
+▌
+26)	«Sofrimento», um estado físico ou mental desagradável e indesejado, resultante da exposição de um cão ou gato a estímulos nocivos ou da ausência continuada de estímulos positivos importantes;
+27)	«Alojamento», edifícios ou espaço exterior delimitado em estabelecimentos onde são detidos cães ou gatos de forma temporária ou permanente;
+28)	«Canil», uma estrutura física que contém um ou mais compartimentos ▌para alojar cães;
+29)	«Gatil», uma estrutura física que contém um ou mais compartimentos ▌para alojar gatos;
+30)	«Tratador de animais», uma pessoa que trata dos cães ou gatos criados ou detidos num estabelecimento, incluindo voluntários, estagiários e trabalhadores a tempo parcial, sob a responsabilidade de um operador;
+31)	«Enriquecimentos», quaisquer materiais ou estruturas presentes no ambiente de um cão ou de um gato, com propriedades ocupacionais ou nutricionais capazes de provocar e satisfazer a curiosidade ou o comportamento apetitivo de um cão ou de um gato, ou de o motivar fisicamente;
+32)	«Amarração», ato de prender um cão ou gato a um ponto de fixação ou a um objeto para o manter numa zona desejada ou para restringir o seu movimento;
+33)	«Contentor», qualquer grade, jaula, caixa ou  recetáculo ou outra estrutura móvel utilizada para confinar cães ou gatos;
+▌
+34)	«Propriedade responsável», conjunto de comportamentos de um proprietário ou futuro proprietário de um cão ou gato coerentes com um compromisso de desempenhar várias funções centradas na satisfação das necessidades de saúde, comportamentais, ambientais e físicas do cão ou do gato e de minimizar os riscos que o cão ou gato pode representar para a comunidade, para outros animais ou para o ambiente;
+35)	«Proprietário de um animal de companhia», uma pessoa singular ou coletiva que é proprietária de um cão ou gato como animal de companhia;
+36)	«Animal de companhia», um cão ou um gato detido para entretenimento pessoal ou para fazer companhia a humanos;
+37)	«Sistema de Alerta Rápido» (iRASFF), o sistema eletrónico que aplica o sistema de alerta rápido descrito no artigo 50.º do Regulamento (CE) n.º 178/2002 do Parlamento Europeu e do Conselho e os procedimentos de assistência e de cooperação administrativas entre Estados-Membros descritos nos artigos 102.º a 108.º do Regulamento (UE) 2017/625, respetivamente;
+38)	«Rede AAC», a rede constituída pela Comissão e pelos organismos de ligação designados pelos Estados-Membros em conformidade com o artigo 103.º, n.º 1, do Regulamento (UE) 2017/625 com o objetivo de facilitar a comunicação entre as autoridades competentes;
+39)	«Circulação sem caráter comercial», a circulação sem caráter comercial na aceção do artigo 4.º, ponto 14, do Regulamento (UE) 2016/429 do Parlamento Europeu e do Conselho, quando o animal de companhia em causa for um cão ou um gato.
+CAPÍTULO II
+OBRIGAÇÕES DOS OPERADORES DE ESTABELECIMENTOS</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -1034,8 +1042,9 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>1. Um estabelecimento de criação que produz no máximo duas ninhadas por ano civil para colocação no mercado fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (n.º 1, alíneas 1b, 1c e 1d), artigo 6a, artigo 7.º, artigo 8.º, artigo 11.º (n.ºs 2, 3 e 3a), artigo 12.º (n.ºs 3, 4 e 7), artigo 13.º (n.º 2, alíneas b, c e d), artigo 14.º (n.ºs 2, 3, 4 e 5a), artigo 15.º, artigo 15a (n.º 1) e ponto 3 e 4.3 do Anexo I.
-2. Um abrigo, onde são mantidos no máximo 15 cães ou gatos em qualquer momento, ou qualquer lar de acolhimento fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (n.ºs 1, 1a, 1b, 1c e 1d), artigo 7.º, artigo 8.º, artigo 11.º (n.ºs 2, 3 e 3a), artigo 12.º (n.ºs 3, 4 e 7), artigo 13.º (n.º 2, alíneas a, b, c e d), artigo 14.º (n.ºs 2, 3, 4 e 5a), artigo 15.º e ponto 4.3 do Anexo I.</t>
+          <t>1.	Um estabelecimento de criação em que não sejam produzidas mais de duas ninhadas por ano civil para colocação no mercado apenas está sujeito às obrigações previstas no artigo 6.º, no artigo 7.º, n.os 1, 3, 4 e 5, no artigo 8.º, no artigo 9.º, no artigo 11.º, no artigo 14.º, n.os 2, 3 e 4, no artigo 15.º, n.os 3, 4 e 8, no artigo 16.º, n.º 1, alíneas b), c) e d), no artigo 17.º, n.º 2, 3, 5 e 7, no artigo 18.º, no artigo 19.º, n.º 1 e nos pontos 3 e 4.3 do anexo I.
+2.	Os abrigos que detenham, no máximo, um total combinado de 15 cães ou gatos, a todo o momento, ou quaisquer lares de acolhimento, apenas estão sujeitos às obrigações previstas no artigo 6.º, no artigo 7.º, n.os 1, 2, 3, 4, e 5, no artigo 9.º, no artigo 11.º, no artigo 14.º, n.os 2, 3 e 4, no artigo 15.º n.os 3, 4 e 8, no artigo 16.º, n.º 1, alíneas a), b), c) e d), no artigo 17.º, n.º 2, 3, 5 e 7, no artigo 18.º e no ponto 4.3 do anexo I.
+▌</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1106,12 +1115,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Os operadores devem aplicar os seguintes princípios gerais de bem-estar aos cães e gatos criados ou detidos nos seus estabelecimentos:
-(a) Os cães e os gatos recebem água e alimentos de qualidade e numa quantidade que assegura a sua boa e adequada nutrição e hidratação;
-(b) os cães e gatos são mantidos num ambiente físico adequado, regularmente limpo, seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, iluminação, proteção face a condições climáticas adversas e facilidade de movimentação, prevenindo a sobrelotação;
-(c) os cães e gatos são mantidos seguros, limpos e com boa saúde, prevenindo doenças, lesões e dor, nomeadamente através de práticas de maneio, manuseamento e reprodução adequadas;
-(d) os cães e gatos são mantidos num ambiente que lhes permite exibir comportamentos específicos da espécie e comportamentos sociais não nocivos, e estabelecer uma relação positiva com os seres humanos;
-(e) (e) os cães e gatos são mantidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo estímulos negativos em duração e intensidade, maximizando oportunidades de estímulos positivos, prevenindo o desenvolvimento de comportamentos repetitivos anormais, tendo em conta as necessidades individuais do animal nos domínios referidos nas alíneas (a) a (d).</t>
+          <t>Os operadores ▌devem aplicar os seguintes princípios gerais de bem‑estar no que diz respeito aos cães ou gatos criados ou detidos no seu estabelecimento:
+a)	Os cães e os gatos recebem água e alimentos de qualidade e numa quantidade que lhes proporcione uma alimentação e abeberamento adequados;
+b)	Os cães e os gatos são detidos num ambiente físico que é adequado e limpo com regularidade, que é seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, luz e proteção contra condições climáticas adversas, e que é suficientemente grande para prevenir a sobrelotação e para lhes proporcionar facilidade de circulação;
+c)	Os cães e os gatos são detidos em segurança, limpos e em boa saúde, devendo as doenças, ▌lesões e dores que decorrem, em especial da gestão, das práticas de manuseamento e das práticas de criação, ser prevenidas;
+d)	Os cães e os gatos são detidos num ambiente que lhes permite exibir comportamentos específicos da espécie e sociais não nocivos e estabelecer uma relação positiva com os seres humanos;
+e)	Os cães e os gatos são detidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo ▌os estímulos negativos em termos de duração e intensidade, bem como maximizando as oportunidades de estímulos positivos em termos de duração e intensidade, de forma que previna o desenvolvimento de comportamentos repetitivos anormais ou de outros comportamentos indicadores de um deficiente bem-estar animal, e que tenha em conta as necessidades individuais de cada animal nos domínios referidos nas alíneas a) a d).</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1217,15 +1226,16 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores são responsáveis pelo bem-estar dos cães e gatos detidos nos estabelecimentos sob a sua responsabilidade e controlo, devendo minimizar quaisquer riscos para o bem-estar desses animais.
-2. No caso das famílias de acolhimento, a responsabilidade incumbe ao operador em cujo nome os cães ou gatos são detidos. Tais operadores não colocam mais do que um total combinado de cinco cães ou gatos ou uma ninhada, com ou sem a mãe, num lar de acolhimento em qualquer momento dado e fornecem à família de acolhimento informações adequadas sobre as obrigações em matéria de bem-estar dos animais, bem como sobre as necessidades individuais dos cães ou gatos, e asseguram que as obrigações relevantes previstas no presente regulamento são cumpridas nos lares de acolhimento.
-O Estado-Membro em que se situa o lar de acolhimento pode autorizar um maior número de cães, gatos ou ninhadas na família de acolhimento, desde que as instalações do lar de acolhimento disponham de espaço suficiente, incluindo espaço exterior, e que o número de cuidadores de animais no lar de acolhimento seja suficiente para garantir o bem-estar dos cães e gatos.
-3. Os operadores não sujeitam qualquer cão ou gato a crueldade, abusos ou maus-tratos, incluindo fazendo-os participar em atividades suscetíveis de resultar em crueldade, abusos ou maus-tratos para os cães ou gatos criados ou detidos pelo operador.
-4. Os operadores não abandonam os cães ou gatos criados ou detidos por eles.
-5. Antes de os operadores cessarem as atividades num estabelecimento, asseguram que os cães ou gatos aí detidos são realojados, seja assumindo eles próprios a propriedade de animal de companhia, seja transferindo a responsabilidade pela propriedade dos cães e gatos para outros operadores ou adquirentes.
-6. Os operadores asseguram que os cães e gatos são manuseados por um número suficiente de cuidadores de animais para satisfazer as necessidades de bem-estar dos cães ou gatos detidos nos seus estabelecimentos, e que esses cuidadores possuem as competências exigidas no artigo 12.º.
-7. Os operadores asseguram o bem-estar dos cães ou gatos pelos quais são responsáveis, monitorizando indicadores baseados nos animais relativos ao comportamento e à aparência física, e adotando ações com base nos resultados desse monitoramento.
-8. A Comissão fica habilitada a adotar atos delegados, nos termos do artigo 28.º, que complementem o presente regulamento, estabelecendo os indicadores baseados nos animais relativos ao comportamento e à aparência física que os operadores devem utilizar para efeitos de monitorização nos termos do n.º 7 do presente artigo, bem como os métodos pelos quais os operadores devem medi-los.</t>
+          <t>1.	Os operadores ▌ são responsáveis pelo bem‑estar dos cães e gatos detidos em estabelecimentos sob a sua responsabilidade e controlo e pela minimização de quaisquer riscos para o bem‑estar desses animais.
+2.	No caso dos lares de acolhimento, a responsabilidade incumbe aos operadores em cujo nome os cães ou gatos são detidos. Tais operadores não podem, em nenhum momento, colocar mais do que um total combinado de cinco cães ou gatos, ou mais do que uma ninhada com ou sem uma mãe, num lar de acolhimento, devem disponibilizar à família de acolhimento as informações adequadas sobre as obrigações em matéria de bem-estar dos animais, assim como sobre as necessidades individuais dos cães ou gatos, e devem assegurar que nos lares de acolhimento sejam respeitadas as obrigações pertinentes previstas no presente regulamento.
+O Estado-Membro em que se situa o lar de acolhimento pode autorizar que um maior número de cães, gatos ou ninhadas seja colocado no lar de acolhimento, desde que as instalações desta disponham de espaço suficiente, incluindo espaço exterior, e que o número de tratadores de animais no referido lar de acolhimento seja suficiente para assegurar o bem-estar dos cães ou gatos.
+3.	Os operadores não podem sujeitar nenhum cão ou gato a crueldade, abuso ou maus-tratos, nomeadamente fazendo-os participar em atividades suscetíveis de resultar em atos de crueldade, abuso ou maus-tratos dos cães ou gatos criados ou detidos pelo operador.
+4.	Os operadores não podem abandonar os cães ou gatos por eles criados ou detidos.
+5.	Antes de cessarem as suas atividades num estabelecimento, os operadores asseguram que os cães ou gatos aí detidos sejam realojados, quer passando eles próprios a ser o proprietário do cão ou gato enquanto animal de companhia, quer transferindo a responsabilidade pelos cães e gatos, ou a propriedade dos mesmos, para outros operadores ou adquirentes.
+6.	Os operadores ▌asseguram que os cães e gatos sejam manuseados por um número de tratadores de animais suficiente para satisfazer as necessidades de bem-estar dos cães ou dos gatos que são detidos nos seus estabelecimentos, e que esses tratadores possuam as ▌competências exigidas nos termos do artigo 12.º.
+7.	Os operadores asseguram o bem-estar dos cães ou dos gatos pelos quais são responsáveis, fazendo uma monitorização dos indicadores relativos ao comportamento e aspeto físico baseados nos animais e tomando medidas em função do resultado dessa monitorização.
+8.	A Comissão fica habilitada a adotar atos delegados nos termos do artigo 28.º que completem o presente regulamento, prevendo indicadores relativos ao comportamento e aspeto físico baseados nos animais, que devem ser usados pelos operadores para efeitos da monitorização a realizar em conformidade com o n.º 7 do presente artigo, assim como os métodos a usar pelos operadores para a sua medição.
+.▌</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1377,29 +1387,7 @@
       </c>
       <c r="N8" s="11" t="inlineStr">
         <is>
-          <t>Necessidade de: (1) criar o conceito de 'família de acolhimento' como extensão da atividade do operador; (2) fixar limite numérico de animais por família (máximo 5, ou 1 ninhada com mãe); (3) atribuir responsabilidade jurídica ao operador, não à família de acolhimento.
-Critério / Determinação do Regulamento | Regulamento (UE) 2023/0447(texto PT-PT) | @rgbeac(proposta jun. 2025) | @codigo(proposta DL n.º 214/2013) | Proposta
-al. (a) — Água e alimentaçãoFornecimento adequado de água e alimentos(nutrição e hidratação) | Os cães e gatos recebem água e alimentos de qualidade e numa quantidade que assegura a sua boa e adequada nutrição e hidratação.(al. (a) do art.º 6.º) | Art.º 7.º, n.º 1, al. a) — proibição de fome, sede ou malnutrição.Art.º 10.º, n.º 1, al. a), ii) — alimentos saudáveis, adequados e convenientes; acesso permanente a água potável.Art.º 51.º, n.º 1 — programa de alimentação bem definido, de valor nutritivo adequado, em quantidade suficiente para as necessidades das espécies e dos indivíduos.Art.º 51.º, n.º 6 — acesso a água potável sem restrição (salvo razões médico-veterinárias).Coberto. | Art.º 4.º — dever de assegurar as necessidades básicas de bem-estar.Art.º 46.º, n.º 1 — programa de alimentação bem definido, de valor nutritivo adequado, em quantidade suficiente para as necessidades das espécies e dos indivíduos (nos locais de criação, manutenção, venda, centros de recolha e hospedagem).Art.º 46.º, n.º 6 — acesso a água potável sem restrição (salvo razões médico-veterinárias).Coberto no âmbito de estabelecimentos (art.º 46.º não se aplica à detenção doméstica individual). | Rgbeac ou código, ampliado à detenção
-al. (b) — Ambiente físico (1/2)Limpo, seguro e confortável(espaço, ar, temperatura, luz, clima) | Os cães e gatos são mantidos num ambiente físico adequado, regularmente limpo, seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, iluminação e proteção face a condições climáticas adversas.(al. (b) do art.º 6.º) | Art.º 7.º, n.º 1, al. b) — proibição de desconforto físico ou térmico.Art.º 10.º, n.º 1, al. a), v) — abrigo adequado com proteção de condições atmosféricas adversas (frio, chuva, sol ou calor excessivos); cama seca, limpa e confortável.Art.º 48.º, n.º 1 — temperatura, ventilação, luminosidade e obscuridade adequadas à manutenção do bem-estar e conforto das espécies.Art.º 48.º, n.º 3 — luz preferencialmente natural; luz artificial o mais próxima do espectro solar.Parcialmente coberto (sem referência explícita a qualidade do ar como parâmetro distinto da ventilação). | Art.º 5.º, n.º 1 — condições de detenção devem salvaguardar bem-estar.Art.º 14.º, n.º 1 — temperatura, ventilação, luminosidade e obscuridade das instalações adequadas ao bem-estar das espécies.Art.º 14.º, n.º 3 — luz preferencialmente natural; artificial o mais próxima do espectro solar.Parcialmente coberto (sem referência explícita a qualidade do ar como parâmetro distinto da ventilação). | Referir qualidade do ar?
-al. (b) — Ambiente físico (2/2)Espaço anti-sobrelotação;liberdade de movimentos | Os cães e gatos são mantidos num espaço suficientemente grande para prevenir a sobrelotação e garantir a facilidade de movimentação.(al. (b) do art.º 6.º) | Art.º 10.º, n.º 1, al. a), iv) — liberdade de movimento; proibição de contenção permanente; espaço e enriquecimento ambiental adequados. Art.º 47.º, n.º 1 — espaço adequado às necessidades fisiológicas e etológicas; prática de exercício físico; fuga de animais agressores. Portaria prevista no art.º 58.º fixará requisitos específicos. Parcialmente coberto (sobrelotação não referenciada de forma autónoma). | Art.º 5.º, n.º 3, al. b) — proibição de restringir a liberdade de movimentos de forma a impedir levantar-se, deitar-se ou virar-se sobre si próprios. Art.º 13.º, n.º 1, als. a) e b) — espaço adequado às necessidades fisiológicas e etológicas; prática de exercício físico; fuga de animais agressores. Parcialmente coberto (sobrelotação não referenciada de forma autónoma). | Rgbeac com referência à sobrelotação
-al. (c) — Saúde e higiene (1/2)Segurança, limpeza, boa saúde;prevenção de doenças, lesões e dor | Os cães e gatos são mantidos seguros, limpos e com boa saúde, prevenindo doenças, lesões e dor.(al. (c) do art.º 6.º) | Art.º 7.º, n.º 1, al. c) — proibição de dor, lesão física ou doença.Art.º 10.º, n.º 1, al. a), iii) — condições higiossanitárias.Art.º 10.º, n.º 1, al. f) — tratamento veterinário preventivo, paliativo ou curativo.Art.º 52.º, n.º 2 — todos os animais alvo de inspeção no início e final do dia e a cada quatro horas; primeiros cuidados imediatos a animais doentes ou lesionados. | Art.º 4.º — dever de salvaguardar a saúde.Art.º 6.º — dever de assegurar cuidados médico-veterinários ao animal ferido ou doente.Art.º 47.º, n.º 3 — inspeção diária de todos os animais; primeiros cuidados imediatos a animais doentes, lesionados ou com alterações comportamentais.Coberto em termos gerais (inspeção diária; sem diferenciação de frequência para animais vulneráveis). | 
-al. (c) — Saúde e higiene (2/2)Prevenção via maneio, manuseamentoe reprodução adequados | Prevenção de doenças, lesões e dor, nomeadamente através de práticas de maneio, manuseamento e reprodução adequadas.(al. (c) do art.º 6.º) | Art.º 12.º, n.º 1, al. b) — proibição de práticas que causem sofrimento, dano, stresse ou angústia.Art.º 52.º, n.ºs 3 e 5 — maneio feito de forma a não causar dores, sofrimento ou distúrbios desnecessários; meios de contenção não devem causar ferimentos, dores ou angústia.Art.º 70.º (normas reprodutivas) — limitações à reprodução para proteção da saúde.Coberto. | Art.º 5.º, n.º 3, al. c) — proibição de usar equipamentos de maneio, contenção ou treino que causem sofrimento desnecessário ou lesões.Art.º 47.º, n.ºs 4 e 5 — manuseamento feito de forma a não causar dores, sofrimento ou distúrbios desnecessários; meios de contenção não devem causar ferimentos, dores ou angústia.Art.º 8.º, n.º 1 e 2 — reprodução planeada e parâmetros reprodutivos.Coberto. | 
-al. (d) — Comportamento (1/2)Expressão de comportamentos da espéciee sociais não nocivos | Os cães e gatos são mantidos num ambiente que lhes permite exibir comportamentos específicos da espécie e comportamentos sociais não nocivos.(al. (d) do art.º 6.º) | Art.º 7.º, n.º 1, al. d) — direito de expressar padrões normais de comportamento.Art.º 10.º, n.º 1, al. a), iv) — espaço e enriquecimento ambiental adequados para a expressão dos comportamentos naturais.Art.º 10.º, n.º 1, al. a), vi) — contato social adequado à espécie, de acordo com a idade e atividade.Art.º 47.º, n.º 4 — enriquecimento ambiental complexo e estimulante com materiais e equipamento que estimulem a expressão do repertório de comportamentos naturais.Coberto. | Art.º 5.º, n.º 1 — condições de detenção que salvaguardem parâmetros de bem-estar.Art.º 13.º, n.º 5 — instalações equipadas com materiais e equipamento que estimulem a expressão dos comportamentos naturais (substrato, cama, ninhos, ramos, buracos, locais para banhos).Parcialmente coberto (enriquecimento ambiental para comportamentos naturais; sem referência explícita a comportamentos sociais não nocivos). | 
-al. (d) — Comportamento (2/2)Relação positiva com os seres humanos | Os cães e gatos são mantidos num ambiente que lhes permite estabelecer uma relação positiva com os seres humanos.(al. (d) do art.º 6.º) | Art.º 10.º, n.º 1, al. c) — dever de educar o animal com recurso a métodos de reforço positivo visando a sua vinculação e integração positivas no espaço familiar e no meio ambiente.Art.º 52.º, n.º 4 — interações do pessoal técnico com os animais devem ser positivas, regulares, previsíveis e não forçadas.Coberto. | Art.º 7.º, n.º 1 — dever de promover o treino dos cães com vista à socialização e obediência.Art.º 7.º, n.º 2 — treino de acordo com boas práticas.Parcialmente coberto (apenas cães; sem referência explícita a relação positiva com os seres humanos como fim autónomo). | 
-al. (e) — Estado mental (1/4)Prevenir/reduzir estímulos negativos(duração e intensidade) | Os cães e gatos são mantidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo estímulos negativos em duração e intensidade.(al. (e) do art.º 6.º) | Art.º 7.º, n.º 1, al. e) — proibição de situações que provoquem stresse, medo ou ansiedade injustificados.Art.º 12.º, n.º 1, al. b) — proibição de práticas que causem sofrimento, dano, stresse ou angústia.Parcialmente coberto (abordagem proibitiva; não preventiva). | Art.º 5.º, n.º 3 — proibição de violência e sofrimento.Sem referência explícita à gestão ativa de estímulos negativos. | 
-al. (e) — Estado mental (2/4)Maximizar estímulos positivos(duração e intensidade) | Os cães e gatos são mantidos de forma a maximizar oportunidades para estímulos positivos em duração e intensidade.(al. (e) do art.º 6.º) | Art.º 10.º, n.º 1, al. a), i) — dever de proporcionar atenção, supervisão, controlo, exercício físico e estímulo mental.Art.º 47.º, n.ºs 6 e 7 — acesso diário a área de exercício (mínimo 2×30 min); equipamento de enriquecimento ambiental e agilidade.Parcialmente coberto. | Art.º 13.º, n.º 5 — materiais e equipamento que estimulem a expressão dos comportamentos naturais.Sem norma positiva explícita sobre maximização de estímulos positivos. | 
-al. (e) — Estado mental (3/4)Prevenir comportamentos repetitivos anormaisou indicativos de bem-estar negativo | Os cães e gatos são mantidos de forma a prevenir o desenvolvimento de comportamentos repetitivos anormais ou outros comportamentos indicativos de bem-estar negativo.(al. (e) do art.º 6.º) | Não regulado explicitamente como norma autónoma.(O art.º 7.º, n.º 1, al. d) e e) e o art.º 47.º do @rgbeac indiretamente impõem condições que previnem o seu aparecimento.) | Não regulado explicitamente. | 
-al. (e) — Estado mental (4/4)Necessidades individuais do animal(als. (a) a (d)) | Os cães e gatos são mantidos tendo em conta as necessidades individuais do animal nos domínios referidos nas alíneas (a) a (d).(al. (e) do art.º 6.º) | Art.º 10.º, n.º 1, al. a) — bem-estar assegurado "de acordo com a sua espécie, raça, idade e necessidades físicas e etológicas".Art.º 48.º, n.º 2 — fatores ambientais adequados às necessidades específicas de animais em fase reprodutiva, recém-nascidos ou doentes.Parcialmente coberto (necessidades da espécie/raça/idade/fase fisiológica; não explicitamente individuais). | Art.º 4.º — necessidades básicas de bem-estar (sem referência à individualidade do animal).Art.º 14.º, n.º 2 — fatores ambientais adequados às necessidades específicas de animais em fase reprodutiva, recém-nascidos ou doentes.Parcialmente coberto. | 
-Critério / Determinação do Regulamento | Regulamento (UE) 2023/0447(texto PT-PT) | @rgbeac(proposta jun. 2025) | @codigo(proposta DL n.º 214/2013) | 
-n.º 1 — Responsabilidade geralBem-estar dos animais;minimizar riscos | Os operadores são responsáveis pelo bem-estar dos cães e gatos detidos nos estabelecimentos sob a sua responsabilidade e controlo, devendo minimizar quaisquer riscos para o bem-estar desses animais.(n.º 1 do art.º 7.º) | Art.º 9.º, n.º 1 — dever geral de todos os cidadãos de notificar infrações.Art.º 10.º, n.º 1 — obrigações especiais dos detentores: assegurar bem-estar.Sem distinção entre detentor doméstico e operador de estabelecimento comercial.Parcialmente coberto. | Art.º 4.º — detenção responsável: cabe aos detentores assegurar as necessidades básicas de bem-estar e salvaguardar a saúde.Sem atribuição explícita de responsabilidade ao "operador" como sujeito autónomo de estabelecimento.Parcialmente coberto. | 
-n.º 2 — Famílias de acolhimento (1/2)Responsabilidade do operador;informação sobre bem-estar e necessidades individuais | No caso das famílias de acolhimento, a responsabilidade incumbe ao operador em cujo nome os cães ou gatos são detidos. O operador presta à família informações adequadas sobre as obrigações de bem-estar e as necessidades individuais dos animais.(n.º 2 do art.º 7.º) | Art.º 4.º — define "Família de acolhimento temporário" como detentor transitório (45 dias, extensível).Art.º 101.º, n.ºs 3 e 4 — contrato escrito entre titular e família; registo no SIAC.Art.º 101.º, n.º 5 — destino do animal é da responsabilidade do titular.Parcialmente coberto (responsabilidade no titular; mas não se fixa o dever de informação ao acolhedor sobre bem-estar e necessidades individuais). | Art.º 9.º — define abandono; não prevê o conceito de família de acolhimento.Não coberto. | 
-n.º 2 — Famílias de acolhimento (2/2)Máx. 5 animais ou 1 ninhada(com/sem mãe) por família | Os operadores não colocam mais do que um total combinado de cinco cães ou gatos ou uma ninhada, com ou sem a mãe, numa família de acolhimento em qualquer momento.(n.º 2 do art.º 7.º) | Art.º 101.º — acolhimento temporário: sem fixação de limite numérico de animais por família.Não coberto. | Não regulado. | 
-n.º 3 — Derrogação (Estados-Membros)Maior número autorizadose espaço e cuidadores suficientes | O Estado-Membro pode autorizar maior número de cães, gatos ou ninhadas na família de acolhimento, desde que as instalações disponham de espaço suficiente (incluindo exterior) e o número de cuidadores seja suficiente.(n.º 3 do art.º 7.º) | Não regulado. | Não regulado. | 
-n.º 4 — Proibição de crueldade e maus-tratosInclui participaçãoem atividades de crueldade | Os operadores não sujeitam qualquer cão ou gato a crueldade, abusos ou maus-tratos, incluindo fazendo-os participar em atividades suscetíveis de resultar em crueldade, abusos ou maus-tratos.(n.º 4 do art.º 7.º) | Art.º 12.º, n.º 1, al. a) — proibição de causar a morte em violação das normas.Art.º 12.º, n.º 1, al. b) — proibição de práticas que causem sofrimento, dano, stresse ou angústia.Art.º 12.º, n.º 1, al. t) — proibição de utilização em eventos que envolvam crueldade, maus-tratos, sofrimento ou morte.Coberto. | Art.º 5.º, n.º 3 — proibição de violência: atos que infligem, sem necessidade, morte, sofrimento, abuso ou lesões a um animal.Art.º 5.º, n.º 4 — proibição de fins didáticos e lúdicos com dor ou sofrimentos consideráveis.Coberto. | 
-n.º 5 — Proibição de abandono | Os operadores não abandonam os cães ou gatos criados ou detidos por eles.(n.º 5 do art.º 7.º) | Art.º 12.º, n.º 1, al. e) — proibição expressa de abandono.Art.º 9.º, n.º 1 — dever de notificação de infrações (inclui abandono).Coberto. | Art.º 9.º — define abandono; não estabelece proibição autónoma expressa (proibição implícita pela definição).Parcialmente coberto. | 
-n.º 6 — Realojamento ao cessar atividadeAdoção ou transferênciapara outros operadores/adquirentes | Antes de os operadores cessarem as atividades num estabelecimento, asseguram que os cães ou gatos aí detidos são realojados, seja assumindo eles próprios a propriedade de animal de companhia, seja transferindo a responsabilidade para outros operadores ou adquirentes.(n.º 6 do art.º 7.º) | Art.º 101.º, n.º 5 — destino do animal é da responsabilidade do titular; mas esta norma aplica-se ao acolhimento temporário, não ao encerramento de estabelecimento.Não coberto (para encerramento de estabelecimento comercial). | Não regulado. | 
-n.º 7 — Cuidadores suficientes e competentes(competências do art.º 12.º) | Os operadores asseguram que os cães e gatos são manuseados por um número suficiente de cuidadores de animais para satisfazer as necessidades de bem-estar, e que esses cuidadores possuem as competências exigidas no artigo 12.º.(n.º 7 do art.º 7.º) | Art.º 52.º, n.º 1 — observação diária dos animais e maneio assegurados por pessoal técnico com formação teórica e prática específica certificada pela DGAV e em número adequado à quantidade e espécies animais alojados.Parcialmente coberto (número adequado e formação exigidos; sem remissão para catálogo de competências específico equivalente ao art.º 12.º do Regulamento). | Art.º 47.º, n.º 1 — observação diária dos animais e maneio assegurados por pessoal com aptidão para o efeito e em número adequado à quantidade e espécies animais.Art.º 47.º, n.º 2 — maneio por pessoal com experiência ou formação adequada, sob orientação de médico veterinário.Parcialmente coberto (número adequado e formação exigidos; sem catálogo de competências específico equivalente ao art.º 12.º do Regulamento). | 
-n.º 8 — Monitorização de indicadoresComportamento e aparência física;ações baseadas em resultados | Os operadores asseguram o bem-estar dos cães ou gatos monitorizando indicadores baseados nos animais relativos ao comportamento e à aparência física, e adotando ações com base nos resultados desse monitoramento.A Comissão adotará atos delegados que estabelecerão os indicadores e os métodos de medição.(n.ºs 8 e 9 do art.º 7.º) | Art.º 10.º, n.º 1, al. b) — dever de vigiar o animal de modo a evitar que cause danos (obrigação de vigilância; não equivale a monitorização de indicadores de bem-estar).Art.º 52.º, n.º 2 — inspeção dos animais no início e final do dia e a cada quatro horas; primeiros cuidados imediatos.Parcialmente coberto (periodicidade de inspeção regulada; sem sistema formal de indicadores baseados nos animais nem obrigação de ação estruturada com base nos resultados). | Art.º 47.º, n.º 3 — inspeção diária de todos os animais; primeiros cuidados imediatos a doentes, lesionados ou com alterações comportamentais.Parcialmente coberto (inspeção diária; sem sistema formal de indicadores de bem-estar nem atos delegados equivalentes). |</t>
+          <t>Necessidade de: (1) criar o conceito de 'família de acolhimento' como extensão da atividade do operador; (2) fixar limite numérico de animais por família (máximo 5, ou 1 ninhada com mãe); (3) atribuir responsabilidade jurídica ao operador, não à família de acolhimento.</t>
         </is>
       </c>
       <c r="O8" s="11" t="inlineStr">
@@ -1445,24 +1433,16 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
-2. Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem características de conformação excessivas que acarretem um elevado risco de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por características de conformação excessivas, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem uma característica de conformação excessiva.
-3. A Comissão tem competência para adotar atos delegados em conformidade com o artigo 28.º que complementem este Regulamento, definindo:
-(a) características dos genótipos a que se refere o n.º 1 que devem ser excluídos da reprodução, e os métodos para a sua avaliação e requisitos de manutenção de registos;
-(b) características de conformação excessivas a que se refere o n.º 2 do presente artigo que devem ser excluídos da reprodução, os métodos para a sua avaliação e requisitos de manutenção de registos.
-4. Ao adotar esses atos delegados, a Comissão tem em conta os pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos (EFSA), bem como os impactos sociais e económicos desses atos delegados.
-5. Os atos delegados relativos aos traços conformacionais excessivos devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
-6. São proibidos na gestão da reprodução de cães e gatos:
-(a) o cruzamento entre progenitores e descendentes, entre irmãos, entre meios-irmãos ou entre avós e netos, exceto com aprovação da autoridade competente por razão de necessidade específica de preservação de raças locais com reserva genética limitada;
-(b) o cruzamento para produção de híbridos.
-@regulamento — Tradução PT-PT · ANEXO I, Ponto 3 do Regulamento 2023/0447
-1.1 As gatas só devem ser utilizadas para reprodução se tiverem, pelo menos, 10 meses de idade.
-2.2 As cadelas só devem ser utilizadas para reprodução a partir do seu segundo estro.
-3.3 Uma cadela ou gata não deve ter mais de 3 ninhadas num período de 2 anos.
-4.4 No caso de cadelas e gatas que tenham tido 3 ninhadas num período de 2 anos, incluindo nado-mortos, deve ser respeitado um período de recuperação de, pelo menos, 1 ano.
-5.5 Qualquer cadela ou gata que tenha sido submetida a duas cesarianas não pode ser utilizada para reprodução.
-6.6 Antes de qualquer cadela com 8 ou mais anos de idade e de qualquer gata com 6 ou mais anos de idade serem utilizadas para reprodução, devem ser submetidas a um exame físico por um médico veterinário que confirme, por escrito, que, à data do exame, não existem contraindicações para a gestação.
-O operador deve conservar a confirmação escrita referida no ponto 3.4.b por um período de, pelo menos, 3 anos.</t>
+          <t>1.	Os operadores de estabelecimentos de criação asseguram que as suas estratégias de reprodução minimizem o risco de produção de cães ou gatos com genótipos associados a efeitos prejudiciais para a saúde e bem-estar desses animais.
+2.	Os operadores de estabelecimentos de criação não podem utilizar, para fins de reprodução, cães ou gatos com características de conformação extremas que acarretem um elevado risco de efeitos prejudiciais para o bem-estar desses cães ou gatos ou da sua descendência. Antes de selecionar um cão ou gato que possa ter uma característica de conformação extrema para a reprodução, o operador consulta um médico veterinário ou uma pessoa qualificada independente que atue sob a responsabilidade de um médico veterinário. Tal médico veterinário ou pessoa qualificada independente avalia se o cão ou gato tem uma característica de conformação extrema.
+3.	A Comissão fica habilitada a adotar atos delegados nos termos do artigo 28.º que completem o presente regulamento, definindo:
+a)	As características dos genótipos a que se refere o n.º 1 do presente artigo que devem ser excluídas da reprodução, bem como os métodos para a sua avaliação e os requisitos em matéria de manutenção de registos;
+b)	As características de conformação extremas a que se refere o n.º 2 do presente artigo que devem ser excluídas da reprodução, os métodos para a sua avaliação e os requisitos em matéria de conservação de registos.
+Ao adotar esses atos delegados, a Comissão toma em consideração o parecer científico da Autoridade Europeia para a Segurança dos Alimentos (EFSA, do inglês European Food Safety Authority), bem como quaisquer impactos sociais e económicos dos referidos atos delegados.
+Os atos delegados relativos às características de conformação excessivas devem ser adotados até 30 de junho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 30 de junho de 2036.
+4.	No contexto da gestão da reprodução de cães e gatos, são proibidas as seguintes práticas:
+a)	Reprodução entre progenitores e descendência, entre irmãos, entre meios-irmãos ou entre avós e netos, salvo aprovação pela autoridade competente com base numa necessidade específica de preservação de raças locais com património genético limitado;
+b)	Reprodução para produção de híbridos.</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1592,50 +1572,7 @@
 (ii) estabelecer máximo imperativo de 3 ninhadas em 2 anos (sem exceções veterinárias); 
 (iii) exigir período de recuperação 1 ano após atingir limite;
 (iv) proibir uso após 2 cesarianas; 
-(v) exigir avaliação veterinária escrita para cadelas ≥8 anos e gatas ≥6 anos.
-Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
-Cadelas (fêmeas canídeos) | A partir do 2.º estro(Anexo I, n.º 2.2) | Raças pequeno/médio porte: 3.º cioRaças grande porte: 2 anos(Art.º 8.º, n.º 2, al. a) + Anexo I) | 18 meses(Art.º 70.º, n.º 2) | Regulamento impõe-se
-Gatas (fêmeas felídeos) | A partir dos 10 meses(Anexo I, n.º 1.1) | 1 ano(Anexo I) | 12 meses(Art.º 70.º, n.º 3) | 1 ano
-Cães (machos canídeos) | Não fixado(Art.º 8.º não estabelece limite mínimo para machos) | Raças pequeno/médio porte: 1,5 anosRaças grande porte: 2 anos(Anexo I) | 12 meses(Art.º 70.º, n.º 4) | Raças pequeno/médio porte: 1,5 anosRaças grande porte: 2 anosv
-Gatos (machos felídeos) | Não fixado | 1 ano(Anexo I) | 12 meses(Art.º 70.º, n.º 4) | 1 ano
-Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
-Cadelas | Exame veterinário escrito obrigatório a partir dos 8 anos (não proibição)(Anexo I, n.º 3.6) | 8 anos; ou 5 anos se for a 1.ª gestação(Anexo I) | 6 anos(Art.º 70.º, n.º 2) | Código, eventualmente com adenda do Regulamentohttps://food.ec.europa.eu/system/files/2020-11/aw_platform_plat-conc_guide_dog-breeding.pdf
-Gatas | Exame veterinário escrito obrigatório a partir dos 6 anos (não proibição)(Anexo I, n.º 3.6) | 12 anos(Anexo I) | 6 anos(Art.º 70.º, n.º 3) | RGBEAC, eventualmente com adenda do Regulamentohttps://food.ec.europa.eu/system/files/2020-11/aw_platform_plat-conc_guide_cat-breeding.pdf
-Cães machos | Não fixado | 12 anos, ou mais se o estatuto sanitário o permitir(Anexo I) | 7 anos(Art.º 70.º, n.º 4) | Debatível. Talvez mais bem definido em Portaria que facilite adaptações.Maior risco de patologias e transmissão de defeitos com o avançar da idade, com queda mais marcada em cães acima de 7–9 anos. Mas esperança média de vida tem aumentado, o risco de patologia reprodutiva aumenta e o risco de abandono potencialmente pode aumentar com propostas mais restritivas
-Gatos machos | Não fixado | 12 anos(Anexo I) | 7 anos(Art.º 70.º, n.º 4) | Ver supra
-Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
-N.º máximo de ninhadas por período | Máx. 3 ninhadas em 2 anos (cadelas e gatas)(Anexo I, n.º 3.3) | Cadelas: 1 ninhada/ano; máx. 4–6 na vidaGatas: 1 ninhada/ano (máx. 3 em 2 anos, com aprovação MV); máx. 8–10 na vida(Anexo I) | Máx. 4 ninhadas na vida reprodutiva(Art.º 70.º, n.ºs 2 e 3) | Definir um número entre 4 e 6. Os documentos supra indicam limites de 4 ninhadas na vida para ambas.
-Intervalo mínimo entre ninhadas | Período de recuperação de, pelo menos, 1 ano após atingir o limite de 3 ninhadas em 2 anos(Anexo I, n.º 4.4) | Cadelas: 1 ciclo reprodutivoGatas: 3–6 meses(Anexo I) | Mínimo de 12 meses entre cada ninhada (cadelas e gatas)(Art.º 70.º, n.ºs 2 e 3) | Rgbeac
-Cios sucessivos (fêmeas) | Não regulado explicitamente | Proibido acasalamento em cios sucessivos(Art.º 8.º, n.º 2, al. a)) | Não regulado explicitamente (intervalo de 12 meses implica proibição) | “É proibido o acasalamento em cios sucessivos, devendo ser assegurando um intervalo mínimo de X meses entre as ninhadas…”
-Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
-Após 1.ª cesariana | Não regulado | Não regulado | Exige atestado do MV assistente confirmando ausência de risco(Art.º 70.º, n.º 10) | ?
-Após 2 cesarianas | Proibição de usar para reprodução(Anexo I, Pt. 3, n.º 5.5) | Não regulado explicitamente | Proibição de usar para reprodução(Art.º 70.º, n.º 12) | Proibição conforme Rregulamento
-Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
-Cruzamentos consanguíneos (pai/filho, irmãos, avós/netos) | Proibidos, salvo autorização da autoridade competente para preservação de raças locais com reserva genética limitada(Art.º 8.º, n.º 6, al. a)) | Não regulado explicitamente;  Exclui animais com defeitos genéticos e malformações específicas(Art.º 8.º, n.º 2, al. c)) | Sujeitos a portaria (coeficiente de consanguinidade e limites definidos por portaria)(Art.º 70.º, n.º 7) | Regulamento
-Produção de híbridos (cruzamento interespecífico/inter-racial para fins comerciais) | Proibida(Art.º 8.º, n.º 6, al. b)) | Proibida, exceto cruzamentos autorizados para melhoramento de raça ou investigação, ou cruzamentos acidentais sem fins comerciais Acresce exceção para cruzamentos de raças, em particular caninas, que tenham ocorrido acidentalmente e não tenham fins comerciais(Art.º 8.º, n.º 3) | Não regulado explicitamente | Regulamento + ponderar excluir cruzamentos acidentais
-Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
-Traços conformacionais excessivos/Conformações extremas | Proibida a reprodução;  Exige consulta prévia a MV; Atos delegados até julho de 2030 definirão critérios(Art.º 8.º, n.ºs 2 e 3, al. b)) | Excluídos da reprodução animais com defeitos genéticos e malformações específicas (ex: displasia da anca, rim poliquístico)(Art.º 8.º, n.º 2, al. c)) | Reprodução condicionada a parecer do MV que ateste ausência de efeito prejudicial com base em genótipo/fenótipo;  Restrição de reprodução de raças específicas por portaria(Art.º 70.º, n.ºs 8 e 9) | Regulamento, com a disposição do rgbeac até haver derrogação?
-Testes genéticos e rastreios de saúde | Atos delegados da Comissão definirão critérios (até julho de 2036 para genótipos)(Art.º 8.º, n.ºs 1 e 3, al. a)) | Excluídos animais com defeitos genéticos específicos (rim poliquístico, displasia, etc.)(Art.º 8.º, n.º 2, al. c)) | Obrigatórios; critérios definidos por portaria específicos para cada raça(Art.º 70.º, n.º 7) | 
-Porte semelhante dos progenitores (prevenção de distócia) | Não regulado explicitamente | Obrigatório(Art.º 8.º, n.º 2, al. b)) | Não regulado explicitamente | Código
-Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
-Inseminação artificial (IA) | Não regulado | Não regulado | Restrita a situações excecionais, previstas em portaria(Art.º 70.º, n.º 11) | rgbeac
-Electroejaculação | Não regulado | Não regulado | Proibida(Art.º 70.º, n.º 12) | rgbeac
-Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
-Critérios comportamentais para seleção de reprodutores | Não regulado | Excluídos animais com alterações comportamentais(Art.º 8.º, n.º 2, al. c)) | Obrigatório temperamento amistoso e confiante; proibida reprodução de animais perigosos ou com comportamento agressivo ou excessivamente tímido(Art.º 70.º, n.º 6) | Combinaria código e rgbeac
-Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
-Registo de reprodutores | Não regulado | Não regulado  | Inscrição obrigatória no SIAC como animal reprodutor(Art.º 70.º, n.º 6) | Rgbeac
-Obrigação de esterilização após fim da vida reprodutiva | Não regulado | Não regulado | Obrigação do detentor de esterilizar o animal e garantir o seu bem-estar até ao final da vida(Art.º 70.º, n.º 13) | Dúvida sobre a aplicabilidade da obrigação, mas a favor do rgbeac
-Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
-Cachorros — idade mínima de separação | 8 semanas (estabelecimentos de criação, abrigos e famílias de acolhimento)Derrogação por razões médicas com parecer escrito do MV(Anexo I, n.º 3.3) | Não regulado especificamente. Proibição de exposição em locais de venda até à 8ª semana (n.º 2, art. 23.º; e n.º 2, art. 82.º) | 10.ª semana de idade(com período de desmame gradual)(Art.º 70.º, n.º 5) | RGBEAC Mais restritivo
-Gatinhos — idade mínima de separação | Abrigos e famílias de acolhimento: 8 semanasEstabelecimentos de criação: 12 semanasDerrogação por razões médicas com parecer escrito do MV. O operador conserva o registo até ao último cachorro/gatinho da ninhada ser colocado no mercado(Anexo I, n.º 4.3) | Não regulado especificamente. Proibição de exposição em locais de venda até à 8ª semana (n.º 2, art. 23.º; e n.º 2, art. 82.º) | 12.ª semana de idade(com período de desmame gradual)(Art.º 70.º, n.º 5) | Regulamento = rgbeac
-Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
-Processo de desmame — duração e método | Introdução gradual de alimentos sólidos ao longo de um período não inferior a 7 dias(Anexo I, n.º 4.4) | Não regulado especificamente.Prevê programa de alimentação adequado à fase fisiológica — Art.º 8.º, n.º 2, al. a) por referência ao Anexo I) | «Período de desmame gradual» salvaguardado antes da separação(Art.º 70.º, n.º 5 — não especifica duração) | Regulamento + rgbeac
-Idade mínima para conclusão do desmame | Não antes das 6 semanas de idade (tanto para cachorros como para gatinhos)(Anexo I, n.º 4.4) | Não regulado explicitamente | Não regulado explicitamente | Regulamento
-Alimentação de cachorros/gatinhos não desmamados | Colostro nos primeiros 2 dias; depois leite da progenitora ou de cadela/gata lactante; se impossível, sucedâneo de leite específico para cachorros/gatinhos(Anexo I, n.º 2.2) | Não regulado especificamente. Descrito nas condições de alimentação e abeberamento: alimentação deve estar de acordo com fase de evolução fisiológica – idade, sexo, fêmeas prenhes ou em fase de lactação. (Art. 46º, n.º 1) | Não regulado especificamente. | Regulamento
-Monitorização do crescimento de não desmamados | Todos os cachorros/gatinhos não desmamados devem receber leite, sucedâneo ou combinação em quantidade suficiente para ganho de peso constante(Anexo I, n.º 3.3) | Não regulado | Não regulado | Regulamento
-Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
-Idade de início e tipo de socialização | A partir das 3 semanas de idade: oportunidades diárias e progressivas de contacto social com congéneres, seres humanos e, sempre que possível, outras espécies(Anexo I, n.º 1.1) | Não regulado especificamente na secção de reprodução(o @codigo exige enriquecimento ambiental — Art.º 13.º, n.º 5) | Todos os alojamentos de criação de cães e gatos devem dispor de um plano de socialização e enriquecimento ambiental(Art.º 52.º, n.º 7 do @rgbeac) | Regulamento + rgbeac
-Separação comportamento agressivo | Animais que representem ameaça ou causem stress excessivo devem ser mantidos separados(Anexo I, n.º 1.1) | Não regulado especificamente. As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar.(Art. 13.º, n.º 3) Artigo 83.º - As fêmeas prenhes, bem como as ninhadas em período de aleitamento, não podem ser mantidas nos locais de venda.   | Não regulado especificamente. 3 - As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar (Art.º 47.º, n.º 3) Artigo 76.º- As fêmeas prenhes, bem como as ninhadas em período de aleitamento, não podem ser mantidas nos locais de venda. | Regulamento + qq um</t>
+(v) exigir avaliação veterinária escrita para cadelas ≥8 anos e gatas ≥6 anos.</t>
         </is>
       </c>
       <c r="O9" s="11" t="inlineStr">
@@ -1674,18 +1611,18 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores devem notificar as autoridades competentes da sua atividade, fornecendo pelo menos as seguintes informações para cada um dos seus estabelecimentos:
-(a) o nome, morada e contactos do operador;
-(b) a localização do estabelecimento;
-(c) o tipo de estabelecimento: estabelecimento de criação, estabelecimento de venda, abrigo ou família de acolhimento;
-(d) as espécies e, para os estabelecimentos de criação, as raças dos cães ou gatos mantidos no estabelecimento;
-(e) a capacidade do estabelecimento, expressa no número máximo de cães e gatos que podem ser alojados no estabelecimento;
-(f) para os estabelecimentos de criação, o número estimado de ninhadas a colocar no mercado por ano.
-2. Os operadores devem notificar a autoridade competente de:
-(a) quaisquer alterações relativas às informações referidas no n.º 1;
-(b) quando aplicável, a data prevista de cessação das suas atividades, o mais tardar cinco dias úteis antes dessa data.
-3.	Os Estados-Membros devem utilizar as informações fornecidas em conformidade com o artigo 84.º do Regulamento (UE) 2016/429. Os operadores não são obrigados a notificar novamente as informações já apresentadas em conformidade com o artigo 84.º do Regulamento (UE) 2016/429.
-4.	A autoridade competente deve manter um registo dos estabelecimentos. A autoridade competente pode utilizar para esse efeito o registo previsto no artigo 101.º, n.º 1, alínea a), do Regulamento (UE) 2016/429.</t>
+          <t>1.	Os operadores ▌notificam as autoridades competentes da sua atividade, facultando pelo menos as seguintes informações para cada um dos seus estabelecimentos:
+a)	O nome, o endereço e dados de contacto do operador;
+b)	A localização do estabelecimento;
+c)	O tipo de estabelecimento: estabelecimento de criação, estabelecimento de venda, abrigo ou lar de acolhimento;
+d)	A espécie e, para os estabelecimentos de criação, as raças dos cães ou gatos detidos no estabelecimento;
+e)	A capacidade do estabelecimento, expressa em termos de número máximo de cães e gatos que podem ser detidos no estabelecimento;
+f)	No caso dos estabelecimentos de criação, o número estimado de ninhadas a colocar no mercado por ano.
+2.	Os operadores comunicam à autoridade competente:
+a)	Qualquer alteração relativa às informações referidas no n.º 1;
+b)	Se for o caso, a data prevista de cessação das suas atividades, o mais tardar cinco dias úteis antes dessa data;
+3.	Os Estados-Membros devem utilizar as informações facultadas em conformidade com o artigo 84.º do Regulamento (UE) 2016/429. Os operadores não são obrigados a notificar novamente as informações já comunicadas em conformidade com o referido artigo.
+4.	A autoridade competente deve manter um registo de estabelecimentos. A autoridade competente pode utilizar, para esse efeito, o registo criado nos termos do artigo 101.º, n.º 1, alínea a), do Regulamento (UE) 2016/429.</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1947,14 +1884,14 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores de estabelecimentos de criação que produzem ou pretendem produzir mais de cinco ninhadas por ano civil ou que mantêm mais do que um total combinado de cinco cadelas ou gatas em qualquer momento podem colocar cães ou gatos no mercado apenas após a aprovação do seu estabelecimento pela autoridade competente.
-2. A autoridade competente deve realizar inspeções no local para verificar que o estabelecimento atende aos requisitos do presente Regulamento. Os Estados-Membros podem permitir que tais inspeções sejam realizadas remotamente, desde que o meio de comunicação à distância utilizado forneça provas suficientes para a autoridade competente realizar inspeções fiáveis. A autoridade competente deve conceder certificados de aprovação apenas aos estabelecimentos de criação que cumprem os requisitos do presente Regulamento.
-3. A autoridade competente deve manter uma lista disponível ao público incluindo as seguintes informações para cada estabelecimento aprovado:
-(a) o nome, dados de contacto e, se disponível, o URL do site do estabelecimento;
-(b) a morada do estabelecimento;
-(c) o nome do operador;
-(d) a(s) espécie(s) e, se relevante, a(s) raça(s) relacionada(s) com as atividades do estabelecimento aprovadas;
-(e) o número de aprovação único atribuído ao estabelecimento pela autoridade competente e a data da aprovação e cessação de atividades.</t>
+          <t>1.	Os operadores de estabelecimentos de criação que produzam ou tencionem produzir mais de cinco ninhadas por ano civil, ou que, a qualquer momento, detenham um total combinado de mais de cinco cadelas ou gatas, só podem colocar cães ou gatos no mercado após aprovação do seu estabelecimento pela autoridade competente.
+2.	A autoridade competente efetua inspeções no local para verificar se o estabelecimento cumpre os requisitos do presente regulamento. Os Estados-Membros podem autorizar que estas inspeções sejam realizadas à distância, desde que o meio de comunicação à distância utilizado permita recolher provas suficientes para que a autoridade competente realize inspeções fiáveis. A autoridade competente só deve conceder certificados de aprovação a estabelecimentos de criação que cumpram os requisitos do presente regulamento.
+3.	A autoridade competente mantém uma lista acessível ao público que contenha as seguintes informações para cada estabelecimento aprovado:
+a)	O nome, os dados de contacto e, sempre que disponível, o URL do sítio Web do estabelecimento;
+b)	O endereço do estabelecimento;
+c)	O nome do operador;
+d)	As espécies e, sendo caso disso, as raças relacionadas com as atividades aprovadas do estabelecimento;
+e)	O número de aprovação único atribuído ao estabelecimento pela autoridade competente e a data de aprovação e de cessação das atividades.</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -2032,11 +1969,12 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores devem fornecer ao adquirente de um cão ou gato informação escrita necessária para lhe permitir assegurar o bem-estar do cão ou gato, incluindo informação sobre detenção responsável e sobre as necessidades específicas do cão ou gato em termos de alimentação, cuidados, saúde e alojamento, bem como informação sobre as suas necessidades comportamentais e historial de saúde.
-2. A informação escrita sobre o historial de saúde do cão ou gato referida no n.º 1 deve incluir pelo menos:
-(a) o estado de vacinação do cão ou gato;
-(b) quaisquer condições médicas ou predisposições a doenças, incluindo alergias, conhecidas pelo operador, e quaisquer resultados de testes de diagnóstico para o cão ou gato que estejam disponíveis para o operador.
-Caso a informação sobre o historial de saúde do cão ou gato esteja prevista num documento exigido nos termos do Regulamento (UE) 2016/429, o operador deve transmitir esse documento ao adquirente.</t>
+          <t>1.	▌Os operadores ▌facultam ao adquirente de um cão ou de um gato as informações escritas necessárias para permitir ao adquirente assegurar o bem‑estar do animal, incluindo informações sobre a propriedade responsável e sobre as necessidades específicas do animal em termos de alimentação, cuidados, saúde e alojamento, assim como informação a respeito das suas necessidades comportamentais e do seu historial clínico e sanitário.
+2.	As informações escritas sobre o historial clínico e sanitário do cão ou gato referidas no n.° 1 devem incluir, pelo menos:
+a)	A situação do animal em termos de vacinação;
+b)	Quaisquer problemas de saúde ou predisposição para doenças, incluindo alergias, que sejam do conhecimento do operador, e quaisquer resultados de testes de diagnóstico do cão ou gato que se encontrem à disposição do operador.
+Sempre que as informações sobre o historial clínico e sanitário do cão ou gato constarem de um documento exigido por força do Regulamento (UE) 2016/429, o operador deve transmitir esse documento ao adquirente.
+▌</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -2128,16 +2066,16 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>1. Os cuidadores de animais, com exceção dos voluntários em abrigos e dos estagiários que atuem sob a responsabilidade de um cuidador de animais competente, devem possuir as seguintes competências no que diz respeito aos cães e gatos que manuseiam:
-(a) compreensão do comportamento biológico dos animais e das respetivas necessidades fisiológicas e etológicas;​
-(b) capacidade para reconhecer as expressões dos animais, incluindo qualquer sinal de sofrimento, e para identificar e adotar as medidas de atenuação adequadas nesses casos;
-(c) capacidade para aplicar boas práticas de gestão animal, incluindo o condicionamento operante e o reforço positivo, para utilizar e manter o equipamento utilizado para os cães ou gatos sob o seu cuidado e para minimizar quaisquer riscos para o bem-estar desses cães ou gatos, prevenindo o seu sofrimento;
-(d) conhecimento das obrigações que lhes incumbem por força do presente regulamento.​
-2. As competências referidas no n.º 1 podem ser adquiridas através de ensino, formação ou experiência profissional. Só o ensino, a formação ou a experiência profissional documentada são tidos em conta para determinar se um cuidador de animais possui as competências referidas no n.º 1.​
-3. Os operadores asseguram que, em cada estabelecimento, pelo menos um cuidador de animais, que não seja voluntário nem estagiário, tenha concluído os cursos de formação a que se refere o artigo 22.º. Os operadores asseguram que esse cuidador de animais transmita os seus conhecimentos aos restantes cuidadores de animais do estabelecimento.
-4. A Comissão adota atos de execução que estabelecem requisitos mínimos relativos ao ensino formal, à formação ou à experiência profissional referidos no n.º 2 do presente artigo, necessários para determinar se um cuidador de animais possui as competências referidas no n.º 1, bem como relativos aos cursos de formação a que se refere o n.º 3.​
-O ato de execução relativo aos cursos de formação referidos no n.º 3 é adotado até … [3 anos a contar da data de entrada em vigor do presente regulamento].​
-Os referidos atos de execução são adotados pelo procedimento de exame a que se refere o artigo 29.º</t>
+          <t>1.	Os tratadores de animais, que não os voluntários em abrigos e os estagiários que atuem sob a responsabilidade de um tratador de animais competente, devem ter as seguintes competências no que diz respeito aos cães e gatos que manuseiam:
+a)	Compreensão do comportamento biológico dos animais e das suas necessidades fisiológicas e etológicas;
+b)	Capacidade para reconhecer as expressões dos animais, incluindo qualquer sinal de sofrimento, e para identificar e tomar as medidas de atenuação adequadas ▌nesses casos;
+c)	Capacidade para aplicar boas práticas de gestão animal, nomeadamente o condicionamento operante e o reforço positivo, para usar e manter o equipamento utilizado para os cães ou gatos sob o seu cuidado e para minimizar quaisquer riscos para o bem-estar desses cães ou gatos, prevenindo o seu sofrimento;
+d)	Conhecimento das obrigações que incumbem aos tratadores por força do presente regulamento.
+2.	As competências referidas no n.º 1 podem ser adquiridas através de ensino, formação ou experiência profissional. Para determinar se um tratador de animais tem as referidas competências apenas são tidos em conta o ensino, a formação ou a experiência profissional que se encontrem documentados.
+3.	Os operadores asseguram que pelo menos um tratador de animais do estabelecimento, que não seja um voluntário ou estagiário, tenha concluído os cursos de formação referidos no artigo 22.º Os operadores asseguram que esse tratador de animais partilhe os seus conhecimentos com os outros tratadores de animais do estabelecimento.
+4.	A Comissão adota atos de execução que estabeleçam requisitos mínimos relativos ao ensino formal, à formação ou à experiência profissional referidos no n.º 2 necessários para determinar se um tratador de animais tem as competências a que se refere o n.º 1 e relativos aos cursos de formação a que se refere o n.º 3.
+O ato de execução relativo aos cursos de formação a que se refere o n.º 3 é adotado até ... [três anos a contar da data de entrada em vigor do presente regulamento].
+Os referidos atos de execução são adotados pelo procedimento de exame a que se refere o artigo 29.º.</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2238,10 +2176,10 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores devem:
-(a) assegurar que os estabelecimentos sob a sua responsabilidade recebem uma visita de um médico veterinário no prazo de um ano a partir da data de aplicação do presente Regulamento ou no prazo de um ano após notificação de novo estabelecimento, com o objetivo de identificar e avaliar quaisquer fatores de risco para o bem-estar dos cães ou gatos e aconselhar o operador sobre medidas para resolver esses riscos; depois, as visitas do médico veterinário devem ocorrer quando apropriado, com base numa análise de risco pelas autoridades competentes; os Estados-Membros podem estabelecer que as visitas de aconselhamento de bem-estar sejam anuais;
-(b) manter registos dos resultados da visita do médico veterinário referida na alínea (a) e das ações de acompanhamento por um período mínimo de 4 anos, a partir da data da visita, e disponibilizá-los às autoridades competentes a pedido e ao médico veterinário que realiza visitas de aconselhamento subsequentes.
-2. Dentro de 24 meses a partir da data de entrada em vigor do presente Regulamento, a Comissão deve adotar atos delegados em conformidade com o artigo 28.º que complementem o presente artigo de forma a estabelecer critérios mínimos a serem avaliados durante a visita de aconselhamento de bem-estar.</t>
+          <t>1.	Os operadores ▌:
+a)	Asseguram que os estabelecimentos sob a sua responsabilidade recebam ▌uma visita de um médico veterinário, a fim de identificar e avaliar qualquer fator de risco para o bem‑estar dos cães ou gatos, assim como aconselhar o operador ▌sobre as medidas destinadas a dar resposta a esses riscos, inicialmente até ... [três anos após a data de entrada em vigor do presente regulamento] ou um ano a contar da notificação de um novo estabelecimento e, posteriormente, se for caso disso, com base numa análise do risco levada a cabo pelas autoridades competentes, ou anualmente, se os Estados-Membros assim o previrem no seu direito nacional;
+b)	Conservam um registo das conclusões da visita do médico veterinário a que se refere a alínea a) e das suas ações de acompanhamento durante ▌pelo menos quatro anos, a contar do dia da visita, e disponibilizar esse registo às autoridades competentes, mediante pedido, assim como aos médicos veterinários que fizerem as visitas de acompanhamento subsequentes.
+2.	Até... [24 meses a contar da data de entrada em vigor do presente regulamento], a Comissão adota atos delegados nos termos do artigo 28.º,que completem o presente artigo, prevendo os critérios mínimos a avaliar pelo médico veterinário durante a visita de aconselhamento para assegurar o bem‑estar.</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2350,18 +2288,18 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores devem assegurar que os cães ou gatos são alimentados em conformidade com os requisitos estabelecidos no ponto 1 do Anexo I.
-2. Os operadores devem assegurar que os cães ou gatos sejam alimentados e hidratados de forma adequada, fornecendo-lhes:
-a) água limpa e fresca, ad libitum;
-b) Alimentos para animais em quantidade e qualidade suficientes para satisfazer as necessidades fisiológicas, nutricionais e metabólicas dos cães e gatos, no âmbito de uma dieta adaptada à idade, raça, categoria, nível de atividade e estado reprodutivo dos cães ou gatos, com o objetivo global de alcançar manter um bom estado saúde;
-c) alimento livre de substâncias que possam causar sofrimento;
-d) alimento de forma a evitar mudanças abruptas e assegurar um sistema gastrointestinal em bom funcionamento, em particular durante a fase de desmame.
-3. Os operadores devem assegurar que as instalações de alimentação e abeberamento sejam mantidas limpas e sejam construídas e instaladas de forma a:
-a) proporcionar acesso igualitário a quantidades adequadas de alimento e água para todos os cães ou gatos e minimizar a competição entre eles;
-b) minimizar derramamentos e evitar a contaminação do alimento e da água com contaminantes físicos, químicos ou biológicos prejudiciais;
-c) evitar ferimentos, afogamento ou outro dano aos cães ou gatos;
-d) ser facilmente limpas e desinfetadas para evitar a propagação de doenças.
-4.	Quando aconselhado por escrito por um médico veterinário, os operadores podem ajustar as frequências de alimentação e hidratação para um cão ou gato individual. Os operadores devem manter um registo do conselho durante toda a sua duração, conforme aconselhado pelo médico veterinário.</t>
+          <t>1.	Os operadores ▌asseguram que os cães e gatos sejam alimentados em conformidade com os requisitos estabelecidos no ponto 1 do anexo I▌.
+2.	Além disso, os operadores ▌asseguram que os cães e gatos sejam alimentados e abeberados de forma adequada, fornecendo-lhes:
+a)	Água limpa e fresca, ad libitum;
+b)	Alimentos para animais em quantidade e qualidade suficientes para satisfazer as necessidades fisiológicas, nutricionais e metabólicas ▌dos cães e gatos, no âmbito de uma dieta adaptada à idade, raça, categoria, nível de atividade, ▌estado de saúde e reprodutivo dos cães ou gatos, com o objetivo geral de atingir e manter a sua boa saúde;
+c)	Alimentos para animais isentos de substâncias suscetíveis de causar sofrimento;
+d)	Alimentos para animais proporcionados de forma que evite alterações bruscas e assegure o bom funcionamento do sistema gastrointestinal, em especial durante a fase de desmame.
+3.	Os operadores ▌asseguram que as instalações de alimentação e de abeberamento sejam mantidas limpas e construídas e instaladas de modo a:
+a)	Proporcionarem igualdade de acesso a quantidades adequadas de alimentos para animais e água a todos os cães ou gatos e minimizarem a disputa entre eles;
+b)	Minimizarem os derrames e evitarem a contaminação dos alimentos para animais e da água com contaminantes físicos, químicos ou biológicos;
+c)	Prevenirem que os cães ou gatos sofram lesões, afogamento ou outros danos;
+d)	Serem facilmente limpas e desinfetadas para prevenir a propagação de doenças.
+4.	Se um médico veterinário os aconselhar por escrito nesse sentido, os operadores podem ajustar as frequências de alimentação e de abeberamento de um determinado cão ou gato. Os operadores mantêm um registo desses conselhos recebidos por escrito ao longo de toda a duração dos referidos ajustamentos.</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2480,24 +2418,25 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores de estabelecimentos de criação e venda devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2 do Anexo I. Os operadores de abrigos devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2.2 do Anexo I.
-2. Os operadores devem assegurar que:
-a) os estabelecimentos onde os cães ou gatos são detidos e o equipamento neles utilizado sejam adequados aos tipos e ao número de cães ou gatos, e permitam o acesso necessário e a inspeção exaustiva de todos os cães ou gatos;​
-b) todos os componentes do edifício do estabelecimento, incluindo o pavimento e o telhado, e as divisões de espaço, bem como o equipamento utilizado para cães ou gatos, sejam construídos e mantidos adequadamente, de modo a garantir que não representem quaisquer riscos para o bem-estar dos cães ou gatos;​
-c) todos os componentes do edifício do estabelecimento, incluindo o pavimento e as divisões de espaço, bem como o equipamento utilizado para cães ou gatos, sejam mantidos limpos, de modo a garantir que não representem quaisquer riscos para o bem-estar dos cães ou gatos;​
-d) nos estabelecimentos de criação e venda onde os cães ou gatos são detidos em espaços interiores, os níveis de poeira, a temperatura, a humidade relativa do ar e as concentrações de gases não sejam prejudiciais para os cães ou gatos e a ventilação seja suficiente para evitar o sobreaquecimento;​
-e) os cães ou gatos disponham de espaço suficiente para circular livremente e exprimir comportamentos específicos da espécie de acordo com as suas necessidades, com a possibilidade de se retirarem e descansarem;​
-f) os cães ou gatos disponham de locais de repouso limpos, confortáveis e secos, suficientemente amplos e numerosos para garantir que todos eles possam deitar-se e descansar em posição natural ao mesmo tempo;​
-g) existam estruturas e medidas adequadas para os cães ou gatos detidos ao ar livre, de modo a protegê-los de condições climáticas adversas, incluindo para prevenir stress térmico, queimaduras solares e queimaduras pelo frio.
-Os operadores não devem manter cães ou gatos em contentores.
-3. Contudo, contentores podem ser utilizados para o transporte, o isolamento de curto prazo de cães ou gatos individuais e durante a participação em espetáculos, exposições e concursos, para cachorros ou gatinhos com capacidade de termorregulação reduzida ou cachorros ou gatinhos acompanhados das respetivas mães, desde que seja minimizado o stress e evitado o sofrimento e os cães e gatos possam estar de pé e deitar-se numa posição natural.
-4. Os operadores não devem manter cães com mais de 8 semanas exclusivamente no interior. Tais cães devem ter acesso diário a uma área ao ar livre, ou ser passeados diariamente, para permitir exercício, exploração e socialização. A duração do acesso diário a uma área ao ar livre ou passeio deve ser mínimo uma hora no total. O operador só pode desviar-se destes requisitos com base no parecer escrito de um veterinário.
-5. Quando gatos são mantidos em gatis, os operadores devem desenhar e construir compartimentos individuais para permitir aos gatos mover-se livremente e expressar o seu comportamento natural.
-6. Os operadores dos estabelecimentos de criação e venda devem garantir que, nas áreas interiores onde os cães e gatos são detidos, seja mantida uma zona termicamente neutra adequada que tenha em conta o tipo de pelagem, a idade, o tamanho, a raça e a saúde deles.
-7. Os operadores dos estabelecimentos de criação e venda devem, quando necessário, utilizar sistemas de aquecimento ou arrefecimento nos recintos interiores dos seus estabelecimentos para manter uma boa qualidade do ar, uma temperatura adequada e eliminar a humidade excessiva.
-8. Os operadores devem garantir que os cães ou gatos sejam expostos à luz e possam permanecer no escuro durante períodos suficientes e ininterruptos, a fim de manter um ritmo circadiano normal.
-Para efeitos do primeiro parágrafo, 'luz' significa luz natural, complementada, quando necessário, devido às condições climáticas e posição geográfica de um Estado-Membro, por luz artificial.
-9. Os n.ºs 2 (a), (b), (c), (f) e (g), 6, 7 e 8 não se aplicam nem aos cães de guarda de gado, nem aos cães de pastoreio, durante os períodos em que tais cães são utilizados para guarda ou pastoreio no contexto da transumância sazonal a pé. A alínea (f) do ponto 2 não se aplica aos cães de guarda de gado durante os períodos em que tais cães são utilizados para fins de formação.</t>
+          <t>1.	Os operadores de estabelecimentos de criação e estabelecimentos de venda asseguram que os cães e gatos sejam alojados em conformidade com o ponto 2 do anexo I. Os operadores de abrigos asseguram que os cães e gatos sejam alojados em conformidade com o ponto 2.2. do anexo I.
+2.	Os operadores ▌asseguram que:
+a)	Os estabelecimentos onde cães ou gatos são detidos e o equipamento neles utilizado sejam adequados aos tipos e ao número de cães ou gatos, e permitam o acesso necessário a todos os cães e gatos e uma inspeção exaustiva dos mesmos;
+b)	Todos os componentes do edifício do estabelecimento, incluindo o pavimento e o telhado, ▌e as divisórias, bem como o equipamento utilizado para cães ou gatos, sejam construídos e mantidos de forma adequada, ▌a fim de garantir que não representam qualquer risco para o bem-estar dos cães ou gatos;
+c)	Todos os componentes do edifício do estabelecimento, incluindo o pavimento, e as divisórias, bem como o equipamento utilizado para cães ou gatos, sejam mantidos limpos a fim de garantir que não representam qualquer risco para o bem-estar dos cães ou gatos;
+d)	▌Em estabelecimentos de criação e estabelecimentos de venda em que os cães ou gatos sejam detidos em espaços interiores, os níveis de poeiras, a temperatura e a humidade relativa do ar e as concentrações de gases ▌não sejam prejudiciais para os cães ou gatos e que a ventilação seja suficiente para evitar o sobreaquecimento ▌;
+e)	Os cães ou os gatos disponham de espaço suficiente para poderem circular livremente e expressar comportamentos específicos da espécie de acordo com as suas necessidades, tendo a possibilidade de se retirarem e de descansarem;
+f)	Os cães ou gatos disponham de zonas de descanso limpas, confortáveis e secas, suficientemente grandes e numerosas para garantir que todos podem deitar-se e descansar ao mesmo tempo numa posição natural;
+g)	Estejam previstas estruturas e medidas adequadas para que cães ou gatos mantidos em espaços exteriores estejam protegidos de condições climáticas adversas, incluindo para prevenir desconforto térmico, queimaduras solares e queimaduras pelo frio.
+3.	▌Os operadores não podem manter os cães ou os gatos em contentores.
+Os contentores podem, no entanto, ser utilizados para o isolamento de curta duração de determinados cães ou gatos, durante a participação em espetáculos de beleza, exposições e concursos, para cachorros ou gatinhos com capacidade de termorregulação reduzida e para cachorros ou gatinhos acompanhados das respetivas mães, desde que, para os cães ou gatos em causa, o stress seja minimizado e o sofrimento evitado, e que os animais sejam capazes de se levantarem, virarem e deitarem numa posição natural.
+4.	Os operadores não podem manter cães com mais de oito semanas exclusivamente em espaços interiores. Tais cães devem ter acesso diário a uma área ao ar livre, ou serem passeados diariamente, ▌de forma que permita exercício físico, exploração e socialização. A duração combinada mínima desse acesso diário ou passeio deve ser de uma hora no total. O operador só pode ficar isento destas exigências com base num parecer escrito de um médico veterinário.
+5.	Quando os gatos são mantidos em gatis, os operadores devem conceber e construir compartimentos individuais para permitir que os gatos circulem livremente e exibam o seu comportamento natural.
+6.	Os operadores de estabelecimentos de criação e estabelecimentos de venda asseguram ▌que nas áreas interiores onde são detidos cães ou gatos, existe uma zona termicamente neutra adequada que tenha em conta o seu tipo de pelagem, a idade, o tamanho, a raça e o estado de saúde.
+7.	Os operadores de estabelecimentos de criação e estabelecimentos de venda devem, sempre que necessário, utilizar sistemas de aquecimento ou de arrefecimento nos compartimentos interiores dos seus estabelecimentos, a fim de manter uma boa qualidade do ar e uma temperatura adequada e remover a humidade excessiva.
+8.	Os operadores asseguram que os cães ou gatos sejam expostos à luz e possam permanecer no escuro durante períodos suficientes e ininterruptos para manterem um ritmo circadiano normal.
+Para efeitos do primeiro parágrafo, entende-se por «luz» a luz natural, complementada, sempre que necessário, devido às condições climáticas e à posição geográfica de um Estado‑Membro, por luz artificial.
+9.	O n.º 2, alíneas a), b), c), f) e g), e os n.os 6, 7 e 8 não são aplicáveis nem aos cães de guarda de gado nem aos cães de pastoreio durante os períodos em que esses cães são usados para guardar ou pastorear no contexto da transumância sazonal a pé. O n.º 2, alínea f), não é aplicável a cães de guarda de gado durante os períodos em que estes cães são usados para treino.
+▌</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2639,22 +2578,25 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores devem assegurar que:
-(a) os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados e fêmeas em período peri-parto, são inspecionados com maior frequência;
-(b) os cães e gatos com bem-estar comprometido são, quando necessário, transferidos sem demora injustificada para uma área separada e, se necessário, recebem tratamento adequado;
-(c) quando a recuperação de um cão ou gato com bem-estar comprometido não seja alcançável e o animal experiencie dor ou sofrimento severo, um médico veterinário é consultado sem demora injustificada para decidir se o animal deve ser objeto de eutanásia para pôr termo ao seu sofrimento e, em caso afirmativo, para realizar a eutanásia com recurso a anestesia e analgesia;
-(d) são implementadas medidas de prevenção e controlo de parasitas externos e internos, bem como vacinações para prevenção de doenças comuns às quais os cães ou gatos são suscetíveis de estar expostos;
-(e) os enriquecimentos não apresentam risco significativo de lesões ou de contaminação biológica ou química, nem qualquer outro risco para a saúde.
-A alínea (a) não se aplica aos cães de guarda de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para fins de guarda ou treino.
-Os Estados-Membros podem conceder derrogações relativamente à alínea (c) em casos de emergência, quando não seja possível contactar um médico veterinário sem demora injustificada, desde que sejam estabelecidas regras nacionais que assegurem que:
-i) é tomada imediatamente uma ação qu